--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil / Porifera — afinidade incerta</t>
+          <t>Metazoário de afinidade incerta — icnofóssil (Oldhamia?) ou esponja (Choia?)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -18925,7 +18925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B332"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -22388,16 +22388,20 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="9" t="n"/>
+      <c r="B324" s="9" t="n"/>
+    </row>
     <row r="325">
-      <c r="A325" s="10" t="inlineStr">
+      <c r="A325" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B325" s="9" t="inlineStr"/>
+      <c r="B325" s="9" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="11" t="inlineStr">
+      <c r="A326" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -22409,7 +22413,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="11" t="inlineStr">
+      <c r="A327" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -22421,7 +22425,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="11" t="inlineStr">
+      <c r="A328" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -22433,7 +22437,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="11" t="inlineStr">
+      <c r="A329" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -22445,7 +22449,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="11" t="inlineStr">
+      <c r="A330" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -22457,7 +22461,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="11" t="inlineStr">
+      <c r="A331" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -22469,12 +22473,104 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="11" t="inlineStr">
+      <c r="A332" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B334" s="9" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B335" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B336" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B337" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B339" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B340" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B341" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$230</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S227"/>
+  <dimension ref="A1:S230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>224 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>227 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — pista de artrópode (locomoção tipo trilobita)</t>
+          <t>Icnofóssil — trilha de artrópode</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Espécimes raros e pequenos; associados a Diplichnites e Diplopodichnus; sugerem comunidade bentônica de artrópodes com comportamento de deslocamento similar a trilobitas</t>
+          <t>Classificação: pista de artrópode (locomoção tipo trilobita). Espécimes raros e pequenos; associados a Diplichnites e Diplopodichnus; sugerem comunidade bentônica de artrópodes com comportamento de deslocamento similar a trilobitas</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — escavação superficial de organismo vermiforme</t>
+          <t>Icnofóssil — escavação de organismo vermiforme</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Icnoespécie dominante na suíte de 'mineradores sob o tapete microbiano' (undermat miners), indicando pastadores de superfície (larvas de inseto, isópodes, anfípodes)</t>
+          <t>Classificação: escavação superficial de organismo vermiforme. Icnoespécie dominante na suíte de 'mineradores sob o tapete microbiano' (undermat miners), indicando pastadores de superfície (larvas de inseto, isópodes, anfípodes)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — pista de artrópode (isópode/anostraca)</t>
+          <t>Icnofóssil — trilha de artrópode</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Espécimes originalmente descritos como Isopodichnus por Marques-Toigo et al. (1989) foram posteriormente colocados em sinonímia com Cruziana cf. problematica por revisão de Balistieri et al. (2002)</t>
+          <t>Classificação: pista de artrópode (isópode/anostraca). Espécimes originalmente descritos como Isopodichnus por Marques-Toigo et al. (1989) foram posteriormente colocados em sinonímia com Cruziana cf. problematica por revisão de Balistieri et al. (2002)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — pista de artrópode (possível crustáceo)</t>
+          <t>Icnofóssil — trilha de artrópode</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Primeira ocorrência do icnogênero Pterichnus no Brasil e a mais antiga registrada no mundo; reavaliação do material originalmente descrito como o anelídeo 'Oliveirania santa catharinae' por Maury (1927); os corpos fósseis atribuídos a anelídeo foram reinterpretados como pseudofósseis de origem inorgânica, mas a pista associada é icnofóssil genuíno</t>
+          <t>Classificação: pista de artrópode (possível crustáceo). Primeira ocorrência do icnogênero Pterichnus no Brasil e a mais antiga registrada no mundo; reavaliação do material originalmente descrito como o anelídeo 'Oliveirania santa catharinae' por Maury (1927); os corpos fósseis atribuídos a anelídeo foram reinterpretados como pseudofósseis de origem inorgânica, mas a pista associada é icnofóssil genuíno</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — esponja marinha</t>
+          <t>Invertebrado — esponja</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Citados como integrantes da biota do Campáleo</t>
+          <t>Classificação: esponja marinha. Citados como integrantes da biota do Campáleo</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — conodonto</t>
+          <t>Microfóssil — conodonte</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Conhecidos desde 1908; 5–6 espécies estimadas; importantes para bioestratigrafia e datação</t>
+          <t>Classificação: conodonto. Conhecidos desde 1908; 5–6 espécies estimadas; importantes para bioestratigrafia e datação</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — molusco gastrópode</t>
+          <t>Invertebrado — gastrópode</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Registro raro de gastrópode na biota do Folhelho Lontras</t>
+          <t>Classificação: molusco gastrópode. Registro raro de gastrópode na biota do Folhelho Lontras</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Invertebrado — esponja hexactinelídea (vítrea)</t>
+          <t>Invertebrado — esponja</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil</t>
+          <t>Classificação: esponja hexactinelídea (vítrea). PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — escavação de bioerosão em concha</t>
+          <t>Icnofóssil — bioerosão em concha</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas</t>
+          <t>Classificação: escavação de bioerosão em concha. Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — molusco gastrópode</t>
+          <t>Invertebrado — gastrópode</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>Gastrópode subordinado na tafocenose, dominada por bivalves, de Taió</t>
+          <t>Classificação: molusco gastrópode. Gastrópode subordinado na tafocenose, dominada por bivalves, de Taió</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — equinodermas (estrela-do-mar e ofiuroide)</t>
+          <t>Invertebrado — equinoderma</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>Registro raro de equinodermas paleozoicos no Brasil; componentes subordinados da tafocenose de Taió</t>
+          <t>Classificação: equinodermas (estrela-do-mar e ofiuroide). Registro raro de equinodermas paleozoicos no Brasil; componentes subordinados da tafocenose de Taió</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — bioerosão em conchas de Heteropecten catharinae</t>
+          <t>Icnofóssil — bioerosão em concha</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>Traços de bioerosão (perfuração e escavação) registrados especificamente nas valvas do bivalve Heteropecten catharinae</t>
+          <t>Classificação: bioerosão em conchas de Heteropecten catharinae. Traços de bioerosão (perfuração e escavação) registrados especificamente nas valvas do bivalve Heteropecten catharinae</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Flora — sementes (Cordaitophyta)</t>
+          <t>Flora — semente</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="K169" s="7" t="inlineStr">
         <is>
-          <t>Associação de sementes mal preservadas, com raros fragmentos vegetais não identificáveis. Taió era conhecida por suas exposições de depósitos MARINHOS, com pectinídeos e equinodermas do Membro Paraguaçu. O achado de níveis com restos vegetais na BASE do mesmo membro, próximo aos afloramentos já conhecidos, ampliou o registro fossilífero local e ajuda a entender a evolução dos paleoambientes deposicionais nesta porção da bacia. O material paleobotânico de Taió provém de três localidades distintas: afloramentos Bruno Peiker, Clube Caça e Tiro e Igreja.</t>
+          <t>Classificação: sementes (Cordaitophyta). Associação de sementes mal preservadas, com raros fragmentos vegetais não identificáveis. Taió era conhecida por suas exposições de depósitos MARINHOS, com pectinídeos e equinodermas do Membro Paraguaçu. O achado de níveis com restos vegetais na BASE do mesmo membro, próximo aos afloramentos já conhecidos, ampliou o registro fossilífero local e ajuda a entender a evolução dos paleoambientes deposicionais nesta porção da bacia. O material paleobotânico de Taió provém de três localidades distintas: afloramentos Bruno Peiker, Clube Caça e Tiro e Igreja.</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr">
@@ -15886,670 +15886,678 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
+          <t>Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Rio Bonito, Mb. Siderópolis / Grupo Guatá — camada de carvão Barro Branco</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Carvão vegetal fóssil (macro-charcoal) de gimnospermas</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>Flora — carvão vegetal fóssil</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Porongos, Lauro Müller, SC (28°25'21,4"S, 49°26'24,0"W, coordenada publicada)</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>Benicio, J.R.W., Jasper, A., Spiekermann, R., Garavaglia, L., Pires-Oliveira, E.F., Machado, N.T.G. &amp; Uhl, D. (2019) — "Recurrent palaeo-wildfires in a Cisuralian coal seam: A palaeobotanical view on high-inertinite coals from the Lower Permian of the Paraná Basin, Brazil", PLoS ONE 14(3):e0213854</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>Univates; Senckenberg (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t>ca. 290–283 Ma (Artinskiano)</t>
+        </is>
+      </c>
+      <c r="K181" s="7" t="inlineStr">
+        <is>
+          <t>Primeira análise detalhada de carvão vegetal fóssil (macro-charcoal) da camada Barro Branco. O carvão aparece nos SEIS níveis carbonosos da sucessão de 2,85 m, o que confirma INCÊNDIOS RECORRENTES durante a formação da turfa. Os dados paleobotânicos e petrológicos indicam vegetação dominada por gimnospermas submetida repetidamente ao fogo, e reforçam a hipótese de que as turfeiras gondwânicas do Cisuraliano eram sistemas de fogo frequente.</t>
+        </is>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0213854</t>
+        </is>
+      </c>
+      <c r="M181" s="7" t="inlineStr"/>
+      <c r="N181" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="O181" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Porongos (Lauro Müller)</t>
+        </is>
+      </c>
+      <c r="P181" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Rio Bonito</t>
+        </is>
+      </c>
+      <c r="Q181" s="6" t="n">
+        <v>-28.4226</v>
+      </c>
+      <c r="R181" s="6" t="n">
+        <v>-49.44</v>
+      </c>
+      <c r="S181" s="6" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0213854</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Fm. Rio Bonito, Mb. Siderópolis / Grupo Guatá — nível acima da camada de carvão Bonito</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Brasilodendron pedroanum (Carruthers) Chaloner, Leistikow &amp; Hill</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Flora — Lycopodiopsida (licófita)</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>Mina Bonito I, bacia carbonífera de Santa Catarina (município não informado na fonte consultada)</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>Manfroi, J., Jasper, A., Guerra-Sommer, M. &amp; Uhl, D. (2012) — "Sub-arborescent lycophytes in coal-bearing strata from the Artinskian (Early Permian/Cisuralian) of the Santa Catarina coalfield (Paraná Basin, SC, Brazil)", Revista Brasileira de Paleontologia 15(2):135–140</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>Univates; UFRGS; Senckenberg (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>Artinskiano (Permiano Inferior)</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="inlineStr">
+        <is>
+          <t>Fragmentos de caule comprimidos de licófitas subarborescentes, preservados como moldes, de um nível clástico sobreposto à camada de carvão Bonito, na mina Bonito I. Os autores interpretam as plantas com esse tipo de almofada foliar como componente importante das associações formadoras de turfa costeira do Permiano Inferior, e como contribuintes relevantes para a biomassa original dos carvões. RESSALVA: a fonte consultada não informa o município da mina; o registro usa a coordenada regional da bacia carbonífera.</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sbpbrasil.org/revista/edicoes/15_2/RBP_02_Manfroi_et_al_Final.pdf</t>
+        </is>
+      </c>
+      <c r="M182" s="5" t="inlineStr"/>
+      <c r="N182" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>Paleoflora Siderópolis (região carbonífera)</t>
+        </is>
+      </c>
+      <c r="P182" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Rio Bonito</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="n">
+        <v>-28.595</v>
+      </c>
+      <c r="R182" s="4" t="n">
+        <v>-49.43</v>
+      </c>
+      <c r="S182" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2012.2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C183" s="7" t="inlineStr">
         <is>
           <t>Krauselcladus canoinhensis Yoshida emend. Fanton et al.</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>Flora — Coniferophyta (conífera)</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
+      <c r="F183" s="7" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G181" s="6" t="inlineStr">
+      <c r="G183" s="6" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H181" s="7" t="inlineStr">
+      <c r="H183" s="7" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
+      <c r="I183" s="6" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J181" s="6" t="inlineStr">
+      <c r="J183" s="6" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K181" s="7" t="inlineStr">
-        <is>
-          <t>ÚNICA localidade de ocorrência do gênero em toda a Bacia do Paraná, e única conífera formalmente conhecida do Guadalupiano da porção gondwânica brasileira. Ramos estéreis com quatro ordens de ramificação, cutícula excepcionalmente preservada — o que permitiu análise anatômica da epiderme. Cutículas grossas, estômatos afundados e ductos resiníferos são adaptações xeromórficas, coerentes com o clima seco interpretado para a Fm. Teresina. Fanton et al. (2006) sinonimizaram K. catarinensis Yoshida em K. canoinhensis. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
-        </is>
-      </c>
-      <c r="L181" s="7" t="inlineStr">
+      <c r="K183" s="7" t="inlineStr">
+        <is>
+          <t>Localidade-tipo e, até 2024, ÚNICA localidade conhecida do gênero em toda a Bacia do Paraná (nova ocorrência, em identificação preliminar, em Major Vieira — registro nº 195), e única conífera formalmente conhecida do Guadalupiano da porção gondwânica brasileira. Ramos estéreis com quatro ordens de ramificação, cutícula excepcionalmente preservada — o que permitiu análise anatômica da epiderme. Cutículas grossas, estômatos afundados e ductos resiníferos são adaptações xeromórficas, coerentes com o clima seco interpretado para a Fm. Teresina. Fanton et al. (2006) sinonimizaram K. catarinensis Yoshida em K. canoinhensis. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
+        </is>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M181" s="7" t="inlineStr"/>
-      <c r="N181" s="6" t="n">
+      <c r="M183" s="7" t="inlineStr"/>
+      <c r="N183" s="6" t="n">
         <v>159</v>
       </c>
-      <c r="O181" s="6" t="inlineStr">
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas</t>
         </is>
       </c>
-      <c r="P181" s="6" t="inlineStr">
+      <c r="P183" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
-      <c r="Q181" s="6" t="n">
+      <c r="Q183" s="6" t="n">
         <v>-26.19994</v>
       </c>
-      <c r="R181" s="6" t="n">
+      <c r="R183" s="6" t="n">
         <v>-50.433</v>
       </c>
-      <c r="S181" s="6" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
+      <c r="S183" s="6" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
         <is>
           <t>Pinzonella neotropica</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D184" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="E184" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G182" s="4" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="H184" s="5" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr">
+      <c r="I184" s="4" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J182" s="4" t="inlineStr">
+      <c r="J184" s="4" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K182" s="5" t="inlineStr">
+      <c r="K184" s="5" t="inlineStr">
         <is>
           <t>Compõe coquina na porção superior do afloramento, misturada a micrófilos permineralizados. A "Assembleia Pinzonella neotropica" é referência cronoestratigráfica para o Neopermiano da Bacia do Paraná. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
-      <c r="L182" s="5" t="inlineStr">
+      <c r="L184" s="5" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M182" s="5" t="inlineStr"/>
-      <c r="N182" s="4" t="n">
+      <c r="M184" s="5" t="inlineStr"/>
+      <c r="N184" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="O182" s="4" t="inlineStr">
+      <c r="O184" s="4" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas</t>
         </is>
       </c>
-      <c r="P182" s="4" t="inlineStr">
+      <c r="P184" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
-      <c r="Q182" s="4" t="n">
+      <c r="Q184" s="4" t="n">
         <v>-26.19994</v>
       </c>
-      <c r="R182" s="4" t="n">
+      <c r="R184" s="4" t="n">
         <v>-50.433</v>
       </c>
-      <c r="S182" s="4" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="6" t="inlineStr">
+      <c r="S184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
         <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C183" s="7" t="inlineStr">
+      <c r="C185" s="7" t="inlineStr">
         <is>
           <t>cf. Jacquesia elongata</t>
         </is>
       </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G183" s="6" t="inlineStr">
+      <c r="G185" s="6" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H183" s="7" t="inlineStr">
+      <c r="H185" s="7" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I183" s="6" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J183" s="6" t="inlineStr">
+      <c r="J185" s="6" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K183" s="7" t="inlineStr">
+      <c r="K185" s="7" t="inlineStr">
         <is>
           <t>Bivalve associado a Pinzonella neotropica na coquina do afloramento. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
-      <c r="L183" s="7" t="inlineStr">
+      <c r="L185" s="7" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M183" s="7" t="inlineStr"/>
-      <c r="N183" s="6" t="n">
+      <c r="M185" s="7" t="inlineStr"/>
+      <c r="N185" s="6" t="n">
         <v>161</v>
       </c>
-      <c r="O183" s="6" t="inlineStr">
+      <c r="O185" s="6" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas</t>
         </is>
       </c>
-      <c r="P183" s="6" t="inlineStr">
+      <c r="P185" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
-      <c r="Q183" s="6" t="n">
+      <c r="Q185" s="6" t="n">
         <v>-26.19994</v>
       </c>
-      <c r="R183" s="6" t="n">
+      <c r="R185" s="6" t="n">
         <v>-50.433</v>
       </c>
-      <c r="S183" s="6" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
+      <c r="S185" s="6" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>?Lycopodiopsis derbyi (caules de licófita)</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>Flora — Lycopodiopsida (licófita)</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
+      <c r="E186" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="G186" s="4" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr">
+      <c r="I186" s="4" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J184" s="4" t="inlineStr">
+      <c r="J186" s="4" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K184" s="5" t="inlineStr">
+      <c r="K186" s="5" t="inlineStr">
         <is>
           <t>Raros caules de licófita permineralizados por sílica, junto à coquina de bivalves. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
-      <c r="L184" s="5" t="inlineStr">
+      <c r="L186" s="5" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M184" s="5" t="inlineStr"/>
-      <c r="N184" s="4" t="n">
+      <c r="M186" s="5" t="inlineStr"/>
+      <c r="N186" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="O184" s="4" t="inlineStr">
+      <c r="O186" s="4" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas</t>
         </is>
       </c>
-      <c r="P184" s="4" t="inlineStr">
+      <c r="P186" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
-      <c r="Q184" s="4" t="n">
+      <c r="Q186" s="4" t="n">
         <v>-26.19994</v>
       </c>
-      <c r="R184" s="4" t="n">
+      <c r="R186" s="4" t="n">
         <v>-50.433</v>
       </c>
-      <c r="S184" s="4" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+      <c r="S186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>Micrófilos permineralizados (indet.)</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>Flora — micrófilos permineralizados</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G185" s="6" t="inlineStr">
+      <c r="G187" s="6" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J185" s="6" t="inlineStr">
+      <c r="J187" s="6" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K185" s="7" t="inlineStr">
+      <c r="K187" s="7" t="inlineStr">
         <is>
           <t>Micrófilos abundantes, permineralizados por sílica, excepcionalmente misturados às conchas de bivalves — associação rara entre restos vegetais e fauna marinha rasa. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
-      <c r="L185" s="7" t="inlineStr">
+      <c r="L187" s="7" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M185" s="7" t="inlineStr"/>
-      <c r="N185" s="6" t="n">
+      <c r="M187" s="7" t="inlineStr"/>
+      <c r="N187" s="6" t="n">
         <v>163</v>
       </c>
-      <c r="O185" s="6" t="inlineStr">
+      <c r="O187" s="6" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas</t>
         </is>
       </c>
-      <c r="P185" s="6" t="inlineStr">
+      <c r="P187" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
-      <c r="Q185" s="6" t="n">
+      <c r="Q187" s="6" t="n">
         <v>-26.19994</v>
       </c>
-      <c r="R185" s="6" t="n">
+      <c r="R187" s="6" t="n">
         <v>-50.433</v>
       </c>
-      <c r="S185" s="6" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="inlineStr">
+      <c r="S187" s="6" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B188" s="4" t="inlineStr">
         <is>
           <t>Fm. Teresina / Grupo Passa Dois (porção superior)</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
         <is>
           <t>Actinopterygii indet. (dentes e escamas em bone beds)</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
+      <c r="E188" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
         <is>
           <t>Afloramento de Canoinhas, km 242 da BR-280, 6 km a sudoeste de Canoinhas, SC</t>
         </is>
       </c>
-      <c r="G186" s="4" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>Material de referência das coleções UNICAMP / UNESP-Rio Claro / IGc-USP</t>
         </is>
       </c>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>Fanton, J., Rohn, R., Ricardi-Branco, F. &amp; Rösler, O. (2009) — SIGEP, Sítio 126, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2:381–388</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr">
+      <c r="I188" s="4" t="inlineStr">
         <is>
           <t>UNICAMP; UNESP-Rio Claro; IGc-USP</t>
         </is>
       </c>
-      <c r="J186" s="4" t="inlineStr">
+      <c r="J188" s="4" t="inlineStr">
         <is>
           <t>ca. 273–265 Ma (Guadalupiano inferior, Roadiano)</t>
         </is>
       </c>
-      <c r="K186" s="5" t="inlineStr">
+      <c r="K188" s="5" t="inlineStr">
         <is>
           <t>Classificação: peixe actinopterígio. Dentes e escamas de peixes concentrados em bone beds na porção média da exposição norte, associados a diques clásticos possivelmente resultantes de abalos sísmicos permianos. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
-      <c r="L186" s="5" t="inlineStr">
+      <c r="L188" s="5" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio126/sitio126.pdf
 https://www.sbpbrasil.org/revista/edicoes/9_2/RBP9-2-fanton.pdf</t>
         </is>
       </c>
-      <c r="M186" s="5" t="inlineStr"/>
-      <c r="N186" s="4" t="n">
-        <v>164</v>
-      </c>
-      <c r="O186" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento de Canoinhas</t>
-        </is>
-      </c>
-      <c r="P186" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Teresina</t>
-        </is>
-      </c>
-      <c r="Q186" s="4" t="n">
-        <v>-26.19994</v>
-      </c>
-      <c r="R186" s="4" t="n">
-        <v>-50.433</v>
-      </c>
-      <c r="S186" s="4" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Médio (Guadalupiano)</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>Fm. Palermo / Grupo Guatá</t>
-        </is>
-      </c>
-      <c r="C187" s="7" t="inlineStr">
-        <is>
-          <t>Dadoxylon sp. (troncos fósseis silicificados)</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t>Flora — lenho fóssil (Gymnospermopsida)</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1 (cota 400 m)</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr">
-        <is>
-          <t>Não informado na fonte consultada</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
-        </is>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>CPRM — Serviço Geológico do Brasil</t>
-        </is>
-      </c>
-      <c r="J187" s="6" t="inlineStr">
-        <is>
-          <t>ca. 279–265 Ma (Kunguriano–base do Kazaniano)</t>
-        </is>
-      </c>
-      <c r="K187" s="7" t="inlineStr">
-        <is>
-          <t>Principal elemento fossilífero da Fm. Palermo, unidade definida por White (1908) como "schistos do Palermo" a partir de afloramentos do sudeste catarinense — é na região carbonífera de SC que ela aparece com as feições mais típicas. Troncos silicificados frequentes, associados a abundantes palinomorfos. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
-        </is>
-      </c>
-      <c r="L187" s="7" t="inlineStr">
-        <is>
-          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
-        </is>
-      </c>
-      <c r="M187" s="7" t="inlineStr"/>
-      <c r="N187" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="O187" s="6" t="inlineStr">
-        <is>
-          <t>Coluna White (Serra do Rio do Rastro)</t>
-        </is>
-      </c>
-      <c r="P187" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Palermo</t>
-        </is>
-      </c>
-      <c r="Q187" s="6" t="n">
-        <v>-28.3889</v>
-      </c>
-      <c r="R187" s="6" t="n">
-        <v>-49.4644</v>
-      </c>
-      <c r="S187" s="6" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Médio (Guadalupiano)</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Fm. Palermo / Grupo Guatá</t>
-        </is>
-      </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>Pelecypoda indet. (Fm. Palermo)</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — bivalve</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>Não informado na fonte consultada</t>
-        </is>
-      </c>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t>CPRM — Serviço Geológico do Brasil</t>
-        </is>
-      </c>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>ca. 279–265 Ma</t>
-        </is>
-      </c>
-      <c r="K188" s="5" t="inlineStr">
-        <is>
-          <t>Pelecípodes localizados em Santa Catarina por Gordon Jr. (1947). Sustentam a interpretação de ambiente marinho transgressivo de plataforma, sob influência de ondas e marés, recobrindo o sistema deltaico-lagunar da Fm. Rio Bonito. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
-        </is>
-      </c>
-      <c r="L188" s="5" t="inlineStr">
-        <is>
-          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
-        </is>
-      </c>
       <c r="M188" s="5" t="inlineStr"/>
       <c r="N188" s="4" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>Coluna White (Serra do Rio do Rastro)</t>
+          <t>Afloramento de Canoinhas</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Palermo</t>
+          <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n">
-        <v>-28.3889</v>
+        <v>-26.19994</v>
       </c>
       <c r="R188" s="4" t="n">
-        <v>-49.4644</v>
+        <v>-50.433</v>
       </c>
       <c r="S188" s="4" t="inlineStr"/>
     </row>
@@ -16566,12 +16574,12 @@
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>Palinoflora da Fm. Palermo (esporomorfos)</t>
+          <t>Dadoxylon sp. (troncos fósseis silicificados)</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — palinomorfos</t>
+          <t>Flora — lenho fóssil (Gymnospermopsida)</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -16581,7 +16589,7 @@
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1 (cota 400 m)</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr">
@@ -16601,12 +16609,12 @@
       </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>ca. 279–265 Ma</t>
+          <t>ca. 279–265 Ma (Kunguriano–base do Kazaniano)</t>
         </is>
       </c>
       <c r="K189" s="7" t="inlineStr">
         <is>
-          <t>Esporomorfos abundantes, base do posicionamento cronoestratigráfico da unidade entre o Kunguriano e a base do Kazaniano. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Principal elemento fossilífero da Fm. Palermo, unidade definida por White (1908) como "schistos do Palermo" a partir de afloramentos do sudeste catarinense — é na região carbonífera de SC que ela aparece com as feições mais típicas. Troncos silicificados frequentes, associados a abundantes palinomorfos. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L189" s="7" t="inlineStr">
@@ -16616,7 +16624,7 @@
       </c>
       <c r="M189" s="7" t="inlineStr"/>
       <c r="N189" s="6" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O189" s="6" t="inlineStr">
         <is>
@@ -16649,12 +16657,12 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>"Loxomma" sp. (tetrápode — identificação a revisar)</t>
+          <t>Pelecypoda indet. (Fm. Palermo)</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Vertebrado — tetrápode (anfíbio?)</t>
+          <t>Invertebrado — bivalve</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -16664,7 +16672,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Região de Criciúma</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -16689,7 +16697,7 @@
       </c>
       <c r="K190" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência do gênero relatada por Putzer (1954) na região de Criciúma, e assim registrada no capítulo SIGEP. ATENÇÃO: Loxomma é um bafetídeo do Carbonífero da Europa, e a atribuição de material permiano brasileiro a esse gênero é taxonomicamente improvável — o registro carece de revisão à luz da sistemática atual. Mantido no catálogo por constar da literatura, mas NÃO deve ser tomado como identificação válida. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Pelecípodes localizados em Santa Catarina por Gordon Jr. (1947). Sustentam a interpretação de ambiente marinho transgressivo de plataforma, sob influência de ondas e marés, recobrindo o sistema deltaico-lagunar da Fm. Rio Bonito. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L190" s="5" t="inlineStr">
@@ -16699,11 +16707,11 @@
       </c>
       <c r="M190" s="5" t="inlineStr"/>
       <c r="N190" s="4" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>Região de Criciúma (Fm. Palermo)</t>
+          <t>Coluna White (Serra do Rio do Rastro)</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
@@ -16712,10 +16720,10 @@
         </is>
       </c>
       <c r="Q190" s="4" t="n">
-        <v>-28.6775</v>
+        <v>-28.3889</v>
       </c>
       <c r="R190" s="4" t="n">
-        <v>-49.3697</v>
+        <v>-49.4644</v>
       </c>
       <c r="S190" s="4" t="inlineStr"/>
     </row>
@@ -16727,233 +16735,233 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
+          <t>Fm. Palermo / Grupo Guatá</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>Palinoflora da Fm. Palermo (esporomorfos)</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 6, km 8,1</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>CPRM — Serviço Geológico do Brasil</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>ca. 279–265 Ma</t>
+        </is>
+      </c>
+      <c r="K191" s="7" t="inlineStr">
+        <is>
+          <t>Esporomorfos abundantes, base do posicionamento cronoestratigráfico da unidade entre o Kunguriano e a base do Kazaniano. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+        </is>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
+        </is>
+      </c>
+      <c r="M191" s="7" t="inlineStr"/>
+      <c r="N191" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="O191" s="6" t="inlineStr">
+        <is>
+          <t>Coluna White (Serra do Rio do Rastro)</t>
+        </is>
+      </c>
+      <c r="P191" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Palermo</t>
+        </is>
+      </c>
+      <c r="Q191" s="6" t="n">
+        <v>-28.3889</v>
+      </c>
+      <c r="R191" s="6" t="n">
+        <v>-49.4644</v>
+      </c>
+      <c r="S191" s="6" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Permiano Médio (Guadalupiano)</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Fm. Palermo / Grupo Guatá</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>"Loxomma" sp. (tetrápode — identificação a revisar)</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Vertebrado — tetrápode (anfíbio?)</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Região de Criciúma</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>CPRM — Serviço Geológico do Brasil</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>ca. 279–265 Ma</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>Ocorrência do gênero relatada por Putzer (1954) na região de Criciúma, e assim registrada no capítulo SIGEP. ATENÇÃO: Loxomma é um bafetídeo do Carbonífero da Europa, e a atribuição de material permiano brasileiro a esse gênero é taxonomicamente improvável — o registro carece de revisão à luz da sistemática atual. Mantido no catálogo por constar da literatura, mas NÃO deve ser tomado como identificação válida. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
+        </is>
+      </c>
+      <c r="M192" s="5" t="inlineStr"/>
+      <c r="N192" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="O192" s="4" t="inlineStr">
+        <is>
+          <t>Região de Criciúma (Fm. Palermo)</t>
+        </is>
+      </c>
+      <c r="P192" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Palermo</t>
+        </is>
+      </c>
+      <c r="Q192" s="4" t="n">
+        <v>-28.6775</v>
+      </c>
+      <c r="R192" s="4" t="n">
+        <v>-49.3697</v>
+      </c>
+      <c r="S192" s="4" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>Permiano Médio (Guadalupiano)</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
           <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
         </is>
       </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="C193" s="7" t="inlineStr">
         <is>
           <t>Parapytanga catarinensis Strapasson, Pinheiro &amp; Soares, 2015</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — anfíbio temnospôndilo (Stereospondylomorpha)</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — anfíbio</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
         <is>
           <t>UFRGS-PV-0355-P (holótipo)</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>Serra do Espigão, região de Santa Cecília, SC (coordenada aproximada da localidade)</t>
         </is>
       </c>
-      <c r="G191" s="6" t="inlineStr">
+      <c r="G193" s="6" t="inlineStr">
         <is>
           <t>UFRGS — Depto. de Paleontologia e Estratigrafia (Porto Alegre, RS)</t>
         </is>
       </c>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>Strapasson, A., Pinheiro, F.L. &amp; Soares, M.B. (2015) — Acta Palaeontologica Polonica 60(4):843–855</t>
         </is>
       </c>
-      <c r="I191" s="6" t="inlineStr">
+      <c r="I193" s="6" t="inlineStr">
         <is>
           <t>UFRGS; UNIPAMPA</t>
         </is>
       </c>
-      <c r="J191" s="6" t="inlineStr">
+      <c r="J193" s="6" t="inlineStr">
         <is>
           <t>ca. 266–254 Ma (Wordiano–Wuchiapingiano)</t>
         </is>
       </c>
-      <c r="K191" s="7" t="inlineStr">
-        <is>
-          <t>O ÚNICO temnospôndilo formalmente nomeado de Santa Catarina, e um dos três descritos para toda a Fm. Rio do Rasto — os outros dois são Australerpeton cosgriffi (Serra do Cadeado, PR) e Bageherpeton longignathus (RS). Coletado em 1985 por equipe da UFRGS, mas só descrito em 2015. O material compreende elementos cranianos (região orbital, basicrânio, estapédio, hemimandíbula direita) e pós-cranianos (vértebras, costelas, cintura peitoral, fêmur direito e um conjunto de escamas). Difere dos rinesuquídeos pelo epipterigoide robusto e alongado e pelos bolsões musculares do parasfenoide mais profundos. De focinho curto e largo — ao contrário do focinho longo e delgado de Australerpeton e Bageherpeton. A análise filogenética o agrupa como táxon-irmão de Australerpeton, em posição transicional entre os temnospôndilos permianos da Plataforma Russa e os sul-africanos, sustentando uma conexão entre as faunas permianas do Brasil e do Leste Europeu. A Serra do Espigão é uma localidade fossilífera de tetrápodes inédita, que amplia geograficamente o registro da Fm. Rio do Rasto.</t>
-        </is>
-      </c>
-      <c r="L191" s="7" t="inlineStr">
+      <c r="K193" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: anfíbio temnospôndilo (Stereospondylomorpha). O ÚNICO temnospôndilo formalmente nomeado de Santa Catarina, e na época da descrição (2015), um dos três temnospôndilos conhecidos da Fm. Rio do Rasto — os outros dois são Australerpeton cosgriffi (Serra do Cadeado, PR) e Bageherpeton longignathus (RS). Coletado em 1985 por equipe da UFRGS, mas só descrito em 2015. O material compreende elementos cranianos (região orbital, basicrânio, estapédio, hemimandíbula direita) e pós-cranianos (vértebras, costelas, cintura peitoral, fêmur direito e um conjunto de escamas). Difere dos rinesuquídeos pelo epipterigoide robusto e alongado e pelos bolsões musculares do parasfenoide mais profundos. De focinho curto e largo — ao contrário do focinho longo e delgado de Australerpeton e Bageherpeton. A análise filogenética o agrupa como táxon-irmão de Australerpeton, em posição transicional entre os temnospôndilos permianos da Plataforma Russa e os sul-africanos, sustentando uma conexão entre as faunas permianas do Brasil e do Leste Europeu. A Serra do Espigão é uma localidade fossilífera de tetrápodes inédita, que amplia geograficamente o registro da Fm. Rio do Rasto.</t>
+        </is>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
         <is>
           <t>https://lume.ufrgs.br/handle/10183/132382
 https://www.lume.ufrgs.br/bitstream/handle/10183/132382/000915740.pdf?isAllowed=y&amp;sequence=1</t>
         </is>
       </c>
-      <c r="M191" s="7" t="inlineStr"/>
-      <c r="N191" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="O191" s="6" t="inlineStr">
-        <is>
-          <t>Serra do Espigão</t>
-        </is>
-      </c>
-      <c r="P191" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
-        </is>
-      </c>
-      <c r="Q191" s="6" t="n">
-        <v>-26.87</v>
-      </c>
-      <c r="R191" s="6" t="n">
-        <v>-50.45</v>
-      </c>
-      <c r="S191" s="6" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Médio (Guadalupiano)</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
-        </is>
-      </c>
-      <c r="C192" s="5" t="inlineStr">
-        <is>
-          <t>Fragmentos vegetais indet. (similares a Calamites sp. e Pecopteris sp.)</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>Flora — fragmentos vegetais</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento de Ponte Alta, Ponte Alta, SC</t>
-        </is>
-      </c>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>Laboratório de Geociências, Universidade Regional de Blumenau (FURB)</t>
-        </is>
-      </c>
-      <c r="H192" s="5" t="inlineStr">
-        <is>
-          <t>Nova localidade fossilífera da Formação Rio do Rasto (Guadalupiano/Lopingiano, Bacia do Paraná) no estado de Santa Catarina, Brasil (2017) — material coletado pelo Laboratório de Paleovertebrados da UFRGS, depositado no Laboratório de Geociências da FURB</t>
-        </is>
-      </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
-          <t>UFRGS — Lab. de Paleovertebrados; FURB</t>
-        </is>
-      </c>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>ca. 266–254 Ma (Wordiano–Wuchiapingiano)</t>
-        </is>
-      </c>
-      <c r="K192" s="5" t="inlineStr">
-        <is>
-          <t>Conjunto de 26 amostras — o componente mais abundante do afloramento. Afloramento descrito a partir de 58 amostras coletadas pelo Laboratório de Paleovertebrados da UFRGS em Ponte Alta, próximo a Otacílio Costa, e depositadas na coleção do Laboratório de Geociências da FURB. Amplia geograficamente o registro da Fm. Rio do Rasto em Santa Catarina, estado ainda pouco explorado quanto ao Permiano.</t>
-        </is>
-      </c>
-      <c r="L192" s="5" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
-        </is>
-      </c>
-      <c r="M192" s="5" t="inlineStr"/>
-      <c r="N192" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="O192" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento de Ponte Alta</t>
-        </is>
-      </c>
-      <c r="P192" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
-        </is>
-      </c>
-      <c r="Q192" s="4" t="n">
-        <v>-27.4839</v>
-      </c>
-      <c r="R192" s="4" t="n">
-        <v>-50.38</v>
-      </c>
-      <c r="S192" s="4" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Médio (Guadalupiano)</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
-        <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
-        </is>
-      </c>
-      <c r="C193" s="7" t="inlineStr">
-        <is>
-          <t>Conchostraca indet. (similares a Cyzicus sp. e Asmussia sp.)</t>
-        </is>
-      </c>
-      <c r="D193" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — conchostráceo</t>
-        </is>
-      </c>
-      <c r="E193" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento de Ponte Alta, Ponte Alta, SC</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr">
-        <is>
-          <t>Laboratório de Geociências, Universidade Regional de Blumenau (FURB)</t>
-        </is>
-      </c>
-      <c r="H193" s="7" t="inlineStr">
-        <is>
-          <t>Nova localidade fossilífera da Formação Rio do Rasto (Guadalupiano/Lopingiano, Bacia do Paraná) no estado de Santa Catarina, Brasil (2017) — material coletado pelo Laboratório de Paleovertebrados da UFRGS, depositado no Laboratório de Geociências da FURB</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>UFRGS — Lab. de Paleovertebrados; FURB</t>
-        </is>
-      </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>ca. 266–254 Ma (Wordiano–Wuchiapingiano)</t>
-        </is>
-      </c>
-      <c r="K193" s="7" t="inlineStr">
-        <is>
-          <t>16 amostras. Os autores registram que o material NÃO preserva caracteres diagnósticos suficientes para determinação genérica segura — a atribuição é por similaridade, não identificação formal. Afloramento descrito a partir de 58 amostras coletadas pelo Laboratório de Paleovertebrados da UFRGS em Ponte Alta, próximo a Otacílio Costa, e depositadas na coleção do Laboratório de Geociências da FURB. Amplia geograficamente o registro da Fm. Rio do Rasto em Santa Catarina, estado ainda pouco explorado quanto ao Permiano.</t>
-        </is>
-      </c>
-      <c r="L193" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
-        </is>
-      </c>
       <c r="M193" s="7" t="inlineStr"/>
       <c r="N193" s="6" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="O193" s="6" t="inlineStr">
         <is>
-          <t>Afloramento de Ponte Alta</t>
+          <t>Serra do Espigão</t>
         </is>
       </c>
       <c r="P193" s="6" t="inlineStr">
@@ -16962,10 +16970,10 @@
         </is>
       </c>
       <c r="Q193" s="6" t="n">
-        <v>-27.4839</v>
+        <v>-26.87</v>
       </c>
       <c r="R193" s="6" t="n">
-        <v>-50.38</v>
+        <v>-50.45</v>
       </c>
       <c r="S193" s="6" t="inlineStr"/>
     </row>
@@ -16977,17 +16985,17 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Fm. Teresina / Grupo Passa Dois</t>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>Krauselcladus canoinhensis — nova ocorrência (Major Vieira)</t>
+          <t>Fragmentos vegetais indet. (similares a Calamites sp. e Pecopteris sp.)</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Flora — Coniferophyta (conífera)</t>
+          <t>Flora — fragmentos vegetais</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -16997,65 +17005,65 @@
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>Interior do município de Major Vieira, SC (localidade precisa não divulgada)</t>
+          <t>Afloramento de Ponte Alta, Ponte Alta, SC</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Laboratório de Geociências, Universidade Regional de Blumenau (FURB)</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>Identificação pelo CENPALEO/UnC (Mafra), divulgada em agosto de 2024</t>
+          <t>Nova localidade fossilífera da Formação Rio do Rasto (Guadalupiano/Lopingiano, Bacia do Paraná) no estado de Santa Catarina, Brasil (2017) — material coletado pelo Laboratório de Paleovertebrados da UFRGS, depositado no Laboratório de Geociências da FURB</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>UFRGS — Lab. de Paleovertebrados; FURB</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>ca. 273–265 Ma (Guadalupiano)</t>
+          <t>ca. 266–254 Ma (Wordiano–Wuchiapingiano)</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr">
         <is>
-          <t>SEGUNDA localidade conhecida de Krauselcladus canoinhensis — gênero cuja ÚNICA ocorrência em toda a Bacia do Paraná é catarinense, descrito originalmente no Afloramento de Canoinhas (SIGEP 126). O espécime foi encontrado em 1º de maio de 2024 por participantes de uma caminhada religiosa e levado para análise. A nova localidade fica próxima a Canoinhas e amplia o entendimento da distribuição paleogeográfica da espécie. ATENÇÃO: a identificação foi feita pelo CENPALEO A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, e não a partir de exame direto do material; não foi localizada publicação científica formal sobre esta ocorrência, nem informação de tombamento ou depositário. A ocorrência do gênero em SC, contudo, é bem estabelecida na literatura (ver registro do Afloramento de Canoinhas).</t>
+          <t>Conjunto de 26 amostras — o componente mais abundante do afloramento. Afloramento descrito a partir de 58 amostras coletadas pelo Laboratório de Paleovertebrados da UFRGS em Ponte Alta, próximo a Otacílio Costa, e depositadas na coleção do Laboratório de Geociências da FURB. Amplia geograficamente o registro da Fm. Rio do Rasto em Santa Catarina, estado ainda pouco explorado quanto ao Permiano.</t>
         </is>
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>https://www.notisul.com.br/fossil-de-270-milhoes-de-anos-e-encontrado-em-sc/</t>
+          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
         </is>
       </c>
       <c r="M194" s="5" t="inlineStr"/>
       <c r="N194" s="4" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>Major Vieira (nova ocorrência de Krauselcladus)</t>
+          <t>Afloramento de Ponte Alta</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Teresina</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n">
-        <v>-26.3717</v>
+        <v>-27.4839</v>
       </c>
       <c r="R194" s="4" t="n">
-        <v>-50.3283</v>
+        <v>-50.38</v>
       </c>
       <c r="S194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>Permiano Superior</t>
+          <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -17065,12 +17073,12 @@
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Schizoneura gondwanensis Feistmantel, 1876</t>
+          <t>Conchostraca indet. (similares a Cyzicus sp. e Asmussia sp.)</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>Flora — Sphenopsida</t>
+          <t>Invertebrado — conchostráceo</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -17080,50 +17088,46 @@
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>13+ afloramentos no norte de SC e PR</t>
+          <t>Afloramento de Ponte Alta, Ponte Alta, SC</t>
         </is>
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>IGc-USP (São Paulo)</t>
+          <t>Laboratório de Geociências, Universidade Regional de Blumenau (FURB)</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>Rohn, R. &amp; Rösler, O. (1986) — "Schizoneura gondwanensis Feistmantel da Formação Rio do Rasto no estado do Paraná e no norte do estado de Santa Catarina", Boletim IG-USP, Série Científica, 17:5–14</t>
+          <t>Nova localidade fossilífera da Formação Rio do Rasto (Guadalupiano/Lopingiano, Bacia do Paraná) no estado de Santa Catarina, Brasil (2017) — material coletado pelo Laboratório de Paleovertebrados da UFRGS, depositado no Laboratório de Geociências da FURB</t>
         </is>
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t>IGc-USP</t>
+          <t>UFRGS — Lab. de Paleovertebrados; FURB</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>ca. 260–252 Ma</t>
+          <t>ca. 266–254 Ma (Wordiano–Wuchiapingiano)</t>
         </is>
       </c>
       <c r="K195" s="7" t="inlineStr">
         <is>
-          <t>Descrita em 13 novos afloramentos; detalhes de mesofilo e epiderme excepcionalmente preservados</t>
+          <t>16 amostras. Os autores registram que o material NÃO preserva caracteres diagnósticos suficientes para determinação genérica segura — a atribuição é por similaridade, não identificação formal. Afloramento descrito a partir de 58 amostras coletadas pelo Laboratório de Paleovertebrados da UFRGS em Ponte Alta, próximo a Otacílio Costa, e depositadas na coleção do Laboratório de Geociências da FURB. Amplia geograficamente o registro da Fm. Rio do Rasto em Santa Catarina, estado ainda pouco explorado quanto ao Permiano.</t>
         </is>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>https://revistas.usp.br/bigsc/en/article/view/45052 (Rohn &amp; Rösler 1986, Bol. IG-USP Sér. Cient.)</t>
-        </is>
-      </c>
-      <c r="M195" s="7" t="inlineStr">
-        <is>
-          <t>ROHN, R.; RÖSLER, O. 1986. Schizoneura gondwanensis Feistmantel da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina, Brasil. Boletim IG-USP. Série Científica, São Paulo, 17, 27–66. DOI: 10.11606/issn.2316-8986.v17i0p27-66 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsc/en/article/view/45052</t>
-        </is>
-      </c>
+          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
+        </is>
+      </c>
+      <c r="M195" s="7" t="inlineStr"/>
       <c r="N195" s="6" t="n">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="O195" s="6" t="inlineStr">
         <is>
-          <t>Afloramentos do norte de SC/PR</t>
+          <t>Afloramento de Ponte Alta</t>
         </is>
       </c>
       <c r="P195" s="6" t="inlineStr">
@@ -17132,32 +17136,32 @@
         </is>
       </c>
       <c r="Q195" s="6" t="n">
-        <v>-26.15</v>
+        <v>-27.4839</v>
       </c>
       <c r="R195" s="6" t="n">
-        <v>-49.9</v>
+        <v>-50.38</v>
       </c>
       <c r="S195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Permiano Superior</t>
+          <t>Permiano Médio (Guadalupiano)</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+          <t>Fm. Teresina / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Glossopteris riorastensis Rohn &amp; Rösler, 1989</t>
+          <t>Krauselcladus canoinhensis — nova ocorrência (Major Vieira)</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Flora — Gymnospermopsida</t>
+          <t>Flora — Coniferophyta (conífera)</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -17167,62 +17171,58 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Afloramentos do norte de SC e PR</t>
+          <t>Interior do município de Major Vieira, SC (localidade precisa não divulgada)</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>IGc-USP (São Paulo)</t>
+          <t>Não informado na fonte consultada</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>Rohn, R. &amp; Rösler, O. (1989) — "Novas ocorrências de Glossopteris na Formação Rio do Rasto em afloramentos do Paraná e de Santa Catarina", Boletim IG-USP, Publicação Especial</t>
+          <t>Identificação pelo CENPALEO/UnC (Mafra), divulgada em agosto de 2024</t>
         </is>
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>IGc-USP</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>ca. 260–252 Ma</t>
+          <t>ca. 273–265 Ma (Guadalupiano)</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
         <is>
-          <t>Uma das 10 espécies descritas em 20 novos afloramentos da Fm. Rio do Rasto em SC e PR</t>
+          <t>SEGUNDA localidade conhecida de Krauselcladus canoinhensis — gênero cuja ÚNICA ocorrência em toda a Bacia do Paraná é catarinense, descrito originalmente no Afloramento de Canoinhas (SIGEP 126). O espécime foi encontrado em 1º de maio de 2024 por participantes de uma caminhada religiosa e levado para análise. A nova localidade fica próxima a Canoinhas e amplia o entendimento da distribuição paleogeográfica da espécie. ATENÇÃO: a identificação foi feita pelo CENPALEO A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, e não a partir de exame direto do material; não foi localizada publicação científica formal sobre esta ocorrência, nem informação de tombamento ou depositário. A ocorrência do gênero em SC, contudo, é bem estabelecida na literatura (ver registro do Afloramento de Canoinhas).</t>
         </is>
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
-        </is>
-      </c>
-      <c r="M196" s="5" t="inlineStr">
-        <is>
-          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
-        </is>
-      </c>
+          <t>https://www.notisul.com.br/fossil-de-270-milhoes-de-anos-e-encontrado-em-sc/</t>
+        </is>
+      </c>
+      <c r="M196" s="5" t="inlineStr"/>
       <c r="N196" s="4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>Afloramentos do norte de SC/PR</t>
+          <t>Major Vieira (nova ocorrência de Krauselcladus)</t>
         </is>
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+          <t>Bacia do Paraná — Fm. Teresina</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n">
-        <v>-26.15</v>
+        <v>-26.3717</v>
       </c>
       <c r="R196" s="4" t="n">
-        <v>-49.9</v>
+        <v>-50.3283</v>
       </c>
       <c r="S196" s="4" t="inlineStr"/>
     </row>
@@ -17239,12 +17239,12 @@
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Glossopteris grafi Rohn &amp; Rösler, 1989</t>
+          <t>Schizoneura gondwanensis Feistmantel, 1876</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>Flora — Gymnospermopsida</t>
+          <t>Flora — Sphenopsida</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Afloramentos do norte de SC e PR</t>
+          <t>13+ afloramentos no norte de SC e PR</t>
         </is>
       </c>
       <c r="G197" s="6" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Rohn, R. &amp; Rösler, O. (1989) — "Novas ocorrências de Glossopteris na Formação Rio do Rasto em afloramentos do Paraná e de Santa Catarina", Boletim IG-USP, Publicação Especial</t>
+          <t>Rohn, R. &amp; Rösler, O. (1986) — "Schizoneura gondwanensis Feistmantel da Formação Rio do Rasto no estado do Paraná e no norte do estado de Santa Catarina", Boletim IG-USP, Série Científica, 17:5–14</t>
         </is>
       </c>
       <c r="I197" s="6" t="inlineStr">
@@ -17279,21 +17279,21 @@
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
-          <t>Espécie inédita descrita para a Fm. Rio do Rasto</t>
+          <t>Descrita em 13 novos afloramentos; detalhes de mesofilo e epiderme excepcionalmente preservados</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
+          <t>https://revistas.usp.br/bigsc/en/article/view/45052 (Rohn &amp; Rösler 1986, Bol. IG-USP Sér. Cient.)</t>
         </is>
       </c>
       <c r="M197" s="7" t="inlineStr">
         <is>
-          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
+          <t>ROHN, R.; RÖSLER, O. 1986. Schizoneura gondwanensis Feistmantel da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina, Brasil. Boletim IG-USP. Série Científica, São Paulo, 17, 27–66. DOI: 10.11606/issn.2316-8986.v17i0p27-66 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsc/en/article/view/45052</t>
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O197" s="6" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Glossopteris cf. G. indica / G. surangei (e outros morfotipos)</t>
+          <t>Glossopteris riorastensis Rohn &amp; Rösler, 1989</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>Total de 15 espécies de Glossopteris registradas para a formação em SC e PR</t>
+          <t>Uma das 10 espécies descritas em 20 novos afloramentos da Fm. Rio do Rasto em SC e PR</t>
         </is>
       </c>
       <c r="L198" s="5" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="N198" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -17408,17 +17408,17 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Grupo Passa Dois (limite Fm. Rio do Rasto / base Fm. Pirambóia)</t>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>Estheria sp. / Leaia sp. (filópodos)</t>
+          <t>Glossopteris grafi Rohn &amp; Rösler, 1989</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>Invertebrado — crustáceo conchostráceo (Branchiopoda)</t>
+          <t>Flora — Gymnospermopsida</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
@@ -17428,50 +17428,50 @@
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Entre Valões e Poço Preto, Lages, SC (estrada Lombo Alto–Lages, próx. km 65)</t>
+          <t>Afloramentos do norte de SC e PR</t>
         </is>
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>Coleção histórica não especificada na fonte consultada</t>
+          <t>IGc-USP (São Paulo)</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Reed, F.R.C. (citado em: Beurlen, K. — Breves Notícias Sobre a Geologia dos Estados do Paraná e Santa Catarina; trad. port. em SciELO)</t>
+          <t>Rohn, R. &amp; Rösler, O. (1989) — "Novas ocorrências de Glossopteris na Formação Rio do Rasto em afloramentos do Paraná e de Santa Catarina", Boletim IG-USP, Publicação Especial</t>
         </is>
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t>Não especificado na fonte consultada</t>
+          <t>IGc-USP</t>
         </is>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>ca. 259–252 Ma</t>
+          <t>ca. 260–252 Ma</t>
         </is>
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
-          <t>Filópodos (conchostráceos) permianos descritos por F.R. Cowper Reed em horizontes vermelhos e argilosos entre Valões e Poço Preto, Lages, SC; a fonte ressalva explicitamente que estes horizontes NÃO pertencem às camadas Estrada Nova, situando-se no contexto Rio do Rasto/Pirambóia</t>
+          <t>Espécie inédita descrita para a Fm. Rio do Rasto</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>https://scielo.br/scielo.php?pid=S1516-89132001000500010&amp;script=sci_arttext (tradução de Beurlen 1957, citando Reed)</t>
+          <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
         </is>
       </c>
       <c r="M199" s="7" t="inlineStr">
         <is>
-          <t>REED, F.R.C. 1930. Fossil fauna from Permian beds in the State of Santa Catharina, Brazil. Geological Magazine, 67(793), 310–322. DOI: 10.1017/S0016756800100968 [Fonte primária]. Citado via: BEURLEN, K. 1957. Breves notícias sobre a geologia dos estados do Paraná e Santa Catarina. Ciência e Cultura, 9(1), 12–24. [Fonte secundária — tradução / nota geológica]</t>
+          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="O199" s="6" t="inlineStr">
         <is>
-          <t>Entre Valões e Poço Preto</t>
+          <t>Afloramentos do norte de SC/PR</t>
         </is>
       </c>
       <c r="P199" s="6" t="inlineStr">
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="Q199" s="6" t="n">
-        <v>-27.8167</v>
+        <v>-26.15</v>
       </c>
       <c r="R199" s="6" t="n">
-        <v>-50.3264</v>
+        <v>-49.9</v>
       </c>
       <c r="S199" s="6" t="inlineStr"/>
     </row>
@@ -17495,17 +17495,17 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Fm. Serra Alta / Grupo Passa Dois</t>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Restos de peixes indet. (Fm. Serra Alta)</t>
+          <t>Glossopteris cf. G. indica / G. surangei (e outros morfotipos)</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Vertebrado — peixes</t>
+          <t>Flora — Gymnospermopsida</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -17515,58 +17515,62 @@
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6 (cota 520 m)</t>
+          <t>Afloramentos do norte de SC e PR</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>IGc-USP (São Paulo)</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
         <is>
-          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
+          <t>Rohn, R. &amp; Rösler, O. (1989) — "Novas ocorrências de Glossopteris na Formação Rio do Rasto em afloramentos do Paraná e de Santa Catarina", Boletim IG-USP, Publicação Especial</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>CPRM — Serviço Geológico do Brasil</t>
+          <t>IGc-USP</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
-          <t>ca. 265–259 Ma (topo do Kazaniano–base do Tatariano)</t>
+          <t>ca. 260–252 Ma</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe. Espessa sequência de folhelhos e siltitos cinza-escuros com laminação plano-paralela e concreções calcárias, depositada em águas calmas abaixo do nível de ação das ondas. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Total de 15 espécies de Glossopteris registradas para a formação em SC e PR</t>
         </is>
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
-        </is>
-      </c>
-      <c r="M200" s="5" t="inlineStr"/>
+          <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
+        </is>
+      </c>
+      <c r="M200" s="5" t="inlineStr">
+        <is>
+          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
+        </is>
+      </c>
       <c r="N200" s="4" t="n">
-        <v>169</v>
+        <v>36</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
-          <t>Coluna White (Serra do Rio do Rastro)</t>
+          <t>Afloramentos do norte de SC/PR</t>
         </is>
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Serra Alta</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n">
-        <v>-28.3889</v>
+        <v>-26.15</v>
       </c>
       <c r="R200" s="4" t="n">
-        <v>-49.4644</v>
+        <v>-49.9</v>
       </c>
       <c r="S200" s="4" t="inlineStr"/>
     </row>
@@ -17578,17 +17582,17 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Fm. Serra Alta / Grupo Passa Dois</t>
+          <t>Grupo Passa Dois (limite Fm. Rio do Rasto / base Fm. Pirambóia)</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Pelecypoda indet. (Fm. Serra Alta)</t>
+          <t>Estheria sp. / Leaia sp. (filópodos)</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>Invertebrado — bivalve</t>
+          <t>Invertebrado — conchostráceo</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -17598,58 +17602,62 @@
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6</t>
+          <t>Entre Valões e Poço Preto, Lages, SC (estrada Lombo Alto–Lages, próx. km 65)</t>
         </is>
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Coleção histórica não especificada na fonte consultada</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
+          <t>Reed, F.R.C. (citado em: Beurlen, K. — Breves Notícias Sobre a Geologia dos Estados do Paraná e Santa Catarina; trad. port. em SciELO)</t>
         </is>
       </c>
       <c r="I201" s="6" t="inlineStr">
         <is>
-          <t>CPRM — Serviço Geológico do Brasil</t>
+          <t>Não especificado na fonte consultada</t>
         </is>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>ca. 265–259 Ma</t>
+          <t>ca. 259–252 Ma</t>
         </is>
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
-          <t>Compõe, junto a peixes e conchostráceos, o conteúdo fossilífero que posiciona a unidade no Permiano Superior. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Classificação: crustáceo conchostráceo (Branchiopoda). Filópodos (conchostráceos) permianos descritos por F.R. Cowper Reed em horizontes vermelhos e argilosos entre Valões e Poço Preto, Lages, SC; a fonte ressalva explicitamente que estes horizontes NÃO pertencem às camadas Estrada Nova, situando-se no contexto Rio do Rasto/Pirambóia</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
-        </is>
-      </c>
-      <c r="M201" s="7" t="inlineStr"/>
+          <t>https://scielo.br/scielo.php?pid=S1516-89132001000500010&amp;script=sci_arttext (tradução de Beurlen 1957, citando Reed)</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>REED, F.R.C. 1930. Fossil fauna from Permian beds in the State of Santa Catharina, Brazil. Geological Magazine, 67(793), 310–322. DOI: 10.1017/S0016756800100968 [Fonte primária]. Citado via: BEURLEN, K. 1957. Breves notícias sobre a geologia dos estados do Paraná e Santa Catarina. Ciência e Cultura, 9(1), 12–24. [Fonte secundária — tradução / nota geológica]</t>
+        </is>
+      </c>
       <c r="N201" s="6" t="n">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="O201" s="6" t="inlineStr">
         <is>
-          <t>Coluna White (Serra do Rio do Rastro)</t>
+          <t>Entre Valões e Poço Preto</t>
         </is>
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Serra Alta</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
         </is>
       </c>
       <c r="Q201" s="6" t="n">
-        <v>-28.3889</v>
+        <v>-27.8167</v>
       </c>
       <c r="R201" s="6" t="n">
-        <v>-49.4644</v>
+        <v>-50.3264</v>
       </c>
       <c r="S201" s="6" t="inlineStr"/>
     </row>
@@ -17666,12 +17674,12 @@
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>Conchostraca indet. (Fm. Serra Alta)</t>
+          <t>Restos de peixes indet. (Fm. Serra Alta)</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — conchostráceo</t>
+          <t>Vertebrado — peixes</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -17681,7 +17689,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6 (cota 520 m)</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -17701,12 +17709,12 @@
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
-          <t>ca. 265–259 Ma</t>
+          <t>ca. 265–259 Ma (topo do Kazaniano–base do Tatariano)</t>
         </is>
       </c>
       <c r="K202" s="5" t="inlineStr">
         <is>
-          <t>Conchostráceos em folhelhos de águas calmas; a Fm. Serra Alta foi separada do "schisto Iraty" de White por Gordon Jr. (1947) e elevada a formação por Sanford &amp; Lange (1960). Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Classificação: peixe. Espessa sequência de folhelhos e siltitos cinza-escuros com laminação plano-paralela e concreções calcárias, depositada em águas calmas abaixo do nível de ação das ondas. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L202" s="5" t="inlineStr">
@@ -17716,7 +17724,7 @@
       </c>
       <c r="M202" s="5" t="inlineStr"/>
       <c r="N202" s="4" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
@@ -17744,17 +17752,17 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto, Mb. Morro Pelado / Grupo Passa Dois</t>
+          <t>Fm. Serra Alta / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Schizoneura sp.</t>
+          <t>Pelecypoda indet. (Fm. Serra Alta)</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>Flora — Sphenopsida (esfenófita)</t>
+          <t>Invertebrado — bivalve</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
@@ -17764,7 +17772,7 @@
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 13-15, km 14,8-16,0</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6</t>
         </is>
       </c>
       <c r="G203" s="6" t="inlineStr">
@@ -17784,12 +17792,12 @@
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>ca. 259–252 Ma (Tatariano)</t>
+          <t>ca. 265–259 Ma</t>
         </is>
       </c>
       <c r="K203" s="7" t="inlineStr">
         <is>
-          <t>Integra a tafoflora do Membro Morro Pelado descrita por Klepzig (1978) NA SUA LOCALIDADE-TIPO, aqui na Serra do Rio do Rastro — o topônimo que batiza a formação. White (1908) usou estas camadas vermelhas como seção padrão do Rio do Rasto. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Compõe, junto a peixes e conchostráceos, o conteúdo fossilífero que posiciona a unidade no Permiano Superior. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L203" s="7" t="inlineStr">
@@ -17799,7 +17807,7 @@
       </c>
       <c r="M203" s="7" t="inlineStr"/>
       <c r="N203" s="6" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O203" s="6" t="inlineStr">
         <is>
@@ -17808,7 +17816,7 @@
       </c>
       <c r="P203" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto, Mb. Morro Pelado</t>
+          <t>Bacia do Paraná — Fm. Serra Alta</t>
         </is>
       </c>
       <c r="Q203" s="6" t="n">
@@ -17827,17 +17835,17 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto, Mb. Morro Pelado / Grupo Passa Dois</t>
+          <t>Fm. Serra Alta / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Dizeugotheca sp.</t>
+          <t>Conchostraca indet. (Fm. Serra Alta)</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Flora — Filicopsida (samambaia)</t>
+          <t>Invertebrado — conchostráceo</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -17847,7 +17855,7 @@
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 13-15</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Ponto 9, km 11,6</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -17867,12 +17875,12 @@
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t>ca. 259–252 Ma</t>
+          <t>ca. 265–259 Ma</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
         <is>
-          <t>Tafoflora do Mb. Morro Pelado na localidade-tipo, descrita por Klepzig (1978). Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Conchostráceos em folhelhos de águas calmas; a Fm. Serra Alta foi separada do "schisto Iraty" de White por Gordon Jr. (1947) e elevada a formação por Sanford &amp; Lange (1960). Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L204" s="5" t="inlineStr">
@@ -17882,7 +17890,7 @@
       </c>
       <c r="M204" s="5" t="inlineStr"/>
       <c r="N204" s="4" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
@@ -17891,7 +17899,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto, Mb. Morro Pelado</t>
+          <t>Bacia do Paraná — Fm. Serra Alta</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n">
@@ -17915,7 +17923,7 @@
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Dichophyllites sp.</t>
+          <t>Schizoneura sp.</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -17930,7 +17938,7 @@
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 11-13, km 14,7-14,8</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 13-15, km 14,8-16,0</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
@@ -17950,12 +17958,12 @@
       </c>
       <c r="J205" s="6" t="inlineStr">
         <is>
-          <t>ca. 259–252 Ma</t>
+          <t>ca. 259–252 Ma (Tatariano)</t>
         </is>
       </c>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>Impressões de folhas e caules identificadas por Bortoluzzi (1975) na Fm. Rio do Rasto de Santa Catarina. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Integra a tafoflora do Membro Morro Pelado descrita por Klepzig (1978) NA SUA LOCALIDADE-TIPO, aqui na Serra do Rio do Rastro — o topônimo que batiza a formação. White (1908) usou estas camadas vermelhas como seção padrão do Rio do Rasto. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
@@ -17965,7 +17973,7 @@
       </c>
       <c r="M205" s="7" t="inlineStr"/>
       <c r="N205" s="6" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O205" s="6" t="inlineStr">
         <is>
@@ -17993,17 +18001,17 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+          <t>Fm. Rio do Rasto, Mb. Morro Pelado / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Anfíbio labirintodonte indet. (Temnospondyli)</t>
+          <t>Dizeugotheca sp.</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Vertebrado — anfíbio (Temnospondyli)</t>
+          <t>Flora — Filicopsida (samambaia)</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -18013,7 +18021,7 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 11-15</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 13-15</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18038,7 +18046,7 @@
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>"Labirintodonte" é termo em desuso, referente ao padrão labiríntico de dobramento da dentina nos dentes — hoje o grupo é tratado como Temnospondyli. O capítulo SIGEP cita a ocorrência sem nomear táxon. Para o temnospôndilo catarinense FORMALMENTE NOMEADO, ver o registro de Parapytanga catarinensis (Serra do Espigão). Anfíbio labirintodonte citado entre os elementos fossilíferos que datam a Fm. Rio do Rasto entre o Permiano Superior e o Triássico Inferior. Junto com pelecípodes, conchostráceos e restos vegetais, marca a transição de ambiente marinho raso para planície costeira e, no topo, sedimentação flúvio-deltaica. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+          <t>Tafoflora do Mb. Morro Pelado na localidade-tipo, descrita por Klepzig (1978). Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
@@ -18048,7 +18056,7 @@
       </c>
       <c r="M206" s="5" t="inlineStr"/>
       <c r="N206" s="4" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
@@ -18057,7 +18065,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto, Mb. Morro Pelado</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n">
@@ -18076,17 +18084,17 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+          <t>Fm. Rio do Rasto, Mb. Morro Pelado / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>Australoxylon duartei (lenho fóssil permineralizado)</t>
+          <t>Dichophyllites sp.</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>Flora — lenho fóssil (Gymnospermopsida)</t>
+          <t>Flora — Sphenopsida (esfenófita)</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -18096,7 +18104,7 @@
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência na Fm. Rio do Rasto em Santa Catarina (localidade não detalhada na fonte consultada)</t>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 11-13, km 14,7-14,8</t>
         </is>
       </c>
       <c r="G207" s="6" t="inlineStr">
@@ -18106,48 +18114,48 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência inventariada em levantamento da Fm. Rio do Rasto em SC (2017)</t>
+          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
         </is>
       </c>
       <c r="I207" s="6" t="inlineStr">
         <is>
-          <t>UFRGS; FURB</t>
+          <t>CPRM — Serviço Geológico do Brasil</t>
         </is>
       </c>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>ca. 266–254 Ma</t>
+          <t>ca. 259–252 Ma</t>
         </is>
       </c>
       <c r="K207" s="7" t="inlineStr">
         <is>
-          <t>Morfogênero de lenho gimnospérmico permineralizado, entre os elementos vegetais já reportados para a Fm. Rio do Rasto em Santa Catarina. RESSALVA: a fonte consultada inventaria a ocorrência sem detalhar localidade, tombo ou depositário — o registro consta da literatura, mas carece de dados de procedência precisos.</t>
+          <t>Impressões de folhas e caules identificadas por Bortoluzzi (1975) na Fm. Rio do Rasto de Santa Catarina. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
         </is>
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
+          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
         </is>
       </c>
       <c r="M207" s="7" t="inlineStr"/>
       <c r="N207" s="6" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="O207" s="6" t="inlineStr">
         <is>
-          <t>Fm. Rio do Rasto — SC (localidade não detalhada)</t>
+          <t>Coluna White (Serra do Rio do Rastro)</t>
         </is>
       </c>
       <c r="P207" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto, Mb. Morro Pelado</t>
         </is>
       </c>
       <c r="Q207" s="6" t="n">
-        <v>-27.5</v>
+        <v>-28.3889</v>
       </c>
       <c r="R207" s="6" t="n">
-        <v>-49.5</v>
+        <v>-49.4644</v>
       </c>
       <c r="S207" s="6" t="inlineStr"/>
     </row>
@@ -18164,224 +18172,224 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
+          <t>Anfíbio labirintodonte indet. (Temnospondyli)</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>Vertebrado — anfíbio (Temnospondyli)</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>Rodovia SC-438, Serra do Rio do Rastro — Pontos 11-15</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>Orlandi Filho, V., Krebs, A.S.J. &amp; Giffoni, L.E. (2006/2009) — SIGEP, Sítio 024, in Sítios Geológicos e Paleontológicos do Brasil, CPRM, v.2</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>CPRM — Serviço Geológico do Brasil</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>ca. 259–252 Ma</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>"Labirintodonte" é termo em desuso, referente ao padrão labiríntico de dobramento da dentina nos dentes — hoje o grupo é tratado como Temnospondyli. O capítulo SIGEP cita a ocorrência sem nomear táxon. Para o temnospôndilo catarinense FORMALMENTE NOMEADO, ver o registro de Parapytanga catarinensis (Serra do Espigão). Anfíbio labirintodonte citado entre os elementos fossilíferos que datam a Fm. Rio do Rasto entre o Permiano Superior e o Triássico Inferior. Junto com pelecípodes, conchostráceos e restos vegetais, marca a transição de ambiente marinho raso para planície costeira e, no topo, sedimentação flúvio-deltaica. Seção da COLUNA WHITE, ao longo da rodovia SC-438 na Serra do Rio do Rastro — a coluna estratigráfica clássica do Gondwana no Brasil, definida por Israel Charles White no relatório de 1908 da Comissão de Estudos das Minas de Carvão de Pedra do Brazil. Foi aqui que White correlacionou o "Systema de Santa Catharina" ao "Systema Karroo" da África do Sul, um dos alicerces da teoria da deriva continental. A seção está demarcada no terreno por 17 marcos de concreto.</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="inlineStr">
+        <is>
+          <t>https://sigep.eco.br/sitio024/sitio024.pdf</t>
+        </is>
+      </c>
+      <c r="M208" s="5" t="inlineStr"/>
+      <c r="N208" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="O208" s="4" t="inlineStr">
+        <is>
+          <t>Coluna White (Serra do Rio do Rastro)</t>
+        </is>
+      </c>
+      <c r="P208" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+        </is>
+      </c>
+      <c r="Q208" s="4" t="n">
+        <v>-28.3889</v>
+      </c>
+      <c r="R208" s="4" t="n">
+        <v>-49.4644</v>
+      </c>
+      <c r="S208" s="4" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>Permiano Superior</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>Australoxylon duartei (lenho fóssil permineralizado)</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>Flora — lenho fóssil (Gymnospermopsida)</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Ocorrência na Fm. Rio do Rasto em Santa Catarina (localidade não detalhada na fonte consultada)</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>Ocorrência inventariada em levantamento da Fm. Rio do Rasto em SC (2017)</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>UFRGS; FURB</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t>ca. 266–254 Ma</t>
+        </is>
+      </c>
+      <c r="K209" s="7" t="inlineStr">
+        <is>
+          <t>Morfogênero de lenho gimnospérmico permineralizado, entre os elementos vegetais já reportados para a Fm. Rio do Rasto em Santa Catarina. RESSALVA: a fonte consultada inventaria a ocorrência sem detalhar localidade, tombo ou depositário — o registro consta da literatura, mas carece de dados de procedência precisos.</t>
+        </is>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/publication/334304105_NOVA_LOCALIDADE_FOSSILIFERA_DA_FORMACAO_RIO_DO_RASTO_GUADALUPIANOLOPINGIANO_BACIA_DO_PARANA_NO_ESTADO_DE_SANTA_CATARINA_BRASIL</t>
+        </is>
+      </c>
+      <c r="M209" s="7" t="inlineStr"/>
+      <c r="N209" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="O209" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto — SC (localidade não detalhada)</t>
+        </is>
+      </c>
+      <c r="P209" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+        </is>
+      </c>
+      <c r="Q209" s="6" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="R209" s="6" t="n">
+        <v>-49.5</v>
+      </c>
+      <c r="S209" s="6" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>Permiano Superior</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
           <t>Palaeolimnadiopsis subalata (Reed, 1929) Raymond, 1946</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="D210" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — conchostráceo (Spinicaudata)</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
+      <c r="E210" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
         <is>
           <t>Afloramentos do norte de Santa Catarina e do Paraná (localidade catarinense não individualizada na fonte)</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>Coleções IG-USP / UNESP-Rio Claro</t>
         </is>
       </c>
-      <c r="H208" s="5" t="inlineStr">
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>Rohn, R. (1987) — "Conchostráceos da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina", Boletim IG-USP, Série Científica, 18:27-66; Ferreira-Oliveira, L.G. &amp; Rohn, R. (2008) — Geologia USP, Série Científica, 8(1):41-52</t>
         </is>
       </c>
-      <c r="I208" s="4" t="inlineStr">
+      <c r="I210" s="4" t="inlineStr">
         <is>
           <t>IG-USP; UNESP-Rio Claro</t>
         </is>
       </c>
-      <c r="J208" s="4" t="inlineStr">
+      <c r="J210" s="4" t="inlineStr">
         <is>
           <t>ca. 259–252 Ma (Tatariano/Wuchiapingiano)</t>
         </is>
       </c>
-      <c r="K208" s="5" t="inlineStr">
+      <c r="K210" s="5" t="inlineStr">
         <is>
           <t>Espécie de carapaça subelíptica, com umbo pequeno e subanterior. Define a Subzona Palaeolimnadiopsis subalata, uma das biozonas de conchostráceos da Fm. Rio do Rasto. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
         </is>
       </c>
-      <c r="L208" s="5" t="inlineStr">
+      <c r="L210" s="5" t="inlineStr">
         <is>
           <t>https://repositorio.usp.br/directbitstream/0fb93b94-9007-4a8e-b405-4fbdf46ba756/0755592.pdf
 https://revistas.usp.br/guspsc/article/view/27442</t>
         </is>
       </c>
-      <c r="M208" s="5" t="inlineStr"/>
-      <c r="N208" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="O208" s="4" t="inlineStr">
-        <is>
-          <t>Afloramentos do norte de SC/PR — conchostráceos</t>
-        </is>
-      </c>
-      <c r="P208" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="n">
-        <v>-26.15</v>
-      </c>
-      <c r="R208" s="4" t="n">
-        <v>-49.9</v>
-      </c>
-      <c r="S208" s="4" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Superior</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
-        </is>
-      </c>
-      <c r="C209" s="7" t="inlineStr">
-        <is>
-          <t>Falsisca brasiliensis Ferreira-Oliveira &amp; Rohn, 2008</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — conchostráceo (Spinicaudata)</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F209" s="7" t="inlineStr">
-        <is>
-          <t>Afloramentos do norte de Santa Catarina e do Paraná (localidade catarinense não individualizada na fonte)</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr">
-        <is>
-          <t>Coleções IG-USP / UNESP-Rio Claro</t>
-        </is>
-      </c>
-      <c r="H209" s="7" t="inlineStr">
-        <is>
-          <t>Ferreira-Oliveira, L.G. &amp; Rohn, R. (2008) — Geologia USP, Série Científica, 8(1):41-52</t>
-        </is>
-      </c>
-      <c r="I209" s="6" t="inlineStr">
-        <is>
-          <t>IG-USP; UNESP-Rio Claro</t>
-        </is>
-      </c>
-      <c r="J209" s="6" t="inlineStr">
-        <is>
-          <t>ca. 259–252 Ma (Tatariano/Wuchiapingiano)</t>
-        </is>
-      </c>
-      <c r="K209" s="7" t="inlineStr">
-        <is>
-          <t>Espécie NOVA descrita na revisão de 2008, de valvas elípticas com umbo grande e anterior (Perilimnadiidae). Marca a PRIMEIRA ocorrência do gênero Falsisca no registro fóssil do Gondwana — até então restrito ao Permiano Superior–Triássico Inferior da Europa e da Ásia, o que corrobora a idade neopermiana dos estratos. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
-        </is>
-      </c>
-      <c r="L209" s="7" t="inlineStr">
-        <is>
-          <t>https://revistas.usp.br/guspsc/article/view/27442</t>
-        </is>
-      </c>
-      <c r="M209" s="7" t="inlineStr"/>
-      <c r="N209" s="6" t="n">
-        <v>186</v>
-      </c>
-      <c r="O209" s="6" t="inlineStr">
-        <is>
-          <t>Afloramentos do norte de SC/PR — conchostráceos</t>
-        </is>
-      </c>
-      <c r="P209" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
-        </is>
-      </c>
-      <c r="Q209" s="6" t="n">
-        <v>-26.15</v>
-      </c>
-      <c r="R209" s="6" t="n">
-        <v>-49.9</v>
-      </c>
-      <c r="S209" s="6" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Superior</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>Monoleiolophus unicostatus (Leaiidae)</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — conchostráceo (Spinicaudata)</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>Afloramentos do norte de Santa Catarina e do Paraná (localidade catarinense não individualizada na fonte)</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
-        <is>
-          <t>Coleções IG-USP / UNESP-Rio Claro</t>
-        </is>
-      </c>
-      <c r="H210" s="5" t="inlineStr">
-        <is>
-          <t>Rohn, R. (1987) — "Conchostráceos da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina", Boletim IG-USP, Série Científica, 18:27-66</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>IG-USP; UNESP-Rio Claro</t>
-        </is>
-      </c>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>ca. 259–252 Ma (Tatariano/Wuchiapingiano)</t>
-        </is>
-      </c>
-      <c r="K210" s="5" t="inlineStr">
-        <is>
-          <t>Define a zona "Monoleaia unicostata" na bioestratigrafia da formação. Os leaiídeos ocorrem quase até o topo da unidade e constituem forte evidência cronoestratigráfica de idade não mais jovem que o Permiano. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
-        </is>
-      </c>
-      <c r="L210" s="5" t="inlineStr">
-        <is>
-          <t>https://repositorio.usp.br/directbitstream/0fb93b94-9007-4a8e-b405-4fbdf46ba756/0755592.pdf</t>
-        </is>
-      </c>
       <c r="M210" s="5" t="inlineStr"/>
       <c r="N210" s="4" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
@@ -18414,7 +18422,7 @@
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>Hemicycloleaia mitchelli</t>
+          <t>Falsisca brasiliensis Ferreira-Oliveira &amp; Rohn, 2008</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -18439,7 +18447,7 @@
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>Rohn, R. (1987) — "Conchostráceos da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina", Boletim IG-USP, Série Científica, 18:27-66</t>
+          <t>Ferreira-Oliveira, L.G. &amp; Rohn, R. (2008) — Geologia USP, Série Científica, 8(1):41-52</t>
         </is>
       </c>
       <c r="I211" s="6" t="inlineStr">
@@ -18454,17 +18462,17 @@
       </c>
       <c r="K211" s="7" t="inlineStr">
         <is>
-          <t>Um dos táxons considerados válidos na revisão de Ferreira-Oliveira (2007) para a Fm. Rio do Rasto. A espécie foi originalmente registrada no Tatariano superior (Wuchiapingiano) da Bacia de Sydney, Austrália — correlação que reforça a idade permiana dos estratos portadores. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
+          <t>Espécie NOVA descrita na revisão de 2008, de valvas elípticas com umbo grande e anterior (Perilimnadiidae). Marca a PRIMEIRA ocorrência do gênero Falsisca no registro fóssil do Gondwana — até então restrito ao Permiano Superior–Triássico Inferior da Europa e da Ásia, o que corrobora a idade neopermiana dos estratos. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
         </is>
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>https://repositorio.usp.br/directbitstream/0fb93b94-9007-4a8e-b405-4fbdf46ba756/0755592.pdf</t>
+          <t>https://revistas.usp.br/guspsc/article/view/27442</t>
         </is>
       </c>
       <c r="M211" s="7" t="inlineStr"/>
       <c r="N211" s="6" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O211" s="6" t="inlineStr">
         <is>
@@ -18487,22 +18495,22 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Jurássico Superior (?) – Cretáceo Inferior (?)</t>
+          <t>Permiano Superior</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Fm. Botucatu (depósitos eólicos do paleodeserto)</t>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Theropoda indet. (afim. Carnosauria) — pista bípede</t>
+          <t>Monoleiolophus unicostatus (Leaiidae)</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — pegada de dinossauro terópode</t>
+          <t>Invertebrado — conchostráceo (Spinicaudata)</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -18512,1414 +18520,1673 @@
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Litoral sul de Santa Catarina, SC (localidade não especificada na fonte)</t>
+          <t>Afloramentos do norte de Santa Catarina e do Paraná (localidade catarinense não individualizada na fonte)</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>Coleções IG-USP / UNESP-Rio Claro</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>Weinschütz, L.C. (CENPALEO/UnC), citado em reportagem ND Mais (2023)</t>
+          <t>Rohn, R. (1987) — "Conchostráceos da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina", Boletim IG-USP, Série Científica, 18:27-66</t>
         </is>
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>IG-USP; UNESP-Rio Claro</t>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t>ca. 150–145 Ma (Jurássico Superior, estimativa indicativa)</t>
+          <t>ca. 259–252 Ma (Tatariano/Wuchiapingiano)</t>
         </is>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>Único registro de dinossauro (icnofóssil) atualmente conhecido para SC; trata-se de pista de animal bípede de porte médio (cerca de 1,7 m), atribuída a terópode do grupo Carnosauria; nenhum osso corporal de dinossauro foi descrito para o Estado até o momento; localidade precisa não divulgada na fonte consultada</t>
+          <t>Define a zona "Monoleaia unicostata" na bioestratigrafia da formação. Os leaiídeos ocorrem quase até o topo da unidade e constituem forte evidência cronoestratigráfica de idade não mais jovem que o Permiano. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
         </is>
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ (ND Mais, 2023)</t>
-        </is>
-      </c>
-      <c r="M212" s="5" t="inlineStr">
-        <is>
-          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação jornalística: NDMAIS. 2023. Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC. Disponível em: https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ [Fonte secundária — sem publicação científica primária identificada no levantamento desta base]</t>
-        </is>
-      </c>
+          <t>https://repositorio.usp.br/directbitstream/0fb93b94-9007-4a8e-b405-4fbdf46ba756/0755592.pdf</t>
+        </is>
+      </c>
+      <c r="M212" s="5" t="inlineStr"/>
       <c r="N212" s="4" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>Litoral sul de SC</t>
+          <t>Afloramentos do norte de SC/PR — conchostráceos</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Botucatu</t>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n">
-        <v>-28.95</v>
+        <v>-26.15</v>
       </c>
       <c r="R212" s="4" t="n">
-        <v>-49.45</v>
+        <v>-49.9</v>
       </c>
       <c r="S212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
+          <t>Permiano Superior</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Grupo Passa Dois</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>Hemicycloleaia mitchelli</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>Invertebrado — conchostráceo (Spinicaudata)</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>Afloramentos do norte de Santa Catarina e do Paraná (localidade catarinense não individualizada na fonte)</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>Coleções IG-USP / UNESP-Rio Claro</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>Rohn, R. (1987) — "Conchostráceos da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina", Boletim IG-USP, Série Científica, 18:27-66</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>IG-USP; UNESP-Rio Claro</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
+          <t>ca. 259–252 Ma (Tatariano/Wuchiapingiano)</t>
+        </is>
+      </c>
+      <c r="K213" s="7" t="inlineStr">
+        <is>
+          <t>Um dos táxons considerados válidos na revisão de Ferreira-Oliveira (2007) para a Fm. Rio do Rasto. A espécie foi originalmente registrada no Tatariano superior (Wuchiapingiano) da Bacia de Sydney, Austrália — correlação que reforça a idade permiana dos estratos portadores. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. RESSALVA: Rohn (1987) trata em conjunto os afloramentos do Paraná e do NORTE de Santa Catarina; a localidade catarinense precisa não é individualizada na fonte, e a coordenada aqui é regional.</t>
+        </is>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>https://repositorio.usp.br/directbitstream/0fb93b94-9007-4a8e-b405-4fbdf46ba756/0755592.pdf</t>
+        </is>
+      </c>
+      <c r="M213" s="7" t="inlineStr"/>
+      <c r="N213" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="O213" s="6" t="inlineStr">
+        <is>
+          <t>Afloramentos do norte de SC/PR — conchostráceos</t>
+        </is>
+      </c>
+      <c r="P213" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Rio do Rasto</t>
+        </is>
+      </c>
+      <c r="Q213" s="6" t="n">
+        <v>-26.15</v>
+      </c>
+      <c r="R213" s="6" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="S213" s="6" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>Jurássico Superior (?) – Cretáceo Inferior (?)</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Fm. Botucatu (depósitos eólicos do paleodeserto)</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>Theropoda indet. (afim. Carnosauria) — pista bípede</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — pegada de dinossauro terópode</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Litoral sul de Santa Catarina, SC (localidade não especificada na fonte)</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>Weinschütz, L.C. (CENPALEO/UnC), citado em reportagem ND Mais (2023)</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>ca. 150–145 Ma (Jurássico Superior, estimativa indicativa)</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>Único registro de dinossauro (icnofóssil) atualmente conhecido para SC; trata-se de pista de animal bípede de porte médio (cerca de 1,7 m), atribuída a terópode do grupo Carnosauria; nenhum osso corporal de dinossauro foi descrito para o Estado até o momento; localidade precisa não divulgada na fonte consultada</t>
+        </is>
+      </c>
+      <c r="L214" s="5" t="inlineStr">
+        <is>
+          <t>https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ (ND Mais, 2023)</t>
+        </is>
+      </c>
+      <c r="M214" s="5" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação jornalística: NDMAIS. 2023. Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC. Disponível em: https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ [Fonte secundária — sem publicação científica primária identificada no levantamento desta base]</t>
+        </is>
+      </c>
+      <c r="N214" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="O214" s="4" t="inlineStr">
+        <is>
+          <t>Litoral sul de SC</t>
+        </is>
+      </c>
+      <c r="P214" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Botucatu</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="n">
+        <v>-28.95</v>
+      </c>
+      <c r="R214" s="4" t="n">
+        <v>-49.45</v>
+      </c>
+      <c r="S214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
           <t>Cretáceo Inferior</t>
         </is>
       </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>Fm. Botucatu (depósitos eólicos do paleodeserto)</t>
         </is>
       </c>
-      <c r="C213" s="7" t="inlineStr">
+      <c r="C215" s="7" t="inlineStr">
         <is>
           <t>Mammaliaformes indet. (cf. Aracoaraichnium) — pista com 4 pegadas</t>
         </is>
       </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — pista de Mammaliaformes (4 pegadas)</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>UERJ-IC-170</t>
         </is>
       </c>
-      <c r="F213" s="7" t="inlineStr">
+      <c r="F215" s="7" t="inlineStr">
         <is>
           <t>Pedreira no município de Turvo, extremo sul de SC</t>
         </is>
       </c>
-      <c r="G213" s="6" t="inlineStr">
+      <c r="G215" s="6" t="inlineStr">
         <is>
           <t>LABPALEO/UERJ (Universidade do Estado do Rio de Janeiro)</t>
         </is>
       </c>
-      <c r="H213" s="7" t="inlineStr">
+      <c r="H215" s="7" t="inlineStr">
         <is>
           <t>Buck, P.V. et al. (2022b) — "As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estado de Santa Catarina, Brasil", Paleontologia em Destaque</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>LABPALEO/UERJ</t>
         </is>
       </c>
-      <c r="J213" s="6" t="inlineStr">
+      <c r="J215" s="6" t="inlineStr">
         <is>
           <t>ca. 130–113 Ma</t>
         </is>
       </c>
-      <c r="K213" s="7" t="inlineStr">
+      <c r="K215" s="7" t="inlineStr">
         <is>
           <t>Laje de arenito com pista de quatro pegadas em epirrelevo côncavo, atribuídas aos pés de um produtor quadrúpede. São as maiores pegadas atribuídas a Mammaliaformes da Fm. Botucatu e possivelmente do Mesozoico — MAIORES que as de Aracoaraichnium, razão pela qual o espécime é atribuído apenas tentativamente ao mesmo morfotipo, e não à icnoespécie A. leonardii (cujo material-tipo provém de Araraquara, SP). Primeiro registro de pegadas de tetrápode descrito para a Fm. Botucatu em Santa Catarina.</t>
         </is>
       </c>
-      <c r="L213" s="7" t="inlineStr">
+      <c r="L215" s="7" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/367511513_AS_MAIORES_PEGADAS_ATRIBUIDAS_A_MAMMALIAFORMES_DA_FORMACAO_BOTUCATU_CRETACEO_INFERIOR_ESTADO_DE_SANTA_CATARINA_BRASIL
 https://www.researchgate.net/publication/317731251_A_new_ichnotaxon_classification_of_large_mammaliform_trackways_from_the_Lower_Cretaceous_Botucatu_Formation_Parana_Basin_Brazil</t>
         </is>
       </c>
-      <c r="M213" s="7" t="inlineStr">
+      <c r="M215" s="7" t="inlineStr">
         <is>
           <t>BUCK, P.V. et al. 2022. As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estados de Santa Catarina e São Paulo, Brasil. In: Resumos, XXVIII Congresso Brasileiro de Paleontologia. Boletim de Resumos. [Fonte primária — publicação em anais de evento; não indexada em periódico com DOI no levantamento]. Disponível em: https://www.researchgate.net/publication/367511513</t>
         </is>
       </c>
-      <c r="N213" s="6" t="n">
+      <c r="N215" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="O213" s="6" t="inlineStr">
+      <c r="O215" s="6" t="inlineStr">
         <is>
           <t>Pedreira de Turvo</t>
         </is>
       </c>
-      <c r="P213" s="6" t="inlineStr">
+      <c r="P215" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Botucatu</t>
         </is>
       </c>
-      <c r="Q213" s="6" t="n">
+      <c r="Q215" s="6" t="n">
         <v>-28.9272</v>
       </c>
-      <c r="R213" s="6" t="n">
+      <c r="R215" s="6" t="n">
         <v>-49.6831</v>
       </c>
-      <c r="S213" s="6" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
+      <c r="S215" s="6" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="B216" s="4" t="inlineStr">
         <is>
           <t>Depósitos superficiais / aluvionares</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
         <is>
           <t>Paleotocas (icnofósseis de escavação — Dasypodidae / Mylodontidae)</t>
         </is>
       </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — túnel de escavação (bioerosão)</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="inlineStr">
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
         <is>
           <t>Municípios do Sul de SC (Geoparque Caminhos dos Cânions do Sul)</t>
         </is>
       </c>
-      <c r="G214" s="4" t="inlineStr">
+      <c r="G216" s="4" t="inlineStr">
         <is>
           <t>Geoparque Caminhos dos Cânions do Sul (Morro Grande, Timbé do Sul, Araranguá)</t>
         </is>
       </c>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Frank et al. (vários); Simão, G. (geólogo Geoparque, 2025)</t>
         </is>
       </c>
-      <c r="I214" s="4" t="inlineStr">
+      <c r="I216" s="4" t="inlineStr">
         <is>
           <t>UNESC / Geoparque UNESCO</t>
         </is>
       </c>
-      <c r="J214" s="4" t="inlineStr">
+      <c r="J216" s="4" t="inlineStr">
         <is>
           <t>5,33 – 0,012 Ma</t>
         </is>
       </c>
-      <c r="K214" s="5" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Mais de 40 estruturas identificadas; algumas interconectadas atingem até 340 m; escavadas por preguiças e tatus-gigantes extintos</t>
-        </is>
-      </c>
-      <c r="L214" s="5" t="inlineStr">
+      <c r="K216" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Mais de 40 estruturas identificadas; algumas interconectadas atingem até 340 m; escavadas por preguiças e tatus-gigantes extintos</t>
+        </is>
+      </c>
+      <c r="L216" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
 https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 (More than fossils: Paleoburrows as geoheritage...)
 https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Proposta de classificação das paleotocas)
-https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/</t>
-        </is>
-      </c>
-      <c r="M214" s="5" t="inlineStr">
+https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M216" s="5" t="inlineStr">
         <is>
           <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
         </is>
       </c>
-      <c r="N214" s="4" t="n">
+      <c r="N216" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="O214" s="4" t="inlineStr">
+      <c r="O216" s="4" t="inlineStr">
         <is>
           <t>Geoparque Caminhos dos Cânions do Sul</t>
         </is>
       </c>
-      <c r="P214" s="4" t="inlineStr">
+      <c r="P216" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Botucatu / Cânions</t>
         </is>
       </c>
-      <c r="Q214" s="4" t="n">
+      <c r="Q216" s="4" t="n">
         <v>-29.19</v>
       </c>
-      <c r="R214" s="4" t="n">
+      <c r="R216" s="4" t="n">
         <v>-49.94</v>
       </c>
-      <c r="S214" s="4" t="inlineStr">
+      <c r="S216" s="4" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>Fm. Botucatu (arenito eólico) — geossítio do Geoparque</t>
         </is>
       </c>
-      <c r="C215" s="7" t="inlineStr">
+      <c r="C217" s="7" t="inlineStr">
         <is>
           <t>Paleotoca Furnas Xocleng (icnofóssil de escavação — Xenarthra)</t>
         </is>
       </c>
-      <c r="D215" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — estrutura de habitação (Domichnia)</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F215" s="7" t="inlineStr">
+      <c r="F217" s="7" t="inlineStr">
         <is>
           <t>Comunidade de Três Barras, interior de Morro Grande, SC — a cerca de 14 a 18 km do centro (coordenada da sede municipal; a do geossítio não é publicada)</t>
         </is>
       </c>
-      <c r="G215" s="6" t="inlineStr">
+      <c r="G217" s="6" t="inlineStr">
         <is>
           <t>Geoparque Mundial da UNESCO Caminhos dos Cânions do Sul (geossítio aberto à visitação)</t>
         </is>
       </c>
-      <c r="H215" s="7" t="inlineStr">
+      <c r="H217" s="7" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional); Bechtel, A.F. (doutorando em geografia, citado em reportagens, 2025/2026)</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Geoparque UNESCO</t>
         </is>
       </c>
-      <c r="J215" s="6" t="inlineStr">
+      <c r="J217" s="6" t="inlineStr">
         <is>
           <t>5,33 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K215" s="7" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Três cavidades subterrâneas somando mais de 100 m de extensão; marcas de garras nas paredes; atribuída a tatus-gigantes (Glyptodon/Pampatherium) e/ou preguiças-gigantes CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande.</t>
-        </is>
-      </c>
-      <c r="L215" s="7" t="inlineStr">
+      <c r="K217" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Três cavidades subterrâneas somando mais de 100 m de extensão; marcas de garras nas paredes; atribuída a tatus-gigantes (Glyptodon/Pampatherium) e/ou preguiças-gigantes CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande.</t>
+        </is>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
-        </is>
-      </c>
-      <c r="M215" s="7" t="inlineStr">
+https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M217" s="7" t="inlineStr">
         <is>
           <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
         </is>
       </c>
-      <c r="N215" s="6" t="n">
+      <c r="N217" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="O215" s="6" t="inlineStr">
+      <c r="O217" s="6" t="inlineStr">
         <is>
           <t>Morro Grande</t>
         </is>
       </c>
-      <c r="P215" s="6" t="inlineStr">
+      <c r="P217" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Botucatu</t>
         </is>
       </c>
-      <c r="Q215" s="6" t="n">
+      <c r="Q217" s="6" t="n">
         <v>-28.8006</v>
       </c>
-      <c r="R215" s="6" t="n">
+      <c r="R217" s="6" t="n">
         <v>-49.7208</v>
       </c>
-      <c r="S215" s="6" t="inlineStr">
+      <c r="S217" s="6" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>Fm. Botucatu (arenito eólico) — geossítio do Geoparque</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>Paleotoca Toca do Tatu (icnofóssil de escavação — Xenarthra)</t>
         </is>
       </c>
-      <c r="D216" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — estrutura de habitação (Domichnia)</t>
-        </is>
-      </c>
-      <c r="E216" s="4" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>Timbé do Sul, SC (a ~7,3 km do município, junto ao rio Rocinha)</t>
-        </is>
-      </c>
-      <c r="G216" s="4" t="inlineStr">
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>Toca do Tatu, Timbé do Sul, SC (28°46'21,2"S, 49°53'45,9"W, coordenada publicada)</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
         <is>
           <t>Geoparque Mundial da UNESCO Caminhos dos Cânions do Sul (geossítio aberto à visitação)</t>
         </is>
       </c>
-      <c r="H216" s="5" t="inlineStr">
-        <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional)</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="inlineStr">
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101; Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
         <is>
           <t>Geoparque UNESCO</t>
         </is>
       </c>
-      <c r="J216" s="4" t="inlineStr">
+      <c r="J218" s="4" t="inlineStr">
         <is>
           <t>5,33 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K216" s="5" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos)</t>
-        </is>
-      </c>
-      <c r="L216" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
+      <c r="K218" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos) CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna.</t>
+        </is>
+      </c>
+      <c r="L218" s="5" t="inlineStr">
+        <is>
+          <t>https://www.semanticscholar.org/paper/THE-COMPLEX-HISTORY-OF-A-SANDSTONE-HOSTED-CAVE-IN-,-Frank-Oliveira/352ac79d172767f56f9a572deea5da8581b08db2
+https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
-        </is>
-      </c>
-      <c r="M216" s="5" t="inlineStr">
+https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M218" s="5" t="inlineStr">
         <is>
           <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
         </is>
       </c>
-      <c r="N216" s="4" t="n">
+      <c r="N218" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="O216" s="4" t="inlineStr">
+      <c r="O218" s="4" t="inlineStr">
         <is>
           <t>Timbé do Sul (rio Rocinha)</t>
         </is>
       </c>
-      <c r="P216" s="4" t="inlineStr">
+      <c r="P218" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Botucatu</t>
         </is>
       </c>
-      <c r="Q216" s="4" t="n">
-        <v>-28.8244</v>
-      </c>
-      <c r="R216" s="4" t="n">
-        <v>-49.9183</v>
-      </c>
-      <c r="S216" s="4" t="inlineStr">
+      <c r="Q218" s="4" t="n">
+        <v>-28.7726</v>
+      </c>
+      <c r="R218" s="4" t="n">
+        <v>-49.8961</v>
+      </c>
+      <c r="S218" s="4" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="6" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Depósitos superficiais / arenitos diversos — geossítios do Geoparque</t>
         </is>
       </c>
-      <c r="C217" s="7" t="inlineStr">
+      <c r="C219" s="7" t="inlineStr">
         <is>
           <t>Paleotocas adicionais (Jacinto Machado e Praia Grande, SC)</t>
         </is>
       </c>
-      <c r="D217" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — estrutura de habitação (Domichnia)</t>
-        </is>
-      </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F217" s="7" t="inlineStr">
+      <c r="F219" s="7" t="inlineStr">
         <is>
           <t>Jacinto Machado, SC (Paleotoca do Engenho Velho); Praia Grande, SC</t>
         </is>
       </c>
-      <c r="G217" s="6" t="inlineStr">
+      <c r="G219" s="6" t="inlineStr">
         <is>
           <t>Geoparque Mundial da UNESCO Caminhos dos Cânions do Sul</t>
         </is>
       </c>
-      <c r="H217" s="7" t="inlineStr">
+      <c r="H219" s="7" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: ND Mais (2025); CircuitoMT (2025), citando especialistas do Geoparque</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I219" s="6" t="inlineStr">
         <is>
           <t>Geoparque UNESCO</t>
         </is>
       </c>
-      <c r="J217" s="6" t="inlineStr">
+      <c r="J219" s="6" t="inlineStr">
         <is>
           <t>5,33 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K217" s="7" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Registros de paleotocas adicionais em cinco municípios do Geoparque (quatro em SC: Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande); mais de 40 estruturas catalogadas no total, algumas interconectadas atingindo até 340 m de extensão</t>
-        </is>
-      </c>
-      <c r="L217" s="7" t="inlineStr">
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Registros de paleotocas adicionais em cinco municípios do Geoparque (quatro em SC: Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande); mais de 40 estruturas catalogadas no total, algumas interconectadas atingindo até 340 m de extensão</t>
+        </is>
+      </c>
+      <c r="L219" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
 https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
-https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/</t>
-        </is>
-      </c>
-      <c r="M217" s="7" t="inlineStr">
+https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M219" s="7" t="inlineStr">
         <is>
           <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 | Divulgação jornalística: NDMAIS. 2025. Cavernas em SC guardam rastros de preguiças e tatus gigantes. Disponível em: https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/ [Fonte secundária complementar]</t>
         </is>
       </c>
-      <c r="N217" s="6" t="n">
+      <c r="N219" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="O217" s="6" t="inlineStr">
+      <c r="O219" s="6" t="inlineStr">
         <is>
           <t>Paleotoca do Engenho Velho</t>
         </is>
       </c>
-      <c r="P217" s="6" t="inlineStr">
+      <c r="P219" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Botucatu / Cânions</t>
         </is>
       </c>
-      <c r="Q217" s="6" t="n">
+      <c r="Q219" s="6" t="n">
         <v>-29.0333</v>
       </c>
-      <c r="R217" s="6" t="n">
+      <c r="R219" s="6" t="n">
         <v>-49.8167</v>
       </c>
-      <c r="S217" s="6" t="inlineStr">
+      <c r="S219" s="6" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B218" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>Depósitos cenozóicos / rochas do Planalto Serrano</t>
         </is>
       </c>
-      <c r="C218" s="5" t="inlineStr">
+      <c r="C220" s="5" t="inlineStr">
         <is>
           <t>Megaichnus major (paleotoca URU-01-P2)</t>
         </is>
       </c>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — paleotoca (Xenarthra)</t>
-        </is>
-      </c>
-      <c r="E218" s="4" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
         <is>
           <t>URU-01-P2 (designação de campo)</t>
         </is>
       </c>
-      <c r="F218" s="5" t="inlineStr">
+      <c r="F220" s="5" t="inlineStr">
         <is>
           <t>Paleotoca de Urubici (URU-01-P2), Urubici, SC</t>
         </is>
       </c>
-      <c r="G218" s="4" t="inlineStr">
+      <c r="G220" s="4" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H218" s="5" t="inlineStr">
+      <c r="H220" s="5" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
         </is>
       </c>
-      <c r="I218" s="4" t="inlineStr">
+      <c r="I220" s="4" t="inlineStr">
         <is>
           <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
         </is>
       </c>
-      <c r="J218" s="4" t="inlineStr">
+      <c r="J220" s="4" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="K218" s="5" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016).</t>
-        </is>
-      </c>
-      <c r="L218" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081</t>
-        </is>
-      </c>
-      <c r="M218" s="5" t="inlineStr"/>
-      <c r="N218" s="4" t="n">
-        <v>178</v>
-      </c>
-      <c r="O218" s="4" t="inlineStr">
-        <is>
-          <t>Paleotoca de Urubici (URU-01-P2)</t>
-        </is>
-      </c>
-      <c r="P218" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
-        </is>
-      </c>
-      <c r="Q218" s="4" t="n">
-        <v>-27.9652</v>
-      </c>
-      <c r="R218" s="4" t="n">
-        <v>-49.5092</v>
-      </c>
-      <c r="S218" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>Plioceno–Pleistoceno</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
-        <is>
-          <t>Escavada na Fm. Taciba (Grupo Itararé, Permiano) — estrutura cenozóica</t>
-        </is>
-      </c>
-      <c r="C219" s="7" t="inlineStr">
-        <is>
-          <t>Megaichnus major (paleotoca de Doutor Pedrinho)</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — paleotoca (Xenarthra)</t>
-        </is>
-      </c>
-      <c r="E219" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F219" s="7" t="inlineStr">
-        <is>
-          <t>Paleotoca de Doutor Pedrinho, Doutor Pedrinho, SC</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr">
-        <is>
-          <t>Estrutura in situ (icnofóssil não coletável)</t>
-        </is>
-      </c>
-      <c r="H219" s="7" t="inlineStr">
-        <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
-        </is>
-      </c>
-      <c r="I219" s="6" t="inlineStr">
-        <is>
-          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
-        </is>
-      </c>
-      <c r="J219" s="6" t="inlineStr">
-        <is>
-          <t>Plioceno–Pleistoceno</t>
-        </is>
-      </c>
-      <c r="K219" s="7" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Paleotoca escavada no ARENITO DA FORMAÇÃO TACIBA (Permiano) — caso que ilustra bem a natureza destes icnofósseis: a estrutura é do Plioceno–Pleistoceno, mas a rocha escavada é ~270 milhões de anos mais antiga. Documentada por fotogrametria, com geração de modelo tridimensional.</t>
-        </is>
-      </c>
-      <c r="L219" s="7" t="inlineStr">
+      <c r="K220" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016).</t>
+        </is>
+      </c>
+      <c r="L220" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://www.researchgate.net/publication/365772145_Fotogrametria_de_um_icnofossil_escavado_por_preguicas-gigantes_Megaichnus_major</t>
-        </is>
-      </c>
-      <c r="M219" s="7" t="inlineStr"/>
-      <c r="N219" s="6" t="n">
-        <v>179</v>
-      </c>
-      <c r="O219" s="6" t="inlineStr">
-        <is>
-          <t>Paleotoca de Doutor Pedrinho</t>
-        </is>
-      </c>
-      <c r="P219" s="6" t="inlineStr">
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M220" s="5" t="inlineStr"/>
+      <c r="N220" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="O220" s="4" t="inlineStr">
+        <is>
+          <t>Paleotoca de Urubici (URU-01-P2)</t>
+        </is>
+      </c>
+      <c r="P220" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
         </is>
       </c>
-      <c r="Q219" s="6" t="n">
-        <v>-26.7217</v>
-      </c>
-      <c r="R219" s="6" t="n">
-        <v>-49.4794</v>
-      </c>
-      <c r="S219" s="6" t="inlineStr">
+      <c r="Q220" s="4" t="n">
+        <v>-27.9652</v>
+      </c>
+      <c r="R220" s="4" t="n">
+        <v>-49.5092</v>
+      </c>
+      <c r="S220" s="4" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>Depósitos cenozóicos / rochas sedimentares do Planalto Norte</t>
-        </is>
-      </c>
-      <c r="C220" s="5" t="inlineStr">
-        <is>
-          <t>Megaichnus isp. (paleotocas de Porto União)</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — paleotoca (Xenarthra)</t>
-        </is>
-      </c>
-      <c r="E220" s="4" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>Escavada na Fm. Taciba (Grupo Itararé, Permiano) — estrutura cenozóica</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>Megaichnus major (paleotoca de Doutor Pedrinho)</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>Paleotocas de Porto União, Porto União, SC</t>
-        </is>
-      </c>
-      <c r="G220" s="4" t="inlineStr">
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>Paleotoca de Doutor Pedrinho, Doutor Pedrinho, SC</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H220" s="5" t="inlineStr">
+      <c r="H221" s="7" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
         </is>
       </c>
-      <c r="I220" s="4" t="inlineStr">
+      <c r="I221" s="6" t="inlineStr">
         <is>
           <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
         </is>
       </c>
-      <c r="J220" s="4" t="inlineStr">
+      <c r="J221" s="6" t="inlineStr">
         <is>
           <t>Plioceno–Pleistoceno</t>
         </is>
       </c>
-      <c r="K220" s="5" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Conjunto de paleotocas do Planalto Norte catarinense, analisadas em conjunto com as de União da Vitória (PR), do outro lado do rio Iguaçu. Levantadas pelo método de amostragem em bola de neve (snowball sampling), com medição de altura e largura dos túneis.</t>
-        </is>
-      </c>
-      <c r="L220" s="5" t="inlineStr">
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Paleotoca escavada no ARENITO DA FORMAÇÃO TACIBA (Permiano) — caso que ilustra bem a natureza destes icnofósseis: a estrutura é do Plioceno–Pleistoceno, mas a rocha escavada é ~270 milhões de anos mais antiga. Documentada por fotogrametria, com geração de modelo tridimensional.</t>
+        </is>
+      </c>
+      <c r="L221" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://rsdjournal.org/rsd/article/view/19176</t>
-        </is>
-      </c>
-      <c r="M220" s="5" t="inlineStr"/>
-      <c r="N220" s="4" t="n">
+https://www.researchgate.net/publication/365772145_Fotogrametria_de_um_icnofossil_escavado_por_preguicas-gigantes_Megaichnus_major
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M221" s="7" t="inlineStr"/>
+      <c r="N221" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="O221" s="6" t="inlineStr">
+        <is>
+          <t>Paleotoca de Doutor Pedrinho</t>
+        </is>
+      </c>
+      <c r="P221" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+        </is>
+      </c>
+      <c r="Q221" s="6" t="n">
+        <v>-26.7217</v>
+      </c>
+      <c r="R221" s="6" t="n">
+        <v>-49.4794</v>
+      </c>
+      <c r="S221" s="6" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos cenozóicos / rochas sedimentares do Planalto Norte</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>Megaichnus isp. (paleotocas de Porto União)</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>Paleotocas de Porto União, Porto União, SC</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Conjunto de paleotocas do Planalto Norte catarinense, analisadas em conjunto com as de União da Vitória (PR), do outro lado do rio Iguaçu. Levantadas pelo método de amostragem em bola de neve (snowball sampling), com medição de altura e largura dos túneis.</t>
+        </is>
+      </c>
+      <c r="L222" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://rsdjournal.org/rsd/article/view/19176
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M222" s="5" t="inlineStr"/>
+      <c r="N222" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="O220" s="4" t="inlineStr">
+      <c r="O222" s="4" t="inlineStr">
         <is>
           <t>Paleotocas de Porto União</t>
         </is>
       </c>
-      <c r="P220" s="4" t="inlineStr">
+      <c r="P222" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
         </is>
       </c>
-      <c r="Q220" s="4" t="n">
+      <c r="Q222" s="4" t="n">
         <v>-26.2383</v>
       </c>
-      <c r="R220" s="4" t="n">
+      <c r="R222" s="4" t="n">
         <v>-51.0772</v>
       </c>
-      <c r="S220" s="4" t="inlineStr">
+      <c r="S222" s="4" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
         <is>
           <t>Depósitos litorâneos / lacustres</t>
         </is>
       </c>
-      <c r="C221" s="7" t="inlineStr">
+      <c r="C223" s="7" t="inlineStr">
         <is>
           <t>Tatu-gigante (Propraopus sp. / Glyptodon sp. — osteodermos)</t>
         </is>
       </c>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — Xenarthra (Cingulata)</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — mamífero</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F221" s="7" t="inlineStr">
+      <c r="F223" s="7" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC (localidades imprecisas)</t>
         </is>
       </c>
-      <c r="G221" s="6" t="inlineStr">
+      <c r="G223" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="7" t="inlineStr">
+      <c r="H223" s="7" t="inlineStr">
         <is>
           <t>Paula-Couto, C. (1980) — Anais ABC 52(3):527-531</t>
         </is>
       </c>
-      <c r="I221" s="6" t="inlineStr">
+      <c r="I223" s="6" t="inlineStr">
         <is>
           <t>Museu Nacional / UFRJ (coleção histórica)</t>
         </is>
       </c>
-      <c r="J221" s="6" t="inlineStr">
+      <c r="J223" s="6" t="inlineStr">
         <is>
           <t>ca. 2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K221" s="7" t="inlineStr">
-        <is>
-          <t>Primeiro registro de tatu-gigante para SC reportado por Paula-Couto (1980)</t>
-        </is>
-      </c>
-      <c r="L221" s="7" t="inlineStr">
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: Xenarthra (Cingulata). Primeiro registro de tatu-gigante para SC reportado por Paula-Couto (1980)</t>
+        </is>
+      </c>
+      <c r="L223" s="7" t="inlineStr">
         <is>
           <t>Artigo original (Paula-Couto, 1980, Anais ABC 52(3):527-531) não localizado em acesso direto
 citado em: https://www.academia.edu/15400290/Icnof%C3%B3sseis_paleotocas_e_crotovinas_atribu%C3%ADdos_a_mam%C3%ADferos_extintos_no_sudeste_e_sul_do_Brasil
 https://www.scielo.br/j/rbzool/a/3q86RZbNfRbQ7rBMCZHmSpP/?lang=pt</t>
         </is>
       </c>
-      <c r="M221" s="7" t="inlineStr">
+      <c r="M223" s="7" t="inlineStr">
         <is>
           <t>PAULA-COUTO, C. 1980. Pleistocene mammals from the state of Santa Catarina, Brazil. Anais da Academia Brasileira de Ciências, 52(3), 527–531. [Fonte primária — sem DOI, publicação pré-digital; localização no acesso via AABC]. Nota: artigo original não localizado em acesso aberto no levantamento desta base; citado em revisões subsequentes.</t>
         </is>
       </c>
-      <c r="N221" s="6" t="n">
+      <c r="N223" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="O221" s="6" t="inlineStr">
+      <c r="O223" s="6" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC</t>
         </is>
       </c>
-      <c r="P221" s="6" t="inlineStr">
+      <c r="P223" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q221" s="6" t="n">
+      <c r="Q223" s="6" t="n">
         <v>-28.95</v>
       </c>
-      <c r="R221" s="6" t="n">
+      <c r="R223" s="6" t="n">
         <v>-49.45</v>
       </c>
-      <c r="S221" s="6" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+      <c r="S223" s="6" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura cenozoica (paleotoca) — rocha encaixante não informada na fonte consultada</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>Paleotoca da Cavidade Linha Mimosa (icnofóssil de escavação de megafauna)</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Cavidade Linha Mimosa, zona rural de Lindóia do Sul, SC (coordenada do município; a da cavidade não foi identificada na fonte consultada)</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Budke, A., Lima, G.L. &amp; Carbonera, M. (2020) — "Análise de cavidades naturais presentes no oeste de Santa Catarina: um estudo de caso no município de Lindóia do Sul", Boletim Paranaense de Geociências 77:1–12</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>UFFS — Campus Chapecó</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>Pleistoceno</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Das três cavidades naturais investigadas na zona rural de Lindóia do Sul, os autores concluíram que a Cavidade Linha Mimosa é uma PALEOTOCA, esculpida por processos biogênicos de mamíferos da megafauna do Pleistoceno; as outras duas não foram atribuídas a megafauna. É o primeiro registro paleontológico do OESTE catarinense neste catálogo. RESSALVA: a fonte consultada publica coordenadas de duas das cavidades, mas não foi possível identificar qual corresponde à Linha Mimosa — usa-se a coordenada central do município.</t>
+        </is>
+      </c>
+      <c r="L224" s="5" t="inlineStr">
+        <is>
+          <t>https://rd.uffs.edu.br/bitstream/prefix/2879/1/BUDKE.pdf
+https://jornalgeograficouffs.wordpress.com/2020/09/02/um-estudo-sobre-cavidades-naturais/</t>
+        </is>
+      </c>
+      <c r="M224" s="5" t="inlineStr"/>
+      <c r="N224" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="O224" s="4" t="inlineStr">
+        <is>
+          <t>Linha Mimosa (Lindóia do Sul)</t>
+        </is>
+      </c>
+      <c r="P224" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — paleotoca cenozoica</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="n">
+        <v>-27.0268</v>
+      </c>
+      <c r="R224" s="4" t="n">
+        <v>-52.0515</v>
+      </c>
+      <c r="S224" s="4" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B225" s="6" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C222" s="5" t="inlineStr">
+      <c r="C225" s="7" t="inlineStr">
         <is>
           <t>Notiomastodon platensis (Ameghino, 1888)</t>
         </is>
       </c>
-      <c r="D222" s="4" t="inlineStr">
-        <is>
-          <t>Vertebrado — mastodonte (Proboscidea, Gomphotheriidae)</t>
-        </is>
-      </c>
-      <c r="E222" s="4" t="inlineStr">
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — mamífero</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F222" s="5" t="inlineStr">
+      <c r="F225" s="7" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (encontrado a ~23 m de profundidade, rede de arrasto)</t>
         </is>
       </c>
-      <c r="G222" s="4" t="inlineStr">
+      <c r="G225" s="6" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
         </is>
       </c>
-      <c r="H222" s="5" t="inlineStr">
+      <c r="H225" s="7" t="inlineStr">
         <is>
           <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024); nome atualizado segundo Mothé, D., Avilla, L.S., Cozzuol, M. &amp; Winck, G.R. (2012) — "Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands", Quaternary International 276–277:2–7</t>
         </is>
       </c>
-      <c r="I222" s="4" t="inlineStr">
+      <c r="I225" s="6" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J222" s="4" t="inlineStr">
+      <c r="J225" s="6" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K222" s="5" t="inlineStr">
-        <is>
-          <t>ATUALIZAÇÃO TAXONÔMICA: registro publicado originalmente como Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a nova combinação Notiomastodon platensis. Parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. Metade esquerda de mandíbula de macho adulto, achada por pescadores; espécie rara em SC, mais comum no RS; estimativa de ~5 m de comprimento e ~3,5 t</t>
-        </is>
-      </c>
-      <c r="L222" s="5" t="inlineStr">
+      <c r="K225" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: mastodonte (Proboscidea, Gomphotheriidae). ATUALIZAÇÃO TAXONÔMICA: registro publicado originalmente como Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a nova combinação Notiomastodon platensis. Parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. Metade esquerda de mandíbula de macho adulto, achada por pescadores; espécie rara em SC, mais comum no RS; estimativa de ~5 m de comprimento e ~3,5 t</t>
+        </is>
+      </c>
+      <c r="L225" s="7" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
 https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio
 https://www.sciencedirect.com/science/article/abs/pii/S1040618211002916</t>
         </is>
       </c>
-      <c r="M222" s="5" t="inlineStr">
+      <c r="M225" s="7" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N222" s="4" t="n">
+      <c r="N225" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="O222" s="4" t="inlineStr">
+      <c r="O225" s="6" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P222" s="4" t="inlineStr">
+      <c r="P225" s="6" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q222" s="4" t="n">
+      <c r="Q225" s="6" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R222" s="4" t="n">
+      <c r="R225" s="6" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S222" s="4" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="6" t="inlineStr">
+      <c r="S225" s="6" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B223" s="6" t="inlineStr">
+      <c r="B226" s="4" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C223" s="7" t="inlineStr">
+      <c r="C226" s="5" t="inlineStr">
         <is>
           <t>Lestodon armatus Gervais, 1855</t>
         </is>
       </c>
-      <c r="D223" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — preguiça-gigante (Xenarthra, Mylodontidae)</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>Vertebrado — mamífero</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F223" s="7" t="inlineStr">
+      <c r="F226" s="5" t="inlineStr">
         <is>
           <t>Plataforma continental entre Passo de Torres e Araranguá, SC (rede de arrasto de camarão)</t>
         </is>
       </c>
-      <c r="G223" s="6" t="inlineStr">
+      <c r="G226" s="4" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras, SC</t>
         </is>
       </c>
-      <c r="H223" s="7" t="inlineStr">
+      <c r="H226" s="5" t="inlineStr">
         <is>
           <t>Divulgação Museu Oceanográfico Univali (2022)</t>
         </is>
       </c>
-      <c r="I223" s="6" t="inlineStr">
+      <c r="I226" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J223" s="6" t="inlineStr">
+      <c r="J226" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K223" s="7" t="inlineStr">
-        <is>
-          <t>Pelo menos dois espécimes; primeiro registro da espécie em Santa Catarina; esqueleto montado é atração do Museu Oceanográfico Univali; estimativa de ~4,5 m de altura e ~3 t</t>
-        </is>
-      </c>
-      <c r="L223" s="7" t="inlineStr">
+      <c r="K226" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: preguiça-gigante (Xenarthra, Mylodontidae). Pelo menos dois espécimes; primeiro registro da espécie em Santa Catarina; esqueleto montado é atração do Museu Oceanográfico Univali; estimativa de ~4,5 m de altura e ~3 t</t>
+        </is>
+      </c>
+      <c r="L226" s="5" t="inlineStr">
         <is>
           <t>https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx</t>
         </is>
       </c>
-      <c r="M223" s="7" t="inlineStr">
+      <c r="M226" s="5" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional: UNIVALI. 2022. Esqueleto de Preguiça Gigante é atração no Museu Oceanográfico. Disponível em: https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N223" s="6" t="n">
+      <c r="N226" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="O223" s="6" t="inlineStr">
+      <c r="O226" s="4" t="inlineStr">
         <is>
           <t>Plataforma continental Passo de Torres–Araranguá</t>
         </is>
       </c>
-      <c r="P223" s="6" t="inlineStr">
+      <c r="P226" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q223" s="6" t="n">
+      <c r="Q226" s="4" t="n">
         <v>-29.28</v>
       </c>
-      <c r="R223" s="6" t="n">
+      <c r="R226" s="4" t="n">
         <v>-49.55</v>
       </c>
-      <c r="S223" s="6" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
+      <c r="S226" s="4" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
+      <c r="B227" s="6" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C224" s="5" t="inlineStr">
+      <c r="C227" s="7" t="inlineStr">
         <is>
           <t>Toxodon sp.</t>
         </is>
       </c>
-      <c r="D224" s="4" t="inlineStr">
-        <is>
-          <t>Vertebrado — toxodonte (Notoungulata, Toxodontidae)</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="inlineStr">
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — mamífero</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr">
+      <c r="F227" s="7" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (vértebra torácica, rede de arrasto)</t>
         </is>
       </c>
-      <c r="G224" s="4" t="inlineStr">
+      <c r="G227" s="6" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
         </is>
       </c>
-      <c r="H224" s="5" t="inlineStr">
+      <c r="H227" s="7" t="inlineStr">
         <is>
           <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024)</t>
         </is>
       </c>
-      <c r="I224" s="4" t="inlineStr">
+      <c r="I227" s="6" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J224" s="4" t="inlineStr">
+      <c r="J227" s="6" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K224" s="5" t="inlineStr">
-        <is>
-          <t>Vértebra torácica recuperada junto à mandíbula de Stegomastodon waringi; toxodontes são notoungulados de grande porte, descritos como morfologicamente convergentes com hipopótamos</t>
-        </is>
-      </c>
-      <c r="L224" s="5" t="inlineStr">
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: toxodonte (Notoungulata, Toxodontidae). Vértebra torácica recuperada junto à mandíbula de Stegomastodon waringi; toxodontes são notoungulados de grande porte, descritos como morfologicamente convergentes com hipopótamos</t>
+        </is>
+      </c>
+      <c r="L227" s="7" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
 https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
         </is>
       </c>
-      <c r="M224" s="5" t="inlineStr">
+      <c r="M227" s="7" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N224" s="4" t="n">
+      <c r="N227" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="O224" s="4" t="inlineStr">
+      <c r="O227" s="6" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P224" s="4" t="inlineStr">
+      <c r="P227" s="6" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q224" s="4" t="n">
+      <c r="Q227" s="6" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R224" s="4" t="n">
+      <c r="R227" s="6" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S224" s="4" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Pleistoceno–Holoceno</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="S227" s="6" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Pleistoceno Superior – Holoceno</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
         <is>
           <t>Planície costeira sul de SC (depósitos lagunares)</t>
         </is>
       </c>
-      <c r="C225" s="7" t="inlineStr">
+      <c r="C228" s="5" t="inlineStr">
         <is>
           <t>Registro paleoambiental (fitólitos, palinomorfos)</t>
         </is>
       </c>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>Microfóssil — material bioestratifráfico</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — fitólitos e palinomorfos</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F225" s="7" t="inlineStr">
+      <c r="F228" s="5" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio, SC</t>
         </is>
       </c>
-      <c r="G225" s="6" t="inlineStr">
+      <c r="G228" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H225" s="7" t="inlineStr">
+      <c r="H228" s="5" t="inlineStr">
         <is>
           <t>SBP Boletim nº 63 (resumo)</t>
         </is>
       </c>
-      <c r="I225" s="6" t="inlineStr">
+      <c r="I228" s="4" t="inlineStr">
         <is>
           <t>UFRGS / UNISINOS</t>
         </is>
       </c>
-      <c r="J225" s="6" t="inlineStr">
+      <c r="J228" s="4" t="inlineStr">
         <is>
           <t>ca. 12.000 – 3.000 a</t>
         </is>
       </c>
-      <c r="K225" s="7" t="inlineStr">
-        <is>
-          <t>Indicadores de paleoníveis marinhos holocênicos na planície costeira</t>
-        </is>
-      </c>
-      <c r="L225" s="7" t="inlineStr">
+      <c r="K228" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: material bioestratigráfico. Indicadores de paleoníveis marinhos holocênicos na planície costeira</t>
+        </is>
+      </c>
+      <c r="L228" s="5" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/344329477_RECONSTITUICAO_PALEOAMBIENTAL_ATRAVES_DE_FITOLITOS_NO_SAMBAQUI_CASA_DE_PEDRA_SAO_FRANCISCO_DO_SUL-SC_BRASIL</t>
         </is>
       </c>
-      <c r="M225" s="7" t="inlineStr">
+      <c r="M228" s="5" t="inlineStr">
         <is>
           <t>MENEZES, J.B.; GARCIA, M.J.; SOUSA, S.H.M.; ANDRADE, P.C.; MAHIQUES, M.M. 2009. Dinoflagelados quaternários da plataforma de Itajaí, Estado de Santa Catarina. In: Resumos, XX Congresso Brasileiro de Paleontologia (PALEO 2009). Boletim Informativo da Sociedade Brasileira de Paleontologia, 63, pp. 9–10. [Fonte primária — publicação em anais de evento; não indexada em periódico com DOI]. Disponível em: https://sbpbrasil.org/?mdocs-file=489</t>
         </is>
       </c>
-      <c r="N225" s="6" t="n">
+      <c r="N228" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="O225" s="6" t="inlineStr">
+      <c r="O228" s="4" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio</t>
         </is>
       </c>
-      <c r="P225" s="6" t="inlineStr">
+      <c r="P228" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q225" s="6" t="n">
+      <c r="Q228" s="4" t="n">
         <v>-29.1133</v>
       </c>
-      <c r="R225" s="6" t="n">
+      <c r="R228" s="4" t="n">
         <v>-49.6306</v>
       </c>
-      <c r="S225" s="6" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+      <c r="S228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>Depósitos superficiais sobre a Fm. Rio Bonito / Depressão da Zona Carbonífera Catarinense</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
+      <c r="C229" s="7" t="inlineStr">
         <is>
           <t>Paleotoca (icnofóssil de escavação — Xenarthra: tatus, preguiças, tamanduás)</t>
         </is>
       </c>
-      <c r="D226" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — estrutura de habitação (Domichnia)</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F226" s="5" t="inlineStr">
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>Lauro Müller, SC</t>
         </is>
       </c>
-      <c r="G226" s="4" t="inlineStr">
+      <c r="G229" s="6" t="inlineStr">
         <is>
           <t>UDESC — Laboratório de Geografia/Geologia (FAED)</t>
         </is>
       </c>
-      <c r="H226" s="5" t="inlineStr">
+      <c r="H229" s="7" t="inlineStr">
         <is>
           <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
         </is>
       </c>
-      <c r="I226" s="4" t="inlineStr">
+      <c r="I229" s="6" t="inlineStr">
         <is>
           <t>UDESC</t>
         </is>
       </c>
-      <c r="J226" s="4" t="inlineStr">
+      <c r="J229" s="6" t="inlineStr">
         <is>
           <t>2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K226" s="5" t="inlineStr">
-        <is>
-          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. 1º registro documentado deste tipo de icnofóssil em rochas da Fm. Rio Bonito e na Depressão da Zona Carbonífera Catarinense; estrutura de habitação distinta das paleotocas já catalogadas no Geoparque Caminhos dos Cânions do Sul</t>
-        </is>
-      </c>
-      <c r="L226" s="5" t="inlineStr">
+      <c r="K229" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. 1º registro documentado deste tipo de icnofóssil em rochas da Fm. Rio Bonito e na Depressão da Zona Carbonífera Catarinense; estrutura de habitação distinta das paleotocas já catalogadas no Geoparque Caminhos dos Cânions do Sul</t>
+        </is>
+      </c>
+      <c r="L229" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
 https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
-https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
-        </is>
-      </c>
-      <c r="M226" s="5" t="inlineStr">
+https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+        </is>
+      </c>
+      <c r="M229" s="7" t="inlineStr">
         <is>
           <t>VALDATI, J. et al. 2025. Identificação de paleotoca em Lauro Müller, SC. Nota técnica/divulgação institucional, UDESC FAEd. [Fonte secundária — publicação científica indexada não localizada no levantamento desta base]. Disponível em: https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller</t>
         </is>
       </c>
-      <c r="N226" s="4" t="n">
+      <c r="N229" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="O226" s="4" t="inlineStr">
+      <c r="O229" s="6" t="inlineStr">
         <is>
           <t>Lauro Müller</t>
         </is>
       </c>
-      <c r="P226" s="4" t="inlineStr">
+      <c r="P229" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Rio Bonito</t>
         </is>
       </c>
-      <c r="Q226" s="4" t="n">
+      <c r="Q229" s="6" t="n">
         <v>-28.4047</v>
       </c>
-      <c r="R226" s="4" t="n">
+      <c r="R229" s="6" t="n">
         <v>-49.3811</v>
       </c>
-      <c r="S226" s="4" t="inlineStr">
+      <c r="S229" s="6" t="inlineStr">
         <is>
           <t>10.4072/rbp.2009.3.07</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B227" s="6" t="inlineStr">
+      <c r="B230" s="4" t="inlineStr">
         <is>
           <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
         </is>
       </c>
-      <c r="C227" s="7" t="inlineStr">
+      <c r="C230" s="5" t="inlineStr">
         <is>
           <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
         </is>
       </c>
-      <c r="D227" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — gastrópode incrustante</t>
-        </is>
-      </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>Invertebrado — gastrópode</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F227" s="7" t="inlineStr">
+      <c r="F230" s="5" t="inlineStr">
         <is>
           <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
         </is>
       </c>
-      <c r="G227" s="6" t="inlineStr">
+      <c r="G230" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="H230" s="5" t="inlineStr">
         <is>
           <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — "Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages", Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
         </is>
       </c>
-      <c r="I227" s="6" t="inlineStr">
+      <c r="I230" s="4" t="inlineStr">
         <is>
           <t>IGc-USP; UFPR</t>
         </is>
       </c>
-      <c r="J227" s="6" t="inlineStr">
+      <c r="J230" s="4" t="inlineStr">
         <is>
           <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
         </is>
       </c>
-      <c r="K227" s="7" t="inlineStr">
-        <is>
-          <t>Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
-        </is>
-      </c>
-      <c r="L227" s="7" t="inlineStr">
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: gastrópode incrustante. Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
+        </is>
+      </c>
+      <c r="L230" s="5" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio075/sitio075.pdf
 https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
         </is>
       </c>
-      <c r="M227" s="7" t="inlineStr"/>
-      <c r="N227" s="6" t="n">
+      <c r="M230" s="5" t="inlineStr"/>
+      <c r="N230" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="O227" s="6" t="inlineStr">
+      <c r="O230" s="4" t="inlineStr">
         <is>
           <t>Costões Laguna–Imbituba</t>
         </is>
       </c>
-      <c r="P227" s="6" t="inlineStr">
+      <c r="P230" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
         </is>
       </c>
-      <c r="Q227" s="6" t="n">
+      <c r="Q230" s="4" t="n">
         <v>-28.42</v>
       </c>
-      <c r="R227" s="6" t="n">
+      <c r="R230" s="4" t="n">
         <v>-48.74</v>
       </c>
-      <c r="S227" s="6" t="inlineStr"/>
+      <c r="S230" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S227"/>
+  <autoFilter ref="A3:S230"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -19934,7 +20201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -24645,16 +24912,20 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="9" t="n"/>
+      <c r="B441" s="9" t="n"/>
+    </row>
     <row r="442">
-      <c r="A442" s="10" t="inlineStr">
+      <c r="A442" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B442" s="9" t="inlineStr"/>
+      <c r="B442" s="9" t="n"/>
     </row>
     <row r="443">
-      <c r="A443" s="11" t="inlineStr">
+      <c r="A443" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -24666,7 +24937,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="11" t="inlineStr">
+      <c r="A444" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -24678,7 +24949,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="11" t="inlineStr">
+      <c r="A445" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -24690,7 +24961,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="11" t="inlineStr">
+      <c r="A446" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -24702,7 +24973,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="11" t="inlineStr">
+      <c r="A447" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -24714,7 +24985,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="11" t="inlineStr">
+      <c r="A448" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -24726,12 +24997,680 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="11" t="inlineStr">
+      <c r="A449" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="n"/>
+      <c r="B450" s="9" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B451" s="9" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B452" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B454" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B455" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B456" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B457" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B458" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="n"/>
+      <c r="B459" s="9" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B460" s="9" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B461" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B462" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B463" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B464" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B465" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B466" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B467" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="n"/>
+      <c r="B468" s="9" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B469" s="9" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B470" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B471" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B472" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B473" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B474" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B475" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B476" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="9" t="n"/>
+      <c r="B477" s="9" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B478" s="9" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B479" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B480" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B481" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B482" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B483" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B484" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B485" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="9" t="n"/>
+      <c r="B486" s="9" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B487" s="9" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B488" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B489" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B490" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B491" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B492" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B493" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B494" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="9" t="n"/>
+      <c r="B495" s="9" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B496" s="9" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B497" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B498" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B499" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B500" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B501" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B502" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B503" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B505" s="9" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B506" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B507" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B508" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B509" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B510" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B511" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B512" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Zucatti da Rosa, A.L. (2005, 2006) — "Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC", Dissertação de Mestrado, Programa de Pós-Graduação em Geologia, UNISINOS; Da Rosa et al. (1997); Sanchez et al. (2010) — Sedimentary Geology</t>
+          <t>Zucatti da Rosa, A.L. (2005, 2006) — "Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC", Dissertação de Mestrado, Programa de Pós-Graduação em Geologia, UNISINOS; Da Rosa et al. (1997); Guadagnin, F. et al. (2010) — "Depositional age and provenance of the Itajaí Basin, Santa Catarina State, Brazil: Implications for SW Gondwana correlation", Precambrian Research (idade deposicional entre 563 ± 3 e 549 ± 4 Ma)</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Disco basal ediacarano amplamente documentado na Bacia do Itajaí; um dos fósseis-chave (junto com Charniodiscus e Cyclomedusa) usados para confirmar idade ediacarana dos sedimentos por correlação com a Bacia de Avalon HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre.</t>
+          <t>Disco basal ediacarano amplamente documentado na Bacia do Itajaí; um dos fósseis-chave (junto com Charniodiscus e Cyclomedusa) usados para confirmar idade ediacarana dos sedimentos por correlação com a Bacia de Avalon HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. CORREÇÃO (2026.09.9): a referência de 2010 estava registrada como "Sanchez et al. — Sedimentary Geology", que não corresponde ao trabalho do link; o correto é Guadagnin et al. (2010), Precambrian Research.</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1756,7 +1756,11 @@
       <c r="R16" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1796,7 +1800,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1811,12 +1815,12 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Nova icnoespécie descrita para os ritmitos de Trombudo Central, distinta de Gluckstadella cooperi (já registrada no Campáleo)</t>
+          <t>Nova icnoespécie descrita para os ritmitos de Trombudo Central, distinta de Gluckstadtella cooperi Savage, 1971, registrada na pedreira de Águas Claras, Rio do Sul (registro nº 014)</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1843,7 +1847,11 @@
       <c r="R17" s="6" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S17" s="6" t="inlineStr"/>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1883,7 +1891,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -1930,7 +1938,11 @@
       <c r="R18" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1970,7 +1982,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1990,7 +2002,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -2017,7 +2029,11 @@
       <c r="R19" s="6" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S19" s="6" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2057,7 +2073,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2077,7 +2093,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2104,7 +2120,11 @@
       <c r="R20" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -3349,7 +3369,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Gluckstadella cooperi</t>
+          <t>Gluckstadtella cooperi Savage, 1971</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -3389,7 +3409,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Impressão de repouso de artrópode. Savage (1971) a descreveu nos ritmitos periglaciais do Grupo Dwyka (Bacia do Karoo, África do Sul) e a interpretou como impressão de crustáceos sincarídeos ou pericarídeos. Na pedreira de Águas Claras, a assembleia é dominada por trilhas de moluscos e por pistas de crustáceos e merostomados, preservadas como subimpressões (Gandini, Netto &amp; Souza, 2007). CORREÇÃO (2026.09.9): o nome estava grafado "Gluckstadella", sem o "t", e sem autoria.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -3922,7 +3942,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300031</t>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
@@ -4005,7 +4025,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300031</t>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr"/>
@@ -4088,7 +4108,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300031</t>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
@@ -4151,7 +4171,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -4171,7 +4191,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300031</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr"/>
@@ -4194,7 +4214,11 @@
       <c r="R44" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S44" s="4" t="inlineStr"/>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4234,7 +4258,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -4254,7 +4278,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300031</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
@@ -4277,7 +4301,11 @@
       <c r="R45" s="6" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4317,7 +4345,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -4337,7 +4365,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr"/>
@@ -4360,7 +4388,11 @@
       <c r="R46" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -4503,7 +4535,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031018208006135
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
@@ -4527,7 +4559,11 @@
       <c r="R48" s="4" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4587,7 +4623,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031018208006135
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
@@ -4611,7 +4647,11 @@
       <c r="R49" s="6" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4671,7 +4711,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0031018208006135
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
@@ -4695,7 +4735,11 @@
       <c r="R50" s="4" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S50" s="4" t="inlineStr"/>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -8141,7 +8185,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Análise palinológica do Afloramento Campáleo — Review of Palaeobotany and Palynology (2023)</t>
+          <t>"Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana", Sedimentary Geology (2023)</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -8156,7 +8200,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade.</t>
+          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade. IDADE: o trabalho situa o Campáleo perto do limite Carbonífero–Permiano, provavelmente no Gzheliano (fim do Carbonífero); outras fontes o posicionam no início do Permiano — a idade do afloramento segue em discussão. CORREÇÃO (2026.09.9): a revista estava registrada como Review of Palaeobotany and Palynology.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -18893,7 +18937,6 @@
         <is>
           <t>https://doi.org/10.4072/rbp.2009.3.07
 https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 (More than fossils: Paleoburrows as geoheritage...)
 https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Proposta de classificação das paleotocas)
 https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
 https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
@@ -20201,7 +20244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -25584,16 +25627,20 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="9" t="n"/>
+      <c r="B504" s="9" t="n"/>
+    </row>
     <row r="505">
-      <c r="A505" s="10" t="inlineStr">
+      <c r="A505" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B505" s="9" t="inlineStr"/>
+      <c r="B505" s="9" t="n"/>
     </row>
     <row r="506">
-      <c r="A506" s="11" t="inlineStr">
+      <c r="A506" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -25605,7 +25652,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="11" t="inlineStr">
+      <c r="A507" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -25617,7 +25664,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="11" t="inlineStr">
+      <c r="A508" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -25629,7 +25676,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="11" t="inlineStr">
+      <c r="A509" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -25641,7 +25688,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="11" t="inlineStr">
+      <c r="A510" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -25653,7 +25700,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="11" t="inlineStr">
+      <c r="A511" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -25665,12 +25712,296 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="11" t="inlineStr">
+      <c r="A512" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="9" t="n"/>
+      <c r="B513" s="9" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B514" s="9" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B515" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B516" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B517" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B518" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B519" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B520" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B521" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="9" t="n"/>
+      <c r="B522" s="9" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B523" s="9" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B524" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B525" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B526" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B527" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B528" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B529" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B530" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B532" s="9" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B533" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B534" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B535" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B536" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B537" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B538" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -3452,67 +3452,70 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Icnofauna do Afloramento Campo da Lança (8 icnogêneros)</t>
+          <t>Palaeoniscidae / Actinopterygii basais (ictiofauna do Campáleo)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Vertebrado — peixes</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CP.V 5202a (exemplar figurado por Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Malabarba, M.C.S.L. (1988); Richter, M. (1991); Hamel, M.-H. (2005)</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>FURB; UNISINOS; UFU</t>
+          <t>CENPALEO/UnC; Uppsala Univ. (colaboração)</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Assembleia com oito icnogêneros reconhecidos no siltito do Campo da Lança, incluindo Protichnites, Rusophycus, Thalassinoides, Diplocraterion e Rhizocorallium. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+          <t>Classificação: peixe actinopterígio basal (paleoniscídeo). Pelo menos duzentos exemplares completos de actinopterígios basais, jovens e adultos, são conhecidos do afloramento — preservados sem compressão em concreções fosfáticas ou achatados no folhelho (Hamel, 2005). As espécies nomeadas estão em registros próprios. CORREÇÃO (2026.09.10): a ficha citava "Figueroa et al. (2025)" e a preservação de "coração", sem fonte, e apontava para o artigo de outra localidade; os morfotipos com encéfalo preservado estão no registro nº 098. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr"/>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>RICHTER, M. 1991. Itacanthus fasciatus n. sp., a palaeonisciform fish from the Lower Permian Lontras Shale of Santa Catarina State, Brazil. Journal of Vertebrate Paleontology, 11(4), 418–430. DOI: 10.1080/02724634.1991.10011414 [Fonte primária]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2 | FIGUEROA, R.T. et al. 2025. [Referência completa não localizada no levantamento desta base — citada em: Researchgate/348390467]</t>
+        </is>
+      </c>
       <c r="N36" s="4" t="n">
-        <v>196</v>
+        <v>15</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
@@ -3521,14 +3524,14 @@
         </is>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>-26.1112</v>
+        <v>-26.1583</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>-49.805</v>
+        <v>-49.8147</v>
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+          <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
@@ -3540,67 +3543,71 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Rusophycus cf. carbonarius Dawson (traço de repouso de artrópode)</t>
+          <t>Chondrichthyes indet. (2 dentes)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Vertebrado — peixes</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — dentes isolados (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+          <t>Pauliv, V.E., Dias, E.V., Sedor, F.A., Weinschütz, L.C. &amp; Ribeiro, A.M. (2023) — Revista Brasileira de Paleontologia 26(3):227–237</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>FURB; UNISINOS; UFU</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Traço de repouso atribuído a artrópode, reconhecido nas assembleias do Grupo Itararé catarinense. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+          <t>Classificação: condrictio. Dois dentes isolados adicionais atribuídos a condrictios indeterminados UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr"/>
+          <t>https://sbpbrasil.org/publications/index.php/rbp/article/view/327
+https://www.researchgate.net/publication/374930987_A_new_symmoriiform_shark_and_other_chondrichthyan_teeth_from_the_earliest_Permian_of_southern_Brazil</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
+        </is>
+      </c>
       <c r="N37" s="6" t="n">
-        <v>197</v>
+        <v>18</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -3609,14 +3616,14 @@
         </is>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>-26.1112</v>
+        <v>-26.1583</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>-49.805</v>
+        <v>-49.8147</v>
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+          <t>10.4072/rbp.2023.3.07</t>
         </is>
       </c>
     </row>
@@ -3628,67 +3635,70 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Protichnites isp. (pista de artrópode)</t>
+          <t>Crossopterygii (celacanto) — morfotipos de escamas</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Vertebrado — peixes</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — séries de escamas (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+          <t>Weinschütz et al. (vários); registros em nova localidade SC (Researchgate 2021)</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>FURB; UNISINOS; UFU</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Pista de artrópode recorrente nas icnocenoses do Grupo Itararé em Santa Catarina. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+          <t>Classificação: peixe de nadadeira lobada. Pelo menos 3 morfotipos de escamas distintos dos conhecidos para o Paleozoico da Bacia do Paraná UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr"/>
+          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
       <c r="N38" s="4" t="n">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>Afloramento Campo da Lança</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3697,16 +3707,12 @@
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>-26.1112</v>
+        <v>-26.1583</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S38" s="4" t="inlineStr">
-        <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
-        </is>
-      </c>
+        <v>-49.8147</v>
+      </c>
+      <c r="S38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -3716,67 +3722,72 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Icnofauna do Afloramento Bela Vista do Sul</t>
+          <t>Anthracoblattina mendesi Pinto &amp; Sedor, 2000</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — inseto (Blattodea)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CP/E 3755b (exemplar em concreção, figurado por Mouro et al., 2020), entre outros</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322</t>
+          <t>Pinto, I.D. &amp; Sedor, F.A. (2000) — descrição original; Ricetti, J.H.Z. et al. (2016) — "Anthracoblattina mendesi Pinto &amp; Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach", Revista Brasileira de Paleontologia 19(2):181–194</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>FURB; UNISINOS; UFU</t>
+          <t>CENPALEO/UnC; UFPR</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Ritmitos síltico-argilosos gradando a síltico-arenosos rumo ao topo, com acamamento ondulado. A icnofauna reúne Cruziana, Diplichnites, Diplopodichnus, Lockeia, Protovirgularia e Rusophycus. Topo da Fm. Rio do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+          <t>Blattodea paleozoico mais completo descrito na América do Sul; piritização excepcional Corresponde a cerca de 54% dos mais de cem insetos do afloramento (Mouro et al., 2020). O exemplar CP/E 3755b, preservado em concreção, conserva o padrão epicuticular da asa. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr"/>
+          <t>https://doi.org/10.22456/1807-9806.20189
+https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach
+https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>PINTO, I.D.; SEDOR, F.A. 2000. Anthracoblattina mendesi sp. nov. (Blattodea, Phyloblattidae), uma nova barata fóssil do Permocarbonífero brasileiro. Pesquisas em Geociências, 27(1), 41–48. [Fonte primária — verificar volume/paginação em repositório IGeo-UFRGS] | RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf</t>
+        </is>
+      </c>
       <c r="N39" s="6" t="n">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>Afloramento Bela Vista do Sul</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -3785,16 +3796,12 @@
         </is>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>-26.1112</v>
+        <v>-26.1583</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
-        </is>
-      </c>
+        <v>-49.8147</v>
+      </c>
+      <c r="S39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3804,67 +3811,70 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Lockeia siliquaria (traço de repouso de bivalve)</t>
+          <t>Braquiópodes indet. (Brachiopoda)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — braquiópode</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322</t>
+          <t>Weinschütz et al. (vários)</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>FURB; UNISINOS; UFU</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Traço de repouso produzido por bivalve, componente da icnofauna de Bela Vista do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+          <t>Presente na biota geral do Folhelho Lontras; detalhes taxonômicos em estudos em andamento UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr"/>
+          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
       <c r="N40" s="4" t="n">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>Afloramento Bela Vista do Sul</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3873,16 +3883,12 @@
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>-26.1112</v>
+        <v>-26.1583</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S40" s="4" t="inlineStr">
-        <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
-        </is>
-      </c>
+        <v>-49.8147</v>
+      </c>
+      <c r="S40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -3892,17 +3898,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Neonereites isp.</t>
+          <t>?Demospongiae indet. (possível demosponja)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — esponja</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3912,46 +3918,50 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>New York State Museum (amostra coletada por E. P. de Oliveira, 1927)</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D. (2017) — Tese de Doutorado, UFRJ</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Escavação rasa que complementa a assembleia dominada por pistas de artrópodes. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Classificação: esponja. Possível demosponja descrita por Mouro (2017) a partir de amostra coletada por Oliveira em 1927 e guardada no New York State Museum. Corresponde à tafofácies T2 de Mouro et al. (2017): esponjas achatadas, com espículas soltas, substituídas sobretudo por pirita — distinta da tafofácies T1, das hexactinélidas. A atribuição a Demospongiae é dada como possível pelos autores. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="inlineStr"/>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
       <c r="N41" s="6" t="n">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -3960,12 +3970,16 @@
         </is>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>-27.305</v>
+        <v>-26.1583</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>-49.795</v>
-      </c>
-      <c r="S41" s="6" t="inlineStr"/>
+        <v>-49.8147</v>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3975,66 +3989,70 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Gluckstadtella isp.</t>
+          <t>Restos vegetais (fragmentos)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Flora — restos indeterminados</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+          <t>Weinschütz et al.</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Escavação rasa presente na assembleia da Fm. Rio do Sul em Trombudo Central. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Fragmentos de plantas presentes na biota geral do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr"/>
+          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
       <c r="N42" s="4" t="n">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -4043,10 +4061,10 @@
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>-27.305</v>
+        <v>-26.1583</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>-49.795</v>
+        <v>-49.8147</v>
       </c>
       <c r="S42" s="4" t="inlineStr"/>
     </row>
@@ -4058,66 +4076,70 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Rusophycus isp. (Pedreira Itaú-Itaúna)</t>
+          <t>Coprólitos (Coprolita espiralada)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Icnofóssil — coprólito</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+          <t>Weinschütz et al.</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Traço de repouso de artrópode, componente menos frequente da assembleia. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Coprólitos espiralados atribuídos a peixes UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr"/>
+          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
       <c r="N43" s="6" t="n">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -4126,10 +4148,10 @@
         </is>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>-27.305</v>
+        <v>-26.1583</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>-49.795</v>
+        <v>-49.8147</v>
       </c>
       <c r="S43" s="6" t="inlineStr"/>
     </row>
@@ -4141,17 +4163,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Icnofauna da Pedreira Waltrick</t>
+          <t>Orbiculoidea guaraunensis Oliveira, 1930</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — braquiópode</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4161,46 +4183,51 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Pedreira Waltrick, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+          <t>Oliveira, E.P. (1930) — "Fósseis marinhos na Série Itararé no Estado de Santa Catharina", Anais da Academia Brasileira de Ciências 2(1):17–21; Carvalho et al. (1942); Ricetti, J.H.Z. et al. (2016) — RBP 19(2):181–194</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Terceira pedreira de ritmitos estudada na área de Trombudo Central (UTM 620026/6981727), ao lado de Itaú-Itaúna e Fama. Integra o conjunto de afloramentos que documenta a icnofauna dos depósitos de deglaciação da Fm. Rio do Sul. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr"/>
+          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
+https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+        </is>
+      </c>
       <c r="N44" s="4" t="n">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>Pedreira Waltrick</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -4209,16 +4236,12 @@
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>-27.305</v>
+        <v>-26.1583</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>-49.795</v>
-      </c>
-      <c r="S44" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
+        <v>-49.8147</v>
+      </c>
+      <c r="S44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4228,66 +4251,72 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Icnofauna da Pedreira Fama</t>
+          <t>Insecta — Blattodea e Grylloblattodea (morfotipos além de Anthracoblattina mendesi)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — inseto</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Pedreira Fama, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Martins-Neto, R.G. (2005); Ricetti, J.H.Z. et al. (2016) — Revista Brasileira de Paleontologia 19(2):181–194</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Pedreira de ritmitos (UTM 619813/6981938) estudada em conjunto com Itaú-Itaúna e Waltrick, compondo o registro icnológico dos depósitos de deglaciação do topo do Grupo Itararé. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Classificação: inseto. Mouro et al. (2020) registram mais de cem espécimes de insetos no afloramento, atribuídos às ordens Blattodea e Grylloblattodea; cerca de 54% pertencem a Anthracoblattina mendesi (registro nº 020). Preservação de dois tipos: compressões carbonosas ou piritizadas, e formas tridimensionais fosfatizadas — algumas com possível tecido muscular preservado, como no espécime CP.I 2276b (articulação fêmur-tíbia). UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr"/>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
+https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+        </is>
+      </c>
       <c r="N45" s="6" t="n">
-        <v>205</v>
+        <v>42</v>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>Pedreira Fama</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
@@ -4296,14 +4325,14 @@
         </is>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>-27.305</v>
+        <v>-26.1583</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>-49.795</v>
+        <v>-49.8147</v>
       </c>
       <c r="S45" s="6" t="inlineStr">
         <is>
-          <t>10.1016/j.jsames.2015.07.008</t>
+          <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
@@ -4315,17 +4344,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Protovirgularia dichotoma</t>
+          <t>Ammonoidea indet. (afim. Uraloceras)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — invertebrado</t>
+          <t>Invertebrado — cefalópode (amonite)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4335,3716 +4364,3693 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Pedreiras de ritmitos, Trombudo Central, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Coleções UNISINOS / UFRGS</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>UNISINOS; UFRGS</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>ca. 300–295 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Traço de locomoção produzido pelo pé de um bivalve. Completa as DEZ icnoespécies reconhecidas por Lima et al. (2015) nos ritmitos de Trombudo Central: Cruziana problematica, Diplichnites gouldi, Diplopodichnus biformis, Glaciichnium liebegastensis, Gluckstadtella elongata, Helminthoidichnites tenuis, Mermia carickensis, Protovirgularia dichotoma, Treptichnus pollardi e Umfolozia sinuosa — todas agora presentes neste catálogo.</t>
+          <t>Pelo menos duas conchas comprimidas e não identificadas em nível específico; preservadas como filme carbonoso/pirita, sem carbonato de cálcio original; afinidade morfológica com Uraloceras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>Pedreira Itaú-Itaúna</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>-27.305</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>-49.795</v>
-      </c>
-      <c r="S46" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / formações Campo Mourão e Taciba</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Icnofósseis indet. de sistema de fiorde (Presidente Getúlio)</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Afloramentos da região de Presidente Getúlio, SC</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Não informado na fonte consultada</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>Oliveira, V.G. (2019) — "Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina", Trabalho de Conclusão de Curso, Geologia, UFSC</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>UFSC</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>Traços fósseis reconhecidos nas formações Campo Mourão e Taciba, em sucessão de 17 litofácies agrupadas em cinco associações que definem subambientes de um amplo SISTEMA DE FIORDE, ligados a ciclos de transgressão–regressão glacio-influenciados. O tamanho reduzido dos traços e a baixa diversidade, em comparação com o esperado para ambientes plenamente marinhos, são justamente o argumento paleoambiental que sustenta a interpretação de fiorde. RESSALVA: o trabalho é de natureza estratigráfica e não identifica os icnofósseis em nível icnotaxonômico — o registro consta como ocorrência, não como táxon determinado.</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>https://repositorio.ufsc.br/handle/123456789/204084</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="6" t="n">
-        <v>207</v>
-      </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>Região de Presidente Getúlio</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v>-27.0453</v>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v>-49.6231</v>
-      </c>
-      <c r="S47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Mafra</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Hormosiroidea meandrica (Fazenda Potreiro)</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>CP/P (coleção CENPALEO)</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>UNISINOS; CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Icnoespécie proposta como nova por Balistieri e colaboradores (2002–2003) a partir dos ritmitos da região de Mafra (SC) e Rio Negro (PR). ATENÇÃO: a fonte consultada não permite afirmar em qual dos afloramentos — o catarinense ou o paranaense — está o material-tipo; por isso esta ficha NÃO a trata como localidade-tipo. Escavação meandrante rasa, preservada sobretudo como crista hipicnial. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="n">
-        <v>-26.1112</v>
-      </c>
-      <c r="R48" s="4" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S48" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.palaeo.2008.10.028</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Mafra</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Undichna consulca</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — vertebrado (trilha de nadadeira de peixe)</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>UNISINOS; CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>Trilha deixada pela nadadeira de um PEIXE ao roçar o fundo lamoso — um dos raros registros de atividade de vertebrado na icnofauna do Grupo Itararé catarinense. Aparece recoberta por trilhas de Diplichnites gouldi, em preservação palimpséstica. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="6" t="n">
-        <v>219</v>
-      </c>
-      <c r="O49" s="6" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro</t>
-        </is>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v>-26.1112</v>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S49" s="6" t="inlineStr">
-        <is>
-          <t>10.1016/j.palaeo.2008.10.028</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Mafra</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Gordia arcuata e Gordia marina</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>UNISINOS; CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Escavações de pastagem finas e sinuosas, componentes da suíte de escavações rasas dos ritmitos lacustres. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
-https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="O50" s="4" t="inlineStr">
-        <is>
-          <t>Fazenda Potreiro</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>-26.1112</v>
-      </c>
-      <c r="R50" s="4" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S50" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.palaeo.2008.10.028</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Escavações tipo Gyrolithes (Gyrolithes-like burrows)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Netto, R.G. et al. (2007) — Revista Brasileira de Paleontologia 10(3):157–168; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>FURB; UNISINOS; UFU</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>Escavações helicoidais semelhantes a Gyrolithes, parte da suíte Glossifungites do Campo da Lança, junto a Thalassinoides, Diplocraterion e ?Rhizocorallium. Indicam colonização de substrato firme exumado por erosão transgressiva. Nos depósitos eopermianos das formações Rio do Sul e Rio Bonito, essas formas ocorrem sempre em suítes de substrato firme. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>https://www.sbpbrasil.org/revista/edicoes/10_3/netto.pdf</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="6" t="n">
-        <v>224</v>
-      </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campo da Lança</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v>-26.1112</v>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S51" s="6" t="inlineStr">
-        <is>
-          <t>10.5212/TerraPlural.v.15.2118322.039</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Actinopterygii indet. (paleoniscídeos) — morfotipo 1</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Vertebrado — peixes</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — séries de espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Richter, M. (1991); Hamel, M.-H. (2005); Figueroa, R.T. et al. (2025) — actinopterígios do Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC; Uppsala Univ. (colaboração)</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: peixe ósseo. Lagerstätte; preserva tecidos moles (cérebro, nervos, coração) via micro-CT</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>RICHTER, M. 1991. Itacanthus fasciatus n. sp., a palaeonisciform fish from the Lower Permian Lontras Shale of Santa Catarina State, Brazil. Journal of Vertebrate Paleontology, 11(4), 418–430. DOI: 10.1080/02724634.1991.10011414 [Fonte primária]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2 | FIGUEROA, R.T. et al. 2025. [Referência completa não localizada no levantamento desta base — citada em: Researchgate/348390467]</t>
-        </is>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O52" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R52" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Actinopterygii indet. — morfotipo 2</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — peixes</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — séries de espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>Richter, M. (1991); Hamel, M.-H. (2005); Figueroa, R.T. et al. (2025) — actinopterígios do Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe ósseo. Duas espécies distintas identificadas por micro-CT; consideradas inéditas na filogenia de actinopterígios</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>RICHTER, M. 1991. Itacanthus fasciatus n. sp., a palaeonisciform fish from the Lower Permian Lontras Shale of Santa Catarina State, Brazil. Journal of Vertebrate Paleontology, 11(4), 418–430. DOI: 10.1080/02724634.1991.10011414 [Fonte primária]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2 | FIGUEROA, R.T. et al. 2025. [Referência completa não localizada no levantamento desta base — citada em: Researchgate/348390467]</t>
-        </is>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="O53" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Chondrichthyes indet. (2 dentes)</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Vertebrado — peixes</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — dentes isolados (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Pauliv, V.E., Dias, E.V., Sedor, F.A., Weinschütz, L.C. &amp; Ribeiro, A.M. (2023) — Revista Brasileira de Paleontologia 26(3):227–237</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: condrictio. Dois dentes isolados adicionais atribuídos a condrictios indeterminados</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>https://sbpbrasil.org/publications/index.php/rbp/article/view/327
-https://www.researchgate.net/publication/374930987_A_new_symmoriiform_shark_and_other_chondrichthyan_teeth_from_the_earliest_Permian_of_southern_Brazil</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O54" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P54" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R54" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S54" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2023.3.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Crossopterygii (celacanto) — morfotipos de escamas</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — peixes</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — séries de escamas (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>Weinschütz et al. (vários); registros em nova localidade SC (Researchgate 2021)</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe de nadadeira lobada. Pelo menos 3 morfotipos de escamas distintos dos conhecidos para o Paleozoico da Bacia do Paraná</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
-        </is>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="O55" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Anthracoblattina mendesi Pinto &amp; Sedor, 2000</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — inseto (Blattodea)</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — 18 ou mais espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>Pinto, I.D. &amp; Sedor, F.A. (2000) — descrição original; Ricetti, J.H.Z. et al. (2016) — "Anthracoblattina mendesi Pinto &amp; Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach", Revista Brasileira de Paleontologia 19(2):181–194</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC; UFPR</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>Blattodea paleozoico mais completo descrito na América do Sul; piritização excepcional</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.22456/1807-9806.20189
-https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>PINTO, I.D.; SEDOR, F.A. 2000. Anthracoblattina mendesi sp. nov. (Blattodea, Phyloblattidae), uma nova barata fóssil do Permocarbonífero brasileiro. Pesquisas em Geociências, 27(1), 41–48. [Fonte primária — verificar volume/paginação em repositório IGeo-UFRGS] | RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf</t>
-        </is>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópodes indet. (Brachiopoda)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — braquiópode</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Weinschütz et al. (vários)</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>Presente na biota geral do Folhelho Lontras; detalhes taxonômicos em estudos em andamento</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
-        </is>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Poríferos (Porifera indet.)</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — esponja</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Weinschütz et al.; Ribeiro (NSC Total, 2021)</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: esponja marinha. Citados como integrantes da biota do Campáleo</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
-        </is>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O58" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Conodontes (Conodonta indet.) — 5–6 espécies</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Microfóssil — conodonte</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Weinschütz &amp; Wilner (UnC); NSC Total (2021)</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9–295 Ma</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: conodonto. Conhecidos desde 1908; 5–6 espécies estimadas; importantes para bioestratigrafia e datação</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>https://lume.ufrgs.br/handle/10183/94761
-https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea — Journal of Geoscience, 9(1), 30–36. DOI: 10.4013/gaea.2016.91.02 [Fonte primária]. Disponível em: https://revistas.unisinos.br/index.php/gaea/article/view/gaea.2016.91.02</t>
-        </is>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="O59" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Restos vegetais (fragmentos)</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Flora — restos indeterminados</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>Weinschütz et al.</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>Fragmentos de plantas presentes na biota geral do Campáleo</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
-        </is>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="O60" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R60" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Coprólitos (Coprolita espiralada)</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — coprólito</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Weinschütz et al.</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Coprólitos espiralados atribuídos a peixes</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
-        </is>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="O61" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Orbiculoidea guaraunensis Oliveira, 1930</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — braquiópode</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>Oliveira, E.P. (1930) — "Fósseis marinhos na Série Itararé no Estado de Santa Catharina", Anais da Academia Brasileira de Ciências 2(1):17–21; Carvalho et al. (1942); Ricetti, J.H.Z. et al. (2016) — RBP 19(2):181–194</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
-https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
-        </is>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R62" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Insecta indet. (morfotipos adicionais, ordens não determinadas)</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — inseto</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Coleção CENPALEO — múltiplos espécimes (número de tombo não informado na fonte)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Ricetti, J.H.Z. et al. (2016) — Revista Brasileira de Paleontologia 19(2):181–194</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>Mais de 150 espécimes de insetos recuperados do afloramento além de Anthracoblattina mendesi; preservação excepcional em folhelhos ricos em pirita</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
-https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="inlineStr">
-        <is>
-          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
-        </is>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Campo Mourão (equivalente lateral do Folhelho Lontras)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Biota fóssil similar ao Campáleo (larvas, coprólitos, braquiópodes, esponjas, peixes)</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Assembleia fóssil (biota mista) — biota mista</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento de Rio dos Cedros, SC</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Citado em revisões do Lontras Shale Lagerstätte (cf. Ricetti et al. 2016 e referências associadas)</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>Camada de folhelho com menos de 1 m de espessura, situada a cerca de 85 km do afloramento Campáleo; possível extensão lateral do mesmo Lagerstätte, ainda pouco estudada</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
-https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
-        </is>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="O64" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento de Rio dos Cedros</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="n">
-        <v>-26.6483</v>
-      </c>
-      <c r="R64" s="4" t="n">
-        <v>-49.2783</v>
-      </c>
-      <c r="S64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Ammonoidea indet. (afim. Uraloceras)</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Invertebrado — cefalópode (amonite)</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>Pelo menos duas conchas comprimidas e não identificadas em nível específico; preservadas como filme carbonoso/pirita, sem carbonato de cálcio original; afinidade morfológica com Uraloceras</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compila Mouro et al. 2018/2020)</t>
         </is>
       </c>
-      <c r="M65" s="7" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
+      <c r="N46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="O65" s="6" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P65" s="6" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q46" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R65" s="6" t="n">
+      <c r="R46" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S65" s="6" t="inlineStr">
+      <c r="S46" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Gastropoda indet.</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: molusco gastrópode. Registro raro de gastrópode na biota do Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: molusco gastrópode. Registro raro de gastrópode na biota do Folhelho Lontras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="O66" s="4" t="inlineStr">
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P66" s="4" t="inlineStr">
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q66" s="4" t="n">
+      <c r="Q47" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R66" s="4" t="n">
+      <c r="R47" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S66" s="4" t="inlineStr">
+      <c r="S47" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Chonetes rionegrensis</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Chonetidae)</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
+      <c r="N48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P67" s="6" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q48" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R67" s="6" t="n">
+      <c r="R48" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S67" s="6" t="inlineStr">
+      <c r="S48" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Langella imbituvensis</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Lingulidae)</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D. et al. (2018, 2020); Vinn, O., Wilson, M.A., Mouro, L.D. &amp; Fernandes, A.C.S. (2019) — Carnets de Géologie 19(19):439–444</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | VINN, O.; MOURO, L.D.; FERNANDES, A.C.S. 2019. Serpulid polychaetes from the Lontras Shale (Late Pennsylvanian–Early Cisuralian), Paraná Basin, Brazil. Carnets Geol., 19(19), 439–444. DOI: 10.4267/2042/70514 [Fonte primária]. Disponível em: https://carnetsgeol.net/cg/19/19/CG1919.pdf</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="O68" s="4" t="inlineStr">
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P68" s="4" t="inlineStr">
+      <c r="P49" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q68" s="4" t="n">
+      <c r="Q49" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R68" s="4" t="n">
+      <c r="R49" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="S49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Beecheria sp.</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Beecheria? sp.</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Beecheriidae)</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópode beecheriídeo da biota do Campáleo</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Braquiópode beecheriídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
+      <c r="N50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="O69" s="6" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P69" s="6" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="Q50" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R69" s="6" t="n">
+      <c r="R50" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S69" s="6" t="inlineStr">
+      <c r="S50" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Biconvexiella sp.</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Biconvexiella roxoi</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Amboceolidae)</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>Braquiópode amboceolídeo da biota do Campáleo</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Braquiópode amboceolídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="O70" s="4" t="inlineStr">
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P70" s="4" t="inlineStr">
+      <c r="P51" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q70" s="4" t="n">
+      <c r="Q51" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R70" s="4" t="n">
+      <c r="R51" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S70" s="4" t="inlineStr">
+      <c r="S51" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Quinquenella sp.</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Quinquenella? sp.</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Rugosochonetidae)</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópode rugosoquonetídeo da biota do Campáleo</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Braquiópode rugosoquonetídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M71" s="7" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
+      <c r="N52" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="O71" s="6" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P71" s="6" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q71" s="6" t="n">
+      <c r="Q52" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R71" s="6" t="n">
+      <c r="R52" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S71" s="6" t="inlineStr">
+      <c r="S52" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Discinidae indet.</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea</t>
-        </is>
-      </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N53" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="O72" s="4" t="inlineStr">
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P72" s="4" t="inlineStr">
+      <c r="P53" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q72" s="4" t="n">
+      <c r="Q53" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R72" s="4" t="n">
+      <c r="R53" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S72" s="4" t="inlineStr">
+      <c r="S53" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Microhemidiscia greinerti</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — esponja</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Mouro, L.D., Fernandes, A.C.S., Rogerio, D.W. &amp; Fonseca, V.M.M. (2014) — Journal of Paleontology 88(1)</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Mouro, L.D., Fernandes, A.C.S., Rogério, D.W. &amp; Fonseca, V.M.M. (2014) — "First articulated sponge from the Paleozoic of Brazil, and a new organization of the Order Hemidiscosa", Journal of Paleontology 88(1):171–178; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: esponja hexactinelídea (vítrea). PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil</t>
-        </is>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: esponja hexactinelídea (vítrea). PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil Segundo Mouro et al. (2020), é a esponja mais abundante do afloramento, com quase cem exemplares completos. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>https://www.cambridge.org/core/journals/journal-of-paleontology/issue/C72F5CC47805A30566C7688AAC416D80
-https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária)</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="inlineStr">
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária)
+https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n">
+      <c r="N54" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="O73" s="6" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P73" s="6" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q54" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R73" s="6" t="n">
+      <c r="R54" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S73" s="6" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="S54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Reticulosa indet.</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — esponja (ordem extinta)</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
         </is>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N55" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="O74" s="4" t="inlineStr">
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P74" s="4" t="inlineStr">
+      <c r="P55" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q74" s="4" t="n">
+      <c r="Q55" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R74" s="4" t="n">
+      <c r="R55" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S74" s="4" t="inlineStr">
+      <c r="S55" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Crioselache wittigi</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Coleção CENPALEO (dente isolado; número não informado na fonte consultada)</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Pauliv, V.E., Dias, E.V., Sedor, F.A., Weinschütz, L.C. &amp; Ribeiro, A.M. (2023) — Revista Brasileira de Paleontologia 26(3):227–237</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC; MCN-RS (SEMA)</t>
         </is>
       </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K75" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: tubarão Symmoriiformes (Chondrichthyes). Primeiro Symmoriiformes registrado no Brasil. Novo táxon de tubarão symmoriiforme descrito formalmente a partir de dente isolado do Campáleo NOTA: versões anteriores do catálogo traziam também um registro nº 017, "Symmoriiformes gen. et sp. nov.", que era o MESMO dente antes de receber nome — duplicata removida em 2026.09.6.</t>
-        </is>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: tubarão Symmoriiformes (Chondrichthyes). Primeiro Symmoriiformes registrado no Brasil. Novo táxon de tubarão symmoriiforme descrito formalmente a partir de dente isolado do Campáleo NOTA: versões anteriores do catálogo traziam também um registro nº 017, "Symmoriiformes gen. et sp. nov.", que era o MESMO dente antes de receber nome — duplicata removida em 2026.09.6. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://sbpbrasil.org/publications/index.php/rbp/article/view/327 (Pauliv et al. 2023)</t>
         </is>
       </c>
-      <c r="M75" s="7" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
+      <c r="N56" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="O75" s="6" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P75" s="6" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="n">
+      <c r="Q56" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R75" s="6" t="n">
+      <c r="R56" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S75" s="6" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>10.4072/rbp.2023.3.07</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Daphnaechelus sp.</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Malabarba, M.C.S.L. (1988) — Revisão dos peixes paleoniscóides do Grupo Itararé; Hamel, M.-H. (2005); Beltan, L. (1975) — descrições originais dos actinopterígios do Folhelho Lontras</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio. Um dos gêneros de peixe de nadadeira raiada (Actinopterygii) com nome formal documentados para o Campáleo</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio. Um dos gêneros de peixe de nadadeira raiada (Actinopterygii) com nome formal documentados para o Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
         </is>
       </c>
-      <c r="N76" s="4" t="n">
+      <c r="N57" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="O76" s="4" t="inlineStr">
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P76" s="4" t="inlineStr">
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q76" s="4" t="n">
+      <c r="Q57" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R76" s="4" t="n">
+      <c r="R57" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S76" s="4" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="S57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Irajapintoseidon uruguayensis Beltan, 1975</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>Malabarba, M.C.S.L. (1988) — Revisão dos peixes paleoniscóides do Grupo Itararé; Hamel, M.-H. (2005); Beltan, L. (1975) — descrições originais dos actinopterígios do Folhelho Lontras</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio. Espécie de actinopterígio nomeada formalmente, registrada no Campáleo</t>
-        </is>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio. Espécie de actinopterígio nomeada formalmente, registrada no Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr">
+      <c r="M58" s="5" t="inlineStr">
         <is>
           <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
         </is>
       </c>
-      <c r="N77" s="6" t="n">
+      <c r="N58" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="O77" s="6" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P77" s="6" t="inlineStr">
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="n">
+      <c r="Q58" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R77" s="6" t="n">
+      <c r="R58" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S77" s="6" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="S58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Roslerichthys riomafrensis Hamel, 2005</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Malabarba, M.C.S.L. (1988) — Revisão dos peixes paleoniscóides do Grupo Itararé; Hamel, M.-H. (2005); Beltan, L. (1975) — descrições originais dos actinopterígios do Folhelho Lontras</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao rio Mafra; um dos peixes formalmente descritos do Lagerstätte</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao rio Mafra; um dos peixes formalmente descritos do Lagerstätte UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
         </is>
       </c>
-      <c r="N78" s="4" t="n">
+      <c r="N59" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="O78" s="4" t="inlineStr">
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P78" s="4" t="inlineStr">
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q78" s="4" t="n">
+      <c r="Q59" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R78" s="4" t="n">
+      <c r="R59" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="S59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Santosichthys mafrensis Malabarba, 1988</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>Malabarba, M.C.S.L. (1988) — Revisão dos peixes paleoniscóides do Grupo Itararé; Hamel, M.-H. (2005); Beltan, L. (1975) — descrições originais dos actinopterígios do Folhelho Lontras</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K79" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao município de Mafra</t>
-        </is>
-      </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao município de Mafra UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr">
         <is>
           <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
         </is>
       </c>
-      <c r="N79" s="6" t="n">
+      <c r="N60" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="O79" s="6" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P79" s="6" t="inlineStr">
+      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q79" s="6" t="n">
+      <c r="Q60" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R79" s="6" t="n">
+      <c r="R60" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S79" s="6" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="S60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Coelacanthus sp.</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr">
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
         </is>
       </c>
-      <c r="N80" s="4" t="n">
+      <c r="N61" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="O80" s="4" t="inlineStr">
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P80" s="4" t="inlineStr">
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q80" s="4" t="n">
+      <c r="Q61" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R80" s="4" t="n">
+      <c r="R61" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S80" s="4" t="inlineStr">
+      <c r="S61" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Annelida indet. (escolecodontes) / Paulinitidae / Polychaetaspidae</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — anelídeo poliqueta (mandíbulas fossilizadas)</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC; também Fm. Mafra e Fm. Rio do Sul</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2011) — Bol. Inf. SBP nº 64:31-32; Mouro et al. (2018, 2020); Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>Mais de 20 escolecodontes articulados (mandíbulas de poliquetas) preservados em concreções, alguns com possíveis vestígios de tecido mole e cerdas (quetas)</t>
-        </is>
-      </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Mais de 20 escolecodontes articulados (mandíbulas de poliquetas) preservados em concreções, alguns com possíveis vestígios de tecido mole e cerdas (quetas) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2011. Ocorrência de Escolecodontes (Annelida, Labidognatha) nas Formações Mafra e Rio do Sul, Permocarbonífero da Bacia do Paraná, Brasil. Boletim Informativo da Sociedade Brasileira de Paleontologia, 64, 31–32. [Fonte primária — nota em boletim de evento, sem DOI]. Nota: também citado como base do registro em Mouro et al. 2018/2020.</t>
         </is>
       </c>
-      <c r="N81" s="6" t="n">
+      <c r="N62" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="O81" s="6" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P81" s="6" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q81" s="6" t="n">
+      <c r="Q62" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R81" s="6" t="n">
+      <c r="R62" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S81" s="6" t="inlineStr">
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Eumalacostraca indet. / Ostracoda indet.</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — crustáceo (malacostráceo e ostracode)</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Malacostráceos muito fragmentários, raramente completos; ostracodes encontrados em pequenos agrupamentos (~175 μm)</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Malacostráceos muito fragmentários, raramente completos; ostracodes encontrados em pequenos agrupamentos (~175 μm) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M82" s="5" t="inlineStr">
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N82" s="4" t="n">
+      <c r="N63" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="O82" s="4" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P82" s="4" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q82" s="4" t="n">
+      <c r="Q63" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R82" s="4" t="n">
+      <c r="R63" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S82" s="4" t="inlineStr">
+      <c r="S63" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Arachnostega isp.</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — bioerosão em concha</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>Vinn, O., Wilson, M.A., Mouro, L.D. &amp; Fernandes, A.C.S. (2019) — Carnets de Géologie 19(19):439–444</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: escavação de bioerosão em concha. Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: escavação de bioerosão em concha. Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>VINN, O.; MOURO, L.D.; FERNANDES, A.C.S. 2019. Serpulid polychaetes from the Lontras Shale (Late Pennsylvanian–Early Cisuralian), Paraná Basin, Brazil. Carnets Geol., 19(19), 439–444. DOI: 10.4267/2042/70514 [Fonte primária]. Disponível em: https://carnetsgeol.net/cg/19/19/CG1919.pdf</t>
         </is>
       </c>
-      <c r="N83" s="6" t="n">
+      <c r="N64" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="O83" s="6" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P83" s="6" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="n">
+      <c r="Q64" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R83" s="6" t="n">
+      <c r="R64" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S83" s="6" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="S64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Oichnus paraboloides / O. simplex</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — perfuração de predação</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>Perfurações em conchas de braquiópodes, evidência provável de predação</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Perfurações em conchas de braquiópodes, evidência provável de predação UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n">
+      <c r="N65" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="O84" s="4" t="inlineStr">
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P84" s="4" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q84" s="4" t="n">
+      <c r="Q65" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R84" s="4" t="n">
+      <c r="R65" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S84" s="4" t="inlineStr">
+      <c r="S65" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Enterospira (espiral intestinal)</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — conteúdo intestinal fossilizado de tubarão</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>Estruturas cilíndricas (~22 mm) preservadas por fosfatização, interpretadas como conteúdo intestinal de condrictes</t>
-        </is>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Estruturas cilíndricas (~22 mm) preservadas por fosfatização, interpretadas como conteúdo intestinal de condrictes UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
+      <c r="N66" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="O85" s="6" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P85" s="6" t="inlineStr">
+      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="n">
+      <c r="Q66" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R85" s="6" t="n">
+      <c r="R66" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S85" s="6" t="inlineStr">
+      <c r="S66" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Agathoxylon sp. / Abietopitys sp.</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Flora — lenho fóssil (gimnosperma araucariácea)</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>ca. 298,9 Ma</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>Restos lenhosos dispersos pelo folhelho, com fragmentos comuns; também há estruturas semelhantes a âmbar (resina fossilizada)</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Restos lenhosos dispersos pelo folhelho, com fragmentos comuns; também há estruturas semelhantes a âmbar (resina fossilizada) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n">
+      <c r="N67" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="O86" s="4" t="inlineStr">
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P86" s="4" t="inlineStr">
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q86" s="4" t="n">
+      <c r="Q67" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R86" s="4" t="n">
+      <c r="R67" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S86" s="4" t="inlineStr">
+      <c r="S67" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Permiano Inferior (Asseliano)</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Mesogondolella spp.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — conodonte (aparelho alimentar gondolelídeo)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO / UFRGS (Instituto de Geociências)</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Wilner, E. (2014) — Dissertação de Mestrado, IGEO-UFRGS; Wilner et al. (2016) — Gaea-Journal of Geoscience 9(1)</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>UFRGS / CENPALEO</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Primeira ocorrência de conodontes (aparelhos alimentares completos e articulados) descrita para toda a Bacia do Paraná; dezenas de elementos ramiformes inicialmente confundidos macroscopicamente com espículas de poríferos; gênero gondolelídeo marcador do Cisuraliano NOTA: o registro nº 023 ("Conodontes indet. — 5–6 espécies", apoiado em reportagem) repetia este material e foi removido em 2026.09.10. Mouro et al. (2020) relatam dezenas de aparelhos articulados e centenas de elementos isolados de Mesogondolella spp., todos fosfatizados (Scomazzon et al., 2013; Wilner et al., 2016a). UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>https://lume.ufrgs.br/handle/10183/94761
+https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>WILNER, E. 2014. Conodontes do Folhelho Lontras (Grupo Itararé, Cisuraliano), Bacia do Paraná: taxonomia, bioestratigrafia e paleoecologia. Dissertação de Mestrado, Instituto de Geociências, UFRGS, Porto Alegre, RS. Disponível em: https://lume.ufrgs.br/handle/10183/94761 [Fonte primária]. | WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea, 9(1), 30–36. DOI: 10.4013/gaea.2016.91.02 [Fonte primária].</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R68" s="4" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Folhelho Lontras</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Actinopterygii indet. — dois morfotipos com encéfalo e tecidos moles preservados em 3D</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo, BR-280 km 166, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Figueroa, R.T., Weinschütz, L.C., Giles, S. &amp; Friedman, M. (2024) — Current Biology, 34(13), 2831–2840.e2</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC; Univ. of Michigan; Univ. of Birmingham</t>
         </is>
       </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>ca. 299 Ma</t>
-        </is>
-      </c>
-      <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio (tecidos moles preservados). Oito espécimes preservados em concreções sideríticas foram tomografados por micro-CT, revelando preservação tridimensional de encéfalo, nervos cranianos, olhos e possíveis tecidos cardiovasculares — condição raríssima no registro fóssil, já que o tecido neural se decompõe muito rápido. Os dois morfotipos diferem tanto no esqueleto quanto no encéfalo: o mais próximo dos actinopterígios viventes apresenta telencéfalo evertido (característica das formas atuais), ausente no outro morfotipo e em Coccocephalus. Fornece um modelo revisado para a evolução do encéfalo dos peixes de nadadeiras raiadas, o maior grupo de vertebrados vivos.</t>
-        </is>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio (tecidos moles preservados). Oito espécimes preservados em concreções sideríticas foram tomografados por micro-CT, revelando preservação tridimensional de encéfalo, nervos cranianos, olhos e possíveis tecidos cardiovasculares — condição raríssima no registro fóssil, já que o tecido neural se decompõe muito rápido. Os dois morfotipos diferem tanto no esqueleto quanto no encéfalo: o mais próximo dos actinopterígios viventes apresenta telencéfalo evertido (característica das formas atuais), ausente no outro morfotipo e em Coccocephalus. Fornece um modelo revisado para a evolução do encéfalo dos peixes de nadadeiras raiadas, o maior grupo de vertebrados vivos. NOTA: o registro nº 016 ("Actinopterygii indet. — morfotipo 2") repetia estes mesmos morfotipos e foi removido em 2026.09.10. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.cub.2024.05.027
 https://www.cell.com/current-biology/fulltext/S0960-9822(24)00670-5
 https://phys.org/news/2024-06-rare-brazilian-fossil-fishes.html</t>
         </is>
       </c>
+      <c r="M69" s="7" t="inlineStr"/>
+      <c r="N69" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R69" s="6" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.cub.2024.05.027</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Folhelho Lontras</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Foraminifera bentônicos aglutinantes (indet.)</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — foraminífero bentônico</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Pigão &amp; Mouro (2019); revisados em análise de microfósseis do Folhelho Lontras — J. South American Earth Sciences (2023)</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Estruturas reconhecidas em lâminas delgadas e discriminadas como foraminíferos bentônicos aglutinantes, sem classificação em nível taxonômico inferior. Integram a microfauna usada para reconstruir as variações paleoambientais do Lagerstätte. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981123002882</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Folhelho Lontras</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Palinoflora do Campáleo (esporos, grãos de pólen, fungos e algas)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>"Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana", Sedimentary Geology (2023)</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade. IDADE: o trabalho situa o Campáleo perto do limite Carbonífero–Permiano, provavelmente no Gzheliano (fim do Carbonífero); outras fontes o posicionam no início do Permiano — a idade do afloramento segue em discussão. CORREÇÃO (2026.09.9): a revista estava registrada como Review of Palaeobotany and Palynology. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0037073823002154</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr"/>
+      <c r="N71" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R71" s="6" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Icnofauna do Afloramento Campo da Lança (8 icnogêneros)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Assembleia com oito icnogêneros reconhecidos no siltito do Campo da Lança, incluindo Protichnites, Rusophycus, Thalassinoides, Diplocraterion e Rhizocorallium. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Rusophycus cf. carbonarius Dawson (traço de repouso de artrópode)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>Traço de repouso atribuído a artrópode, reconhecido nas assembleias do Grupo Itararé catarinense. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr"/>
+      <c r="N73" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Protichnites isp. (pista de artrópode)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Pista de artrópode recorrente nas icnocenoses do Grupo Itararé em Santa Catarina. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R74" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Icnofauna do Afloramento Bela Vista do Sul</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Ritmitos síltico-argilosos gradando a síltico-arenosos rumo ao topo, com acamamento ondulado. A icnofauna reúne Cruziana, Diplichnites, Diplopodichnus, Lockeia, Protovirgularia e Rusophycus. Topo da Fm. Rio do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr"/>
+      <c r="N75" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Bela Vista do Sul</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Lockeia siliquaria (traço de repouso de bivalve)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Traço de repouso produzido por bivalve, componente da icnofauna de Bela Vista do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr"/>
+      <c r="N76" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Bela Vista do Sul</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R76" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S76" s="4" t="inlineStr">
+        <is>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Neonereites isp.</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Escavação rasa que complementa a assembleia dominada por pistas de artrópodes. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr"/>
+      <c r="N77" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R77" s="6" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Gluckstadtella isp.</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Escavação rasa presente na assembleia da Fm. Rio do Sul em Trombudo Central. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Rusophycus isp. (Pedreira Itaú-Itaúna)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b), Acta Geologica Leopoldensia 52/53:387–396</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>Traço de repouso de artrópode, componente menos frequente da assembleia. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R79" s="6" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Icnofauna da Pedreira Waltrick</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Pedreira Waltrick, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Terceira pedreira de ritmitos estudada na área de Trombudo Central (UTM 620026/6981727), ao lado de Itaú-Itaúna e Fama. Integra o conjunto de afloramentos que documenta a icnofauna dos depósitos de deglaciação da Fm. Rio do Sul. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>Pedreira Waltrick</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S80" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Icnofauna da Pedreira Fama</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Pedreira Fama, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>Pedreira de ritmitos (UTM 619813/6981938) estudada em conjunto com Itaú-Itaúna e Waltrick, compondo o registro icnológico dos depósitos de deglaciação do topo do Grupo Itararé. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr"/>
+      <c r="N81" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>Pedreira Fama</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Protovirgularia dichotoma</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Pedreiras de ritmitos, Trombudo Central, SC</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Coleções UNISINOS / UFRGS</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>UNISINOS; UFRGS</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Traço de locomoção produzido pelo pé de um bivalve. Completa as DEZ icnoespécies reconhecidas por Lima et al. (2015) nos ritmitos de Trombudo Central: Cruziana problematica, Diplichnites gouldi, Diplopodichnus biformis, Glaciichnium liebegastensis, Gluckstadtella elongata, Helminthoidichnites tenuis, Mermia carickensis, Protovirgularia dichotoma, Treptichnus pollardi e Umfolozia sinuosa — todas agora presentes neste catálogo.</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>Pedreira Itaú-Itaúna</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>-27.305</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>-49.795</v>
+      </c>
+      <c r="S82" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / formações Campo Mourão e Taciba</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Icnofósseis indet. de sistema de fiorde (Presidente Getúlio)</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Afloramentos da região de Presidente Getúlio, SC</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Oliveira, V.G. (2019) — "Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina", Trabalho de Conclusão de Curso, Geologia, UFSC</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>UFSC</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>Traços fósseis reconhecidos nas formações Campo Mourão e Taciba, em sucessão de 17 litofácies agrupadas em cinco associações que definem subambientes de um amplo SISTEMA DE FIORDE, ligados a ciclos de transgressão–regressão glacio-influenciados. O tamanho reduzido dos traços e a baixa diversidade, em comparação com o esperado para ambientes plenamente marinhos, são justamente o argumento paleoambiental que sustenta a interpretação de fiorde. RESSALVA: o trabalho é de natureza estratigráfica e não identifica os icnofósseis em nível icnotaxonômico — o registro consta como ocorrência, não como táxon determinado.</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>https://repositorio.ufsc.br/handle/123456789/204084</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr"/>
+      <c r="N83" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>Região de Presidente Getúlio</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v>-27.0453</v>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v>-49.6231</v>
+      </c>
+      <c r="S83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Mafra</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Hormosiroidea meandrica (Fazenda Potreiro)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>CP/P (coleção CENPALEO)</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>UNISINOS; CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Icnoespécie proposta como nova por Balistieri e colaboradores (2002–2003) a partir dos ritmitos da região de Mafra (SC) e Rio Negro (PR). ATENÇÃO: a fonte consultada não permite afirmar em qual dos afloramentos — o catarinense ou o paranaense — está o material-tipo; por isso esta ficha NÃO a trata como localidade-tipo. Escavação meandrante rasa, preservada sobretudo como crista hipicnial. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr"/>
+      <c r="N84" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Mafra</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Undichna consulca</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — vertebrado (trilha de nadadeira de peixe)</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>UNISINOS; CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>Trilha deixada pela nadadeira de um PEIXE ao roçar o fundo lamoso — um dos raros registros de atividade de vertebrado na icnofauna do Grupo Itararé catarinense. Aparece recoberta por trilhas de Diplichnites gouldi, em preservação palimpséstica. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr"/>
+      <c r="N85" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Mafra</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Gordia arcuata e Gordia marina</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002); Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>UNISINOS; CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Escavações de pastagem finas e sinuosas, componentes da suíte de escavações rasas dos ritmitos lacustres. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.palaeo.2008.10.028
+https://revistas.uepg.br/index.php/tp/article/view/18322</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr"/>
+      <c r="N86" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>Fazenda Potreiro</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R86" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S86" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2008.10.028</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Escavações tipo Gyrolithes (Gyrolithes-like burrows)</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Netto, R.G. et al. (2007) — Revista Brasileira de Paleontologia 10(3):157–168; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>Escavações helicoidais semelhantes a Gyrolithes, parte da suíte Glossifungites do Campo da Lança, junto a Thalassinoides, Diplocraterion e ?Rhizocorallium. Indicam colonização de substrato firme exumado por erosão transgressiva. Nos depósitos eopermianos das formações Rio do Sul e Rio Bonito, essas formas ocorrem sempre em suítes de substrato firme. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sbpbrasil.org/revista/edicoes/10_3/netto.pdf</t>
+        </is>
+      </c>
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="6" t="n">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="O87" s="6" t="inlineStr">
         <is>
-          <t>Afloramento Campáleo (Mafra)</t>
+          <t>Afloramento Campo da Lança</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
@@ -8053,21 +8059,21 @@
         </is>
       </c>
       <c r="Q87" s="6" t="n">
-        <v>-26.1583</v>
+        <v>-26.1112</v>
       </c>
       <c r="R87" s="6" t="n">
-        <v>-49.8147</v>
+        <v>-49.805</v>
       </c>
       <c r="S87" s="6" t="inlineStr">
         <is>
-          <t>10.1016/j.cub.2024.05.027</t>
+          <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Permiano Inferior (Asseliano)</t>
+          <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -8077,12 +8083,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Foraminifera bentônicos aglutinantes (indet.)</t>
+          <t>Estojos larvais de Trichoptera / Permotrichoptera</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Microfóssil — foraminífero bentônico</t>
+          <t>Invertebrado — inseto</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -8092,7 +8098,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Afloramento Campáleo, BR-280 km 166, Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -8102,32 +8108,37 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>Pigão &amp; Mouro (2019); revisados em análise de microfósseis do Folhelho Lontras — J. South American Earth Sciences (2023)</t>
+          <t>Mouro, L.D., Zatoń, M., Fernandes, A.C.S. &amp; Waichel, B.L. (2016) — "Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana", Scientific Reports 6:19215; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>CENPALEO/UnC; UFPR</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>ca. 299 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>Estruturas reconhecidas em lâminas delgadas e discriminadas como foraminíferos bentônicos aglutinantes, sem classificação em nível taxonômico inferior. Integram a microfauna usada para reconstruir as variações paleoambientais do Lagerstätte.</t>
+          <t>Classificação: inseto (estojo larval). Possivelmente os estojos larvais de tricópteros mais antigos conhecidos, relacionados às ordens Trichoptera ou Permotrichoptera. São faixas esbranquiçadas com estruturas filamentosas semelhantes à seda das larvas atuais, enriquecidas em cálcio e enxofre segundo análise por EDS. Notáveis por ocorrerem num ambiente marinho. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981123002882</t>
-        </is>
-      </c>
-      <c r="M88" s="5" t="inlineStr"/>
+          <t>https://doi.org/10.1038/srep19215
+https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>PINTO, I.D.; SEDOR, F.A. 2000. Anthracoblattina mendesi sp. nov. (Blattodea, Phyloblattidae), uma nova barata fóssil do Permocarbonífero brasileiro. Pesquisas em Geociências, 27(1), 41–48. [Fonte primária — verificar volume/paginação em repositório IGeo-UFRGS] | RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf</t>
+        </is>
+      </c>
       <c r="N88" s="4" t="n">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
@@ -8145,12 +8156,16 @@
       <c r="R88" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S88" s="4" t="inlineStr"/>
+      <c r="S88" s="4" t="inlineStr">
+        <is>
+          <t>10.1038/srep19215</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Permiano Inferior (Asseliano)</t>
+          <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -8160,12 +8175,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Palinoflora do Campáleo (esporos, grãos de pólen, fungos e algas)</t>
+          <t>Estrutura semelhante a âmbar (possível resina fóssil)</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — palinomorfos</t>
+          <t>Flora — resina fóssil</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -8175,7 +8190,7 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Afloramento Campáleo, BR-280 km 166, Mafra, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -8185,32 +8200,36 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>"Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana", Sedimentary Geology (2023)</t>
+          <t>Wilner, E., Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2016) — "Comunicado de possível primeiro âmbar paleozoico da Bacia do Paraná", Paleontologia em Destaque 31(69):136; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>CENPALEO/UnC; UFPR</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>ca. 299 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade. IDADE: o trabalho situa o Campáleo perto do limite Carbonífero–Permiano, provavelmente no Gzheliano (fim do Carbonífero); outras fontes o posicionam no início do Permiano — a idade do afloramento segue em discussão. CORREÇÃO (2026.09.9): a revista estava registrada como Review of Palaeobotany and Palynology.</t>
+          <t>Estrutura semelhante a âmbar comunicada como possível primeiro âmbar paleozoico da Bacia do Paraná. RESSALVA: segundo Mouro et al. (2020), segue em descrição — a natureza do material ainda não foi confirmada. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0037073823002154</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr"/>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>PINTO, I.D.; SEDOR, F.A. 2000. Anthracoblattina mendesi sp. nov. (Blattodea, Phyloblattidae), uma nova barata fóssil do Permocarbonífero brasileiro. Pesquisas em Geociências, 27(1), 41–48. [Fonte primária — verificar volume/paginação em repositório IGeo-UFRGS] | RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf</t>
+        </is>
+      </c>
       <c r="N89" s="6" t="n">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
@@ -8233,22 +8252,22 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Permiano Inferior (Cisuraliano)</t>
+          <t>Permiano Inferior (Asseliano)</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Rio do Sul — Folhelho Lontras</t>
+          <t>Grupo Itararé / Fm. Campo Mourão (equivalente lateral do Folhelho Lontras)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Mesogondolella spp.</t>
+          <t>Biota fóssil similar ao Campáleo (larvas, coprólitos, braquiópodes, esponjas, peixes)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Microfóssil — conodonte (aparelho alimentar gondolelídeo)</t>
+          <t>Assembleia fóssil (biota mista) — biota mista</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -8258,51 +8277,51 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Afloramento Campáleo, Mafra, SC</t>
+          <t>Afloramento de Rio dos Cedros, SC</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO / UFRGS (Instituto de Geociências)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>Wilner, E. (2014) — Dissertação de Mestrado, IGEO-UFRGS; Wilner et al. (2016) — Gaea-Journal of Geoscience 9(1)</t>
+          <t>Citado em revisões do Lontras Shale Lagerstätte (cf. Ricetti et al. 2016 e referências associadas)</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>UFRGS / CENPALEO</t>
+          <t>CENPALEO/UnC</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>ca. 298,9–295 Ma</t>
+          <t>ca. 298,9 Ma</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>Primeira ocorrência de conodontes (aparelhos alimentares completos e articulados) descrita para toda a Bacia do Paraná; dezenas de elementos ramiformes inicialmente confundidos macroscopicamente com espículas de poríferos; gênero gondolelídeo marcador do Cisuraliano</t>
+          <t>Camada de folhelho com menos de 1 m de espessura, situada a cerca de 85 km do afloramento Campáleo; possível extensão lateral do mesmo Lagerstätte, ainda pouco estudada</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>https://lume.ufrgs.br/handle/10183/94761
-https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
+          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
+https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>WILNER, E. 2014. Conodontes do Folhelho Lontras (Grupo Itararé, Cisuraliano), Bacia do Paraná: taxonomia, bioestratigrafia e paleoecologia. Dissertação de Mestrado, Instituto de Geociências, UFRGS, Porto Alegre, RS. Disponível em: https://lume.ufrgs.br/handle/10183/94761 [Fonte primária]. | WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea, 9(1), 30–36. DOI: 10.4013/gaea.2016.91.02 [Fonte primária].</t>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
         </is>
       </c>
       <c r="N90" s="4" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>Afloramento Campáleo (Mafra)</t>
+          <t>Afloramento de Rio dos Cedros</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -8311,10 +8330,10 @@
         </is>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>-26.1583</v>
+        <v>-26.6483</v>
       </c>
       <c r="R90" s="4" t="n">
-        <v>-49.8147</v>
+        <v>-49.2783</v>
       </c>
       <c r="S90" s="4" t="inlineStr"/>
     </row>
@@ -20244,7 +20263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -25915,16 +25934,20 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="9" t="n"/>
+      <c r="B531" s="9" t="n"/>
+    </row>
     <row r="532">
-      <c r="A532" s="10" t="inlineStr">
+      <c r="A532" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B532" s="9" t="inlineStr"/>
+      <c r="B532" s="9" t="n"/>
     </row>
     <row r="533">
-      <c r="A533" s="11" t="inlineStr">
+      <c r="A533" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -25936,7 +25959,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="11" t="inlineStr">
+      <c r="A534" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -25948,7 +25971,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="11" t="inlineStr">
+      <c r="A535" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -25960,7 +25983,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="11" t="inlineStr">
+      <c r="A536" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -25972,7 +25995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="11" t="inlineStr">
+      <c r="A537" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -25984,7 +26007,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="11" t="inlineStr">
+      <c r="A538" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -25996,12 +26019,296 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="11" t="inlineStr">
+      <c r="A539" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="9" t="n"/>
+      <c r="B540" s="9" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B541" s="9" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B542" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B543" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B544" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B545" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B546" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B548" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="9" t="n"/>
+      <c r="B549" s="9" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B550" s="9" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B551" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B552" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B553" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B554" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B555" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B556" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B559" s="9" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B560" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B562" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B564" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B566" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S230"/>
+  <dimension ref="A1:S231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>227 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>228 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Não informado na fonte consultada</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.; Hamel, M.-H. (2005) — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.; Hamel, M.-H. (2005) — "A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. | HAMEL, M.-H. 2005. A new actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26.</t>
+          <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26.</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Classificação: condrictio. Dois dentes isolados adicionais atribuídos a condrictios indeterminados UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Classificação: condrictio. Dois dentes isolados adicionais atribuídos a condrictios indeterminados. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe de nadadeira lobada. Pelo menos 3 morfotipos de escamas distintos dos conhecidos para o Paleozoico da Bacia do Paraná UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Classificação: peixe de nadadeira lobada. Pelo menos 3 morfotipos de escamas distintos dos conhecidos para o Paleozoico da Bacia do Paraná. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Presente na biota geral do Folhelho Lontras; detalhes taxonômicos em estudos em andamento UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Presente na biota geral do Folhelho Lontras; detalhes taxonômicos em estudos em andamento. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Fragmentos de plantas presentes na biota geral do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Fragmentos de plantas presentes na biota geral do Campáleo. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Coprólitos espiralados atribuídos a peixes UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Coprólitos espiralados atribuídos a peixes. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -4395,1079 +4395,1076 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
+          <t>Grupo Itararé / Fm. Campo Mourão (equivalente lateral do Folhelho Lontras)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Folhelho fossilífero de Rio dos Cedros (possível equivalente do Folhelho Lontras)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Assembleia fóssil (biota mista) — biota mista</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento de Rio dos Cedros, SC</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Saldanha, J.P. et al. (2023) — "Exploring the restricted Lontras Shale fossil record: Data biases or preservational casualties?", Sedimentary Geology 458:106533</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Não informada na fonte</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Não datado para Rio dos Cedros (o Folhelho Lontras, em Mafra, tem ca. 298,9 Ma por U-Pb)</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>CITAÇÃO EM REVISÃO — o material não foi examinado por este banco. Segundo a síntese da Wikipédia sobre o Lagerstätte Folhelho Lontras, que remete a Saldanha et al. (2023, Sedimentary Geology 458:106533), há em Rio dos Cedros um depósito de folhelho com menos de 1 m de espessura, a cerca de 85 km do Folhelho Lontras (afloramento Campáleo, Mafra); não está claro se ele pertence ao mesmo Lagerstätte ou é um nível distinto, porque há poucos estudos. O texto integral do artigo não pôde ser aberto (acesso bloqueado). CONTEÚDO FOSSILÍFERO: a lista 'larvas, coprólitos, braquiópodes, esponjas, peixes' que constava neste registro NÃO foi confirmada em nenhuma fonte consultada e foi retirada do título. HISTÓRICO DE CORREÇÃO: o registro citava Ricetti et al. (2016, Rev. Bras. Paleontol. 19(2)) e Oliveira (1930), trabalhos que não mencionam Rio dos Cedros; foram substituídos pela fonte acima. POSSÍVEL LIGAÇÃO: o registro 37 cita um resumo sobre uma 'nova localidade equivalente ao Folhelho Lontras' que pode se referir a este mesmo depósito — não foi possível confirmar (o resumo não pôde ser aberto).</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0037073823002051
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (síntese que cita Saldanha et al. 2023 — o artigo integral não foi aberto)</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>SALDANHA, J.P. et al. 2023. Exploring the restricted Lontras Shale fossil record: Data biases or preservational casualties?. Sedimentary Geology, 458, 106533.</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento de Rio dos Cedros</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé (equivalente possível do Folhelho Lontras)</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>-26.6483</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>-49.2783</v>
+      </c>
+      <c r="S46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Ammonoidea indet. (afim. Uraloceras)</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — cefalópode (amonite)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Pelo menos duas conchas comprimidas e não identificadas em nível específico; preservadas como filme carbonoso/pirita, sem carbonato de cálcio original; afinidade morfológica com Uraloceras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Pelo menos duas conchas comprimidas e não identificadas em nível específico; preservadas como filme carbonoso/pirita, sem carbonato de cálcio original; afinidade morfológica com Uraloceras. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compila Mouro et al. 2018/2020)</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N47" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="n">
+      <c r="Q47" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R46" s="4" t="n">
+      <c r="R47" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S46" s="4" t="inlineStr">
+      <c r="S47" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Gastropoda indet.</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: molusco gastrópode. Registro raro de gastrópode na biota do Folhelho Lontras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: molusco gastrópode. Registro raro de gastrópode na biota do Folhelho Lontras. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N48" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="O47" s="6" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P47" s="6" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q48" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="R48" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S47" s="6" t="inlineStr">
+      <c r="S48" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Chonetes rionegrensis</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Chonetidae)</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N49" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="O48" s="4" t="inlineStr">
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr">
+      <c r="P49" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="n">
+      <c r="Q49" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R48" s="4" t="n">
+      <c r="R49" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S48" s="4" t="inlineStr">
+      <c r="S49" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Langella imbituvensis</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Lingulidae)</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Fernandes, A.C.S., Carvalho, M.A. &amp; Weinschütz, L.C. (2018) — "O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual", Anuário do Instituto de Geociências 41(2):636–646; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Vinn, O., Zabini, C. &amp; Weinschütz, L.C. (2019) — "Ichnofossils associated with lingulide shells from the Lower Permian of Brazil", Carnets de Géologie 2019(19):439–444, DOI 10.4267/2042/70636</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências, 41(2), 636–646. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | VINN, O.; ZABINI, C.; WEINSCHÜTZ, L.C. 2019. Ichnofossils associated with lingulide shells from the Lower Permian of Brazil. Carnets de Géologie, 2019(19), 439–444. DOI: 10.4267/2042/70636</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N50" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="O49" s="6" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P49" s="6" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q50" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R49" s="6" t="n">
+      <c r="R50" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="S50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Beecheria? sp.</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Beecheriidae)</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Braquiópode beecheriídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Braquiópode beecheriídeo da biota do Campáleo. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N51" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="O50" s="4" t="inlineStr">
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
+      <c r="P51" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="n">
+      <c r="Q51" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R50" s="4" t="n">
+      <c r="R51" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S50" s="4" t="inlineStr">
+      <c r="S51" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Biconvexiella roxoi</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Amboceolidae)</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>Braquiópode amboceolídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Braquiópode amboceolídeo da biota do Campáleo. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
+      <c r="N52" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="O51" s="6" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P51" s="6" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="n">
+      <c r="Q52" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R51" s="6" t="n">
+      <c r="R52" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S51" s="6" t="inlineStr">
+      <c r="S52" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Quinquenella? sp.</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode (Rugosochonetidae)</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Braquiópode rugosoquonetídeo da biota do Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Braquiópode rugosoquonetídeo da biota do Campáleo. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N53" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="O52" s="4" t="inlineStr">
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P52" s="4" t="inlineStr">
+      <c r="P53" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="n">
+      <c r="Q53" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R52" s="4" t="n">
+      <c r="R53" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S52" s="4" t="inlineStr">
+      <c r="S53" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Discinidae indet.</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — braquiópode</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J53" s="6" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
+      <c r="N54" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="O53" s="6" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P53" s="6" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="n">
+      <c r="Q54" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R53" s="6" t="n">
+      <c r="R54" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S53" s="6" t="inlineStr">
+      <c r="S54" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Microhemidiscia greinerti</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — esponja</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Fernandes, A.C.S., Rogério, D.W. &amp; Fonseca, V.M.M. (2014) — "First articulated sponge from the Paleozoic of Brazil, and a new organization of the Order Hemidiscosa", Journal of Paleontology 88(1):171–178; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>Classificação: esponja hexactinelídea (vítrea). PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil Segundo Mouro et al. (2020), é a esponja mais abundante do afloramento, com quase cem exemplares completos. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>https://www.cambridge.org/core/journals/journal-of-paleontology/issue/C72F5CC47805A30566C7688AAC416D80
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária)
 https://doi.org/10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; FERNANDES, A.C.S.; ROGÉRIO, D.W. et al. 2014. First articulated sponge from the Paleozoic of Brazil, and a new organization of the Order Hemidiscosa. Journal of Paleontology, 88(1), 171–178. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N55" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="O54" s="4" t="inlineStr">
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr">
+      <c r="P55" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="n">
+      <c r="Q55" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R54" s="4" t="n">
+      <c r="R55" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="S55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Reticulosa indet.</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — esponja (ordem extinta)</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M55" s="7" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
+      <c r="N56" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="O55" s="6" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P55" s="6" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="n">
+      <c r="Q56" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R55" s="6" t="n">
+      <c r="R56" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S55" s="6" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Crioselache wittigi</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Coleção CENPALEO (dente isolado; número não informado na fonte consultada)</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Pauliv, V.E., Dias, E.V., Sedor, F.A., Weinschütz, L.C. &amp; Ribeiro, A.M. (2023) — "A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil", Revista Brasileira de Paleontologia 26(3):227–237, DOI 10.4072/rbp.2023.3.07</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC; MCN-RS (SEMA)</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>Classificação: tubarão Symmoriiformes (Chondrichthyes). Primeiro Symmoriiformes registrado no Brasil. Novo táxon de tubarão symmoriiforme descrito formalmente a partir de dente isolado do Campáleo NOTA: versões anteriores do catálogo traziam também um registro nº 017, "Symmoriiformes gen. et sp. nov.", que era o MESMO dente antes de receber nome — duplicata removida em 2026.09.6. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://sbpbrasil.org/publications/index.php/rbp/article/view/327 (Pauliv et al. 2023)</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A. et al. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N57" s="6" t="n">
         <v>55</v>
-      </c>
-      <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R56" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S56" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2023.3.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Daphnaechelus sp.</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Vertebrado — peixes</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Hamel, M.-H. (2005) — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe actinopterígio. Um dos gêneros de peixe de nadadeira raiada (Actinopterygii) com nome formal documentados para o Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299. | HAMEL, M.-H. 2005. A new actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
-        </is>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>56</v>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
@@ -5485,7 +5482,11 @@
       <c r="R57" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2023.3.07</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -5500,7 +5501,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Irajapintoseidon uruguayensis Beltan, 1975</t>
+          <t>Daphnaechelus sp.</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -5525,7 +5526,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Hamel, M.-H. (2005) — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>Citação de mídia — Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -5540,21 +5541,21 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio. Espécie de actinopterígio nomeada formalmente, registrada no Campáleo UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica que trate deste táxon. A Wikipédia (verbete «Lontras Shale Lagerstätte») lista Daphnaechelus sp. no afloramento Campáleo como «a ray-finned fish», sem autoria, ano nem referência para o táxon; o texto de Mouro et al. (2020) não cita o gênero. A classificação como peixe actinopterígio e a atribuição ao Campáleo seguem apenas esse verbete. CORREÇÃO (2026.09.14): a ficha citava Malabarba (1988), Hamel (2005) e Richter (1991), obras que tratam de outros táxons ou da ictiofauna em geral, e apontava para um artigo sobre larvas de tricóptero; ambos foram retirados. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
+          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (listagem de fósseis do Campáleo — compilação secundária, sem referência por táxon)</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299. | HAMEL, M.-H. 2005. A new actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
@@ -5587,7 +5588,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Roslerichthys riomafrensis Hamel, 2005</t>
+          <t>Irajapintoseidon uruguayensis</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -5612,7 +5613,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Hamel, M.-H. (2005) — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>Citação de mídia — Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -5627,21 +5628,21 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao rio Mafra; um dos peixes formalmente descritos do Lagerstätte UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica que trate deste táxon. A Wikipédia (verbete «Lontras Shale Lagerstätte») lista Irajapintoseidon uruguayensis no afloramento Campáleo como «a ray-finned fish», sem autoria, ano nem referência para o táxon; o texto de Mouro et al. (2020) não cita a espécie. A classificação como peixe actinopterígio e a atribuição ao Campáleo seguem apenas esse verbete. CORREÇÃO (2026.09.14): a ficha trazia a autoria «Beltan, 1975», que não foi confirmada em nenhuma fonte consultada e foi retirada; também citava Malabarba (1988), Hamel (2005) e Richter (1991), que tratam de outros táxons ou da ictiofauna em geral, e um artigo sobre larvas de tricóptero, todos retirados. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
+          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (listagem de fósseis do Campáleo — compilação secundária, sem referência por táxon)</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299. | HAMEL, M.-H. 2005. A new actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
         </is>
       </c>
       <c r="N59" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
@@ -5674,7 +5675,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Santosichthys mafrensis Malabarba, 1988</t>
+          <t>Roslerichthys riomafrensis Hamel, 2005</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -5699,7 +5700,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Hamel, M.-H. (2005) — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26; Richter, M. (1991) — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>Hamel, M.-H. (2005) — "A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -5714,21 +5715,23 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio. Epíteto específico faz referência ao município de Mafra UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Classificação: peixe actinopterígio; o título da obra que descreve o táxon fala em «lower actinopterygian». CONTEXTO CIENTÍFICO: Mouro et al. (2020) afirmam que cerca de duzentos actinopterígios basais completos do Folhelho Lontras 'foram há muito descritos' citando Malabarba (1988), Richter (1991) e Hamel (2005), mas o texto não nomeia as espécies. A atribuição da espécie ao afloramento Campáleo segue a listagem do verbete «Lontras Shale Lagerstätte» (Wikipédia, secundária). CORREÇÃO (2026.09.14): a ficha repetia as mesmas três obras dos demais peixes do Campáleo (inclusive Malabarba, 1988, que trata de outra espécie) e uma frase sobre a origem do epíteto que não tinha fonte; ambas retiradas. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
+          <t>https://www.researchgate.net/publication/232677809_A_new_lower_actinopterygian_from_the_Early_Permian_of_the_Parana_Basin_Brazil (página da obra de Hamel, 2005 — texto integral não consultado)
+https://doi.org/10.1016/j.palaeo.2020.109850 (contexto do Folhelho Lontras — Mouro et al., 2020; não nomeia a espécie)
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (listagem de fósseis do Campáleo — compilação secundária)</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299 — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299. | HAMEL, M.-H. 2005. A new actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26 — "A new actinopterygian from the Early Permian of the Paraná Basin, Brazil", Journal of Vertebrate Paleontology 25(1):19–26. | RICHTER, M. 1991. A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil. Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp. — "A New Marine Ichthyofauna from the Permian of the Paraná Basin of Southern Brazil", Tese de Doutorado (Ph.D.), King's College London, University of London, 233 pp.</t>
+          <t>HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
@@ -5761,892 +5764,889 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Santosichthys mafrensis Malabarba, 1988</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — peixes</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Malabarba, M.C.S.L. (1988) — "A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil", Zoological Journal of the Linnean Society 94:287–299; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: peixe actinopterígio; o título da obra que descreve o táxon fala em «stem group actinopteran fish». CONTEXTO CIENTÍFICO: Mouro et al. (2020) afirmam que cerca de duzentos actinopterígios basais completos do Folhelho Lontras 'foram há muito descritos' citando Malabarba (1988), Richter (1991) e Hamel (2005), mas o texto não nomeia as espécies. A atribuição da espécie ao afloramento Campáleo segue a listagem do verbete «Lontras Shale Lagerstätte» (Wikipédia, secundária). CORREÇÃO (2026.09.14): a ficha repetia as mesmas três obras dos demais peixes do Campáleo (inclusive Hamel, 2005, que trata de outra espécie) e uma frase sobre a origem do epíteto que não tinha fonte; ambas retiradas. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850 (contexto do Folhelho Lontras — Mouro et al., 2020; não nomeia a espécie)
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (listagem de fósseis do Campáleo — compilação secundária)</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>MALABARBA, M.C.S.L. 1988. A new genus and species of stem group actinopteran fish from the Lower Permian of Santa Catarina State, Brazil. Zoological Journal of the Linnean Society, 94, 287–299. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Grupo Itararé / Folhelho Lontras</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
           <t>Coelacanthus sp.</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M61" s="7" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
+      <c r="N62" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="O61" s="6" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P61" s="6" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="n">
+      <c r="Q62" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R61" s="6" t="n">
+      <c r="R62" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S61" s="6" t="inlineStr">
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Annelida indet. (escolecodontes) / Paulinitidae / Polychaetaspidae</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — anelídeo poliqueta (mandíbulas fossilizadas)</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2011) — "Ocorrência de escolecodontes (Annelida, Labidognatha) nas formações Mafra e Rio do Sul, Permo-Carbonífero da Bacia do Paraná, Brasil", Paleontologia em Destaque 64:31–32; Mouro, L.D., Fernandes, A.C.S., Carvalho, M.A. &amp; Weinschütz, L.C. (2018) — "O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual", Anuário do Instituto de Geociências 41(2):636–646; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>Mais de 20 escolecodontes articulados (mandíbulas de poliquetas) preservados em concreções, alguns com possíveis vestígios de tecido mole e cerdas (quetas) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2011. Ocorrência de escolecodontes (Annelida, Labidognatha) nas formações Mafra e Rio do Sul, Permo-Carbonífero da Bacia do Paraná, Brasil. Paleontologia em Destaque, 64, 31–32. | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências, 41(2), 636–646. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N63" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="O62" s="4" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P62" s="4" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q62" s="4" t="n">
+      <c r="Q63" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R62" s="4" t="n">
+      <c r="R63" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S62" s="4" t="inlineStr">
+      <c r="S63" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Eumalacostraca indet. / Ostracoda indet.</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — crustáceo (malacostráceo e ostracode)</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>Malacostráceos muito fragmentários, raramente completos; ostracodes encontrados em pequenos agrupamentos (~175 μm) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M63" s="7" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
+      <c r="N64" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="O63" s="6" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
+      <c r="Q64" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R63" s="6" t="n">
+      <c r="R64" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S63" s="6" t="inlineStr">
+      <c r="S64" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Arachnostega isp.</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — bioerosão em concha</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>Vinn, O., Zabini, C. &amp; Weinschütz, L.C. (2019) — "Ichnofossils associated with lingulide shells from the Lower Permian of Brazil", Carnets de Géologie 2019(19):439–444, DOI 10.4267/2042/70636</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: escavação de bioerosão em concha. Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano. Verificação (2026.09.13): a autoria anterior desta ficha (Vinn, Wilson, Mouro &amp; Fernandes) estava incorreta; a página bibliográfica consultada informa apenas 'Permiano Inferior do Brasil', e a procedência no afloramento Campáleo (Folhelho Lontras, Mafra) vem da compilação secundária do Folhelho Lontras e da coautoria de Weinschütz (CENPALEO/UnC). O mesmo artigo cita Oichnus paraboloides e O. simplex em conchas de lingulídeos.</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: escavação de bioerosão em concha. Traços de escavação no interior de conchas de braquiópodes lingulídeos, indicativos de colonização por poliquetas. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano. Verificação (2026.09.13): a autoria anterior desta ficha (Vinn, Wilson, Mouro &amp; Fernandes) estava incorreta; a página bibliográfica consultada informa apenas 'Permiano Inferior do Brasil', e a procedência no afloramento Campáleo (Folhelho Lontras, Mafra) vem da compilação secundária do Folhelho Lontras e da coautoria de Weinschütz (CENPALEO/UnC). O mesmo artigo cita Oichnus paraboloides e O. simplex em conchas de lingulídeos.</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>VINN, O.; ZABINI, C.; WEINSCHÜTZ, L.C. 2019. Ichnofossils associated with lingulide shells from the Lower Permian of Brazil. Carnets de Géologie, 2019(19), 439–444. DOI: 10.4267/2042/70636</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N65" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="O64" s="4" t="inlineStr">
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P64" s="4" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q64" s="4" t="n">
+      <c r="Q65" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R64" s="4" t="n">
+      <c r="R65" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S64" s="4" t="inlineStr">
+      <c r="S65" s="6" t="inlineStr">
         <is>
           <t>10.4267/2042/70636</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Oichnus paraboloides / O. simplex</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — perfuração de predação</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>Perfurações em conchas de braquiópodes, evidência provável de predação UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Perfurações em conchas de braquiópodes, evidência provável de predação. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M65" s="7" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
+      <c r="N66" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="O65" s="6" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P65" s="6" t="inlineStr">
+      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q66" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R65" s="6" t="n">
+      <c r="R66" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S65" s="6" t="inlineStr">
+      <c r="S66" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Enterospira (espiral intestinal)</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — conteúdo intestinal fossilizado de tubarão</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Estruturas cilíndricas (~22 mm) preservadas por fosfatização, interpretadas como conteúdo intestinal de condrictes UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Estruturas cilíndricas (~22 mm) preservadas por fosfatização, interpretadas como conteúdo intestinal de condrictes. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N67" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="O66" s="4" t="inlineStr">
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P66" s="4" t="inlineStr">
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q66" s="4" t="n">
+      <c r="Q67" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R66" s="4" t="n">
+      <c r="R67" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S66" s="4" t="inlineStr">
+      <c r="S67" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Agathoxylon sp. / Abietopitys sp.</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Flora — lenho fóssil (gimnosperma araucariácea)</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>Restos lenhosos dispersos pelo folhelho, com fragmentos comuns; também há estruturas semelhantes a âmbar (resina fossilizada) UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2020.109850
 https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
 https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 | MOURO, L.D.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. et al. 2021. Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro. in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221.</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
+      <c r="N68" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P67" s="6" t="inlineStr">
+      <c r="P68" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q68" s="4" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R67" s="6" t="n">
+      <c r="R68" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S67" s="6" t="inlineStr">
+      <c r="S68" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Mesogondolella spp.</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — conodonte (aparelho alimentar gondolelídeo)</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / UFRGS (Instituto de Geociências)</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Wilner, E. (2014) — Dissertação de Mestrado, Instituto de Geociências, UFRGS, Porto Alegre; Wilner, E., Lemos, V.B. &amp; Scomazzon, A.K. (2016) — "Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná", Gaea — Journal of Geoscience 9(1):30–36</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>UFRGS / CENPALEO</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>Primeira ocorrência de conodontes (aparelhos alimentares completos e articulados) descrita para toda a Bacia do Paraná; dezenas de elementos ramiformes inicialmente confundidos macroscopicamente com espículas de poríferos; gênero gondolelídeo marcador do Cisuraliano NOTA: o registro nº 023 ("Conodontes indet. — 5–6 espécies", apoiado em reportagem) repetia este material e foi removido em 2026.09.10. Mouro et al. (2020) relatam dezenas de aparelhos articulados e centenas de elementos isolados de Mesogondolella spp., todos fosfatizados (Scomazzon et al., 2013; Wilner et al., 2016a). UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>https://lume.ufrgs.br/handle/10183/94761
 https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>WILNER, E. 2014. Dissertação de Mestrado, Instituto de Geociências, UFRGS, Porto Alegre. | WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea — Journal of Geoscience, 9(1), 30–36.</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N69" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="O68" s="4" t="inlineStr">
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
-      <c r="P68" s="4" t="inlineStr">
+      <c r="P69" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q68" s="4" t="n">
+      <c r="Q69" s="6" t="n">
         <v>-26.1583</v>
       </c>
-      <c r="R68" s="4" t="n">
+      <c r="R69" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="S69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Actinopterygii indet. — dois morfotipos com encéfalo e tecidos moles preservados em 3D</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — peixes</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>Figueroa, R.T., Weinschütz, L.C., Giles, S. &amp; Friedman, M. (2024) — "Soft-tissue fossilization illuminates the stepwise evolution of the ray-finned fish brain", Current Biology 34(13):2831–2840, DOI 10.1016/j.cub.2024.05.027</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>CENPALEO/UnC; Univ. of Michigan; Univ. of Birmingham</t>
         </is>
       </c>
-      <c r="J69" s="6" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>Classificação: peixe actinopterígio (tecidos moles preservados). Oito espécimes preservados em concreções sideríticas foram tomografados por micro-CT, revelando preservação tridimensional de encéfalo, nervos cranianos, olhos e possíveis tecidos cardiovasculares — condição raríssima no registro fóssil, já que o tecido neural se decompõe muito rápido. Os dois morfotipos diferem tanto no esqueleto quanto no encéfalo: o mais próximo dos actinopterígios viventes apresenta telencéfalo evertido (característica das formas atuais), ausente no outro morfotipo e em Coccocephalus. Fornece um modelo revisado para a evolução do encéfalo dos peixes de nadadeiras raiadas, o maior grupo de vertebrados vivos. NOTA: o registro nº 016 ("Actinopterygii indet. — morfotipo 2") repetia estes mesmos morfotipos e foi removido em 2026.09.10. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.cub.2024.05.027
 https://www.cell.com/current-biology/fulltext/S0960-9822(24)00670-5
 https://phys.org/news/2024-06-rare-brazilian-fossil-fishes.html</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>FIGUEROA, R.T.; WEINSCHÜTZ, L.C.; GILES, S. et al. 2024. Soft-tissue fossilization illuminates the stepwise evolution of the ray-finned fish brain. Current Biology, 34(13), 2831–2840. DOI: 10.1016/j.cub.2024.05.027</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
+      <c r="N70" s="4" t="n">
         <v>98</v>
-      </c>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R69" s="6" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>10.1016/j.cub.2024.05.027</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Foraminifera bentônicos aglutinantes (indet.)</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Microfóssil — foraminífero bentônico</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>Pigão &amp; Mouro (2019) [citação completa não localizada nesta revisão]; Silva, D.C. et al. (2023) — "Paleoenvironmental variations indicated by microfossils in the upper Paleozoic Konservat-Lagerstätte of the Paraná Basin, Santa Catarina, Brazil", Journal of South American Earth Sciences</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>Estruturas reconhecidas em lâminas delgadas e discriminadas como foraminíferos bentônicos aglutinantes, sem classificação em nível taxonômico inferior. Integram a microfauna usada para reconstruir as variações paleoambientais do Lagerstätte. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981123002882</t>
-        </is>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>PIGÃO; MOURO 2019. [citação completa não localizada nesta revisão] | SILVA, D.C. et al. 2023. Paleoenvironmental variations indicated by microfossils in the upper Paleozoic Konservat-Lagerstätte of the Paraná Basin, Santa Catarina, Brazil. Journal of South American Earth Sciences.</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>99</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
@@ -6664,7 +6664,11 @@
       <c r="R70" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.cub.2024.05.027</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -6679,12 +6683,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Palinoflora do Campáleo (esporos, grãos de pólen, fungos e algas)</t>
+          <t>Foraminifera bentônicos aglutinantes (indet.)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — palinomorfos</t>
+          <t>Microfóssil — foraminífero bentônico</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -6704,7 +6708,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Boardman, D.R., Souza, P.A., Scomazzon, A.K., Félix, C.M., Mori, A.L.O. &amp; Weinschütz, L.C. (2023) — "Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana", Sedimentary Geology 459:106543, DOI 10.1016/j.sedgeo.2023.106543</t>
+          <t>Pigão &amp; Mouro (2019) [citação completa não localizada nesta revisão]; Silva, D.C. et al. (2023) — "Paleoenvironmental variations indicated by microfossils in the upper Paleozoic Konservat-Lagerstätte of the Paraná Basin, Santa Catarina, Brazil", Journal of South American Earth Sciences</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -6719,21 +6723,21 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade. IDADE: o trabalho situa o Campáleo perto do limite Carbonífero–Permiano, provavelmente no Gzheliano (fim do Carbonífero); outras fontes o posicionam no início do Permiano — a idade do afloramento segue em discussão. CORREÇÃO (2026.09.9): a revista estava registrada como Review of Palaeobotany and Palynology. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+          <t>Estruturas reconhecidas em lâminas delgadas e discriminadas como foraminíferos bentônicos aglutinantes, sem classificação em nível taxonômico inferior. Integram a microfauna usada para reconstruir as variações paleoambientais do Lagerstätte. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.sedgeo.2023.106543</t>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981123002882</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>BOARDMAN, D.R.; SOUZA, P.A.; SCOMAZZON, A.K. et al. 2023. Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana. Sedimentary Geology, 459, 106543. DOI: 10.1016/j.sedgeo.2023.106543</t>
+          <t>PIGÃO; MOURO 2019. [citação completa não localizada nesta revisão] | SILVA, D.C. et al. 2023. Paleoenvironmental variations indicated by microfossils in the upper Paleozoic Konservat-Lagerstätte of the Paraná Basin, Santa Catarina, Brazil. Journal of South American Earth Sciences.</t>
         </is>
       </c>
       <c r="N71" s="6" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
@@ -6751,11 +6755,7 @@
       <c r="R71" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>10.1016/j.sedgeo.2023.106543</t>
-        </is>
-      </c>
+      <c r="S71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -6765,544 +6765,548 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
+          <t>Grupo Itararé / Folhelho Lontras</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Palinoflora do Campáleo (esporos, grãos de pólen, fungos e algas)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Boardman, D.R., Souza, P.A., Scomazzon, A.K., Félix, C.M., Mori, A.L.O. &amp; Weinschütz, L.C. (2023) — "Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana", Sedimentary Geology 459:106543, DOI 10.1016/j.sedgeo.2023.106543</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>CENPALEO/UnC</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Assembleias palinológicas recuperadas de 12 horizontes estratigráficos do Campáleo, com esporos, grãos de pólen, fungos e algas bem preservados — 10 amostras férteis vindas de 1,15 m de folhelhos negros fossilíferos (incluindo uma concreção calcária) e 2 dos ritmitos subjacentes com dropstones. Sustentam o posicionamento do Folhelho Lontras na biozona Vittatina costabilis, uma das principais bases da datação relativa da unidade. IDADE: o trabalho situa o Campáleo perto do limite Carbonífero–Permiano, provavelmente no Gzheliano (fim do Carbonífero); outras fontes o posicionam no início do Permiano — a idade do afloramento segue em discussão. CORREÇÃO (2026.09.9): a revista estava registrada como Review of Palaeobotany and Palynology. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.sedgeo.2023.106543</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>BOARDMAN, D.R.; SOUZA, P.A.; SCOMAZZON, A.K. et al. 2023. Palynological analysis (biochronostratigraphy and paleoenvironments) from a fossil-Lagerstätte section within the Late Paleozoic Ice Age unit of the Paraná Basin (Itararé Group), Western Gondwana. Sedimentary Geology, 459, 106543. DOI: 10.1016/j.sedgeo.2023.106543</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campáleo (Mafra)</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>-26.1583</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>-49.8147</v>
+      </c>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.sedgeo.2023.106543</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
           <t>Grupo Itararé / Fm. Rio do Sul</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Icnofauna do Afloramento Campo da Lança (8 icnogêneros)</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança, região de Mafra, SC</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322, DOI 10.5212/TerraPlural.v.15.2118322.039; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>FURB; UNISINOS; UFU</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>Assembleia com oito icnogêneros reconhecidos no siltito do Campo da Lança, incluindo Protichnites, Rusophycus, Thalassinoides, Diplocraterion e Rhizocorallium. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="M73" s="7" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; SEDORKO, D. 2021. Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil. Terr@Plural, 15, e2118322. DOI: 10.5212/TerraPlural.v.15.2118322.039 | BALISTIERI, P.R.M.N.; NETTO, R.G. 2002. A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints. Acta Geologica Leopoldensia, 55, 91–106.</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N73" s="6" t="n">
         <v>196</v>
       </c>
-      <c r="O72" s="4" t="inlineStr">
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança</t>
         </is>
       </c>
-      <c r="P72" s="4" t="inlineStr">
+      <c r="P73" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q72" s="4" t="n">
+      <c r="Q73" s="6" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R72" s="4" t="n">
+      <c r="R73" s="6" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S72" s="4" t="inlineStr">
+      <c r="S73" s="6" t="inlineStr">
         <is>
           <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Rio do Sul</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Rusophycus cf. carbonarius Dawson (traço de repouso de artrópode)</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança, região de Mafra, SC</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322, DOI 10.5212/TerraPlural.v.15.2118322.039; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>FURB; UNISINOS; UFU</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K73" s="7" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>Traço de repouso atribuído a artrópode, reconhecido nas assembleias do Grupo Itararé catarinense. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
         </is>
       </c>
-      <c r="L73" s="7" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M73" s="7" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; SEDORKO, D. 2021. Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil. Terr@Plural, 15, e2118322. DOI: 10.5212/TerraPlural.v.15.2118322.039 | BALISTIERI, P.R.M.N.; NETTO, R.G. 2002. A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints. Acta Geologica Leopoldensia, 55, 91–106.</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n">
+      <c r="N74" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="O73" s="6" t="inlineStr">
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança</t>
         </is>
       </c>
-      <c r="P73" s="6" t="inlineStr">
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q74" s="4" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R73" s="6" t="n">
+      <c r="R74" s="4" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S73" s="6" t="inlineStr">
+      <c r="S74" s="4" t="inlineStr">
         <is>
           <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Rio do Sul</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Protichnites isp. (pista de artrópode)</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança, região de Mafra, SC</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322, DOI 10.5212/TerraPlural.v.15.2118322.039; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>FURB; UNISINOS; UFU</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>Pista de artrópode recorrente nas icnocenoses do Grupo Itararé em Santa Catarina. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.7): o Afloramento Campo da Lança fica na REGIÃO DE MAFRA (Netto et al., 2007, perfil do afloramento; Balistieri &amp; Netto, 2002); versões anteriores o atribuíam a Doutor Pedrinho, por engano. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M75" s="7" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; SEDORKO, D. 2021. Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil. Terr@Plural, 15, e2118322. DOI: 10.5212/TerraPlural.v.15.2118322.039 | BALISTIERI, P.R.M.N.; NETTO, R.G. 2002. A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints. Acta Geologica Leopoldensia, 55, 91–106.</t>
         </is>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N75" s="6" t="n">
         <v>198</v>
       </c>
-      <c r="O74" s="4" t="inlineStr">
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>Afloramento Campo da Lança</t>
         </is>
       </c>
-      <c r="P74" s="4" t="inlineStr">
+      <c r="P75" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q74" s="4" t="n">
+      <c r="Q75" s="6" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R74" s="4" t="n">
+      <c r="R75" s="6" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S74" s="4" t="inlineStr">
+      <c r="S75" s="6" t="inlineStr">
         <is>
           <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Icnofauna do Afloramento Bela Vista do Sul</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322, DOI 10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>FURB; UNISINOS; UFU</t>
         </is>
       </c>
-      <c r="J75" s="6" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K75" s="7" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>Ritmitos síltico-argilosos gradando a síltico-arenosos rumo ao topo, com acamamento ondulado. A icnofauna reúne Cruziana, Diplichnites, Diplopodichnus, Lockeia, Protovirgularia e Rusophycus. Topo da Fm. Rio do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M75" s="7" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; SEDORKO, D. 2021. Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil. Terr@Plural, 15, e2118322. DOI: 10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
+      <c r="N76" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="O75" s="6" t="inlineStr">
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>Afloramento Bela Vista do Sul</t>
         </is>
       </c>
-      <c r="P75" s="6" t="inlineStr">
+      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="n">
+      <c r="Q76" s="4" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R75" s="6" t="n">
+      <c r="R76" s="4" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S75" s="6" t="inlineStr">
+      <c r="S76" s="4" t="inlineStr">
         <is>
           <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Rio do Sul (topo)</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Lockeia siliquaria (traço de repouso de bivalve)</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Distrito de Bela Vista do Sul, Mafra, SC</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Sedorko, D. (2021) — "Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil", Terr@Plural 15:e2118322, DOI 10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>FURB; UNISINOS; UFU</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J77" s="6" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>Traço de repouso produzido por bivalve, componente da icnofauna de Bela Vista do Sul. Revisão que reuniu 17 trabalhos descrevendo a icnofauna de SEIS afloramentos em CINCO municípios catarinenses — os únicos estudados de toda a faixa aflorante das formações Mafra e Rio do Sul no estado. Foram reconhecidas as icnofácies Mermia, Scoyenia, Cruziana empobrecida e Glossifungites, além das mistas Mermia-Scoyenia e Scoyenia-Cruziana. O registro icnológico catarinense do Grupo Itararé remonta a Maury (1927), em Anitápolis. CORREÇÃO (2026.09.6): Bela Vista do Sul é distrito do município de MAFRA; versões anteriores atribuíam este afloramento a Doutor Pedrinho, por engano. RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.5212/TerraPlural.v.15.2118322.039
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; SEDORKO, D. 2021. Estado da arte da Paleoicnologia do Grupo Itararé no estado de Santa Catarina e município de Rio Negro, PR, Brasil. Terr@Plural, 15, e2118322. DOI: 10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
-      <c r="N76" s="4" t="n">
+      <c r="N77" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="O76" s="4" t="inlineStr">
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>Afloramento Bela Vista do Sul</t>
         </is>
       </c>
-      <c r="P76" s="4" t="inlineStr">
+      <c r="P77" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q76" s="4" t="n">
+      <c r="Q77" s="6" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R76" s="4" t="n">
+      <c r="R77" s="6" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S76" s="4" t="inlineStr">
+      <c r="S77" s="6" t="inlineStr">
         <is>
           <t>10.5212/TerraPlural.v.15.2118322.039</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Neonereites isp.</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Coleções UNISINOS / UFRGS</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b) — "A presença de Cruziana nos sedimentos da Formação Rio do Sul (Grupo Itararé, Permo-Carbonífero da Bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:387–396</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>UNISINOS; UFRGS</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>Escavação rasa que complementa a assembleia dominada por pistas de artrópodes. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
-        </is>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="inlineStr">
-        <is>
-          <t>NOGUEIRA, M.S.; NETTO, R.G. 2001a. Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil. Acta Geologica Leopoldensia, 52/53, 397–406. | NOGUEIRA, M.S.; NETTO, R.G. 2001b. A presença de Cruziana nos sedimentos da Formação Rio do Sul (Grupo Itararé, Permo-Carbonífero da Bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil. Acta Geologica Leopoldensia, 52/53, 387–396.</t>
-        </is>
-      </c>
-      <c r="N77" s="6" t="n">
-        <v>201</v>
-      </c>
-      <c r="O77" s="6" t="inlineStr">
-        <is>
-          <t>Pedreira Itaú-Itaúna</t>
-        </is>
-      </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q77" s="6" t="n">
-        <v>-27.305</v>
-      </c>
-      <c r="R77" s="6" t="n">
-        <v>-49.795</v>
-      </c>
-      <c r="S77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -7317,7 +7321,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Gluckstadtella isp.</t>
+          <t>Neonereites isp.</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7357,7 +7361,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>Escavação rasa presente na assembleia da Fm. Rio do Sul em Trombudo Central. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Escavação rasa que complementa a assembleia dominada por pistas de artrópodes. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
@@ -7371,7 +7375,7 @@
         </is>
       </c>
       <c r="N78" s="4" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Rusophycus isp. (Pedreira Itaú-Itaúna)</t>
+          <t>Gluckstadtella isp.</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -7444,7 +7448,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Traço de repouso de artrópode, componente menos frequente da assembleia. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Escavação rasa presente na assembleia da Fm. Rio do Sul em Trombudo Central. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -7458,7 +7462,7 @@
         </is>
       </c>
       <c r="N79" s="6" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
@@ -7491,7 +7495,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Icnofauna da Pedreira Waltrick</t>
+          <t>Rusophycus isp. (Pedreira Itaú-Itaúna)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -7506,7 +7510,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Pedreira Waltrick, Trombudo Central, SC</t>
+          <t>Pedreira Itaú-Itaúna, Trombudo Central, SC</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -7516,7 +7520,7 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148, DOI 10.1016/j.jsames.2015.07.008</t>
+          <t>Nogueira, M.S. &amp; Netto, R.G. (2001a) — "Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:397–406; Nogueira, M.S. &amp; Netto, R.G. (2001b) — "A presença de Cruziana nos sedimentos da Formação Rio do Sul (Grupo Itararé, Permo-Carbonífero da Bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil", Acta Geologica Leopoldensia 52/53:387–396</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -7531,25 +7535,25 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>Terceira pedreira de ritmitos estudada na área de Trombudo Central (UTM 620026/6981727), ao lado de Itaú-Itaúna e Fama. Integra o conjunto de afloramentos que documenta a icnofauna dos depósitos de deglaciação da Fm. Rio do Sul. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Traço de repouso de artrópode, componente menos frequente da assembleia. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
+          <t>https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G. et al. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 63, 137–148. DOI: 10.1016/j.jsames.2015.07.008</t>
+          <t>NOGUEIRA, M.S.; NETTO, R.G. 2001a. Icnofauna da Formação Rio do Sul (Grupo Itararé, Permiano da bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil. Acta Geologica Leopoldensia, 52/53, 397–406. | NOGUEIRA, M.S.; NETTO, R.G. 2001b. A presença de Cruziana nos sedimentos da Formação Rio do Sul (Grupo Itararé, Permo-Carbonífero da Bacia do Paraná) na Pedreira Itaú-Itaúna, Santa Catarina, Brasil. Acta Geologica Leopoldensia, 52/53, 387–396.</t>
         </is>
       </c>
       <c r="N80" s="4" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>Pedreira Waltrick</t>
+          <t>Pedreira Itaú-Itaúna</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -7563,11 +7567,7 @@
       <c r="R80" s="4" t="n">
         <v>-49.795</v>
       </c>
-      <c r="S80" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.jsames.2015.07.008</t>
-        </is>
-      </c>
+      <c r="S80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Icnofauna da Pedreira Fama</t>
+          <t>Icnofauna da Pedreira Waltrick</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Pedreira Fama, Trombudo Central, SC</t>
+          <t>Pedreira Waltrick, Trombudo Central, SC</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Pedreira de ritmitos (UTM 619813/6981938) estudada em conjunto com Itaú-Itaúna e Waltrick, compondo o registro icnológico dos depósitos de deglaciação do topo do Grupo Itararé. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
+          <t>Terceira pedreira de ritmitos estudada na área de Trombudo Central (UTM 620026/6981727), ao lado de Itaú-Itaúna e Fama. Integra o conjunto de afloramentos que documenta a icnofauna dos depósitos de deglaciação da Fm. Rio do Sul. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -7636,11 +7636,11 @@
         </is>
       </c>
       <c r="N81" s="6" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
-          <t>Pedreira Fama</t>
+          <t>Pedreira Waltrick</t>
         </is>
       </c>
       <c r="P81" s="6" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Protovirgularia dichotoma</t>
+          <t>Icnofauna da Pedreira Fama</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Pedreiras de ritmitos, Trombudo Central, SC</t>
+          <t>Pedreira Fama, Trombudo Central, SC</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>Traço de locomoção produzido pelo pé de um bivalve. Completa as DEZ icnoespécies reconhecidas por Lima et al. (2015) nos ritmitos de Trombudo Central: Cruziana problematica, Diplichnites gouldi, Diplopodichnus biformis, Glaciichnium liebegastensis, Gluckstadtella elongata, Helminthoidichnites tenuis, Mermia carickensis, Protovirgularia dichotoma, Treptichnus pollardi e Umfolozia sinuosa — todas agora presentes neste catálogo.</t>
+          <t>Pedreira de ritmitos (UTM 619813/6981938) estudada em conjunto com Itaú-Itaúna e Waltrick, compondo o registro icnológico dos depósitos de deglaciação do topo do Grupo Itararé. A Fm. Rio do Sul registra a MAIOR DIVERSIDADE FOSSILÍFERA do Grupo Itararé, com cerca de 17 icnogêneros descritos. Na pedreira Itaú-Itaúna a assembleia é dominada por pistas de locomoção (Umfolozia, Diplopodichnus, Diplichnites), complementadas por escavações rasas. Compõe duas suítes: uma de pistas de artrópodes e escavações rasas, ligada à icnofácies Scoyenia; outra dominada por Helminthoidichnites, indicando pastagem em ambiente subaquático. A análise paleobiológica indica que animais terrestres (milípedes) e aquáticos (crustáceos e larvas de insetos) colonizaram os substratos, num ambiente deposicional dinâmico.</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="N82" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>Pedreira Itaú-Itaúna</t>
+          <t>Pedreira Fama</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Grupo Itararé / formações Campo Mourão e Taciba</t>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Icnofósseis indet. de sistema de fiorde (Presidente Getúlio)</t>
+          <t>Protovirgularia dichotoma</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -7779,22 +7779,22 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Afloramentos da região de Presidente Getúlio, SC</t>
+          <t>Pedreiras de ritmitos, Trombudo Central, SC</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Coleções UNISINOS / UFRGS</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Oliveira, V.G. (2019) — "Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina", Trabalho de Conclusão de Curso, Geologia, UFSC</t>
+          <t>Lima, J.H.D., Netto, R.G., Corrêa, C.G. &amp; Lavina, E.L.C. (2015) — "Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil)", Journal of South American Earth Sciences 63:137–148, DOI 10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>UNISINOS; UFRGS</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
@@ -7804,25 +7804,25 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Traços fósseis reconhecidos nas formações Campo Mourão e Taciba, em sucessão de 17 litofácies agrupadas em cinco associações que definem subambientes de um amplo SISTEMA DE FIORDE, ligados a ciclos de transgressão–regressão glacio-influenciados. O tamanho reduzido dos traços e a baixa diversidade, em comparação com o esperado para ambientes plenamente marinhos, são justamente o argumento paleoambiental que sustenta a interpretação de fiorde. RESSALVA: o trabalho é de natureza estratigráfica e não identifica os icnofósseis em nível icnotaxonômico — o registro consta como ocorrência, não como táxon determinado.</t>
+          <t>Traço de locomoção produzido pelo pé de um bivalve. Completa as DEZ icnoespécies reconhecidas por Lima et al. (2015) nos ritmitos de Trombudo Central: Cruziana problematica, Diplichnites gouldi, Diplopodichnus biformis, Glaciichnium liebegastensis, Gluckstadtella elongata, Helminthoidichnites tenuis, Mermia carickensis, Protovirgularia dichotoma, Treptichnus pollardi e Umfolozia sinuosa — todas agora presentes neste catálogo.</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>https://repositorio.ufsc.br/handle/123456789/204084</t>
+          <t>https://doi.org/10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>OLIVEIRA, V.G. 2019. Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina. Trabalho de Conclusão de Curso, Geologia, UFSC.</t>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G. et al. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 63, 137–148. DOI: 10.1016/j.jsames.2015.07.008</t>
         </is>
       </c>
       <c r="N83" s="6" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>Região de Presidente Getúlio</t>
+          <t>Pedreira Itaú-Itaúna</t>
         </is>
       </c>
       <c r="P83" s="6" t="inlineStr">
@@ -7831,12 +7831,16 @@
         </is>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>-27.0453</v>
+        <v>-27.305</v>
       </c>
       <c r="R83" s="6" t="n">
-        <v>-49.6231</v>
-      </c>
-      <c r="S83" s="6" t="inlineStr"/>
+        <v>-49.795</v>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2015.07.008</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -7846,346 +7850,342 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
+          <t>Grupo Itararé / formações Campo Mourão e Taciba</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Icnofósseis indet. de sistema de fiorde (Presidente Getúlio)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Afloramentos da região de Presidente Getúlio, SC</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Oliveira, V.G. (2019) — "Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina", Trabalho de Conclusão de Curso, Geologia, UFSC</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>UFSC</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Traços fósseis reconhecidos nas formações Campo Mourão e Taciba, em sucessão de 17 litofácies agrupadas em cinco associações que definem subambientes de um amplo SISTEMA DE FIORDE, ligados a ciclos de transgressão–regressão glacio-influenciados. O tamanho reduzido dos traços e a baixa diversidade, em comparação com o esperado para ambientes plenamente marinhos, são justamente o argumento paleoambiental que sustenta a interpretação de fiorde. RESSALVA: o trabalho é de natureza estratigráfica e não identifica os icnofósseis em nível icnotaxonômico — o registro consta como ocorrência, não como táxon determinado.</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>https://repositorio.ufsc.br/handle/123456789/204084</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>OLIVEIRA, V.G. 2019. Evolução paleoambiental e estratigráfica do Grupo Itararé (Bacia do Paraná) região de Presidente Getúlio, Santa Catarina. Trabalho de Conclusão de Curso, Geologia, UFSC.</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>Região de Presidente Getúlio</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>-27.0453</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>-49.6231</v>
+      </c>
+      <c r="S84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
           <t>Grupo Itararé / Fm. Mafra</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Hormosiroidea meandrica (Fazenda Potreiro)</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>CP/P (coleção CENPALEO)</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>Fazenda Potreiro, Mafra, SC</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002) — "Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy", Revista Brasileira de Paleontologia 4:13–26; Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255, DOI 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>UNISINOS; CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J85" s="6" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>Icnoespécie proposta como nova por Balistieri e colaboradores (2002–2003) a partir dos ritmitos da região de Mafra (SC) e Rio Negro (PR). ATENÇÃO: a fonte consultada não permite afirmar em qual dos afloramentos — o catarinense ou o paranaense — está o material-tipo; por isso esta ficha NÃO a trata como localidade-tipo. Escavação meandrante rasa, preservada sobretudo como crista hipicnial. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="M85" s="7" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; LAVINA, E.L.C. 2002. Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy. Revista Brasileira de Paleontologia, 4, 13–26. | NETTO, R.G.; BALISTIERI, P.R.M.N.; LAVINA, E.L.C. et al. 2009. Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil). Palaeogeography, Palaeoclimatology, Palaeoecology, 272, 240–255. DOI: 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n">
+      <c r="N85" s="6" t="n">
         <v>218</v>
       </c>
-      <c r="O84" s="4" t="inlineStr">
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>Fazenda Potreiro</t>
         </is>
       </c>
-      <c r="P84" s="4" t="inlineStr">
+      <c r="P85" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q84" s="4" t="n">
+      <c r="Q85" s="6" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R84" s="4" t="n">
+      <c r="R85" s="6" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S84" s="4" t="inlineStr">
+      <c r="S85" s="6" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Mafra</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Undichna consulca</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — vertebrado (trilha de nadadeira de peixe)</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>Fazenda Potreiro, Mafra, SC</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002) — "Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy", Revista Brasileira de Paleontologia 4:13–26; Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255, DOI 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>UNISINOS; CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t>Trilha deixada pela nadadeira de um PEIXE ao roçar o fundo lamoso — um dos raros registros de atividade de vertebrado na icnofauna do Grupo Itararé catarinense. Aparece recoberta por trilhas de Diplichnites gouldi, em preservação palimpséstica. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; LAVINA, E.L.C. 2002. Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy. Revista Brasileira de Paleontologia, 4, 13–26. | NETTO, R.G.; BALISTIERI, P.R.M.N.; LAVINA, E.L.C. et al. 2009. Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil). Palaeogeography, Palaeoclimatology, Palaeoecology, 272, 240–255. DOI: 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
+      <c r="N86" s="4" t="n">
         <v>219</v>
       </c>
-      <c r="O85" s="6" t="inlineStr">
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Fazenda Potreiro</t>
         </is>
       </c>
-      <c r="P85" s="6" t="inlineStr">
+      <c r="P86" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Grupo Itararé</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="n">
+      <c r="Q86" s="4" t="n">
         <v>-26.1112</v>
       </c>
-      <c r="R85" s="6" t="n">
+      <c r="R86" s="4" t="n">
         <v>-49.805</v>
       </c>
-      <c r="S85" s="6" t="inlineStr">
+      <c r="S86" s="4" t="inlineStr">
         <is>
           <t>10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Grupo Itararé / Fm. Mafra</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>Gordia arcuata e Gordia marina</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — invertebrado</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Fazenda Potreiro, Mafra, SC</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>Balistieri, P.R.M.N., Netto, R.G. &amp; Lavina, E.L.C. (2002) — "Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy", Revista Brasileira de Paleontologia 4:13–26; Netto, R.G., Balistieri, P.R.M.N., Lavina, E.L.C. &amp; Silveira, D.M. (2009) — "Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil)", Palaeogeography, Palaeoclimatology, Palaeoecology 272:240–255, DOI 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>UNISINOS; CENPALEO/UnC</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J87" s="6" t="inlineStr">
         <is>
           <t>ca. 300–295 Ma</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>Escavações de pastagem finas e sinuosas, componentes da suíte de escavações rasas dos ritmitos lacustres. Fazenda Potreiro, Mafra: ritmitos da Fm. Mafra interpretados como depósitos de LAGOS RASOS DE ÁGUA DOCE da glaciação neopaleozoica. A suíte é dominada por escavações rasas de pastagem e alimentação (icnocenose Mermia), evidência de colonização subaquática de substratos moles por organismos não marinhos. Material na coleção do CENPALEO (sigla CP/P). RESSALVA DE COORDENADA: a fonte não publica a coordenada exata da localidade; usa-se a da sede municipal de Mafra.</t>
         </is>
       </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.palaeo.2008.10.028
 https://revistas.uepg.br/index.php/tp/article/view/18322</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="M87" s="7" t="inlineStr">
         <is>
           <t>BALISTIERI, P.R.M.N.; NETTO, R.G.; LAVINA, E.L.C. 2002. Ichnofauna from the Upper Carboniferous-Lower Permian rhythmites from Mafra, Santa Catarina State, Brazil: Ichnotaxonomy. Revista Brasileira de Paleontologia, 4, 13–26. | NETTO, R.G.; BALISTIERI, P.R.M.N.; LAVINA, E.L.C. et al. 2009. Ichnological signatures of shallow freshwater lakes in the glacial Itararé Group (Mafra Formation, Upper Carboniferous–Lower Permian of Paraná Basin, S Brazil). Palaeogeography, Palaeoclimatology, Palaeoecology, 272, 240–255. DOI: 10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n">
+      <c r="N87" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="O86" s="4" t="inlineStr">
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>Fazenda Potreiro</t>
-        </is>
-      </c>
-      <c r="P86" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="n">
-        <v>-26.1112</v>
-      </c>
-      <c r="R86" s="4" t="n">
-        <v>-49.805</v>
-      </c>
-      <c r="S86" s="4" t="inlineStr">
-        <is>
-          <t>10.1016/j.palaeo.2008.10.028</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Fm. Rio do Sul</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Escavações tipo Gyrolithes (Gyrolithes-like burrows)</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Icnofóssil — invertebrado</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>Netto, R.G., Buatois, L.A., Mángano, M.G. &amp; Balistieri, P. (2007) — "Gyrolithes as a multipurpose burrow: an ethologic approach", Revista Brasileira de Paleontologia 10(3):157–168, DOI 10.4072/rbp.2007.3.03; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>FURB; UNISINOS; UFU</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>ca. 300–295 Ma</t>
-        </is>
-      </c>
-      <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>Escavações helicoidais semelhantes a Gyrolithes, parte da suíte Glossifungites do Campo da Lança, junto a Thalassinoides, Diplocraterion e ?Rhizocorallium. Indicam colonização de substrato firme exumado por erosão transgressiva. Nos depósitos eopermianos das formações Rio do Sul e Rio Bonito, essas formas ocorrem sempre em suítes de substrato firme. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
-        </is>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>https://www.sbpbrasil.org/revista/edicoes/10_3/netto.pdf</t>
-        </is>
-      </c>
-      <c r="M87" s="7" t="inlineStr">
-        <is>
-          <t>NETTO, R.G.; BUATOIS, L.A.; MÁNGANO, M.G. et al. 2007. Gyrolithes as a multipurpose burrow: an ethologic approach. Revista Brasileira de Paleontologia, 10(3), 157–168. DOI: 10.4072/rbp.2007.3.03 | BALISTIERI, P.R.M.N.; NETTO, R.G. 2002. A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints. Acta Geologica Leopoldensia, 55, 91–106.</t>
-        </is>
-      </c>
-      <c r="N87" s="6" t="n">
-        <v>224</v>
-      </c>
-      <c r="O87" s="6" t="inlineStr">
-        <is>
-          <t>Afloramento Campo da Lança</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="S87" s="6" t="inlineStr">
         <is>
-          <t>10.4072/rbp.2007.3.03</t>
+          <t>10.1016/j.palaeo.2008.10.028</t>
         </is>
       </c>
     </row>
@@ -8213,158 +8213,158 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>Grupo Itararé / Fm. Rio do Sul</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Escavações tipo Gyrolithes (Gyrolithes-like burrows)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — invertebrado</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança, região de Mafra, SC</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Coleção do Centro Paleontológico de Mafra (CENPALEO/UnC)</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Netto, R.G., Buatois, L.A., Mángano, M.G. &amp; Balistieri, P. (2007) — "Gyrolithes as a multipurpose burrow: an ethologic approach", Revista Brasileira de Paleontologia 10(3):157–168, DOI 10.4072/rbp.2007.3.03; Balistieri, P.R.M.N. &amp; Netto, R.G. (2002) — "A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints", Acta Geologica Leopoldensia 55:91–106</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>FURB; UNISINOS; UFU</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>ca. 300–295 Ma</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Escavações helicoidais semelhantes a Gyrolithes, parte da suíte Glossifungites do Campo da Lança, junto a Thalassinoides, Diplocraterion e ?Rhizocorallium. Indicam colonização de substrato firme exumado por erosão transgressiva. Nos depósitos eopermianos das formações Rio do Sul e Rio Bonito, essas formas ocorrem sempre em suítes de substrato firme. Coordenada da sede municipal de Mafra; a do afloramento não é publicada.</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sbpbrasil.org/revista/edicoes/10_3/netto.pdf</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>NETTO, R.G.; BUATOIS, L.A.; MÁNGANO, M.G. et al. 2007. Gyrolithes as a multipurpose burrow: an ethologic approach. Revista Brasileira de Paleontologia, 10(3), 157–168. DOI: 10.4072/rbp.2007.3.03 | BALISTIERI, P.R.M.N.; NETTO, R.G. 2002. A Glossifungites suite in deposits of the Itararé Group (Upper Carboniferous–Lower Permian of Paraná Basin) at Mafra region, North of Santa Catarina State, Brazil: Ichnotaxonomy, and paleoecological and stratigraphical constraints. Acta Geologica Leopoldensia, 55, 91–106.</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>Afloramento Campo da Lança</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Grupo Itararé</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>-26.1112</v>
+      </c>
+      <c r="R88" s="4" t="n">
+        <v>-49.805</v>
+      </c>
+      <c r="S88" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2007.3.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Carbonífero – Permiano Inferior</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
           <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Estojos larvais de Trichoptera / Permotrichoptera</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — inseto</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>Mouro, L.D., Zatoń, M., Fernandes, A.C.S. &amp; Waichel, B.L. (2016) — "Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana", Scientific Reports 6:19215, DOI 10.1038/srep19215; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>CENPALEO/UnC; UFPR</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J89" s="6" t="inlineStr">
         <is>
           <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
+      <c r="K89" s="7" t="inlineStr">
         <is>
           <t>Classificação: inseto (estojo larval). Possivelmente os estojos larvais de tricópteros mais antigos conhecidos, relacionados às ordens Trichoptera ou Permotrichoptera. São faixas esbranquiçadas com estruturas filamentosas semelhantes à seda das larvas atuais, enriquecidas em cálcio e enxofre segundo análise por EDS. Notáveis por ocorrerem num ambiente marinho. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1038/srep19215
 https://doi.org/10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="M89" s="7" t="inlineStr">
         <is>
           <t>MOURO, L.D.; ZATOŃ, M.; FERNANDES, A.C.S. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n">
+      <c r="N89" s="6" t="n">
         <v>230</v>
-      </c>
-      <c r="O88" s="4" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo (Mafra)</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Grupo Itararé</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="n">
-        <v>-26.1583</v>
-      </c>
-      <c r="R88" s="4" t="n">
-        <v>-49.8147</v>
-      </c>
-      <c r="S88" s="4" t="inlineStr">
-        <is>
-          <t>10.1038/srep19215</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Carbonífero – Permiano Inferior</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Grupo Itararé / Folhelho Lontras</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Estrutura semelhante a âmbar (possível resina fóssil)</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>Flora — resina fóssil</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Wilner, E., Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2016) — "Comunicado de possível primeiro âmbar paleozoico da Bacia do Paraná", Paleontologia em Destaque 31(69):136; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>CENPALEO/UnC; UFPR</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="inlineStr">
-        <is>
-          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>Estrutura semelhante a âmbar comunicada como possível primeiro âmbar paleozoico da Bacia do Paraná. RESSALVA: segundo Mouro et al. (2020), segue em descrição — a natureza do material ainda não foi confirmada. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.palaeo.2020.109850</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>WILNER, E.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2016. Comunicado de possível primeiro âmbar paleozoico da Bacia do Paraná. Paleontologia em Destaque, 31(69), 136. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
-        </is>
-      </c>
-      <c r="N89" s="6" t="n">
-        <v>231</v>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
@@ -8382,27 +8382,31 @@
       <c r="R89" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S89" s="6" t="inlineStr"/>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>10.1038/srep19215</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Permiano Inferior (Asseliano)</t>
+          <t>Carbonífero – Permiano Inferior</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Grupo Itararé / Fm. Campo Mourão (equivalente lateral do Folhelho Lontras)</t>
+          <t>Grupo Itararé / Folhelho Lontras</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Biota fóssil similar ao Campáleo (larvas, coprólitos, braquiópodes, esponjas, peixes)</t>
+          <t>Estrutura semelhante a âmbar (possível resina fóssil)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Assembleia fóssil (biota mista) — biota mista</t>
+          <t>Flora — resina fóssil</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -8412,51 +8416,50 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Afloramento de Rio dos Cedros, SC</t>
+          <t>Afloramento Campáleo — BR-280, a 2 km do entroncamento com a BR-116, área urbana de Mafra, SC (26°09′30,22″S, 49°48′52,82″W; Mouro et al., 2020)</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CENPALEO / Museu da Terra e da Vida, UnC, Mafra, SC</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>Citado em revisões do Lontras Shale Lagerstätte (cf. Ricetti et al. 2016 e referências associadas)</t>
+          <t>Wilner, E., Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2016) — "Comunicado de possível primeiro âmbar paleozoico da Bacia do Paraná", Paleontologia em Destaque 31(69):136; Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — "Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age", Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850, DOI 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>CENPALEO/UnC; UFPR</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>ca. 298,9 Ma</t>
+          <t>ca. 303–295 Ma (limite Carbonífero–Permiano; idade em discussão)</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>Camada de folhelho com menos de 1 m de espessura, situada a cerca de 85 km do afloramento Campáleo; possível extensão lateral do mesmo Lagerstätte, ainda pouco estudada</t>
+          <t>Estrutura semelhante a âmbar comunicada como possível primeiro âmbar paleozoico da Bacia do Paraná. RESSALVA: segundo Mouro et al. (2020), segue em descrição — a natureza do material ainda não foi confirmada. UNIDADE E IDADE (Mouro et al., 2020): o Folhelho Lontras é o topo da Fm. Campo Mourão (França &amp; Potter, 1988) — na nomenclatura de superfície de SC, base da Fm. Rio do Sul. A idade está em discussão: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano; datações U-Pb em zircão apontam Pennsylvaniano.</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf
-https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+          <t>WILNER, E.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2016. Comunicado de possível primeiro âmbar paleozoico da Bacia do Paraná. Paleontologia em Destaque, 31(69), 136. | MOURO, L.D.; PACHECO, M.L.A.F.; RICETTI, J.H.Z. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850</t>
         </is>
       </c>
       <c r="N90" s="4" t="n">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>Afloramento de Rio dos Cedros</t>
+          <t>Afloramento Campáleo (Mafra)</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -8465,10 +8468,10 @@
         </is>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>-26.6483</v>
+        <v>-26.1583</v>
       </c>
       <c r="R90" s="4" t="n">
-        <v>-49.2783</v>
+        <v>-49.8147</v>
       </c>
       <c r="S90" s="4" t="inlineStr"/>
     </row>
@@ -9136,7 +9139,7 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe ósseo. Inclui escamas de celacanto, coprólitos espiralados, braquiópodes, vegetais e poríferos</t>
+          <t>Classificação: peixe ósseo. Inclui escamas de celacanto, coprólitos espiralados, braquiópodes, vegetais e poríferos POSSÍVEL LIGAÇÃO: a 'nova localidade' pode ser a de Rio dos Cedros (registro 43), único depósito equivalente ao Folhelho Lontras citado em Saldanha et al. (2023); não confirmado, porque o resumo não pôde ser aberto.</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
@@ -10073,12 +10076,12 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC, Mafra, SC (parte do material destinada ao Museu do Contestado, Três Barras, SC)</t>
+          <t>Preparação no CENPALEO/UnC (Mafra), segundo a reportagem de 2020; em 2022, 20 peças transferidas do CENPALEO foram expostas no Museu do Patrimônio Histórico João Bedrechuk, Três Barras (Prefeitura de Três Barras)</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Identificação inicial por C.E. Fiolek (Museu do Contestado); estudo por equipe do CENPALEO/UnC (L.C. Weinschütz, E. Wilner, J.H.Z. Ricetti), divulgado em 2020; Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC</t>
+          <t>Citação de mídia — NSC Total (18/05/2020), reportagem «Seca leva à descoberta de fósseis de 280 milhões de anos em Três Barras, no Norte de SC», que atribui a identificação inicial a C.E. Fiolek (coordenador do museu de Três Barras) e a pesquisa ao CENPALEO/UnC; Citação de mídia — Prefeitura de Três Barras (05/05/2022), notícia «Fósseis de mesossauro já estão em exposição no Museu de Três Barras»; Elias, R.L. (2020) — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -10088,17 +10091,18 @@
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>ca. 280 Ma</t>
+          <t>ca. 280 Ma, segundo a reportagem (método de datação não informado)</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>Répteis aquáticos de 80 cm a 1 m, com membranas entre os dedos e dieta de pequenos crustáceos, que habitaram o "Golfo Irati". Estruturas expostas nas margens do Rio Negro durante estiagens que rebaixaram o rio (achados divulgados em 2018 e em 2020), que rebaixou o nível do rio. Os mesossauros ocorrem tanto no sul do Brasil quanto na África do Sul (Fm. Whitehill), e essa correspondência foi uma das evidências históricas da deriva continental. ATENÇÃO: registro divulgado pela imprensa a partir de identificação do CENPALEO; não foi localizada publicação científica formal descrevendo este material específico — a ocorrência de Mesosauridae na Fm. Irati em SC, contudo, é bem estabelecida na literatura. Mesossauros da Fm. Irati concentram-se, na região, em Três Barras (SC) e São Mateus do Sul (PR), e o CENPALEO guarda várias amostras. Segundo a compilação de vertebrados fósseis de SC da UFSC, não há trabalho de descrição do material de mesossauros do estado. TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este material; Elias (2020) registra que nenhum dos achados de mesossauro de SC foi descrito em periódico científico. Segundo o NSC Total (18/05/2020), a estiagem de março de 2020 rebaixou o Rio Negro e expôs, em Três Barras, leitos rochosos com fósseis de mesossauro, vistos por pessoas da comunidade e identificados inicialmente por Carlos Eduardo Fiolek; a pesquisa é do Cenpaleo-UnC (Mafra). A matéria descreve os mesossauros em geral como répteis de 80 cm a 1 m, com membranas entre os dedos, que comiam pequenos crustáceos e viviam no 'Golfo Irati', há cerca de 280 milhões de anos — descrição do grupo, não medição deste material. O material seria preparado no Cenpaleo e parte dele cedida ao museu de Três Barras; a Prefeitura informou em 05/05/2022 que 20 peças transferidas do CENPALEO estavam expostas. As reportagens não citam formação, espécie, número de espécimes nem datação; a atribuição à Fm. Irati é a da literatura geral para mesossaurídeos da Bacia do Paraná (Elias 2020 registra também paleoniscídeos da Fm. Irati em Três Barras). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
           <t>https://www.nsctotal.com.br/noticias/seca-leva-a-descoberta-de-fosseis-de-280-milhoes-de-anos-em-tres-barras-no-norte-de-sc
+https://www.tresbarras.sc.gov.br/cultura/fosseis-de-mesossauro-ja-estao-em-exposicao-no-museu-de-tres-barras/
 https://www.diariodoplanalto.com.br/seca-do-rio-negro-revela-f%C3%B3ssil-de-animal-pr%C3%A9-hist%C3%B3rico-em-tr%C3%AAs-barras-1.2089668
 https://revistaplaneta.com.br/seca-em-santa-catarina-expoe-fosseis-de-mais-de-280-milhoes-de-anos
 https://repositorio.ufsc.br/bitstream/handle/123456789/225085/TCC.pdf?sequence=1&amp;isAllowed=y</t>
@@ -10106,7 +10110,7 @@
       </c>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>[referência sem formato bibliográfico, transcrita do descritor: Identificação inicial por C.E. Fiolek (Museu do Contestado); estudo por equipe do CENPALEO/UnC (L.C. Weinschütz, E. Wilner, J.H.Z. Ricetti), divulgado em 2020; Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: NSC Total (18/05/2020), reportagem «Seca leva à descoberta de fósseis de 280 milhões de anos em Três Barras, no Norte de SC», que atribui a identificação inicial a C.E. Fiolek (coordenador do museu de Três Barras) e a pesquisa ao CENPALEO/UnC] | [Citação de mídia, sem publicação científica primária identificada: Prefeitura de Três Barras (05/05/2022), notícia «Fósseis de mesossauro já estão em exposição no Museu de Três Barras»] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N109" s="6" t="n">
@@ -16143,7 +16147,7 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>Karl, H.-V., Gröning, E. &amp; Brauckmann, C. (2007) — "The Mesosauria in the collections of Göttingen and Clausthal: implications for a modified classification", Clausthaler Geowissenschaften 6:63–78; Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC</t>
+          <t>Karl, H.-V., Gröning, E. &amp; Brauckmann, C. (2007) — "The Mesosauria in the collections of Göttingen and Clausthal: implications for a modified classification", Clausthaler Geowissenschaften 6:63–78; Elias, R.L. (2020) — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
@@ -16169,7 +16173,7 @@
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>KARL, H.-V.; GRÖNING, E.; BRAUCKMANN, C. 2007. The Mesosauria in the collections of Göttingen and Clausthal: implications for a modified classification. Clausthaler Geowissenschaften, 6, 63–78. | [referência sem formato bibliográfico, transcrita do descritor: Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC]</t>
+          <t>KARL, H.-V.; GRÖNING, E.; BRAUCKMANN, C. 2007. The Mesosauria in the collections of Göttingen and Clausthal: implications for a modified classification. Clausthaler Geowissenschaften, 6, 63–78. | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N178" s="4" t="n">
@@ -16201,7 +16205,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>Fm. Irati / Grupo Passa Dois</t>
+          <t>Fm. Irati? (inferida do grupo; não informada na fonte)</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
@@ -16226,12 +16230,12 @@
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>Exposto em museu do município de Taió, SC</t>
+          <t>Museu Paleo-Arqueológico e Histórico Prefeito Bertoldo Jacobsen, Taió, SC (exposição, segundo a Prefeitura de Taió, 2017)</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>Prefeitura de Taió (2017), divulgação; Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC</t>
+          <t>Citação de mídia — Prefeitura de Taió (28/04/2017), notícia «Museu Paleo-Arqueológico e Histórico Prefeito Bertoldo Jacobsen abre Exposição de fóssil de Mesossauro em Taió», conforme citada por Elias (2020); Elias, R.L. (2020) — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr">
@@ -16246,17 +16250,18 @@
       </c>
       <c r="K179" s="7" t="inlineStr">
         <is>
-          <t>Exemplar encontrado em Ribeirão das Pedras e hoje exposto ao público em museu de Taió. Conhecido apenas por divulgação da prefeitura, compilada pela UFSC. RESSALVA: coordenada do município; sem tombo nem descrição. Segundo a compilação de vertebrados fósseis de SC da UFSC, não há trabalho de descrição do material de mesossauros do estado. TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
+          <t>CITAÇÃO DE MÍDIA — o exemplar é conhecido apenas por divulgação municipal. Segundo Elias (2020), que cita a notícia da Prefeitura de Taió (28/04/2017) e atribui o achado à diretora do museu, um exemplar de mesossauro encontrado em Ribeirão das Pedras (Taió) está exposto no museu local. Sem número de tombo e sem descrição científica; coordenada do município. Elias (2020) registra que nenhum dos achados de mesossauro de SC foi descrito em periódico científico. A fonte não informa a formação: a atribuição à Fm. Irati é inferida do grupo (mesossaurídeos da Bacia do Paraná). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
         </is>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>https://repositorio.ufsc.br/bitstream/handle/123456789/225085/TCC.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://www.taio.sc.gov.br/noticias/index/ver/codMapaItem/20161/codNoticia/419871 (notícia da Prefeitura de Taió, 28/04/2017, conforme citada por Elias 2020)
+https://repositorio.ufsc.br/bitstream/handle/123456789/225085/TCC.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="M179" s="7" t="inlineStr">
         <is>
-          <t>PREFEITURA DE TAIÓ 2017. divulgação. | [referência sem formato bibliográfico, transcrita do descritor: Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Prefeitura de Taió (28/04/2017), notícia «Museu Paleo-Arqueológico e Histórico Prefeito Bertoldo Jacobsen abre Exposição de fóssil de Mesossauro em Taió», conforme citada por Elias (2020)] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N179" s="6" t="n">
@@ -16318,7 +16323,7 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>Nizer &amp; Weinschütz (2015) — Paleontologia em Destaque 68:140 [título e autoria completa não localizados nesta revisão]; Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC</t>
+          <t>Nizer &amp; Weinschütz (2015) — Paleontologia em Destaque 68:140 [título e autoria completa não localizados nesta revisão]; Elias, R.L. (2020) — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
@@ -16343,7 +16348,7 @@
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>[referência sem formato bibliográfico, transcrita do descritor: Nizer &amp; Weinschütz (2015) — Paleontologia em Destaque 68:140 [título e autoria completa não localizados nesta revisão]] | [referência sem formato bibliográfico, transcrita do descritor: Luiz, E. R. — "Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense", Trabalho de Conclusão de Curso, UFSC]</t>
+          <t>[referência sem formato bibliográfico, transcrita do descritor: Nizer &amp; Weinschütz (2015) — Paleontologia em Destaque 68:140 [título e autoria completa não localizados nesta revisão]] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N180" s="4" t="n">
@@ -17782,7 +17787,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Fm. Teresina / Grupo Passa Dois</t>
+          <t>Não informada na reportagem (ocorrência-tipo do gênero: Fm. Teresina, Canoinhas — registro 159)</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
@@ -17812,7 +17817,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Identificação pelo CENPALEO/UnC (Mafra), divulgada em agosto de 2024</t>
+          <t>Citação de mídia — Notisul (22/08/2024), reportagem «Fóssil de 270 milhões de anos é encontrado em SC», que informa a identificação pelo Centro de Pesquisa Paleontológica da Universidade do Contestado (Mafra) a partir de fotos e vídeos</t>
         </is>
       </c>
       <c r="I197" s="6" t="inlineStr">
@@ -17822,12 +17827,12 @@
       </c>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>ca. 273–265 Ma (Guadalupiano)</t>
+          <t>ca. 270 Ma, segundo a reportagem (método de datação não informado)</t>
         </is>
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
-          <t>SEGUNDA localidade conhecida de Krauselcladus canoinhensis — gênero cuja ÚNICA ocorrência em toda a Bacia do Paraná é catarinense, descrito originalmente no Afloramento de Canoinhas (SIGEP 126). O espécime foi encontrado em 1º de maio de 2024 por participantes de uma caminhada religiosa e levado para análise. A nova localidade fica próxima a Canoinhas e amplia o entendimento da distribuição paleogeográfica da espécie. ATENÇÃO: a identificação foi feita pelo CENPALEO A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, e não a partir de exame direto do material; não foi localizada publicação científica formal sobre esta ocorrência, nem informação de tombamento ou depositário. A ocorrência do gênero em SC, contudo, é bem estabelecida na literatura (ver registro do Afloramento de Canoinhas).</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre esta ocorrência. Segundo o Notisul (22/08/2024), o fóssil foi descoberto em 1º de maio de 2024 por dois participantes de uma caminhada religiosa no interior de Major Vieira e identificado como Krauselcladus canoinhensis ('planta aparentada das atuais araucárias') pelo centro de pesquisa da Universidade do Contestado A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, sem exame direto do material documentado na reportagem; a idade de 270 milhões de anos é a da reportagem. A reportagem não informa localidade precisa, nome de quem identificou, tombo nem depositário. Se confirmada, seria uma segunda localidade do gênero, descrito no Afloramento de Canoinhas (SIGEP 126; registro 159).</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
@@ -17837,7 +17842,7 @@
       </c>
       <c r="M197" s="7" t="inlineStr">
         <is>
-          <t>[referência sem formato bibliográfico, transcrita do descritor: Identificação pelo CENPALEO/UnC (Mafra), divulgada em agosto de 2024]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Notisul (22/08/2024), reportagem «Fóssil de 270 milhões de anos é encontrado em SC», que informa a identificação pelo Centro de Pesquisa Paleontológica da Universidade do Contestado (Mafra) a partir de fotos e vídeos]</t>
         </is>
       </c>
       <c r="N197" s="6" t="n">
@@ -17850,7 +17855,7 @@
       </c>
       <c r="P197" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Teresina</t>
+          <t>Bacia do Paraná (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="Q197" s="6" t="n">
@@ -19344,17 +19349,17 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>Jurássico Superior (?) – Cretáceo Inferior (?)</t>
+          <t>Jurássico (segundo a reportagem)</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Fm. Botucatu (depósitos eólicos do paleodeserto)</t>
+          <t>Não informada na reportagem (que cita apenas 'Jurássico')</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>Theropoda indet. (afim. Carnosauria) — pista bípede</t>
+          <t>Theropoda indet. (afim. Carnosauria) — pegadas bípedes</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
@@ -19369,32 +19374,32 @@
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>Litoral sul de Santa Catarina, SC (localidade não especificada na fonte)</t>
+          <t>Litoral sul de SC (segundo a reportagem; município e localidade não informados — coordenada aproximada da região)</t>
         </is>
       </c>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>Não informado na reportagem</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>Weinschütz, L.C. (CENPALEO/UnC), citado em reportagem ND Mais (2023)</t>
+          <t>Citação de mídia — ND Mais (2023), reportagem «Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC», que tem como fonte o paleontólogo L.C. Weinschütz (CENPALEO/UnC)</t>
         </is>
       </c>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t>CENPALEO/UnC</t>
+          <t>Não informada (a reportagem cita L.C. Weinschütz, CENPALEO/UnC, como fonte, sem dizer que ele estudou estas pegadas)</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>ca. 150–145 Ma (Jurássico Superior, estimativa indicativa)</t>
+          <t>Jurássico (a reportagem não indica idade numérica)</t>
         </is>
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
-          <t>Único registro de dinossauro (icnofóssil) atualmente conhecido para SC; trata-se de pista de animal bípede de porte médio (cerca de 1,7 m), atribuída a terópode do grupo Carnosauria; nenhum osso corporal de dinossauro foi descrito para o Estado até o momento; localidade precisa não divulgada na fonte consultada</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica que descreva estas pegadas. A reportagem (ND Mais, 2023), com o paleontólogo L.C. Weinschütz (coordenador do CENPALEO/UnC) como fonte, diz que em Santa Catarina 'ainda não encontramos ossos fossilizados de dinossauros, mas já encontramos algumas pegadas', de terópodes bípedes 'não muito grande (+/-1,7m)' e 'provavelmente do grupo Carnosauria', 'principalmente no litoral sul do estado', e situa as ocorrências do Estado no Jurássico. Não informa formação, município, depósito, número de tombo nem datação, e não diz explicitamente que Weinschütz tenha estudado essas pegadas. Os campos de formação e bacia NÃO constam na reportagem. HISTÓRICO DE CORREÇÃO: versões anteriores deste banco atribuíam o registro à Fm. Botucatu, a 'ca. 150–145 Ma' e ao CENPALEO como depositário — informações que a fonte não traz e foram retiradas. Para pegadas de tetrápodes na Fm. Botucatu em SC com respaldo científico, ver o registro 96 (mamaliaformes, Turvo).</t>
         </is>
       </c>
       <c r="L215" s="7" t="inlineStr">
@@ -19404,7 +19409,7 @@
       </c>
       <c r="M215" s="7" t="inlineStr">
         <is>
-          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação jornalística: NDMAIS. 2023. Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC. Disponível em: https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ [Fonte secundária — sem publicação científica primária identificada no levantamento desta base]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (2023), reportagem «Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC», que tem como fonte o paleontólogo L.C. Weinschütz (CENPALEO/UnC)]</t>
         </is>
       </c>
       <c r="N215" s="6" t="n">
@@ -19417,7 +19422,7 @@
       </c>
       <c r="P215" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná — Fm. Botucatu</t>
+          <t>Bacia do Paraná (inferência do compilador; a reportagem não cita bacia)</t>
         </is>
       </c>
       <c r="Q215" s="6" t="n">
@@ -19466,7 +19471,7 @@
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>Buck, P.V. et al. (2022b) — "As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estado de Santa Catarina, Brasil", Paleontologia em Destaque</t>
+          <t>Buck, P.V. et al. (2022b) — "As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estado de Santa Catarina, Brasil", Paleontologia em Destaque; Buck, P.V., Ghilardi, A.M., Aureliano, T., Ade, M.V.B., Dino, R., Antonioli, L., Geremias, M.L., Fernandes, M.A. &amp; Araújo-Júnior, H.I. (2026) — "Remarkably large mammal-like tracks from the Botucatu Formation (Lower Cretaceous), Paraná Basin, Brazil: implications for the evolution of large size in Mammaliaformes", Journal of South American Earth Sciences (artigo 106223), DOI 10.1016/j.jsames.2026.106223</t>
         </is>
       </c>
       <c r="I216" s="4" t="inlineStr">
@@ -19481,18 +19486,20 @@
       </c>
       <c r="K216" s="5" t="inlineStr">
         <is>
-          <t>Laje de arenito com pista de quatro pegadas em epirrelevo côncavo, atribuídas aos pés de um produtor quadrúpede. São as maiores pegadas atribuídas a Mammaliaformes da Fm. Botucatu e possivelmente do Mesozoico — MAIORES que as de Aracoaraichnium, razão pela qual o espécime é atribuído apenas tentativamente ao mesmo morfotipo, e não à icnoespécie A. leonardii (cujo material-tipo provém de Araraquara, SP). Primeiro registro de pegadas de tetrápode descrito para a Fm. Botucatu em Santa Catarina.</t>
+          <t>Laje de arenito com pista de quatro pegadas em epirrelevo côncavo, atribuídas aos pés de um produtor quadrúpede. São as maiores pegadas atribuídas a Mammaliaformes da Fm. Botucatu e possivelmente do Mesozoico — MAIORES que as de Aracoaraichnium, razão pela qual o espécime é atribuído apenas tentativamente ao mesmo morfotipo, e não à icnoespécie A. leonardii (cujo material-tipo provém de Araraquara, SP). Primeiro registro de pegadas de tetrápode descrito para a Fm. Botucatu em Santa Catarina. HISTÓRICO TAXONÔMICO: o resumo de 2022 atribui o material, com ressalva, ao morfotipo de Aracoaraichnium. A versão completa parece ter sido publicada em Buck et al. (2026, J. South Am. Earth Sci.): segundo a cobertura jornalística do artigo (Diário de Pernambuco; IFLScience; Daily Galaxy), as maiores pegadas medem 11,4 cm de comprimento por 13,4 cm de largura, com passada de ~40 cm, e são atribuídas à família Chelichnopodidae, sem designação de icnoespécie — ou seja, a atribuição provisória a Aracoaraichnium não é mantida em nível de icnogênero nessa cobertura. A correspondência entre o espécime UERJ-IC-170 e o artigo de 2026 é inferida (mesmo grupo de autores, pedreira de Turvo e tema); o texto integral do artigo não foi aberto — conferir antes de citar.</t>
         </is>
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/367511513_AS_MAIORES_PEGADAS_ATRIBUIDAS_A_MAMMALIAFORMES_DA_FORMACAO_BOTUCATU_CRETACEO_INFERIOR_ESTADO_DE_SANTA_CATARINA_BRASIL
-https://www.researchgate.net/publication/317731251_A_new_ichnotaxon_classification_of_large_mammaliform_trackways_from_the_Lower_Cretaceous_Botucatu_Formation_Parana_Basin_Brazil</t>
+https://www.researchgate.net/publication/317731251_A_new_ichnotaxon_classification_of_large_mammaliform_trackways_from_the_Lower_Cretaceous_Botucatu_Formation_Parana_Basin_Brazil
+https://doi.org/10.1016/j.jsames.2026.106223
+https://www.diariodepernambuco.com.br/dptrends/pegadas-encontradas-em-santa-catarina-indicam-que-um-mamifero-do-tamanho-de-um-puma-viveu-entre-os-dinossauros/</t>
         </is>
       </c>
       <c r="M216" s="5" t="inlineStr">
         <is>
-          <t>BUCK, P.V. et al. 2022b. As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estado de Santa Catarina, Brasil. Paleontologia em Destaque.</t>
+          <t>BUCK, P.V. et al. 2022b. As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estado de Santa Catarina, Brasil. Paleontologia em Destaque. | BUCK, P.V.; GHILARDI, A.M.; AURELIANO, T. et al. 2026. Remarkably large mammal-like tracks from the Botucatu Formation (Lower Cretaceous), Paraná Basin, Brazil: implications for the evolution of large size in Mammaliaformes. Journal of South American Earth Sciences (artigo 106223). DOI: 10.1016/j.jsames.2026.106223</t>
         </is>
       </c>
       <c r="N216" s="4" t="n">
@@ -19514,7 +19521,11 @@
       <c r="R216" s="4" t="n">
         <v>-49.6831</v>
       </c>
-      <c r="S216" s="4" t="inlineStr"/>
+      <c r="S216" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jsames.2026.106223</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -19524,7 +19535,7 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>Depósitos superficiais / aluvionares</t>
+          <t>Não informada nas reportagens (ver observações)</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -19554,7 +19565,7 @@
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Frank et al. (vários); Simão, G. (geólogo Geoparque, 2025)</t>
+          <t>Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão; Citação de mídia — Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann</t>
         </is>
       </c>
       <c r="I217" s="6" t="inlineStr">
@@ -19569,21 +19580,20 @@
       </c>
       <c r="K217" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Mais de 40 estruturas identificadas; algumas interconectadas atingem até 340 m; escavadas por preguiças e tatus-gigantes extintos</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: a ocorrência e os números deste registro (paleotocas no Geoparque Caminhos dos Cânions do Sul, Praia Grande, Timbé do Sul e municípios vizinhos) vêm de reportagens. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. Litologia não informada nas reportagens. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. </t>
         </is>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Proposta de classificação das paleotocas)
-https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+          <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/
+https://doi.org/10.4072/rbp.2009.3.07
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Valdati et al. 2024, contexto do Geoparque)</t>
         </is>
       </c>
       <c r="M217" s="7" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Frank et al. (vários). | SIMÃO, G. geólogo Geoparque, 2025.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão] | [Citação de mídia, sem publicação científica primária identificada: Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann]</t>
         </is>
       </c>
       <c r="N217" s="6" t="n">
@@ -19605,11 +19615,7 @@
       <c r="R217" s="6" t="n">
         <v>-49.94</v>
       </c>
-      <c r="S217" s="6" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -19619,12 +19625,12 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Fm. Botucatu (arenito eólico) — geossítio do Geoparque</t>
+          <t>Fm. Botucatu? (não informada para esta cavidade; ver observações)</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Paleotoca Furnas Xocleng (icnofóssil de escavação — Xenarthra)</t>
+          <t>Paleotoca Xocleng (icnofóssil de escavação — Xenarthra)</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -19649,7 +19655,7 @@
       </c>
       <c r="H218" s="5" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional); Bechtel, A.F. (doutorando em geografia, citado em reportagens, 2025/2026)</t>
+          <t>Citação de mídia — Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande); Citação de mídia — Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande)</t>
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr">
@@ -19664,20 +19670,19 @@
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Três cavidades subterrâneas somando mais de 100 m de extensão; marcas de garras nas paredes; atribuída a tatus-gigantes (Glyptodon/Pampatherium) e/ou preguiças-gigantes CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande.</t>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: a existência e a descrição desta paleotoca são conhecidas por divulgação institucional e turística. A página do Geoparque descreve o geossítio como 'um conjunto de 3 estruturas subterrâneas', com acesso a cerca de 18 km do centro de Morro Grande; o guia turístico registra marcas de garras nas paredes e extensão somada superior a 100 m, e cita preguiças-gigantes e tatus como possíveis escavadores. Nenhuma das duas páginas informa a unidade geológica desta cavidade, idade ou estudo científico específico. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. HISTÓRICO DE NOME: este banco chamava o registro de 'Furnas Xocleng'; esse nome não consta nas fontes consultadas, que usam 'Xocleng' (Geoparque) e 'Paleotoca Xocleng' (guia). CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande.</t>
         </is>
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+          <t>https://canionsdosul.org/geossitios/?lang=en-us
 https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+https://doi.org/10.4072/rbp.2009.3.07</t>
         </is>
       </c>
       <c r="M218" s="5" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional). | BECHTEL, A.F. doutorando em geografia, citado em reportagens, 2025/2026.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande)] | [Citação de mídia, sem publicação científica primária identificada: Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande)]</t>
         </is>
       </c>
       <c r="N218" s="4" t="n">
@@ -19699,11 +19704,7 @@
       <c r="R218" s="4" t="n">
         <v>-49.7208</v>
       </c>
-      <c r="S218" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -19743,7 +19744,7 @@
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101; Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.)</t>
+          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101</t>
         </is>
       </c>
       <c r="I219" s="6" t="inlineStr">
@@ -19758,21 +19759,20 @@
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos) CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna.</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos) CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
           <t>https://www.semanticscholar.org/paper/THE-COMPLEX-HISTORY-OF-A-SANDSTONE-HOSTED-CAVE-IN-,-Frank-Oliveira/352ac79d172767f56f9a572deea5da8581b08db2
 https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
 https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+https://canionsdosul.org/geossitios/?lang=en-us</t>
         </is>
       </c>
       <c r="M219" s="7" t="inlineStr">
         <is>
-          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101. | BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.).</t>
+          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101.</t>
         </is>
       </c>
       <c r="N219" s="6" t="n">
@@ -19794,11 +19794,7 @@
       <c r="R219" s="6" t="n">
         <v>-49.8961</v>
       </c>
-      <c r="S219" s="6" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -19808,7 +19804,7 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Depósitos superficiais / arenitos diversos — geossítios do Geoparque</t>
+          <t>Não informada nas reportagens (ver observações)</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -19828,7 +19824,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Jacinto Machado, SC (Paleotoca do Engenho Velho); Praia Grande, SC</t>
+          <t>Jacinto Machado e Praia Grande, SC (cavidades não individualizadas nas reportagens; coordenada de Jacinto Machado)</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19838,7 +19834,7 @@
       </c>
       <c r="H220" s="5" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: ND Mais (2025); CircuitoMT (2025), citando especialistas do Geoparque</t>
+          <t>Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»; Citação de mídia — CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»</t>
         </is>
       </c>
       <c r="I220" s="4" t="inlineStr">
@@ -19853,21 +19849,19 @@
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Registros de paleotocas adicionais em cinco municípios do Geoparque (quatro em SC: Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande); mais de 40 estruturas catalogadas no total, algumas interconectadas atingindo até 340 m de extensão</t>
+          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: as duas reportagens (ND Mais, 10/08/2025; CircuitoMT, 11/08/2025), que têm o geólogo do Geoparque G. Simão como único especialista citado, listam paleotocas em cinco municípios do território do Geoparque — Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande (SC) e Cambará do Sul (RS) —, mais de 40 estruturas no total, algumas com até 340 m, e três abertas à visitação. Não informam quantas há em cada município nem nomeiam as de Jacinto Machado e Praia Grande. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. HISTÓRICO DE NOME: o sítio deste registro constava como 'Paleotoca do Engenho Velho'; esse nome não foi encontrado em nenhuma fonte consultada (nem na página de geossítios do Geoparque) e foi substituído por uma descrição genérica.</t>
         </is>
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
+          <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
 https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+https://doi.org/10.4072/rbp.2009.3.07</t>
         </is>
       </c>
       <c r="M220" s="5" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: ND Mais (2025). | CIRCUITOMT 2025. citando especialistas do Geoparque.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»] | [Citação de mídia, sem publicação científica primária identificada: CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»]</t>
         </is>
       </c>
       <c r="N220" s="4" t="n">
@@ -19875,7 +19869,7 @@
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>Paleotoca do Engenho Velho</t>
+          <t>Jacinto Machado e Praia Grande (paleotocas do Geoparque)</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
@@ -19889,11 +19883,7 @@
       <c r="R220" s="4" t="n">
         <v>-49.8167</v>
       </c>
-      <c r="S220" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -19903,7 +19893,7 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>Depósitos cenozóicos / rochas do Planalto Serrano</t>
+          <t>Não informada no artigo (Munhoz et al. 2024)</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
@@ -19933,12 +19923,12 @@
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.)</t>
+          <t>Munhoz, M.S., Audi, C. &amp; Buchmann, F.S.C. (2024) — "Propagação sonora em Megaichnus major (paleotocas) como evidência de comunicação acústica de Mylodontoidea fossoriais", Revista Brasileira de Paleontologia 27(4):e20240428, DOI 10.4072/rbp.2024.4.0428</t>
         </is>
       </c>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+          <t>UNESP — Campus do Litoral Paulista (afiliação de F.S.C. Buchmann; demais afiliações a conferir no artigo)</t>
         </is>
       </c>
       <c r="J221" s="6" t="inlineStr">
@@ -19948,19 +19938,18 @@
       </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016).</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016). O artigo analisa apenas o túnel URU-01-P2 (15 m, sem ramificações) da 'paleotoca Caverna do Rio dos Bugres, URU-01', e informa que a identidade do escavador é incerta (não há fósseis associados); formação e rocha NÃO são informadas. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+          <t>https://doi.org/10.4072/rbp.2024.4.0428
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081</t>
         </is>
       </c>
       <c r="M221" s="7" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.).</t>
+          <t>MUNHOZ, M.S.; AUDI, C.; BUCHMANN, F.S.C. 2024. Propagação sonora em Megaichnus major (paleotocas) como evidência de comunicação acústica de Mylodontoidea fossoriais. Revista Brasileira de Paleontologia, 27(4), e20240428. DOI: 10.4072/rbp.2024.4.0428</t>
         </is>
       </c>
       <c r="N221" s="6" t="n">
@@ -19973,7 +19962,7 @@
       </c>
       <c r="P221" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+          <t>Bacia do Paraná (inferência do compilador; o artigo não cita bacia nem formação)</t>
         </is>
       </c>
       <c r="Q221" s="6" t="n">
@@ -19984,7 +19973,7 @@
       </c>
       <c r="S221" s="6" t="inlineStr">
         <is>
-          <t>10.4072/rbp.2009.3.07</t>
+          <t>10.4072/rbp.2024.4.0428</t>
         </is>
       </c>
     </row>
@@ -20026,12 +20015,12 @@
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.)</t>
+          <t>Audi, C. (2022) — "Fotogrametria de uma paleotoca escavada por preguiças-gigantes (Megaichnus major)", Dissertação de Mestrado, Universidade Estadual Paulista (Unesp), Programa de Pós-graduação em Biodiversidade de Ambientes Costeiros, campus do Litoral Paulista (orientador: F.S.C. Buchmann)</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+          <t>Unesp — Campus do Litoral Paulista (Pós-graduação em Biodiversidade de Ambientes Costeiros)</t>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
@@ -20041,20 +20030,18 @@
       </c>
       <c r="K222" s="5" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Paleotoca escavada no ARENITO DA FORMAÇÃO TACIBA (Permiano) — caso que ilustra bem a natureza destes icnofósseis: a estrutura é do Plioceno–Pleistoceno, mas a rocha escavada é ~270 milhões de anos mais antiga. Documentada por fotogrametria, com geração de modelo tridimensional.</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca escavada no ARENITO DA FORMAÇÃO TACIBA (Permiano) — caso que ilustra bem a natureza destes icnofósseis: a estrutura é do Plioceno–Pleistoceno, mas a rocha escavada é ~270 milhões de anos mais antiga. Documentada por fotogrametria, com geração de modelo tridimensional. O resumo da dissertação localiza a paleotoca em Doutor Pedrinho (SC) e informa que a estrutura foi escavada no arenito da Fm. Taciba; não informa dimensões. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://www.researchgate.net/publication/365772145_Fotogrametria_de_um_icnofossil_escavado_por_preguicas-gigantes_Megaichnus_major
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+          <t>https://repositorio.unesp.br/items/a7a21c5b-d669-4f0c-b86a-cf6d4ced7815
+https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/ (notícia sobre a paleotoca digitalizada de Doutor Pedrinho)</t>
         </is>
       </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.).</t>
+          <t>AUDI, C. 2022. Fotogrametria de uma paleotoca escavada por preguiças-gigantes (Megaichnus major). Dissertação de Mestrado, Universidade Estadual Paulista (Unesp), Programa de Pós-graduação em Biodiversidade de Ambientes Costeiros, campus do Litoral Paulista (orientador: F.S.C. Buchmann).</t>
         </is>
       </c>
       <c r="N222" s="4" t="n">
@@ -20076,11 +20063,7 @@
       <c r="R222" s="4" t="n">
         <v>-49.4794</v>
       </c>
-      <c r="S222" s="4" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -20090,7 +20073,7 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Depósitos cenozóicos / rochas sedimentares do Planalto Norte</t>
+          <t>Fm. Botucatu (arenitos), segundo Santos et al. (2021)</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -20120,12 +20103,12 @@
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.)</t>
+          <t>Santos, R.F., Schipanski, H.J., Martello, A.R. &amp; Vogel, H.F. (2021) — "Preliminary analysis of paleoburrows in Porto União-SC and União da Vitória-PR, Brazil", Research, Society and Development 10(11):e330101119176, DOI 10.33448/rsd-v10i11.19176</t>
         </is>
       </c>
       <c r="I223" s="6" t="inlineStr">
         <is>
-          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+          <t>Não informada no resumo consultado</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
@@ -20135,20 +20118,18 @@
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. Conjunto de paleotocas do Planalto Norte catarinense, analisadas em conjunto com as de União da Vitória (PR), do outro lado do rio Iguaçu. Levantadas pelo método de amostragem em bola de neve (snowball sampling), com medição de altura e largura dos túneis.</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Conjunto de paleotocas do Planalto Norte catarinense, analisadas em conjunto com as de União da Vitória (PR), do outro lado do rio Iguaçu. Levantadas pelo método de amostragem em bola de neve (snowball sampling), com medição de altura e largura dos túneis. Segundo o resumo, foram achadas 13 paleotocas livres ou parcialmente obstruídas e 6 crotovinas, todas em arenitos, somando União da Vitória (PR) e Porto União (SC) — o resumo não separa as contagens por município —, com quatro morfologias de túnel e cinco tipos de icnofósseis, alguns atribuídos a Mylodontidae; não nomeia localidades dentro de Porto União. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://rsdjournal.org/rsd/article/view/19176
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+          <t>https://doi.org/10.33448/rsd-v10i11.19176
+https://rsdjournal.org/rsd/article/view/19176</t>
         </is>
       </c>
       <c r="M223" s="7" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.).</t>
+          <t>SANTOS, R.F.; SCHIPANSKI, H.J.; MARTELLO, A.R. et al. 2021. Preliminary analysis of paleoburrows in Porto União-SC and União da Vitória-PR, Brazil. Research, Society and Development, 10(11), e330101119176. DOI: 10.33448/rsd-v10i11.19176</t>
         </is>
       </c>
       <c r="N223" s="6" t="n">
@@ -20161,7 +20142,7 @@
       </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+          <t>Bacia do Paraná — Fm. Botucatu</t>
         </is>
       </c>
       <c r="Q223" s="6" t="n">
@@ -20172,7 +20153,7 @@
       </c>
       <c r="S223" s="6" t="inlineStr">
         <is>
-          <t>10.4072/rbp.2009.3.07</t>
+          <t>10.33448/rsd-v10i11.19176</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20190,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Não informado na fonte consultada</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -20361,7 +20342,7 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
+          <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
@@ -20381,17 +20362,17 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Costa de Sombrio, SC (encontrado a ~23 m de profundidade, rede de arrasto)</t>
+          <t>Costa de Sombrio, SC (a ~23 m de profundidade, em pesca de arrasto, no fim de março de 2018 — coordenada aproximada)</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
+          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
         <is>
-          <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024); nome atualizado segundo Mothé, D., Avilla, L.S., Cozzuol, M. &amp; Winck, G.R. (2012) — "Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands", Quaternary International 276–277:2–7</t>
+          <t>Citação de mídia — Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade); Mothé, D., Avilla, L.S., Cozzuol, M. &amp; Winck, G.R. (2012) — "Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands", Quaternary International 276–277:2–7</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
@@ -20401,24 +20382,25 @@
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>ca. 30.000 anos (Pleistoceno Superior)</t>
+          <t>ca. 30.000 anos, segundo a reportagem (método de datação não informado)</t>
         </is>
       </c>
       <c r="K226" s="5" t="inlineStr">
         <is>
-          <t>Classificação: mastodonte (Proboscidea, Gomphotheriidae). ATUALIZAÇÃO TAXONÔMICA: registro publicado originalmente como Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a nova combinação Notiomastodon platensis. Parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. Metade esquerda de mandíbula de macho adulto, achada por pescadores; espécie rara em SC, mais comum no RS; estimativa de ~5 m de comprimento e ~3,5 t</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este espécime. Segundo as reportagens, pescadores recolheram no fim de março de 2018 a metade esquerda da mandíbula de um macho adulto, a cerca de 23 m de profundidade, em pesca de arrasto na costa de Sombrio; pesquisadores da Univali a identificaram como Stegomastodon waringi, de cerca de 30 mil anos, com estimativa de ~5 m de comprimento, ~2,5 m de altura e ~3,5 t; fósseis dessa espécie seriam raros em SC e mais comuns no RS. Local de guarda, número de tombo e formação NÃO são informados. HISTÓRICO TAXONÔMICO: a reportagem usa Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a combinação Notiomastodon platensis; parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. O nome do registro segue essa revisão; a reportagem não o usa. CONTEXTO CIENTÍFICO (não trata deste espécime): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27, DOI 10.1016/j.jsames.2010.11.003) relatam, para a plataforma continental do sul do Brasil (o resumo fala em 'porção mais meridional da costa', com palavra-chave Rio Grande do Sul), restos de Toxodon sp. e um molar de Stegomastodon waringi recolhidos por pescadores a cerca de 20 m de profundidade.</t>
         </is>
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
-https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio
-https://www.sciencedirect.com/science/article/abs/pii/S1040618211002916</t>
+https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/
+https://www.sciencedirect.com/science/article/abs/pii/S1040618211002916
+https://doi.org/10.1016/j.jsames.2010.11.003</t>
         </is>
       </c>
       <c r="M226" s="5" t="inlineStr">
         <is>
-          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)] | MOTHÉ, D.; AVILLA, L.S.; COZZUOL, M. et al. 2012. Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands. Quaternary International 276–277:2–7.</t>
         </is>
       </c>
       <c r="N226" s="4" t="n">
@@ -20431,7 +20413,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>Plataforma Continental — Fm. Laguna-Barreira</t>
+          <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n">
@@ -20470,7 +20452,7 @@
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
-          <t>Plataforma continental entre Passo de Torres e Araranguá, SC (rede de arrasto de camarão)</t>
+          <t>Plataforma continental entre Passo de Torres e Araranguá, SC (redes de arrasto de camarão — coordenada aproximada)</t>
         </is>
       </c>
       <c r="G227" s="6" t="inlineStr">
@@ -20480,7 +20462,7 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>Divulgação Museu Oceanográfico Univali (2022)</t>
+          <t>Citação de mídia — Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)</t>
         </is>
       </c>
       <c r="I227" s="6" t="inlineStr">
@@ -20490,22 +20472,23 @@
       </c>
       <c r="J227" s="6" t="inlineStr">
         <is>
-          <t>ca. 30.000 anos (Pleistoceno Superior)</t>
+          <t>ca. 30.000 anos antes do presente, segundo a divulgação (método não informado)</t>
         </is>
       </c>
       <c r="K227" s="7" t="inlineStr">
         <is>
-          <t>Classificação: preguiça-gigante (Xenarthra, Mylodontidae). Pelo menos dois espécimes; primeiro registro da espécie em Santa Catarina; esqueleto montado é atração do Museu Oceanográfico Univali; estimativa de ~4,5 m de altura e ~3 t</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica. Segundo a divulgação, fósseis de lestodonte (Lestodon armatus) saíram de redes de arrasto de camarão na plataforma continental entre Passo de Torres e Araranguá, pertencem à 'formação Laguna-Barreira' e são 'datados de cerca de 30 mil anos antes do presente'; a equipe do museu encontrou 'ao menos dois' lestodontes, 'tratando-se do primeiro registro desta espécie no Estado'. A altura (~4,5 m) e o peso (~3 t) citados descrevem a espécie em geral, não o exemplar. O esqueleto montado está exposto no Museu Oceanográfico Univali (Balneário Piçarras). Não são informados identificador, tombo, data da coleta nem método de datação.</t>
         </is>
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx</t>
+          <t>https://novomomento.com.br/preguica-gigante-museu-oceanografico/
+https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx (página original; indisponível em 08/10/2026)</t>
         </is>
       </c>
       <c r="M227" s="7" t="inlineStr">
         <is>
-          <t>DIVULGAÇÃO MUSEU OCEANOGRÁFICO UNIVALI 2022.</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)]</t>
         </is>
       </c>
       <c r="N227" s="6" t="n">
@@ -20537,12 +20520,12 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
+          <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>Toxodon sp.</t>
+          <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -20557,17 +20540,17 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Costa de Sombrio, SC (vértebra torácica, rede de arrasto)</t>
+          <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
+          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
         <is>
-          <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024)</t>
+          <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
         </is>
       </c>
       <c r="I228" s="4" t="inlineStr">
@@ -20577,23 +20560,23 @@
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>ca. 30.000 anos (Pleistoceno Superior)</t>
+          <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
         </is>
       </c>
       <c r="K228" s="5" t="inlineStr">
         <is>
-          <t>Classificação: toxodonte (Notoungulata, Toxodontidae). Vértebra torácica recuperada junto à mandíbula de Stegomastodon waringi; toxodontes são notoungulados de grande porte, descritos como morfologicamente convergentes com hipopótamos</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27, DOI 10.1016/j.jsames.2010.11.003) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
         </is>
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
-https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
+          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/
+https://doi.org/10.1016/j.jsames.2010.11.003</t>
         </is>
       </c>
       <c r="M228" s="5" t="inlineStr">
         <is>
-          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
         </is>
       </c>
       <c r="N228" s="4" t="n">
@@ -20606,7 +20589,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>Plataforma Continental — Fm. Laguna-Barreira</t>
+          <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n">
@@ -20625,12 +20608,12 @@
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>Depósitos superficiais sobre a Fm. Rio Bonito / Depressão da Zona Carbonífera Catarinense</t>
+          <t>Fm. Rio Bonito (segundo o comunicado da UDESC e a reportagem do ND Mais)</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>Paleotoca (icnofóssil de escavação — Xenarthra: tatus, preguiças, tamanduás)</t>
+          <t>Paleotoca Amaral de Baixo (icnofóssil de escavação — provável tatu extinto)</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
@@ -20645,46 +20628,43 @@
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>Lauro Müller, SC</t>
+          <t>Localidade Rio Amaral Gruta, Lauro Müller, SC (coordenada do município)</t>
         </is>
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>UDESC — Laboratório de Geografia/Geologia (FAED)</t>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
-          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — "Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil", Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07; Lopes, R.P., Frank, H.T., Buchmann, F.S.C. &amp; Caron, F. (2017) — "Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America", Ichnos 24(2):133–145 (erige Megaichnus igen. nov.)</t>
+          <t>Citação de mídia — UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF); Citação de mídia — ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)</t>
         </is>
       </c>
       <c r="I229" s="6" t="inlineStr">
         <is>
-          <t>UDESC</t>
+          <t>UDESC — Laboratório de Geografia Física (LGEF), grupo BioGeo, FAED (segundo o comunicado da UDESC); equipe técnica do Geoparque (segundo o ND Mais)</t>
         </is>
       </c>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>2,58 Ma – 11.700 a</t>
+          <t>Não datada; a reportagem fala em animais que viveram 'há cerca de 10 mil anos'</t>
         </is>
       </c>
       <c r="K229" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Segundo F. S. C. Buchmann, em entrevista ao Jornal da Unesp (2022), mais de duas mil paleotocas foram registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul. 1º registro documentado deste tipo de icnofóssil em rochas da Fm. Rio Bonito e na Depressão da Zona Carbonífera Catarinense; estrutura de habitação distinta das paleotocas já catalogadas no Geoparque Caminhos dos Cânions do Sul</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4072/rbp.2009.3.07
-https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
-https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
-https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/
-https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/</t>
+          <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
+https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
       <c r="M229" s="7" t="inlineStr">
         <is>
-          <t>BUCHMANN, F.S.C.; LOPES, R.P.; CARON, F. 2009. Icnofósseis (paleotocas e crotovinas) atribuídos a mamíferos extintos no sudeste e sul do Brasil. Revista Brasileira de Paleontologia, 12(3), 247–256. DOI: 10.4072/rbp.2009.3.07 | LOPES, R.P.; FRANK, H.T.; BUCHMANN, F.S.C. et al. 2017. Megaichnus igen. nov.: giant paleoburrows attributed to extinct Cenozoic mammals from South America. Ichnos, 24(2), 133–145 (erige Megaichnus igen. nov.).</t>
+          <t>[Citação de mídia, sem publicação científica primária identificada: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia, sem publicação científica primária identificada: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
         </is>
       </c>
       <c r="N229" s="6" t="n">
@@ -20706,11 +20686,7 @@
       <c r="R229" s="6" t="n">
         <v>-49.3811</v>
       </c>
-      <c r="S229" s="6" t="inlineStr">
-        <is>
-          <t>10.4072/rbp.2009.3.07</t>
-        </is>
-      </c>
+      <c r="S229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -20800,8 +20776,100 @@
       </c>
       <c r="S230" s="4" t="inlineStr"/>
     </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Depósitos turfosos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>Palinomorfos holocênicos (54 morfotipos: fungos, algas, briófitas, pteridófitas, pólen de gimnospermas e outros)</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>Duas seções com turfa na Planície Costeira sul-catarinense, nos municípios de Santa Rosa do Sul e São João do Sul, SC (nomes das turfeiras e coordenadas não informados no resumo consultado; ponto aproximado, entre os centros dos dois municípios)</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>Não informado no resumo consultado</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>Cancelli, R.R., Souza, P.A. &amp; Neves, P.C.P. (2012) — "Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil", Acta Botanica Brasilica 26(1):20–37, DOI 10.1590/S0102-33062012000100004</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>UFRGS (Porto Alegre) e Universidade Luterana do Brasil (Canoas) — afiliações dos autores</t>
+        </is>
+      </c>
+      <c r="J231" s="6" t="inlineStr">
+        <is>
+          <t>ca. 7.908 anos AP (base do testemunho de Santa Rosa do Sul) até o presente — 0,0079 Ma</t>
+        </is>
+      </c>
+      <c r="K231" s="7" t="inlineStr">
+        <is>
+          <t>Segundo o resumo, o estudo apresenta resultados palinológicos de duas seções com turfa na Planície Costeira sul-catarinense, em Santa Rosa do Sul e São João do Sul; uma amostra basal do testemunho de Santa Rosa do Sul foi datada em 7908 ± 33 anos AP (Holoceno Inferior; o título cita ± 30). Foram descritos e ilustrados 54 palinomorfos: 21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 pólens de gimnospermas e 7 outros (uma cápsula de briófita, 4 fragmentos de invertebrados e 2 palinoforaminíferos indeterminados). Nomes das turfeiras, coordenadas, espessura dos testemunhos e táxons individuais NÃO constam no resumo consultado (o texto integral não foi aberto); por isso o ponto no mapa é aproximado. REGISTRO NOVO (2026.09.14), com fonte própria; não deve ser confundido com o nº 040 (Lagoa do Sombrio), removido em 2026.09.13.</t>
+        </is>
+      </c>
+      <c r="L231" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1590/S0102-33062012000100004
+https://paperity.org/p/187352977/fungos-criptogamas-e-outros-palinomorfos-holocenicos-7908-30-anos-ap-atual-da-planicie</t>
+        </is>
+      </c>
+      <c r="M231" s="7" t="inlineStr">
+        <is>
+          <t>CANCELLI, R.R.; SOUZA, P.A.; NEVES, P.C.P. 2012. Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil. Acta Botanica Brasilica, 26(1), 20–37. DOI: 10.1590/S0102-33062012000100004</t>
+        </is>
+      </c>
+      <c r="N231" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="O231" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira sul-catarinense (turfeiras de Santa Rosa do Sul e São João do Sul)</t>
+        </is>
+      </c>
+      <c r="P231" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q231" s="6" t="n">
+        <v>-29.1613</v>
+      </c>
+      <c r="R231" s="6" t="n">
+        <v>-49.7767</v>
+      </c>
+      <c r="S231" s="6" t="inlineStr">
+        <is>
+          <t>10.1590/S0102-33062012000100004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:S230"/>
+  <autoFilter ref="A3:S231"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -20816,7 +20884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B656"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -27735,16 +27803,20 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="9" t="n"/>
+      <c r="B648" s="9" t="n"/>
+    </row>
     <row r="649">
-      <c r="A649" s="10" t="inlineStr">
+      <c r="A649" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B649" s="9" t="inlineStr"/>
+      <c r="B649" s="9" t="n"/>
     </row>
     <row r="650">
-      <c r="A650" s="11" t="inlineStr">
+      <c r="A650" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -27756,7 +27828,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="11" t="inlineStr">
+      <c r="A651" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -27768,7 +27840,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="11" t="inlineStr">
+      <c r="A652" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -27780,7 +27852,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="11" t="inlineStr">
+      <c r="A653" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -27792,7 +27864,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="11" t="inlineStr">
+      <c r="A654" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -27804,7 +27876,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="11" t="inlineStr">
+      <c r="A655" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -27816,12 +27888,968 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="11" t="inlineStr">
+      <c r="A656" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="9" t="n"/>
+      <c r="B657" s="9" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B658" s="9" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B659" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B660" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B661" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B662" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B663" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B664" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B665" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="9" t="n"/>
+      <c r="B666" s="9" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B667" s="9" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B668" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B669" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B670" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B671" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B672" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B673" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B674" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="9" t="n"/>
+      <c r="B675" s="9" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B676" s="9" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B677" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B678" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B679" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B680" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B681" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B682" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B683" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="9" t="n"/>
+      <c r="B684" s="9" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B685" s="9" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B686" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B687" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B688" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B689" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B690" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B691" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B692" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="n"/>
+      <c r="B693" s="9" t="n"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B694" s="9" t="n"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B695" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B696" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B697" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B698" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B699" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B700" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B701" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="9" t="n"/>
+      <c r="B702" s="9" t="n"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B703" s="9" t="n"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B704" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B705" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B706" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B707" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B708" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B709" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B710" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="n"/>
+      <c r="B711" s="9" t="n"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B712" s="9" t="n"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B713" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B714" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B715" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B716" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B717" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B718" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B719" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="9" t="n"/>
+      <c r="B720" s="9" t="n"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B721" s="9" t="n"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B722" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B723" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B724" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B725" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B726" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B727" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B728" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="9" t="n"/>
+      <c r="B729" s="9" t="n"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B730" s="9" t="n"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B731" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B732" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B733" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B734" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B735" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B736" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B737" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B739" s="9" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B740" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B741" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B742" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B743" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B744" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B745" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B746" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S262"/>
+  <dimension ref="A1:S266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>259 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>263 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Traço de pastagem, frequentemente ASSOCIADO a impressões de espículas de esponjas hexactinélidas — associação que liga diretamente a icnofauna à fauna corpórea da bacia. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os icnofósseis descritos anteriormente foram reavaliados — conferir o texto completo antes de citar esta ocorrência. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): as escavações horizontais descritas como Gordia por Netto &amp; Zucatti-da-Rosa (1997) foram atribuídas a Helminthoidichnites isp. por Zucatti-da-Rosa (2006). O registro nº 211 trata do mesmo tipo de traço sob o nome posterior; este registro preserva o nome da descrição original. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Traço de pastagem, frequentemente ASSOCIADO a impressões de espículas de esponjas hexactinélidas — associação que liga diretamente a icnofauna à fauna corpórea da bacia. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): as escavações horizontais descritas como Gordia por Netto &amp; Zucatti-da-Rosa (1997) foram atribuídas a Helminthoidichnites isp. por Zucatti-da-Rosa (2006). O registro nº 211 trata do mesmo tipo de traço sob o nome posterior; este registro preserva o nome da descrição original. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Escavação em U com spreiten, indicativa de substrato firme e de organismo suspensívoro. Também aparece associada às espículas de esponjas. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os icnofósseis descritos anteriormente foram reavaliados — conferir o texto completo antes de citar esta ocorrência. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): Netto &amp; Zucatti-da-Rosa (1997) registraram Diplocraterion (em suposta preservação de acamamento); Zucatti-da-Rosa (2006) redescreveu essas estruturas em haltere como impressões («morfotipo I»), sem o nome Diplocraterion. O nome da descrição original é mantido neste registro. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Escavação em U com spreiten, indicativa de substrato firme e de organismo suspensívoro. Também aparece associada às espículas de esponjas. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): Netto &amp; Zucatti-da-Rosa (1997) registraram Diplocraterion (em suposta preservação de acamamento); Zucatti-da-Rosa (2006) redescreveu essas estruturas em haltere como impressões («morfotipo I»), sem o nome Diplocraterion. O nome da descrição original é mantido neste registro. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Traço de locomoção e pastagem de organismo provavelmente vermiforme e epifaunal. Indica ambiente marinho relativamente profundo, de águas calmas e substrato lamoso. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os icnofósseis descritos anteriormente foram reavaliados — conferir o texto completo antes de citar esta ocorrência. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): o nome Helminthoidichnites isp. é de Zucatti-da-Rosa (2006); em Netto &amp; Zucatti-da-Rosa (1997) as mesmas escavações horizontais aparecem como Gordia (ver registro nº 209). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Traço de locomoção e pastagem de organismo provavelmente vermiforme e epifaunal. Indica ambiente marinho relativamente profundo, de águas calmas e substrato lamoso. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): o nome Helminthoidichnites isp. é de Zucatti-da-Rosa (2006); em Netto &amp; Zucatti-da-Rosa (1997) as mesmas escavações horizontais aparecem como Gordia (ver registro nº 209). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Registrado com interrogação pelos próprios autores: as estruturas admitem interpretação como o icnogênero Oldhamia ou como a esponja demospongia Choia. A ambiguidade é relevante — Oldhamia é icnofóssil-guia do Cambriano Inferior, e Choia é fóssil corpóreo, de modo que a leitura escolhida altera tanto a natureza do registro quanto sua implicação cronoestratigráfica. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os icnofósseis descritos anteriormente foram reavaliados — conferir o texto completo antes de citar esta ocorrência. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): Netto &amp; Zucatti-da-Rosa (1997) registraram ?Oldhamia; Zucatti-da-Rosa (2006) reinterpretou as estruturas radiais como Choia?. Netto (2012) observa que sulcos de pastagem podem imitar o nicho dos produtores de Oldhamia e que Oldhamia não foi registrada em rochas ediacaranas. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Registrado com interrogação pelos próprios autores: as estruturas admitem interpretação como o icnogênero Oldhamia ou como a esponja demospongia Choia. A ambiguidade é relevante — Oldhamia é icnofóssil-guia do Cambriano Inferior, e Choia é fóssil corpóreo, de modo que a leitura escolhida altera tanto a natureza do registro quanto sua implicação cronoestratigráfica. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): Netto &amp; Zucatti-da-Rosa (1997) registraram ?Oldhamia; Zucatti-da-Rosa (2006) reinterpretou as estruturas radiais como Choia?. Netto (2012) observa que sulcos de pastagem podem imitar o nicho dos produtores de Oldhamia e que Oldhamia não foi registrada em rochas ediacaranas. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Impressões atribuídas com dúvida a Arumberia, interpretadas como marcas de repouso de organismos medusoides. Arumberia é forma clássica do Ediacarano terminal, cuja própria natureza biológica é debatida — há quem a interprete como estrutura sedimentar induzida por tapetes microbianos. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os icnofósseis descritos anteriormente foram reavaliados — conferir o texto completo antes de citar esta ocorrência. INTERPRETAÇÃO (2026.10.09, segundo Netto, 2012): o resumo de Netto &amp; Zucatti-da-Rosa (1997) é citado por Netto (2012) para Diplocraterion, Gordia e ?Oldhamia, não para este táxon, e foi retirado do descritor desta ficha. Netto (2012) inclui «estruturas do tipo Arumberia» entre as estruturas sedimentares induzidas por tapetes microbianos (MISS) da Bacia do Itajaí — isto é, de origem microbiana, e não impressões de repouso de medusoides como descrito acima; a ficha mantém a leitura da dissertação, com a ressalva. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Impressões atribuídas com dúvida a Arumberia, interpretadas como marcas de repouso de organismos medusoides. Arumberia é forma clássica do Ediacarano terminal, cuja própria natureza biológica é debatida — há quem a interprete como estrutura sedimentar induzida por tapetes microbianos. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. INTERPRETAÇÃO (2026.10.09, segundo Netto, 2012): o resumo de Netto &amp; Zucatti-da-Rosa (1997) é citado por Netto (2012) para Diplocraterion, Gordia e ?Oldhamia, não para este táxon, e foi retirado do descritor desta ficha. Netto (2012) inclui «estruturas do tipo Arumberia» entre as estruturas sedimentares induzidas por tapetes microbianos (MISS) da Bacia do Itajaí — isto é, de origem microbiana, e não impressões de repouso de medusoides como descrito acima; a ficha mantém a leitura da dissertação, com a ressalva. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Classificação: macrofóssil ediacarano (gênero Palaeopascichnus; o resumo menciona apenas o gênero). Becker-Kerber et al. (2020) descrevem macrofósseis ediacaranos da Bacia do Itajaí datados em cerca de 563 Ma, entre os mais antigos da biota ediacarana em Gondwana; ocorrem em ambientes rasos, com tapetes microbianos tridimensionais bem preservados e estruturas sedimentares induzidas por tapetes microbianos (MISS), e os autores sugerem que a biota pode registrar vida bentônica adaptando-se a ambientes mais rasos e iluminados, que depois caracterizariam a Assembleia do Mar Branco. O resumo consultado não informa espécie, formação, afloramento, número de tombo nem depositário. ATENÇÃO: Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na mesma bacia, marcas interpretadas como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os macrofósseis de 2020 foram reavaliados — conferir o texto completo. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Classificação: macrofóssil ediacarano (gênero Palaeopascichnus; o resumo menciona apenas o gênero). Becker-Kerber et al. (2020) descrevem macrofósseis ediacaranos da Bacia do Itajaí datados em cerca de 563 Ma, entre os mais antigos da biota ediacarana em Gondwana; ocorrem em ambientes rasos, com tapetes microbianos tridimensionais bem preservados e estruturas sedimentares induzidas por tapetes microbianos (MISS), e os autores sugerem que a biota pode registrar vida bentônica adaptando-se a ambientes mais rasos e iluminados, que depois caracterizariam a Assembleia do Mar Branco. O resumo consultado não informa espécie, formação, afloramento, número de tombo nem depositário. ATENÇÃO: Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na mesma bacia, marcas interpretadas como tectógrafos (pseudofósseis por cisalhamento entre camadas), em ocorrência nova em Gaspar. Na leitura do texto integral (2026.10.09): o artigo não reavalia os fósseis de Becker-Kerber et al. (2020) — cita Palaeopascichnus como fóssil da bacia (ritmitos da sequência deposicional 2) e lista, no resumo, Aspidella, Nimbia, estruturas microbianas (MISS) e fósseis filamentosos como a assembleia da bacia; diz ainda que os tectógrafos de Itajaí lembram os fósseis filamentosos descritos na mesma bacia (Becker-Kerber et al. 2021b), mas diferem deles (os filamentos não mostram cruzamentos nem padrões repetidos com orientação comum). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Classificação: estrutura discoidal ediacarana (gênero Nimbia; o resumo menciona apenas o gênero). Becker-Kerber et al. (2020) descrevem macrofósseis ediacaranos da Bacia do Itajaí datados em cerca de 563 Ma, entre os mais antigos da biota ediacarana em Gondwana; ocorrem em ambientes rasos, com tapetes microbianos tridimensionais bem preservados e estruturas sedimentares induzidas por tapetes microbianos (MISS), e os autores sugerem que a biota pode registrar vida bentônica adaptando-se a ambientes mais rasos e iluminados, que depois caracterizariam a Assembleia do Mar Branco. O resumo consultado não informa espécie, formação, afloramento, número de tombo nem depositário. ATENÇÃO: Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na mesma bacia, marcas interpretadas como tectógrafos (pseudofósseis por cisalhamento entre camadas); o resumo consultado não informa se os macrofósseis de 2020 foram reavaliados — conferir o texto completo. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Classificação: estrutura discoidal ediacarana (gênero Nimbia; o resumo menciona apenas o gênero). Becker-Kerber et al. (2020) descrevem macrofósseis ediacaranos da Bacia do Itajaí datados em cerca de 563 Ma, entre os mais antigos da biota ediacarana em Gondwana; ocorrem em ambientes rasos, com tapetes microbianos tridimensionais bem preservados e estruturas sedimentares induzidas por tapetes microbianos (MISS), e os autores sugerem que a biota pode registrar vida bentônica adaptando-se a ambientes mais rasos e iluminados, que depois caracterizariam a Assembleia do Mar Branco. O resumo consultado não informa espécie, formação, afloramento, número de tombo nem depositário. ATENÇÃO: Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na mesma bacia, marcas interpretadas como tectógrafos (pseudofósseis por cisalhamento entre camadas), em ocorrência nova em Gaspar. Na leitura do texto integral (2026.10.09): o artigo não reavalia os fósseis de Becker-Kerber et al. (2020) — cita Palaeopascichnus como fóssil da bacia (ritmitos da sequência deposicional 2) e lista, no resumo, Aspidella, Nimbia, estruturas microbianas (MISS) e fósseis filamentosos como a assembleia da bacia; diz ainda que os tectógrafos de Itajaí lembram os fósseis filamentosos descritos na mesma bacia (Becker-Kerber et al. 2021b), mas diferem deles (os filamentos não mostram cruzamentos nem padrões repetidos com orientação comum). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Wikipédia (enciclopédia on-line), verbete «Lontras Shale Lagerstätte», tabela de fósseis do afloramento Campáleo, que lista o táxon como «a ray-finned fish» sem autoria, ano nem referência primária]</t>
         </is>
       </c>
       <c r="N61" s="6" t="n">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este material; Elias (2020) registra que nenhum dos achados de mesossauro de SC foi descrito em periódico científico. Segundo o NSC Total (18/05/2020), a estiagem de março de 2020 rebaixou o Rio Negro e expôs, em Três Barras, leitos rochosos com fósseis de mesossauro, vistos por pessoas da comunidade e identificados inicialmente por Carlos Eduardo Fiolek; a pesquisa é do Cenpaleo-UnC (Mafra). A matéria descreve os mesossauros em geral como répteis de 80 cm a 1 m, com membranas entre os dedos, que comiam pequenos crustáceos e viviam no 'Golfo Irati', há cerca de 280 milhões de anos — descrição do grupo, não medição deste material. O material seria preparado no Cenpaleo e parte dele cedida ao museu de Três Barras; a Prefeitura informou em 05/05/2022 que 20 peças transferidas do CENPALEO estavam expostas. As reportagens não citam formação, espécie, número de espécimes nem datação; a atribuição à Fm. Irati é a da literatura geral para mesossaurídeos da Bacia do Paraná (Elias 2020 registra também paleoniscídeos da Fm. Irati em Três Barras). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
+          <t>BASE (2026.10.09): Elias (2020, Trabalho de Conclusão de Curso, UFSC) cataloga os achados de mesossauro de SC e registra que nenhum deles foi descrito em periódico científico — não há descrição formal deste material. CITAÇÃO DE MÍDIA: o que segue vem de reportagens. Segundo o NSC Total (18/05/2020), a estiagem de março de 2020 rebaixou o Rio Negro e expôs, em Três Barras, leitos rochosos com fósseis de mesossauro, vistos por pessoas da comunidade e identificados inicialmente por Carlos Eduardo Fiolek; a pesquisa é do Cenpaleo-UnC (Mafra). A matéria descreve os mesossauros em geral como répteis de 80 cm a 1 m, com membranas entre os dedos, que comiam pequenos crustáceos e viviam no 'Golfo Irati', há cerca de 280 milhões de anos — descrição do grupo, não medição deste material. O material seria preparado no Cenpaleo e parte dele cedida ao museu de Três Barras; a Prefeitura informou em 05/05/2022 que 20 peças transferidas do CENPALEO estavam expostas. As reportagens não citam formação, espécie, número de espécimes nem datação; a atribuição à Fm. Irati é a da literatura geral para mesossaurídeos da Bacia do Paraná (Elias 2020 registra também paleoniscídeos da Fm. Irati em Três Barras). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: NSC Total (18/05/2020), reportagem «Seca leva à descoberta de fósseis de 280 milhões de anos em Três Barras, no Norte de SC», que atribui a identificação inicial a C.E. Fiolek (coordenador do museu de Três Barras) e a pesquisa ao CENPALEO/UnC] | [Citação de mídia, sem publicação científica primária identificada: Prefeitura de Três Barras (05/05/2022), notícia «Fósseis de mesossauro já estão em exposição no Museu de Três Barras»] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: NSC Total (18/05/2020), reportagem «Seca leva à descoberta de fósseis de 280 milhões de anos em Três Barras, no Norte de SC», que atribui a identificação inicial a C.E. Fiolek (coordenador do museu de Três Barras) e a pesquisa ao CENPALEO/UnC] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Prefeitura de Três Barras (05/05/2022), notícia «Fósseis de mesossauro já estão em exposição no Museu de Três Barras»] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N111" s="6" t="n">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="K181" s="7" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — o exemplar é conhecido apenas por divulgação municipal. Segundo Elias (2020), que cita a notícia da Prefeitura de Taió (28/04/2017) e atribui o achado à diretora do museu, um exemplar de mesossauro encontrado em Ribeirão das Pedras (Taió) está exposto no museu local. Sem número de tombo e sem descrição científica; coordenada do município. Elias (2020) registra que nenhum dos achados de mesossauro de SC foi descrito em periódico científico. A fonte não informa a formação: a atribuição à Fm. Irati é inferida do grupo (mesossaurídeos da Bacia do Paraná). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
+          <t>BASE (2026.10.09): Elias (2020, Trabalho de Conclusão de Curso, UFSC) registra o exemplar e cita a notícia da Prefeitura de Taió (28/04/2017); não há descrição científica dele. CITAÇÃO DE MÍDIA: a notícia da Prefeitura, conforme Elias (2020), atribui o achado à diretora do museu; um exemplar de mesossauro encontrado em Ribeirão das Pedras (Taió) está exposto no museu local. Sem número de tombo e sem descrição científica; coordenada do município. Elias (2020) registra que nenhum dos achados de mesossauro de SC foi descrito em periódico científico. A fonte não informa a formação: a atribuição à Fm. Irati é inferida do grupo (mesossaurídeos da Bacia do Paraná). TAXONOMIA: estudos recentes indicam que Mesosaurus tenuidens é a única espécie válida de Mesosauridae — "Stereosternum tumidum" e "Brazilosaurus sanpauloensis" representariam estágios imaturos ou exemplares incompletos de Mesosaurus (Verrière &amp; Fröbisch, 2022, PeerJ, DOI 10.7717/peerj.13866). Como NENHUM exemplar catarinense foi descrito formalmente, os registros de SC permanecem como Mesosauridae indet.</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="M181" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Prefeitura de Taió (28/04/2017), notícia «Museu Paleo-Arqueológico e Histórico Prefeito Bertoldo Jacobsen abre Exposição de fóssil de Mesossauro em Taió», conforme citada por Elias (2020)] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Prefeitura de Taió (28/04/2017), notícia «Museu Paleo-Arqueológico e Histórico Prefeito Bertoldo Jacobsen abre Exposição de fóssil de Mesossauro em Taió», conforme citada por Elias (2020)] | ELIAS, R.L. 2020. Vertebrados fósseis de Santa Catarina: uma cartilha sobre o patrimônio paleontológico catarinense. Trabalho de Conclusão de Curso (Geografia), Universidade Federal de Santa Catarina.</t>
         </is>
       </c>
       <c r="N181" s="6" t="n">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="M202" s="5" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Notisul (22/08/2024), reportagem «Fóssil de 270 milhões de anos é encontrado em SC», que informa a identificação pelo Centro de Pesquisa Paleontológica da Universidade do Contestado (Mafra) a partir de fotos e vídeos]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Notisul (22/08/2024), reportagem «Fóssil de 270 milhões de anos é encontrado em SC», que informa a identificação pelo Centro de Pesquisa Paleontológica da Universidade do Contestado (Mafra) a partir de fotos e vídeos]</t>
         </is>
       </c>
       <c r="N202" s="4" t="n">
@@ -19948,7 +19948,7 @@
       </c>
       <c r="M220" s="5" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (2023), reportagem «Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC», que tem como fonte o paleontólogo L.C. Weinschütz (CENPALEO/UnC)]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (2023), reportagem «Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC», que tem como fonte o paleontólogo L.C. Weinschütz (CENPALEO/UnC)]</t>
         </is>
       </c>
       <c r="N220" s="4" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão; Citação de mídia — Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann</t>
+          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão; Citação de mídia — Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
@@ -20119,20 +20119,22 @@
       </c>
       <c r="K222" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: a ocorrência e os números deste registro (paleotocas no Geoparque Caminhos dos Cânions do Sul, Praia Grande, Timbé do Sul e municípios vizinhos) vêm de reportagens. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. Litologia não informada nas reportagens. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): a existência de paleotocas no Geoparque tem base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque Caminhos dos Cânions do Sul (2.830 km², sete municípios: Timbé do Sul, Jacinto Machado, Praia Grande e Morro Grande, em SC, e três no RS) e descrevem três delas — duas nas Escarpas da Serra Geral, em Morro Grande (registros nº 268 e 269), e uma no Planalto dos Campos Gerais, em Cambará do Sul/RS (fora do escopo deste banco). Segundo o texto consultado, foram catalogadas 24 paleotocas no Geoparque, a maior parte das feições descritas até agora está em Morro Grande, e a Toca do Tatu (Timbé do Sul, registro nº 82) é tratada com base em Frank et al. (2012). O artigo não individualiza, no texto consultado, cavidades de Praia Grande. Um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural que não traz inventário de paleotocas, registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a Paleotoca Toca do Tatu (registro nº 82) e que o de Praia Grande não cita paleotocas (lista Pedra Branca, Cânion Itaimbezinho e Cânion Malacara); o de Jacinto Machado cita paleotocas ocupadas pelos Laklãnõ-Xokleng (registros nº 81 e 83). CITAÇÃO DE MÍDIA: os números e a localização em Praia Grande e Timbé do Sul, aqui, vêm de reportagens, não de publicação. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. Litologia não informada nas reportagens. Esses números (mais de 40 estruturas; mais de duas mil no Brasil) não coincidem com o catálogo do artigo (24 no Geoparque) e os critérios de contagem das reportagens não foram conciliados. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
         </is>
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
           <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
 https://jornal.unesp.br/2022/01/18/uma-visita-a-casa-dos-gigantes/
+https://doi.org/10.26848/rbgf.v17.3.p1905-1920
 https://doi.org/10.4072/rbp.2009.3.07
-https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Valdati et al. 2024, contexto do Geoparque)</t>
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418
+https://doi.org/10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão] | [Citação de mídia, sem publicação científica primária identificada: Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann]</t>
+          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920 | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann]</t>
         </is>
       </c>
       <c r="N222" s="4" t="n">
@@ -20154,7 +20156,11 @@
       <c r="R222" s="4" t="n">
         <v>-49.94</v>
       </c>
-      <c r="S222" s="4" t="inlineStr"/>
+      <c r="S222" s="4" t="inlineStr">
+        <is>
+          <t>10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -20164,7 +20170,7 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Fm. Botucatu? (não informada para esta cavidade; ver observações)</t>
+          <t>Fm. Botucatu (arenito eólico; segundo a ficha do SGB e a página do Geoparque Costões e Lagunas)</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -20194,12 +20200,12 @@
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>Citação de mídia — Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande); Citação de mídia — Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande)</t>
+          <t>Godoy, M.M., Binotto, R.B. &amp; Wildner, W. (2011) — "Paleotocas Xocleng", Ficha de geossítio nº 1841 (Geossit), Serviço Geológico do Brasil (SGB/CPRM); Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Citação de mídia — Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande); Citação de mídia — Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande); Citação de mídia — Geoparque Costões e Lagunas, página «05 Paleotoca Furnas Xocleng (Morro Grande/SC)» (14/05/2020)</t>
         </is>
       </c>
       <c r="I223" s="6" t="inlineStr">
         <is>
-          <t>Geoparque UNESCO</t>
+          <t>SGB/CPRM (ficha do geossítio); Geoparque UNESCO</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
@@ -20209,19 +20215,24 @@
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: a existência e a descrição desta paleotoca são conhecidas por divulgação institucional e turística. A página do Geoparque descreve o geossítio como 'um conjunto de 3 estruturas subterrâneas', com acesso a cerca de 18 km do centro de Morro Grande; o guia turístico registra marcas de garras nas paredes e extensão somada superior a 100 m, e cita preguiças-gigantes e tatus como possíveis escavadores. Nenhuma das duas páginas informa a unidade geológica desta cavidade, idade ou estudo científico específico. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. HISTÓRICO DE NOME: este banco chamava o registro de 'Furnas Xocleng'; esse nome não consta nas fontes consultadas, que usam 'Xocleng' (Geoparque) e 'Paleotoca Xocleng' (guia). CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande.</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. BASE (2026.10.09): (1) a ficha de geossítio «Paleotocas Xocleng» (nº 1841) do Geossit, banco de geossítios do Serviço Geológico do Brasil (Godoy, Binotto &amp; Wildner, 2011), descreve um conjunto de 3 estruturas subterrâneas muito próximas entre si, com mais de 100 m de desenvolvimento linear total, em arenitos da Fm. Botucatu (Juro-Cretáceo, ambiente desértico eólico) num pequeno morro-testemunho; as galerias maiores são atribuídas a preguiças-gigantes e as menores a animais como tatus, com marcas de garras espalhadas; a ficha a apresenta como a maior paleotoca conhecida no território do projeto do Geoparque Cânions do Sul. (2) Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) citam o «complexo de paleotocas das Três Barras (Paleotocas índios Xokleng)» — junto de Tatu e Nardi I, II e III — como exceção ao estado praticamente intocado das demais paleotocas do Geoparque, sem descrevê-lo nem informar o município. DIVERGÊNCIA DE LOCALIZAÇÃO (não resolvida): a ficha do SGB situa o geossítio em Jacinto Machado (Engenho Velho, Costão da Pedra; −29,0343, −49,8616; 140 m de altitude), enquanto a página do Geoparque e o guia turístico o situam em Morro Grande (comunidade de Três Barras). Este banco mantém Morro Grande, com a coordenada da sede municipal, e deixa a divergência sinalizada; o histórico de revisão da ficha do SGB mostra, ainda, dois pareceres «Reprovado» (junho e julho de 2022) e a situação «Consistido», cujo sentido não foi esclarecido. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural (não de paleontologia), analisam os Planos Municipais de Cultura (2015) dos quatro municípios catarinenses do Geoparque e registram que (a) o plano de Jacinto Machado cita as paleotocas — feitas por animais pré-históricos — ocupadas pelos Laklãnõ-Xokleng como sítios arqueológicos da região; (b) o de Morro Grande lista «Furnas» entre os geossítios locais; e (c) dos 23 geossítios catarinenses catalogados pelo Geoparque, os planos mencionam só cinco, um deles descrito como «paleotocas e furnas ocupadas pelos indígenas Laklãnõ-Xokleng (Jacinto Machado e Morro Grande)». O artigo não individualiza a feição, não traz coordenadas e não identifica as «Furnas» do plano de Morro Grande com a «Paleotoca Xocleng»; o nome «Furnas» também aparece no resumo da ficha do SGB («Furnas Índios Xocleng»). Portanto, compatível com as duas localizações, e a divergência acima continua sem solução. CITAÇÃO DE MÍDIA: A página do Geoparque descreve o geossítio como 'um conjunto de 3 estruturas subterrâneas', com acesso a cerca de 18 km do centro de Morro Grande; o guia turístico registra marcas de garras nas paredes e extensão somada superior a 100 m, e cita preguiças-gigantes e tatus como possíveis escavadores. Nenhuma das duas páginas informa estudo científico específico desta cavidade. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. HISTÓRICO DE NOME: este banco chamava o registro de «Furnas Xocleng»; o nome foi dado como ausente das fontes consultadas, mas consta na página do Geoparque Costões e Lagunas («Paleotoca Furnas Xocleng», Morro Grande, 14/05/2020 — túnel em arenito da Fm. Botucatu atribuído a tatus e/ou preguiças extintos há mais de 10 mil anos, sem autoria, coordenadas nem dimensões) e no resumo da ficha do SGB («Furnas Índios Xocleng»); a grafia «Xokleng» é a de Valdati et al. (2024). CORREÇÃO (2026.09.7): a coordenada anterior caía no município vizinho de Nova Veneza; passou a ser a da sede de Morro Grande. CORREÇÃO (2026.10.09): a formação, antes marcada com interrogação («Fm. Botucatu?»), é confirmada pela ficha do SGB. Valores das fontes lidos em resumo da ferramenta de leitura, não nos originais: conferir antes de citar. Santos et al. (2024) lidos no texto da cópia pré-publicação do artigo (sem DOI na cópia); a referência bibliográfica (DOI, páginas, ordem dos autores) foi conferida na página do periódico, que difere da cópia na ordem dos autores. </t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>https://canionsdosul.org/geossitios/?lang=en-us
+          <t>https://www.sgb.gov.br/geossit/geossitios/ver/1841 (ficha do geossítio, SGB/CPRM)
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418
+https://doi.org/10.26848/rbgf.v17.3.p1905-1920
+https://canionsdosul.org/geossitios/?lang=en-us
 https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
-https://doi.org/10.4072/rbp.2009.3.07</t>
+https://www.geoparquecostoeselagunas.com/05-paleotoca-furnas-xocleng-morro-grande-sc/
+https://doi.org/10.4072/rbp.2009.3.07
+https://doi.org/10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="M223" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande)] | [Citação de mídia, sem publicação científica primária identificada: Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande)]</t>
+          <t>GODOY, M.M.; BINOTTO, R.B.; WILDNER, W. 2011. Paleotocas Xocleng. Ficha de geossítio nº 1841 (Geossit), Serviço Geológico do Brasil (SGB/CPRM). | VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920 | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Geoparque Caminhos dos Cânions do Sul, página «Geossítios» (geossítio Paleotoca Xocleng, Morro Grande)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Recanto dos Canyons, página «Geoparque Caminho dos Canyons do Sul: guia completo» (Paleotoca Xocleng, Morro Grande)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Geoparque Costões e Lagunas, página «05 Paleotoca Furnas Xocleng (Morro Grande/SC)» (14/05/2020)]</t>
         </is>
       </c>
       <c r="N223" s="6" t="n">
@@ -20243,7 +20254,11 @@
       <c r="R223" s="6" t="n">
         <v>-49.7208</v>
       </c>
-      <c r="S223" s="6" t="inlineStr"/>
+      <c r="S223" s="6" t="inlineStr">
+        <is>
+          <t>10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -20283,7 +20298,7 @@
       </c>
       <c r="H224" s="5" t="inlineStr">
         <is>
-          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101</t>
+          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101; Cezaro, H.S., Santos, M.C.P. &amp; Campos, J.B. (2016) — "Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu", Revista Memorare 3(1):47–72; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr">
@@ -20298,7 +20313,7 @@
       </c>
       <c r="K224" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos) CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos). CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. ARTE RUPESTRE (2026.10.09): Cezaro, Santos &amp; Campos (2016, Revista Memorare 3(1):47–72) tratam a Toca do Tatu (Timbé do Sul) como caverna de 48,5 m com dois túneis, registrada pelo Projeto Paleotocas e descrita como abrigo «escavado provavelmente por preguiças gigantes durante o Cenozoico»; nas zonas iluminadas dos dois túneis há gravuras (não pinturas) que cobrem mais de 35 m², com sulcos finos de cerca de 5 mm e grafismos de mais de sete geometrias distintas, classificados pelos autores na Tradição Geométrica Meridional; a semelhança com motivos de pintura corporal de grupos Jê meridionais é, no artigo, uma hipótese interpretativa com ressalvas, não um achado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551) — artigo de patrimônio cultural, não de paleontologia — registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a «Paleotoca Toca do Tatu» e suas inscrições rupestres como sítios arqueológicos da região, e que a Toca do Tatu é um dos cinco geossítios catarinenses (de 23 catalogados pelo Geoparque) mencionados nos planos municipais; o artigo não traz dados paleontológicos sobre a cavidade. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores de Cezaro et al. (2016) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
         </is>
       </c>
       <c r="L224" s="5" t="inlineStr">
@@ -20306,12 +20321,14 @@
           <t>https://www.semanticscholar.org/paper/THE-COMPLEX-HISTORY-OF-A-SANDSTONE-HOSTED-CAVE-IN-,-Frank-Oliveira/352ac79d172767f56f9a572deea5da8581b08db2
 https://doi.org/10.4072/rbp.2009.3.07
 https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
-https://canionsdosul.org/geossitios/?lang=en-us</t>
+https://canionsdosul.org/geossitios/?lang=en-us
+https://portaldeperiodicos.animaeducacao.com.br/index.php/memorare_grupep/article/download/3736/2647/9066
+https://doi.org/10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="M224" s="5" t="inlineStr">
         <is>
-          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101.</t>
+          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101. | CEZARO, H.S.; SANTOS, M.C.P.; CAMPOS, J.B. 2016. Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu. Revista Memorare, 3(1), 47–72. | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="N224" s="4" t="n">
@@ -20373,7 +20390,7 @@
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
-          <t>Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»; Citação de mídia — CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»</t>
+          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»; Citação de mídia — CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»</t>
         </is>
       </c>
       <c r="I225" s="6" t="inlineStr">
@@ -20388,19 +20405,23 @@
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
-          <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA: as duas reportagens (ND Mais, 10/08/2025; CircuitoMT, 11/08/2025), que têm o geólogo do Geoparque G. Simão como único especialista citado, listam paleotocas em cinco municípios do território do Geoparque — Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande (SC) e Cambará do Sul (RS) —, mais de 40 estruturas no total, algumas com até 340 m, e três abertas à visitação. Não informam quantas há em cada município nem nomeiam as de Jacinto Machado e Praia Grande. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Sobre o Geoparque: Valdati, Gomes, Weinschütz, Ricetti &amp; Bechtel (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas do Geoparque Caminhos dos Cânions do Sul e descrevem três delas (duas nas Escarpas da Serra Geral, uma no Planalto dos Campos Gerais); um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. Esses trabalhos não individualizam as cavidades deste registro. HISTÓRICO DE NOME: o sítio deste registro constava como 'Paleotoca do Engenho Velho'; esse nome não foi encontrado em nenhuma fonte consultada (nem na página de geossítios do Geoparque) e foi substituído por uma descrição genérica.</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque (quatro municípios catarinenses, entre eles Jacinto Machado e Praia Grande) e descrevem três delas, nenhuma em Jacinto Machado ou Praia Grande; o texto consultado não individualiza cavidades desses dois municípios. A ficha de geossítio nº 1841 do Geossit (Godoy, Binotto &amp; Wildner, 2011, SGB/CPRM), «Paleotocas Xocleng», situa em Jacinto Machado (Engenho Velho, Costão da Pedra) um conjunto de 3 paleotocas; não se sabe se é a ocorrência a que as reportagens se referem — ver registro nº 81, onde essa divergência de localização é discutida. CONTEXTO CULTURAL (2026.10.09): segundo Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural, o Plano Municipal de Cultura de Jacinto Machado (2015) cita as paleotocas — feitas por animais pré-históricos — ocupadas pelos Laklãnõ-Xokleng como sítios arqueológicos da região, sem nomear, localizar ou dimensionar nenhuma; já o de Praia Grande menciona três sítios arqueológicos/geossítios (Pedra Branca, Cânion Itaimbezinho e Cânion Malacara), nenhum deles paleotoca. Isso não confirma nem contraria as reportagens de Praia Grande, porque um plano municipal de cultura não é inventário de paleotocas. CITAÇÃO DE MÍDIA: as duas reportagens (ND Mais, 10/08/2025; CircuitoMT, 11/08/2025), que têm o geólogo do Geoparque G. Simão como único especialista citado, listam paleotocas em cinco municípios do território do Geoparque — Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande (SC) e Cambará do Sul (RS) —, mais de 40 estruturas no total, algumas com até 340 m, e três abertas à visitação. Não informam quantas há em cada município nem nomeiam as de Jacinto Machado e Praia Grande. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. HISTÓRICO DE NOME: o sítio deste registro constava como 'Paleotoca do Engenho Velho'; esse nome não foi encontrado em nenhuma fonte consultada (nem na página de geossítios do Geoparque) e foi substituído por uma descrição genérica. ATUALIZAÇÃO (2026.10.09): «Engenho Velho» (Jacinto Machado) consta como localidade da ficha do SGB «Paleotocas Xocleng» (ver registro nº 81); o nome «Paleotoca do Engenho Velho», como tal, continua sem fonte. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Santos et al. (2024) lidos no texto da cópia pré-publicação do artigo (sem DOI na cópia); a referência bibliográfica foi conferida na página do periódico. </t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
           <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
 https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/
-https://doi.org/10.4072/rbp.2009.3.07</t>
+https://doi.org/10.4072/rbp.2009.3.07
+https://doi.org/10.26848/rbgf.v17.3.p1905-1920
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418
+https://www.sgb.gov.br/geossit/geossitios/ver/1841 (ficha do SGB, localização em Jacinto Machado)
+https://doi.org/10.18616/rdsd.v10i1.8551</t>
         </is>
       </c>
       <c r="M225" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»] | [Citação de mídia, sem publicação científica primária identificada: CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»]</t>
+          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920 | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes»] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: CircuitoMT (11/08/2025), reportagem «Cavernas pré-históricas de SC guardam registros de animais gigantes extintos há 10 mil anos»]</t>
         </is>
       </c>
       <c r="N225" s="6" t="n">
@@ -20422,7 +20443,11 @@
       <c r="R225" s="6" t="n">
         <v>-49.8167</v>
       </c>
-      <c r="S225" s="6" t="inlineStr"/>
+      <c r="S225" s="6" t="inlineStr">
+        <is>
+          <t>10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -20699,683 +20724,864 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Botucatu (arenito) — segundo Valdati et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
+        <is>
+          <t>Megaichnus major (Paleotoca do Veisom)</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>Paleotoca do Veisom, nordeste do município de Morro Grande, SC — Vale do Pingador (cânion), Escarpa da Serra Geral, em propriedade privada; 440 m de altitude (coordenada do registro = sede municipal: as coordenadas do artigo não são publicadas)</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="inlineStr">
+        <is>
+          <t>Geoparque UNESCO (área de estudo do artigo); afiliações dos autores a conferir no original</t>
+        </is>
+      </c>
+      <c r="J229" s="6" t="inlineStr">
+        <is>
+          <t>Não datada; intervalo convencional deste banco para paleotocas atribuídas à megafauna extinta (5,33 Ma – 11.700 a)</t>
+        </is>
+      </c>
+      <c r="K229" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Descrita por Valdati et al. (2024) como uma das três paleotocas detalhadas no artigo (ficha de catálogo com altura, largura, comprimento, marcas de garras e direção da escavação). Segundo o artigo: escavada em arenitos da Fm. Botucatu, a 440 m, numa encosta de declividade acentuada dentro do cânion do Vale do Pingador, sob Floresta Ombrófila Densa secundária; 10 m de extensão total, largura média de 1,20 m e altura média de 1,30 m; entrada colapsada; poucas marcas de escavação, de paredes lisas; classificada, pelo critério de Lopes et al. (2017), como Megaichnus major. Fica a cerca de 20 m da paleotoca da Aparência (registro nº 269); os autores sugerem que pode ser o início de outro túnel ligado à da Aparência, o que indicaria gregarismo, ou obra de um organismo menor. Sem datação; o intervalo de idade é a convenção deste banco para paleotocas atribuídas à megafauna extinta. Pino do mapa aproximado (sede de Morro Grande). Valores lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
+        </is>
+      </c>
+      <c r="L229" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.26848/rbgf.v17.3.p1905-1920
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418</t>
+        </is>
+      </c>
+      <c r="M229" s="7" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+      <c r="N229" s="6" t="n">
+        <v>268</v>
+      </c>
+      <c r="O229" s="6" t="inlineStr">
+        <is>
+          <t>Morro Grande</t>
+        </is>
+      </c>
+      <c r="P229" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Botucatu</t>
+        </is>
+      </c>
+      <c r="Q229" s="6" t="n">
+        <v>-28.8006</v>
+      </c>
+      <c r="R229" s="6" t="n">
+        <v>-49.7208</v>
+      </c>
+      <c r="S229" s="6" t="inlineStr">
+        <is>
+          <t>10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>Fm. Botucatu (arenito) — segundo Valdati et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>Megaichnus major (Paleotoca da Aparência)</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Paleotoca da Aparência, Morro Grande, SC — Vale do Pingador (cânion), Escarpa da Serra Geral, perto da paleotoca do Veisom; 430 m de altitude (coordenada do registro = sede municipal: as coordenadas do artigo não são publicadas)</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>Geoparque UNESCO (área de estudo do artigo); afiliações dos autores a conferir no original</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>Não datada; intervalo convencional deste banco para paleotocas atribuídas à megafauna extinta (5,33 Ma – 11.700 a)</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Descrita por Valdati et al. (2024) como uma das três paleotocas detalhadas no artigo. Segundo o artigo: perto da paleotoca do Veisom (registro nº 268; cerca de 20 m), no mesmo compartimento geomorfológico (Escarpa da Serra Geral, Vale do Pingador), na mesma litologia (arenitos da Fm. Botucatu) e fisionomia (Floresta Ombrófila Densa secundária, em encosta íngreme usada no passado para agricultura), a 430 m de altitude; 61 m de extensão total, largura máxima de 3,37 m e altura máxima de 3,35 m; azimute variando ao longo do túnel entre 257° (oés-sudoeste) e 192° (sul); marcas de garras visíveis no interior, de diversos tamanhos; paredes lisas; classificada, pelo critério de Lopes et al. (2017), como Megaichnus major, e atribuída pelos autores a um milodontídeo ou megaterídeo. Sem datação; o intervalo de idade é a convenção deste banco para paleotocas atribuídas à megafauna extinta. Pino do mapa aproximado (sede de Morro Grande). Valores lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
+        </is>
+      </c>
+      <c r="L230" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.26848/rbgf.v17.3.p1905-1920
+https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418</t>
+        </is>
+      </c>
+      <c r="M230" s="5" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+      <c r="N230" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="O230" s="4" t="inlineStr">
+        <is>
+          <t>Morro Grande</t>
+        </is>
+      </c>
+      <c r="P230" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Botucatu</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="n">
+        <v>-28.8006</v>
+      </c>
+      <c r="R230" s="4" t="n">
+        <v>-49.7208</v>
+      </c>
+      <c r="S230" s="4" t="inlineStr">
+        <is>
+          <t>10.26848/rbgf.v17.3.p1905-1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B229" s="6" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>Depósitos litorâneos / lacustres</t>
         </is>
       </c>
-      <c r="C229" s="7" t="inlineStr">
+      <c r="C231" s="7" t="inlineStr">
         <is>
           <t>Tatu-gigante (Propraopus sp. / Glyptodon sp. — osteodermos)</t>
         </is>
       </c>
-      <c r="D229" s="6" t="inlineStr">
+      <c r="D231" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E231" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F229" s="7" t="inlineStr">
+      <c r="F231" s="7" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC (localidades imprecisas)</t>
         </is>
       </c>
-      <c r="G229" s="6" t="inlineStr">
+      <c r="G231" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H229" s="7" t="inlineStr">
+      <c r="H231" s="7" t="inlineStr">
         <is>
           <t>Paula-Couto, C. (1980) — Anais da Academia Brasileira de Ciências 52(3):527–531 [artigo original não consultado; citado em Buchmann et al.]</t>
         </is>
       </c>
-      <c r="I229" s="6" t="inlineStr">
+      <c r="I231" s="6" t="inlineStr">
         <is>
           <t>Museu Nacional / UFRJ (coleção histórica)</t>
         </is>
       </c>
-      <c r="J229" s="6" t="inlineStr">
+      <c r="J231" s="6" t="inlineStr">
         <is>
           <t>ca. 2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K229" s="7" t="inlineStr">
+      <c r="K231" s="7" t="inlineStr">
         <is>
           <t>Classificação: Xenarthra (Cingulata). Primeiro registro de tatu-gigante para SC reportado por Paula-Couto (1980)</t>
         </is>
       </c>
-      <c r="L229" s="7" t="inlineStr">
+      <c r="L231" s="7" t="inlineStr">
         <is>
           <t>Artigo original (Paula-Couto, 1980, Anais ABC 52(3):527-531) não localizado em acesso direto
 citado em: https://www.academia.edu/15400290/Icnof%C3%B3sseis_paleotocas_e_crotovinas_atribu%C3%ADdos_a_mam%C3%ADferos_extintos_no_sudeste_e_sul_do_Brasil
 https://www.scielo.br/j/rbzool/a/3q86RZbNfRbQ7rBMCZHmSpP/?lang=pt</t>
         </is>
       </c>
-      <c r="M229" s="7" t="inlineStr">
+      <c r="M231" s="7" t="inlineStr">
         <is>
           <t>PAULA-COUTO, C. 1980. Anais da Academia Brasileira de Ciências 52(3):527–531 [artigo original não consultado; citado em Buchmann et al.].</t>
         </is>
       </c>
-      <c r="N229" s="6" t="n">
+      <c r="N231" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="O229" s="6" t="inlineStr">
+      <c r="O231" s="6" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC</t>
         </is>
       </c>
-      <c r="P229" s="6" t="inlineStr">
+      <c r="P231" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q229" s="6" t="n">
+      <c r="Q231" s="6" t="n">
         <v>-28.95</v>
       </c>
-      <c r="R229" s="6" t="n">
+      <c r="R231" s="6" t="n">
         <v>-49.45</v>
       </c>
-      <c r="S229" s="6" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+      <c r="S231" s="6" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B232" s="4" t="inlineStr">
         <is>
           <t>Estrutura cenozoica (paleotoca) — rocha encaixante não informada na fonte consultada</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
         <is>
           <t>Paleotoca da Cavidade Linha Mimosa (icnofóssil de escavação de megafauna)</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — paleotoca</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
+      <c r="E232" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr">
         <is>
           <t>Cavidade Linha Mimosa, zona rural de Lindóia do Sul, SC (coordenada do município; a da cavidade não foi identificada na fonte consultada)</t>
         </is>
       </c>
-      <c r="G230" s="4" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H230" s="5" t="inlineStr">
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>Budke, A., Lima, G.L. &amp; Carbonera, M. (2020) — "Análise de cavidades naturais presentes no oeste de Santa Catarina: um estudo de caso no município de Lindóia do Sul", Boletim Paranaense de Geociências 77:1–12</t>
         </is>
       </c>
-      <c r="I230" s="4" t="inlineStr">
+      <c r="I232" s="4" t="inlineStr">
         <is>
           <t>UFFS — Campus Chapecó</t>
         </is>
       </c>
-      <c r="J230" s="4" t="inlineStr">
+      <c r="J232" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="K230" s="5" t="inlineStr">
+      <c r="K232" s="5" t="inlineStr">
         <is>
           <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Das três cavidades naturais investigadas na zona rural de Lindóia do Sul, os autores concluíram que a Cavidade Linha Mimosa é uma PALEOTOCA, esculpida por processos biogênicos de mamíferos da megafauna do Pleistoceno; as outras duas não foram atribuídas a megafauna. É o primeiro registro paleontológico do OESTE catarinense neste catálogo. RESSALVA: a fonte consultada publica coordenadas de duas das cavidades, mas não foi possível identificar qual corresponde à Linha Mimosa — usa-se a coordenada central do município.</t>
         </is>
       </c>
-      <c r="L230" s="5" t="inlineStr">
+      <c r="L232" s="5" t="inlineStr">
         <is>
           <t>https://rd.uffs.edu.br/bitstream/prefix/2879/1/BUDKE.pdf
 https://jornalgeograficouffs.wordpress.com/2020/09/02/um-estudo-sobre-cavidades-naturais/</t>
         </is>
       </c>
-      <c r="M230" s="5" t="inlineStr">
+      <c r="M232" s="5" t="inlineStr">
         <is>
           <t>BUDKE, A.; LIMA, G.L.; CARBONERA, M. 2020. Análise de cavidades naturais presentes no oeste de Santa Catarina: um estudo de caso no município de Lindóia do Sul. Boletim Paranaense de Geociências, 77, 1–12.</t>
         </is>
       </c>
-      <c r="N230" s="4" t="n">
+      <c r="N232" s="4" t="n">
         <v>227</v>
       </c>
-      <c r="O230" s="4" t="inlineStr">
+      <c r="O232" s="4" t="inlineStr">
         <is>
           <t>Linha Mimosa (Lindóia do Sul)</t>
         </is>
       </c>
-      <c r="P230" s="4" t="inlineStr">
+      <c r="P232" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — paleotoca cenozoica</t>
         </is>
       </c>
-      <c r="Q230" s="4" t="n">
+      <c r="Q232" s="4" t="n">
         <v>-27.0268</v>
       </c>
-      <c r="R230" s="4" t="n">
+      <c r="R232" s="4" t="n">
         <v>-52.0515</v>
       </c>
-      <c r="S230" s="4" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="6" t="inlineStr">
+      <c r="S232" s="4" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>Areia marinha rasa pleistocênica (unidade litoestratigráfica não nomeada no trecho consultado)</t>
         </is>
       </c>
-      <c r="C231" s="7" t="inlineStr">
+      <c r="C233" s="7" t="inlineStr">
         <is>
           <t>Escavações biogênicas, provavelmente de Callichirus (crustáceo decápode)</t>
         </is>
       </c>
-      <c r="D231" s="6" t="inlineStr">
+      <c r="D233" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — escavação</t>
         </is>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E233" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F231" s="7" t="inlineStr">
+      <c r="F233" s="7" t="inlineStr">
         <is>
           <t>«Perto de Paulo Lopes», SC (expressão do artigo); local exato não informado. Ponto do mapa = centro do município de Paulo Lopes (referência regional)</t>
         </is>
       </c>
-      <c r="G231" s="6" t="inlineStr">
+      <c r="G233" s="6" t="inlineStr">
         <is>
           <t>Não aplicável (observação de campo; sem material coletado informado)</t>
         </is>
       </c>
-      <c r="H231" s="7" t="inlineStr">
+      <c r="H233" s="7" t="inlineStr">
         <is>
           <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011</t>
         </is>
       </c>
-      <c r="I231" s="6" t="inlineStr">
+      <c r="I233" s="6" t="inlineStr">
         <is>
           <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores</t>
         </is>
       </c>
-      <c r="J231" s="6" t="inlineStr">
+      <c r="J233" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno (idade numérica não informada para este afloramento)</t>
         </is>
       </c>
-      <c r="K231" s="7" t="inlineStr">
+      <c r="K233" s="7" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO (segundo o artigo): os autores registram escavações biogênicas em areia marinha rasa de idade pleistocênica, «provavelmente devidas a Callichirus», perto de Paulo Lopes; a atribuição ao decápode é dada como provável e o artigo não descreve nem ilustra as estruturas no trecho consultado. NOTA DE FONTE (2026.10.09): o trecho consultado não nomeia a unidade litoestratigráfica nem dá datação para esse afloramento; o município de Paulo Lopes é a única referência de local. Não há número de tombo, e as escavações não foram atribuídas a um icnogênero.</t>
         </is>
       </c>
-      <c r="L231" s="7" t="inlineStr">
+      <c r="L233" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0001-37652000000200011
 https://www.scielo.br/j/aabc/a/PV3LvmfpkshVK6wWx8WgWSc/?lang=en (Caruso Júnior, Suguio &amp; Nakamura, 2000 — texto integral)</t>
         </is>
       </c>
-      <c r="M231" s="7" t="inlineStr">
+      <c r="M233" s="7" t="inlineStr">
         <is>
           <t>CARUSO JÚNIOR, F.; SUGUIO, K.; NAKAMURA, T. 2000. The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil). Anais da Academia Brasileira de Ciências, 72(2), 257–270. DOI: 10.1590/S0001-37652000000200011</t>
         </is>
       </c>
-      <c r="N231" s="6" t="n">
+      <c r="N233" s="6" t="n">
         <v>267</v>
       </c>
-      <c r="O231" s="6" t="inlineStr">
+      <c r="O233" s="6" t="inlineStr">
         <is>
           <t>Paulo Lopes (areia marinha rasa pleistocênica com escavações)</t>
         </is>
       </c>
-      <c r="P231" s="6" t="inlineStr">
+      <c r="P233" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q231" s="6" t="n">
+      <c r="Q233" s="6" t="n">
         <v>-27.9617</v>
       </c>
-      <c r="R231" s="6" t="n">
+      <c r="R233" s="6" t="n">
         <v>-48.7601</v>
       </c>
-      <c r="S231" s="6" t="inlineStr">
+      <c r="S233" s="6" t="inlineStr">
         <is>
           <t>10.1590/S0001-37652000000200011</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
+      <c r="C234" s="5" t="inlineStr">
         <is>
           <t>Notiomastodon platensis (Ameghino, 1888)</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D234" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
+      <c r="E234" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
+      <c r="F234" s="5" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (a ~23 m de profundidade, em pesca de arrasto, no fim de março de 2018 — coordenada aproximada)</t>
         </is>
       </c>
-      <c r="G232" s="4" t="inlineStr">
+      <c r="G234" s="4" t="inlineStr">
         <is>
           <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>Citação de mídia — Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade); Mothé, D., Avilla, L.S., Cozzuol, M. &amp; Winck, G.R. (2012) — "Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands", Quaternary International 276–277:2–7</t>
-        </is>
-      </c>
-      <c r="I232" s="4" t="inlineStr">
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>Citação de mídia — Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J232" s="4" t="inlineStr">
+      <c r="J234" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos, segundo a reportagem (método de datação não informado)</t>
         </is>
       </c>
-      <c r="K232" s="5" t="inlineStr">
-        <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este espécime. Segundo as reportagens, pescadores recolheram no fim de março de 2018 a metade esquerda da mandíbula de um macho adulto, a cerca de 23 m de profundidade, em pesca de arrasto na costa de Sombrio; pesquisadores da Univali a identificaram como Stegomastodon waringi, de cerca de 30 mil anos, com estimativa de ~5 m de comprimento, ~2,5 m de altura e ~3,5 t; fósseis dessa espécie seriam raros em SC e mais comuns no RS. Local de guarda, número de tombo e formação NÃO são informados. HISTÓRICO TAXONÔMICO: a reportagem usa Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a combinação Notiomastodon platensis; parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. O nome do registro segue essa revisão; a reportagem não o usa. CONTEXTO CIENTÍFICO (não trata deste espécime): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27, DOI 10.1016/j.jsames.2010.11.003) relatam, para a plataforma continental do sul do Brasil (o resumo fala em 'porção mais meridional da costa', com palavra-chave Rio Grande do Sul), restos de Toxodon sp. e um molar de Stegomastodon waringi recolhidos por pescadores a cerca de 20 m de profundidade.</t>
-        </is>
-      </c>
-      <c r="L232" s="5" t="inlineStr">
+      <c r="K234" s="5" t="inlineStr">
+        <is>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este espécime. Segundo as reportagens, pescadores recolheram no fim de março de 2018 a metade esquerda da mandíbula de um macho adulto, a cerca de 23 m de profundidade, em pesca de arrasto na costa de Sombrio; pesquisadores da Univali a identificaram como Stegomastodon waringi, de cerca de 30 mil anos, com estimativa de ~5 m de comprimento, ~2,5 m de altura e ~3,5 t; fósseis dessa espécie seriam raros em SC e mais comuns no RS. Local de guarda, número de tombo e formação NÃO são informados. HISTÓRICO TAXONÔMICO: a reportagem usa Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International 276–277:2–7; trabalho de contexto taxonômico, que não trata deste espécime) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a combinação Notiomastodon platensis; parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. O nome do registro segue essa revisão; a reportagem não o usa. CONTEXTO CIENTÍFICO (não trata deste espécime): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam, para a plataforma continental do sul do Brasil (o resumo fala em 'porção mais meridional da costa', com palavra-chave Rio Grande do Sul), restos de Toxodon sp. e um molar de Stegomastodon waringi recolhidos por pescadores a cerca de 20 m de profundidade.</t>
+        </is>
+      </c>
+      <c r="L234" s="5" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
-https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/
-https://www.sciencedirect.com/science/article/abs/pii/S1040618211002916
-https://doi.org/10.1016/j.jsames.2010.11.003</t>
-        </is>
-      </c>
-      <c r="M232" s="5" t="inlineStr">
-        <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)] | MOTHÉ, D.; AVILLA, L.S.; COZZUOL, M. et al. 2012. Taxonomic revision of the Quaternary gomphotheres (Mammalia: Proboscidea: Gomphotheriidae) from the South American lowlands. Quaternary International 276–277:2–7.</t>
-        </is>
-      </c>
-      <c r="N232" s="4" t="n">
+https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
+        </is>
+      </c>
+      <c r="M234" s="5" t="inlineStr">
+        <is>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="O232" s="4" t="inlineStr">
+      <c r="O234" s="4" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P232" s="4" t="inlineStr">
+      <c r="P234" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="Q232" s="4" t="n">
+      <c r="Q234" s="4" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R232" s="4" t="n">
+      <c r="R234" s="4" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S232" s="4" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
+      <c r="S234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C233" s="7" t="inlineStr">
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>Lestodon armatus Gervais, 1855</t>
         </is>
       </c>
-      <c r="D233" s="6" t="inlineStr">
+      <c r="D235" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E235" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F233" s="7" t="inlineStr">
+      <c r="F235" s="7" t="inlineStr">
         <is>
           <t>Plataforma continental entre Passo de Torres e Araranguá, SC (redes de arrasto de camarão — coordenada aproximada)</t>
         </is>
       </c>
-      <c r="G233" s="6" t="inlineStr">
+      <c r="G235" s="6" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras, SC</t>
         </is>
       </c>
-      <c r="H233" s="7" t="inlineStr">
+      <c r="H235" s="7" t="inlineStr">
         <is>
           <t>Citação de mídia — Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
+      <c r="I235" s="6" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J233" s="6" t="inlineStr">
+      <c r="J235" s="6" t="inlineStr">
         <is>
           <t>ca. 30.000 anos antes do presente, segundo a divulgação (método não informado)</t>
         </is>
       </c>
-      <c r="K233" s="7" t="inlineStr">
+      <c r="K235" s="7" t="inlineStr">
         <is>
           <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica. Segundo a divulgação, fósseis de lestodonte (Lestodon armatus) saíram de redes de arrasto de camarão na plataforma continental entre Passo de Torres e Araranguá, pertencem à 'formação Laguna-Barreira' e são 'datados de cerca de 30 mil anos antes do presente'; a equipe do museu encontrou 'ao menos dois' lestodontes, 'tratando-se do primeiro registro desta espécie no Estado'. A altura (~4,5 m) e o peso (~3 t) citados descrevem a espécie em geral, não o exemplar. O esqueleto montado está exposto no Museu Oceanográfico Univali (Balneário Piçarras). Não são informados identificador, tombo, data da coleta nem método de datação.</t>
         </is>
       </c>
-      <c r="L233" s="7" t="inlineStr">
+      <c r="L235" s="7" t="inlineStr">
         <is>
           <t>https://novomomento.com.br/preguica-gigante-museu-oceanografico/
 https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx (página original; indisponível em 08/10/2026)</t>
         </is>
       </c>
-      <c r="M233" s="7" t="inlineStr">
-        <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)]</t>
-        </is>
-      </c>
-      <c r="N233" s="6" t="n">
+      <c r="M235" s="7" t="inlineStr">
+        <is>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)]</t>
+        </is>
+      </c>
+      <c r="N235" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="O233" s="6" t="inlineStr">
+      <c r="O235" s="6" t="inlineStr">
         <is>
           <t>Plataforma continental Passo de Torres–Araranguá</t>
         </is>
       </c>
-      <c r="P233" s="6" t="inlineStr">
+      <c r="P235" s="6" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q233" s="6" t="n">
+      <c r="Q235" s="6" t="n">
         <v>-29.28</v>
       </c>
-      <c r="R233" s="6" t="n">
+      <c r="R235" s="6" t="n">
         <v>-49.55</v>
       </c>
-      <c r="S233" s="6" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+      <c r="S235" s="6" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B236" s="4" t="inlineStr">
         <is>
           <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
+      <c r="C236" s="5" t="inlineStr">
         <is>
           <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D236" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr">
+      <c r="E236" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
+      <c r="F236" s="5" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
         </is>
       </c>
-      <c r="G234" s="4" t="inlineStr">
+      <c r="G236" s="4" t="inlineStr">
         <is>
           <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
-      <c r="H234" s="5" t="inlineStr">
+      <c r="H236" s="5" t="inlineStr">
         <is>
           <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr">
+      <c r="I236" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J234" s="4" t="inlineStr">
+      <c r="J236" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
         </is>
       </c>
-      <c r="K234" s="5" t="inlineStr">
-        <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27, DOI 10.1016/j.jsames.2010.11.003) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
-        </is>
-      </c>
-      <c r="L234" s="5" t="inlineStr">
-        <is>
-          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/
-https://doi.org/10.1016/j.jsames.2010.11.003</t>
-        </is>
-      </c>
-      <c r="M234" s="5" t="inlineStr">
-        <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
-        </is>
-      </c>
-      <c r="N234" s="4" t="n">
+      <c r="K236" s="5" t="inlineStr">
+        <is>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="inlineStr">
+        <is>
+          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="inlineStr">
+        <is>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
+        </is>
+      </c>
+      <c r="N236" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="O234" s="4" t="inlineStr">
+      <c r="O236" s="4" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P234" s="4" t="inlineStr">
+      <c r="P236" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="Q234" s="4" t="n">
+      <c r="Q236" s="4" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R234" s="4" t="n">
+      <c r="R236" s="4" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S234" s="4" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="inlineStr">
+      <c r="S236" s="4" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B235" s="6" t="inlineStr">
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>Fm. Rio Bonito (segundo o comunicado da UDESC e a reportagem do ND Mais)</t>
         </is>
       </c>
-      <c r="C235" s="7" t="inlineStr">
+      <c r="C237" s="7" t="inlineStr">
         <is>
           <t>Paleotoca Amaral de Baixo (icnofóssil de escavação — provável tatu extinto)</t>
         </is>
       </c>
-      <c r="D235" s="6" t="inlineStr">
+      <c r="D237" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — paleotoca</t>
         </is>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E237" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F235" s="7" t="inlineStr">
+      <c r="F237" s="7" t="inlineStr">
         <is>
           <t>Localidade Rio Amaral Gruta, Lauro Müller, SC (coordenada do município)</t>
         </is>
       </c>
-      <c r="G235" s="6" t="inlineStr">
+      <c r="G237" s="6" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H235" s="7" t="inlineStr">
+      <c r="H237" s="7" t="inlineStr">
         <is>
           <t>Citação de mídia — UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF); Citação de mídia — ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)</t>
         </is>
       </c>
-      <c r="I235" s="6" t="inlineStr">
+      <c r="I237" s="6" t="inlineStr">
         <is>
           <t>UDESC — Laboratório de Geografia Física (LGEF), grupo BioGeo, FAED (segundo o comunicado da UDESC); equipe técnica do Geoparque (segundo o ND Mais)</t>
         </is>
       </c>
-      <c r="J235" s="6" t="inlineStr">
+      <c r="J237" s="6" t="inlineStr">
         <is>
           <t>Não datada; a reportagem fala em animais que viveram 'há cerca de 10 mil anos'</t>
         </is>
       </c>
-      <c r="K235" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
-        </is>
-      </c>
-      <c r="L235" s="7" t="inlineStr">
+      <c r="K237" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
+        </is>
+      </c>
+      <c r="L237" s="7" t="inlineStr">
         <is>
           <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
 https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
-      <c r="M235" s="7" t="inlineStr">
-        <is>
-          <t>[Citação de mídia, sem publicação científica primária identificada: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia, sem publicação científica primária identificada: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
-        </is>
-      </c>
-      <c r="N235" s="6" t="n">
+      <c r="M237" s="7" t="inlineStr">
+        <is>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
+        </is>
+      </c>
+      <c r="N237" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="O235" s="6" t="inlineStr">
+      <c r="O237" s="6" t="inlineStr">
         <is>
           <t>Lauro Müller</t>
         </is>
       </c>
-      <c r="P235" s="6" t="inlineStr">
+      <c r="P237" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Rio Bonito</t>
         </is>
       </c>
-      <c r="Q235" s="6" t="n">
+      <c r="Q237" s="6" t="n">
         <v>-28.4047</v>
       </c>
-      <c r="R235" s="6" t="n">
+      <c r="R237" s="6" t="n">
         <v>-49.3811</v>
       </c>
-      <c r="S235" s="6" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
+      <c r="S237" s="6" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="B238" s="4" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada)</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
         <is>
           <t>Pólen, esporos e carvão de turfeira da Serra do Tabuleiro (testemunho Ciama 2; ~39.700 anos)</t>
         </is>
       </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos) e partículas de carvão</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
+      <c r="E238" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
         <is>
           <t>Turfeira «Ciama 2», Parque Estadual da Serra do Tabuleiro, SC (27°53′48,46″ S; 48°52′5,33″ O; 860 m de altitude); testemunho de 169 cm coletado em 2005 com amostrador Russian</t>
         </is>
       </c>
-      <c r="G236" s="4" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>Jeske-Pieruschka, V., Pillar, V.D., De Oliveira, M.A.T. &amp; Behling, H. (2013) — "New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro", Vegetation History and Archaeobotany 22(4):299–314, DOI 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
-      <c r="I236" s="4" t="inlineStr">
+      <c r="I238" s="4" t="inlineStr">
         <is>
           <t>Universität Göttingen (projeto de doutorado de V. Jeske-Pieruschka, sob H. Behling, segundo a página do projeto)</t>
         </is>
       </c>
-      <c r="J236" s="4" t="inlineStr">
+      <c r="J238" s="4" t="inlineStr">
         <is>
           <t>Últimos ~39.720 anos 14C AP (base extrapolada a 168 cm) até 2005 d.C. — do Pleistoceno Superior (glacial) ao Holoceno</t>
         </is>
       </c>
-      <c r="K236" s="5" t="inlineStr">
+      <c r="K238" s="5" t="inlineStr">
         <is>
           <t>Classificação: microfósseis (pólen e esporos) e partículas de carvão de um testemunho de turfeira — registro paleoambiental quaternário, não um fóssil em rocha. Segundo o artigo, o testemunho (169 cm; oito datações AMS) cobre cerca de 39.720 anos. Resultados dos autores: campos (gramíneas subtropicais) cobriram extensas áreas do planalto durante todo o período glacial registrado, o que eles ligam a clima frio e seco; a floresta pluvial atlântica começou a se espalhar pelas encostas por volta de 10.400 anos cal AP, com clima mais quente e úmido; a floresta de araucária surge no Holoceno tardio (a partir de ~2.160 anos cal AP, com máximo após ~300 anos cal AP); e há abertura da floresta por perturbação recente (inclusive extração de madeira), com avanço dos campos entre 1940 e 2005. Fogo ausente no glacial e comum entre ~10.400 e ~3.600 anos cal AP, provavelmente por ameríndios (inferência dos autores). Os autores concluem que a serra costeira do Tabuleiro não foi refúgio glacial para táxons da floresta pluvial atlântica no Último Máximo Glacial. LOCALIZAÇÃO (2026.10.09): o artigo dá o Parque Estadual da Serra do Tabuleiro e as coordenadas acima, mas não nomeia o município. O parque abrange Florianópolis, Palhoça, Santo Amaro da Imperatriz, Águas Mornas, São Bonifácio, São Martinho, Imaruí e Paulo Lopes (Wikipédia). A etiqueta «São Bonifácio (região)» é uma derivação do compilador: as coordenadas informadas caem no polígono desse município na malha municipal do site; confirme com o mapa oficial antes de citar o município. NOTA DE FONTE: consultados a página do artigo no Springer (resumo e trechos do texto) e a cópia do resumo no Paperity; tabela de datações e diagramas não foram acessados. Número de tombo e depositário não se aplicam/não foram informados.</t>
         </is>
       </c>
-      <c r="L236" s="5" t="inlineStr">
+      <c r="L238" s="5" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/s00334-012-0382-y (Jeske-Pieruschka et al., 2013 — página do artigo)
 https://paperity.org/p/6235978/new-insights-into-vegetation-climate-and-fire-history-of-southern-brazil-revealed-by-a-40 (cópia do resumo)
@@ -21383,2401 +21589,2589 @@
 https://en.wikipedia.org/wiki/Serra_do_Tabuleiro_State_Park (municípios do parque)</t>
         </is>
       </c>
-      <c r="M236" s="5" t="inlineStr">
+      <c r="M238" s="5" t="inlineStr">
         <is>
           <t>JESKE-PIERUSCHKA, V.; PILLAR, V.D.; DE OLIVEIRA, M.A.T. et al. 2013. New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro. Vegetation History and Archaeobotany, 22(4), 299–314. DOI: 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
-      <c r="N236" s="4" t="n">
+      <c r="N238" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="O236" s="4" t="inlineStr">
+      <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Serra do Tabuleiro (turfeira Ciama 2)</t>
         </is>
       </c>
-      <c r="P236" s="4" t="inlineStr">
+      <c r="P238" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q236" s="4" t="n">
+      <c r="Q238" s="4" t="n">
         <v>-27.8968</v>
       </c>
-      <c r="R236" s="4" t="n">
+      <c r="R238" s="4" t="n">
         <v>-48.8681</v>
       </c>
-      <c r="S236" s="4" t="inlineStr">
+      <c r="S238" s="4" t="inlineStr">
         <is>
           <t>10.1007/s00334-012-0382-y</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="6" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C237" s="7" t="inlineStr">
+      <c r="C239" s="7" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira do Morro da Igreja (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D237" s="6" t="inlineStr">
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>Turfeira de altitude no «Morro da Igreja», SC (Behling, 1995). O resumo não traz município nem coordenadas da turfeira; ponto aproximado no próprio Morro da Igreja, em Urubici (28°07′30″ S; 49°28′28″ O; 1.822 m, segundo a Wikipédia)</t>
-        </is>
-      </c>
-      <c r="G237" s="6" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>Turfeira de altitude (cerca de 1.800 m) na borda do Parque Nacional de São Joaquim, a 300 m a oeste do ponto mais alto do Morro da Igreja, Urubici, SC (Behling, 1995; ponto do mapa aproximado, no próprio morro: ver observações)</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I237" s="6" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J237" s="6" t="inlineStr">
-        <is>
-          <t>Cobertura do perfil não detalhada no resumo; segundo o resumo e Behling et al. (2004), os campos dominam até cerca de 1000 anos AP, quando a araucária se expande sobre eles</t>
-        </is>
-      </c>
-      <c r="K237" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário. Behling (1995) estuda três turfeiras de altitude e um perfil da planície costeira de SC. Segundo o resumo, nas turfeiras do Morro da Igreja e da Serra do Rio Rastro a dominância de campos continuou até cerca de 1000 anos AP; a floresta de araucária (Araucaria angustifolia) se expandiu no último milênio; para o conjunto das turfeiras de altitude, o Pleistoceno tardio (14.000–10.000 anos 14C AP, não calibrados) teve campos, com araucária só em vales profundos, sob clima frio e relativamente seco. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses: a primeira expansão da floresta de araucária em 3460 ± 195 anos 14C AP (Serra da Boa Vista) e 2385 ± 225 anos 14C AP (Serra do Rio Rastro), e a expansão marcante da araucária sobre os campos em cerca de 1000 anos 14C AP (Morro da Igreja e Serra do Rio Rastro). Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. LOCALIZAÇÃO (2026.10.09): a posição da turfeira dentro do Morro da Igreja não consta no resumo; o ponto do mapa é o do morro (Urubici, 1.822 m) e é apenas aproximado. NOTA DE FONTE: só o resumo de Behling (1995) foi lido; o texto integral, com diagramas e datações por perfil, não foi acessado. Os outros dois perfis do mesmo estudo (Serra da Boa Vista, turfeira; Poço Grande, planície costeira) não foram cadastrados porque nenhuma fonte consultada informa onde ficam. Número de tombo e depositário não informados.</t>
-        </is>
-      </c>
-      <c r="L237" s="7" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — resumo)
+      <c r="J239" s="6" t="inlineStr">
+        <is>
+          <t>Perfil de 144 cm: base datada em 10.200 ± 275 anos 14C AP até o presente (60 ± 120 anos AP aos 40–44 cm, idade que o autor atribui a influência de raízes atuais); idades não calibradas</t>
+        </is>
+      </c>
+      <c r="K239" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 30 × 40 m numa encosta voltada a oeste, de leve inclinação, a cerca de 1.800 m, na borda do Parque Nacional de São Joaquim e 300 m a oeste do ponto mais alto do morro, junto ao limite entre o planalto e as terras baixas; o autor a descreve nos campos da região alta, com floresta nebular nas encostas íngremes próximas. Amostragem em 04/12/1989 (amostrador Dachnowski); perfil de turfa de 144 cm sobre rocha (149 cm); contagem mínima de 1.215 grãos de pólen por amostra (média de 2.353). Duas datações por 14C (Laboratório de Hanover, Hv 17557 e Hv 17558): 60 ± 120 anos AP aos 40–44 cm e 10.200 ± 275 anos AP aos 140–144 cm, na base do perfil; idades não calibradas. RESULTADO: do início do perfil (~10.200 anos AP) até cerca de 1.000 anos AP os campos dominam o pólen; a floresta de araucária (Araucaria angustifolia, de 1% a 10% do pólen) se expande sobre os campos na zona 4a, que o autor estima em não mais de ~1.000 anos; a zona 4b (cerca de 100 anos) traz sinais de ação humana — queda da araucária (extração de madeira), grãos de Pinus e um de Zea mays — e o desaparecimento de Weinmannia entre 8 e 16 cm, que o autor atribui provavelmente ao grande incêndio de 1951 na floresta nebular da Serra Geral. Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco; esta turfeira registra apenas o fim dessa fase. LOCALIZAÇÃO (2026.10.09): o artigo dá o morro em 28°11′ S, 49°52′ O, «25 km a sudeste da vila de Urubici»; essas coordenadas caem, na malha municipal deste site, em São Joaquim (cerca de 30 km a oés-sudoeste de Urubici), o que não combina com «sudeste» nem com o morro conhecido (Wikipédia: 28°07′30″ S, 49°28′28″ O, 1.822 m, em Urubici). Possível erro de impressão no artigo, não verificado; o pino segue no próprio morro e é apenas aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
+        </is>
+      </c>
+      <c r="L239" s="7" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
 https://www.uni-goettingen.de/de/document/download/7704cdc9d93f4bdd3c6e232529ec697f.pdf/2004_Behling_PPP_CambaradoSul_Brazil.pdf (Behling et al., 2004 — idades de SC citadas)
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M237" s="7" t="inlineStr">
+      <c r="M239" s="7" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N237" s="6" t="n">
+      <c r="N239" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="O237" s="6" t="inlineStr">
+      <c r="O239" s="6" t="inlineStr">
         <is>
           <t>Morro da Igreja (Urubici)</t>
         </is>
       </c>
-      <c r="P237" s="6" t="inlineStr">
+      <c r="P239" s="6" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q237" s="6" t="n">
+      <c r="Q239" s="6" t="n">
         <v>-28.125</v>
       </c>
-      <c r="R237" s="6" t="n">
+      <c r="R239" s="6" t="n">
         <v>-49.4744</v>
       </c>
-      <c r="S237" s="6" t="inlineStr">
+      <c r="S239" s="6" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B238" s="4" t="inlineStr">
+      <c r="B240" s="4" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira da Serra do Rio do Rastro (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="D240" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
+      <c r="E240" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>Turfeira de altitude na «Serra do Rio Rastro» (grafia de Behling, 1995; a serra é conhecida como Serra do Rio do Rastro), SC. O resumo não traz município nem coordenadas da turfeira; ponto aproximado na serra, entre Lauro Müller e Bom Jardim da Serra (28°24′26″ S; 49°32′46″ O, segundo a Wikipédia)</t>
-        </is>
-      </c>
-      <c r="G238" s="4" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>Turfeira de altitude a 1.420 m, perto da rodovia SC-438, na Serra do Rio Rastro (grafia de Behling, 1995; a serra é conhecida como Serra do Rio do Rastro), entre Lauro Müller e Bom Jardim da Serra, SC; 28°23′ S, 49°33′ O segundo o artigo (precisão de minuto, ~2 km)</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I238" s="4" t="inlineStr">
+      <c r="I240" s="4" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J238" s="4" t="inlineStr">
-        <is>
-          <t>Cobertura do perfil não detalhada no resumo; segundo o resumo e Behling et al. (2004), campos até cerca de 1000 anos AP, com primeira expansão da araucária em 2385 ± 225 anos 14C AP</t>
-        </is>
-      </c>
-      <c r="K238" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo do registro nº 255 (Behling, 1995). Segundo o resumo, a dominância de campos continuou até cerca de 1000 anos AP nesta turfeira e no Morro da Igreja. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses: a primeira expansão da floresta de araucária em 3460 ± 195 anos 14C AP (Serra da Boa Vista) e 2385 ± 225 anos 14C AP (Serra do Rio Rastro), e a expansão marcante da araucária sobre os campos em cerca de 1000 anos 14C AP (Morro da Igreja e Serra do Rio Rastro). Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. LOCALIZAÇÃO (2026.10.09): a posição da turfeira dentro da serra não consta no resumo; o ponto do mapa é o da serra (Wikipédia: entre Lauro Müller e Bom Jardim da Serra; ponto mais alto 1.460 m) e é apenas aproximado. NOTA DE FONTE: só o resumo de Behling (1995) foi lido; o texto integral não foi acessado. Número de tombo e depositário não informados.</t>
-        </is>
-      </c>
-      <c r="L238" s="5" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — resumo)
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>Perfil de 223 cm: base datada em 11.210 ± 385 anos 14C AP até o presente (6.410 ± 190 aos 150–155 cm; 2.385 ± 225 aos 74–79 cm); idades não calibradas</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo do registro nº 255. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 50 × 50 m numa pequena depressão rasa junto à escarpa íngreme da Serra Geral, a 1.420 m (400 m abaixo do Morro da Igreja), perto da rodovia SC-438 — o artigo diz «11 km a oeste da vila de Bom Jardim da Serra» e dá 28°23′ S, 49°33′ O. Amostragem em 04/05/1989 e 05/12/1989; perfil de 223 cm (argila sobre rocha abaixo disso); contagem mínima de 1.203 grãos por amostra (média de 5.917). Três datações por 14C: 2.385 ± 225 anos AP (74–79 cm, limite das zonas 2c e 3), 6.410 ± 190 (150–155 cm, perto da base da zona 2ab) e 11.210 ± 385 (215–220 cm, base do perfil); idades não calibradas. O autor nota que 6.410 anos AP é bem mais novo que os ~9.000 esperados no limite Pleistoceno–Holoceno, e explica a diferença por sedimentação extremamente lenta ou por um hiato. RESULTADO: na base (~11.200 anos AP) 93% do pólen é de campos (Poaceae ~55%, Cyperaceae ~15%, Asteraceae ~10%), sem floresta de araucária no local e com a floresta nebular ausente ou pouco representada; no Holoceno inicial e médio os campos seguem dominando (campo sujo mais desenvolvido na zona 2ab), com mudanças na floresta pluvial atlântica (queda de Myrtaceae, alta de Alchornea e Urticales); na zona 3 (7–76 cm) a araucária sobe de 1% a 5% e os campos descem de 89% a 83%, possivelmente com florestas de galeria ao longo dos rios; na zona 4a (0–7 cm) a araucária aumenta fortemente, como no Morro da Igreja. Segundo o resumo do artigo, a dominância dos campos continuou até cerca de 1.000 anos AP nas turfeiras do Morro da Igreja e da Serra do Rio Rastro. O autor aponta uma discrepância ainda não explicada entre a idade do limite 2c/3 aqui (2.385 ± 225) e a do início da zona 3 na Serra da Boa Vista (3.460 ± 195). LOCALIZAÇÃO (2026.10.09): pino movido para as coordenadas impressas no artigo (28°23′ S, 49°33′ O), que na malha deste site caem em Bom Jardim da Serra, a menos de 1 km da divisa com Lauro Müller (por isso o município segue como «região»); antes, o pino era o ponto da serra segundo a Wikipédia, em Lauro Müller. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
+        </is>
+      </c>
+      <c r="L240" s="5" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
 https://www.uni-goettingen.de/de/document/download/7704cdc9d93f4bdd3c6e232529ec697f.pdf/2004_Behling_PPP_CambaradoSul_Brazil.pdf (Behling et al., 2004 — idades de SC citadas)
 https://en.wikipedia.org/wiki/Serra_do_Rio_do_Rastro (localização da serra)</t>
         </is>
       </c>
-      <c r="M238" s="5" t="inlineStr">
+      <c r="M240" s="5" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N240" s="4" t="n">
         <v>256</v>
       </c>
-      <c r="O238" s="4" t="inlineStr">
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Serra do Rio do Rastro (Lauro Müller / Bom Jardim da Serra)</t>
         </is>
       </c>
-      <c r="P238" s="4" t="inlineStr">
+      <c r="P240" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q238" s="4" t="n">
-        <v>-28.4072</v>
-      </c>
-      <c r="R238" s="4" t="n">
-        <v>-49.5461</v>
-      </c>
-      <c r="S238" s="4" t="inlineStr">
+      <c r="Q240" s="4" t="n">
+        <v>-28.3833</v>
+      </c>
+      <c r="R240" s="4" t="n">
+        <v>-49.55</v>
+      </c>
+      <c r="S240" s="4" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="6" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Quaternário (Pleistoceno–Holoceno)</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C241" s="7" t="inlineStr">
+        <is>
+          <t>Pólen e esporos da turfeira da Serra da Boa Vista (campos, floresta pluvial atlântica e floresta de araucária)</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos (pólen e esporos)</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>Turfeira de altitude a 1.160 m, nos contrafortes nordeste da Serra Geral, perto da BR-282 e a 10 km a leste da vila de São Leonardo (Behling, 1995); 27°42′ S, 49°09′ O segundo o artigo (precisão de minuto). O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner (por isso «região»)</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H241" s="7" t="inlineStr">
+        <is>
+          <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="inlineStr">
+        <is>
+          <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
+        </is>
+      </c>
+      <c r="J241" s="6" t="inlineStr">
+        <is>
+          <t>Perfil de 140 cm: base ≈ 13.900–14.100 anos 14C AP (13.905 ± 295 aos 131–135 cm; 14.105 ± 510 aos 61–65 cm), 6.930 ± 195 aos 45–50 cm e 3.460 ± 185 aos 31–35 cm (± 195 no texto); idades não calibradas</t>
+        </is>
+      </c>
+      <c r="K241" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo dos registros nº 255 e 256. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 10–16 × 40 m numa pequena encosta de inclinação leste–oeste relativamente íngreme, atrás de uma escarpa de 3 m, a 1.160 m, nos contrafortes nordeste da Serra Geral, «não longe da BR 282» e a 10 km a leste da vila de São Leonardo; 27°42′ S, 49°09′ O. Amostragem em 03/12/1989; perfil de 140 cm (subsolo rochoso aos 140 cm); contagem mínima de 979 grãos por amostra (média de 3.683). Quatro datações por 14C (Hv 17563–17566): 3.460 ± 185 anos AP (31–35 cm; ± 195 no texto), 6.930 ± 195 (45–50 cm), 14.105 ± 510 (61–65 cm) e 13.905 ± 295 (131–135 cm); idades não calibradas. O autor nota que 6.930 anos AP, no início do Holoceno, é mais novo que o esperado, e explica por sedimentação extremamente lenta ou por um hiato. RESULTADO: a turfeira está na zona de campos. Na base (zona 1a, ~14.000 anos AP) cerca de 90% do pólen é de campos (Poaceae ~60%), com os táxons da floresta de araucária raros — a araucária ficava nos vales — e Myrtaceae dominando a planície costeira; a zona 1c é estimada, por taxa de sedimentação constante, em ~10.000–10.500 anos AP; na zona 2 (6.930 anos AP) há florestação intensa, com Weinmannia paulliniifolia (floresta pluvial atlântica) chegando a 50% do pólen; na zona 3 (a partir de 3.460 anos AP) os campos avançam e Ilex, Symplocos e Clethra, da floresta de araucária, têm a maior representação, o que o autor atribui a clima mais frio; nas zonas 4a e 4b a floresta pluvial atlântica (Alchornea, Urticales) se expande, a araucária fica abaixo de 2% do pólen (contra 10% no Morro da Igreja e na Serra do Rio Rastro) e a 4b (cerca de 100 anos) mostra ação humana (Pinus de plantios modernos, desmatamento de araucária). Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
+        </is>
+      </c>
+      <c r="L241" s="7" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
+https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
+https://www.uni-goettingen.de/de/document/download/7704cdc9d93f4bdd3c6e232529ec697f.pdf/2004_Behling_PPP_CambaradoSul_Brazil.pdf (Behling et al., 2004 — idades de SC citadas)
+https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
+        </is>
+      </c>
+      <c r="M241" s="7" t="inlineStr">
+        <is>
+          <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
+        </is>
+      </c>
+      <c r="N241" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="O241" s="6" t="inlineStr">
+        <is>
+          <t>Serra da Boa Vista (Rancho Queimado / Alfredo Wagner)</t>
+        </is>
+      </c>
+      <c r="P241" s="6" t="inlineStr">
+        <is>
+          <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
+        </is>
+      </c>
+      <c r="Q241" s="6" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="R241" s="6" t="n">
+        <v>-49.15</v>
+      </c>
+      <c r="S241" s="6" t="inlineStr">
+        <is>
+          <t>10.1007/BF00203932</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
         <is>
           <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
         </is>
       </c>
-      <c r="C239" s="7" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
         <is>
           <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
         </is>
       </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E242" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
         <is>
           <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
         </is>
       </c>
-      <c r="G239" s="6" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H239" s="7" t="inlineStr">
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — "Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages", Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I242" s="4" t="inlineStr">
         <is>
           <t>IGc-USP; UFPR</t>
         </is>
       </c>
-      <c r="J239" s="6" t="inlineStr">
+      <c r="J242" s="4" t="inlineStr">
         <is>
           <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
         </is>
       </c>
-      <c r="K239" s="7" t="inlineStr">
+      <c r="K242" s="5" t="inlineStr">
         <is>
           <t>Classificação: gastrópode incrustante. Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
         </is>
       </c>
-      <c r="L239" s="7" t="inlineStr">
+      <c r="L242" s="5" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio075/sitio075.pdf
 https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
         </is>
       </c>
-      <c r="M239" s="7" t="inlineStr">
+      <c r="M242" s="5" t="inlineStr">
         <is>
           <t>ANGULO, R.J.; GIANNINI, P.C.F.; SUGUIO, K. et al. 1999. Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages. Marine Geology, 159, 323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222.</t>
         </is>
       </c>
-      <c r="N239" s="6" t="n">
+      <c r="N242" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="O239" s="6" t="inlineStr">
+      <c r="O242" s="4" t="inlineStr">
         <is>
           <t>Costões Laguna–Imbituba</t>
         </is>
       </c>
-      <c r="P239" s="6" t="inlineStr">
+      <c r="P242" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
         </is>
       </c>
-      <c r="Q239" s="6" t="n">
+      <c r="Q242" s="4" t="n">
         <v>-28.42</v>
       </c>
-      <c r="R239" s="6" t="n">
+      <c r="R242" s="4" t="n">
         <v>-48.74</v>
       </c>
-      <c r="S239" s="6" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+      <c r="S242" s="4" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>Depósitos turfosos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
+      <c r="C243" s="7" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos (54 morfotipos: fungos, algas, briófitas, pteridófitas, pólen de gimnospermas e outros)</t>
         </is>
       </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
+      <c r="F243" s="7" t="inlineStr">
         <is>
           <t>Duas seções com turfa na Planície Costeira sul-catarinense, nos municípios de Santa Rosa do Sul e São João do Sul, SC (nomes das turfeiras e coordenadas não informados no resumo consultado; ponto aproximado, entre os centros dos dois municípios)</t>
         </is>
       </c>
-      <c r="G240" s="4" t="inlineStr">
+      <c r="G243" s="6" t="inlineStr">
         <is>
           <t>Não informado no resumo consultado</t>
         </is>
       </c>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="H243" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Souza, P.A. &amp; Neves, P.C.P. (2012) — "Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil", Acta Botanica Brasilica 26(1):20–37, DOI 10.1590/S0102-33062012000100004</t>
         </is>
       </c>
-      <c r="I240" s="4" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>UFRGS (Porto Alegre) e Universidade Luterana do Brasil (Canoas) — afiliações dos autores</t>
         </is>
       </c>
-      <c r="J240" s="4" t="inlineStr">
+      <c r="J243" s="6" t="inlineStr">
         <is>
           <t>ca. 7.908 anos AP (base do testemunho de Santa Rosa do Sul) até o presente — 0,0079 Ma</t>
         </is>
       </c>
-      <c r="K240" s="5" t="inlineStr">
+      <c r="K243" s="7" t="inlineStr">
         <is>
           <t>Segundo o resumo, o estudo apresenta resultados palinológicos de duas seções com turfa na Planície Costeira sul-catarinense, em Santa Rosa do Sul e São João do Sul; uma amostra basal do testemunho de Santa Rosa do Sul foi datada em 7908 ± 33 anos AP (Holoceno Inferior; o título cita ± 30). Foram descritos e ilustrados 54 palinomorfos: 21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 pólens de gimnospermas e 7 outros (uma cápsula de briófita, 4 fragmentos de invertebrados e 2 palinoforaminíferos indeterminados). Nomes das turfeiras, coordenadas, espessura dos testemunhos e táxons individuais NÃO constam no resumo consultado (o texto integral não foi aberto); por isso o ponto no mapa é aproximado. REGISTRO NOVO (2026.09.14), com fonte própria; não deve ser confundido com o nº 040 (Lagoa do Sombrio), removido em 2026.09.13. VERIFICAÇÃO (2026.10.09): o resumo de Cancelli, Souza &amp; Dehnhardt (XIII ABEQUA) descreve o testemunho de Santa Rosa do Sul como PCSC-1 (29°10'42"S, 49°44'58"W, mata paludial próxima à Lagoa do Sombrio, 570 cm, base datada em 7.908 ± 33 anos cal AP) e informa 112 palinomorfos ao todo — 58 de pólen de angiospermas mais os 54 palinomorfos não-pólen (21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 gimnospermas e 7 outros) que o artigo de 2012 descreve e ilustra. A microfauna do mesmo testemunho está no registro nº 264. O ponto deste registro continua aproximado porque ele cobre também a seção de São João do Sul, cujo local não foi informado.</t>
         </is>
       </c>
-      <c r="L240" s="5" t="inlineStr">
+      <c r="L243" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0102-33062012000100004
 https://paperity.org/p/187352977/fungos-criptogamas-e-outros-palinomorfos-holocenicos-7908-30-anos-ap-atual-da-planicie
 https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
-      <c r="M240" s="5" t="inlineStr">
+      <c r="M243" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; SOUZA, P.A.; NEVES, P.C.P. 2012. Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil. Acta Botanica Brasilica, 26(1), 20–37. DOI: 10.1590/S0102-33062012000100004</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N243" s="6" t="n">
         <v>233</v>
       </c>
-      <c r="O240" s="4" t="inlineStr">
+      <c r="O243" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira sul-catarinense (turfeiras de Santa Rosa do Sul e São João do Sul)</t>
         </is>
       </c>
-      <c r="P240" s="4" t="inlineStr">
+      <c r="P243" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q240" s="4" t="n">
+      <c r="Q243" s="6" t="n">
         <v>-29.1613</v>
       </c>
-      <c r="R240" s="4" t="n">
+      <c r="R243" s="6" t="n">
         <v>-49.7767</v>
       </c>
-      <c r="S240" s="4" t="inlineStr">
+      <c r="S243" s="6" t="inlineStr">
         <is>
           <t>10.1590/S0102-33062012000100004</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="6" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="B244" s="4" t="inlineStr">
         <is>
           <t>Sedimentos holocênicos da Lagoa do Peri (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C241" s="7" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
         <is>
           <t>Diatomáceas holocênicas da Lagoa do Peri (44 táxons; Aulacoseira ambigua, Paralia sulcata)</t>
         </is>
       </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="D244" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — diatomáceas</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E244" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F241" s="7" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
         <is>
           <t>Lagoa do Peri, Florianópolis, SC (27°43′30″S, 48°32′30″W); testemunho coletado com amostrador de Livingstone, da superfície a 2,10 m</t>
         </is>
       </c>
-      <c r="G241" s="6" t="inlineStr">
+      <c r="G244" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H241" s="7" t="inlineStr">
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>Saupe, A.C. &amp; Mosimann, R.M.S. (2003) — "Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil", Insula 32:33 [resumo de uma página]</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I244" s="4" t="inlineStr">
         <is>
           <t>Tecpar (Curitiba) e UFSC (Florianópolis) — afiliações das autoras</t>
         </is>
       </c>
-      <c r="J241" s="6" t="inlineStr">
+      <c r="J244" s="4" t="inlineStr">
         <is>
           <t>Holoceno (o resumo cita o método do 14C, mas não informa idades)</t>
         </is>
       </c>
-      <c r="K241" s="7" t="inlineStr">
+      <c r="K244" s="5" t="inlineStr">
         <is>
           <t>Classificação: microfóssil silicoso (diatomáceas em sedimento holocênico). Saupe &amp; Mosimann (2003) analisaram 26 amostras de um testemunho da Lagoa do Peri, da superfície a 2,10 m, e identificaram 44 táxons específicos e infraespecíficos, de 30 gêneros e 25 famílias; Triceratiaceae e Plagiogrammaceae são as famílias mais bem representadas (três gêneros cada) e Pinnularia, o gênero mais rico (cinco espécies). Aulacoseira ambigua é abundante nas camadas superiores e indica o ambiente atual, de água doce; Paralia sulcata é abundante nas camadas profundas, o que as autoras associam à origem marinha original da lagoa. O resumo não traz a lista completa de espécies, idades, depositário nem número de tombo; a fonte é um resumo de uma página.</t>
         </is>
       </c>
-      <c r="L241" s="7" t="inlineStr">
+      <c r="L244" s="5" t="inlineStr">
         <is>
           <t>https://periodicos.ufsc.br/index.php/insula/article/view/21194 (Saupe &amp; Mosimann, 2003 — resumo)</t>
         </is>
       </c>
-      <c r="M241" s="7" t="inlineStr">
+      <c r="M244" s="5" t="inlineStr">
         <is>
           <t>SAUPE, A.C.; MOSIMANN, R.M.S. 2003. Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil. Insula, 32, 33 [resumo de uma página].</t>
         </is>
       </c>
-      <c r="N241" s="6" t="n">
+      <c r="N244" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="O241" s="6" t="inlineStr">
+      <c r="O244" s="4" t="inlineStr">
         <is>
           <t>Lagoa do Peri (Florianópolis)</t>
         </is>
       </c>
-      <c r="P241" s="6" t="inlineStr">
+      <c r="P244" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q241" s="6" t="n">
+      <c r="Q244" s="4" t="n">
         <v>-27.725</v>
       </c>
-      <c r="R241" s="6" t="n">
+      <c r="R244" s="4" t="n">
         <v>-48.5417</v>
       </c>
-      <c r="S241" s="6" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
+      <c r="S244" s="4" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B245" s="6" t="inlineStr">
         <is>
           <t>Sedimentos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
+      <c r="C245" s="7" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos de Garopaba (84 táxons: pólen, esporos, fungos, algas, acritarcos, cistos de dinoflagelados)</t>
         </is>
       </c>
-      <c r="D242" s="4" t="inlineStr">
+      <c r="D245" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
+      <c r="E245" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
+      <c r="F245" s="7" t="inlineStr">
         <is>
           <t>Planície Costeira de Santa Catarina, município de Garopaba, SC — testemunho PCSC-3 (450 cm), a cerca de 2 km do oceano (coordenadas do testemunho não informadas; ponto aproximado no centro do município)</t>
         </is>
       </c>
-      <c r="G242" s="4" t="inlineStr">
+      <c r="G245" s="6" t="inlineStr">
         <is>
           <t>Não informado nos resumos consultados</t>
         </is>
       </c>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="H245" s="7" t="inlineStr">
         <is>
           <t>Kuhn, L.A., Souza, P.A., Cancelli, R.R., Silva, W.G. &amp; Macedo, R.B. (2017) — "Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State", Anais da Academia Brasileira de Ciências 89(4):2581–2595, DOI 10.1590/0001-3765201720160895; Kuhn, L.A. (2017) — "Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil)", Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul</t>
         </is>
       </c>
-      <c r="I242" s="4" t="inlineStr">
+      <c r="I245" s="6" t="inlineStr">
         <is>
           <t>UFRGS (Instituto de Geociências)</t>
         </is>
       </c>
-      <c r="J242" s="4" t="inlineStr">
+      <c r="J245" s="6" t="inlineStr">
         <is>
           <t>ca. 5.390 anos cal AP (base) até o presente — Holoceno Médio a Superior</t>
         </is>
       </c>
-      <c r="K242" s="5" t="inlineStr">
+      <c r="K245" s="7" t="inlineStr">
         <is>
           <t>Classificação: microfósseis orgânicos (palinomorfos) de um testemunho holocênico. Foram analisadas 46 amostras do testemunho PCSC-3 (450 cm), com três datações por radiocarbono (5.390 anos cal AP aos 430 cm; 3.756 aos 360 cm; 858 aos 80 cm), e reconhecidos 84 táxons: pólen de angiospermas e de gimnospermas, esporos de pteridófitas e de briófitas, esporos de fungos, algas, três acritarcos (descritos e ilustrados na dissertação), dois cistos de dinoflagelados e forros de microforaminíferos. Entre os táxons citados no artigo estão Ilex, Myrtaceae, Arecaceae, Araucaria angustifolia, Alnus, Botryococcus, Micrhystridium, Operculodinium e Spiniferites. A análise de agrupamento definiu três fases: I, laguna com influência marinha (desde ~5.390 anos cal AP); II, ainda lagunar, com menos influência marinha e mais algas de água doce (~3.032 a 858 anos cal AP); III, sedimentação subaquosa em condições de pântano (últimos ~856 anos). Número de tombo e depositário não constam nos resumos consultados; as contagens por grupo diferem entre o resumo da dissertação e o do artigo, e por isso só o total de 84 táxons é dado aqui.</t>
         </is>
       </c>
-      <c r="L242" s="5" t="inlineStr">
+      <c r="L245" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/0001-3765201720160895
 https://www.redalyc.org/pdf/327/32754216004.pdf (Kuhn et al., 2017)
 https://lume.ufrgs.br/handle/10183/153388 (dissertação de Kuhn, 2017)</t>
         </is>
       </c>
-      <c r="M242" s="5" t="inlineStr">
+      <c r="M245" s="7" t="inlineStr">
         <is>
           <t>KUHN, L.A.; SOUZA, P.A.; CANCELLI, R.R. et al. 2017. Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State. Anais da Academia Brasileira de Ciências, 89(4), 2581–2595. DOI: 10.1590/0001-3765201720160895 | KUHN, L.A. 2017. Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil). Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul.</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N245" s="6" t="n">
         <v>237</v>
       </c>
-      <c r="O242" s="4" t="inlineStr">
+      <c r="O245" s="6" t="inlineStr">
         <is>
           <t>Garopaba (testemunho PCSC-3)</t>
         </is>
       </c>
-      <c r="P242" s="4" t="inlineStr">
+      <c r="P245" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q242" s="4" t="n">
+      <c r="Q245" s="6" t="n">
         <v>-28.0276</v>
       </c>
-      <c r="R242" s="4" t="n">
+      <c r="R245" s="6" t="n">
         <v>-48.6195</v>
       </c>
-      <c r="S242" s="4" t="inlineStr">
+      <c r="S245" s="6" t="inlineStr">
         <is>
           <t>10.1590/0001-3765201720160895</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="6" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B246" s="4" t="inlineStr">
         <is>
           <t>Sedimentos holocênicos da Planície Costeira sul-catarinense (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C243" s="7" t="inlineStr">
+      <c r="C246" s="5" t="inlineStr">
         <is>
           <t>Diatomáceas holocênicas da Lagoa do Sombrio (Paralia sulcata, Navicula schadei, Staurosira construens, Cyclotella baltica)</t>
         </is>
       </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — diatomáceas</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F243" s="7" t="inlineStr">
+      <c r="F246" s="5" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio, Planície Costeira do sul de Santa Catarina — testemunho de 570 cm (município e coordenadas não informados no resumo; ponto aproximado na sede de Sombrio)</t>
         </is>
       </c>
-      <c r="G243" s="6" t="inlineStr">
+      <c r="G246" s="4" t="inlineStr">
         <is>
           <t>Não informado no resumo consultado</t>
         </is>
       </c>
-      <c r="H243" s="7" t="inlineStr">
+      <c r="H246" s="5" t="inlineStr">
         <is>
           <t>Santos, S.M. &amp; Souza, P.A. (2016) — "Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas", XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo]</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I246" s="4" t="inlineStr">
         <is>
           <t>UFRGS (Porto Alegre)</t>
         </is>
       </c>
-      <c r="J243" s="6" t="inlineStr">
+      <c r="J246" s="4" t="inlineStr">
         <is>
           <t>ca. 7.900 a 2.500 anos AP (segundo o resumo; resultados parciais)</t>
         </is>
       </c>
-      <c r="K243" s="7" t="inlineStr">
+      <c r="K246" s="5" t="inlineStr">
         <is>
           <t>Classificação: microfóssil silicoso (diatomáceas) de sedimento holocênico. O resumo trata de resultados parciais de um testemunho de 570 cm, do qual foram estudadas 12 amostras (50 a 570 cm): 14 ordens, 45 gêneros e 37 espécies, além de oito táxons determinados só até gênero. Na base (500–400 cm) há apenas espécies marinhas, com predomínio de Paralia sulcata, registrada em todas as amostras; na porção intermediária (350–300 cm), um pântano de água doce, com espécies bentônicas (Navicula schadei, Staurosira construens) e uma planctônica marinha (Cyclotella baltica); no topo (250–50 cm) não se encontraram frústulas, o que os autores atribuem à transformação do ambiente em continental, à dissolução tafonômica ou à falta de nutrientes. Idades citadas: ~7.900–3.800 anos AP, influência marinha; ~3.800–2.500, pântano de água doce. Os níveis de 550 e 570 cm ainda não haviam sido analisados. Número de tombo e depositário não informados. É um resumo de iniciação científica, sem revisão de periódico. VERIFICAÇÃO (2026.10.09): o resumo do Salão de Iniciação Científica de 2015 (Santos &amp; Souza, mesma pesquisa) chama o testemunho de PCSC-01, com 570 cm, na Lagoa do Sombrio, município de Santa Rosa do Sul, e diz que naquela etapa as 12 amostras (espaçadas de 50 cm) ainda aguardavam identificação das espécies. A profundidade (570 cm) e a área coincidem com o testemunho PCSC-1 dos registros nº 233 e nº 264 (Cancelli et al.), mas nenhuma das fontes consultadas declara que se trata do mesmo testemunho; por isso a equivalência não é afirmada.</t>
         </is>
       </c>
-      <c r="L243" s="7" t="inlineStr">
+      <c r="L246" s="5" t="inlineStr">
         <is>
           <t>https://lume.ufrgs.br/bitstream/10183/154894/1/Resumo_48227.pdf (resumo do XXVIII Salão de Iniciação Científica da UFRGS, 2016)
 https://lume.ufrgs.br/bitstream/10183/137304/1/Resumo_42627.pdf (Santos &amp; Souza — resumo do XXVII Salão de Iniciação Científica da UFRGS, 2015)</t>
         </is>
       </c>
-      <c r="M243" s="7" t="inlineStr">
+      <c r="M246" s="5" t="inlineStr">
         <is>
           <t>SANTOS, S.M.; SOUZA, P.A. 2016. Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas. XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo].</t>
         </is>
       </c>
-      <c r="N243" s="6" t="n">
+      <c r="N246" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="O243" s="6" t="inlineStr">
+      <c r="O246" s="4" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio</t>
         </is>
       </c>
-      <c r="P243" s="6" t="inlineStr">
+      <c r="P246" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q243" s="6" t="n">
+      <c r="Q246" s="4" t="n">
         <v>-29.1078</v>
       </c>
-      <c r="R243" s="6" t="n">
+      <c r="R246" s="4" t="n">
         <v>-49.6325</v>
       </c>
-      <c r="S243" s="6" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
+      <c r="S246" s="4" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B244" s="4" t="inlineStr">
+      <c r="B247" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
+      <c r="C247" s="7" t="inlineStr">
         <is>
           <t>Diatomáceas, pólen e esporos holocênicos de lagunas de Jaguaruna</t>
         </is>
       </c>
-      <c r="D244" s="4" t="inlineStr">
+      <c r="D247" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — diatomáceas e palinomorfos</t>
         </is>
       </c>
-      <c r="E244" s="4" t="inlineStr">
+      <c r="E247" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
+      <c r="F247" s="7" t="inlineStr">
         <is>
           <t>Região de Jaguaruna, costa centro-sul de Santa Catarina — três testemunhos rasos, de até 2,5 m (localidades e coordenadas não informadas no resumo; ponto aproximado na sede de Jaguaruna)</t>
         </is>
       </c>
-      <c r="G244" s="4" t="inlineStr">
+      <c r="G247" s="6" t="inlineStr">
         <is>
           <t>Não informado no resumo consultado</t>
         </is>
       </c>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="H247" s="7" t="inlineStr">
         <is>
           <t>Amaral, P.G.C. (2008) — "Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada", Tese de Doutorado, Universidade de São Paulo</t>
         </is>
       </c>
-      <c r="I244" s="4" t="inlineStr">
+      <c r="I247" s="6" t="inlineStr">
         <is>
           <t>Universidade de São Paulo</t>
         </is>
       </c>
-      <c r="J244" s="4" t="inlineStr">
+      <c r="J247" s="6" t="inlineStr">
         <is>
           <t>ca. 5.000 a 2.370 anos cal AP (fase lagunar até a última desconexão com o mar)</t>
         </is>
       </c>
-      <c r="K244" s="5" t="inlineStr">
+      <c r="K247" s="7" t="inlineStr">
         <is>
           <t>Classificação: microfósseis (diatomáceas e palinomorfos) de sedimentos lagunares holocênicos. A tese combina dados sedimentológicos, de diatomáceas, de pólen e esporos e geoquímicos (C, N, δ13C, δ15N) de três testemunhos rasos (até 2,5 m). Segundo o resumo, o local era um sistema de lagunas interligadas, com conexão marinha evidenciada por diatomáceas marinhas e pelo sinal da matéria orgânica; a laguna perdeu a conexão com o mar em momentos diferentes em cada testemunho, a última por volta de 2.740–2.370 anos cal AP; as mudanças nas diatomáceas sugerem ao menos duas grandes variações de salinidade, que a autora liga a mudanças de precipitação, e o pólen mostra vegetação estável desde pelo menos 4.000 anos cal AP. A fase lagunar vem de cerca de 5.000 anos cal AP. O resumo consultado não nomeia espécies. CONTEXTO: Amaral et al. (2012, Journal of Quaternary Science 27(2):181–191, DOI 10.1002/jqs.1531) tem título que trata do sistema lagunar da região de Jaguaruna; a página do artigo não pôde ser lida (acesso limitado) e o seu conteúdo não foi usado aqui. Número de tombo e depositário não informados.</t>
         </is>
       </c>
-      <c r="L244" s="5" t="inlineStr">
+      <c r="L247" s="7" t="inlineStr">
         <is>
           <t>https://teses.usp.br/teses/disponiveis/44/44141/tde-19122008-160829/en.php (resumo da tese de Amaral, 2008)</t>
         </is>
       </c>
-      <c r="M244" s="5" t="inlineStr">
+      <c r="M247" s="7" t="inlineStr">
         <is>
           <t>AMARAL, P.G.C. 2008. Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada. Tese de Doutorado, Universidade de São Paulo.</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N247" s="6" t="n">
         <v>239</v>
       </c>
-      <c r="O244" s="4" t="inlineStr">
+      <c r="O247" s="6" t="inlineStr">
         <is>
           <t>Região de Jaguaruna (lagunas holocênicas)</t>
         </is>
       </c>
-      <c r="P244" s="4" t="inlineStr">
+      <c r="P247" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q244" s="4" t="n">
+      <c r="Q247" s="6" t="n">
         <v>-28.6148</v>
       </c>
-      <c r="R244" s="4" t="n">
+      <c r="R247" s="6" t="n">
         <v>-49.0286</v>
       </c>
-      <c r="S244" s="4" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="6" t="inlineStr">
+      <c r="S247" s="6" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="B248" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C245" s="7" t="inlineStr">
+      <c r="C248" s="5" t="inlineStr">
         <is>
           <t>Bulla striata</t>
         </is>
       </c>
-      <c r="D245" s="6" t="inlineStr">
+      <c r="D248" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E248" s="4" t="inlineStr">
         <is>
           <t>UFSC 418</t>
         </is>
       </c>
-      <c r="F245" s="7" t="inlineStr">
+      <c r="F248" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G245" s="6" t="inlineStr">
+      <c r="G248" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H245" s="7" t="inlineStr">
+      <c r="H248" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I245" s="6" t="inlineStr">
+      <c r="I248" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J245" s="6" t="inlineStr">
+      <c r="J248" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K245" s="7" t="inlineStr">
+      <c r="K248" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 418, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L245" s="7" t="inlineStr">
+      <c r="L248" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M245" s="7" t="inlineStr">
+      <c r="M248" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N245" s="6" t="n">
+      <c r="N248" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="O245" s="6" t="inlineStr">
+      <c r="O248" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P245" s="6" t="inlineStr">
+      <c r="P248" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q245" s="6" t="n">
+      <c r="Q248" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R245" s="6" t="n">
+      <c r="R248" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S245" s="6" t="inlineStr">
+      <c r="S248" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="4" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B249" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C246" s="5" t="inlineStr">
+      <c r="C249" s="7" t="inlineStr">
         <is>
           <t>Bostrycapulus odites</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="D249" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
+      <c r="E249" s="6" t="inlineStr">
         <is>
           <t>UFSC 421</t>
         </is>
       </c>
-      <c r="F246" s="5" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G246" s="4" t="inlineStr">
+      <c r="G249" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H246" s="5" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I246" s="4" t="inlineStr">
+      <c r="I249" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J246" s="4" t="inlineStr">
+      <c r="J249" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K246" s="5" t="inlineStr">
+      <c r="K249" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 421, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L246" s="5" t="inlineStr">
+      <c r="L249" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M246" s="5" t="inlineStr">
+      <c r="M249" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N249" s="6" t="n">
         <v>241</v>
       </c>
-      <c r="O246" s="4" t="inlineStr">
+      <c r="O249" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P246" s="4" t="inlineStr">
+      <c r="P249" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q246" s="4" t="n">
+      <c r="Q249" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R246" s="4" t="n">
+      <c r="R249" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S246" s="4" t="inlineStr">
+      <c r="S249" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="6" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B247" s="6" t="inlineStr">
+      <c r="B250" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C247" s="7" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
         <is>
           <t>Cerithium atratum</t>
         </is>
       </c>
-      <c r="D247" s="6" t="inlineStr">
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E250" s="4" t="inlineStr">
         <is>
           <t>UFSC 410</t>
         </is>
       </c>
-      <c r="F247" s="7" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G247" s="6" t="inlineStr">
+      <c r="G250" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H247" s="7" t="inlineStr">
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I247" s="6" t="inlineStr">
+      <c r="I250" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J247" s="6" t="inlineStr">
+      <c r="J250" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K247" s="7" t="inlineStr">
+      <c r="K250" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 410, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L247" s="7" t="inlineStr">
+      <c r="L250" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M247" s="7" t="inlineStr">
+      <c r="M250" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N247" s="6" t="n">
+      <c r="N250" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="O247" s="6" t="inlineStr">
+      <c r="O250" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P247" s="6" t="inlineStr">
+      <c r="P250" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q247" s="6" t="n">
+      <c r="Q250" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R247" s="6" t="n">
+      <c r="R250" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S247" s="6" t="inlineStr">
+      <c r="S250" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="4" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B248" s="4" t="inlineStr">
+      <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C248" s="5" t="inlineStr">
+      <c r="C251" s="7" t="inlineStr">
         <is>
           <t>Chichoreus senegalensis</t>
         </is>
       </c>
-      <c r="D248" s="4" t="inlineStr">
+      <c r="D251" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
+      <c r="E251" s="6" t="inlineStr">
         <is>
           <t>UFSC 424 (exemplar fragmentado)</t>
         </is>
       </c>
-      <c r="F248" s="5" t="inlineStr">
+      <c r="F251" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G248" s="4" t="inlineStr">
+      <c r="G251" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H248" s="5" t="inlineStr">
+      <c r="H251" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I248" s="4" t="inlineStr">
+      <c r="I251" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J248" s="4" t="inlineStr">
+      <c r="J251" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K248" s="5" t="inlineStr">
+      <c r="K251" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 424 (exemplar fragmentado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L248" s="5" t="inlineStr">
+      <c r="L251" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M248" s="5" t="inlineStr">
+      <c r="M251" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N251" s="6" t="n">
         <v>243</v>
       </c>
-      <c r="O248" s="4" t="inlineStr">
+      <c r="O251" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P248" s="4" t="inlineStr">
+      <c r="P251" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q248" s="4" t="n">
+      <c r="Q251" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R248" s="4" t="n">
+      <c r="R251" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S248" s="4" t="inlineStr">
+      <c r="S251" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="6" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="B252" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C249" s="7" t="inlineStr">
+      <c r="C252" s="5" t="inlineStr">
         <is>
           <t>Nassarius vibex</t>
         </is>
       </c>
-      <c r="D249" s="6" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E252" s="4" t="inlineStr">
         <is>
           <t>UFSC 416</t>
         </is>
       </c>
-      <c r="F249" s="7" t="inlineStr">
+      <c r="F252" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G249" s="6" t="inlineStr">
+      <c r="G252" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H249" s="7" t="inlineStr">
+      <c r="H252" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I249" s="6" t="inlineStr">
+      <c r="I252" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J249" s="6" t="inlineStr">
+      <c r="J252" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K249" s="7" t="inlineStr">
+      <c r="K252" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 416, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L249" s="7" t="inlineStr">
+      <c r="L252" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M249" s="7" t="inlineStr">
+      <c r="M252" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N249" s="6" t="n">
+      <c r="N252" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="O249" s="6" t="inlineStr">
+      <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P249" s="6" t="inlineStr">
+      <c r="P252" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q249" s="6" t="n">
+      <c r="Q252" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R249" s="6" t="n">
+      <c r="R252" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S249" s="6" t="inlineStr">
+      <c r="S252" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="4" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B250" s="4" t="inlineStr">
+      <c r="B253" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
+      <c r="C253" s="7" t="inlineStr">
         <is>
           <t>Trachycardium muricatum</t>
         </is>
       </c>
-      <c r="D250" s="4" t="inlineStr">
+      <c r="D253" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E250" s="4" t="inlineStr">
+      <c r="E253" s="6" t="inlineStr">
         <is>
           <t>UFSC 427</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
+      <c r="F253" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G250" s="4" t="inlineStr">
+      <c r="G253" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="H253" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I250" s="4" t="inlineStr">
+      <c r="I253" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J250" s="4" t="inlineStr">
+      <c r="J253" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K250" s="5" t="inlineStr">
+      <c r="K253" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 427, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L250" s="5" t="inlineStr">
+      <c r="L253" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M250" s="5" t="inlineStr">
+      <c r="M253" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N253" s="6" t="n">
         <v>245</v>
       </c>
-      <c r="O250" s="4" t="inlineStr">
+      <c r="O253" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P250" s="4" t="inlineStr">
+      <c r="P253" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q250" s="4" t="n">
+      <c r="Q253" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R250" s="4" t="n">
+      <c r="R253" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S250" s="4" t="inlineStr">
+      <c r="S253" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C251" s="7" t="inlineStr">
+      <c r="C254" s="5" t="inlineStr">
         <is>
           <t>Corbula caribaea</t>
         </is>
       </c>
-      <c r="D251" s="6" t="inlineStr">
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E254" s="4" t="inlineStr">
         <is>
           <t>UFSC 422</t>
         </is>
       </c>
-      <c r="F251" s="7" t="inlineStr">
+      <c r="F254" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G251" s="6" t="inlineStr">
+      <c r="G254" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H251" s="7" t="inlineStr">
+      <c r="H254" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I251" s="6" t="inlineStr">
+      <c r="I254" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J251" s="6" t="inlineStr">
+      <c r="J254" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K251" s="7" t="inlineStr">
+      <c r="K254" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 422, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L251" s="7" t="inlineStr">
+      <c r="L254" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M251" s="7" t="inlineStr">
+      <c r="M254" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N251" s="6" t="n">
+      <c r="N254" s="4" t="n">
         <v>246</v>
       </c>
-      <c r="O251" s="6" t="inlineStr">
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P251" s="6" t="inlineStr">
+      <c r="P254" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q251" s="6" t="n">
+      <c r="Q254" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R251" s="6" t="n">
+      <c r="R254" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S251" s="6" t="inlineStr">
+      <c r="S254" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B255" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C252" s="5" t="inlineStr">
+      <c r="C255" s="7" t="inlineStr">
         <is>
           <t>Iphigenia brasiliensis</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D255" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
+      <c r="E255" s="6" t="inlineStr">
         <is>
           <t>UFSC 428</t>
         </is>
       </c>
-      <c r="F252" s="5" t="inlineStr">
+      <c r="F255" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr">
+      <c r="G255" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H252" s="5" t="inlineStr">
+      <c r="H255" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I252" s="4" t="inlineStr">
+      <c r="I255" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J252" s="4" t="inlineStr">
+      <c r="J255" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K252" s="5" t="inlineStr">
+      <c r="K255" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 428, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L252" s="5" t="inlineStr">
+      <c r="L255" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M252" s="5" t="inlineStr">
+      <c r="M255" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N255" s="6" t="n">
         <v>247</v>
       </c>
-      <c r="O252" s="4" t="inlineStr">
+      <c r="O255" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P252" s="4" t="inlineStr">
+      <c r="P255" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q252" s="4" t="n">
+      <c r="Q255" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R252" s="4" t="n">
+      <c r="R255" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S252" s="4" t="inlineStr">
+      <c r="S255" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="6" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C253" s="7" t="inlineStr">
+      <c r="C256" s="5" t="inlineStr">
         <is>
           <t>Lucina pectinata</t>
         </is>
       </c>
-      <c r="D253" s="6" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
         <is>
           <t>UFSC 402 (articulado); UFSC 430 (valva esquerda)</t>
         </is>
       </c>
-      <c r="F253" s="7" t="inlineStr">
+      <c r="F256" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G253" s="6" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H253" s="7" t="inlineStr">
+      <c r="H256" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I253" s="6" t="inlineStr">
+      <c r="I256" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J253" s="6" t="inlineStr">
+      <c r="J256" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K253" s="7" t="inlineStr">
+      <c r="K256" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.260 ± 30 anos AP (calibrada 5.620–5.440); UFSC 430 é uma valva esquerda fragmentada. Número de tombo: UFSC 402 (articulado); UFSC 430 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L253" s="7" t="inlineStr">
+      <c r="L256" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M253" s="7" t="inlineStr">
+      <c r="M256" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N253" s="6" t="n">
+      <c r="N256" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="O253" s="6" t="inlineStr">
+      <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P253" s="6" t="inlineStr">
+      <c r="P256" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q253" s="6" t="n">
+      <c r="Q256" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R253" s="6" t="n">
+      <c r="R256" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S253" s="6" t="inlineStr">
+      <c r="S256" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B257" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C254" s="5" t="inlineStr">
+      <c r="C257" s="7" t="inlineStr">
         <is>
           <t>Ostrea equestris</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D257" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
+      <c r="E257" s="6" t="inlineStr">
         <is>
           <t>UFSC 395; UFSC 433 (valva direita)</t>
         </is>
       </c>
-      <c r="F254" s="5" t="inlineStr">
+      <c r="F257" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G254" s="4" t="inlineStr">
+      <c r="G257" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H254" s="5" t="inlineStr">
+      <c r="H257" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I254" s="4" t="inlineStr">
+      <c r="I257" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J254" s="4" t="inlineStr">
+      <c r="J257" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K254" s="5" t="inlineStr">
+      <c r="K257" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada, mas fora de posição de vida (distribuição aleatória quanto ao plano de acamamento), e foi datada em 5.410 ± 30 anos AP (calibrada 5.805–5.580); UFSC 433 é uma valva direita com bioerosão e fragmentação. Número de tombo: UFSC 395; UFSC 433 (valva direita), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L254" s="5" t="inlineStr">
+      <c r="L257" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M254" s="5" t="inlineStr">
+      <c r="M257" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N257" s="6" t="n">
         <v>249</v>
       </c>
-      <c r="O254" s="4" t="inlineStr">
+      <c r="O257" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P254" s="4" t="inlineStr">
+      <c r="P257" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q254" s="4" t="n">
+      <c r="Q257" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R254" s="4" t="n">
+      <c r="R257" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S254" s="4" t="inlineStr">
+      <c r="S257" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="6" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B255" s="6" t="inlineStr">
+      <c r="B258" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C255" s="7" t="inlineStr">
+      <c r="C258" s="5" t="inlineStr">
         <is>
           <t>Strigilla pisiformis</t>
         </is>
       </c>
-      <c r="D255" s="6" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="E258" s="4" t="inlineStr">
         <is>
           <t>UFSC 425</t>
         </is>
       </c>
-      <c r="F255" s="7" t="inlineStr">
+      <c r="F258" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G255" s="6" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H255" s="7" t="inlineStr">
+      <c r="H258" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I255" s="6" t="inlineStr">
+      <c r="I258" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J255" s="6" t="inlineStr">
+      <c r="J258" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K255" s="7" t="inlineStr">
+      <c r="K258" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 425, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L255" s="7" t="inlineStr">
+      <c r="L258" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M255" s="7" t="inlineStr">
+      <c r="M258" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N255" s="6" t="n">
+      <c r="N258" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="O255" s="6" t="inlineStr">
+      <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P255" s="6" t="inlineStr">
+      <c r="P258" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q255" s="6" t="n">
+      <c r="Q258" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R255" s="6" t="n">
+      <c r="R258" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S255" s="6" t="inlineStr">
+      <c r="S258" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="4" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="B259" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C256" s="5" t="inlineStr">
+      <c r="C259" s="7" t="inlineStr">
         <is>
           <t>Tagelus plebeius</t>
         </is>
       </c>
-      <c r="D256" s="4" t="inlineStr">
+      <c r="D259" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
+      <c r="E259" s="6" t="inlineStr">
         <is>
           <t>UFSC 429 (articulado)</t>
         </is>
       </c>
-      <c r="F256" s="5" t="inlineStr">
+      <c r="F259" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G256" s="4" t="inlineStr">
+      <c r="G259" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H256" s="5" t="inlineStr">
+      <c r="H259" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I256" s="4" t="inlineStr">
+      <c r="I259" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J256" s="4" t="inlineStr">
+      <c r="J259" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K256" s="5" t="inlineStr">
+      <c r="K259" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.620 ± 30 anos AP (calibrada 6.000–5.840). Número de tombo: UFSC 429 (articulado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L256" s="5" t="inlineStr">
+      <c r="L259" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M256" s="5" t="inlineStr">
+      <c r="M259" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N259" s="6" t="n">
         <v>251</v>
       </c>
-      <c r="O256" s="4" t="inlineStr">
+      <c r="O259" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P256" s="4" t="inlineStr">
+      <c r="P259" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q256" s="4" t="n">
+      <c r="Q259" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R256" s="4" t="n">
+      <c r="R259" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S256" s="4" t="inlineStr">
+      <c r="S259" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="6" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B257" s="6" t="inlineStr">
+      <c r="B260" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C257" s="7" t="inlineStr">
+      <c r="C260" s="5" t="inlineStr">
         <is>
           <t>Anomalocardia brasiliana</t>
         </is>
       </c>
-      <c r="D257" s="6" t="inlineStr">
+      <c r="D260" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="E260" s="4" t="inlineStr">
         <is>
           <t>UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda)</t>
         </is>
       </c>
-      <c r="F257" s="7" t="inlineStr">
+      <c r="F260" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G257" s="6" t="inlineStr">
+      <c r="G260" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H257" s="7" t="inlineStr">
+      <c r="H260" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I257" s="6" t="inlineStr">
+      <c r="I260" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J257" s="6" t="inlineStr">
+      <c r="J260" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K257" s="7" t="inlineStr">
+      <c r="K260" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. É a espécie mais bem representada, com cerca de 90% do volume total dos fósseis; ocorre articulada e em posição de vida, e as valvas isoladas (UFSC 431 e 432) mostram desgaste, fragmentação e bioerosão. Não foi datada individualmente. Número de tombo: UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L257" s="7" t="inlineStr">
+      <c r="L260" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M257" s="7" t="inlineStr">
+      <c r="M260" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N257" s="6" t="n">
+      <c r="N260" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="O257" s="6" t="inlineStr">
+      <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P257" s="6" t="inlineStr">
+      <c r="P260" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q257" s="6" t="n">
+      <c r="Q260" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R257" s="6" t="n">
+      <c r="R260" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S257" s="6" t="inlineStr">
+      <c r="S260" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="4" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B258" s="4" t="inlineStr">
+      <c r="B261" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C258" s="5" t="inlineStr">
+      <c r="C261" s="7" t="inlineStr">
         <is>
           <t>Chione pubera</t>
         </is>
       </c>
-      <c r="D258" s="4" t="inlineStr">
+      <c r="D261" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
+      <c r="E261" s="6" t="inlineStr">
         <is>
           <t>UFSC 423</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
+      <c r="F261" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="G261" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H258" s="5" t="inlineStr">
+      <c r="H261" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I258" s="4" t="inlineStr">
+      <c r="I261" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J258" s="4" t="inlineStr">
+      <c r="J261" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K258" s="5" t="inlineStr">
+      <c r="K261" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 423, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L258" s="5" t="inlineStr">
+      <c r="L261" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M258" s="5" t="inlineStr">
+      <c r="M261" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N261" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="O258" s="4" t="inlineStr">
+      <c r="O261" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P258" s="4" t="inlineStr">
+      <c r="P261" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q258" s="4" t="n">
+      <c r="Q261" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R258" s="4" t="n">
+      <c r="R261" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S258" s="4" t="inlineStr">
+      <c r="S261" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="6" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B259" s="6" t="inlineStr">
+      <c r="B262" s="4" t="inlineStr">
         <is>
           <t>Sedimentos turfosos holocênicos (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C259" s="7" t="inlineStr">
+      <c r="C262" s="5" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos de turfeira dos Campos do Quiriri (47 palinomorfos)</t>
         </is>
       </c>
-      <c r="D259" s="6" t="inlineStr">
+      <c r="D262" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E262" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F259" s="7" t="inlineStr">
+      <c r="F262" s="5" t="inlineStr">
         <is>
           <t>Turfeira dos Campos do Quiriri, no Planalto de São Bento do Sul, SC; testemunho de até 175 cm. O resumo não informa município, coordenadas nem altitude; ponto aproximado em São Bento do Sul, município que dá nome ao planalto</t>
         </is>
       </c>
-      <c r="G259" s="6" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H259" s="7" t="inlineStr">
+      <c r="H262" s="5" t="inlineStr">
         <is>
           <t>Lima, G.L., Bauermann, S.G. &amp; Oliveira, M.A.T. (2011) — "Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil", Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011)</t>
         </is>
       </c>
-      <c r="I259" s="6" t="inlineStr">
+      <c r="I262" s="4" t="inlineStr">
         <is>
           <t>UFFS (Chapecó, SC) / ULBRA (Canoas, RS) / UFSC (Florianópolis, SC)</t>
         </is>
       </c>
-      <c r="J259" s="6" t="inlineStr">
+      <c r="J262" s="4" t="inlineStr">
         <is>
           <t>Holoceno — base do testemunho em ~6,2 ka AP (6.220 ± 30 anos AP, segundo o resumo)</t>
         </is>
       </c>
-      <c r="K259" s="7" t="inlineStr">
+      <c r="K262" s="5" t="inlineStr">
         <is>
           <t>Classificação: microfósseis (pólen e esporos) de turfeira — registro paleoambiental holocênico. Segundo o resumo, foram identificados 47 palinomorfos, agrupados por afinidade ecológica: elementos campestres (Poaceae, Asteraceae, Cyperaceae, Apiaceae, Xyris), elementos florestais (Myrsine, Myrtaceae, Alchornea, Weinmannia, Ilex, Mimosa scabrella e, em um único grão, Araucaria angustifolia), pteridófitas (Blechnum, Cyatheaceae, Marattia, Dicksonia sellowiana) e Sphagnum. Uma amostra da base do testemunho foi enviada à Universidade da Geórgia (EUA) para datação por radiocarbono. NOTA DE FONTE (2026.10.09): o PDF do resumo não traz o ano; 2011 é o ano do XIII Congresso da ABEQUA e III Encontro do Quaternário Sul-Americano (Armação dos Búzios, RJ, 8–13/10/2011, segundo o calendário da PAGES). Município e coordenadas da turfeira não constam: o resumo diz apenas «Planalto de São Bento do Sul». Tombo e depositário não informados.</t>
         </is>
       </c>
-      <c r="L259" s="7" t="inlineStr">
+      <c r="L262" s="5" t="inlineStr">
         <is>
           <t>https://www.abequa.org.br/anais/ABEQUA_GISELE_LIMA.pdf (resumo — Lima, Bauermann &amp; Oliveira)
 https://pastglobalchanges.org/calendar/127-pages/1056%E2%88%92xiii-congress-of-abequa-and-iii-south-america-quaternary-meeting (data e local do XIII Congresso da ABEQUA)</t>
         </is>
       </c>
-      <c r="M259" s="7" t="inlineStr">
+      <c r="M262" s="5" t="inlineStr">
         <is>
           <t>LIMA, G.L.; BAUERMANN, S.G.; OLIVEIRA, M.A.T. 2011. Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil. Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011).</t>
         </is>
       </c>
-      <c r="N259" s="6" t="n">
+      <c r="N262" s="4" t="n">
         <v>257</v>
       </c>
-      <c r="O259" s="6" t="inlineStr">
+      <c r="O262" s="4" t="inlineStr">
         <is>
           <t>Campos do Quiriri (Planalto de São Bento do Sul)</t>
         </is>
       </c>
-      <c r="P259" s="6" t="inlineStr">
+      <c r="P262" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q259" s="6" t="n">
+      <c r="Q262" s="4" t="n">
         <v>-26.2503</v>
       </c>
-      <c r="R259" s="6" t="n">
+      <c r="R262" s="4" t="n">
         <v>-49.3792</v>
       </c>
-      <c r="S259" s="6" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+      <c r="S262" s="4" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>Depósitos paludais/lagunares holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
+      <c r="C263" s="7" t="inlineStr">
         <is>
           <t>Microfauna holocênica do testemunho PCSC-1 (15 táxons: 5 bivalves, 8 gastrópodes, 1 foraminífero e 1 ostracode)</t>
         </is>
       </c>
-      <c r="D260" s="4" t="inlineStr">
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — microfauna (moluscos, foraminífero e ostracode)</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
+      <c r="F263" s="7" t="inlineStr">
         <is>
           <t>Testemunho PCSC-1, em mata paludial próxima à Lagoa do Sombrio, município de Santa Rosa do Sul, SC (acesso pela BR-101 e estradas secundárias); coordenadas do próprio resumo: 29°10'42"S, 49°44'58"W; Russian Peat Borer, profundidade de 570 cm</t>
         </is>
       </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="G263" s="6" t="inlineStr">
         <is>
           <t>Não informado no resumo (triagem da microfauna no CECO/UFRGS)</t>
         </is>
       </c>
-      <c r="H260" s="5" t="inlineStr">
+      <c r="H263" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Souza, P.A. &amp; Dehnhardt, B.A. (2011) — "Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos", Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo)</t>
         </is>
       </c>
-      <c r="I260" s="4" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>Universidade Federal do Rio Grande do Sul (UFRGS) — afiliação dos autores</t>
         </is>
       </c>
-      <c r="J260" s="4" t="inlineStr">
+      <c r="J263" s="6" t="inlineStr">
         <is>
           <t>base do testemunho ca. 7.908 ± 33 anos cal AP (única datação AMS, nível basal; 0,0079 Ma); os níveis com microfauna ficam entre 570 e 320 cm, sem datação própria</t>
         </is>
       </c>
-      <c r="K260" s="5" t="inlineStr">
+      <c r="K263" s="7" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): a microfauna foi triada em níveis selecionados do testemunho e reúne 15 táxons — bivalves: Anomalocardia brasiliana, Brachiodontes sp., Tellina versicolor, Pitar rostratus e Ostrea puelchana; gastrópodes: Parodizia uruguayensis, Heleobia australis australis, Bittium varium, Odostomia seminuda, Crepidula aculeata, Bulla striata, Solariorbis shimeri e Solariorbis shumoi; foraminífero: Quinqueloculina lamarckiana; ostracode: Cyprideis sp. O resumo não atribui cada espécie a uma profundidade: informa apenas que a base (570–560 cm) é um concheiro com fauna interpretada como autóctone, bem preservada e adaptada a salinidade elevada, e que pequenos fragmentos de conchas continuam até 320 cm, com pouco indício de retrabalhamento. INTERPRETAÇÃO (dos autores): fase I (570–560 cm) com influência marinha ou fortemente salina; fase II (560–320 cm) com ingressão marinha que ultrapassou os limites atuais, com pico em torno de 450 cm (palinoforaminíferos e Micrhystridium), ligada ao recuo da margem oeste da Lagoa do Sombrio; fase III (320–0 cm) com aumento de árvores da Mata Atlântica, briófitas, pteridófitas e algas de água doce, ambiente de influência lagunar substituído por influência de água doce. LOCALIZAÇÃO: o testemunho PCSC-1 é de Santa Rosa do Sul; o ponto do mapa usa as coordenadas do resumo. NOTA DE FONTE: só o resumo foi consultado; os autores afirmam que obterão novas datações ao longo do perfil (só a base foi datada), por isso a idade dos níveis com microfauna não é conhecida. Os nomes de espécie estão como no resumo; sinonímias e a grafia atual não foram verificadas. O resumo não informa depositário nem numeração de tombo. RELAÇÃO COM OUTROS REGISTROS (2026.10.09): os dados palinológicos do mesmo testemunho (112 palinomorfos no total, dos quais 54 não-pólen) correspondem ao registro nº 233. LIGAÇÃO COM O REGISTRO Nº 238 (2026.10.09): o testemunho PCSC-01 (570 cm, Lagoa do Sombrio, Santa Rosa do Sul) das diatomáceas de Santos &amp; Souza tem a mesma profundidade e a mesma área, mas as fontes não declaram que seja o mesmo testemunho do PCSC-1 aqui descrito.</t>
         </is>
       </c>
-      <c r="L260" s="5" t="inlineStr">
+      <c r="L263" s="7" t="inlineStr">
         <is>
           <t>https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
-      <c r="M260" s="5" t="inlineStr">
+      <c r="M263" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; SOUZA, P.A.; DEHNHARDT, B.A. 2011. Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos. Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo).</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N263" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="O260" s="4" t="inlineStr">
+      <c r="O263" s="6" t="inlineStr">
         <is>
           <t>Testemunho PCSC-1 (Santa Rosa do Sul)</t>
         </is>
       </c>
-      <c r="P260" s="4" t="inlineStr">
+      <c r="P263" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q260" s="4" t="n">
+      <c r="Q263" s="6" t="n">
         <v>-29.1783</v>
       </c>
-      <c r="R260" s="4" t="n">
+      <c r="R263" s="6" t="n">
         <v>-49.7494</v>
       </c>
-      <c r="S260" s="4" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="6" t="inlineStr">
+      <c r="S263" s="6" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="B264" s="4" t="inlineStr">
         <is>
           <t>Depósitos holocênicos de planície costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C261" s="7" t="inlineStr">
+      <c r="C264" s="5" t="inlineStr">
         <is>
           <t>Foraminíferos bentônicos holocênicos — Miliolida (testemunho de Volta Velha, Itapoá)</t>
         </is>
       </c>
-      <c r="D261" s="6" t="inlineStr">
+      <c r="D264" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — foraminífero bentônico</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E264" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F261" s="7" t="inlineStr">
+      <c r="F264" s="5" t="inlineStr">
         <is>
           <t>Região de Volta Velha, Itapoá, SC — uma das três sondagens manuais feitas ali; coordenadas do resumo: 26°4'58,5"S, 48°37'54,3"W (a amostra com miliolídeos vem do estrato mais profundo do testemunho de Volta Velha)</t>
         </is>
       </c>
-      <c r="G261" s="6" t="inlineStr">
+      <c r="G264" s="4" t="inlineStr">
         <is>
           <t>Não informado no resumo</t>
         </is>
       </c>
-      <c r="H261" s="7" t="inlineStr">
+      <c r="H264" s="5" t="inlineStr">
         <is>
           <t>Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)</t>
         </is>
       </c>
-      <c r="I261" s="6" t="inlineStr">
+      <c r="I264" s="4" t="inlineStr">
         <is>
           <t>Universidade Federal do Paraná (LECOST) e Universidade do Algarve (CIMA, Portugal) — afiliações dos autores</t>
         </is>
       </c>
-      <c r="J261" s="6" t="inlineStr">
+      <c r="J264" s="4" t="inlineStr">
         <is>
           <t>Holoceno (os autores tratam os depósitos como holocênicos; idade do testemunho de Volta Velha não informada no resumo)</t>
         </is>
       </c>
-      <c r="K261" s="7" t="inlineStr">
+      <c r="K264" s="5" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): foram feitas 35 sondagens manuais em planícies costeiras do norte de Santa Catarina e do sul do Paraná — seis em SC (três em Volta Velha, Itapoá, e três na parte interna da Baía de São Francisco, nas planícies de Joinville e de Garuva) e uma no Paraná (Cabaraquara, Guaratuba) — para analisar foraminíferos. No testemunho de Volta Velha só uma amostra, a do estrato mais profundo, trouxe fauna composta predominantemente por miliolídeos; os autores a interpretam como indício de ambiente mais oxigenado, com maior influência marinha e salinidade mais alta, provavelmente uma região mais externa da baía. ESCOPO: o resumo não traz resultados separados nem identificação de espécies para as sondagens de Itapoá (demais amostras) e da Baía de São Francisco (Joinville/Garuva); os gêneros Ammonia e Elphidium que o resumo menciona são do testemunho de Guaratuba, no Paraná, e por isso não fazem parte deste registro. NOTA DE FONTE: só o resumo foi consultado e o texto declara resultados preliminares, com espécies ainda não identificadas. O documento não informa o evento nem o ano (agradece ao projeto CNPq 471039/2013-6), por isso a data está como s.d.; profundidade e datação 14C do testemunho de Volta Velha também não constam.</t>
         </is>
       </c>
-      <c r="L261" s="7" t="inlineStr">
+      <c r="L264" s="5" t="inlineStr">
         <is>
           <t>https://www.abequa.org.br/anais/247_resumo.pdf (Silva, Angulo, Souza &amp; Boski — resumo; evento e ano não constam do documento)</t>
         </is>
       </c>
-      <c r="M261" s="7" t="inlineStr">
+      <c r="M264" s="5" t="inlineStr">
         <is>
           <t>[referência sem formato bibliográfico, transcrita do descritor: Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)]</t>
         </is>
       </c>
-      <c r="N261" s="6" t="n">
+      <c r="N264" s="4" t="n">
         <v>265</v>
       </c>
-      <c r="O261" s="6" t="inlineStr">
+      <c r="O264" s="4" t="inlineStr">
         <is>
           <t>Volta Velha (Itapoá) — testemunho da planície costeira</t>
         </is>
       </c>
-      <c r="P261" s="6" t="inlineStr">
+      <c r="P264" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q261" s="6" t="n">
+      <c r="Q264" s="4" t="n">
         <v>-26.0829</v>
       </c>
-      <c r="R261" s="6" t="n">
+      <c r="R264" s="4" t="n">
         <v>-48.6318</v>
       </c>
-      <c r="S261" s="6" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+      <c r="S264" s="4" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B262" s="4" t="inlineStr">
+      <c r="B265" s="6" t="inlineStr">
         <is>
           <t>Depósito conchífero natural holocênico (lagunar/paleolagunar) da planície costeira; unidade litoestratigráfica formal não nomeada nas fontes consultadas</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr">
+      <c r="C265" s="7" t="inlineStr">
         <is>
           <t>Moluscos subfósseis do concheiro de Nova Brasília (12 espécies; dominantes: Heleobia australis, Cerithiopsis greeni, Crepidula plana, Nassarius vibex, Tellina lineata, Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="D262" s="4" t="inlineStr">
+      <c r="D265" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — moluscos (assembleia de bivalves e gastrópodes)</t>
         </is>
       </c>
-      <c r="E262" s="4" t="inlineStr">
+      <c r="E265" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
+      <c r="F265" s="7" t="inlineStr">
         <is>
           <t>Concheiro natural do rio D'Una, localidade de Nova Brasília, Imbituba, SC, na planície de inundação do rio D'Una, extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio; frentes de lavra de calcário de conchas (cerca de 4.000 m de comprimento, 420 m de largura e 0,60–6 m de espessura). Coordenadas não informadas nas fontes; ponto do mapa = centro do município de Imbituba (referência regional)</t>
         </is>
       </c>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="G265" s="6" t="inlineStr">
         <is>
           <t>Não informado</t>
         </is>
       </c>
-      <c r="H262" s="5" t="inlineStr">
+      <c r="H265" s="7" t="inlineStr">
         <is>
           <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011; Caruso Júnior, F. (1992) — "Geologia dos depósitos de conchas calcárias no estado de Santa Catarina", Geosul 7(14):101–136</t>
         </is>
       </c>
-      <c r="I262" s="4" t="inlineStr">
+      <c r="I265" s="6" t="inlineStr">
         <is>
           <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores (2000)</t>
         </is>
       </c>
-      <c r="J262" s="4" t="inlineStr">
+      <c r="J265" s="6" t="inlineStr">
         <is>
           <t>4.490 ± 200 anos AP (conchas; datação de Martin &amp; Suguio, 1986, citada por Caruso et al., 2000; 0,0045 Ma) — os próprios autores ressalvam que as conchas são alóctones e que a idade pode não ser a deposicional</t>
         </is>
       </c>
-      <c r="K262" s="5" t="inlineStr">
+      <c r="K265" s="7" t="inlineStr">
         <is>
           <t>CITAÇÃO EM REVISÃO — a lista de espécies é compilada por Caruso Júnior et al. (2000) a partir de levantamentos malacológicos anteriores (que o texto atribui a Forti-Esteves, 1986; Mendes, 1993; Pitoni, 1993), e esses levantamentos não foram examinados por este banco. CLASSIFICAÇÃO E CONTEÚDO (segundo o artigo): as espécies mais abundantes são Heleobia australis (d'Orbigny, 1835), Cerithiopsis greeni (C.B. Adams, 1839), Crepidula plana, Nassarius vibex, Tellina (Eurytellina) lineata e Tagelus plebeius; as duas primeiras são tidas como estuarinas e as demais como marinhas litorâneas. Também são citadas Neritina virginea, Cerithium stratum, Bulla striata, Ostrea equestris, Codakia costata e Anomalocardia brasiliana. O artigo grafa «Cerithiopis greeni» e «Nassarius viabex»; a grafia foi corrigida aqui. SEDIMENTOLOGIA E TAFONOMIA: o depósito tem unidades tabulares com estratificação cruzada de grande porte, alternando camadas arenosas e conchíferas, com gradação inversa; os autores propõem transporte por barras de corrente e um bloqueio do transporte sul–norte por um terraço pleistocênico, o que teria depositado o cascalho de conchas. LOCALIZAÇÃO: o artigo de 2000 localiza o depósito no extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio, na região de Nova Brasília; Caruso Júnior (1992) o situa na localidade de Nova Brasília, município de Imbituba, na planície de inundação do rio D'Una. VERIFICAÇÃO (2026.10.09): o artigo de 2000 não chama as conchas de «fósseis»; elas vêm de depósitos holocênicos e são tratadas aqui como subfósseis, no mesmo critério dos demais moluscos holocênicos do banco. A lista de ~30 táxons do anexo de Caruso Júnior (1992), identificada por I.P.F. Esteves em 1986, não traz o depósito de origem no trecho legível e a bibliografia da obra só cita um trabalho de Esteves sobre o concheiro de Jaboticabeira; por isso ela não foi atribuída a Nova Brasília nem aproveitada aqui.</t>
         </is>
       </c>
-      <c r="L262" s="5" t="inlineStr">
+      <c r="L265" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0001-37652000000200011
 https://www.scielo.br/j/aabc/a/PV3LvmfpkshVK6wWx8WgWSc/?lang=en (Caruso Júnior, Suguio &amp; Nakamura, 2000 — texto integral)
 https://periodicos.ufsc.br/index.php/geosul/article/download/12805/11988/39566 (Caruso Júnior, 1992 — texto integral, Geosul)</t>
         </is>
       </c>
-      <c r="M262" s="5" t="inlineStr">
+      <c r="M265" s="7" t="inlineStr">
         <is>
           <t>CARUSO JÚNIOR, F.; SUGUIO, K.; NAKAMURA, T. 2000. The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil). Anais da Academia Brasileira de Ciências, 72(2), 257–270. DOI: 10.1590/S0001-37652000000200011 | CARUSO JÚNIOR, F. 1992. Geologia dos depósitos de conchas calcárias no estado de Santa Catarina. Geosul, 7(14), 101–136.</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n">
+      <c r="N265" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="O262" s="4" t="inlineStr">
+      <c r="O265" s="6" t="inlineStr">
         <is>
           <t>Concheiro natural de Nova Brasília (Imbituba)</t>
         </is>
       </c>
-      <c r="P262" s="4" t="inlineStr">
+      <c r="P265" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q262" s="4" t="n">
+      <c r="Q265" s="6" t="n">
         <v>-28.193</v>
       </c>
-      <c r="R262" s="4" t="n">
+      <c r="R265" s="6" t="n">
         <v>-48.7019</v>
       </c>
-      <c r="S262" s="4" t="inlineStr"/>
+      <c r="S265" s="6" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos holocênicos de turfa, lama detrítica e areia fina da planície costeira (unidade litoestratigráfica não nomeada no artigo)</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>Pólen e esporos do perfil de Poço Grande (planície costeira: dunas, plantas aquáticas e floresta pluvial atlântica)</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — palinomorfos (pólen e esporos)</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Planície costeira norte de SC, a 800 m a noroeste do fim da estrada para o Rancho Nutrimental, perto da vila de Poço Grande (15 km ao sul de Joinville e a cerca de 20 km do Atlântico, segundo o artigo); 26°25′ S, 48°52′ O; 10–16 m de altitude. O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Guaramirim, a ~1 km da divisa com Joinville (por isso «região»)</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="inlineStr">
+        <is>
+          <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno superior: base do perfil extrapolada em ~4.840 anos 14C AP, até o presente; datações de 4.680 ± 150 (507–514 cm), 4.265 ± 190 (327–332 cm), 4.230 ± 185 (214–219 cm) e 3.525 ± 175 (127–132 cm); idades não calibradas; provável hiato</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de perfil sedimentar da planície costeira — registro paleoambiental do Holoceno superior. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): perfil de 587 cm (turfa «carr» com madeira, lama detrítica e areia fina; começa 5 cm abaixo da superfície), amostrado em 12/10/1989 perto do Rancho Nutrimental (o autor não pôde terminar a coleta por uma mudança de proprietário do rancho); contagem mínima de 508 grãos por amostra (média de 1.383). Quatro datações por 14C (Hv 17559–17562): 3.525 ± 175 anos AP (127–132 cm), 4.230 ± 185 (214–219), 4.265 ± 190 (327–332) e 4.680 ± 150 (507–514); idades não calibradas. RESULTADO (zonas A–E, segundo o autor e o resumo): A (~4.840–4.590 anos AP) — alternância repetida de duas comunidades de dunas perto do local (Myrtaceae, de dunas estáveis; Palmae, Ilex, Weinmannia e Schinus, de dunas pouco móveis) com variações do nível da água; B (~4.590–4.265) — depósitos de água doce, com sucessão de plantas aquáticas (Cabomba, Potamogeton, Myriophyllum, Echinodorus) e pólen alto de Alchornea, Urticales e Rapanea; C (~4.265–4.230) — curta, com Rapanea chegando a 15%; D (~4.230–3.525) — Alchornea chega a 24% e indica floresta densa perto do local; E (0–133 cm, início datado em 3.525 anos AP) — alto de Cyperaceae e sinais de ação humana no topo (queda de Alchornea, alta de Rapanea, drenagem da área do rancho). O autor aponta um provável hiato (a idade extrapolada para o início de E seria ~4.030 anos AP) e que a parte superior de E pode ter só alguns séculos. Os valores de Araucaria angustifolia e Dicksonia sellowiana (até ~2% e 5%) indicam, segundo ele, expansão da floresta de araucária no planalto no Holoceno superior. O autor relaciona mudanças do nível d’água na planície a variações do nível do mar (Fairbridge, 1962; Bigarella, 1965), sem comprová-las neste perfil. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Guaramirim, a ~1 km da divisa com Joinville; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
+https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
+https://www.uni-goettingen.de/de/document/download/7704cdc9d93f4bdd3c6e232529ec697f.pdf/2004_Behling_PPP_CambaradoSul_Brazil.pdf (Behling et al., 2004 — idades de SC citadas)
+https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
+        </is>
+      </c>
+      <c r="M266" s="5" t="inlineStr">
+        <is>
+          <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
+        </is>
+      </c>
+      <c r="N266" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="O266" s="4" t="inlineStr">
+        <is>
+          <t>Poço Grande (Guaramirim / Joinville)</t>
+        </is>
+      </c>
+      <c r="P266" s="4" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="n">
+        <v>-26.4167</v>
+      </c>
+      <c r="R266" s="4" t="n">
+        <v>-48.8667</v>
+      </c>
+      <c r="S266" s="4" t="inlineStr">
+        <is>
+          <t>10.1007/BF00203932</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S262"/>
+  <autoFilter ref="A3:S266"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -23792,7 +24186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B863"/>
+  <dimension ref="A1:B917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -32919,16 +33313,20 @@
         </is>
       </c>
     </row>
+    <row r="855">
+      <c r="A855" s="9" t="n"/>
+      <c r="B855" s="9" t="n"/>
+    </row>
     <row r="856">
-      <c r="A856" s="10" t="inlineStr">
+      <c r="A856" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B856" s="9" t="inlineStr"/>
+      <c r="B856" s="9" t="n"/>
     </row>
     <row r="857">
-      <c r="A857" s="11" t="inlineStr">
+      <c r="A857" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -32940,7 +33338,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" s="11" t="inlineStr">
+      <c r="A858" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -32952,7 +33350,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="11" t="inlineStr">
+      <c r="A859" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -32964,7 +33362,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" s="11" t="inlineStr">
+      <c r="A860" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -32976,7 +33374,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="11" t="inlineStr">
+      <c r="A861" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -32988,7 +33386,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" s="11" t="inlineStr">
+      <c r="A862" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -33000,12 +33398,584 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" s="11" t="inlineStr">
+      <c r="A863" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="9" t="n"/>
+      <c r="B864" s="9" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B865" s="9" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B867" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B869" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B870" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B871" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B872" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="9" t="n"/>
+      <c r="B873" s="9" t="n"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B874" s="9" t="n"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B875" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B876" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B877" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B878" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B879" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B880" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B881" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="9" t="n"/>
+      <c r="B882" s="9" t="n"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B883" s="9" t="n"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B884" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B885" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B886" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B887" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B888" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B889" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B890" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="9" t="n"/>
+      <c r="B891" s="9" t="n"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B892" s="9" t="n"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B893" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B894" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B895" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B896" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B897" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B898" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B899" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="9" t="n"/>
+      <c r="B900" s="9" t="n"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B901" s="9" t="n"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B902" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B903" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B904" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B905" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B906" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B907" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B908" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B910" s="9" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B911" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B912" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B913" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B914" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B915" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B916" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B917" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -20104,7 +20104,7 @@
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão; Citação de mídia — Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann</t>
+          <t>Valdati, J., Gomes, M.C.V., Weinschütz, L.C., Ricetti, J.H.Z. &amp; Bechtel, A.P. (2024) — "Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas", Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Bechtel, A.P., Valdati, J., Weinschütz, L.C. &amp; Ricetti, J.H.Z. (2023) — "Patrimônio paleontológico e sua distribuição nos compartimentos de relevo no Geoparque Mundial UNESCO Caminhos dos Cânions do Sul", Anais do 14º Simpósio Nacional de Geomorfologia (SINAGEO), Corumbá/MS, 24–30/08/2023; Bechtel, A.P., Valdati, J., Weinschütz, L.C. &amp; Ricetti, J.H.Z. (2023) — "Icnofósseis da megafauna: distribuição nos compartimentos de relevo no Geoparque Mundial da UNESCO Caminhos dos Cânions do Sul", Anais do Seminário de Pesquisas do Geoparque Caminhos dos Cânions do Sul, vol. 2, p. 27; Bechtel, A.P. (2022) — "Registro da megafauna pliocênica-quaternária no Geoparque Caminhos dos Cânions do Sul e Irineópolis, SC", Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC); Citação de mídia — ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão; Citação de mídia — Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann; Citação de mídia — Revista Oeste (31/03/2026), reportagem «A maior concentração de túneis pré-históricos do mundo fica no Sul do Brasil e foi escavada por gigantes extintos», que cita o acervo do Geoparque Caminhos dos Cânions do Sul</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
@@ -20119,7 +20119,7 @@
       </c>
       <c r="K222" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): a existência de paleotocas no Geoparque tem base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque Caminhos dos Cânions do Sul (2.830 km², sete municípios: Timbé do Sul, Jacinto Machado, Praia Grande e Morro Grande, em SC, e três no RS) e descrevem três delas — duas nas Escarpas da Serra Geral, em Morro Grande (registros nº 268 e 269), e uma no Planalto dos Campos Gerais, em Cambará do Sul/RS (fora do escopo deste banco). Segundo o texto consultado, foram catalogadas 24 paleotocas no Geoparque, a maior parte das feições descritas até agora está em Morro Grande, e a Toca do Tatu (Timbé do Sul, registro nº 82) é tratada com base em Frank et al. (2012). O artigo não individualiza, no texto consultado, cavidades de Praia Grande. Um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural que não traz inventário de paleotocas, registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a Paleotoca Toca do Tatu (registro nº 82) e que o de Praia Grande não cita paleotocas (lista Pedra Branca, Cânion Itaimbezinho e Cânion Malacara); o de Jacinto Machado cita paleotocas ocupadas pelos Laklãnõ-Xokleng (registros nº 81 e 83). CITAÇÃO DE MÍDIA: os números e a localização em Praia Grande e Timbé do Sul, aqui, vêm de reportagens, não de publicação. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. Litologia não informada nas reportagens. Esses números (mais de 40 estruturas; mais de duas mil no Brasil) não coincidem com o catálogo do artigo (24 no Geoparque) e os critérios de contagem das reportagens não foram conciliados. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): a existência de paleotocas no Geoparque tem base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque Caminhos dos Cânions do Sul (2.830 km², sete municípios: Timbé do Sul, Jacinto Machado, Praia Grande e Morro Grande, em SC, e três no RS) e descrevem três delas — duas nas Escarpas da Serra Geral, em Morro Grande (registros nº 268 e 269), e uma no Planalto dos Campos Gerais, em Cambará do Sul/RS (fora do escopo deste banco). Segundo o texto consultado, foram catalogadas 24 paleotocas no Geoparque, a maior parte das feições descritas até agora está em Morro Grande, e a Toca do Tatu (Timbé do Sul, registro nº 82) é tratada com base em Frank et al. (2012). O artigo não individualiza, no texto consultado, cavidades de Praia Grande. Um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. CONTAGENS EM PUBLICAÇÕES (2026.10.09), por trabalho: 17 paleotocas — Bechtel et al. (2023, SINAGEO: 1 no Planalto da Serra Geral, 6 nos Patamares e 10 nas Escarpas; 16 em arenito da Fm. Botucatu e uma em basalto intemperizado, a «paleotoca do Parque»; altitude média de 382 m nas escarpas e de 87,5 m nos patamares) e um resumo da UDESC sem data (Bechtel &amp; Valdati, «Distribuição de paleotocas no território do Geoparque…»: 9 nas Escarpas, 4 nos Patamares, 2 na Planície colúvio-aluvionar e 1 no Planalto); 23 — Bechtel et al. (2023, Anais do Seminário de Pesquisas, vol. 2, p. 27: 1 no Planalto dos Campos Gerais, 9 nas Escarpas e 13 nos Patamares; 22 em Botucatu e uma em basalto; relatos de moradores sugerem que pode haver cerca do dobro) e o resumo da UDESC sem data «Registro da Megafauna do Quaternário…» (pelo menos 20 outras ainda sem visita); 24 — Valdati et al. (2024). O TCC de Bechtel (2022) nomeia só três no Geoparque (Aparência, Parque e Veisom), além de duas em Irineópolis, e cita a Toca do Tatu a partir de Frank et al. (2012). As contagens e as distribuições por compartimento são de épocas e critérios diferentes e não foram conciliadas; nenhuma é desagregada por município. Em Praia Grande, um relatório de iniciação científica da UDESC (Souza &amp; Valdati, sem ano na cópia consultada) descreve o complexo «Furnas do Itamar / Reserva Caeté» (campo em 19–23/03/2024: três paleotocas já conhecidas e oito novas, duas delas crotovinas — 11 feições), sem coordenadas nem dimensões no texto lido (ver registro nº 83). CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural que não traz inventário de paleotocas, registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a Paleotoca Toca do Tatu (registro nº 82) e que o de Praia Grande não cita paleotocas (lista Pedra Branca, Cânion Itaimbezinho e Cânion Malacara); o de Jacinto Machado cita paleotocas ocupadas pelos Laklãnõ-Xokleng (registros nº 81 e 83). CITAÇÃO DE MÍDIA: os números e a localização em Praia Grande e Timbé do Sul, aqui, vêm de reportagens, não de publicação. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. A Revista Oeste (31/03/2026), ao tratar do túnel de Lauro Müller (registro nº 44), diz que o acervo do Geoparque soma cerca de 30 paleotocas registradas em Morro Grande, Jacinto Machado e Timbé do Sul; não informa quantas há em cada município nem nomeia nenhuma [citação de mídia]. Litologia não informada nas reportagens. Esses números (mais de 40 estruturas; mais de duas mil no Brasil) não coincidem com o catálogo do artigo (24 no Geoparque) e os critérios de contagem das reportagens não foram conciliados. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Valores de Bechtel et al. (2023), dos resumos e do TCC da UDESC lidos em resumo da ferramenta de leitura, não nos PDFs: conferir nos originais antes de citar. </t>
         </is>
       </c>
       <c r="L222" s="5" t="inlineStr">
@@ -20129,12 +20129,17 @@
 https://doi.org/10.26848/rbgf.v17.3.p1905-1920
 https://doi.org/10.4072/rbp.2009.3.07
 https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418
-https://doi.org/10.18616/rdsd.v10i1.8551</t>
+https://doi.org/10.18616/rdsd.v10i1.8551
+https://www.sinageo.org.br/2023/trabalhos/13/279-83.pdf
+https://revistaoeste.com/oestegeral/2026/03/31/a-maior-concentracao-de-tuneis-pre-historicos-do-mundo-fica-no-sul-do-brasil-e-foi-escavada-por-gigantes-extintos/
+https://canionsdosul.org/wp-content/uploads/2023/11/Anais-do-Seminario-de-Pesquisas-Vol-2.pdf
+https://sistemabu.udesc.br/pergamumweb/vinculos/0000a3/0000a31d.pdf
+https://www.udesc.br/arquivos/udesc/id_cpmenu/15666/DISTRIBUI__O_DE_PALEOTOCAS_NO_TERRIT_RIO_DO_GEOPARQUE_CAMINHOS_DOS_C_NIONS_DO_SUL_16632667806571_15666.pdf</t>
         </is>
       </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
-          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920 | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann]</t>
+          <t>VALDATI, J.; GOMES, M.C.V.; WEINSCHÜTZ, L.C. et al. 2024. Proposta de classificação das paleotocas com base nas características fisionômicas e morfológicas. Revista Brasileira de Geografia Física, 17(3), 1905–1920. DOI: 10.26848/rbgf.v17.3.p1905-1920 | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | BECHTEL, A.P.; VALDATI, J.; WEINSCHÜTZ, L.C. et al. 2023. Patrimônio paleontológico e sua distribuição nos compartimentos de relevo no Geoparque Mundial UNESCO Caminhos dos Cânions do Sul. Anais do 14º Simpósio Nacional de Geomorfologia (SINAGEO), Corumbá/MS, 24–30/08/2023. | BECHTEL, A.P.; VALDATI, J.; WEINSCHÜTZ, L.C. et al. 2023. Icnofósseis da megafauna: distribuição nos compartimentos de relevo no Geoparque Mundial da UNESCO Caminhos dos Cânions do Sul. Anais do Seminário de Pesquisas do Geoparque Caminhos dos Cânions do Sul, vol. 2, p. 27. | BECHTEL, A.P. 2022. Registro da megafauna pliocênica-quaternária no Geoparque Caminhos dos Cânions do Sul e Irineópolis, SC. Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC). | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (10/08/2025), reportagem «Cavernas em SC guardam rastros de preguiças e tatus gigantes», que cita o geólogo do Geoparque G. Simão] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Jornal da Unesp (18/01/2022), reportagem «Uma visita à casa dos gigantes», que relata declaração de F. S. C. Buchmann] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: Revista Oeste (31/03/2026), reportagem «A maior concentração de túneis pré-históricos do mundo fica no Sul do Brasil e foi escavada por gigantes extintos», que cita o acervo do Geoparque Caminhos dos Cânions do Sul]</t>
         </is>
       </c>
       <c r="N222" s="4" t="n">
@@ -20298,7 +20303,7 @@
       </c>
       <c r="H224" s="5" t="inlineStr">
         <is>
-          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101; Cezaro, H.S., Santos, M.C.P. &amp; Campos, J.B. (2016) — "Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu", Revista Memorare 3(1):47–72; Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551</t>
+          <t>Frank, H.T., Oliveira, L.D., Vicroski, F.N., Breier, R., Pasqualon, N.G., Araújo, T., Buchmann, F.S.C., Fornari, M., Lima, L.G., Lopes, R.P. &amp; Caron, F. (2012) — "The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil", Espeleo-Tema 23(2):87–101; Cezaro, H.S., Santos, M.C.P. &amp; Campos, J.B. (2016) — "Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu", Revista Memorare 3(1):47–72; Provedan, B.S. (2019) — "Roteiros geoturísticos para o município de Timbé do Sul", Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC); Bechtel, A.P. (2022) — "Registro da megafauna pliocênica-quaternária no Geoparque Caminhos dos Cânions do Sul e Irineópolis, SC", Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC); Santos, A.L., Campos, J.B., Bandeira, D.R., Carelli, M.N., Miziescki, M. &amp; Silva, J.G.S. (2024) — "O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul", Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551; Miranda, L. (2025) — "Capacidade de carga turística aplicada à trilha Portal do Palmiro, Timbé do Sul, SC: Caminhos dos Cânions do Sul Geoparque Mundial da UNESCO", Dissertação de Mestrado (Ciências Ambientais), Universidade do Extremo Sul Catarinense (UNESC); Rodrigues, M. (2025) — "Did giant ice age beasts carve these vast caves in South America?", Nature 637:1036–1037, DOI 10.1038/d41586-025-00216-x</t>
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr">
@@ -20313,7 +20318,7 @@
       </c>
       <c r="K224" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos). CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. ARTE RUPESTRE (2026.10.09): Cezaro, Santos &amp; Campos (2016, Revista Memorare 3(1):47–72) tratam a Toca do Tatu (Timbé do Sul) como caverna de 48,5 m com dois túneis, registrada pelo Projeto Paleotocas e descrita como abrigo «escavado provavelmente por preguiças gigantes durante o Cenozoico»; nas zonas iluminadas dos dois túneis há gravuras (não pinturas) que cobrem mais de 35 m², com sulcos finos de cerca de 5 mm e grafismos de mais de sete geometrias distintas, classificados pelos autores na Tradição Geométrica Meridional; a semelhança com motivos de pintura corporal de grupos Jê meridionais é, no artigo, uma hipótese interpretativa com ressalvas, não um achado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551) — artigo de patrimônio cultural, não de paleontologia — registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a «Paleotoca Toca do Tatu» e suas inscrições rupestres como sítios arqueológicos da região, e que a Toca do Tatu é um dos cinco geossítios catarinenses (de 23 catalogados pelo Geoparque) mencionados nos planos municipais; o artigo não traz dados paleontológicos sobre a cavidade. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores de Cezaro et al. (2016) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos). CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. ARTE RUPESTRE (2026.10.09): Cezaro, Santos &amp; Campos (2016, Revista Memorare 3(1):47–72) tratam a Toca do Tatu (Timbé do Sul) como caverna de 48,5 m com dois túneis, registrada pelo Projeto Paleotocas e descrita como abrigo «escavado provavelmente por preguiças gigantes durante o Cenozoico»; nas zonas iluminadas dos dois túneis há gravuras (não pinturas) que cobrem mais de 35 m², com sulcos finos de cerca de 5 mm e grafismos de mais de sete geometrias distintas, classificados pelos autores na Tradição Geométrica Meridional; a semelhança com motivos de pintura corporal de grupos Jê meridionais é, no artigo, uma hipótese interpretativa com ressalvas, não um achado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551) — artigo de patrimônio cultural, não de paleontologia — registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a «Paleotoca Toca do Tatu» e suas inscrições rupestres como sítios arqueológicos da região, e que a Toca do Tatu é um dos cinco geossítios catarinenses (de 23 catalogados pelo Geoparque) mencionados nos planos municipais; o artigo não traz dados paleontológicos sobre a cavidade. DADOS DO TEXTO DE FRANK ET AL. (2012) (2026.10.09): coordenada 28°46′21,2″S, 49°53′45,9″W; a caverna fica numa encosta íngreme voltada para SW, numa das «canhoneiras» do escarpamento da Serra Geral, a cerca de 100 m da margem esquerda do rio que corre no fundo do cânion e a 20–30 m acima do nível dele; planta em «U», com dois túneis quase paralelos (separados por menos de 3 m de rocha) que convergem para um salão; extensão total de 48,5 m; túnel norte quase retilíneo, com cerca de 4 m de largura na entrada (reduzida a ~2,6 m perto do salão) e ~2,0 m de altura; túnel sul em arco, com seção decrescente; salão com 1,48–2,86 m de altura; saída traseira com menos de 1,5 m de diâmetro; volume escavado superior a 100 m³ (mais de 200 t de arenito, segundo os autores); arenito eólico da Fm. Botucatu (Jurássico Superior–Cretáceo Inferior), coberto pelo basalto da Fm. Serra Geral; a dissolução é descartada (rocha não solúvel, sem sinais de drenagem subterrânea). Marcas de garras: sulcos largos (tipo C) de até ~5 cm de largura, ~6 cm de profundidade e ~50 cm de comprimento, até ~2,5 m de altura, na base das paredes dos dois túneis, e superfície contínua de marcas no salão. Grafismos de sulcos finos (tipo D), atribuídos a populações pré-coloniais, possivelmente do grupo Gê (Tradição Geométrica, Subtradição Morro do Avencal, segundo Prous, 1992): grades, radiais (as maiores com 1,0 e 1,2 m de diâmetro), ondulações angulares e cerca de uma dúzia de desenhos complexos, concentrados nos primeiros 11 m do túnel norte e cobrindo mais de 35 m² de paredes e teto (o resumo do texto fala em «mais de cinco geometrias»; Cezaro et al., 2016, em «mais de sete» — contagens não conciliadas). Escavação atribuída a preguiças-gigantes («possivelmente Scelidotherium, Mylodon, Glossotherium ou Lestodon»), em etapas; sem datação radiométrica — o limite inferior de idade é a extinção da megafauna, há cerca de 10 mil anos. Alterações posteriores: caçadores de tesouros (testemunhos locais os situam no início da década de 1970) removeram sedimentos e ampliaram entradas; visitantes deixaram 119 conjuntos de nomes, datas (1956–1991, entre outras) e símbolos nos primeiros 10 m do túnel norte; os autores recomendam interromper qualquer ação que possa destruir mais a caverna. O termo «baixos-relevos» da ficha anterior não aparece no resumo do texto consultado, que fala em sulcos finos (grafismos gravados): conferir no original. OUTRAS FONTES SOBRE A CAVIDADE (2026.10.09): o TCC de Provedan (2019, UDESC, Geografia) trata a Toca do Tatu como a única paleotoca que nomeia no município e a situa na comunidade que o texto grafa «Rochinha» (grafia a conferir; este banco usa «rio Rocinha», de Frank et al., 2012), a cerca de 7,5 km da sede; descreve dois túneis paralelos que convergem numa câmara maior, com cerca de 48,5 m (valor que o TCC atribui a Lima &amp; Vargas, 2018, trabalho não localizado), em arenito da Fm. Botucatu — rocha não solúvel, o que, segundo os autores, descarta a dissolução como origem. A dissertação de Miranda (2025, UNESC, Ciências Ambientais) mapeia a trilha Portal do Palmiro, que dá acesso à paleotoca, e calcula a capacidade de carga turística em 69 pessoas por dia (só o resumo foi lido). A página de geossítios do Geoparque dá 7,3 km do centro da cidade, trilha de cerca de 3,5 km (ida e volta) e guia obrigatório. Valdati et al. (2024) citam a Toca do Tatu como estudada por Frank et al. (2012) e, na discussão, listam «Tatu» — sem afirmar expressamente que seja esta cavidade — entre as exceções ao estado praticamente intocado das demais paleotocas do Geoparque (ver registro nº 81). A matéria de Rodrigues (2025, Nature 637:1036–1037, DOI 10.1038/d41586-025-00216-x) — texto jornalístico da seção de notícias, não artigo de pesquisa — chama a cavidade de «Toca do Tatu (Armadillo's Den)», diz que a entrada comporta uma van, que os sulcos do teto são atribuídos a preguiças-gigantes extintas há mais de 10 mil anos e que é uma das paleotocas mais bem preservadas do Brasil, embora coberta de grafites (Frank et al., 2012, descrevem danos e inscrições modernas), e cita um guia local segundo o qual uma gravura em zigue-zague representa o rio Rocinha; J. B. Campos (UNESC) a chama de «maravilha arqueológica e paleontológica». O nome «Rocinha» aparece, assim, ligado à cavidade em Provedan (comunidade «Rochinha») e na matéria da Nature (rio Rocinha, segundo o guia); o texto de Frank et al. não nomeia o rio, e Pontelli (1998, dissertação citada por Rapanos et al., 2022) registra um rio Rocinha em Timbé do Sul. O TCC de Bechtel (2022, UDESC) cita «a paleotoca do Tatu, no município de Timbé do Sul» como a estudada por Frank et al. (2012) e, no trecho lido, não traz paleotoca catalogada pelo autor nesse município. BUSCA DE OUTRAS PALEOTOCAS EM TIMBÉ DO SUL (2026.10.09): em artigos, teses, trabalhos de eventos, na página de geossítios do Geoparque e em reportagens não foi localizada nenhuma outra paleotoca nomeada no município; as reportagens consultadas (NSC Total, 14/09/2024; ND Mais, 22/02/2026 e 11/08/2025; Portal Tela, 28/01/2025) e a matéria da Nature (30/01/2025) tratam só da Toca do Tatu, e o TCC de Bechtel (2022) a cita como a única de Timbé do Sul. Isso não prova que não existam outras: as contagens do Geoparque (ver registro nº 38) não são desagregadas por município. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores de Cezaro et al. (2016) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Valores de Provedan (2019) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar (inclusive a grafia do nome do autor e da comunidade). Valores de Frank et al. (2012), do TCC de Bechtel (2022) e da matéria da Nature lidos em resumo da ferramenta de leitura, não nos PDFs: conferir nos originais antes de citar. </t>
         </is>
       </c>
       <c r="L224" s="5" t="inlineStr">
@@ -20323,12 +20328,18 @@
 https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/
 https://canionsdosul.org/geossitios/?lang=en-us
 https://portaldeperiodicos.animaeducacao.com.br/index.php/memorare_grupep/article/download/3736/2647/9066
-https://doi.org/10.18616/rdsd.v10i1.8551</t>
+https://doi.org/10.18616/rdsd.v10i1.8551
+https://sistemabu.udesc.br/pergamumweb/vinculos/000096/00009610.pdf
+https://bdtd.ibict.br/vufind/Record/UNESC-1_7356230d522f36cf9b2afbb075145fe4
+https://sistemabu.udesc.br/pergamumweb/vinculos/0000a3/0000a31d.pdf
+https://doi.org/10.1038/d41586-025-00216-x
+https://www.cavernas.org.br/wp-content/uploads/2021/02/Espeleo-Tema_v23_n2_087-101.pdf
+https://canionsdosul.org/noticias/reportagem-da-revista-nature-destaca-pesquisa-sobre-as-paleotocas-do-geoparque-caminhos-do-canions-do-sul/</t>
         </is>
       </c>
       <c r="M224" s="5" t="inlineStr">
         <is>
-          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101. | CEZARO, H.S.; SANTOS, M.C.P.; CAMPOS, J.B. 2016. Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu. Revista Memorare, 3(1), 47–72. | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551</t>
+          <t>FRANK, H.T.; OLIVEIRA, L.D.; VICROSKI, F.N. et al. 2012. The complex history of a sandstone-hosted cave in the state of Santa Catarina, Brazil. Espeleo-Tema, 23(2), 87–101. | CEZARO, H.S.; SANTOS, M.C.P.; CAMPOS, J.B. 2016. Possibilidades para uma interpretação de sítios com arte pré-histórica: o caso do sítio Malacara I e Toca do Tatu. Revista Memorare, 3(1), 47–72. | PROVEDAN, B.S. 2019. Roteiros geoturísticos para o município de Timbé do Sul. Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC). | BECHTEL, A.P. 2022. Registro da megafauna pliocênica-quaternária no Geoparque Caminhos dos Cânions do Sul e Irineópolis, SC. Trabalho de Conclusão de Curso (Geografia), Universidade do Estado de Santa Catarina (UDESC). | SANTOS, A.L.; CAMPOS, J.B.; BANDEIRA, D.R. et al. 2024. O patrimônio cultural nos municípios catarinenses integrantes do geoparque mundial da UNESCO Caminhos dos Cânions do Sul. Desenvolvimento Socioeconômico em Debate, 10(1), 86–104. DOI: 10.18616/rdsd.v10i1.8551 | MIRANDA, L. 2025. Capacidade de carga turística aplicada à trilha Portal do Palmiro, Timbé do Sul, SC: Caminhos dos Cânions do Sul Geoparque Mundial da UNESCO. Dissertação de Mestrado (Ciências Ambientais), Universidade do Extremo Sul Catarinense (UNESC). | RODRIGUES, M. 2025. Did giant ice age beasts carve these vast caves in South America? Nature, 637, 1036–1037. DOI: 10.1038/d41586-025-00216-x</t>
         </is>
       </c>
       <c r="N224" s="4" t="n">
@@ -20405,7 +20416,7 @@
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque (quatro municípios catarinenses, entre eles Jacinto Machado e Praia Grande) e descrevem três delas, nenhuma em Jacinto Machado ou Praia Grande; o texto consultado não individualiza cavidades desses dois municípios. A ficha de geossítio nº 1841 do Geossit (Godoy, Binotto &amp; Wildner, 2011, SGB/CPRM), «Paleotocas Xocleng», situa em Jacinto Machado (Engenho Velho, Costão da Pedra) um conjunto de 3 paleotocas; não se sabe se é a ocorrência a que as reportagens se referem — ver registro nº 81, onde essa divergência de localização é discutida. CONTEXTO CULTURAL (2026.10.09): segundo Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural, o Plano Municipal de Cultura de Jacinto Machado (2015) cita as paleotocas — feitas por animais pré-históricos — ocupadas pelos Laklãnõ-Xokleng como sítios arqueológicos da região, sem nomear, localizar ou dimensionar nenhuma; já o de Praia Grande menciona três sítios arqueológicos/geossítios (Pedra Branca, Cânion Itaimbezinho e Cânion Malacara), nenhum deles paleotoca. Isso não confirma nem contraria as reportagens de Praia Grande, porque um plano municipal de cultura não é inventário de paleotocas. CITAÇÃO DE MÍDIA: as duas reportagens (ND Mais, 10/08/2025; CircuitoMT, 11/08/2025), que têm o geólogo do Geoparque G. Simão como único especialista citado, listam paleotocas em cinco municípios do território do Geoparque — Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande (SC) e Cambará do Sul (RS) —, mais de 40 estruturas no total, algumas com até 340 m, e três abertas à visitação. Não informam quantas há em cada município nem nomeiam as de Jacinto Machado e Praia Grande. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. HISTÓRICO DE NOME: o sítio deste registro constava como 'Paleotoca do Engenho Velho'; esse nome não foi encontrado em nenhuma fonte consultada (nem na página de geossítios do Geoparque) e foi substituído por uma descrição genérica. ATUALIZAÇÃO (2026.10.09): «Engenho Velho» (Jacinto Machado) consta como localidade da ficha do SGB «Paleotocas Xocleng» (ver registro nº 81); o nome «Paleotoca do Engenho Velho», como tal, continua sem fonte. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Santos et al. (2024) lidos no texto da cópia pré-publicação do artigo (sem DOI na cópia); a referência bibliográfica foi conferida na página do periódico. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque (quatro municípios catarinenses, entre eles Jacinto Machado e Praia Grande) e descrevem três delas, nenhuma em Jacinto Machado ou Praia Grande; o texto consultado não individualiza cavidades desses dois municípios. A ficha de geossítio nº 1841 do Geossit (Godoy, Binotto &amp; Wildner, 2011, SGB/CPRM), «Paleotocas Xocleng», situa em Jacinto Machado (Engenho Velho, Costão da Pedra) um conjunto de 3 paleotocas; não se sabe se é a ocorrência a que as reportagens se referem — ver registro nº 81, onde essa divergência de localização é discutida. CONTEXTO CULTURAL (2026.10.09): segundo Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural, o Plano Municipal de Cultura de Jacinto Machado (2015) cita as paleotocas — feitas por animais pré-históricos — ocupadas pelos Laklãnõ-Xokleng como sítios arqueológicos da região, sem nomear, localizar ou dimensionar nenhuma; já o de Praia Grande menciona três sítios arqueológicos/geossítios (Pedra Branca, Cânion Itaimbezinho e Cânion Malacara), nenhum deles paleotoca. Isso não confirma nem contraria as reportagens de Praia Grande, porque um plano municipal de cultura não é inventário de paleotocas. COMPLEXO EM PRAIA GRANDE (2026.10.09): um relatório de iniciação científica da UDESC (Souza &amp; Valdati, sem ano na cópia consultada; PROBIC/BIOGEO) descreve o complexo «Furnas do Itamar / Reserva Caeté», em Praia Grande: campo em 19–23/03/2024, três paleotocas já conhecidas e oito novas (duas delas crotovinas, cavidades preenchidas por sedimento), 11 feições no total; o texto lido não traz coordenadas, dimensões nem nomes individuais, e o complexo ainda não tem registro próprio neste banco. Isso sustenta que há paleotocas em Praia Grande, mas não resolve o que as reportagens citam para o município. CITAÇÃO DE MÍDIA: as duas reportagens (ND Mais, 10/08/2025; CircuitoMT, 11/08/2025), que têm o geólogo do Geoparque G. Simão como único especialista citado, listam paleotocas em cinco municípios do território do Geoparque — Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande (SC) e Cambará do Sul (RS) —, mais de 40 estruturas no total, algumas com até 340 m, e três abertas à visitação. Não informam quantas há em cada município nem nomeiam as de Jacinto Machado e Praia Grande. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. HISTÓRICO DE NOME: o sítio deste registro constava como 'Paleotoca do Engenho Velho'; esse nome não foi encontrado em nenhuma fonte consultada (nem na página de geossítios do Geoparque) e foi substituído por uma descrição genérica. ATUALIZAÇÃO (2026.10.09): «Engenho Velho» (Jacinto Machado) consta como localidade da ficha do SGB «Paleotocas Xocleng» (ver registro nº 81); o nome «Paleotoca do Engenho Velho», como tal, continua sem fonte. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Santos et al. (2024) lidos no texto da cópia pré-publicação do artigo (sem DOI na cópia); a referência bibliográfica foi conferida na página do periódico. Valores do relatório de Souza &amp; Valdati lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. </t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr">
@@ -20416,7 +20427,8 @@
 https://doi.org/10.26848/rbgf.v17.3.p1905-1920
 https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418
 https://www.sgb.gov.br/geossit/geossitios/ver/1841 (ficha do SGB, localização em Jacinto Machado)
-https://doi.org/10.18616/rdsd.v10i1.8551</t>
+https://doi.org/10.18616/rdsd.v10i1.8551
+https://udesc.br/arquivos/udesc/id_cpmenu/19200/Pedro_Cau__Rocha_Souza_17266948577003_19200.pdf</t>
         </is>
       </c>
       <c r="M225" s="7" t="inlineStr">
@@ -24186,7 +24198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B917"/>
+  <dimension ref="A1:B935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -33889,16 +33901,20 @@
         </is>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" s="9" t="n"/>
+      <c r="B909" s="9" t="n"/>
+    </row>
     <row r="910">
-      <c r="A910" s="10" t="inlineStr">
+      <c r="A910" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B910" s="9" t="inlineStr"/>
+      <c r="B910" s="9" t="n"/>
     </row>
     <row r="911">
-      <c r="A911" s="11" t="inlineStr">
+      <c r="A911" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -33910,7 +33926,7 @@
       </c>
     </row>
     <row r="912">
-      <c r="A912" s="11" t="inlineStr">
+      <c r="A912" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -33922,7 +33938,7 @@
       </c>
     </row>
     <row r="913">
-      <c r="A913" s="11" t="inlineStr">
+      <c r="A913" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -33934,7 +33950,7 @@
       </c>
     </row>
     <row r="914">
-      <c r="A914" s="11" t="inlineStr">
+      <c r="A914" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -33946,7 +33962,7 @@
       </c>
     </row>
     <row r="915">
-      <c r="A915" s="11" t="inlineStr">
+      <c r="A915" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -33958,7 +33974,7 @@
       </c>
     </row>
     <row r="916">
-      <c r="A916" s="11" t="inlineStr">
+      <c r="A916" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -33970,12 +33986,200 @@
       </c>
     </row>
     <row r="917">
-      <c r="A917" s="11" t="inlineStr">
+      <c r="A917" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="9" t="n"/>
+      <c r="B918" s="9" t="n"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B919" s="9" t="n"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B921" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B923" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B924" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B925" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B926" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B928" s="9" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B929" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B930" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B931" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B932" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B933" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B934" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B935" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S266"/>
+  <dimension ref="A1:S267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>263 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>264 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="K226" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016). O artigo analisa apenas o túnel URU-01-P2 (15 m, sem ramificações) da 'paleotoca Caverna do Rio dos Bugres, URU-01', e informa que a identidade do escavador é incerta (não há fósseis associados); formação e rocha NÃO são informadas. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016). O artigo analisa apenas o túnel URU-01-P2 (15 m, sem ramificações) da 'paleotoca Caverna do Rio dos Bugres, URU-01', e informa que a identidade do escavador é incerta (não há fósseis associados); formação e rocha NÃO são informadas. OUTRA CAVIDADE EM URUBICI (2026.10.09): a «Caverna do Gigante», com marcas de garras de preguiça-gigante, consta no registro nº 272. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L226" s="5" t="inlineStr">
@@ -20920,680 +20920,767 @@
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Fm. Botucatu (arenito) — segundo Sessegolo et al. (2023)</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>Caverna do Gigante (marcas de garras de preguiça-gigante; potencial paleotoca)</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>Caverna do Gigante, topo de morro do Planalto de Lages, Urubici, SC (UTM 22J 630.042 E / 6.903.852 N, SIRGAS 2000; 1.057 m; coordenada publicada, convertida)</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>Sessegolo, G.C., Wosniak, A.P.G., Carlisbino, T., Rocha, L.F.S. &amp; Zakrzewski, D.P. (2023) — "Aspectos físicos e paleontológicos da Caverna do Gigante, Urubici/SC", Anais do 37º Congresso Brasileiro de Espeleologia, Curitiba/PR, 26–29/07/2023, p. 311–319</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>Afiliações dos autores a conferir no original (o artigo cita um laudo espeleológico não publicado de consultoria ambiental, 2022)</t>
+        </is>
+      </c>
+      <c r="J231" s="6" t="inlineStr">
+        <is>
+          <t>Não datada; intervalo convencional deste banco para marcas atribuídas à megafauna extinta (5,33 Ma – 11.700 a)</t>
+        </is>
+      </c>
+      <c r="K231" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: cavidade identificada pelos autores como «potencial paleotoca». Atenção: o trabalho atribui a formação da caverna a piping (erosão subterrânea por fluxo de água) e fala em uso como abrigo por preguiça-gigante; esta ficha NÃO afirma que o mamífero a tenha escavado. Descrita por Sessegolo et al. (2023, Anais do 37º Congresso Brasileiro de Espeleologia, p. 311–319), que estudam a «Caverna do Gigante» para avaliar sua gênese, estabilidade e uso como abrigo de mamíferos do Pleistoceno, com topografia e análises geoespeleológicas e paleontológicas. Segundo o trabalho: fica em Urubici, no topo de um morro do Planalto de Lages, com a planície do rio Vacariano no vale abaixo; coordenadas UTM 630.042 E / 6.903.852 N (zona 22J, datum SIRGAS 2000), cota de 1.057 m (convertidas neste banco para −27,9841 / −49,6777; o ponto cai em Urubici); arenito da Fm. Botucatu (Juro-Cretáceo), avermelhado e friável, com estratificação cruzada tabular de grande porte; conduto único no sentido SW–NE, com quatro entradas (E1 a E4) e uma pequena claraboia (menos de 0,5 m); projeção horizontal de 30,5 m, desenvolvimento linear de 33,8 m, desnível total de 2 m, área de projeção de 63 m² e volume aproximado de 180 m³; cavidade seca, sem espeleotemas, com feições (scallops) que indicam circulação antiga de água em fluxo turbulento. Marcas de garras: sulcos estreitos, curvos, verticais e oblíquos, de cerca de 10 a 22 cm, frequentemente em pares e separados por 1 a 5 cm, sem sulcos espelhados (marcação com um membro por vez); os autores consideram que o provável grupo que marcou as paredes seja o das preguiças-gigantes, e não o dos tatus, porque as marcas em pares são compatíveis com a mão de algumas preguiças extintas e não com a de gliptodontídeos. Sem datação; o intervalo de idade é a convenção deste banco para marcas atribuídas à megafauna extinta (o texto só indica que preguiças terrícolas viveram na América do Sul há pelo menos 12.000 anos). O texto não aplica o icnogênero Megaichnus a esta cavidade. A cavidade não consta no cadastro do CECAV, embora Urubici tenha 32 cavernas cadastradas. Conservação: a visitação ocasional e sem controle já destruiu e alterou características da cavidade; há riscos de erosão do material friável, crescimento da claraboia e desplacamento do teto; os autores recomendam monitoramento semestral, retirada da trilha e da escada que passam sobre a caverna e Plano de Manejo Espeleológico antes de qualquer intervenção, e o estudo buscou embasar a análise de viabilidade de licenciamento ambiental para uso turístico. ATRAÇÃO «CAVERNA E MIRANTE MORRO AZUL» (2026.10.09): em Campestre, Urubici, existe uma atração turística com esse nome; nenhuma publicação científica sobre ela foi localizada, e não foi possível confirmar se corresponde à Caverna do Gigante. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores de Sessegolo et al. (2023) lidos em resumo da ferramenta de leitura, com conferência por trechos literais (coordenadas, entradas, projeção horizontal, desenvolvimento linear, marcas de garras, cadastro e visitação): conferir no original antes de citar. Pino do mapa conforme a coordenada publicada.</t>
+        </is>
+      </c>
+      <c r="L231" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cavernas.org.br/wp-content/uploads/2023/10/37cbe_311-319.pdf</t>
+        </is>
+      </c>
+      <c r="M231" s="7" t="inlineStr">
+        <is>
+          <t>SESSEGOLO, G.C.; WOSNIAK, A.P.G.; CARLISBINO, T. et al. 2023. Aspectos físicos e paleontológicos da Caverna do Gigante, Urubici/SC. Anais do 37º Congresso Brasileiro de Espeleologia, Curitiba/PR, 26–29/07/2023, p. 311–319.</t>
+        </is>
+      </c>
+      <c r="N231" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="O231" s="6" t="inlineStr">
+        <is>
+          <t>Caverna do Gigante (Urubici)</t>
+        </is>
+      </c>
+      <c r="P231" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Fm. Botucatu</t>
+        </is>
+      </c>
+      <c r="Q231" s="6" t="n">
+        <v>-27.9841</v>
+      </c>
+      <c r="R231" s="6" t="n">
+        <v>-49.6777</v>
+      </c>
+      <c r="S231" s="6" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
+      <c r="B232" s="4" t="inlineStr">
         <is>
           <t>Depósitos litorâneos / lacustres</t>
         </is>
       </c>
-      <c r="C231" s="7" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
         <is>
           <t>Tatu-gigante (Propraopus sp. / Glyptodon sp. — osteodermos)</t>
         </is>
       </c>
-      <c r="D231" s="6" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E232" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F231" s="7" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC (localidades imprecisas)</t>
         </is>
       </c>
-      <c r="G231" s="6" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H231" s="7" t="inlineStr">
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>Paula-Couto, C. (1980) — Anais da Academia Brasileira de Ciências 52(3):527–531 [artigo original não consultado; citado em Buchmann et al.]</t>
         </is>
       </c>
-      <c r="I231" s="6" t="inlineStr">
+      <c r="I232" s="4" t="inlineStr">
         <is>
           <t>Museu Nacional / UFRJ (coleção histórica)</t>
         </is>
       </c>
-      <c r="J231" s="6" t="inlineStr">
+      <c r="J232" s="4" t="inlineStr">
         <is>
           <t>ca. 2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K231" s="7" t="inlineStr">
+      <c r="K232" s="5" t="inlineStr">
         <is>
           <t>Classificação: Xenarthra (Cingulata). Primeiro registro de tatu-gigante para SC reportado por Paula-Couto (1980)</t>
         </is>
       </c>
-      <c r="L231" s="7" t="inlineStr">
+      <c r="L232" s="5" t="inlineStr">
         <is>
           <t>Artigo original (Paula-Couto, 1980, Anais ABC 52(3):527-531) não localizado em acesso direto
 citado em: https://www.academia.edu/15400290/Icnof%C3%B3sseis_paleotocas_e_crotovinas_atribu%C3%ADdos_a_mam%C3%ADferos_extintos_no_sudeste_e_sul_do_Brasil
 https://www.scielo.br/j/rbzool/a/3q86RZbNfRbQ7rBMCZHmSpP/?lang=pt</t>
         </is>
       </c>
-      <c r="M231" s="7" t="inlineStr">
+      <c r="M232" s="5" t="inlineStr">
         <is>
           <t>PAULA-COUTO, C. 1980. Anais da Academia Brasileira de Ciências 52(3):527–531 [artigo original não consultado; citado em Buchmann et al.].</t>
         </is>
       </c>
-      <c r="N231" s="6" t="n">
+      <c r="N232" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="O231" s="6" t="inlineStr">
+      <c r="O232" s="4" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC</t>
         </is>
       </c>
-      <c r="P231" s="6" t="inlineStr">
+      <c r="P232" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q231" s="6" t="n">
+      <c r="Q232" s="4" t="n">
         <v>-28.95</v>
       </c>
-      <c r="R231" s="6" t="n">
+      <c r="R232" s="4" t="n">
         <v>-49.45</v>
       </c>
-      <c r="S231" s="6" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+      <c r="S232" s="4" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>Estrutura cenozoica (paleotoca) — rocha encaixante não informada na fonte consultada</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
+      <c r="C233" s="7" t="inlineStr">
         <is>
           <t>Paleotoca da Cavidade Linha Mimosa (icnofóssil de escavação de megafauna)</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D233" s="6" t="inlineStr">
         <is>
           <t>Icnofóssil — paleotoca</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
+      <c r="E233" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
+      <c r="F233" s="7" t="inlineStr">
         <is>
           <t>Cavidade Linha Mimosa, zona rural de Lindóia do Sul, SC (coordenada do município; a da cavidade não foi identificada na fonte consultada)</t>
         </is>
       </c>
-      <c r="G232" s="4" t="inlineStr">
+      <c r="G233" s="6" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H232" s="5" t="inlineStr">
+      <c r="H233" s="7" t="inlineStr">
         <is>
           <t>Budke, A., Lima, G.L. &amp; Carbonera, M. (2020) — "Análise de cavidades naturais presentes no oeste de Santa Catarina: um estudo de caso no município de Lindóia do Sul", Boletim Paranaense de Geociências 77:1–12</t>
         </is>
       </c>
-      <c r="I232" s="4" t="inlineStr">
+      <c r="I233" s="6" t="inlineStr">
         <is>
           <t>UFFS — Campus Chapecó</t>
         </is>
       </c>
-      <c r="J232" s="4" t="inlineStr">
+      <c r="J233" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="K232" s="5" t="inlineStr">
+      <c r="K233" s="7" t="inlineStr">
         <is>
           <t>Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Das três cavidades naturais investigadas na zona rural de Lindóia do Sul, os autores concluíram que a Cavidade Linha Mimosa é uma PALEOTOCA, esculpida por processos biogênicos de mamíferos da megafauna do Pleistoceno; as outras duas não foram atribuídas a megafauna. É o primeiro registro paleontológico do OESTE catarinense neste catálogo. RESSALVA: a fonte consultada publica coordenadas de duas das cavidades, mas não foi possível identificar qual corresponde à Linha Mimosa — usa-se a coordenada central do município.</t>
         </is>
       </c>
-      <c r="L232" s="5" t="inlineStr">
+      <c r="L233" s="7" t="inlineStr">
         <is>
           <t>https://rd.uffs.edu.br/bitstream/prefix/2879/1/BUDKE.pdf
 https://jornalgeograficouffs.wordpress.com/2020/09/02/um-estudo-sobre-cavidades-naturais/</t>
         </is>
       </c>
-      <c r="M232" s="5" t="inlineStr">
+      <c r="M233" s="7" t="inlineStr">
         <is>
           <t>BUDKE, A.; LIMA, G.L.; CARBONERA, M. 2020. Análise de cavidades naturais presentes no oeste de Santa Catarina: um estudo de caso no município de Lindóia do Sul. Boletim Paranaense de Geociências, 77, 1–12.</t>
         </is>
       </c>
-      <c r="N232" s="4" t="n">
+      <c r="N233" s="6" t="n">
         <v>227</v>
       </c>
-      <c r="O232" s="4" t="inlineStr">
+      <c r="O233" s="6" t="inlineStr">
         <is>
           <t>Linha Mimosa (Lindóia do Sul)</t>
         </is>
       </c>
-      <c r="P232" s="4" t="inlineStr">
+      <c r="P233" s="6" t="inlineStr">
         <is>
           <t>Bacia do Paraná — paleotoca cenozoica</t>
         </is>
       </c>
-      <c r="Q232" s="4" t="n">
+      <c r="Q233" s="6" t="n">
         <v>-27.0268</v>
       </c>
-      <c r="R232" s="4" t="n">
+      <c r="R233" s="6" t="n">
         <v>-52.0515</v>
       </c>
-      <c r="S232" s="4" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
+      <c r="S233" s="6" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>Areia marinha rasa pleistocênica (unidade litoestratigráfica não nomeada no trecho consultado)</t>
         </is>
       </c>
-      <c r="C233" s="7" t="inlineStr">
+      <c r="C234" s="5" t="inlineStr">
         <is>
           <t>Escavações biogênicas, provavelmente de Callichirus (crustáceo decápode)</t>
         </is>
       </c>
-      <c r="D233" s="6" t="inlineStr">
+      <c r="D234" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — escavação</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E234" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F233" s="7" t="inlineStr">
+      <c r="F234" s="5" t="inlineStr">
         <is>
           <t>«Perto de Paulo Lopes», SC (expressão do artigo); local exato não informado. Ponto do mapa = centro do município de Paulo Lopes (referência regional)</t>
         </is>
       </c>
-      <c r="G233" s="6" t="inlineStr">
+      <c r="G234" s="4" t="inlineStr">
         <is>
           <t>Não aplicável (observação de campo; sem material coletado informado)</t>
         </is>
       </c>
-      <c r="H233" s="7" t="inlineStr">
+      <c r="H234" s="5" t="inlineStr">
         <is>
           <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
+      <c r="I234" s="4" t="inlineStr">
         <is>
           <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores</t>
         </is>
       </c>
-      <c r="J233" s="6" t="inlineStr">
+      <c r="J234" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno (idade numérica não informada para este afloramento)</t>
         </is>
       </c>
-      <c r="K233" s="7" t="inlineStr">
+      <c r="K234" s="5" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO (segundo o artigo): os autores registram escavações biogênicas em areia marinha rasa de idade pleistocênica, «provavelmente devidas a Callichirus», perto de Paulo Lopes; a atribuição ao decápode é dada como provável e o artigo não descreve nem ilustra as estruturas no trecho consultado. NOTA DE FONTE (2026.10.09): o trecho consultado não nomeia a unidade litoestratigráfica nem dá datação para esse afloramento; o município de Paulo Lopes é a única referência de local. Não há número de tombo, e as escavações não foram atribuídas a um icnogênero.</t>
         </is>
       </c>
-      <c r="L233" s="7" t="inlineStr">
+      <c r="L234" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0001-37652000000200011
 https://www.scielo.br/j/aabc/a/PV3LvmfpkshVK6wWx8WgWSc/?lang=en (Caruso Júnior, Suguio &amp; Nakamura, 2000 — texto integral)</t>
         </is>
       </c>
-      <c r="M233" s="7" t="inlineStr">
+      <c r="M234" s="5" t="inlineStr">
         <is>
           <t>CARUSO JÚNIOR, F.; SUGUIO, K.; NAKAMURA, T. 2000. The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil). Anais da Academia Brasileira de Ciências, 72(2), 257–270. DOI: 10.1590/S0001-37652000000200011</t>
         </is>
       </c>
-      <c r="N233" s="6" t="n">
+      <c r="N234" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="O233" s="6" t="inlineStr">
+      <c r="O234" s="4" t="inlineStr">
         <is>
           <t>Paulo Lopes (areia marinha rasa pleistocênica com escavações)</t>
         </is>
       </c>
-      <c r="P233" s="6" t="inlineStr">
+      <c r="P234" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q233" s="6" t="n">
+      <c r="Q234" s="4" t="n">
         <v>-27.9617</v>
       </c>
-      <c r="R233" s="6" t="n">
+      <c r="R234" s="4" t="n">
         <v>-48.7601</v>
       </c>
-      <c r="S233" s="6" t="inlineStr">
+      <c r="S234" s="4" t="inlineStr">
         <is>
           <t>10.1590/S0001-37652000000200011</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>Notiomastodon platensis (Ameghino, 1888)</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D235" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr">
+      <c r="E235" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
+      <c r="F235" s="7" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (a ~23 m de profundidade, em pesca de arrasto, no fim de março de 2018 — coordenada aproximada)</t>
         </is>
       </c>
-      <c r="G234" s="4" t="inlineStr">
+      <c r="G235" s="6" t="inlineStr">
         <is>
           <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
-      <c r="H234" s="5" t="inlineStr">
+      <c r="H235" s="7" t="inlineStr">
         <is>
           <t>Citação de mídia — Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr">
+      <c r="I235" s="6" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J234" s="4" t="inlineStr">
+      <c r="J235" s="6" t="inlineStr">
         <is>
           <t>ca. 30.000 anos, segundo a reportagem (método de datação não informado)</t>
         </is>
       </c>
-      <c r="K234" s="5" t="inlineStr">
+      <c r="K235" s="7" t="inlineStr">
         <is>
           <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este espécime. Segundo as reportagens, pescadores recolheram no fim de março de 2018 a metade esquerda da mandíbula de um macho adulto, a cerca de 23 m de profundidade, em pesca de arrasto na costa de Sombrio; pesquisadores da Univali a identificaram como Stegomastodon waringi, de cerca de 30 mil anos, com estimativa de ~5 m de comprimento, ~2,5 m de altura e ~3,5 t; fósseis dessa espécie seriam raros em SC e mais comuns no RS. Local de guarda, número de tombo e formação NÃO são informados. HISTÓRICO TAXONÔMICO: a reportagem usa Stegomastodon waringi (Holland, 1920). Mothé, Avilla, Cozzuol &amp; Winck (2012, Quaternary International 276–277:2–7; trabalho de contexto taxonômico, que não trata deste espécime) revisaram os gonfotérios das terras baixas sul-americanas com amostra ampla e concluíram que os caracteres usados para separar S. waringi de S. platensis variam dentro de uma mesma população — há um único gonfotério de terras baixas na América do Sul, sob a combinação Notiomastodon platensis; parte da literatura (Lucas e colaboradores) ainda defende duas espécies, mas a combinação de 2012 é a adotada majoritariamente. O nome do registro segue essa revisão; a reportagem não o usa. CONTEXTO CIENTÍFICO (não trata deste espécime): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam, para a plataforma continental do sul do Brasil (o resumo fala em 'porção mais meridional da costa', com palavra-chave Rio Grande do Sul), restos de Toxodon sp. e um molar de Stegomastodon waringi recolhidos por pescadores a cerca de 20 m de profundidade.</t>
         </is>
       </c>
-      <c r="L234" s="5" t="inlineStr">
+      <c r="L235" s="7" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
 https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
         </is>
       </c>
-      <c r="M234" s="5" t="inlineStr">
+      <c r="M235" s="7" t="inlineStr">
         <is>
           <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Destino Florianópolis (26/04/2018), reportagem «Fóssil de elefante pré-histórico é encontrado em Santa Catarina», e Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), que atribuem a identificação a pesquisadores da Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
         </is>
       </c>
-      <c r="N234" s="4" t="n">
+      <c r="N235" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="O234" s="4" t="inlineStr">
+      <c r="O235" s="6" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P234" s="4" t="inlineStr">
+      <c r="P235" s="6" t="inlineStr">
         <is>
           <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
-      <c r="Q234" s="4" t="n">
+      <c r="Q235" s="6" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R234" s="4" t="n">
+      <c r="R235" s="6" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S234" s="4" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="inlineStr">
+      <c r="S235" s="6" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B235" s="6" t="inlineStr">
+      <c r="B236" s="4" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C235" s="7" t="inlineStr">
+      <c r="C236" s="5" t="inlineStr">
         <is>
           <t>Lestodon armatus Gervais, 1855</t>
         </is>
       </c>
-      <c r="D235" s="6" t="inlineStr">
+      <c r="D236" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — mamífero</t>
         </is>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E236" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F235" s="7" t="inlineStr">
+      <c r="F236" s="5" t="inlineStr">
         <is>
           <t>Plataforma continental entre Passo de Torres e Araranguá, SC (redes de arrasto de camarão — coordenada aproximada)</t>
         </is>
       </c>
-      <c r="G235" s="6" t="inlineStr">
+      <c r="G236" s="4" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras, SC</t>
         </is>
       </c>
-      <c r="H235" s="7" t="inlineStr">
+      <c r="H236" s="5" t="inlineStr">
         <is>
           <t>Citação de mídia — Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)</t>
         </is>
       </c>
-      <c r="I235" s="6" t="inlineStr">
+      <c r="I236" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J235" s="6" t="inlineStr">
+      <c r="J236" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos antes do presente, segundo a divulgação (método não informado)</t>
         </is>
       </c>
-      <c r="K235" s="7" t="inlineStr">
+      <c r="K236" s="5" t="inlineStr">
         <is>
           <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica. Segundo a divulgação, fósseis de lestodonte (Lestodon armatus) saíram de redes de arrasto de camarão na plataforma continental entre Passo de Torres e Araranguá, pertencem à 'formação Laguna-Barreira' e são 'datados de cerca de 30 mil anos antes do presente'; a equipe do museu encontrou 'ao menos dois' lestodontes, 'tratando-se do primeiro registro desta espécie no Estado'. A altura (~4,5 m) e o peso (~3 t) citados descrevem a espécie em geral, não o exemplar. O esqueleto montado está exposto no Museu Oceanográfico Univali (Balneário Piçarras). Não são informados identificador, tombo, data da coleta nem método de datação.</t>
         </is>
       </c>
-      <c r="L235" s="7" t="inlineStr">
+      <c r="L236" s="5" t="inlineStr">
         <is>
           <t>https://novomomento.com.br/preguica-gigante-museu-oceanografico/
 https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx (página original; indisponível em 08/10/2026)</t>
         </is>
       </c>
-      <c r="M235" s="7" t="inlineStr">
+      <c r="M236" s="5" t="inlineStr">
         <is>
           <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)]</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
+      <c r="N236" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="O235" s="6" t="inlineStr">
+      <c r="O236" s="4" t="inlineStr">
         <is>
           <t>Plataforma continental Passo de Torres–Araranguá</t>
         </is>
       </c>
-      <c r="P235" s="6" t="inlineStr">
+      <c r="P236" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q235" s="6" t="n">
+      <c r="Q236" s="4" t="n">
         <v>-29.28</v>
       </c>
-      <c r="R235" s="6" t="n">
+      <c r="R236" s="4" t="n">
         <v>-49.55</v>
-      </c>
-      <c r="S235" s="6" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>Pleistoceno Superior</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>Plataforma continental (formação não informada na reportagem)</t>
-        </is>
-      </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
-        <is>
-          <t>Vertebrado — mamífero</t>
-        </is>
-      </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
-        </is>
-      </c>
-      <c r="G236" s="4" t="inlineStr">
-        <is>
-          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
-        </is>
-      </c>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
-        </is>
-      </c>
-      <c r="I236" s="4" t="inlineStr">
-        <is>
-          <t>Univali</t>
-        </is>
-      </c>
-      <c r="J236" s="4" t="inlineStr">
-        <is>
-          <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
-        </is>
-      </c>
-      <c r="K236" s="5" t="inlineStr">
-        <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
-        </is>
-      </c>
-      <c r="L236" s="5" t="inlineStr">
-        <is>
-          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
-        </is>
-      </c>
-      <c r="M236" s="5" t="inlineStr">
-        <is>
-          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
-        </is>
-      </c>
-      <c r="N236" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="O236" s="4" t="inlineStr">
-        <is>
-          <t>Costa de Sombrio (plataforma continental)</t>
-        </is>
-      </c>
-      <c r="P236" s="4" t="inlineStr">
-        <is>
-          <t>Plataforma Continental (formação não informada na reportagem)</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="n">
-        <v>-29.22</v>
-      </c>
-      <c r="R236" s="4" t="n">
-        <v>-49.5</v>
       </c>
       <c r="S236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
+          <t>Pleistoceno Superior</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>Plataforma continental (formação não informada na reportagem)</t>
+        </is>
+      </c>
+      <c r="C237" s="7" t="inlineStr">
+        <is>
+          <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t>Vertebrado — mamífero</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
+        </is>
+      </c>
+      <c r="H237" s="7" t="inlineStr">
+        <is>
+          <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
+        </is>
+      </c>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>Univali</t>
+        </is>
+      </c>
+      <c r="J237" s="6" t="inlineStr">
+        <is>
+          <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
+        </is>
+      </c>
+      <c r="K237" s="7" t="inlineStr">
+        <is>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
+        </is>
+      </c>
+      <c r="L237" s="7" t="inlineStr">
+        <is>
+          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
+        </is>
+      </c>
+      <c r="M237" s="7" t="inlineStr">
+        <is>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
+        </is>
+      </c>
+      <c r="N237" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="O237" s="6" t="inlineStr">
+        <is>
+          <t>Costa de Sombrio (plataforma continental)</t>
+        </is>
+      </c>
+      <c r="P237" s="6" t="inlineStr">
+        <is>
+          <t>Plataforma Continental (formação não informada na reportagem)</t>
+        </is>
+      </c>
+      <c r="Q237" s="6" t="n">
+        <v>-29.22</v>
+      </c>
+      <c r="R237" s="6" t="n">
+        <v>-49.5</v>
+      </c>
+      <c r="S237" s="6" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="B238" s="4" t="inlineStr">
         <is>
           <t>Fm. Rio Bonito (segundo o comunicado da UDESC e a reportagem do ND Mais)</t>
         </is>
       </c>
-      <c r="C237" s="7" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
         <is>
           <t>Paleotoca Amaral de Baixo (icnofóssil de escavação — provável tatu extinto)</t>
         </is>
       </c>
-      <c r="D237" s="6" t="inlineStr">
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — paleotoca</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E238" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
         <is>
           <t>Localidade Rio Amaral Gruta, Lauro Müller, SC (coordenada do município)</t>
         </is>
       </c>
-      <c r="G237" s="6" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr">
         <is>
           <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>Citação de mídia — UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF); Citação de mídia — ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)</t>
         </is>
       </c>
-      <c r="I237" s="6" t="inlineStr">
+      <c r="I238" s="4" t="inlineStr">
         <is>
           <t>UDESC — Laboratório de Geografia Física (LGEF), grupo BioGeo, FAED (segundo o comunicado da UDESC); equipe técnica do Geoparque (segundo o ND Mais)</t>
         </is>
       </c>
-      <c r="J237" s="6" t="inlineStr">
+      <c r="J238" s="4" t="inlineStr">
         <is>
           <t>Não datada; a reportagem fala em animais que viveram 'há cerca de 10 mil anos'</t>
         </is>
       </c>
-      <c r="K237" s="7" t="inlineStr">
+      <c r="K238" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
-      <c r="L237" s="7" t="inlineStr">
+      <c r="L238" s="5" t="inlineStr">
         <is>
           <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
 https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
-      <c r="M237" s="7" t="inlineStr">
+      <c r="M238" s="5" t="inlineStr">
         <is>
           <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
         </is>
       </c>
-      <c r="N237" s="6" t="n">
+      <c r="N238" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="O237" s="6" t="inlineStr">
+      <c r="O238" s="4" t="inlineStr">
         <is>
           <t>Lauro Müller</t>
         </is>
       </c>
-      <c r="P237" s="6" t="inlineStr">
+      <c r="P238" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Rio Bonito</t>
         </is>
       </c>
-      <c r="Q237" s="6" t="n">
+      <c r="Q238" s="4" t="n">
         <v>-28.4047</v>
       </c>
-      <c r="R237" s="6" t="n">
+      <c r="R238" s="4" t="n">
         <v>-49.3811</v>
       </c>
-      <c r="S237" s="6" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+      <c r="S238" s="4" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B238" s="4" t="inlineStr">
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada)</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
+      <c r="C239" s="7" t="inlineStr">
         <is>
           <t>Pólen, esporos e carvão de turfeira da Serra do Tabuleiro (testemunho Ciama 2; ~39.700 anos)</t>
         </is>
       </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos) e partículas de carvão</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
         <is>
           <t>Turfeira «Ciama 2», Parque Estadual da Serra do Tabuleiro, SC (27°53′48,46″ S; 48°52′5,33″ O; 860 m de altitude); testemunho de 169 cm coletado em 2005 com amostrador Russian</t>
         </is>
       </c>
-      <c r="G238" s="4" t="inlineStr">
+      <c r="G239" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>Jeske-Pieruschka, V., Pillar, V.D., De Oliveira, M.A.T. &amp; Behling, H. (2013) — "New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro", Vegetation History and Archaeobotany 22(4):299–314, DOI 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
-      <c r="I238" s="4" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Universität Göttingen (projeto de doutorado de V. Jeske-Pieruschka, sob H. Behling, segundo a página do projeto)</t>
         </is>
       </c>
-      <c r="J238" s="4" t="inlineStr">
+      <c r="J239" s="6" t="inlineStr">
         <is>
           <t>Últimos ~39.720 anos 14C AP (base extrapolada a 168 cm) até 2005 d.C. — do Pleistoceno Superior (glacial) ao Holoceno</t>
         </is>
       </c>
-      <c r="K238" s="5" t="inlineStr">
+      <c r="K239" s="7" t="inlineStr">
         <is>
           <t>Classificação: microfósseis (pólen e esporos) e partículas de carvão de um testemunho de turfeira — registro paleoambiental quaternário, não um fóssil em rocha. Segundo o artigo, o testemunho (169 cm; oito datações AMS) cobre cerca de 39.720 anos. Resultados dos autores: campos (gramíneas subtropicais) cobriram extensas áreas do planalto durante todo o período glacial registrado, o que eles ligam a clima frio e seco; a floresta pluvial atlântica começou a se espalhar pelas encostas por volta de 10.400 anos cal AP, com clima mais quente e úmido; a floresta de araucária surge no Holoceno tardio (a partir de ~2.160 anos cal AP, com máximo após ~300 anos cal AP); e há abertura da floresta por perturbação recente (inclusive extração de madeira), com avanço dos campos entre 1940 e 2005. Fogo ausente no glacial e comum entre ~10.400 e ~3.600 anos cal AP, provavelmente por ameríndios (inferência dos autores). Os autores concluem que a serra costeira do Tabuleiro não foi refúgio glacial para táxons da floresta pluvial atlântica no Último Máximo Glacial. LOCALIZAÇÃO (2026.10.09): o artigo dá o Parque Estadual da Serra do Tabuleiro e as coordenadas acima, mas não nomeia o município. O parque abrange Florianópolis, Palhoça, Santo Amaro da Imperatriz, Águas Mornas, São Bonifácio, São Martinho, Imaruí e Paulo Lopes (Wikipédia). A etiqueta «São Bonifácio (região)» é uma derivação do compilador: as coordenadas informadas caem no polígono desse município na malha municipal do site; confirme com o mapa oficial antes de citar o município. NOTA DE FONTE: consultados a página do artigo no Springer (resumo e trechos do texto) e a cópia do resumo no Paperity; tabela de datações e diagramas não foram acessados. Número de tombo e depositário não se aplicam/não foram informados.</t>
         </is>
       </c>
-      <c r="L238" s="5" t="inlineStr">
+      <c r="L239" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/s00334-012-0382-y (Jeske-Pieruschka et al., 2013 — página do artigo)
 https://paperity.org/p/6235978/new-insights-into-vegetation-climate-and-fire-history-of-southern-brazil-revealed-by-a-40 (cópia do resumo)
@@ -21601,93 +21688,93 @@
 https://en.wikipedia.org/wiki/Serra_do_Tabuleiro_State_Park (municípios do parque)</t>
         </is>
       </c>
-      <c r="M238" s="5" t="inlineStr">
+      <c r="M239" s="7" t="inlineStr">
         <is>
           <t>JESKE-PIERUSCHKA, V.; PILLAR, V.D.; DE OLIVEIRA, M.A.T. et al. 2013. New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro. Vegetation History and Archaeobotany, 22(4), 299–314. DOI: 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N239" s="6" t="n">
         <v>254</v>
       </c>
-      <c r="O238" s="4" t="inlineStr">
+      <c r="O239" s="6" t="inlineStr">
         <is>
           <t>Serra do Tabuleiro (turfeira Ciama 2)</t>
         </is>
       </c>
-      <c r="P238" s="4" t="inlineStr">
+      <c r="P239" s="6" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q238" s="4" t="n">
+      <c r="Q239" s="6" t="n">
         <v>-27.8968</v>
       </c>
-      <c r="R238" s="4" t="n">
+      <c r="R239" s="6" t="n">
         <v>-48.8681</v>
       </c>
-      <c r="S238" s="4" t="inlineStr">
+      <c r="S239" s="6" t="inlineStr">
         <is>
           <t>10.1007/s00334-012-0382-y</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="6" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B240" s="4" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C239" s="7" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira do Morro da Igreja (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="D240" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E240" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
         <is>
           <t>Turfeira de altitude (cerca de 1.800 m) na borda do Parque Nacional de São Joaquim, a 300 m a oeste do ponto mais alto do Morro da Igreja, Urubici, SC (Behling, 1995; ponto do mapa aproximado, no próprio morro: ver observações)</t>
         </is>
       </c>
-      <c r="G239" s="6" t="inlineStr">
+      <c r="G240" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H239" s="7" t="inlineStr">
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I240" s="4" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J239" s="6" t="inlineStr">
+      <c r="J240" s="4" t="inlineStr">
         <is>
           <t>Perfil de 144 cm: base datada em 10.200 ± 275 anos 14C AP até o presente (60 ± 120 anos AP aos 40–44 cm, idade que o autor atribui a influência de raízes atuais); idades não calibradas</t>
         </is>
       </c>
-      <c r="K239" s="7" t="inlineStr">
+      <c r="K240" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 30 × 40 m numa encosta voltada a oeste, de leve inclinação, a cerca de 1.800 m, na borda do Parque Nacional de São Joaquim e 300 m a oeste do ponto mais alto do morro, junto ao limite entre o planalto e as terras baixas; o autor a descreve nos campos da região alta, com floresta nebular nas encostas íngremes próximas. Amostragem em 04/12/1989 (amostrador Dachnowski); perfil de turfa de 144 cm sobre rocha (149 cm); contagem mínima de 1.215 grãos de pólen por amostra (média de 2.353). Duas datações por 14C (Laboratório de Hanover, Hv 17557 e Hv 17558): 60 ± 120 anos AP aos 40–44 cm e 10.200 ± 275 anos AP aos 140–144 cm, na base do perfil; idades não calibradas. RESULTADO: do início do perfil (~10.200 anos AP) até cerca de 1.000 anos AP os campos dominam o pólen; a floresta de araucária (Araucaria angustifolia, de 1% a 10% do pólen) se expande sobre os campos na zona 4a, que o autor estima em não mais de ~1.000 anos; a zona 4b (cerca de 100 anos) traz sinais de ação humana — queda da araucária (extração de madeira), grãos de Pinus e um de Zea mays — e o desaparecimento de Weinmannia entre 8 e 16 cm, que o autor atribui provavelmente ao grande incêndio de 1951 na floresta nebular da Serra Geral. Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco; esta turfeira registra apenas o fim dessa fase. LOCALIZAÇÃO (2026.10.09): o artigo dá o morro em 28°11′ S, 49°52′ O, «25 km a sudeste da vila de Urubici»; essas coordenadas caem, na malha municipal deste site, em São Joaquim (cerca de 30 km a oés-sudoeste de Urubici), o que não combina com «sudeste» nem com o morro conhecido (Wikipédia: 28°07′30″ S, 49°28′28″ O, 1.822 m, em Urubici). Possível erro de impressão no artigo, não verificado; o pino segue no próprio morro e é apenas aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
         </is>
       </c>
-      <c r="L239" s="7" t="inlineStr">
+      <c r="L240" s="5" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -21695,93 +21782,93 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M239" s="7" t="inlineStr">
+      <c r="M240" s="5" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N239" s="6" t="n">
+      <c r="N240" s="4" t="n">
         <v>255</v>
       </c>
-      <c r="O239" s="6" t="inlineStr">
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>Morro da Igreja (Urubici)</t>
         </is>
       </c>
-      <c r="P239" s="6" t="inlineStr">
+      <c r="P240" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q239" s="6" t="n">
+      <c r="Q240" s="4" t="n">
         <v>-28.125</v>
       </c>
-      <c r="R239" s="6" t="n">
+      <c r="R240" s="4" t="n">
         <v>-49.4744</v>
       </c>
-      <c r="S239" s="6" t="inlineStr">
+      <c r="S240" s="4" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
+      <c r="C241" s="7" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira da Serra do Rio do Rastro (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
+      <c r="F241" s="7" t="inlineStr">
         <is>
           <t>Turfeira de altitude a 1.420 m, perto da rodovia SC-438, na Serra do Rio Rastro (grafia de Behling, 1995; a serra é conhecida como Serra do Rio do Rastro), entre Lauro Müller e Bom Jardim da Serra, SC; 28°23′ S, 49°33′ O segundo o artigo (precisão de minuto, ~2 km)</t>
         </is>
       </c>
-      <c r="G240" s="4" t="inlineStr">
+      <c r="G241" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="H241" s="7" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I240" s="4" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J240" s="4" t="inlineStr">
+      <c r="J241" s="6" t="inlineStr">
         <is>
           <t>Perfil de 223 cm: base datada em 11.210 ± 385 anos 14C AP até o presente (6.410 ± 190 aos 150–155 cm; 2.385 ± 225 aos 74–79 cm); idades não calibradas</t>
         </is>
       </c>
-      <c r="K240" s="5" t="inlineStr">
+      <c r="K241" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo do registro nº 255. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 50 × 50 m numa pequena depressão rasa junto à escarpa íngreme da Serra Geral, a 1.420 m (400 m abaixo do Morro da Igreja), perto da rodovia SC-438 — o artigo diz «11 km a oeste da vila de Bom Jardim da Serra» e dá 28°23′ S, 49°33′ O. Amostragem em 04/05/1989 e 05/12/1989; perfil de 223 cm (argila sobre rocha abaixo disso); contagem mínima de 1.203 grãos por amostra (média de 5.917). Três datações por 14C: 2.385 ± 225 anos AP (74–79 cm, limite das zonas 2c e 3), 6.410 ± 190 (150–155 cm, perto da base da zona 2ab) e 11.210 ± 385 (215–220 cm, base do perfil); idades não calibradas. O autor nota que 6.410 anos AP é bem mais novo que os ~9.000 esperados no limite Pleistoceno–Holoceno, e explica a diferença por sedimentação extremamente lenta ou por um hiato. RESULTADO: na base (~11.200 anos AP) 93% do pólen é de campos (Poaceae ~55%, Cyperaceae ~15%, Asteraceae ~10%), sem floresta de araucária no local e com a floresta nebular ausente ou pouco representada; no Holoceno inicial e médio os campos seguem dominando (campo sujo mais desenvolvido na zona 2ab), com mudanças na floresta pluvial atlântica (queda de Myrtaceae, alta de Alchornea e Urticales); na zona 3 (7–76 cm) a araucária sobe de 1% a 5% e os campos descem de 89% a 83%, possivelmente com florestas de galeria ao longo dos rios; na zona 4a (0–7 cm) a araucária aumenta fortemente, como no Morro da Igreja. Segundo o resumo do artigo, a dominância dos campos continuou até cerca de 1.000 anos AP nas turfeiras do Morro da Igreja e da Serra do Rio Rastro. O autor aponta uma discrepância ainda não explicada entre a idade do limite 2c/3 aqui (2.385 ± 225) e a do início da zona 3 na Serra da Boa Vista (3.460 ± 195). LOCALIZAÇÃO (2026.10.09): pino movido para as coordenadas impressas no artigo (28°23′ S, 49°33′ O), que na malha deste site caem em Bom Jardim da Serra, a menos de 1 km da divisa com Lauro Müller (por isso o município segue como «região»); antes, o pino era o ponto da serra segundo a Wikipédia, em Lauro Müller. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
         </is>
       </c>
-      <c r="L240" s="5" t="inlineStr">
+      <c r="L241" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -21789,93 +21876,93 @@
 https://en.wikipedia.org/wiki/Serra_do_Rio_do_Rastro (localização da serra)</t>
         </is>
       </c>
-      <c r="M240" s="5" t="inlineStr">
+      <c r="M241" s="7" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N241" s="6" t="n">
         <v>256</v>
       </c>
-      <c r="O240" s="4" t="inlineStr">
+      <c r="O241" s="6" t="inlineStr">
         <is>
           <t>Serra do Rio do Rastro (Lauro Müller / Bom Jardim da Serra)</t>
         </is>
       </c>
-      <c r="P240" s="4" t="inlineStr">
+      <c r="P241" s="6" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q240" s="4" t="n">
+      <c r="Q241" s="6" t="n">
         <v>-28.3833</v>
       </c>
-      <c r="R240" s="4" t="n">
+      <c r="R241" s="6" t="n">
         <v>-49.55</v>
       </c>
-      <c r="S240" s="4" t="inlineStr">
+      <c r="S241" s="6" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="6" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C241" s="7" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira da Serra da Boa Vista (campos, floresta pluvial atlântica e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E242" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F241" s="7" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
         <is>
           <t>Turfeira de altitude a 1.160 m, nos contrafortes nordeste da Serra Geral, perto da BR-282 e a 10 km a leste da vila de São Leonardo (Behling, 1995); 27°42′ S, 49°09′ O segundo o artigo (precisão de minuto). O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner (por isso «região»)</t>
         </is>
       </c>
-      <c r="G241" s="6" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H241" s="7" t="inlineStr">
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I242" s="4" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J241" s="6" t="inlineStr">
+      <c r="J242" s="4" t="inlineStr">
         <is>
           <t>Perfil de 140 cm: base ≈ 13.900–14.100 anos 14C AP (13.905 ± 295 aos 131–135 cm; 14.105 ± 510 aos 61–65 cm), 6.930 ± 195 aos 45–50 cm e 3.460 ± 185 aos 31–35 cm (± 195 no texto); idades não calibradas</t>
         </is>
       </c>
-      <c r="K241" s="7" t="inlineStr">
+      <c r="K242" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo dos registros nº 255 e 256. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 10–16 × 40 m numa pequena encosta de inclinação leste–oeste relativamente íngreme, atrás de uma escarpa de 3 m, a 1.160 m, nos contrafortes nordeste da Serra Geral, «não longe da BR 282» e a 10 km a leste da vila de São Leonardo; 27°42′ S, 49°09′ O. Amostragem em 03/12/1989; perfil de 140 cm (subsolo rochoso aos 140 cm); contagem mínima de 979 grãos por amostra (média de 3.683). Quatro datações por 14C (Hv 17563–17566): 3.460 ± 185 anos AP (31–35 cm; ± 195 no texto), 6.930 ± 195 (45–50 cm), 14.105 ± 510 (61–65 cm) e 13.905 ± 295 (131–135 cm); idades não calibradas. O autor nota que 6.930 anos AP, no início do Holoceno, é mais novo que o esperado, e explica por sedimentação extremamente lenta ou por um hiato. RESULTADO: a turfeira está na zona de campos. Na base (zona 1a, ~14.000 anos AP) cerca de 90% do pólen é de campos (Poaceae ~60%), com os táxons da floresta de araucária raros — a araucária ficava nos vales — e Myrtaceae dominando a planície costeira; a zona 1c é estimada, por taxa de sedimentação constante, em ~10.000–10.500 anos AP; na zona 2 (6.930 anos AP) há florestação intensa, com Weinmannia paulliniifolia (floresta pluvial atlântica) chegando a 50% do pólen; na zona 3 (a partir de 3.460 anos AP) os campos avançam e Ilex, Symplocos e Clethra, da floresta de araucária, têm a maior representação, o que o autor atribui a clima mais frio; nas zonas 4a e 4b a floresta pluvial atlântica (Alchornea, Urticales) se expande, a araucária fica abaixo de 2% do pólen (contra 10% no Morro da Igreja e na Serra do Rio Rastro) e a 4b (cerca de 100 anos) mostra ação humana (Pinus de plantios modernos, desmatamento de araucária). Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
         </is>
       </c>
-      <c r="L241" s="7" t="inlineStr">
+      <c r="L242" s="5" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -21883,303 +21970,216 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M241" s="7" t="inlineStr">
+      <c r="M242" s="5" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N241" s="6" t="n">
+      <c r="N242" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="O241" s="6" t="inlineStr">
+      <c r="O242" s="4" t="inlineStr">
         <is>
           <t>Serra da Boa Vista (Rancho Queimado / Alfredo Wagner)</t>
         </is>
       </c>
-      <c r="P241" s="6" t="inlineStr">
+      <c r="P242" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q241" s="6" t="n">
+      <c r="Q242" s="4" t="n">
         <v>-27.7</v>
       </c>
-      <c r="R241" s="6" t="n">
+      <c r="R242" s="4" t="n">
         <v>-49.15</v>
       </c>
-      <c r="S241" s="6" t="inlineStr">
+      <c r="S242" s="4" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
+      <c r="C243" s="7" t="inlineStr">
         <is>
           <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
         </is>
       </c>
-      <c r="D242" s="4" t="inlineStr">
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
+      <c r="F243" s="7" t="inlineStr">
         <is>
           <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
         </is>
       </c>
-      <c r="G242" s="4" t="inlineStr">
+      <c r="G243" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="H243" s="7" t="inlineStr">
         <is>
           <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — "Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages", Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
         </is>
       </c>
-      <c r="I242" s="4" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>IGc-USP; UFPR</t>
         </is>
       </c>
-      <c r="J242" s="4" t="inlineStr">
+      <c r="J243" s="6" t="inlineStr">
         <is>
           <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
         </is>
       </c>
-      <c r="K242" s="5" t="inlineStr">
+      <c r="K243" s="7" t="inlineStr">
         <is>
           <t>Classificação: gastrópode incrustante. Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
         </is>
       </c>
-      <c r="L242" s="5" t="inlineStr">
+      <c r="L243" s="7" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio075/sitio075.pdf
 https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
         </is>
       </c>
-      <c r="M242" s="5" t="inlineStr">
+      <c r="M243" s="7" t="inlineStr">
         <is>
           <t>ANGULO, R.J.; GIANNINI, P.C.F.; SUGUIO, K. et al. 1999. Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages. Marine Geology, 159, 323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222.</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N243" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="O242" s="4" t="inlineStr">
+      <c r="O243" s="6" t="inlineStr">
         <is>
           <t>Costões Laguna–Imbituba</t>
         </is>
       </c>
-      <c r="P242" s="4" t="inlineStr">
+      <c r="P243" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
         </is>
       </c>
-      <c r="Q242" s="4" t="n">
+      <c r="Q243" s="6" t="n">
         <v>-28.42</v>
       </c>
-      <c r="R242" s="4" t="n">
+      <c r="R243" s="6" t="n">
         <v>-48.74</v>
       </c>
-      <c r="S242" s="4" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="6" t="inlineStr">
+      <c r="S243" s="6" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B244" s="4" t="inlineStr">
         <is>
           <t>Depósitos turfosos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C243" s="7" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos (54 morfotipos: fungos, algas, briófitas, pteridófitas, pólen de gimnospermas e outros)</t>
         </is>
       </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="D244" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E244" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F243" s="7" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
         <is>
           <t>Duas seções com turfa na Planície Costeira sul-catarinense, nos municípios de Santa Rosa do Sul e São João do Sul, SC (nomes das turfeiras e coordenadas não informados no resumo consultado; ponto aproximado, entre os centros dos dois municípios)</t>
         </is>
       </c>
-      <c r="G243" s="6" t="inlineStr">
+      <c r="G244" s="4" t="inlineStr">
         <is>
           <t>Não informado no resumo consultado</t>
         </is>
       </c>
-      <c r="H243" s="7" t="inlineStr">
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Souza, P.A. &amp; Neves, P.C.P. (2012) — "Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil", Acta Botanica Brasilica 26(1):20–37, DOI 10.1590/S0102-33062012000100004</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I244" s="4" t="inlineStr">
         <is>
           <t>UFRGS (Porto Alegre) e Universidade Luterana do Brasil (Canoas) — afiliações dos autores</t>
         </is>
       </c>
-      <c r="J243" s="6" t="inlineStr">
+      <c r="J244" s="4" t="inlineStr">
         <is>
           <t>ca. 7.908 anos AP (base do testemunho de Santa Rosa do Sul) até o presente — 0,0079 Ma</t>
         </is>
       </c>
-      <c r="K243" s="7" t="inlineStr">
+      <c r="K244" s="5" t="inlineStr">
         <is>
           <t>Segundo o resumo, o estudo apresenta resultados palinológicos de duas seções com turfa na Planície Costeira sul-catarinense, em Santa Rosa do Sul e São João do Sul; uma amostra basal do testemunho de Santa Rosa do Sul foi datada em 7908 ± 33 anos AP (Holoceno Inferior; o título cita ± 30). Foram descritos e ilustrados 54 palinomorfos: 21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 pólens de gimnospermas e 7 outros (uma cápsula de briófita, 4 fragmentos de invertebrados e 2 palinoforaminíferos indeterminados). Nomes das turfeiras, coordenadas, espessura dos testemunhos e táxons individuais NÃO constam no resumo consultado (o texto integral não foi aberto); por isso o ponto no mapa é aproximado. REGISTRO NOVO (2026.09.14), com fonte própria; não deve ser confundido com o nº 040 (Lagoa do Sombrio), removido em 2026.09.13. VERIFICAÇÃO (2026.10.09): o resumo de Cancelli, Souza &amp; Dehnhardt (XIII ABEQUA) descreve o testemunho de Santa Rosa do Sul como PCSC-1 (29°10'42"S, 49°44'58"W, mata paludial próxima à Lagoa do Sombrio, 570 cm, base datada em 7.908 ± 33 anos cal AP) e informa 112 palinomorfos ao todo — 58 de pólen de angiospermas mais os 54 palinomorfos não-pólen (21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 gimnospermas e 7 outros) que o artigo de 2012 descreve e ilustra. A microfauna do mesmo testemunho está no registro nº 264. O ponto deste registro continua aproximado porque ele cobre também a seção de São João do Sul, cujo local não foi informado.</t>
         </is>
       </c>
-      <c r="L243" s="7" t="inlineStr">
+      <c r="L244" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0102-33062012000100004
 https://paperity.org/p/187352977/fungos-criptogamas-e-outros-palinomorfos-holocenicos-7908-30-anos-ap-atual-da-planicie
 https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
-      <c r="M243" s="7" t="inlineStr">
+      <c r="M244" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; SOUZA, P.A.; NEVES, P.C.P. 2012. Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil. Acta Botanica Brasilica, 26(1), 20–37. DOI: 10.1590/S0102-33062012000100004</t>
         </is>
       </c>
-      <c r="N243" s="6" t="n">
+      <c r="N244" s="4" t="n">
         <v>233</v>
       </c>
-      <c r="O243" s="6" t="inlineStr">
+      <c r="O244" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira sul-catarinense (turfeiras de Santa Rosa do Sul e São João do Sul)</t>
         </is>
       </c>
-      <c r="P243" s="6" t="inlineStr">
+      <c r="P244" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q243" s="6" t="n">
+      <c r="Q244" s="4" t="n">
         <v>-29.1613</v>
       </c>
-      <c r="R243" s="6" t="n">
+      <c r="R244" s="4" t="n">
         <v>-49.7767</v>
       </c>
-      <c r="S243" s="6" t="inlineStr">
+      <c r="S244" s="4" t="inlineStr">
         <is>
           <t>10.1590/S0102-33062012000100004</t>
         </is>
       </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>Sedimentos holocênicos da Lagoa do Peri (unidade litoestratigráfica não informada no resumo)</t>
-        </is>
-      </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>Diatomáceas holocênicas da Lagoa do Peri (44 táxons; Aulacoseira ambigua, Paralia sulcata)</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>Microfóssil — diatomáceas</t>
-        </is>
-      </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>Lagoa do Peri, Florianópolis, SC (27°43′30″S, 48°32′30″W); testemunho coletado com amostrador de Livingstone, da superfície a 2,10 m</t>
-        </is>
-      </c>
-      <c r="G244" s="4" t="inlineStr">
-        <is>
-          <t>Não informado na fonte consultada</t>
-        </is>
-      </c>
-      <c r="H244" s="5" t="inlineStr">
-        <is>
-          <t>Saupe, A.C. &amp; Mosimann, R.M.S. (2003) — "Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil", Insula 32:33 [resumo de uma página]</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="inlineStr">
-        <is>
-          <t>Tecpar (Curitiba) e UFSC (Florianópolis) — afiliações das autoras</t>
-        </is>
-      </c>
-      <c r="J244" s="4" t="inlineStr">
-        <is>
-          <t>Holoceno (o resumo cita o método do 14C, mas não informa idades)</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: microfóssil silicoso (diatomáceas em sedimento holocênico). Saupe &amp; Mosimann (2003) analisaram 26 amostras de um testemunho da Lagoa do Peri, da superfície a 2,10 m, e identificaram 44 táxons específicos e infraespecíficos, de 30 gêneros e 25 famílias; Triceratiaceae e Plagiogrammaceae são as famílias mais bem representadas (três gêneros cada) e Pinnularia, o gênero mais rico (cinco espécies). Aulacoseira ambigua é abundante nas camadas superiores e indica o ambiente atual, de água doce; Paralia sulcata é abundante nas camadas profundas, o que as autoras associam à origem marinha original da lagoa. O resumo não traz a lista completa de espécies, idades, depositário nem número de tombo; a fonte é um resumo de uma página.</t>
-        </is>
-      </c>
-      <c r="L244" s="5" t="inlineStr">
-        <is>
-          <t>https://periodicos.ufsc.br/index.php/insula/article/view/21194 (Saupe &amp; Mosimann, 2003 — resumo)</t>
-        </is>
-      </c>
-      <c r="M244" s="5" t="inlineStr">
-        <is>
-          <t>SAUPE, A.C.; MOSIMANN, R.M.S. 2003. Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil. Insula, 32, 33 [resumo de uma página].</t>
-        </is>
-      </c>
-      <c r="N244" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="O244" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa do Peri (Florianópolis)</t>
-        </is>
-      </c>
-      <c r="P244" s="4" t="inlineStr">
-        <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
-        </is>
-      </c>
-      <c r="Q244" s="4" t="n">
-        <v>-27.725</v>
-      </c>
-      <c r="R244" s="4" t="n">
-        <v>-48.5417</v>
-      </c>
-      <c r="S244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -22189,263 +22189,263 @@
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
+          <t>Sedimentos holocênicos da Lagoa do Peri (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="inlineStr">
+        <is>
+          <t>Diatomáceas holocênicas da Lagoa do Peri (44 táxons; Aulacoseira ambigua, Paralia sulcata)</t>
+        </is>
+      </c>
+      <c r="D245" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — diatomáceas</t>
+        </is>
+      </c>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>Lagoa do Peri, Florianópolis, SC (27°43′30″S, 48°32′30″W); testemunho coletado com amostrador de Livingstone, da superfície a 2,10 m</t>
+        </is>
+      </c>
+      <c r="G245" s="6" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H245" s="7" t="inlineStr">
+        <is>
+          <t>Saupe, A.C. &amp; Mosimann, R.M.S. (2003) — "Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil", Insula 32:33 [resumo de uma página]</t>
+        </is>
+      </c>
+      <c r="I245" s="6" t="inlineStr">
+        <is>
+          <t>Tecpar (Curitiba) e UFSC (Florianópolis) — afiliações das autoras</t>
+        </is>
+      </c>
+      <c r="J245" s="6" t="inlineStr">
+        <is>
+          <t>Holoceno (o resumo cita o método do 14C, mas não informa idades)</t>
+        </is>
+      </c>
+      <c r="K245" s="7" t="inlineStr">
+        <is>
+          <t>Classificação: microfóssil silicoso (diatomáceas em sedimento holocênico). Saupe &amp; Mosimann (2003) analisaram 26 amostras de um testemunho da Lagoa do Peri, da superfície a 2,10 m, e identificaram 44 táxons específicos e infraespecíficos, de 30 gêneros e 25 famílias; Triceratiaceae e Plagiogrammaceae são as famílias mais bem representadas (três gêneros cada) e Pinnularia, o gênero mais rico (cinco espécies). Aulacoseira ambigua é abundante nas camadas superiores e indica o ambiente atual, de água doce; Paralia sulcata é abundante nas camadas profundas, o que as autoras associam à origem marinha original da lagoa. O resumo não traz a lista completa de espécies, idades, depositário nem número de tombo; a fonte é um resumo de uma página.</t>
+        </is>
+      </c>
+      <c r="L245" s="7" t="inlineStr">
+        <is>
+          <t>https://periodicos.ufsc.br/index.php/insula/article/view/21194 (Saupe &amp; Mosimann, 2003 — resumo)</t>
+        </is>
+      </c>
+      <c r="M245" s="7" t="inlineStr">
+        <is>
+          <t>SAUPE, A.C.; MOSIMANN, R.M.S. 2003. Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil. Insula, 32, 33 [resumo de uma página].</t>
+        </is>
+      </c>
+      <c r="N245" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="O245" s="6" t="inlineStr">
+        <is>
+          <t>Lagoa do Peri (Florianópolis)</t>
+        </is>
+      </c>
+      <c r="P245" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q245" s="6" t="n">
+        <v>-27.725</v>
+      </c>
+      <c r="R245" s="6" t="n">
+        <v>-48.5417</v>
+      </c>
+      <c r="S245" s="6" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
           <t>Sedimentos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C245" s="7" t="inlineStr">
+      <c r="C246" s="5" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos de Garopaba (84 táxons: pólen, esporos, fungos, algas, acritarcos, cistos de dinoflagelados)</t>
         </is>
       </c>
-      <c r="D245" s="6" t="inlineStr">
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F245" s="7" t="inlineStr">
+      <c r="F246" s="5" t="inlineStr">
         <is>
           <t>Planície Costeira de Santa Catarina, município de Garopaba, SC — testemunho PCSC-3 (450 cm), a cerca de 2 km do oceano (coordenadas do testemunho não informadas; ponto aproximado no centro do município)</t>
         </is>
       </c>
-      <c r="G245" s="6" t="inlineStr">
+      <c r="G246" s="4" t="inlineStr">
         <is>
           <t>Não informado nos resumos consultados</t>
         </is>
       </c>
-      <c r="H245" s="7" t="inlineStr">
+      <c r="H246" s="5" t="inlineStr">
         <is>
           <t>Kuhn, L.A., Souza, P.A., Cancelli, R.R., Silva, W.G. &amp; Macedo, R.B. (2017) — "Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State", Anais da Academia Brasileira de Ciências 89(4):2581–2595, DOI 10.1590/0001-3765201720160895; Kuhn, L.A. (2017) — "Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil)", Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul</t>
         </is>
       </c>
-      <c r="I245" s="6" t="inlineStr">
+      <c r="I246" s="4" t="inlineStr">
         <is>
           <t>UFRGS (Instituto de Geociências)</t>
         </is>
       </c>
-      <c r="J245" s="6" t="inlineStr">
+      <c r="J246" s="4" t="inlineStr">
         <is>
           <t>ca. 5.390 anos cal AP (base) até o presente — Holoceno Médio a Superior</t>
         </is>
       </c>
-      <c r="K245" s="7" t="inlineStr">
+      <c r="K246" s="5" t="inlineStr">
         <is>
           <t>Classificação: microfósseis orgânicos (palinomorfos) de um testemunho holocênico. Foram analisadas 46 amostras do testemunho PCSC-3 (450 cm), com três datações por radiocarbono (5.390 anos cal AP aos 430 cm; 3.756 aos 360 cm; 858 aos 80 cm), e reconhecidos 84 táxons: pólen de angiospermas e de gimnospermas, esporos de pteridófitas e de briófitas, esporos de fungos, algas, três acritarcos (descritos e ilustrados na dissertação), dois cistos de dinoflagelados e forros de microforaminíferos. Entre os táxons citados no artigo estão Ilex, Myrtaceae, Arecaceae, Araucaria angustifolia, Alnus, Botryococcus, Micrhystridium, Operculodinium e Spiniferites. A análise de agrupamento definiu três fases: I, laguna com influência marinha (desde ~5.390 anos cal AP); II, ainda lagunar, com menos influência marinha e mais algas de água doce (~3.032 a 858 anos cal AP); III, sedimentação subaquosa em condições de pântano (últimos ~856 anos). Número de tombo e depositário não constam nos resumos consultados; as contagens por grupo diferem entre o resumo da dissertação e o do artigo, e por isso só o total de 84 táxons é dado aqui.</t>
         </is>
       </c>
-      <c r="L245" s="7" t="inlineStr">
+      <c r="L246" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/0001-3765201720160895
 https://www.redalyc.org/pdf/327/32754216004.pdf (Kuhn et al., 2017)
 https://lume.ufrgs.br/handle/10183/153388 (dissertação de Kuhn, 2017)</t>
         </is>
       </c>
-      <c r="M245" s="7" t="inlineStr">
+      <c r="M246" s="5" t="inlineStr">
         <is>
           <t>KUHN, L.A.; SOUZA, P.A.; CANCELLI, R.R. et al. 2017. Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State. Anais da Academia Brasileira de Ciências, 89(4), 2581–2595. DOI: 10.1590/0001-3765201720160895 | KUHN, L.A. 2017. Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil). Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul.</t>
         </is>
       </c>
-      <c r="N245" s="6" t="n">
+      <c r="N246" s="4" t="n">
         <v>237</v>
       </c>
-      <c r="O245" s="6" t="inlineStr">
+      <c r="O246" s="4" t="inlineStr">
         <is>
           <t>Garopaba (testemunho PCSC-3)</t>
         </is>
       </c>
-      <c r="P245" s="6" t="inlineStr">
+      <c r="P246" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q245" s="6" t="n">
+      <c r="Q246" s="4" t="n">
         <v>-28.0276</v>
       </c>
-      <c r="R245" s="6" t="n">
+      <c r="R246" s="4" t="n">
         <v>-48.6195</v>
       </c>
-      <c r="S245" s="6" t="inlineStr">
+      <c r="S246" s="4" t="inlineStr">
         <is>
           <t>10.1590/0001-3765201720160895</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="4" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B247" s="6" t="inlineStr">
         <is>
           <t>Sedimentos holocênicos da Planície Costeira sul-catarinense (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C246" s="5" t="inlineStr">
+      <c r="C247" s="7" t="inlineStr">
         <is>
           <t>Diatomáceas holocênicas da Lagoa do Sombrio (Paralia sulcata, Navicula schadei, Staurosira construens, Cyclotella baltica)</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="D247" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — diatomáceas</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
+      <c r="E247" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F246" s="5" t="inlineStr">
+      <c r="F247" s="7" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio, Planície Costeira do sul de Santa Catarina — testemunho de 570 cm (município e coordenadas não informados no resumo; ponto aproximado na sede de Sombrio)</t>
         </is>
       </c>
-      <c r="G246" s="4" t="inlineStr">
+      <c r="G247" s="6" t="inlineStr">
         <is>
           <t>Não informado no resumo consultado</t>
         </is>
       </c>
-      <c r="H246" s="5" t="inlineStr">
+      <c r="H247" s="7" t="inlineStr">
         <is>
           <t>Santos, S.M. &amp; Souza, P.A. (2016) — "Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas", XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo]</t>
         </is>
       </c>
-      <c r="I246" s="4" t="inlineStr">
+      <c r="I247" s="6" t="inlineStr">
         <is>
           <t>UFRGS (Porto Alegre)</t>
         </is>
       </c>
-      <c r="J246" s="4" t="inlineStr">
+      <c r="J247" s="6" t="inlineStr">
         <is>
           <t>ca. 7.900 a 2.500 anos AP (segundo o resumo; resultados parciais)</t>
         </is>
       </c>
-      <c r="K246" s="5" t="inlineStr">
+      <c r="K247" s="7" t="inlineStr">
         <is>
           <t>Classificação: microfóssil silicoso (diatomáceas) de sedimento holocênico. O resumo trata de resultados parciais de um testemunho de 570 cm, do qual foram estudadas 12 amostras (50 a 570 cm): 14 ordens, 45 gêneros e 37 espécies, além de oito táxons determinados só até gênero. Na base (500–400 cm) há apenas espécies marinhas, com predomínio de Paralia sulcata, registrada em todas as amostras; na porção intermediária (350–300 cm), um pântano de água doce, com espécies bentônicas (Navicula schadei, Staurosira construens) e uma planctônica marinha (Cyclotella baltica); no topo (250–50 cm) não se encontraram frústulas, o que os autores atribuem à transformação do ambiente em continental, à dissolução tafonômica ou à falta de nutrientes. Idades citadas: ~7.900–3.800 anos AP, influência marinha; ~3.800–2.500, pântano de água doce. Os níveis de 550 e 570 cm ainda não haviam sido analisados. Número de tombo e depositário não informados. É um resumo de iniciação científica, sem revisão de periódico. VERIFICAÇÃO (2026.10.09): o resumo do Salão de Iniciação Científica de 2015 (Santos &amp; Souza, mesma pesquisa) chama o testemunho de PCSC-01, com 570 cm, na Lagoa do Sombrio, município de Santa Rosa do Sul, e diz que naquela etapa as 12 amostras (espaçadas de 50 cm) ainda aguardavam identificação das espécies. A profundidade (570 cm) e a área coincidem com o testemunho PCSC-1 dos registros nº 233 e nº 264 (Cancelli et al.), mas nenhuma das fontes consultadas declara que se trata do mesmo testemunho; por isso a equivalência não é afirmada.</t>
         </is>
       </c>
-      <c r="L246" s="5" t="inlineStr">
+      <c r="L247" s="7" t="inlineStr">
         <is>
           <t>https://lume.ufrgs.br/bitstream/10183/154894/1/Resumo_48227.pdf (resumo do XXVIII Salão de Iniciação Científica da UFRGS, 2016)
 https://lume.ufrgs.br/bitstream/10183/137304/1/Resumo_42627.pdf (Santos &amp; Souza — resumo do XXVII Salão de Iniciação Científica da UFRGS, 2015)</t>
         </is>
       </c>
-      <c r="M246" s="5" t="inlineStr">
+      <c r="M247" s="7" t="inlineStr">
         <is>
           <t>SANTOS, S.M.; SOUZA, P.A. 2016. Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas. XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo].</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N247" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="O246" s="4" t="inlineStr">
+      <c r="O247" s="6" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio</t>
         </is>
       </c>
-      <c r="P246" s="4" t="inlineStr">
+      <c r="P247" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q246" s="4" t="n">
+      <c r="Q247" s="6" t="n">
         <v>-29.1078</v>
       </c>
-      <c r="R246" s="4" t="n">
+      <c r="R247" s="6" t="n">
         <v>-49.6325</v>
-      </c>
-      <c r="S246" s="4" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
-        <is>
-          <t>Sedimentos lagunares holocênicos (unidade litoestratigráfica não informada no resumo)</t>
-        </is>
-      </c>
-      <c r="C247" s="7" t="inlineStr">
-        <is>
-          <t>Diatomáceas, pólen e esporos holocênicos de lagunas de Jaguaruna</t>
-        </is>
-      </c>
-      <c r="D247" s="6" t="inlineStr">
-        <is>
-          <t>Microfóssil — diatomáceas e palinomorfos</t>
-        </is>
-      </c>
-      <c r="E247" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F247" s="7" t="inlineStr">
-        <is>
-          <t>Região de Jaguaruna, costa centro-sul de Santa Catarina — três testemunhos rasos, de até 2,5 m (localidades e coordenadas não informadas no resumo; ponto aproximado na sede de Jaguaruna)</t>
-        </is>
-      </c>
-      <c r="G247" s="6" t="inlineStr">
-        <is>
-          <t>Não informado no resumo consultado</t>
-        </is>
-      </c>
-      <c r="H247" s="7" t="inlineStr">
-        <is>
-          <t>Amaral, P.G.C. (2008) — "Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada", Tese de Doutorado, Universidade de São Paulo</t>
-        </is>
-      </c>
-      <c r="I247" s="6" t="inlineStr">
-        <is>
-          <t>Universidade de São Paulo</t>
-        </is>
-      </c>
-      <c r="J247" s="6" t="inlineStr">
-        <is>
-          <t>ca. 5.000 a 2.370 anos cal AP (fase lagunar até a última desconexão com o mar)</t>
-        </is>
-      </c>
-      <c r="K247" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: microfósseis (diatomáceas e palinomorfos) de sedimentos lagunares holocênicos. A tese combina dados sedimentológicos, de diatomáceas, de pólen e esporos e geoquímicos (C, N, δ13C, δ15N) de três testemunhos rasos (até 2,5 m). Segundo o resumo, o local era um sistema de lagunas interligadas, com conexão marinha evidenciada por diatomáceas marinhas e pelo sinal da matéria orgânica; a laguna perdeu a conexão com o mar em momentos diferentes em cada testemunho, a última por volta de 2.740–2.370 anos cal AP; as mudanças nas diatomáceas sugerem ao menos duas grandes variações de salinidade, que a autora liga a mudanças de precipitação, e o pólen mostra vegetação estável desde pelo menos 4.000 anos cal AP. A fase lagunar vem de cerca de 5.000 anos cal AP. O resumo consultado não nomeia espécies. CONTEXTO: Amaral et al. (2012, Journal of Quaternary Science 27(2):181–191, DOI 10.1002/jqs.1531) tem título que trata do sistema lagunar da região de Jaguaruna; a página do artigo não pôde ser lida (acesso limitado) e o seu conteúdo não foi usado aqui. Número de tombo e depositário não informados.</t>
-        </is>
-      </c>
-      <c r="L247" s="7" t="inlineStr">
-        <is>
-          <t>https://teses.usp.br/teses/disponiveis/44/44141/tde-19122008-160829/en.php (resumo da tese de Amaral, 2008)</t>
-        </is>
-      </c>
-      <c r="M247" s="7" t="inlineStr">
-        <is>
-          <t>AMARAL, P.G.C. 2008. Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada. Tese de Doutorado, Universidade de São Paulo.</t>
-        </is>
-      </c>
-      <c r="N247" s="6" t="n">
-        <v>239</v>
-      </c>
-      <c r="O247" s="6" t="inlineStr">
-        <is>
-          <t>Região de Jaguaruna (lagunas holocênicas)</t>
-        </is>
-      </c>
-      <c r="P247" s="6" t="inlineStr">
-        <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
-        </is>
-      </c>
-      <c r="Q247" s="6" t="n">
-        <v>-28.6148</v>
-      </c>
-      <c r="R247" s="6" t="n">
-        <v>-49.0286</v>
       </c>
       <c r="S247" s="6" t="inlineStr"/>
     </row>
@@ -22457,1458 +22457,1458 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
+          <t>Sedimentos lagunares holocênicos (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>Diatomáceas, pólen e esporos holocênicos de lagunas de Jaguaruna</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — diatomáceas e palinomorfos</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>Região de Jaguaruna, costa centro-sul de Santa Catarina — três testemunhos rasos, de até 2,5 m (localidades e coordenadas não informadas no resumo; ponto aproximado na sede de Jaguaruna)</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>Não informado no resumo consultado</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>Amaral, P.G.C. (2008) — "Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada", Tese de Doutorado, Universidade de São Paulo</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>Universidade de São Paulo</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>ca. 5.000 a 2.370 anos cal AP (fase lagunar até a última desconexão com o mar)</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: microfósseis (diatomáceas e palinomorfos) de sedimentos lagunares holocênicos. A tese combina dados sedimentológicos, de diatomáceas, de pólen e esporos e geoquímicos (C, N, δ13C, δ15N) de três testemunhos rasos (até 2,5 m). Segundo o resumo, o local era um sistema de lagunas interligadas, com conexão marinha evidenciada por diatomáceas marinhas e pelo sinal da matéria orgânica; a laguna perdeu a conexão com o mar em momentos diferentes em cada testemunho, a última por volta de 2.740–2.370 anos cal AP; as mudanças nas diatomáceas sugerem ao menos duas grandes variações de salinidade, que a autora liga a mudanças de precipitação, e o pólen mostra vegetação estável desde pelo menos 4.000 anos cal AP. A fase lagunar vem de cerca de 5.000 anos cal AP. O resumo consultado não nomeia espécies. CONTEXTO: Amaral et al. (2012, Journal of Quaternary Science 27(2):181–191, DOI 10.1002/jqs.1531) tem título que trata do sistema lagunar da região de Jaguaruna; a página do artigo não pôde ser lida (acesso limitado) e o seu conteúdo não foi usado aqui. Número de tombo e depositário não informados.</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="inlineStr">
+        <is>
+          <t>https://teses.usp.br/teses/disponiveis/44/44141/tde-19122008-160829/en.php (resumo da tese de Amaral, 2008)</t>
+        </is>
+      </c>
+      <c r="M248" s="5" t="inlineStr">
+        <is>
+          <t>AMARAL, P.G.C. 2008. Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada. Tese de Doutorado, Universidade de São Paulo.</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="O248" s="4" t="inlineStr">
+        <is>
+          <t>Região de Jaguaruna (lagunas holocênicas)</t>
+        </is>
+      </c>
+      <c r="P248" s="4" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="n">
+        <v>-28.6148</v>
+      </c>
+      <c r="R248" s="4" t="n">
+        <v>-49.0286</v>
+      </c>
+      <c r="S248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C248" s="5" t="inlineStr">
+      <c r="C249" s="7" t="inlineStr">
         <is>
           <t>Bulla striata</t>
         </is>
       </c>
-      <c r="D248" s="4" t="inlineStr">
+      <c r="D249" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
+      <c r="E249" s="6" t="inlineStr">
         <is>
           <t>UFSC 418</t>
         </is>
       </c>
-      <c r="F248" s="5" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G248" s="4" t="inlineStr">
+      <c r="G249" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H248" s="5" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I248" s="4" t="inlineStr">
+      <c r="I249" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J248" s="4" t="inlineStr">
+      <c r="J249" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K248" s="5" t="inlineStr">
+      <c r="K249" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 418, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L248" s="5" t="inlineStr">
+      <c r="L249" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M248" s="5" t="inlineStr">
+      <c r="M249" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N249" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="O248" s="4" t="inlineStr">
+      <c r="O249" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P248" s="4" t="inlineStr">
+      <c r="P249" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q248" s="4" t="n">
+      <c r="Q249" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R248" s="4" t="n">
+      <c r="R249" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S248" s="4" t="inlineStr">
+      <c r="S249" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="6" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="B250" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C249" s="7" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
         <is>
           <t>Bostrycapulus odites</t>
         </is>
       </c>
-      <c r="D249" s="6" t="inlineStr">
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E250" s="4" t="inlineStr">
         <is>
           <t>UFSC 421</t>
         </is>
       </c>
-      <c r="F249" s="7" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G249" s="6" t="inlineStr">
+      <c r="G250" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H249" s="7" t="inlineStr">
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I249" s="6" t="inlineStr">
+      <c r="I250" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J249" s="6" t="inlineStr">
+      <c r="J250" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K249" s="7" t="inlineStr">
+      <c r="K250" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 421, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L249" s="7" t="inlineStr">
+      <c r="L250" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M249" s="7" t="inlineStr">
+      <c r="M250" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N249" s="6" t="n">
+      <c r="N250" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="O249" s="6" t="inlineStr">
+      <c r="O250" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P249" s="6" t="inlineStr">
+      <c r="P250" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q249" s="6" t="n">
+      <c r="Q250" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R249" s="6" t="n">
+      <c r="R250" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S249" s="6" t="inlineStr">
+      <c r="S250" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="4" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B250" s="4" t="inlineStr">
+      <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
+      <c r="C251" s="7" t="inlineStr">
         <is>
           <t>Cerithium atratum</t>
         </is>
       </c>
-      <c r="D250" s="4" t="inlineStr">
+      <c r="D251" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E250" s="4" t="inlineStr">
+      <c r="E251" s="6" t="inlineStr">
         <is>
           <t>UFSC 410</t>
         </is>
       </c>
-      <c r="F250" s="5" t="inlineStr">
+      <c r="F251" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G250" s="4" t="inlineStr">
+      <c r="G251" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H250" s="5" t="inlineStr">
+      <c r="H251" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I250" s="4" t="inlineStr">
+      <c r="I251" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J250" s="4" t="inlineStr">
+      <c r="J251" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K250" s="5" t="inlineStr">
+      <c r="K251" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 410, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L250" s="5" t="inlineStr">
+      <c r="L251" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M250" s="5" t="inlineStr">
+      <c r="M251" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N251" s="6" t="n">
         <v>242</v>
       </c>
-      <c r="O250" s="4" t="inlineStr">
+      <c r="O251" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P250" s="4" t="inlineStr">
+      <c r="P251" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q250" s="4" t="n">
+      <c r="Q251" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R250" s="4" t="n">
+      <c r="R251" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S250" s="4" t="inlineStr">
+      <c r="S251" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B252" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C251" s="7" t="inlineStr">
+      <c r="C252" s="5" t="inlineStr">
         <is>
           <t>Chichoreus senegalensis</t>
         </is>
       </c>
-      <c r="D251" s="6" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E252" s="4" t="inlineStr">
         <is>
           <t>UFSC 424 (exemplar fragmentado)</t>
         </is>
       </c>
-      <c r="F251" s="7" t="inlineStr">
+      <c r="F252" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G251" s="6" t="inlineStr">
+      <c r="G252" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H251" s="7" t="inlineStr">
+      <c r="H252" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I251" s="6" t="inlineStr">
+      <c r="I252" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J251" s="6" t="inlineStr">
+      <c r="J252" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K251" s="7" t="inlineStr">
+      <c r="K252" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 424 (exemplar fragmentado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L251" s="7" t="inlineStr">
+      <c r="L252" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M251" s="7" t="inlineStr">
+      <c r="M252" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N251" s="6" t="n">
+      <c r="N252" s="4" t="n">
         <v>243</v>
       </c>
-      <c r="O251" s="6" t="inlineStr">
+      <c r="O252" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P251" s="6" t="inlineStr">
+      <c r="P252" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q251" s="6" t="n">
+      <c r="Q252" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R251" s="6" t="n">
+      <c r="R252" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S251" s="6" t="inlineStr">
+      <c r="S252" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B253" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C252" s="5" t="inlineStr">
+      <c r="C253" s="7" t="inlineStr">
         <is>
           <t>Nassarius vibex</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D253" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
+      <c r="E253" s="6" t="inlineStr">
         <is>
           <t>UFSC 416</t>
         </is>
       </c>
-      <c r="F252" s="5" t="inlineStr">
+      <c r="F253" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr">
+      <c r="G253" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H252" s="5" t="inlineStr">
+      <c r="H253" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I252" s="4" t="inlineStr">
+      <c r="I253" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J252" s="4" t="inlineStr">
+      <c r="J253" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K252" s="5" t="inlineStr">
+      <c r="K253" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 416, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L252" s="5" t="inlineStr">
+      <c r="L253" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M252" s="5" t="inlineStr">
+      <c r="M253" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N253" s="6" t="n">
         <v>244</v>
       </c>
-      <c r="O252" s="4" t="inlineStr">
+      <c r="O253" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P252" s="4" t="inlineStr">
+      <c r="P253" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q252" s="4" t="n">
+      <c r="Q253" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R252" s="4" t="n">
+      <c r="R253" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S252" s="4" t="inlineStr">
+      <c r="S253" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="6" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C253" s="7" t="inlineStr">
+      <c r="C254" s="5" t="inlineStr">
         <is>
           <t>Trachycardium muricatum</t>
         </is>
       </c>
-      <c r="D253" s="6" t="inlineStr">
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E254" s="4" t="inlineStr">
         <is>
           <t>UFSC 427</t>
         </is>
       </c>
-      <c r="F253" s="7" t="inlineStr">
+      <c r="F254" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G253" s="6" t="inlineStr">
+      <c r="G254" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H253" s="7" t="inlineStr">
+      <c r="H254" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I253" s="6" t="inlineStr">
+      <c r="I254" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J253" s="6" t="inlineStr">
+      <c r="J254" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K253" s="7" t="inlineStr">
+      <c r="K254" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 427, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L253" s="7" t="inlineStr">
+      <c r="L254" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M253" s="7" t="inlineStr">
+      <c r="M254" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N253" s="6" t="n">
+      <c r="N254" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="O253" s="6" t="inlineStr">
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P253" s="6" t="inlineStr">
+      <c r="P254" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q253" s="6" t="n">
+      <c r="Q254" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R253" s="6" t="n">
+      <c r="R254" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S253" s="6" t="inlineStr">
+      <c r="S254" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B255" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C254" s="5" t="inlineStr">
+      <c r="C255" s="7" t="inlineStr">
         <is>
           <t>Corbula caribaea</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D255" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
+      <c r="E255" s="6" t="inlineStr">
         <is>
           <t>UFSC 422</t>
         </is>
       </c>
-      <c r="F254" s="5" t="inlineStr">
+      <c r="F255" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G254" s="4" t="inlineStr">
+      <c r="G255" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H254" s="5" t="inlineStr">
+      <c r="H255" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I254" s="4" t="inlineStr">
+      <c r="I255" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J254" s="4" t="inlineStr">
+      <c r="J255" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K254" s="5" t="inlineStr">
+      <c r="K255" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 422, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L254" s="5" t="inlineStr">
+      <c r="L255" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M254" s="5" t="inlineStr">
+      <c r="M255" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N255" s="6" t="n">
         <v>246</v>
       </c>
-      <c r="O254" s="4" t="inlineStr">
+      <c r="O255" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P254" s="4" t="inlineStr">
+      <c r="P255" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q254" s="4" t="n">
+      <c r="Q255" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R254" s="4" t="n">
+      <c r="R255" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S254" s="4" t="inlineStr">
+      <c r="S255" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="6" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B255" s="6" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C255" s="7" t="inlineStr">
+      <c r="C256" s="5" t="inlineStr">
         <is>
           <t>Iphigenia brasiliensis</t>
         </is>
       </c>
-      <c r="D255" s="6" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
         <is>
           <t>UFSC 428</t>
         </is>
       </c>
-      <c r="F255" s="7" t="inlineStr">
+      <c r="F256" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G255" s="6" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H255" s="7" t="inlineStr">
+      <c r="H256" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I255" s="6" t="inlineStr">
+      <c r="I256" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J255" s="6" t="inlineStr">
+      <c r="J256" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K255" s="7" t="inlineStr">
+      <c r="K256" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 428, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L255" s="7" t="inlineStr">
+      <c r="L256" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M255" s="7" t="inlineStr">
+      <c r="M256" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N255" s="6" t="n">
+      <c r="N256" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="O255" s="6" t="inlineStr">
+      <c r="O256" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P255" s="6" t="inlineStr">
+      <c r="P256" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q255" s="6" t="n">
+      <c r="Q256" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R255" s="6" t="n">
+      <c r="R256" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S255" s="6" t="inlineStr">
+      <c r="S256" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="4" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="B257" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C256" s="5" t="inlineStr">
+      <c r="C257" s="7" t="inlineStr">
         <is>
           <t>Lucina pectinata</t>
         </is>
       </c>
-      <c r="D256" s="4" t="inlineStr">
+      <c r="D257" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
+      <c r="E257" s="6" t="inlineStr">
         <is>
           <t>UFSC 402 (articulado); UFSC 430 (valva esquerda)</t>
         </is>
       </c>
-      <c r="F256" s="5" t="inlineStr">
+      <c r="F257" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G256" s="4" t="inlineStr">
+      <c r="G257" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H256" s="5" t="inlineStr">
+      <c r="H257" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I256" s="4" t="inlineStr">
+      <c r="I257" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J256" s="4" t="inlineStr">
+      <c r="J257" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K256" s="5" t="inlineStr">
+      <c r="K257" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.260 ± 30 anos AP (calibrada 5.620–5.440); UFSC 430 é uma valva esquerda fragmentada. Número de tombo: UFSC 402 (articulado); UFSC 430 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L256" s="5" t="inlineStr">
+      <c r="L257" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M256" s="5" t="inlineStr">
+      <c r="M257" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N257" s="6" t="n">
         <v>248</v>
       </c>
-      <c r="O256" s="4" t="inlineStr">
+      <c r="O257" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P256" s="4" t="inlineStr">
+      <c r="P257" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q256" s="4" t="n">
+      <c r="Q257" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R256" s="4" t="n">
+      <c r="R257" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S256" s="4" t="inlineStr">
+      <c r="S257" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="6" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B257" s="6" t="inlineStr">
+      <c r="B258" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C257" s="7" t="inlineStr">
+      <c r="C258" s="5" t="inlineStr">
         <is>
           <t>Ostrea equestris</t>
         </is>
       </c>
-      <c r="D257" s="6" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="E258" s="4" t="inlineStr">
         <is>
           <t>UFSC 395; UFSC 433 (valva direita)</t>
         </is>
       </c>
-      <c r="F257" s="7" t="inlineStr">
+      <c r="F258" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G257" s="6" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H257" s="7" t="inlineStr">
+      <c r="H258" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I257" s="6" t="inlineStr">
+      <c r="I258" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J257" s="6" t="inlineStr">
+      <c r="J258" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K257" s="7" t="inlineStr">
+      <c r="K258" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada, mas fora de posição de vida (distribuição aleatória quanto ao plano de acamamento), e foi datada em 5.410 ± 30 anos AP (calibrada 5.805–5.580); UFSC 433 é uma valva direita com bioerosão e fragmentação. Número de tombo: UFSC 395; UFSC 433 (valva direita), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L257" s="7" t="inlineStr">
+      <c r="L258" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M257" s="7" t="inlineStr">
+      <c r="M258" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N257" s="6" t="n">
+      <c r="N258" s="4" t="n">
         <v>249</v>
       </c>
-      <c r="O257" s="6" t="inlineStr">
+      <c r="O258" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P257" s="6" t="inlineStr">
+      <c r="P258" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q257" s="6" t="n">
+      <c r="Q258" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R257" s="6" t="n">
+      <c r="R258" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S257" s="6" t="inlineStr">
+      <c r="S258" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="4" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B258" s="4" t="inlineStr">
+      <c r="B259" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C258" s="5" t="inlineStr">
+      <c r="C259" s="7" t="inlineStr">
         <is>
           <t>Strigilla pisiformis</t>
         </is>
       </c>
-      <c r="D258" s="4" t="inlineStr">
+      <c r="D259" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
+      <c r="E259" s="6" t="inlineStr">
         <is>
           <t>UFSC 425</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
+      <c r="F259" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G258" s="4" t="inlineStr">
+      <c r="G259" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H258" s="5" t="inlineStr">
+      <c r="H259" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I258" s="4" t="inlineStr">
+      <c r="I259" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J258" s="4" t="inlineStr">
+      <c r="J259" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K258" s="5" t="inlineStr">
+      <c r="K259" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 425, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L258" s="5" t="inlineStr">
+      <c r="L259" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M258" s="5" t="inlineStr">
+      <c r="M259" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N259" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="O258" s="4" t="inlineStr">
+      <c r="O259" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P258" s="4" t="inlineStr">
+      <c r="P259" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q258" s="4" t="n">
+      <c r="Q259" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R258" s="4" t="n">
+      <c r="R259" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S258" s="4" t="inlineStr">
+      <c r="S259" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="6" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B259" s="6" t="inlineStr">
+      <c r="B260" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C259" s="7" t="inlineStr">
+      <c r="C260" s="5" t="inlineStr">
         <is>
           <t>Tagelus plebeius</t>
         </is>
       </c>
-      <c r="D259" s="6" t="inlineStr">
+      <c r="D260" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E260" s="4" t="inlineStr">
         <is>
           <t>UFSC 429 (articulado)</t>
         </is>
       </c>
-      <c r="F259" s="7" t="inlineStr">
+      <c r="F260" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G259" s="6" t="inlineStr">
+      <c r="G260" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H259" s="7" t="inlineStr">
+      <c r="H260" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I259" s="6" t="inlineStr">
+      <c r="I260" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J259" s="6" t="inlineStr">
+      <c r="J260" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K259" s="7" t="inlineStr">
+      <c r="K260" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.620 ± 30 anos AP (calibrada 6.000–5.840). Número de tombo: UFSC 429 (articulado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L259" s="7" t="inlineStr">
+      <c r="L260" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M259" s="7" t="inlineStr">
+      <c r="M260" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N259" s="6" t="n">
+      <c r="N260" s="4" t="n">
         <v>251</v>
       </c>
-      <c r="O259" s="6" t="inlineStr">
+      <c r="O260" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P259" s="6" t="inlineStr">
+      <c r="P260" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q259" s="6" t="n">
+      <c r="Q260" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R259" s="6" t="n">
+      <c r="R260" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S259" s="6" t="inlineStr">
+      <c r="S260" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="B261" s="6" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
+      <c r="C261" s="7" t="inlineStr">
         <is>
           <t>Anomalocardia brasiliana</t>
         </is>
       </c>
-      <c r="D260" s="4" t="inlineStr">
+      <c r="D261" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
+      <c r="E261" s="6" t="inlineStr">
         <is>
           <t>UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda)</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
+      <c r="F261" s="7" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="G261" s="6" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H260" s="5" t="inlineStr">
+      <c r="H261" s="7" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I260" s="4" t="inlineStr">
+      <c r="I261" s="6" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J260" s="4" t="inlineStr">
+      <c r="J261" s="6" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K260" s="5" t="inlineStr">
+      <c r="K261" s="7" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. É a espécie mais bem representada, com cerca de 90% do volume total dos fósseis; ocorre articulada e em posição de vida, e as valvas isoladas (UFSC 431 e 432) mostram desgaste, fragmentação e bioerosão. Não foi datada individualmente. Número de tombo: UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L260" s="5" t="inlineStr">
+      <c r="L261" s="7" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M260" s="5" t="inlineStr">
+      <c r="M261" s="7" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N261" s="6" t="n">
         <v>252</v>
       </c>
-      <c r="O260" s="4" t="inlineStr">
+      <c r="O261" s="6" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P260" s="4" t="inlineStr">
+      <c r="P261" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q260" s="4" t="n">
+      <c r="Q261" s="6" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R260" s="4" t="n">
+      <c r="R261" s="6" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S260" s="4" t="inlineStr">
+      <c r="S261" s="6" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="6" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="B262" s="4" t="inlineStr">
         <is>
           <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
-      <c r="C261" s="7" t="inlineStr">
+      <c r="C262" s="5" t="inlineStr">
         <is>
           <t>Chione pubera</t>
         </is>
       </c>
-      <c r="D261" s="6" t="inlineStr">
+      <c r="D262" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — bivalve</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E262" s="4" t="inlineStr">
         <is>
           <t>UFSC 423</t>
         </is>
       </c>
-      <c r="F261" s="7" t="inlineStr">
+      <c r="F262" s="5" t="inlineStr">
         <is>
           <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
-      <c r="G261" s="6" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
-      <c r="H261" s="7" t="inlineStr">
+      <c r="H262" s="5" t="inlineStr">
         <is>
           <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="I261" s="6" t="inlineStr">
+      <c r="I262" s="4" t="inlineStr">
         <is>
           <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
-      <c r="J261" s="6" t="inlineStr">
+      <c r="J262" s="4" t="inlineStr">
         <is>
           <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="K261" s="7" t="inlineStr">
+      <c r="K262" s="5" t="inlineStr">
         <is>
           <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 423, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
-      <c r="L261" s="7" t="inlineStr">
+      <c r="L262" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.22456/1807-9806.78267
 https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
-      <c r="M261" s="7" t="inlineStr">
+      <c r="M262" s="5" t="inlineStr">
         <is>
           <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
-      <c r="N261" s="6" t="n">
+      <c r="N262" s="4" t="n">
         <v>253</v>
       </c>
-      <c r="O261" s="6" t="inlineStr">
+      <c r="O262" s="4" t="inlineStr">
         <is>
           <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
-      <c r="P261" s="6" t="inlineStr">
+      <c r="P262" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q261" s="6" t="n">
+      <c r="Q262" s="4" t="n">
         <v>-27.9021</v>
       </c>
-      <c r="R261" s="6" t="n">
+      <c r="R262" s="4" t="n">
         <v>-48.6681</v>
       </c>
-      <c r="S261" s="6" t="inlineStr">
+      <c r="S262" s="4" t="inlineStr">
         <is>
           <t>10.22456/1807-9806.78267</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B262" s="4" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>Sedimentos turfosos holocênicos (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr">
+      <c r="C263" s="7" t="inlineStr">
         <is>
           <t>Palinomorfos holocênicos de turfeira dos Campos do Quiriri (47 palinomorfos)</t>
         </is>
       </c>
-      <c r="D262" s="4" t="inlineStr">
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E262" s="4" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
+      <c r="F263" s="7" t="inlineStr">
         <is>
           <t>Turfeira dos Campos do Quiriri, no Planalto de São Bento do Sul, SC; testemunho de até 175 cm. O resumo não informa município, coordenadas nem altitude; ponto aproximado em São Bento do Sul, município que dá nome ao planalto</t>
         </is>
       </c>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="G263" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H262" s="5" t="inlineStr">
+      <c r="H263" s="7" t="inlineStr">
         <is>
           <t>Lima, G.L., Bauermann, S.G. &amp; Oliveira, M.A.T. (2011) — "Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil", Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011)</t>
         </is>
       </c>
-      <c r="I262" s="4" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>UFFS (Chapecó, SC) / ULBRA (Canoas, RS) / UFSC (Florianópolis, SC)</t>
         </is>
       </c>
-      <c r="J262" s="4" t="inlineStr">
+      <c r="J263" s="6" t="inlineStr">
         <is>
           <t>Holoceno — base do testemunho em ~6,2 ka AP (6.220 ± 30 anos AP, segundo o resumo)</t>
         </is>
       </c>
-      <c r="K262" s="5" t="inlineStr">
+      <c r="K263" s="7" t="inlineStr">
         <is>
           <t>Classificação: microfósseis (pólen e esporos) de turfeira — registro paleoambiental holocênico. Segundo o resumo, foram identificados 47 palinomorfos, agrupados por afinidade ecológica: elementos campestres (Poaceae, Asteraceae, Cyperaceae, Apiaceae, Xyris), elementos florestais (Myrsine, Myrtaceae, Alchornea, Weinmannia, Ilex, Mimosa scabrella e, em um único grão, Araucaria angustifolia), pteridófitas (Blechnum, Cyatheaceae, Marattia, Dicksonia sellowiana) e Sphagnum. Uma amostra da base do testemunho foi enviada à Universidade da Geórgia (EUA) para datação por radiocarbono. NOTA DE FONTE (2026.10.09): o PDF do resumo não traz o ano; 2011 é o ano do XIII Congresso da ABEQUA e III Encontro do Quaternário Sul-Americano (Armação dos Búzios, RJ, 8–13/10/2011, segundo o calendário da PAGES). Município e coordenadas da turfeira não constam: o resumo diz apenas «Planalto de São Bento do Sul». Tombo e depositário não informados.</t>
         </is>
       </c>
-      <c r="L262" s="5" t="inlineStr">
+      <c r="L263" s="7" t="inlineStr">
         <is>
           <t>https://www.abequa.org.br/anais/ABEQUA_GISELE_LIMA.pdf (resumo — Lima, Bauermann &amp; Oliveira)
 https://pastglobalchanges.org/calendar/127-pages/1056%E2%88%92xiii-congress-of-abequa-and-iii-south-america-quaternary-meeting (data e local do XIII Congresso da ABEQUA)</t>
         </is>
       </c>
-      <c r="M262" s="5" t="inlineStr">
+      <c r="M263" s="7" t="inlineStr">
         <is>
           <t>LIMA, G.L.; BAUERMANN, S.G.; OLIVEIRA, M.A.T. 2011. Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil. Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011).</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n">
+      <c r="N263" s="6" t="n">
         <v>257</v>
       </c>
-      <c r="O262" s="4" t="inlineStr">
+      <c r="O263" s="6" t="inlineStr">
         <is>
           <t>Campos do Quiriri (Planalto de São Bento do Sul)</t>
         </is>
       </c>
-      <c r="P262" s="4" t="inlineStr">
+      <c r="P263" s="6" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q262" s="4" t="n">
+      <c r="Q263" s="6" t="n">
         <v>-26.2503</v>
       </c>
-      <c r="R262" s="4" t="n">
+      <c r="R263" s="6" t="n">
         <v>-49.3792</v>
-      </c>
-      <c r="S262" s="4" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
-        <is>
-          <t>Depósitos paludais/lagunares holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
-        </is>
-      </c>
-      <c r="C263" s="7" t="inlineStr">
-        <is>
-          <t>Microfauna holocênica do testemunho PCSC-1 (15 táxons: 5 bivalves, 8 gastrópodes, 1 foraminífero e 1 ostracode)</t>
-        </is>
-      </c>
-      <c r="D263" s="6" t="inlineStr">
-        <is>
-          <t>Microfóssil — microfauna (moluscos, foraminífero e ostracode)</t>
-        </is>
-      </c>
-      <c r="E263" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F263" s="7" t="inlineStr">
-        <is>
-          <t>Testemunho PCSC-1, em mata paludial próxima à Lagoa do Sombrio, município de Santa Rosa do Sul, SC (acesso pela BR-101 e estradas secundárias); coordenadas do próprio resumo: 29°10'42"S, 49°44'58"W; Russian Peat Borer, profundidade de 570 cm</t>
-        </is>
-      </c>
-      <c r="G263" s="6" t="inlineStr">
-        <is>
-          <t>Não informado no resumo (triagem da microfauna no CECO/UFRGS)</t>
-        </is>
-      </c>
-      <c r="H263" s="7" t="inlineStr">
-        <is>
-          <t>Cancelli, R.R., Souza, P.A. &amp; Dehnhardt, B.A. (2011) — "Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos", Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo)</t>
-        </is>
-      </c>
-      <c r="I263" s="6" t="inlineStr">
-        <is>
-          <t>Universidade Federal do Rio Grande do Sul (UFRGS) — afiliação dos autores</t>
-        </is>
-      </c>
-      <c r="J263" s="6" t="inlineStr">
-        <is>
-          <t>base do testemunho ca. 7.908 ± 33 anos cal AP (única datação AMS, nível basal; 0,0079 Ma); os níveis com microfauna ficam entre 570 e 320 cm, sem datação própria</t>
-        </is>
-      </c>
-      <c r="K263" s="7" t="inlineStr">
-        <is>
-          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): a microfauna foi triada em níveis selecionados do testemunho e reúne 15 táxons — bivalves: Anomalocardia brasiliana, Brachiodontes sp., Tellina versicolor, Pitar rostratus e Ostrea puelchana; gastrópodes: Parodizia uruguayensis, Heleobia australis australis, Bittium varium, Odostomia seminuda, Crepidula aculeata, Bulla striata, Solariorbis shimeri e Solariorbis shumoi; foraminífero: Quinqueloculina lamarckiana; ostracode: Cyprideis sp. O resumo não atribui cada espécie a uma profundidade: informa apenas que a base (570–560 cm) é um concheiro com fauna interpretada como autóctone, bem preservada e adaptada a salinidade elevada, e que pequenos fragmentos de conchas continuam até 320 cm, com pouco indício de retrabalhamento. INTERPRETAÇÃO (dos autores): fase I (570–560 cm) com influência marinha ou fortemente salina; fase II (560–320 cm) com ingressão marinha que ultrapassou os limites atuais, com pico em torno de 450 cm (palinoforaminíferos e Micrhystridium), ligada ao recuo da margem oeste da Lagoa do Sombrio; fase III (320–0 cm) com aumento de árvores da Mata Atlântica, briófitas, pteridófitas e algas de água doce, ambiente de influência lagunar substituído por influência de água doce. LOCALIZAÇÃO: o testemunho PCSC-1 é de Santa Rosa do Sul; o ponto do mapa usa as coordenadas do resumo. NOTA DE FONTE: só o resumo foi consultado; os autores afirmam que obterão novas datações ao longo do perfil (só a base foi datada), por isso a idade dos níveis com microfauna não é conhecida. Os nomes de espécie estão como no resumo; sinonímias e a grafia atual não foram verificadas. O resumo não informa depositário nem numeração de tombo. RELAÇÃO COM OUTROS REGISTROS (2026.10.09): os dados palinológicos do mesmo testemunho (112 palinomorfos no total, dos quais 54 não-pólen) correspondem ao registro nº 233. LIGAÇÃO COM O REGISTRO Nº 238 (2026.10.09): o testemunho PCSC-01 (570 cm, Lagoa do Sombrio, Santa Rosa do Sul) das diatomáceas de Santos &amp; Souza tem a mesma profundidade e a mesma área, mas as fontes não declaram que seja o mesmo testemunho do PCSC-1 aqui descrito.</t>
-        </is>
-      </c>
-      <c r="L263" s="7" t="inlineStr">
-        <is>
-          <t>https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
-        </is>
-      </c>
-      <c r="M263" s="7" t="inlineStr">
-        <is>
-          <t>CANCELLI, R.R.; SOUZA, P.A.; DEHNHARDT, B.A. 2011. Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos. Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo).</t>
-        </is>
-      </c>
-      <c r="N263" s="6" t="n">
-        <v>264</v>
-      </c>
-      <c r="O263" s="6" t="inlineStr">
-        <is>
-          <t>Testemunho PCSC-1 (Santa Rosa do Sul)</t>
-        </is>
-      </c>
-      <c r="P263" s="6" t="inlineStr">
-        <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
-        </is>
-      </c>
-      <c r="Q263" s="6" t="n">
-        <v>-29.1783</v>
-      </c>
-      <c r="R263" s="6" t="n">
-        <v>-49.7494</v>
       </c>
       <c r="S263" s="6" t="inlineStr"/>
     </row>
@@ -23920,17 +23920,17 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Depósitos holocênicos de planície costeira (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Depósitos paludais/lagunares holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Foraminíferos bentônicos holocênicos — Miliolida (testemunho de Volta Velha, Itapoá)</t>
+          <t>Microfauna holocênica do testemunho PCSC-1 (15 táxons: 5 bivalves, 8 gastrópodes, 1 foraminífero e 1 ostracode)</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Microfóssil — foraminífero bentônico</t>
+          <t>Microfóssil — microfauna (moluscos, foraminífero e ostracode)</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr">
@@ -23940,50 +23940,50 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Região de Volta Velha, Itapoá, SC — uma das três sondagens manuais feitas ali; coordenadas do resumo: 26°4'58,5"S, 48°37'54,3"W (a amostra com miliolídeos vem do estrato mais profundo do testemunho de Volta Velha)</t>
+          <t>Testemunho PCSC-1, em mata paludial próxima à Lagoa do Sombrio, município de Santa Rosa do Sul, SC (acesso pela BR-101 e estradas secundárias); coordenadas do próprio resumo: 29°10'42"S, 49°44'58"W; Russian Peat Borer, profundidade de 570 cm</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>Não informado no resumo</t>
+          <t>Não informado no resumo (triagem da microfauna no CECO/UFRGS)</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)</t>
+          <t>Cancelli, R.R., Souza, P.A. &amp; Dehnhardt, B.A. (2011) — "Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos", Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo)</t>
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>Universidade Federal do Paraná (LECOST) e Universidade do Algarve (CIMA, Portugal) — afiliações dos autores</t>
+          <t>Universidade Federal do Rio Grande do Sul (UFRGS) — afiliação dos autores</t>
         </is>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
-          <t>Holoceno (os autores tratam os depósitos como holocênicos; idade do testemunho de Volta Velha não informada no resumo)</t>
+          <t>base do testemunho ca. 7.908 ± 33 anos cal AP (única datação AMS, nível basal; 0,0079 Ma); os níveis com microfauna ficam entre 570 e 320 cm, sem datação própria</t>
         </is>
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): foram feitas 35 sondagens manuais em planícies costeiras do norte de Santa Catarina e do sul do Paraná — seis em SC (três em Volta Velha, Itapoá, e três na parte interna da Baía de São Francisco, nas planícies de Joinville e de Garuva) e uma no Paraná (Cabaraquara, Guaratuba) — para analisar foraminíferos. No testemunho de Volta Velha só uma amostra, a do estrato mais profundo, trouxe fauna composta predominantemente por miliolídeos; os autores a interpretam como indício de ambiente mais oxigenado, com maior influência marinha e salinidade mais alta, provavelmente uma região mais externa da baía. ESCOPO: o resumo não traz resultados separados nem identificação de espécies para as sondagens de Itapoá (demais amostras) e da Baía de São Francisco (Joinville/Garuva); os gêneros Ammonia e Elphidium que o resumo menciona são do testemunho de Guaratuba, no Paraná, e por isso não fazem parte deste registro. NOTA DE FONTE: só o resumo foi consultado e o texto declara resultados preliminares, com espécies ainda não identificadas. O documento não informa o evento nem o ano (agradece ao projeto CNPq 471039/2013-6), por isso a data está como s.d.; profundidade e datação 14C do testemunho de Volta Velha também não constam.</t>
+          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): a microfauna foi triada em níveis selecionados do testemunho e reúne 15 táxons — bivalves: Anomalocardia brasiliana, Brachiodontes sp., Tellina versicolor, Pitar rostratus e Ostrea puelchana; gastrópodes: Parodizia uruguayensis, Heleobia australis australis, Bittium varium, Odostomia seminuda, Crepidula aculeata, Bulla striata, Solariorbis shimeri e Solariorbis shumoi; foraminífero: Quinqueloculina lamarckiana; ostracode: Cyprideis sp. O resumo não atribui cada espécie a uma profundidade: informa apenas que a base (570–560 cm) é um concheiro com fauna interpretada como autóctone, bem preservada e adaptada a salinidade elevada, e que pequenos fragmentos de conchas continuam até 320 cm, com pouco indício de retrabalhamento. INTERPRETAÇÃO (dos autores): fase I (570–560 cm) com influência marinha ou fortemente salina; fase II (560–320 cm) com ingressão marinha que ultrapassou os limites atuais, com pico em torno de 450 cm (palinoforaminíferos e Micrhystridium), ligada ao recuo da margem oeste da Lagoa do Sombrio; fase III (320–0 cm) com aumento de árvores da Mata Atlântica, briófitas, pteridófitas e algas de água doce, ambiente de influência lagunar substituído por influência de água doce. LOCALIZAÇÃO: o testemunho PCSC-1 é de Santa Rosa do Sul; o ponto do mapa usa as coordenadas do resumo. NOTA DE FONTE: só o resumo foi consultado; os autores afirmam que obterão novas datações ao longo do perfil (só a base foi datada), por isso a idade dos níveis com microfauna não é conhecida. Os nomes de espécie estão como no resumo; sinonímias e a grafia atual não foram verificadas. O resumo não informa depositário nem numeração de tombo. RELAÇÃO COM OUTROS REGISTROS (2026.10.09): os dados palinológicos do mesmo testemunho (112 palinomorfos no total, dos quais 54 não-pólen) correspondem ao registro nº 233. LIGAÇÃO COM O REGISTRO Nº 238 (2026.10.09): o testemunho PCSC-01 (570 cm, Lagoa do Sombrio, Santa Rosa do Sul) das diatomáceas de Santos &amp; Souza tem a mesma profundidade e a mesma área, mas as fontes não declaram que seja o mesmo testemunho do PCSC-1 aqui descrito.</t>
         </is>
       </c>
       <c r="L264" s="5" t="inlineStr">
         <is>
-          <t>https://www.abequa.org.br/anais/247_resumo.pdf (Silva, Angulo, Souza &amp; Boski — resumo; evento e ano não constam do documento)</t>
+          <t>https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
       <c r="M264" s="5" t="inlineStr">
         <is>
-          <t>[referência sem formato bibliográfico, transcrita do descritor: Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)]</t>
+          <t>CANCELLI, R.R.; SOUZA, P.A.; DEHNHARDT, B.A. 2011. Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos. Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo).</t>
         </is>
       </c>
       <c r="N264" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
-          <t>Volta Velha (Itapoá) — testemunho da planície costeira</t>
+          <t>Testemunho PCSC-1 (Santa Rosa do Sul)</t>
         </is>
       </c>
       <c r="P264" s="4" t="inlineStr">
@@ -23992,10 +23992,10 @@
         </is>
       </c>
       <c r="Q264" s="4" t="n">
-        <v>-26.0829</v>
+        <v>-29.1783</v>
       </c>
       <c r="R264" s="4" t="n">
-        <v>-48.6318</v>
+        <v>-49.7494</v>
       </c>
       <c r="S264" s="4" t="inlineStr"/>
     </row>
@@ -24007,144 +24007,231 @@
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
+          <t>Depósitos holocênicos de planície costeira (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C265" s="7" t="inlineStr">
+        <is>
+          <t>Foraminíferos bentônicos holocênicos — Miliolida (testemunho de Volta Velha, Itapoá)</t>
+        </is>
+      </c>
+      <c r="D265" s="6" t="inlineStr">
+        <is>
+          <t>Microfóssil — foraminífero bentônico</t>
+        </is>
+      </c>
+      <c r="E265" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>Região de Volta Velha, Itapoá, SC — uma das três sondagens manuais feitas ali; coordenadas do resumo: 26°4'58,5"S, 48°37'54,3"W (a amostra com miliolídeos vem do estrato mais profundo do testemunho de Volta Velha)</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>Não informado no resumo</t>
+        </is>
+      </c>
+      <c r="H265" s="7" t="inlineStr">
+        <is>
+          <t>Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)</t>
+        </is>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Paraná (LECOST) e Universidade do Algarve (CIMA, Portugal) — afiliações dos autores</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr">
+        <is>
+          <t>Holoceno (os autores tratam os depósitos como holocênicos; idade do testemunho de Volta Velha não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="K265" s="7" t="inlineStr">
+        <is>
+          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): foram feitas 35 sondagens manuais em planícies costeiras do norte de Santa Catarina e do sul do Paraná — seis em SC (três em Volta Velha, Itapoá, e três na parte interna da Baía de São Francisco, nas planícies de Joinville e de Garuva) e uma no Paraná (Cabaraquara, Guaratuba) — para analisar foraminíferos. No testemunho de Volta Velha só uma amostra, a do estrato mais profundo, trouxe fauna composta predominantemente por miliolídeos; os autores a interpretam como indício de ambiente mais oxigenado, com maior influência marinha e salinidade mais alta, provavelmente uma região mais externa da baía. ESCOPO: o resumo não traz resultados separados nem identificação de espécies para as sondagens de Itapoá (demais amostras) e da Baía de São Francisco (Joinville/Garuva); os gêneros Ammonia e Elphidium que o resumo menciona são do testemunho de Guaratuba, no Paraná, e por isso não fazem parte deste registro. NOTA DE FONTE: só o resumo foi consultado e o texto declara resultados preliminares, com espécies ainda não identificadas. O documento não informa o evento nem o ano (agradece ao projeto CNPq 471039/2013-6), por isso a data está como s.d.; profundidade e datação 14C do testemunho de Volta Velha também não constam.</t>
+        </is>
+      </c>
+      <c r="L265" s="7" t="inlineStr">
+        <is>
+          <t>https://www.abequa.org.br/anais/247_resumo.pdf (Silva, Angulo, Souza &amp; Boski — resumo; evento e ano não constam do documento)</t>
+        </is>
+      </c>
+      <c r="M265" s="7" t="inlineStr">
+        <is>
+          <t>[referência sem formato bibliográfico, transcrita do descritor: Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)]</t>
+        </is>
+      </c>
+      <c r="N265" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="O265" s="6" t="inlineStr">
+        <is>
+          <t>Volta Velha (Itapoá) — testemunho da planície costeira</t>
+        </is>
+      </c>
+      <c r="P265" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q265" s="6" t="n">
+        <v>-26.0829</v>
+      </c>
+      <c r="R265" s="6" t="n">
+        <v>-48.6318</v>
+      </c>
+      <c r="S265" s="6" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
           <t>Depósito conchífero natural holocênico (lagunar/paleolagunar) da planície costeira; unidade litoestratigráfica formal não nomeada nas fontes consultadas</t>
         </is>
       </c>
-      <c r="C265" s="7" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
         <is>
           <t>Moluscos subfósseis do concheiro de Nova Brasília (12 espécies; dominantes: Heleobia australis, Cerithiopsis greeni, Crepidula plana, Nassarius vibex, Tellina lineata, Tagelus plebeius)</t>
         </is>
       </c>
-      <c r="D265" s="6" t="inlineStr">
+      <c r="D266" s="4" t="inlineStr">
         <is>
           <t>Invertebrado — moluscos (assembleia de bivalves e gastrópodes)</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E266" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F265" s="7" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
         <is>
           <t>Concheiro natural do rio D'Una, localidade de Nova Brasília, Imbituba, SC, na planície de inundação do rio D'Una, extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio; frentes de lavra de calcário de conchas (cerca de 4.000 m de comprimento, 420 m de largura e 0,60–6 m de espessura). Coordenadas não informadas nas fontes; ponto do mapa = centro do município de Imbituba (referência regional)</t>
         </is>
       </c>
-      <c r="G265" s="6" t="inlineStr">
+      <c r="G266" s="4" t="inlineStr">
         <is>
           <t>Não informado</t>
         </is>
       </c>
-      <c r="H265" s="7" t="inlineStr">
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011; Caruso Júnior, F. (1992) — "Geologia dos depósitos de conchas calcárias no estado de Santa Catarina", Geosul 7(14):101–136</t>
         </is>
       </c>
-      <c r="I265" s="6" t="inlineStr">
+      <c r="I266" s="4" t="inlineStr">
         <is>
           <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores (2000)</t>
         </is>
       </c>
-      <c r="J265" s="6" t="inlineStr">
+      <c r="J266" s="4" t="inlineStr">
         <is>
           <t>4.490 ± 200 anos AP (conchas; datação de Martin &amp; Suguio, 1986, citada por Caruso et al., 2000; 0,0045 Ma) — os próprios autores ressalvam que as conchas são alóctones e que a idade pode não ser a deposicional</t>
         </is>
       </c>
-      <c r="K265" s="7" t="inlineStr">
+      <c r="K266" s="5" t="inlineStr">
         <is>
           <t>CITAÇÃO EM REVISÃO — a lista de espécies é compilada por Caruso Júnior et al. (2000) a partir de levantamentos malacológicos anteriores (que o texto atribui a Forti-Esteves, 1986; Mendes, 1993; Pitoni, 1993), e esses levantamentos não foram examinados por este banco. CLASSIFICAÇÃO E CONTEÚDO (segundo o artigo): as espécies mais abundantes são Heleobia australis (d'Orbigny, 1835), Cerithiopsis greeni (C.B. Adams, 1839), Crepidula plana, Nassarius vibex, Tellina (Eurytellina) lineata e Tagelus plebeius; as duas primeiras são tidas como estuarinas e as demais como marinhas litorâneas. Também são citadas Neritina virginea, Cerithium stratum, Bulla striata, Ostrea equestris, Codakia costata e Anomalocardia brasiliana. O artigo grafa «Cerithiopis greeni» e «Nassarius viabex»; a grafia foi corrigida aqui. SEDIMENTOLOGIA E TAFONOMIA: o depósito tem unidades tabulares com estratificação cruzada de grande porte, alternando camadas arenosas e conchíferas, com gradação inversa; os autores propõem transporte por barras de corrente e um bloqueio do transporte sul–norte por um terraço pleistocênico, o que teria depositado o cascalho de conchas. LOCALIZAÇÃO: o artigo de 2000 localiza o depósito no extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio, na região de Nova Brasília; Caruso Júnior (1992) o situa na localidade de Nova Brasília, município de Imbituba, na planície de inundação do rio D'Una. VERIFICAÇÃO (2026.10.09): o artigo de 2000 não chama as conchas de «fósseis»; elas vêm de depósitos holocênicos e são tratadas aqui como subfósseis, no mesmo critério dos demais moluscos holocênicos do banco. A lista de ~30 táxons do anexo de Caruso Júnior (1992), identificada por I.P.F. Esteves em 1986, não traz o depósito de origem no trecho legível e a bibliografia da obra só cita um trabalho de Esteves sobre o concheiro de Jaboticabeira; por isso ela não foi atribuída a Nova Brasília nem aproveitada aqui.</t>
         </is>
       </c>
-      <c r="L265" s="7" t="inlineStr">
+      <c r="L266" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0001-37652000000200011
 https://www.scielo.br/j/aabc/a/PV3LvmfpkshVK6wWx8WgWSc/?lang=en (Caruso Júnior, Suguio &amp; Nakamura, 2000 — texto integral)
 https://periodicos.ufsc.br/index.php/geosul/article/download/12805/11988/39566 (Caruso Júnior, 1992 — texto integral, Geosul)</t>
         </is>
       </c>
-      <c r="M265" s="7" t="inlineStr">
+      <c r="M266" s="5" t="inlineStr">
         <is>
           <t>CARUSO JÚNIOR, F.; SUGUIO, K.; NAKAMURA, T. 2000. The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil). Anais da Academia Brasileira de Ciências, 72(2), 257–270. DOI: 10.1590/S0001-37652000000200011 | CARUSO JÚNIOR, F. 1992. Geologia dos depósitos de conchas calcárias no estado de Santa Catarina. Geosul, 7(14), 101–136.</t>
         </is>
       </c>
-      <c r="N265" s="6" t="n">
+      <c r="N266" s="4" t="n">
         <v>266</v>
       </c>
-      <c r="O265" s="6" t="inlineStr">
+      <c r="O266" s="4" t="inlineStr">
         <is>
           <t>Concheiro natural de Nova Brasília (Imbituba)</t>
         </is>
       </c>
-      <c r="P265" s="6" t="inlineStr">
+      <c r="P266" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q265" s="6" t="n">
+      <c r="Q266" s="4" t="n">
         <v>-28.193</v>
       </c>
-      <c r="R265" s="6" t="n">
+      <c r="R266" s="4" t="n">
         <v>-48.7019</v>
       </c>
-      <c r="S265" s="6" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
+      <c r="S266" s="4" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>Depósitos holocênicos de turfa, lama detrítica e areia fina da planície costeira (unidade litoestratigráfica não nomeada no artigo)</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
+      <c r="C267" s="7" t="inlineStr">
         <is>
           <t>Pólen e esporos do perfil de Poço Grande (planície costeira: dunas, plantas aquáticas e floresta pluvial atlântica)</t>
         </is>
       </c>
-      <c r="D266" s="4" t="inlineStr">
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E266" s="4" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
+      <c r="F267" s="7" t="inlineStr">
         <is>
           <t>Planície costeira norte de SC, a 800 m a noroeste do fim da estrada para o Rancho Nutrimental, perto da vila de Poço Grande (15 km ao sul de Joinville e a cerca de 20 km do Atlântico, segundo o artigo); 26°25′ S, 48°52′ O; 10–16 m de altitude. O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Guaramirim, a ~1 km da divisa com Joinville (por isso «região»)</t>
         </is>
       </c>
-      <c r="G266" s="4" t="inlineStr">
+      <c r="G267" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="H267" s="7" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I266" s="4" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J266" s="4" t="inlineStr">
+      <c r="J267" s="6" t="inlineStr">
         <is>
           <t>Holoceno superior: base do perfil extrapolada em ~4.840 anos 14C AP, até o presente; datações de 4.680 ± 150 (507–514 cm), 4.265 ± 190 (327–332 cm), 4.230 ± 185 (214–219 cm) e 3.525 ± 175 (127–132 cm); idades não calibradas; provável hiato</t>
         </is>
       </c>
-      <c r="K266" s="5" t="inlineStr">
+      <c r="K267" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de perfil sedimentar da planície costeira — registro paleoambiental do Holoceno superior. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): perfil de 587 cm (turfa «carr» com madeira, lama detrítica e areia fina; começa 5 cm abaixo da superfície), amostrado em 12/10/1989 perto do Rancho Nutrimental (o autor não pôde terminar a coleta por uma mudança de proprietário do rancho); contagem mínima de 508 grãos por amostra (média de 1.383). Quatro datações por 14C (Hv 17559–17562): 3.525 ± 175 anos AP (127–132 cm), 4.230 ± 185 (214–219), 4.265 ± 190 (327–332) e 4.680 ± 150 (507–514); idades não calibradas. RESULTADO (zonas A–E, segundo o autor e o resumo): A (~4.840–4.590 anos AP) — alternância repetida de duas comunidades de dunas perto do local (Myrtaceae, de dunas estáveis; Palmae, Ilex, Weinmannia e Schinus, de dunas pouco móveis) com variações do nível da água; B (~4.590–4.265) — depósitos de água doce, com sucessão de plantas aquáticas (Cabomba, Potamogeton, Myriophyllum, Echinodorus) e pólen alto de Alchornea, Urticales e Rapanea; C (~4.265–4.230) — curta, com Rapanea chegando a 15%; D (~4.230–3.525) — Alchornea chega a 24% e indica floresta densa perto do local; E (0–133 cm, início datado em 3.525 anos AP) — alto de Cyperaceae e sinais de ação humana no topo (queda de Alchornea, alta de Rapanea, drenagem da área do rancho). O autor aponta um provável hiato (a idade extrapolada para o início de E seria ~4.030 anos AP) e que a parte superior de E pode ter só alguns séculos. Os valores de Araucaria angustifolia e Dicksonia sellowiana (até ~2% e 5%) indicam, segundo ele, expansão da floresta de araucária no planalto no Holoceno superior. O autor relaciona mudanças do nível d’água na planície a variações do nível do mar (Fairbridge, 1962; Bigarella, 1965), sem comprová-las neste perfil. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Guaramirim, a ~1 km da divisa com Joinville; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
         </is>
       </c>
-      <c r="L266" s="5" t="inlineStr">
+      <c r="L267" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -24152,38 +24239,38 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M266" s="5" t="inlineStr">
+      <c r="M267" s="7" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n">
+      <c r="N267" s="6" t="n">
         <v>271</v>
       </c>
-      <c r="O266" s="4" t="inlineStr">
+      <c r="O267" s="6" t="inlineStr">
         <is>
           <t>Poço Grande (Guaramirim / Joinville)</t>
         </is>
       </c>
-      <c r="P266" s="4" t="inlineStr">
+      <c r="P267" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q266" s="4" t="n">
+      <c r="Q267" s="6" t="n">
         <v>-26.4167</v>
       </c>
-      <c r="R266" s="4" t="n">
+      <c r="R267" s="6" t="n">
         <v>-48.8667</v>
       </c>
-      <c r="S266" s="4" t="inlineStr">
+      <c r="S267" s="6" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S266"/>
+  <autoFilter ref="A3:S267"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -24198,7 +24285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B935"/>
+  <dimension ref="A1:B944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -34093,16 +34180,20 @@
         </is>
       </c>
     </row>
+    <row r="927">
+      <c r="A927" s="9" t="n"/>
+      <c r="B927" s="9" t="n"/>
+    </row>
     <row r="928">
-      <c r="A928" s="10" t="inlineStr">
+      <c r="A928" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B928" s="9" t="inlineStr"/>
+      <c r="B928" s="9" t="n"/>
     </row>
     <row r="929">
-      <c r="A929" s="11" t="inlineStr">
+      <c r="A929" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -34114,7 +34205,7 @@
       </c>
     </row>
     <row r="930">
-      <c r="A930" s="11" t="inlineStr">
+      <c r="A930" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -34126,7 +34217,7 @@
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="11" t="inlineStr">
+      <c r="A931" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -34138,7 +34229,7 @@
       </c>
     </row>
     <row r="932">
-      <c r="A932" s="11" t="inlineStr">
+      <c r="A932" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -34150,7 +34241,7 @@
       </c>
     </row>
     <row r="933">
-      <c r="A933" s="11" t="inlineStr">
+      <c r="A933" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -34162,7 +34253,7 @@
       </c>
     </row>
     <row r="934">
-      <c r="A934" s="11" t="inlineStr">
+      <c r="A934" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -34174,12 +34265,104 @@
       </c>
     </row>
     <row r="935">
-      <c r="A935" s="11" t="inlineStr">
+      <c r="A935" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B937" s="9" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B938" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B939" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B940" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B941" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B942" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B943" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B944" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -27222,7 +27222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B971"/>
+  <dimension ref="A1:B989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -37501,16 +37501,20 @@
         </is>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" s="9" t="n"/>
+      <c r="B963" s="9" t="n"/>
+    </row>
     <row r="964">
-      <c r="A964" s="10" t="inlineStr">
+      <c r="A964" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B964" s="9" t="inlineStr"/>
+      <c r="B964" s="9" t="n"/>
     </row>
     <row r="965">
-      <c r="A965" s="11" t="inlineStr">
+      <c r="A965" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -37522,7 +37526,7 @@
       </c>
     </row>
     <row r="966">
-      <c r="A966" s="11" t="inlineStr">
+      <c r="A966" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -37534,7 +37538,7 @@
       </c>
     </row>
     <row r="967">
-      <c r="A967" s="11" t="inlineStr">
+      <c r="A967" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -37546,7 +37550,7 @@
       </c>
     </row>
     <row r="968">
-      <c r="A968" s="11" t="inlineStr">
+      <c r="A968" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -37558,7 +37562,7 @@
       </c>
     </row>
     <row r="969">
-      <c r="A969" s="11" t="inlineStr">
+      <c r="A969" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -37570,7 +37574,7 @@
       </c>
     </row>
     <row r="970">
-      <c r="A970" s="11" t="inlineStr">
+      <c r="A970" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -37582,12 +37586,200 @@
       </c>
     </row>
     <row r="971">
-      <c r="A971" s="11" t="inlineStr">
+      <c r="A971" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="9" t="n"/>
+      <c r="B972" s="9" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B973" s="9" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B974" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B975" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B976" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B977" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B978" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B979" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B980" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B982" s="9" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B983" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B984" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B985" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B986" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B987" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B988" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B989" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$298</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S299"/>
+  <dimension ref="A1:S298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>296 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>295 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -24306,12 +24306,12 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
+          <t>Plataforma continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Lestodon armatus Gervais, 1855</t>
+          <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -24326,17 +24326,17 @@
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Plataforma continental entre Passo de Torres e Araranguá, SC (redes de arrasto de camarão — coordenada aproximada)</t>
+          <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>Museu Oceanográfico Univali, Balneário Piçarras, SC</t>
+          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>Citação de mídia — Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)</t>
+          <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr">
@@ -24346,65 +24346,64 @@
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>ca. 30.000 anos antes do presente, segundo a divulgação (método não informado)</t>
+          <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
         </is>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica. Segundo a divulgação, fósseis de lestodonte (Lestodon armatus) saíram de redes de arrasto de camarão na plataforma continental entre Passo de Torres e Araranguá, pertencem à 'formação Laguna-Barreira' e são 'datados de cerca de 30 mil anos antes do presente'; a equipe do museu encontrou 'ao menos dois' lestodontes, 'tratando-se do primeiro registro desta espécie no Estado'. A altura (~4,5 m) e o peso (~3 t) citados descrevem a espécie em geral, não o exemplar. O esqueleto montado está exposto no Museu Oceanográfico Univali (Balneário Piçarras). Não são informados identificador, tombo, data da coleta nem método de datação.</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
         </is>
       </c>
       <c r="L268" s="5" t="inlineStr">
         <is>
-          <t>https://novomomento.com.br/preguica-gigante-museu-oceanografico/
-https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx (página original; indisponível em 08/10/2026)</t>
+          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
         </is>
       </c>
       <c r="M268" s="5" t="inlineStr">
         <is>
-          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Museu Oceanográfico Univali, divulgação «Esqueleto de Preguiça-Gigante é atração no Museu Oceanográfico» (julho de 2022; página original indisponível em 08/10/2026), conforme reproduzida por Novo Momento (25/07/2022)]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
         </is>
       </c>
       <c r="N268" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
-          <t>Plataforma continental Passo de Torres–Araranguá</t>
+          <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>Plataforma Continental — Fm. Laguna-Barreira</t>
+          <t>Plataforma Continental (formação não informada na reportagem)</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n">
-        <v>-29.28</v>
+        <v>-29.22</v>
       </c>
       <c r="R268" s="4" t="n">
-        <v>-49.55</v>
+        <v>-49.5</v>
       </c>
       <c r="S268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>Pleistoceno Superior</t>
+          <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>Plataforma continental (formação não informada na reportagem)</t>
+          <t>Fm. Rio Bonito (segundo o comunicado da UDESC e a reportagem do ND Mais)</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
         <is>
-          <t>Toxodontidae indet. (“toxodonte” na reportagem; anteriormente rotulado Toxodon sp.)</t>
+          <t>Paleotoca Amaral de Baixo (icnofóssil de escavação — provável tatu extinto)</t>
         </is>
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>Vertebrado — mamífero</t>
+          <t>Icnofóssil — paleotoca</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
@@ -24414,62 +24413,63 @@
       </c>
       <c r="F269" s="7" t="inlineStr">
         <is>
-          <t>Costa de Sombrio, SC (vértebra torácica; achado em pesca de arrasto — coordenada aproximada)</t>
+          <t>Localidade Rio Amaral Gruta, Lauro Müller, SC (coordenada do município)</t>
         </is>
       </c>
       <c r="G269" s="6" t="inlineStr">
         <is>
-          <t>Não informado na reportagem (a descoberta foi divulgada pelo Museu Oceanográfico Univali)</t>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
         </is>
       </c>
       <c r="H269" s="7" t="inlineStr">
         <is>
-          <t>Citação de mídia — Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)</t>
+          <t>Citação de mídia — UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF); Citação de mídia — ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)</t>
         </is>
       </c>
       <c r="I269" s="6" t="inlineStr">
         <is>
-          <t>Univali</t>
+          <t>UDESC — Laboratório de Geografia Física (LGEF), grupo BioGeo, FAED (segundo o comunicado da UDESC); equipe técnica do Geoparque (segundo o ND Mais)</t>
         </is>
       </c>
       <c r="J269" s="6" t="inlineStr">
         <is>
-          <t>ca. 30.000 anos, segundo a reportagem para o conjunto do achado (método não informado)</t>
+          <t>Não datada; a reportagem fala em animais que viveram 'há cerca de 10 mil anos'</t>
         </is>
       </c>
       <c r="K269" s="7" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre este achado. A reportagem do Portal Litoral Sul diz que, junto à mandíbula do mastodonte (registro 68), foi recuperada 'uma vértebra torácica de um toxodonte, um animal parecido com o atual hipopótamo'. A reportagem usa apenas o nome popular 'toxodonte' (não menciona o gênero Toxodon); por isso o registro está em Toxodontidae indet. — o rótulo anterior deste banco, 'Toxodon sp.', ia além da fonte. Formação, tombo e local de guarda NÃO são informados. A segunda reportagem usada no registro 68 (Destino Florianópolis) não menciona o toxodonte. CONTEXTO CIENTÍFICO (não trata deste achado): Lopes &amp; Buchmann (2011, Journal of South American Earth Sciences 31(1):17–27) relatam restos de Toxodon sp. recolhidos por pescadores a cerca de 20 m na plataforma do sul do Brasil (o resumo cita Rio Grande do Sul).</t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
         </is>
       </c>
       <c r="L269" s="7" t="inlineStr">
         <is>
-          <t>https://portallitoralsul.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio/</t>
+          <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
+https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
       <c r="M269" s="7" t="inlineStr">
         <is>
-          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: Portal Litoral Sul, reportagem «Fóssil de elefante pré-histórico é encontrado em Sombrio» (que cita o G1), sobre achado divulgado pelo Museu Oceanográfico Univali (prof. Jules Soto, coordenador dos museus da universidade)]</t>
+          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
         </is>
       </c>
       <c r="N269" s="6" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="O269" s="6" t="inlineStr">
         <is>
-          <t>Costa de Sombrio (plataforma continental)</t>
+          <t>Lauro Müller</t>
         </is>
       </c>
       <c r="P269" s="6" t="inlineStr">
         <is>
-          <t>Plataforma Continental (formação não informada na reportagem)</t>
+          <t>Bacia do Paraná — Fm. Rio Bonito</t>
         </is>
       </c>
       <c r="Q269" s="6" t="n">
-        <v>-29.22</v>
+        <v>-28.4047</v>
       </c>
       <c r="R269" s="6" t="n">
-        <v>-49.5</v>
+        <v>-49.3811</v>
       </c>
       <c r="S269" s="6" t="inlineStr"/>
     </row>
@@ -24481,17 +24481,17 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Fm. Rio Bonito (segundo o comunicado da UDESC e a reportagem do ND Mais)</t>
+          <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada)</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Paleotoca Amaral de Baixo (icnofóssil de escavação — provável tatu extinto)</t>
+          <t>Pólen, esporos e carvão de turfeira da Serra do Tabuleiro (testemunho Ciama 2; ~39.700 anos)</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Icnofóssil — paleotoca</t>
+          <t>Microfóssil — palinomorfos (pólen e esporos) e partículas de carvão</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
@@ -24501,123 +24501,35 @@
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Localidade Rio Amaral Gruta, Lauro Müller, SC (coordenada do município)</t>
+          <t>Turfeira «Ciama 2», Parque Estadual da Serra do Tabuleiro, SC (27°53′48,46″ S; 48°52′5,33″ O; 860 m de altitude); testemunho de 169 cm coletado em 2005 com amostrador Russian</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>Estrutura in situ (icnofóssil não coletável)</t>
+          <t>Não informado na fonte consultada</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>Citação de mídia — UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF); Citação de mídia — ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)</t>
+          <t>Jeske-Pieruschka, V., Pillar, V.D., De Oliveira, M.A.T. &amp; Behling, H. (2013) — "New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro", Vegetation History and Archaeobotany 22(4):299–314, DOI 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
-          <t>UDESC — Laboratório de Geografia Física (LGEF), grupo BioGeo, FAED (segundo o comunicado da UDESC); equipe técnica do Geoparque (segundo o ND Mais)</t>
+          <t>Universität Göttingen (projeto de doutorado de V. Jeske-Pieruschka, sob H. Behling, segundo a página do projeto)</t>
         </is>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>Não datada; a reportagem fala em animais que viveram 'há cerca de 10 mil anos'</t>
+          <t>Últimos ~39.720 anos 14C AP (base extrapolada a 168 cm) até 2005 d.C. — do Pleistoceno Superior (glacial) ao Holoceno</t>
         </is>
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. CITAÇÃO DE MÍDIA — não foi localizada publicação científica (a UDESC informa que os dados serão apresentados no 4º Encontro Luso-Brasileiro de Patrimônio Geomorfológico e Geoconservação, em Pelotas/RS, em outubro). Segundo a UDESC (08/04/2026), a 'Paleotoca Amaral de Baixo', na localidade Rio Amaral Gruta, tem cerca de 25,9 m de comprimento, com uma ramificação, está na Fm. Rio Bonito (Depressão da Zona Carbonífera Catarinense) — 'primeiro registro documentado desse tipo de icnofóssil nessas rochas e nesse relevo' — e teria sido 'provavelmente' escavada por tatus extintos, com base nas marcas de garras e na posição elevada, próxima a cursos d'água. O ND Mais (24/03/2026) fala em cerca de 20 m de extensão e 1 m de diâmetro, ramificação obstruída, marcas de garras (G. Simão) e 'tatus gigantes, que viveram há cerca de 10 mil anos', e diz que a maioria das paleotocas do Sul do Brasil está em outras formações. Não há datação, coordenadas nem identificação da espécie. HISTÓRICO DE CORREÇÃO: o táxon constava como 'Xenarthra: tatus, preguiças, tamanduás' e a formação como 'depósitos superficiais sobre a Fm. Rio Bonito'; o comunicado cita preguiças e tamanduás só como exemplos do grupo e fala em Fm. Rio Bonito. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. </t>
+          <t>Classificação: microfósseis (pólen e esporos) e partículas de carvão de um testemunho de turfeira — registro paleoambiental quaternário, não um fóssil em rocha. Segundo o artigo, o testemunho (169 cm; oito datações AMS) cobre cerca de 39.720 anos. Resultados dos autores: campos (gramíneas subtropicais) cobriram extensas áreas do planalto durante todo o período glacial registrado, o que eles ligam a clima frio e seco; a floresta pluvial atlântica começou a se espalhar pelas encostas por volta de 10.400 anos cal AP, com clima mais quente e úmido; a floresta de araucária surge no Holoceno tardio (a partir de ~2.160 anos cal AP, com máximo após ~300 anos cal AP); e há abertura da floresta por perturbação recente (inclusive extração de madeira), com avanço dos campos entre 1940 e 2005. Fogo ausente no glacial e comum entre ~10.400 e ~3.600 anos cal AP, provavelmente por ameríndios (inferência dos autores). Os autores concluem que a serra costeira do Tabuleiro não foi refúgio glacial para táxons da floresta pluvial atlântica no Último Máximo Glacial. LOCALIZAÇÃO (2026.10.09): o artigo dá o Parque Estadual da Serra do Tabuleiro e as coordenadas acima, mas não nomeia o município. O parque abrange Florianópolis, Palhoça, Santo Amaro da Imperatriz, Águas Mornas, São Bonifácio, São Martinho, Imaruí e Paulo Lopes (Wikipédia). A etiqueta «São Bonifácio (região)» é uma derivação do compilador: as coordenadas informadas caem no polígono desse município na malha municipal do site; confirme com o mapa oficial antes de citar o município. NOTA DE FONTE: consultados a página do artigo no Springer (resumo e trechos do texto) e a cópia do resumo no Paperity; tabela de datações e diagramas não foram acessados. Número de tombo e depositário não se aplicam/não foram informados.</t>
         </is>
       </c>
       <c r="L270" s="5" t="inlineStr">
-        <is>
-          <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
-https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
-        </is>
-      </c>
-      <c r="M270" s="5" t="inlineStr">
-        <is>
-          <t>[Citação de mídia — reportagem ou divulgação, não é publicação científica: UDESC (08/04/2026), notícia «Pesquisadores da Udesc Faed identificam paleotoca em Lauro Müller», que cita o prof. Jairo Valdati (coordenador do LGEF)] | [Citação de mídia — reportagem ou divulgação, não é publicação científica: ND Mais (24/03/2026), reportagem «Túnel misterioso em SC revela marcas pré-históricas», que cita o geólogo G. Simão (Geoparque Caminhos dos Cânions do Sul)]</t>
-        </is>
-      </c>
-      <c r="N270" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="O270" s="4" t="inlineStr">
-        <is>
-          <t>Lauro Müller</t>
-        </is>
-      </c>
-      <c r="P270" s="4" t="inlineStr">
-        <is>
-          <t>Bacia do Paraná — Fm. Rio Bonito</t>
-        </is>
-      </c>
-      <c r="Q270" s="4" t="n">
-        <v>-28.4047</v>
-      </c>
-      <c r="R270" s="4" t="n">
-        <v>-49.3811</v>
-      </c>
-      <c r="S270" s="4" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Quaternário (Pleistoceno–Holoceno)</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
-        <is>
-          <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada)</t>
-        </is>
-      </c>
-      <c r="C271" s="7" t="inlineStr">
-        <is>
-          <t>Pólen, esporos e carvão de turfeira da Serra do Tabuleiro (testemunho Ciama 2; ~39.700 anos)</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
-        <is>
-          <t>Microfóssil — palinomorfos (pólen e esporos) e partículas de carvão</t>
-        </is>
-      </c>
-      <c r="E271" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F271" s="7" t="inlineStr">
-        <is>
-          <t>Turfeira «Ciama 2», Parque Estadual da Serra do Tabuleiro, SC (27°53′48,46″ S; 48°52′5,33″ O; 860 m de altitude); testemunho de 169 cm coletado em 2005 com amostrador Russian</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr">
-        <is>
-          <t>Não informado na fonte consultada</t>
-        </is>
-      </c>
-      <c r="H271" s="7" t="inlineStr">
-        <is>
-          <t>Jeske-Pieruschka, V., Pillar, V.D., De Oliveira, M.A.T. &amp; Behling, H. (2013) — "New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro", Vegetation History and Archaeobotany 22(4):299–314, DOI 10.1007/s00334-012-0382-y</t>
-        </is>
-      </c>
-      <c r="I271" s="6" t="inlineStr">
-        <is>
-          <t>Universität Göttingen (projeto de doutorado de V. Jeske-Pieruschka, sob H. Behling, segundo a página do projeto)</t>
-        </is>
-      </c>
-      <c r="J271" s="6" t="inlineStr">
-        <is>
-          <t>Últimos ~39.720 anos 14C AP (base extrapolada a 168 cm) até 2005 d.C. — do Pleistoceno Superior (glacial) ao Holoceno</t>
-        </is>
-      </c>
-      <c r="K271" s="7" t="inlineStr">
-        <is>
-          <t>Classificação: microfósseis (pólen e esporos) e partículas de carvão de um testemunho de turfeira — registro paleoambiental quaternário, não um fóssil em rocha. Segundo o artigo, o testemunho (169 cm; oito datações AMS) cobre cerca de 39.720 anos. Resultados dos autores: campos (gramíneas subtropicais) cobriram extensas áreas do planalto durante todo o período glacial registrado, o que eles ligam a clima frio e seco; a floresta pluvial atlântica começou a se espalhar pelas encostas por volta de 10.400 anos cal AP, com clima mais quente e úmido; a floresta de araucária surge no Holoceno tardio (a partir de ~2.160 anos cal AP, com máximo após ~300 anos cal AP); e há abertura da floresta por perturbação recente (inclusive extração de madeira), com avanço dos campos entre 1940 e 2005. Fogo ausente no glacial e comum entre ~10.400 e ~3.600 anos cal AP, provavelmente por ameríndios (inferência dos autores). Os autores concluem que a serra costeira do Tabuleiro não foi refúgio glacial para táxons da floresta pluvial atlântica no Último Máximo Glacial. LOCALIZAÇÃO (2026.10.09): o artigo dá o Parque Estadual da Serra do Tabuleiro e as coordenadas acima, mas não nomeia o município. O parque abrange Florianópolis, Palhoça, Santo Amaro da Imperatriz, Águas Mornas, São Bonifácio, São Martinho, Imaruí e Paulo Lopes (Wikipédia). A etiqueta «São Bonifácio (região)» é uma derivação do compilador: as coordenadas informadas caem no polígono desse município na malha municipal do site; confirme com o mapa oficial antes de citar o município. NOTA DE FONTE: consultados a página do artigo no Springer (resumo e trechos do texto) e a cópia do resumo no Paperity; tabela de datações e diagramas não foram acessados. Número de tombo e depositário não se aplicam/não foram informados.</t>
-        </is>
-      </c>
-      <c r="L271" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/s00334-012-0382-y (Jeske-Pieruschka et al., 2013 — página do artigo)
 https://paperity.org/p/6235978/new-insights-into-vegetation-climate-and-fire-history-of-southern-brazil-revealed-by-a-40 (cópia do resumo)
@@ -24625,93 +24537,93 @@
 https://en.wikipedia.org/wiki/Serra_do_Tabuleiro_State_Park (municípios do parque)</t>
         </is>
       </c>
-      <c r="M271" s="7" t="inlineStr">
+      <c r="M270" s="5" t="inlineStr">
         <is>
           <t>JESKE-PIERUSCHKA, V.; PILLAR, V.D.; DE OLIVEIRA, M.A.T. et al. 2013. New insights into vegetation, climate and fire history of southern Brazil revealed by a 40,000 year environmental record from the State Park Serra do Tabuleiro. Vegetation History and Archaeobotany, 22(4), 299–314. DOI: 10.1007/s00334-012-0382-y</t>
         </is>
       </c>
-      <c r="N271" s="6" t="n">
+      <c r="N270" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="O271" s="6" t="inlineStr">
+      <c r="O270" s="4" t="inlineStr">
         <is>
           <t>Serra do Tabuleiro (turfeira Ciama 2)</t>
         </is>
       </c>
-      <c r="P271" s="6" t="inlineStr">
+      <c r="P270" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q271" s="6" t="n">
+      <c r="Q270" s="4" t="n">
         <v>-27.8968</v>
       </c>
-      <c r="R271" s="6" t="n">
+      <c r="R270" s="4" t="n">
         <v>-48.8681</v>
       </c>
-      <c r="S271" s="6" t="inlineStr">
+      <c r="S270" s="4" t="inlineStr">
         <is>
           <t>10.1007/s00334-012-0382-y</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B272" s="4" t="inlineStr">
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C272" s="5" t="inlineStr">
+      <c r="C271" s="7" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira do Morro da Igreja (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D272" s="4" t="inlineStr">
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E272" s="4" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F272" s="5" t="inlineStr">
+      <c r="F271" s="7" t="inlineStr">
         <is>
           <t>Turfeira de altitude (cerca de 1.800 m) na borda do Parque Nacional de São Joaquim, a 300 m a oeste do ponto mais alto do Morro da Igreja, Urubici, SC (Behling, 1995; ponto do mapa aproximado, no próprio morro: ver observações)</t>
         </is>
       </c>
-      <c r="G272" s="4" t="inlineStr">
+      <c r="G271" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H272" s="5" t="inlineStr">
+      <c r="H271" s="7" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I272" s="4" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J272" s="4" t="inlineStr">
+      <c r="J271" s="6" t="inlineStr">
         <is>
           <t>Perfil de 144 cm: base datada em 10.200 ± 275 anos 14C AP até o presente (60 ± 120 anos AP aos 40–44 cm, idade que o autor atribui a influência de raízes atuais); idades não calibradas</t>
         </is>
       </c>
-      <c r="K272" s="5" t="inlineStr">
+      <c r="K271" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 30 × 40 m numa encosta voltada a oeste, de leve inclinação, a cerca de 1.800 m, na borda do Parque Nacional de São Joaquim e 300 m a oeste do ponto mais alto do morro, junto ao limite entre o planalto e as terras baixas; o autor a descreve nos campos da região alta, com floresta nebular nas encostas íngremes próximas. Amostragem em 04/12/1989 (amostrador Dachnowski); perfil de turfa de 144 cm sobre rocha (149 cm); contagem mínima de 1.215 grãos de pólen por amostra (média de 2.353). Duas datações por 14C (Laboratório de Hanover, Hv 17557 e Hv 17558): 60 ± 120 anos AP aos 40–44 cm e 10.200 ± 275 anos AP aos 140–144 cm, na base do perfil; idades não calibradas. RESULTADO: do início do perfil (~10.200 anos AP) até cerca de 1.000 anos AP os campos dominam o pólen; a floresta de araucária (Araucaria angustifolia, de 1% a 10% do pólen) se expande sobre os campos na zona 4a, que o autor estima em não mais de ~1.000 anos; a zona 4b (cerca de 100 anos) traz sinais de ação humana — queda da araucária (extração de madeira), grãos de Pinus e um de Zea mays — e o desaparecimento de Weinmannia entre 8 e 16 cm, que o autor atribui provavelmente ao grande incêndio de 1951 na floresta nebular da Serra Geral. Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco; esta turfeira registra apenas o fim dessa fase. LOCALIZAÇÃO (2026.10.09): o artigo dá o morro em 28°11′ S, 49°52′ O, «25 km a sudeste da vila de Urubici»; essas coordenadas caem, na malha municipal deste site, em São Joaquim (cerca de 30 km a oés-sudoeste de Urubici), o que não combina com «sudeste» nem com o morro conhecido (Wikipédia: 28°07′30″ S, 49°28′28″ O, 1.822 m, em Urubici). Possível erro de impressão no artigo, não verificado; o pino segue no próprio morro e é apenas aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
         </is>
       </c>
-      <c r="L272" s="5" t="inlineStr">
+      <c r="L271" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -24719,93 +24631,93 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M272" s="5" t="inlineStr">
+      <c r="M271" s="7" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N272" s="4" t="n">
+      <c r="N271" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="O272" s="4" t="inlineStr">
+      <c r="O271" s="6" t="inlineStr">
         <is>
           <t>Morro da Igreja (Urubici)</t>
         </is>
       </c>
-      <c r="P272" s="4" t="inlineStr">
+      <c r="P271" s="6" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q272" s="4" t="n">
+      <c r="Q271" s="6" t="n">
         <v>-28.125</v>
       </c>
-      <c r="R272" s="4" t="n">
+      <c r="R271" s="6" t="n">
         <v>-49.4744</v>
       </c>
-      <c r="S272" s="4" t="inlineStr">
+      <c r="S271" s="6" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B273" s="6" t="inlineStr">
+      <c r="B272" s="4" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C273" s="7" t="inlineStr">
+      <c r="C272" s="5" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira da Serra do Rio do Rastro (campos e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D273" s="6" t="inlineStr">
+      <c r="D272" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E272" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F273" s="7" t="inlineStr">
+      <c r="F272" s="5" t="inlineStr">
         <is>
           <t>Turfeira de altitude a 1.420 m, perto da rodovia SC-438, na Serra do Rio Rastro (grafia de Behling, 1995; a serra é conhecida como Serra do Rio do Rastro), entre Lauro Müller e Bom Jardim da Serra, SC; 28°23′ S, 49°33′ O segundo o artigo (precisão de minuto, ~2 km)</t>
         </is>
       </c>
-      <c r="G273" s="6" t="inlineStr">
+      <c r="G272" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H273" s="7" t="inlineStr">
+      <c r="H272" s="5" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I273" s="6" t="inlineStr">
+      <c r="I272" s="4" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J273" s="6" t="inlineStr">
+      <c r="J272" s="4" t="inlineStr">
         <is>
           <t>Perfil de 223 cm: base datada em 11.210 ± 385 anos 14C AP até o presente (6.410 ± 190 aos 150–155 cm; 2.385 ± 225 aos 74–79 cm); idades não calibradas</t>
         </is>
       </c>
-      <c r="K273" s="7" t="inlineStr">
+      <c r="K272" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo do registro nº 255. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 50 × 50 m numa pequena depressão rasa junto à escarpa íngreme da Serra Geral, a 1.420 m (400 m abaixo do Morro da Igreja), perto da rodovia SC-438 — o artigo diz «11 km a oeste da vila de Bom Jardim da Serra» e dá 28°23′ S, 49°33′ O. Amostragem em 04/05/1989 e 05/12/1989; perfil de 223 cm (argila sobre rocha abaixo disso); contagem mínima de 1.203 grãos por amostra (média de 5.917). Três datações por 14C: 2.385 ± 225 anos AP (74–79 cm, limite das zonas 2c e 3), 6.410 ± 190 (150–155 cm, perto da base da zona 2ab) e 11.210 ± 385 (215–220 cm, base do perfil); idades não calibradas. O autor nota que 6.410 anos AP é bem mais novo que os ~9.000 esperados no limite Pleistoceno–Holoceno, e explica a diferença por sedimentação extremamente lenta ou por um hiato. RESULTADO: na base (~11.200 anos AP) 93% do pólen é de campos (Poaceae ~55%, Cyperaceae ~15%, Asteraceae ~10%), sem floresta de araucária no local e com a floresta nebular ausente ou pouco representada; no Holoceno inicial e médio os campos seguem dominando (campo sujo mais desenvolvido na zona 2ab), com mudanças na floresta pluvial atlântica (queda de Myrtaceae, alta de Alchornea e Urticales); na zona 3 (7–76 cm) a araucária sobe de 1% a 5% e os campos descem de 89% a 83%, possivelmente com florestas de galeria ao longo dos rios; na zona 4a (0–7 cm) a araucária aumenta fortemente, como no Morro da Igreja. Segundo o resumo do artigo, a dominância dos campos continuou até cerca de 1.000 anos AP nas turfeiras do Morro da Igreja e da Serra do Rio Rastro. O autor aponta uma discrepância ainda não explicada entre a idade do limite 2c/3 aqui (2.385 ± 225) e a do início da zona 3 na Serra da Boa Vista (3.460 ± 195). LOCALIZAÇÃO (2026.10.09): pino movido para as coordenadas impressas no artigo (28°23′ S, 49°33′ O), que na malha deste site caem em Bom Jardim da Serra, a menos de 1 km da divisa com Lauro Müller (por isso o município segue como «região»); antes, o pino era o ponto da serra segundo a Wikipédia, em Lauro Müller. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. </t>
         </is>
       </c>
-      <c r="L273" s="7" t="inlineStr">
+      <c r="L272" s="5" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -24813,93 +24725,93 @@
 https://en.wikipedia.org/wiki/Serra_do_Rio_do_Rastro (localização da serra)</t>
         </is>
       </c>
-      <c r="M273" s="7" t="inlineStr">
+      <c r="M272" s="5" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N273" s="6" t="n">
+      <c r="N272" s="4" t="n">
         <v>256</v>
       </c>
-      <c r="O273" s="6" t="inlineStr">
+      <c r="O272" s="4" t="inlineStr">
         <is>
           <t>Serra do Rio do Rastro (Lauro Müller / Bom Jardim da Serra)</t>
         </is>
       </c>
-      <c r="P273" s="6" t="inlineStr">
+      <c r="P272" s="4" t="inlineStr">
         <is>
           <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
-      <c r="Q273" s="6" t="n">
+      <c r="Q272" s="4" t="n">
         <v>-28.3833</v>
       </c>
-      <c r="R273" s="6" t="n">
+      <c r="R272" s="4" t="n">
         <v>-49.55</v>
       </c>
-      <c r="S273" s="6" t="inlineStr">
+      <c r="S272" s="4" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B273" s="6" t="inlineStr">
         <is>
           <t>Depósito de turfeira quaternário (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
-      <c r="C274" s="5" t="inlineStr">
+      <c r="C273" s="7" t="inlineStr">
         <is>
           <t>Pólen e esporos da turfeira da Serra da Boa Vista (campos, floresta pluvial atlântica e floresta de araucária)</t>
         </is>
       </c>
-      <c r="D274" s="4" t="inlineStr">
+      <c r="D273" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E274" s="4" t="inlineStr">
+      <c r="E273" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F274" s="5" t="inlineStr">
+      <c r="F273" s="7" t="inlineStr">
         <is>
           <t>Turfeira de altitude a 1.160 m, nos contrafortes nordeste da Serra Geral, perto da BR-282 e a 10 km a leste da vila de São Leonardo (Behling, 1995); 27°42′ S, 49°09′ O segundo o artigo (precisão de minuto). O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner (por isso «região»)</t>
         </is>
       </c>
-      <c r="G274" s="4" t="inlineStr">
+      <c r="G273" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H274" s="5" t="inlineStr">
+      <c r="H273" s="7" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I274" s="4" t="inlineStr">
+      <c r="I273" s="6" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J274" s="4" t="inlineStr">
+      <c r="J273" s="6" t="inlineStr">
         <is>
           <t>Perfil de 140 cm: base ≈ 13.900–14.100 anos 14C AP (13.905 ± 295 aos 131–135 cm; 14.105 ± 510 aos 61–65 cm), 6.930 ± 195 aos 45–50 cm e 3.460 ± 185 aos 31–35 cm (± 195 no texto); idades não calibradas</t>
         </is>
       </c>
-      <c r="K274" s="5" t="inlineStr">
+      <c r="K273" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de turfeira de altitude — registro paleoambiental quaternário, do mesmo estudo dos registros nº 255 e 256. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): turfeira de 10–16 × 40 m numa pequena encosta de inclinação leste–oeste relativamente íngreme, atrás de uma escarpa de 3 m, a 1.160 m, nos contrafortes nordeste da Serra Geral, «não longe da BR 282» e a 10 km a leste da vila de São Leonardo; 27°42′ S, 49°09′ O. Amostragem em 03/12/1989; perfil de 140 cm (subsolo rochoso aos 140 cm); contagem mínima de 979 grãos por amostra (média de 3.683). Quatro datações por 14C (Hv 17563–17566): 3.460 ± 185 anos AP (31–35 cm; ± 195 no texto), 6.930 ± 195 (45–50 cm), 14.105 ± 510 (61–65 cm) e 13.905 ± 295 (131–135 cm); idades não calibradas. O autor nota que 6.930 anos AP, no início do Holoceno, é mais novo que o esperado, e explica por sedimentação extremamente lenta ou por um hiato. RESULTADO: a turfeira está na zona de campos. Na base (zona 1a, ~14.000 anos AP) cerca de 90% do pólen é de campos (Poaceae ~60%), com os táxons da floresta de araucária raros — a araucária ficava nos vales — e Myrtaceae dominando a planície costeira; a zona 1c é estimada, por taxa de sedimentação constante, em ~10.000–10.500 anos AP; na zona 2 (6.930 anos AP) há florestação intensa, com Weinmannia paulliniifolia (floresta pluvial atlântica) chegando a 50% do pólen; na zona 3 (a partir de 3.460 anos AP) os campos avançam e Ilex, Symplocos e Clethra, da floresta de araucária, têm a maior representação, o que o autor atribui a clima mais frio; nas zonas 4a e 4b a floresta pluvial atlântica (Alchornea, Urticales) se expande, a araucária fica abaixo de 2% do pólen (contra 10% no Morro da Igreja e na Serra do Rio Rastro) e a 4b (cerca de 100 anos) mostra ação humana (Pinus de plantios modernos, desmatamento de araucária). Para o Pleistoceno tardio (14.000–10.000 anos 14C AP) o conjunto das turfeiras indica campos, com araucária só em vales profundos, sob clima frio e relativamente seco. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Rancho Queimado, a ~0,3 km da divisa com Alfredo Wagner; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. CONTEXTO CIENTÍFICO: Behling, Pillar, Orlóci &amp; Bauermann (2004, Palaeogeography, Palaeoclimatology, Palaeoecology 203:277–297, DOI 10.1016/S0031-0182(03)00687-4), ao discutir o testemunho de Cambará do Sul (RS), retomam as idades de Behling (1995) para as turfeiras catarinenses (3460 ± 195 anos 14C AP na Serra da Boa Vista e 2385 ± 225 na Serra do Rio Rastro, e a expansão marcante da araucária por volta de 1000 anos AP no Morro da Igreja e na Serra do Rio Rastro), que conferem com as datações do artigo original. Esse artigo trata de um sítio do Rio Grande do Sul; só as idades de SC foram aproveitadas aqui. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
         </is>
       </c>
-      <c r="L274" s="5" t="inlineStr">
+      <c r="L273" s="7" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -24907,35 +24819,123 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
+      <c r="M273" s="7" t="inlineStr">
+        <is>
+          <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
+        </is>
+      </c>
+      <c r="N273" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="O273" s="6" t="inlineStr">
+        <is>
+          <t>Serra da Boa Vista (Rancho Queimado / Alfredo Wagner)</t>
+        </is>
+      </c>
+      <c r="P273" s="6" t="inlineStr">
+        <is>
+          <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
+        </is>
+      </c>
+      <c r="Q273" s="6" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="R273" s="6" t="n">
+        <v>-49.15</v>
+      </c>
+      <c r="S273" s="6" t="inlineStr">
+        <is>
+          <t>10.1007/BF00203932</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>Invertebrado — gastrópode</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H274" s="5" t="inlineStr">
+        <is>
+          <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — "Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages", Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>IGc-USP; UFPR</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: gastrópode incrustante. Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="inlineStr">
+        <is>
+          <t>https://sigep.eco.br/sitio075/sitio075.pdf
+https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
+        </is>
+      </c>
       <c r="M274" s="5" t="inlineStr">
         <is>
-          <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
+          <t>ANGULO, R.J.; GIANNINI, P.C.F.; SUGUIO, K. et al. 1999. Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages. Marine Geology, 159, 323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222.</t>
         </is>
       </c>
       <c r="N274" s="4" t="n">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="O274" s="4" t="inlineStr">
         <is>
-          <t>Serra da Boa Vista (Rancho Queimado / Alfredo Wagner)</t>
+          <t>Costões Laguna–Imbituba</t>
         </is>
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
+          <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n">
-        <v>-27.7</v>
+        <v>-28.42</v>
       </c>
       <c r="R274" s="4" t="n">
-        <v>-49.15</v>
-      </c>
-      <c r="S274" s="4" t="inlineStr">
-        <is>
-          <t>10.1007/BF00203932</t>
-        </is>
-      </c>
+        <v>-48.74</v>
+      </c>
+      <c r="S274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -24945,17 +24945,17 @@
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
+          <t>Depósitos turfosos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
+          <t>Palinomorfos holocênicos (54 morfotipos: fungos, algas, briófitas, pteridófitas, pólen de gimnospermas e outros)</t>
         </is>
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>Invertebrado — gastrópode</t>
+          <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
@@ -24965,140 +24965,143 @@
       </c>
       <c r="F275" s="7" t="inlineStr">
         <is>
-          <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
+          <t>Duas seções com turfa na Planície Costeira sul-catarinense, nos municípios de Santa Rosa do Sul e São João do Sul, SC (nomes das turfeiras e coordenadas não informados no resumo consultado; ponto aproximado, entre os centros dos dois municípios)</t>
         </is>
       </c>
       <c r="G275" s="6" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Não informado no resumo consultado</t>
         </is>
       </c>
       <c r="H275" s="7" t="inlineStr">
         <is>
-          <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — "Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages", Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
+          <t>Cancelli, R.R., Souza, P.A. &amp; Neves, P.C.P. (2012) — "Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil", Acta Botanica Brasilica 26(1):20–37, DOI 10.1590/S0102-33062012000100004</t>
         </is>
       </c>
       <c r="I275" s="6" t="inlineStr">
         <is>
-          <t>IGc-USP; UFPR</t>
+          <t>UFRGS (Porto Alegre) e Universidade Luterana do Brasil (Canoas) — afiliações dos autores</t>
         </is>
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
+          <t>ca. 7.908 anos AP (base do testemunho de Santa Rosa do Sul) até o presente — 0,0079 Ma</t>
         </is>
       </c>
       <c r="K275" s="7" t="inlineStr">
         <is>
-          <t>Classificação: gastrópode incrustante. Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
+          <t>Segundo o resumo, o estudo apresenta resultados palinológicos de duas seções com turfa na Planície Costeira sul-catarinense, em Santa Rosa do Sul e São João do Sul; uma amostra basal do testemunho de Santa Rosa do Sul foi datada em 7908 ± 33 anos AP (Holoceno Inferior; o título cita ± 30). Foram descritos e ilustrados 54 palinomorfos: 21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 pólens de gimnospermas e 7 outros (uma cápsula de briófita, 4 fragmentos de invertebrados e 2 palinoforaminíferos indeterminados). Nomes das turfeiras, coordenadas, espessura dos testemunhos e táxons individuais NÃO constam no resumo consultado (o texto integral não foi aberto); por isso o ponto no mapa é aproximado. REGISTRO NOVO (2026.09.14), com fonte própria; não deve ser confundido com o nº 040 (Lagoa do Sombrio), removido em 2026.09.13. VERIFICAÇÃO (2026.10.09): o resumo de Cancelli, Souza &amp; Dehnhardt (XIII ABEQUA) descreve o testemunho de Santa Rosa do Sul como PCSC-1 (29°10'42"S, 49°44'58"W, mata paludial próxima à Lagoa do Sombrio, 570 cm, base datada em 7.908 ± 33 anos cal AP) e informa 112 palinomorfos ao todo — 58 de pólen de angiospermas mais os 54 palinomorfos não-pólen (21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 gimnospermas e 7 outros) que o artigo de 2012 descreve e ilustra. A microfauna do mesmo testemunho está no registro nº 264. O ponto deste registro continua aproximado porque ele cobre também a seção de São João do Sul, cujo local não foi informado.</t>
         </is>
       </c>
       <c r="L275" s="7" t="inlineStr">
-        <is>
-          <t>https://sigep.eco.br/sitio075/sitio075.pdf
-https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
-        </is>
-      </c>
-      <c r="M275" s="7" t="inlineStr">
-        <is>
-          <t>ANGULO, R.J.; GIANNINI, P.C.F.; SUGUIO, K. et al. 1999. Relative sea-level changes in the last 5500 years in southern Brazil (Laguna–Imbituba region, Santa Catarina State) based on vermetid 14C ages. Marine Geology, 159, 323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222.</t>
-        </is>
-      </c>
-      <c r="N275" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="O275" s="6" t="inlineStr">
-        <is>
-          <t>Costões Laguna–Imbituba</t>
-        </is>
-      </c>
-      <c r="P275" s="6" t="inlineStr">
-        <is>
-          <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
-        </is>
-      </c>
-      <c r="Q275" s="6" t="n">
-        <v>-28.42</v>
-      </c>
-      <c r="R275" s="6" t="n">
-        <v>-48.74</v>
-      </c>
-      <c r="S275" s="6" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="4" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>Depósitos turfosos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
-        </is>
-      </c>
-      <c r="C276" s="5" t="inlineStr">
-        <is>
-          <t>Palinomorfos holocênicos (54 morfotipos: fungos, algas, briófitas, pteridófitas, pólen de gimnospermas e outros)</t>
-        </is>
-      </c>
-      <c r="D276" s="4" t="inlineStr">
-        <is>
-          <t>Microfóssil — palinomorfos</t>
-        </is>
-      </c>
-      <c r="E276" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>Duas seções com turfa na Planície Costeira sul-catarinense, nos municípios de Santa Rosa do Sul e São João do Sul, SC (nomes das turfeiras e coordenadas não informados no resumo consultado; ponto aproximado, entre os centros dos dois municípios)</t>
-        </is>
-      </c>
-      <c r="G276" s="4" t="inlineStr">
-        <is>
-          <t>Não informado no resumo consultado</t>
-        </is>
-      </c>
-      <c r="H276" s="5" t="inlineStr">
-        <is>
-          <t>Cancelli, R.R., Souza, P.A. &amp; Neves, P.C.P. (2012) — "Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil", Acta Botanica Brasilica 26(1):20–37, DOI 10.1590/S0102-33062012000100004</t>
-        </is>
-      </c>
-      <c r="I276" s="4" t="inlineStr">
-        <is>
-          <t>UFRGS (Porto Alegre) e Universidade Luterana do Brasil (Canoas) — afiliações dos autores</t>
-        </is>
-      </c>
-      <c r="J276" s="4" t="inlineStr">
-        <is>
-          <t>ca. 7.908 anos AP (base do testemunho de Santa Rosa do Sul) até o presente — 0,0079 Ma</t>
-        </is>
-      </c>
-      <c r="K276" s="5" t="inlineStr">
-        <is>
-          <t>Segundo o resumo, o estudo apresenta resultados palinológicos de duas seções com turfa na Planície Costeira sul-catarinense, em Santa Rosa do Sul e São João do Sul; uma amostra basal do testemunho de Santa Rosa do Sul foi datada em 7908 ± 33 anos AP (Holoceno Inferior; o título cita ± 30). Foram descritos e ilustrados 54 palinomorfos: 21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 pólens de gimnospermas e 7 outros (uma cápsula de briófita, 4 fragmentos de invertebrados e 2 palinoforaminíferos indeterminados). Nomes das turfeiras, coordenadas, espessura dos testemunhos e táxons individuais NÃO constam no resumo consultado (o texto integral não foi aberto); por isso o ponto no mapa é aproximado. REGISTRO NOVO (2026.09.14), com fonte própria; não deve ser confundido com o nº 040 (Lagoa do Sombrio), removido em 2026.09.13. VERIFICAÇÃO (2026.10.09): o resumo de Cancelli, Souza &amp; Dehnhardt (XIII ABEQUA) descreve o testemunho de Santa Rosa do Sul como PCSC-1 (29°10'42"S, 49°44'58"W, mata paludial próxima à Lagoa do Sombrio, 570 cm, base datada em 7.908 ± 33 anos cal AP) e informa 112 palinomorfos ao todo — 58 de pólen de angiospermas mais os 54 palinomorfos não-pólen (21 fungos, 5 algas, 1 acritarco, 1 incertae sedis, 2 briófitas, 15 pteridófitas, 2 gimnospermas e 7 outros) que o artigo de 2012 descreve e ilustra. A microfauna do mesmo testemunho está no registro nº 264. O ponto deste registro continua aproximado porque ele cobre também a seção de São João do Sul, cujo local não foi informado.</t>
-        </is>
-      </c>
-      <c r="L276" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0102-33062012000100004
 https://paperity.org/p/187352977/fungos-criptogamas-e-outros-palinomorfos-holocenicos-7908-30-anos-ap-atual-da-planicie
 https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
+      <c r="M275" s="7" t="inlineStr">
+        <is>
+          <t>CANCELLI, R.R.; SOUZA, P.A.; NEVES, P.C.P. 2012. Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil. Acta Botanica Brasilica, 26(1), 20–37. DOI: 10.1590/S0102-33062012000100004</t>
+        </is>
+      </c>
+      <c r="N275" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="O275" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira sul-catarinense (turfeiras de Santa Rosa do Sul e São João do Sul)</t>
+        </is>
+      </c>
+      <c r="P275" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q275" s="6" t="n">
+        <v>-29.1613</v>
+      </c>
+      <c r="R275" s="6" t="n">
+        <v>-49.7767</v>
+      </c>
+      <c r="S275" s="6" t="inlineStr">
+        <is>
+          <t>10.1590/S0102-33062012000100004</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Sedimentos holocênicos da Lagoa do Peri (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>Diatomáceas holocênicas da Lagoa do Peri (44 táxons; Aulacoseira ambigua, Paralia sulcata)</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — diatomáceas</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Lagoa do Peri, Florianópolis, SC (27°43′30″S, 48°32′30″W); testemunho coletado com amostrador de Livingstone, da superfície a 2,10 m</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
+        <is>
+          <t>Saupe, A.C. &amp; Mosimann, R.M.S. (2003) — "Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil", Insula 32:33 [resumo de uma página]</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>Tecpar (Curitiba) e UFSC (Florianópolis) — afiliações das autoras</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno (o resumo cita o método do 14C, mas não informa idades)</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: microfóssil silicoso (diatomáceas em sedimento holocênico). Saupe &amp; Mosimann (2003) analisaram 26 amostras de um testemunho da Lagoa do Peri, da superfície a 2,10 m, e identificaram 44 táxons específicos e infraespecíficos, de 30 gêneros e 25 famílias; Triceratiaceae e Plagiogrammaceae são as famílias mais bem representadas (três gêneros cada) e Pinnularia, o gênero mais rico (cinco espécies). Aulacoseira ambigua é abundante nas camadas superiores e indica o ambiente atual, de água doce; Paralia sulcata é abundante nas camadas profundas, o que as autoras associam à origem marinha original da lagoa. O resumo não traz a lista completa de espécies, idades, depositário nem número de tombo; a fonte é um resumo de uma página.</t>
+        </is>
+      </c>
+      <c r="L276" s="5" t="inlineStr">
+        <is>
+          <t>https://periodicos.ufsc.br/index.php/insula/article/view/21194 (Saupe &amp; Mosimann, 2003 — resumo)</t>
+        </is>
+      </c>
       <c r="M276" s="5" t="inlineStr">
         <is>
-          <t>CANCELLI, R.R.; SOUZA, P.A.; NEVES, P.C.P. 2012. Fungos, criptógamas e outros palinomorfos holocênicos (7908±30 anos AP-atual) da Planície Costeira sul-catarinense, Brasil. Acta Botanica Brasilica, 26(1), 20–37. DOI: 10.1590/S0102-33062012000100004</t>
+          <t>SAUPE, A.C.; MOSIMANN, R.M.S. 2003. Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil. Insula, 32, 33 [resumo de uma página].</t>
         </is>
       </c>
       <c r="N276" s="4" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="O276" s="4" t="inlineStr">
         <is>
-          <t>Planície Costeira sul-catarinense (turfeiras de Santa Rosa do Sul e São João do Sul)</t>
+          <t>Lagoa do Peri (Florianópolis)</t>
         </is>
       </c>
       <c r="P276" s="4" t="inlineStr">
@@ -25107,16 +25110,12 @@
         </is>
       </c>
       <c r="Q276" s="4" t="n">
-        <v>-29.1613</v>
+        <v>-27.725</v>
       </c>
       <c r="R276" s="4" t="n">
-        <v>-49.7767</v>
-      </c>
-      <c r="S276" s="4" t="inlineStr">
-        <is>
-          <t>10.1590/S0102-33062012000100004</t>
-        </is>
-      </c>
+        <v>-48.5417</v>
+      </c>
+      <c r="S276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -25126,17 +25125,17 @@
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>Sedimentos holocênicos da Lagoa do Peri (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Sedimentos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>Diatomáceas holocênicas da Lagoa do Peri (44 táxons; Aulacoseira ambigua, Paralia sulcata)</t>
+          <t>Palinomorfos holocênicos de Garopaba (84 táxons: pólen, esporos, fungos, algas, acritarcos, cistos de dinoflagelados)</t>
         </is>
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — diatomáceas</t>
+          <t>Microfóssil — palinomorfos</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
@@ -25146,139 +25145,144 @@
       </c>
       <c r="F277" s="7" t="inlineStr">
         <is>
-          <t>Lagoa do Peri, Florianópolis, SC (27°43′30″S, 48°32′30″W); testemunho coletado com amostrador de Livingstone, da superfície a 2,10 m</t>
+          <t>Planície Costeira de Santa Catarina, município de Garopaba, SC — testemunho PCSC-3 (450 cm), a cerca de 2 km do oceano (coordenadas do testemunho não informadas; ponto aproximado no centro do município)</t>
         </is>
       </c>
       <c r="G277" s="6" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Não informado nos resumos consultados</t>
         </is>
       </c>
       <c r="H277" s="7" t="inlineStr">
         <is>
-          <t>Saupe, A.C. &amp; Mosimann, R.M.S. (2003) — "Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil", Insula 32:33 [resumo de uma página]</t>
+          <t>Kuhn, L.A., Souza, P.A., Cancelli, R.R., Silva, W.G. &amp; Macedo, R.B. (2017) — "Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State", Anais da Academia Brasileira de Ciências 89(4):2581–2595, DOI 10.1590/0001-3765201720160895; Kuhn, L.A. (2017) — "Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil)", Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
         <is>
-          <t>Tecpar (Curitiba) e UFSC (Florianópolis) — afiliações das autoras</t>
+          <t>UFRGS (Instituto de Geociências)</t>
         </is>
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>Holoceno (o resumo cita o método do 14C, mas não informa idades)</t>
+          <t>ca. 5.390 anos cal AP (base) até o presente — Holoceno Médio a Superior</t>
         </is>
       </c>
       <c r="K277" s="7" t="inlineStr">
         <is>
-          <t>Classificação: microfóssil silicoso (diatomáceas em sedimento holocênico). Saupe &amp; Mosimann (2003) analisaram 26 amostras de um testemunho da Lagoa do Peri, da superfície a 2,10 m, e identificaram 44 táxons específicos e infraespecíficos, de 30 gêneros e 25 famílias; Triceratiaceae e Plagiogrammaceae são as famílias mais bem representadas (três gêneros cada) e Pinnularia, o gênero mais rico (cinco espécies). Aulacoseira ambigua é abundante nas camadas superiores e indica o ambiente atual, de água doce; Paralia sulcata é abundante nas camadas profundas, o que as autoras associam à origem marinha original da lagoa. O resumo não traz a lista completa de espécies, idades, depositário nem número de tombo; a fonte é um resumo de uma página.</t>
+          <t>Classificação: microfósseis orgânicos (palinomorfos) de um testemunho holocênico. Foram analisadas 46 amostras do testemunho PCSC-3 (450 cm), com três datações por radiocarbono (5.390 anos cal AP aos 430 cm; 3.756 aos 360 cm; 858 aos 80 cm), e reconhecidos 84 táxons: pólen de angiospermas e de gimnospermas, esporos de pteridófitas e de briófitas, esporos de fungos, algas, três acritarcos (descritos e ilustrados na dissertação), dois cistos de dinoflagelados e forros de microforaminíferos. Entre os táxons citados no artigo estão Ilex, Myrtaceae, Arecaceae, Araucaria angustifolia, Alnus, Botryococcus, Micrhystridium, Operculodinium e Spiniferites. A análise de agrupamento definiu três fases: I, laguna com influência marinha (desde ~5.390 anos cal AP); II, ainda lagunar, com menos influência marinha e mais algas de água doce (~3.032 a 858 anos cal AP); III, sedimentação subaquosa em condições de pântano (últimos ~856 anos). Número de tombo e depositário não constam nos resumos consultados; as contagens por grupo diferem entre o resumo da dissertação e o do artigo, e por isso só o total de 84 táxons é dado aqui.</t>
         </is>
       </c>
       <c r="L277" s="7" t="inlineStr">
-        <is>
-          <t>https://periodicos.ufsc.br/index.php/insula/article/view/21194 (Saupe &amp; Mosimann, 2003 — resumo)</t>
-        </is>
-      </c>
-      <c r="M277" s="7" t="inlineStr">
-        <is>
-          <t>SAUPE, A.C.; MOSIMANN, R.M.S. 2003. Diatomáceas (Bacillariophyta) preservadas nos sedimentos holocênicos da Lagoa do Peri, Florianópolis, SC, Brasil. Insula, 32, 33 [resumo de uma página].</t>
-        </is>
-      </c>
-      <c r="N277" s="6" t="n">
-        <v>236</v>
-      </c>
-      <c r="O277" s="6" t="inlineStr">
-        <is>
-          <t>Lagoa do Peri (Florianópolis)</t>
-        </is>
-      </c>
-      <c r="P277" s="6" t="inlineStr">
-        <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
-        </is>
-      </c>
-      <c r="Q277" s="6" t="n">
-        <v>-27.725</v>
-      </c>
-      <c r="R277" s="6" t="n">
-        <v>-48.5417</v>
-      </c>
-      <c r="S277" s="6" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="4" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>Sedimentos holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
-        </is>
-      </c>
-      <c r="C278" s="5" t="inlineStr">
-        <is>
-          <t>Palinomorfos holocênicos de Garopaba (84 táxons: pólen, esporos, fungos, algas, acritarcos, cistos de dinoflagelados)</t>
-        </is>
-      </c>
-      <c r="D278" s="4" t="inlineStr">
-        <is>
-          <t>Microfóssil — palinomorfos</t>
-        </is>
-      </c>
-      <c r="E278" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>Planície Costeira de Santa Catarina, município de Garopaba, SC — testemunho PCSC-3 (450 cm), a cerca de 2 km do oceano (coordenadas do testemunho não informadas; ponto aproximado no centro do município)</t>
-        </is>
-      </c>
-      <c r="G278" s="4" t="inlineStr">
-        <is>
-          <t>Não informado nos resumos consultados</t>
-        </is>
-      </c>
-      <c r="H278" s="5" t="inlineStr">
-        <is>
-          <t>Kuhn, L.A., Souza, P.A., Cancelli, R.R., Silva, W.G. &amp; Macedo, R.B. (2017) — "Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State", Anais da Academia Brasileira de Ciências 89(4):2581–2595, DOI 10.1590/0001-3765201720160895; Kuhn, L.A. (2017) — "Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil)", Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul</t>
-        </is>
-      </c>
-      <c r="I278" s="4" t="inlineStr">
-        <is>
-          <t>UFRGS (Instituto de Geociências)</t>
-        </is>
-      </c>
-      <c r="J278" s="4" t="inlineStr">
-        <is>
-          <t>ca. 5.390 anos cal AP (base) até o presente — Holoceno Médio a Superior</t>
-        </is>
-      </c>
-      <c r="K278" s="5" t="inlineStr">
-        <is>
-          <t>Classificação: microfósseis orgânicos (palinomorfos) de um testemunho holocênico. Foram analisadas 46 amostras do testemunho PCSC-3 (450 cm), com três datações por radiocarbono (5.390 anos cal AP aos 430 cm; 3.756 aos 360 cm; 858 aos 80 cm), e reconhecidos 84 táxons: pólen de angiospermas e de gimnospermas, esporos de pteridófitas e de briófitas, esporos de fungos, algas, três acritarcos (descritos e ilustrados na dissertação), dois cistos de dinoflagelados e forros de microforaminíferos. Entre os táxons citados no artigo estão Ilex, Myrtaceae, Arecaceae, Araucaria angustifolia, Alnus, Botryococcus, Micrhystridium, Operculodinium e Spiniferites. A análise de agrupamento definiu três fases: I, laguna com influência marinha (desde ~5.390 anos cal AP); II, ainda lagunar, com menos influência marinha e mais algas de água doce (~3.032 a 858 anos cal AP); III, sedimentação subaquosa em condições de pântano (últimos ~856 anos). Número de tombo e depositário não constam nos resumos consultados; as contagens por grupo diferem entre o resumo da dissertação e o do artigo, e por isso só o total de 84 táxons é dado aqui.</t>
-        </is>
-      </c>
-      <c r="L278" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/0001-3765201720160895
 https://www.redalyc.org/pdf/327/32754216004.pdf (Kuhn et al., 2017)
 https://lume.ufrgs.br/handle/10183/153388 (dissertação de Kuhn, 2017)</t>
         </is>
       </c>
+      <c r="M277" s="7" t="inlineStr">
+        <is>
+          <t>KUHN, L.A.; SOUZA, P.A.; CANCELLI, R.R. et al. 2017. Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State. Anais da Academia Brasileira de Ciências, 89(4), 2581–2595. DOI: 10.1590/0001-3765201720160895 | KUHN, L.A. 2017. Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil). Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul.</t>
+        </is>
+      </c>
+      <c r="N277" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="O277" s="6" t="inlineStr">
+        <is>
+          <t>Garopaba (testemunho PCSC-3)</t>
+        </is>
+      </c>
+      <c r="P277" s="6" t="inlineStr">
+        <is>
+          <t>Planície Costeira — Depósitos Quaternários</t>
+        </is>
+      </c>
+      <c r="Q277" s="6" t="n">
+        <v>-28.0276</v>
+      </c>
+      <c r="R277" s="6" t="n">
+        <v>-48.6195</v>
+      </c>
+      <c r="S277" s="6" t="inlineStr">
+        <is>
+          <t>10.1590/0001-3765201720160895</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Sedimentos holocênicos da Planície Costeira sul-catarinense (unidade litoestratigráfica não informada no resumo)</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>Diatomáceas holocênicas da Lagoa do Sombrio (Paralia sulcata, Navicula schadei, Staurosira construens, Cyclotella baltica)</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>Microfóssil — diatomáceas</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Lagoa do Sombrio, Planície Costeira do sul de Santa Catarina — testemunho de 570 cm (município e coordenadas não informados no resumo; ponto aproximado na sede de Sombrio)</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>Não informado no resumo consultado</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
+          <t>Santos, S.M. &amp; Souza, P.A. (2016) — "Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas", XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo]</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr">
+        <is>
+          <t>UFRGS (Porto Alegre)</t>
+        </is>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>ca. 7.900 a 2.500 anos AP (segundo o resumo; resultados parciais)</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="inlineStr">
+        <is>
+          <t>Classificação: microfóssil silicoso (diatomáceas) de sedimento holocênico. O resumo trata de resultados parciais de um testemunho de 570 cm, do qual foram estudadas 12 amostras (50 a 570 cm): 14 ordens, 45 gêneros e 37 espécies, além de oito táxons determinados só até gênero. Na base (500–400 cm) há apenas espécies marinhas, com predomínio de Paralia sulcata, registrada em todas as amostras; na porção intermediária (350–300 cm), um pântano de água doce, com espécies bentônicas (Navicula schadei, Staurosira construens) e uma planctônica marinha (Cyclotella baltica); no topo (250–50 cm) não se encontraram frústulas, o que os autores atribuem à transformação do ambiente em continental, à dissolução tafonômica ou à falta de nutrientes. Idades citadas: ~7.900–3.800 anos AP, influência marinha; ~3.800–2.500, pântano de água doce. Os níveis de 550 e 570 cm ainda não haviam sido analisados. Número de tombo e depositário não informados. É um resumo de iniciação científica, sem revisão de periódico. VERIFICAÇÃO (2026.10.09): o resumo do Salão de Iniciação Científica de 2015 (Santos &amp; Souza, mesma pesquisa) chama o testemunho de PCSC-01, com 570 cm, na Lagoa do Sombrio, município de Santa Rosa do Sul, e diz que naquela etapa as 12 amostras (espaçadas de 50 cm) ainda aguardavam identificação das espécies. A profundidade (570 cm) e a área coincidem com o testemunho PCSC-1 dos registros nº 233 e nº 264 (Cancelli et al.), mas nenhuma das fontes consultadas declara que se trata do mesmo testemunho; por isso a equivalência não é afirmada.</t>
+        </is>
+      </c>
+      <c r="L278" s="5" t="inlineStr">
+        <is>
+          <t>https://lume.ufrgs.br/bitstream/10183/154894/1/Resumo_48227.pdf (resumo do XXVIII Salão de Iniciação Científica da UFRGS, 2016)
+https://lume.ufrgs.br/bitstream/10183/137304/1/Resumo_42627.pdf (Santos &amp; Souza — resumo do XXVII Salão de Iniciação Científica da UFRGS, 2015)</t>
+        </is>
+      </c>
       <c r="M278" s="5" t="inlineStr">
         <is>
-          <t>KUHN, L.A.; SOUZA, P.A.; CANCELLI, R.R. et al. 2017. Paleoenvironmental evolution of the coastal plain of Southern Brazil: palynological data from a Holocene core in Santa Catarina State. Anais da Academia Brasileira de Ciências, 89(4), 2581–2595. DOI: 10.1590/0001-3765201720160895 | KUHN, L.A. 2017. Palinologia de depósitos quaternários da planície costeira de Santa Catarina (Garopaba, Brasil). Dissertação de Mestrado, Programa de Pós-Graduação em Geociências, Universidade Federal do Rio Grande do Sul.</t>
+          <t>SANTOS, S.M.; SOUZA, P.A. 2016. Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas. XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo].</t>
         </is>
       </c>
       <c r="N278" s="4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O278" s="4" t="inlineStr">
         <is>
-          <t>Garopaba (testemunho PCSC-3)</t>
+          <t>Lagoa do Sombrio</t>
         </is>
       </c>
       <c r="P278" s="4" t="inlineStr">
@@ -25287,16 +25291,12 @@
         </is>
       </c>
       <c r="Q278" s="4" t="n">
-        <v>-28.0276</v>
+        <v>-29.1078</v>
       </c>
       <c r="R278" s="4" t="n">
-        <v>-48.6195</v>
-      </c>
-      <c r="S278" s="4" t="inlineStr">
-        <is>
-          <t>10.1590/0001-3765201720160895</t>
-        </is>
-      </c>
+        <v>-49.6325</v>
+      </c>
+      <c r="S278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -25306,17 +25306,17 @@
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>Sedimentos holocênicos da Planície Costeira sul-catarinense (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Sedimentos lagunares holocênicos (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Diatomáceas holocênicas da Lagoa do Sombrio (Paralia sulcata, Navicula schadei, Staurosira construens, Cyclotella baltica)</t>
+          <t>Diatomáceas, pólen e esporos holocênicos de lagunas de Jaguaruna</t>
         </is>
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — diatomáceas</t>
+          <t>Microfóssil — diatomáceas e palinomorfos</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
@@ -25326,7 +25326,7 @@
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
-          <t>Lagoa do Sombrio, Planície Costeira do sul de Santa Catarina — testemunho de 570 cm (município e coordenadas não informados no resumo; ponto aproximado na sede de Sombrio)</t>
+          <t>Região de Jaguaruna, costa centro-sul de Santa Catarina — três testemunhos rasos, de até 2,5 m (localidades e coordenadas não informadas no resumo; ponto aproximado na sede de Jaguaruna)</t>
         </is>
       </c>
       <c r="G279" s="6" t="inlineStr">
@@ -25336,41 +25336,40 @@
       </c>
       <c r="H279" s="7" t="inlineStr">
         <is>
-          <t>Santos, S.M. &amp; Souza, P.A. (2016) — "Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas", XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo]</t>
+          <t>Amaral, P.G.C. (2008) — "Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada", Tese de Doutorado, Universidade de São Paulo</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
         <is>
-          <t>UFRGS (Porto Alegre)</t>
+          <t>Universidade de São Paulo</t>
         </is>
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>ca. 7.900 a 2.500 anos AP (segundo o resumo; resultados parciais)</t>
+          <t>ca. 5.000 a 2.370 anos cal AP (fase lagunar até a última desconexão com o mar)</t>
         </is>
       </c>
       <c r="K279" s="7" t="inlineStr">
         <is>
-          <t>Classificação: microfóssil silicoso (diatomáceas) de sedimento holocênico. O resumo trata de resultados parciais de um testemunho de 570 cm, do qual foram estudadas 12 amostras (50 a 570 cm): 14 ordens, 45 gêneros e 37 espécies, além de oito táxons determinados só até gênero. Na base (500–400 cm) há apenas espécies marinhas, com predomínio de Paralia sulcata, registrada em todas as amostras; na porção intermediária (350–300 cm), um pântano de água doce, com espécies bentônicas (Navicula schadei, Staurosira construens) e uma planctônica marinha (Cyclotella baltica); no topo (250–50 cm) não se encontraram frústulas, o que os autores atribuem à transformação do ambiente em continental, à dissolução tafonômica ou à falta de nutrientes. Idades citadas: ~7.900–3.800 anos AP, influência marinha; ~3.800–2.500, pântano de água doce. Os níveis de 550 e 570 cm ainda não haviam sido analisados. Número de tombo e depositário não informados. É um resumo de iniciação científica, sem revisão de periódico. VERIFICAÇÃO (2026.10.09): o resumo do Salão de Iniciação Científica de 2015 (Santos &amp; Souza, mesma pesquisa) chama o testemunho de PCSC-01, com 570 cm, na Lagoa do Sombrio, município de Santa Rosa do Sul, e diz que naquela etapa as 12 amostras (espaçadas de 50 cm) ainda aguardavam identificação das espécies. A profundidade (570 cm) e a área coincidem com o testemunho PCSC-1 dos registros nº 233 e nº 264 (Cancelli et al.), mas nenhuma das fontes consultadas declara que se trata do mesmo testemunho; por isso a equivalência não é afirmada.</t>
+          <t>Classificação: microfósseis (diatomáceas e palinomorfos) de sedimentos lagunares holocênicos. A tese combina dados sedimentológicos, de diatomáceas, de pólen e esporos e geoquímicos (C, N, δ13C, δ15N) de três testemunhos rasos (até 2,5 m). Segundo o resumo, o local era um sistema de lagunas interligadas, com conexão marinha evidenciada por diatomáceas marinhas e pelo sinal da matéria orgânica; a laguna perdeu a conexão com o mar em momentos diferentes em cada testemunho, a última por volta de 2.740–2.370 anos cal AP; as mudanças nas diatomáceas sugerem ao menos duas grandes variações de salinidade, que a autora liga a mudanças de precipitação, e o pólen mostra vegetação estável desde pelo menos 4.000 anos cal AP. A fase lagunar vem de cerca de 5.000 anos cal AP. O resumo consultado não nomeia espécies. CONTEXTO: Amaral et al. (2012, Journal of Quaternary Science 27(2):181–191, DOI 10.1002/jqs.1531) tem título que trata do sistema lagunar da região de Jaguaruna; a página do artigo não pôde ser lida (acesso limitado) e o seu conteúdo não foi usado aqui. Número de tombo e depositário não informados.</t>
         </is>
       </c>
       <c r="L279" s="7" t="inlineStr">
         <is>
-          <t>https://lume.ufrgs.br/bitstream/10183/154894/1/Resumo_48227.pdf (resumo do XXVIII Salão de Iniciação Científica da UFRGS, 2016)
-https://lume.ufrgs.br/bitstream/10183/137304/1/Resumo_42627.pdf (Santos &amp; Souza — resumo do XXVII Salão de Iniciação Científica da UFRGS, 2015)</t>
+          <t>https://teses.usp.br/teses/disponiveis/44/44141/tde-19122008-160829/en.php (resumo da tese de Amaral, 2008)</t>
         </is>
       </c>
       <c r="M279" s="7" t="inlineStr">
         <is>
-          <t>SANTOS, S.M.; SOUZA, P.A. 2016. Paleoecologia e variação da salinidade da Lagoa do Sombrio (Santa Catarina) durante o Holoceno, com base em diatomáceas. XXVIII Salão de Iniciação Científica da UFRGS, Campus do Vale [resumo].</t>
+          <t>AMARAL, P.G.C. 2008. Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada. Tese de Doutorado, Universidade de São Paulo.</t>
         </is>
       </c>
       <c r="N279" s="6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O279" s="6" t="inlineStr">
         <is>
-          <t>Lagoa do Sombrio</t>
+          <t>Região de Jaguaruna (lagunas holocênicas)</t>
         </is>
       </c>
       <c r="P279" s="6" t="inlineStr">
@@ -25379,10 +25378,10 @@
         </is>
       </c>
       <c r="Q279" s="6" t="n">
-        <v>-29.1078</v>
+        <v>-28.6148</v>
       </c>
       <c r="R279" s="6" t="n">
-        <v>-49.6325</v>
+        <v>-49.0286</v>
       </c>
       <c r="S279" s="6" t="inlineStr"/>
     </row>
@@ -25394,70 +25393,71 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Sedimentos lagunares holocênicos (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Diatomáceas, pólen e esporos holocênicos de lagunas de Jaguaruna</t>
+          <t>Bulla striata</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Microfóssil — diatomáceas e palinomorfos</t>
+          <t>Invertebrado — gastrópode</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UFSC 418</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Região de Jaguaruna, costa centro-sul de Santa Catarina — três testemunhos rasos, de até 2,5 m (localidades e coordenadas não informadas no resumo; ponto aproximado na sede de Jaguaruna)</t>
+          <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>Não informado no resumo consultado</t>
+          <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>Amaral, P.G.C. (2008) — "Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada", Tese de Doutorado, Universidade de São Paulo</t>
+          <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
         </is>
       </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>Universidade de São Paulo</t>
+          <t>UFRGS e UFSC — material depositado na UFSC</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
-          <t>ca. 5.000 a 2.370 anos cal AP (fase lagunar até a última desconexão com o mar)</t>
+          <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
         </is>
       </c>
       <c r="K280" s="5" t="inlineStr">
         <is>
-          <t>Classificação: microfósseis (diatomáceas e palinomorfos) de sedimentos lagunares holocênicos. A tese combina dados sedimentológicos, de diatomáceas, de pólen e esporos e geoquímicos (C, N, δ13C, δ15N) de três testemunhos rasos (até 2,5 m). Segundo o resumo, o local era um sistema de lagunas interligadas, com conexão marinha evidenciada por diatomáceas marinhas e pelo sinal da matéria orgânica; a laguna perdeu a conexão com o mar em momentos diferentes em cada testemunho, a última por volta de 2.740–2.370 anos cal AP; as mudanças nas diatomáceas sugerem ao menos duas grandes variações de salinidade, que a autora liga a mudanças de precipitação, e o pólen mostra vegetação estável desde pelo menos 4.000 anos cal AP. A fase lagunar vem de cerca de 5.000 anos cal AP. O resumo consultado não nomeia espécies. CONTEXTO: Amaral et al. (2012, Journal of Quaternary Science 27(2):181–191, DOI 10.1002/jqs.1531) tem título que trata do sistema lagunar da região de Jaguaruna; a página do artigo não pôde ser lida (acesso limitado) e o seu conteúdo não foi usado aqui. Número de tombo e depositário não informados.</t>
+          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 418, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L280" s="5" t="inlineStr">
         <is>
-          <t>https://teses.usp.br/teses/disponiveis/44/44141/tde-19122008-160829/en.php (resumo da tese de Amaral, 2008)</t>
+          <t>https://doi.org/10.22456/1807-9806.78267
+https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
         </is>
       </c>
       <c r="M280" s="5" t="inlineStr">
         <is>
-          <t>AMARAL, P.G.C. 2008. Evolução da sedimentação lagunar holocênica na região de Jaguaruna, Estado de Santa Catarina: uma abordagem sedimentológica-micropaleontológica integrada. Tese de Doutorado, Universidade de São Paulo.</t>
+          <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
         </is>
       </c>
       <c r="N280" s="4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O280" s="4" t="inlineStr">
         <is>
-          <t>Região de Jaguaruna (lagunas holocênicas)</t>
+          <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
         </is>
       </c>
       <c r="P280" s="4" t="inlineStr">
@@ -25466,12 +25466,16 @@
         </is>
       </c>
       <c r="Q280" s="4" t="n">
-        <v>-28.6148</v>
+        <v>-27.9021</v>
       </c>
       <c r="R280" s="4" t="n">
-        <v>-49.0286</v>
-      </c>
-      <c r="S280" s="4" t="inlineStr"/>
+        <v>-48.6681</v>
+      </c>
+      <c r="S280" s="4" t="inlineStr">
+        <is>
+          <t>10.22456/1807-9806.78267</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -25486,7 +25490,7 @@
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Bulla striata</t>
+          <t>Bostrycapulus odites</t>
         </is>
       </c>
       <c r="D281" s="6" t="inlineStr">
@@ -25496,7 +25500,7 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>UFSC 418</t>
+          <t>UFSC 421</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
@@ -25526,7 +25530,7 @@
       </c>
       <c r="K281" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 418, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 421, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L281" s="7" t="inlineStr">
@@ -25541,7 +25545,7 @@
         </is>
       </c>
       <c r="N281" s="6" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O281" s="6" t="inlineStr">
         <is>
@@ -25578,7 +25582,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Bostrycapulus odites</t>
+          <t>Cerithium atratum</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -25588,7 +25592,7 @@
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>UFSC 421</t>
+          <t>UFSC 410</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
@@ -25618,7 +25622,7 @@
       </c>
       <c r="K282" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 421, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 410, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L282" s="5" t="inlineStr">
@@ -25633,7 +25637,7 @@
         </is>
       </c>
       <c r="N282" s="4" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -25670,7 +25674,7 @@
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Cerithium atratum</t>
+          <t>Chichoreus senegalensis</t>
         </is>
       </c>
       <c r="D283" s="6" t="inlineStr">
@@ -25680,7 +25684,7 @@
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>UFSC 410</t>
+          <t>UFSC 424 (exemplar fragmentado)</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -25710,7 +25714,7 @@
       </c>
       <c r="K283" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 410, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 424 (exemplar fragmentado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L283" s="7" t="inlineStr">
@@ -25725,7 +25729,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O283" s="6" t="inlineStr">
         <is>
@@ -25762,7 +25766,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Chichoreus senegalensis</t>
+          <t>Nassarius vibex</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -25772,7 +25776,7 @@
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>UFSC 424 (exemplar fragmentado)</t>
+          <t>UFSC 416</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
@@ -25802,7 +25806,7 @@
       </c>
       <c r="K284" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 424 (exemplar fragmentado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 416, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L284" s="5" t="inlineStr">
@@ -25817,7 +25821,7 @@
         </is>
       </c>
       <c r="N284" s="4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -25854,17 +25858,17 @@
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Nassarius vibex</t>
+          <t>Trachycardium muricatum</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>Invertebrado — gastrópode</t>
+          <t>Invertebrado — bivalve</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>UFSC 416</t>
+          <t>UFSC 427</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -25894,7 +25898,7 @@
       </c>
       <c r="K285" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco gastrópode holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 416, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 427, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L285" s="7" t="inlineStr">
@@ -25909,7 +25913,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O285" s="6" t="inlineStr">
         <is>
@@ -25946,7 +25950,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Trachycardium muricatum</t>
+          <t>Corbula caribaea</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -25956,7 +25960,7 @@
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>UFSC 427</t>
+          <t>UFSC 422</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
@@ -25986,7 +25990,7 @@
       </c>
       <c r="K286" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 427, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 422, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L286" s="5" t="inlineStr">
@@ -26001,7 +26005,7 @@
         </is>
       </c>
       <c r="N286" s="4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -26038,7 +26042,7 @@
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Corbula caribaea</t>
+          <t>Iphigenia brasiliensis</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
@@ -26048,7 +26052,7 @@
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>UFSC 422</t>
+          <t>UFSC 428</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -26078,7 +26082,7 @@
       </c>
       <c r="K287" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 422, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 428, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L287" s="7" t="inlineStr">
@@ -26093,7 +26097,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O287" s="6" t="inlineStr">
         <is>
@@ -26130,7 +26134,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Iphigenia brasiliensis</t>
+          <t>Lucina pectinata</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -26140,7 +26144,7 @@
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>UFSC 428</t>
+          <t>UFSC 402 (articulado); UFSC 430 (valva esquerda)</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
@@ -26170,7 +26174,7 @@
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 428, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.260 ± 30 anos AP (calibrada 5.620–5.440); UFSC 430 é uma valva esquerda fragmentada. Número de tombo: UFSC 402 (articulado); UFSC 430 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
@@ -26185,7 +26189,7 @@
         </is>
       </c>
       <c r="N288" s="4" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -26222,7 +26226,7 @@
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>Lucina pectinata</t>
+          <t>Ostrea equestris</t>
         </is>
       </c>
       <c r="D289" s="6" t="inlineStr">
@@ -26232,7 +26236,7 @@
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>UFSC 402 (articulado); UFSC 430 (valva esquerda)</t>
+          <t>UFSC 395; UFSC 433 (valva direita)</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -26262,7 +26266,7 @@
       </c>
       <c r="K289" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.260 ± 30 anos AP (calibrada 5.620–5.440); UFSC 430 é uma valva esquerda fragmentada. Número de tombo: UFSC 402 (articulado); UFSC 430 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada, mas fora de posição de vida (distribuição aleatória quanto ao plano de acamamento), e foi datada em 5.410 ± 30 anos AP (calibrada 5.805–5.580); UFSC 433 é uma valva direita com bioerosão e fragmentação. Número de tombo: UFSC 395; UFSC 433 (valva direita), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L289" s="7" t="inlineStr">
@@ -26277,7 +26281,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O289" s="6" t="inlineStr">
         <is>
@@ -26314,7 +26318,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Ostrea equestris</t>
+          <t>Strigilla pisiformis</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -26324,7 +26328,7 @@
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>UFSC 395; UFSC 433 (valva direita)</t>
+          <t>UFSC 425</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
@@ -26354,7 +26358,7 @@
       </c>
       <c r="K290" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada, mas fora de posição de vida (distribuição aleatória quanto ao plano de acamamento), e foi datada em 5.410 ± 30 anos AP (calibrada 5.805–5.580); UFSC 433 é uma valva direita com bioerosão e fragmentação. Número de tombo: UFSC 395; UFSC 433 (valva direita), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 425, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L290" s="5" t="inlineStr">
@@ -26369,7 +26373,7 @@
         </is>
       </c>
       <c r="N290" s="4" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -26406,7 +26410,7 @@
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>Strigilla pisiformis</t>
+          <t>Tagelus plebeius</t>
         </is>
       </c>
       <c r="D291" s="6" t="inlineStr">
@@ -26416,7 +26420,7 @@
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>UFSC 425</t>
+          <t>UFSC 429 (articulado)</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
@@ -26446,7 +26450,7 @@
       </c>
       <c r="K291" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 425, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.620 ± 30 anos AP (calibrada 6.000–5.840). Número de tombo: UFSC 429 (articulado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L291" s="7" t="inlineStr">
@@ -26461,7 +26465,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O291" s="6" t="inlineStr">
         <is>
@@ -26498,7 +26502,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Tagelus plebeius</t>
+          <t>Anomalocardia brasiliana</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -26508,7 +26512,7 @@
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>UFSC 429 (articulado)</t>
+          <t>UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda)</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
@@ -26538,7 +26542,7 @@
       </c>
       <c r="K292" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie ocorre articulada e em posição de vida, e foi datada em 5.620 ± 30 anos AP (calibrada 6.000–5.840). Número de tombo: UFSC 429 (articulado), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. É a espécie mais bem representada, com cerca de 90% do volume total dos fósseis; ocorre articulada e em posição de vida, e as valvas isoladas (UFSC 431 e 432) mostram desgaste, fragmentação e bioerosão. Não foi datada individualmente. Número de tombo: UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L292" s="5" t="inlineStr">
@@ -26553,7 +26557,7 @@
         </is>
       </c>
       <c r="N292" s="4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -26590,7 +26594,7 @@
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>Anomalocardia brasiliana</t>
+          <t>Chione pubera</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
@@ -26600,7 +26604,7 @@
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda)</t>
+          <t>UFSC 423</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -26630,7 +26634,7 @@
       </c>
       <c r="K293" s="7" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. É a espécie mais bem representada, com cerca de 90% do volume total dos fósseis; ocorre articulada e em posição de vida, e as valvas isoladas (UFSC 431 e 432) mostram desgaste, fragmentação e bioerosão. Não foi datada individualmente. Número de tombo: UFSC 392 (articulado); UFSC 431 (valva direita); UFSC 432 (valva esquerda), exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 423, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
         </is>
       </c>
       <c r="L293" s="7" t="inlineStr">
@@ -26645,7 +26649,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O293" s="6" t="inlineStr">
         <is>
@@ -26677,89 +26681,85 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Sedimentos lagunares holocênicos da barreira Pinheira–Guarda–Gamboa (unidade litoestratigráfica não informada no artigo)</t>
+          <t>Sedimentos turfosos holocênicos (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Chione pubera</t>
+          <t>Palinomorfos holocênicos de turfeira dos Campos do Quiriri (47 palinomorfos)</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado — bivalve</t>
+          <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>UFSC 423</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Retrobarreira Pinheira–Guarda–Gamboa, Planície do Campo de Araçatuba, Palhoça, SC (27°54,127′S, 48°40,088′W; folha Paulo Lopes, SG-22-Z-D-V-4)</t>
+          <t>Turfeira dos Campos do Quiriri, no Planalto de São Bento do Sul, SC; testemunho de até 175 cm. O resumo não informa município, coordenadas nem altitude; ponto aproximado em São Bento do Sul, município que dá nome ao planalto</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>Coleção de Fósseis do Departamento de Geociências, Universidade Federal de Santa Catarina (UFSC)</t>
+          <t>Não informado na fonte consultada</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>Cancelli, R.R., Testa, E.H., Hadler, P., Saafeld, K., Barboza, E.G. &amp; Dillenburg, S.R. (2017) — "Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais", Pesquisas em Geociências 44(1):143–153, DOI 10.22456/1807-9806.78267</t>
+          <t>Lima, G.L., Bauermann, S.G. &amp; Oliveira, M.A.T. (2011) — "Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil", Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011)</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>UFRGS e UFSC — material depositado na UFSC</t>
+          <t>UFFS (Chapecó, SC) / ULBRA (Canoas, RS) / UFSC (Florianópolis, SC)</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>ca. 6.000 a 5.440 anos cal AP (Holoceno Médio; datações em Lucina pectinata, Ostrea equestris e Tagelus plebeius)</t>
+          <t>Holoceno — base do testemunho em ~6,2 ka AP (6.220 ± 30 anos AP, segundo o resumo)</t>
         </is>
       </c>
       <c r="K294" s="5" t="inlineStr">
         <is>
-          <t>Classificação: molusco bivalve holocênico de sedimentos lagunares (nome conforme o artigo, sem autoria). Cancelli et al. (2017) registraram 14 espécies (5 gastrópodes e 9 bivalves) em sedimentos lagunares do retrobarreira Pinheira–Guarda–Gamboa, na Planície do Campo de Araçatuba (folha Paulo Lopes); quatro bivalves ocorrem articulados (Ostrea equestris, Anomalocardia brasiliana, Lucina pectinata e Tagelus plebeius), os três últimos em posição de vida. Datações por 14C (AMS) em três espécies situam o conjunto no Holoceno Médio: Lucina pectinata 5.260 ± 30 anos AP (calibrada 5.620–5.440), Ostrea equestris 5.410 ± 30 (5.805–5.580) e Tagelus plebeius 5.620 ± 30 (6.000–5.840). O topo do afloramento está a 2 m acima do nível relativo atual do mar, e a associação indica um ambiente lagunar-estuarino posteriormente colmatado em resposta ao rebaixamento do nível do mar. Esta espécie não foi datada individualmente; o artigo trata a associação como do Holoceno Médio com base nas três espécies datadas. Número de tombo: UFSC 423, exemplar(es) figurado(s) na Figura 3 do artigo.</t>
+          <t>Classificação: microfósseis (pólen e esporos) de turfeira — registro paleoambiental holocênico. Segundo o resumo, foram identificados 47 palinomorfos, agrupados por afinidade ecológica: elementos campestres (Poaceae, Asteraceae, Cyperaceae, Apiaceae, Xyris), elementos florestais (Myrsine, Myrtaceae, Alchornea, Weinmannia, Ilex, Mimosa scabrella e, em um único grão, Araucaria angustifolia), pteridófitas (Blechnum, Cyatheaceae, Marattia, Dicksonia sellowiana) e Sphagnum. Uma amostra da base do testemunho foi enviada à Universidade da Geórgia (EUA) para datação por radiocarbono. NOTA DE FONTE (2026.10.09): o PDF do resumo não traz o ano; 2011 é o ano do XIII Congresso da ABEQUA e III Encontro do Quaternário Sul-Americano (Armação dos Búzios, RJ, 8–13/10/2011, segundo o calendário da PAGES). Município e coordenadas da turfeira não constam: o resumo diz apenas «Planalto de São Bento do Sul». Tombo e depositário não informados.</t>
         </is>
       </c>
       <c r="L294" s="5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.22456/1807-9806.78267
-https://seer.ufrgs.br/index.php/PesquisasemGeociencias/article/view/78267 (Cancelli et al., 2017)</t>
+          <t>https://www.abequa.org.br/anais/ABEQUA_GISELE_LIMA.pdf (resumo — Lima, Bauermann &amp; Oliveira)
+https://pastglobalchanges.org/calendar/127-pages/1056%E2%88%92xiii-congress-of-abequa-and-iii-south-america-quaternary-meeting (data e local do XIII Congresso da ABEQUA)</t>
         </is>
       </c>
       <c r="M294" s="5" t="inlineStr">
         <is>
-          <t>CANCELLI, R.R.; TESTA, E.H.; HADLER, P. et al. 2017. Moluscos holocênicos em sedimentos lagunares associados à barreira arenosa da Pinheira-Guarda-Gamboa, Santa Catarina: implicações paleoambientais. Pesquisas em Geociências, 44(1), 143–153. DOI: 10.22456/1807-9806.78267</t>
+          <t>LIMA, G.L.; BAUERMANN, S.G.; OLIVEIRA, M.A.T. 2011. Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil. Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011).</t>
         </is>
       </c>
       <c r="N294" s="4" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>Barreira Pinheira–Guarda–Gamboa (Palhoça)</t>
+          <t>Campos do Quiriri (Planalto de São Bento do Sul)</t>
         </is>
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
+          <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n">
-        <v>-27.9021</v>
+        <v>-26.2503</v>
       </c>
       <c r="R294" s="4" t="n">
-        <v>-48.6681</v>
-      </c>
-      <c r="S294" s="4" t="inlineStr">
-        <is>
-          <t>10.22456/1807-9806.78267</t>
-        </is>
-      </c>
+        <v>-49.3792</v>
+      </c>
+      <c r="S294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
@@ -26769,17 +26769,17 @@
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>Sedimentos turfosos holocênicos (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Depósitos paludais/lagunares holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Palinomorfos holocênicos de turfeira dos Campos do Quiriri (47 palinomorfos)</t>
+          <t>Microfauna holocênica do testemunho PCSC-1 (15 táxons: 5 bivalves, 8 gastrópodes, 1 foraminífero e 1 ostracode)</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — palinomorfos (pólen e esporos)</t>
+          <t>Microfóssil — microfauna (moluscos, foraminífero e ostracode)</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
@@ -26789,63 +26789,62 @@
       </c>
       <c r="F295" s="7" t="inlineStr">
         <is>
-          <t>Turfeira dos Campos do Quiriri, no Planalto de São Bento do Sul, SC; testemunho de até 175 cm. O resumo não informa município, coordenadas nem altitude; ponto aproximado em São Bento do Sul, município que dá nome ao planalto</t>
+          <t>Testemunho PCSC-1, em mata paludial próxima à Lagoa do Sombrio, município de Santa Rosa do Sul, SC (acesso pela BR-101 e estradas secundárias); coordenadas do próprio resumo: 29°10'42"S, 49°44'58"W; Russian Peat Borer, profundidade de 570 cm</t>
         </is>
       </c>
       <c r="G295" s="6" t="inlineStr">
         <is>
-          <t>Não informado na fonte consultada</t>
+          <t>Não informado no resumo (triagem da microfauna no CECO/UFRGS)</t>
         </is>
       </c>
       <c r="H295" s="7" t="inlineStr">
         <is>
-          <t>Lima, G.L., Bauermann, S.G. &amp; Oliveira, M.A.T. (2011) — "Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil", Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011)</t>
+          <t>Cancelli, R.R., Souza, P.A. &amp; Dehnhardt, B.A. (2011) — "Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos", Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo)</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
         <is>
-          <t>UFFS (Chapecó, SC) / ULBRA (Canoas, RS) / UFSC (Florianópolis, SC)</t>
+          <t>Universidade Federal do Rio Grande do Sul (UFRGS) — afiliação dos autores</t>
         </is>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>Holoceno — base do testemunho em ~6,2 ka AP (6.220 ± 30 anos AP, segundo o resumo)</t>
+          <t>base do testemunho ca. 7.908 ± 33 anos cal AP (única datação AMS, nível basal; 0,0079 Ma); os níveis com microfauna ficam entre 570 e 320 cm, sem datação própria</t>
         </is>
       </c>
       <c r="K295" s="7" t="inlineStr">
         <is>
-          <t>Classificação: microfósseis (pólen e esporos) de turfeira — registro paleoambiental holocênico. Segundo o resumo, foram identificados 47 palinomorfos, agrupados por afinidade ecológica: elementos campestres (Poaceae, Asteraceae, Cyperaceae, Apiaceae, Xyris), elementos florestais (Myrsine, Myrtaceae, Alchornea, Weinmannia, Ilex, Mimosa scabrella e, em um único grão, Araucaria angustifolia), pteridófitas (Blechnum, Cyatheaceae, Marattia, Dicksonia sellowiana) e Sphagnum. Uma amostra da base do testemunho foi enviada à Universidade da Geórgia (EUA) para datação por radiocarbono. NOTA DE FONTE (2026.10.09): o PDF do resumo não traz o ano; 2011 é o ano do XIII Congresso da ABEQUA e III Encontro do Quaternário Sul-Americano (Armação dos Búzios, RJ, 8–13/10/2011, segundo o calendário da PAGES). Município e coordenadas da turfeira não constam: o resumo diz apenas «Planalto de São Bento do Sul». Tombo e depositário não informados.</t>
+          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): a microfauna foi triada em níveis selecionados do testemunho e reúne 15 táxons — bivalves: Anomalocardia brasiliana, Brachiodontes sp., Tellina versicolor, Pitar rostratus e Ostrea puelchana; gastrópodes: Parodizia uruguayensis, Heleobia australis australis, Bittium varium, Odostomia seminuda, Crepidula aculeata, Bulla striata, Solariorbis shimeri e Solariorbis shumoi; foraminífero: Quinqueloculina lamarckiana; ostracode: Cyprideis sp. O resumo não atribui cada espécie a uma profundidade: informa apenas que a base (570–560 cm) é um concheiro com fauna interpretada como autóctone, bem preservada e adaptada a salinidade elevada, e que pequenos fragmentos de conchas continuam até 320 cm, com pouco indício de retrabalhamento. INTERPRETAÇÃO (dos autores): fase I (570–560 cm) com influência marinha ou fortemente salina; fase II (560–320 cm) com ingressão marinha que ultrapassou os limites atuais, com pico em torno de 450 cm (palinoforaminíferos e Micrhystridium), ligada ao recuo da margem oeste da Lagoa do Sombrio; fase III (320–0 cm) com aumento de árvores da Mata Atlântica, briófitas, pteridófitas e algas de água doce, ambiente de influência lagunar substituído por influência de água doce. LOCALIZAÇÃO: o testemunho PCSC-1 é de Santa Rosa do Sul; o ponto do mapa usa as coordenadas do resumo. NOTA DE FONTE: só o resumo foi consultado; os autores afirmam que obterão novas datações ao longo do perfil (só a base foi datada), por isso a idade dos níveis com microfauna não é conhecida. Os nomes de espécie estão como no resumo; sinonímias e a grafia atual não foram verificadas. O resumo não informa depositário nem numeração de tombo. RELAÇÃO COM OUTROS REGISTROS (2026.10.09): os dados palinológicos do mesmo testemunho (112 palinomorfos no total, dos quais 54 não-pólen) correspondem ao registro nº 233. LIGAÇÃO COM O REGISTRO Nº 238 (2026.10.09): o testemunho PCSC-01 (570 cm, Lagoa do Sombrio, Santa Rosa do Sul) das diatomáceas de Santos &amp; Souza tem a mesma profundidade e a mesma área, mas as fontes não declaram que seja o mesmo testemunho do PCSC-1 aqui descrito.</t>
         </is>
       </c>
       <c r="L295" s="7" t="inlineStr">
         <is>
-          <t>https://www.abequa.org.br/anais/ABEQUA_GISELE_LIMA.pdf (resumo — Lima, Bauermann &amp; Oliveira)
-https://pastglobalchanges.org/calendar/127-pages/1056%E2%88%92xiii-congress-of-abequa-and-iii-south-america-quaternary-meeting (data e local do XIII Congresso da ABEQUA)</t>
+          <t>https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
         </is>
       </c>
       <c r="M295" s="7" t="inlineStr">
         <is>
-          <t>LIMA, G.L.; BAUERMANN, S.G.; OLIVEIRA, M.A.T. 2011. Análise palinológica de sedimentos turfosos holocênicos: Campos do Quiriri, Estado de Santa Catarina, sul do Brasil. Anais do XIII Congresso da ABEQUA (Armação dos Búzios, RJ, 8–13 out. 2011).</t>
+          <t>CANCELLI, R.R.; SOUZA, P.A.; DEHNHARDT, B.A. 2011. Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos. Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo).</t>
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="O295" s="6" t="inlineStr">
         <is>
-          <t>Campos do Quiriri (Planalto de São Bento do Sul)</t>
+          <t>Testemunho PCSC-1 (Santa Rosa do Sul)</t>
         </is>
       </c>
       <c r="P295" s="6" t="inlineStr">
         <is>
-          <t>Depósitos Quaternários de turfeira (planalto e serras)</t>
+          <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
       <c r="Q295" s="6" t="n">
-        <v>-26.2503</v>
+        <v>-29.1783</v>
       </c>
       <c r="R295" s="6" t="n">
-        <v>-49.3792</v>
+        <v>-49.7494</v>
       </c>
       <c r="S295" s="6" t="inlineStr"/>
     </row>
@@ -26857,17 +26856,17 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Depósitos paludais/lagunares holocênicos da Planície Costeira (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Depósitos holocênicos de planície costeira (unidade litoestratigráfica não informada no resumo)</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Microfauna holocênica do testemunho PCSC-1 (15 táxons: 5 bivalves, 8 gastrópodes, 1 foraminífero e 1 ostracode)</t>
+          <t>Foraminíferos bentônicos holocênicos — Miliolida (testemunho de Volta Velha, Itapoá)</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Microfóssil — microfauna (moluscos, foraminífero e ostracode)</t>
+          <t>Microfóssil — foraminífero bentônico</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
@@ -26877,50 +26876,50 @@
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>Testemunho PCSC-1, em mata paludial próxima à Lagoa do Sombrio, município de Santa Rosa do Sul, SC (acesso pela BR-101 e estradas secundárias); coordenadas do próprio resumo: 29°10'42"S, 49°44'58"W; Russian Peat Borer, profundidade de 570 cm</t>
+          <t>Região de Volta Velha, Itapoá, SC — uma das três sondagens manuais feitas ali; coordenadas do resumo: 26°4'58,5"S, 48°37'54,3"W (a amostra com miliolídeos vem do estrato mais profundo do testemunho de Volta Velha)</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>Não informado no resumo (triagem da microfauna no CECO/UFRGS)</t>
+          <t>Não informado no resumo</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>Cancelli, R.R., Souza, P.A. &amp; Dehnhardt, B.A. (2011) — "Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos", Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo)</t>
+          <t>Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>Universidade Federal do Rio Grande do Sul (UFRGS) — afiliação dos autores</t>
+          <t>Universidade Federal do Paraná (LECOST) e Universidade do Algarve (CIMA, Portugal) — afiliações dos autores</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>base do testemunho ca. 7.908 ± 33 anos cal AP (única datação AMS, nível basal; 0,0079 Ma); os níveis com microfauna ficam entre 570 e 320 cm, sem datação própria</t>
+          <t>Holoceno (os autores tratam os depósitos como holocênicos; idade do testemunho de Volta Velha não informada no resumo)</t>
         </is>
       </c>
       <c r="K296" s="5" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): a microfauna foi triada em níveis selecionados do testemunho e reúne 15 táxons — bivalves: Anomalocardia brasiliana, Brachiodontes sp., Tellina versicolor, Pitar rostratus e Ostrea puelchana; gastrópodes: Parodizia uruguayensis, Heleobia australis australis, Bittium varium, Odostomia seminuda, Crepidula aculeata, Bulla striata, Solariorbis shimeri e Solariorbis shumoi; foraminífero: Quinqueloculina lamarckiana; ostracode: Cyprideis sp. O resumo não atribui cada espécie a uma profundidade: informa apenas que a base (570–560 cm) é um concheiro com fauna interpretada como autóctone, bem preservada e adaptada a salinidade elevada, e que pequenos fragmentos de conchas continuam até 320 cm, com pouco indício de retrabalhamento. INTERPRETAÇÃO (dos autores): fase I (570–560 cm) com influência marinha ou fortemente salina; fase II (560–320 cm) com ingressão marinha que ultrapassou os limites atuais, com pico em torno de 450 cm (palinoforaminíferos e Micrhystridium), ligada ao recuo da margem oeste da Lagoa do Sombrio; fase III (320–0 cm) com aumento de árvores da Mata Atlântica, briófitas, pteridófitas e algas de água doce, ambiente de influência lagunar substituído por influência de água doce. LOCALIZAÇÃO: o testemunho PCSC-1 é de Santa Rosa do Sul; o ponto do mapa usa as coordenadas do resumo. NOTA DE FONTE: só o resumo foi consultado; os autores afirmam que obterão novas datações ao longo do perfil (só a base foi datada), por isso a idade dos níveis com microfauna não é conhecida. Os nomes de espécie estão como no resumo; sinonímias e a grafia atual não foram verificadas. O resumo não informa depositário nem numeração de tombo. RELAÇÃO COM OUTROS REGISTROS (2026.10.09): os dados palinológicos do mesmo testemunho (112 palinomorfos no total, dos quais 54 não-pólen) correspondem ao registro nº 233. LIGAÇÃO COM O REGISTRO Nº 238 (2026.10.09): o testemunho PCSC-01 (570 cm, Lagoa do Sombrio, Santa Rosa do Sul) das diatomáceas de Santos &amp; Souza tem a mesma profundidade e a mesma área, mas as fontes não declaram que seja o mesmo testemunho do PCSC-1 aqui descrito.</t>
+          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): foram feitas 35 sondagens manuais em planícies costeiras do norte de Santa Catarina e do sul do Paraná — seis em SC (três em Volta Velha, Itapoá, e três na parte interna da Baía de São Francisco, nas planícies de Joinville e de Garuva) e uma no Paraná (Cabaraquara, Guaratuba) — para analisar foraminíferos. No testemunho de Volta Velha só uma amostra, a do estrato mais profundo, trouxe fauna composta predominantemente por miliolídeos; os autores a interpretam como indício de ambiente mais oxigenado, com maior influência marinha e salinidade mais alta, provavelmente uma região mais externa da baía. ESCOPO: o resumo não traz resultados separados nem identificação de espécies para as sondagens de Itapoá (demais amostras) e da Baía de São Francisco (Joinville/Garuva); os gêneros Ammonia e Elphidium que o resumo menciona são do testemunho de Guaratuba, no Paraná, e por isso não fazem parte deste registro. NOTA DE FONTE: só o resumo foi consultado e o texto declara resultados preliminares, com espécies ainda não identificadas. O documento não informa o evento nem o ano (agradece ao projeto CNPq 471039/2013-6), por isso a data está como s.d.; profundidade e datação 14C do testemunho de Volta Velha também não constam.</t>
         </is>
       </c>
       <c r="L296" s="5" t="inlineStr">
         <is>
-          <t>https://www.abequa.org.br/anais/resumo_ABEQUA212_.pdf (Cancelli, Souza &amp; Dehnhardt — resumo do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano)</t>
+          <t>https://www.abequa.org.br/anais/247_resumo.pdf (Silva, Angulo, Souza &amp; Boski — resumo; evento e ano não constam do documento)</t>
         </is>
       </c>
       <c r="M296" s="5" t="inlineStr">
         <is>
-          <t>CANCELLI, R.R.; SOUZA, P.A.; DEHNHARDT, B.A. 2011. Evolução holocênica da planície costeira sul catarinense (Santa Rosa do Sul, Brasil), através de dados palinológicos e microfaunísticos. Anais do XIII Congresso da ABEQUA e III Encontro do Quaternário Sulamericano (resumo).</t>
+          <t>[referência sem formato bibliográfico, transcrita do descritor: Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)]</t>
         </is>
       </c>
       <c r="N296" s="4" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>Testemunho PCSC-1 (Santa Rosa do Sul)</t>
+          <t>Volta Velha (Itapoá) — testemunho da planície costeira</t>
         </is>
       </c>
       <c r="P296" s="4" t="inlineStr">
@@ -26929,10 +26928,10 @@
         </is>
       </c>
       <c r="Q296" s="4" t="n">
-        <v>-29.1783</v>
+        <v>-26.0829</v>
       </c>
       <c r="R296" s="4" t="n">
-        <v>-49.7494</v>
+        <v>-48.6318</v>
       </c>
       <c r="S296" s="4" t="inlineStr"/>
     </row>
@@ -26944,17 +26943,17 @@
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>Depósitos holocênicos de planície costeira (unidade litoestratigráfica não informada no resumo)</t>
+          <t>Depósito conchífero natural holocênico (lagunar/paleolagunar) da planície costeira; unidade litoestratigráfica formal não nomeada nas fontes consultadas</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Foraminíferos bentônicos holocênicos — Miliolida (testemunho de Volta Velha, Itapoá)</t>
+          <t>Moluscos subfósseis do concheiro de Nova Brasília (12 espécies; dominantes: Heleobia australis, Cerithiopsis greeni, Crepidula plana, Nassarius vibex, Tellina lineata, Tagelus plebeius)</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>Microfóssil — foraminífero bentônico</t>
+          <t>Invertebrado — moluscos (assembleia de bivalves e gastrópodes)</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
@@ -26964,211 +26963,124 @@
       </c>
       <c r="F297" s="7" t="inlineStr">
         <is>
-          <t>Região de Volta Velha, Itapoá, SC — uma das três sondagens manuais feitas ali; coordenadas do resumo: 26°4'58,5"S, 48°37'54,3"W (a amostra com miliolídeos vem do estrato mais profundo do testemunho de Volta Velha)</t>
+          <t>Concheiro natural do rio D'Una, localidade de Nova Brasília, Imbituba, SC, na planície de inundação do rio D'Una, extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio; frentes de lavra de calcário de conchas (cerca de 4.000 m de comprimento, 420 m de largura e 0,60–6 m de espessura). Coordenadas não informadas nas fontes; ponto do mapa = centro do município de Imbituba (referência regional)</t>
         </is>
       </c>
       <c r="G297" s="6" t="inlineStr">
         <is>
-          <t>Não informado no resumo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="H297" s="7" t="inlineStr">
         <is>
-          <t>Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)</t>
+          <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011; Caruso Júnior, F. (1992) — "Geologia dos depósitos de conchas calcárias no estado de Santa Catarina", Geosul 7(14):101–136</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
         <is>
-          <t>Universidade Federal do Paraná (LECOST) e Universidade do Algarve (CIMA, Portugal) — afiliações dos autores</t>
+          <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores (2000)</t>
         </is>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Holoceno (os autores tratam os depósitos como holocênicos; idade do testemunho de Volta Velha não informada no resumo)</t>
+          <t>4.490 ± 200 anos AP (conchas; datação de Martin &amp; Suguio, 1986, citada por Caruso et al., 2000; 0,0045 Ma) — os próprios autores ressalvam que as conchas são alóctones e que a idade pode não ser a deposicional</t>
         </is>
       </c>
       <c r="K297" s="7" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇÃO E CONTEÚDO (segundo o resumo): foram feitas 35 sondagens manuais em planícies costeiras do norte de Santa Catarina e do sul do Paraná — seis em SC (três em Volta Velha, Itapoá, e três na parte interna da Baía de São Francisco, nas planícies de Joinville e de Garuva) e uma no Paraná (Cabaraquara, Guaratuba) — para analisar foraminíferos. No testemunho de Volta Velha só uma amostra, a do estrato mais profundo, trouxe fauna composta predominantemente por miliolídeos; os autores a interpretam como indício de ambiente mais oxigenado, com maior influência marinha e salinidade mais alta, provavelmente uma região mais externa da baía. ESCOPO: o resumo não traz resultados separados nem identificação de espécies para as sondagens de Itapoá (demais amostras) e da Baía de São Francisco (Joinville/Garuva); os gêneros Ammonia e Elphidium que o resumo menciona são do testemunho de Guaratuba, no Paraná, e por isso não fazem parte deste registro. NOTA DE FONTE: só o resumo foi consultado e o texto declara resultados preliminares, com espécies ainda não identificadas. O documento não informa o evento nem o ano (agradece ao projeto CNPq 471039/2013-6), por isso a data está como s.d.; profundidade e datação 14C do testemunho de Volta Velha também não constam.</t>
+          <t>CITAÇÃO EM REVISÃO — a lista de espécies é compilada por Caruso Júnior et al. (2000) a partir de levantamentos malacológicos anteriores (que o texto atribui a Forti-Esteves, 1986; Mendes, 1993; Pitoni, 1993), e esses levantamentos não foram examinados por este banco. CLASSIFICAÇÃO E CONTEÚDO (segundo o artigo): as espécies mais abundantes são Heleobia australis (d'Orbigny, 1835), Cerithiopsis greeni (C.B. Adams, 1839), Crepidula plana, Nassarius vibex, Tellina (Eurytellina) lineata e Tagelus plebeius; as duas primeiras são tidas como estuarinas e as demais como marinhas litorâneas. Também são citadas Neritina virginea, Cerithium stratum, Bulla striata, Ostrea equestris, Codakia costata e Anomalocardia brasiliana. O artigo grafa «Cerithiopis greeni» e «Nassarius viabex»; a grafia foi corrigida aqui. SEDIMENTOLOGIA E TAFONOMIA: o depósito tem unidades tabulares com estratificação cruzada de grande porte, alternando camadas arenosas e conchíferas, com gradação inversa; os autores propõem transporte por barras de corrente e um bloqueio do transporte sul–norte por um terraço pleistocênico, o que teria depositado o cascalho de conchas. LOCALIZAÇÃO: o artigo de 2000 localiza o depósito no extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio, na região de Nova Brasília; Caruso Júnior (1992) o situa na localidade de Nova Brasília, município de Imbituba, na planície de inundação do rio D'Una. VERIFICAÇÃO (2026.10.09): o artigo de 2000 não chama as conchas de «fósseis»; elas vêm de depósitos holocênicos e são tratadas aqui como subfósseis, no mesmo critério dos demais moluscos holocênicos do banco. A lista de ~30 táxons do anexo de Caruso Júnior (1992), identificada por I.P.F. Esteves em 1986, não traz o depósito de origem no trecho legível e a bibliografia da obra só cita um trabalho de Esteves sobre o concheiro de Jaboticabeira; por isso ela não foi atribuída a Nova Brasília nem aproveitada aqui.</t>
         </is>
       </c>
       <c r="L297" s="7" t="inlineStr">
-        <is>
-          <t>https://www.abequa.org.br/anais/247_resumo.pdf (Silva, Angulo, Souza &amp; Boski — resumo; evento e ano não constam do documento)</t>
-        </is>
-      </c>
-      <c r="M297" s="7" t="inlineStr">
-        <is>
-          <t>[referência sem formato bibliográfico, transcrita do descritor: Silva, C.E., Angulo, R.J., Souza, M.C. &amp; Boski, T. (s.d.) — "Caracterização micropaleontológica de testemunhos rasos das planícies costeiras holocênicas do Paraná e norte de Santa Catarina — resultados preliminares", Anais da ABEQUA (resumo nº 247; evento e ano não constam do documento)]</t>
-        </is>
-      </c>
-      <c r="N297" s="6" t="n">
-        <v>265</v>
-      </c>
-      <c r="O297" s="6" t="inlineStr">
-        <is>
-          <t>Volta Velha (Itapoá) — testemunho da planície costeira</t>
-        </is>
-      </c>
-      <c r="P297" s="6" t="inlineStr">
-        <is>
-          <t>Planície Costeira — Depósitos Quaternários</t>
-        </is>
-      </c>
-      <c r="Q297" s="6" t="n">
-        <v>-26.0829</v>
-      </c>
-      <c r="R297" s="6" t="n">
-        <v>-48.6318</v>
-      </c>
-      <c r="S297" s="6" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="4" t="inlineStr">
-        <is>
-          <t>Holoceno</t>
-        </is>
-      </c>
-      <c r="B298" s="4" t="inlineStr">
-        <is>
-          <t>Depósito conchífero natural holocênico (lagunar/paleolagunar) da planície costeira; unidade litoestratigráfica formal não nomeada nas fontes consultadas</t>
-        </is>
-      </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>Moluscos subfósseis do concheiro de Nova Brasília (12 espécies; dominantes: Heleobia australis, Cerithiopsis greeni, Crepidula plana, Nassarius vibex, Tellina lineata, Tagelus plebeius)</t>
-        </is>
-      </c>
-      <c r="D298" s="4" t="inlineStr">
-        <is>
-          <t>Invertebrado — moluscos (assembleia de bivalves e gastrópodes)</t>
-        </is>
-      </c>
-      <c r="E298" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>Concheiro natural do rio D'Una, localidade de Nova Brasília, Imbituba, SC, na planície de inundação do rio D'Una, extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio; frentes de lavra de calcário de conchas (cerca de 4.000 m de comprimento, 420 m de largura e 0,60–6 m de espessura). Coordenadas não informadas nas fontes; ponto do mapa = centro do município de Imbituba (referência regional)</t>
-        </is>
-      </c>
-      <c r="G298" s="4" t="inlineStr">
-        <is>
-          <t>Não informado</t>
-        </is>
-      </c>
-      <c r="H298" s="5" t="inlineStr">
-        <is>
-          <t>Caruso Júnior, F., Suguio, K. &amp; Nakamura, T. (2000) — "The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil)", Anais da Academia Brasileira de Ciências 72(2):257–270, DOI 10.1590/S0001-37652000000200011; Caruso Júnior, F. (1992) — "Geologia dos depósitos de conchas calcárias no estado de Santa Catarina", Geosul 7(14):101–136</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr">
-        <is>
-          <t>Universidade do Vale do Itajaí (CTTMAR), Universidade de São Paulo e Universidade de Nagoya — afiliações dos autores (2000)</t>
-        </is>
-      </c>
-      <c r="J298" s="4" t="inlineStr">
-        <is>
-          <t>4.490 ± 200 anos AP (conchas; datação de Martin &amp; Suguio, 1986, citada por Caruso et al., 2000; 0,0045 Ma) — os próprios autores ressalvam que as conchas são alóctones e que a idade pode não ser a deposicional</t>
-        </is>
-      </c>
-      <c r="K298" s="5" t="inlineStr">
-        <is>
-          <t>CITAÇÃO EM REVISÃO — a lista de espécies é compilada por Caruso Júnior et al. (2000) a partir de levantamentos malacológicos anteriores (que o texto atribui a Forti-Esteves, 1986; Mendes, 1993; Pitoni, 1993), e esses levantamentos não foram examinados por este banco. CLASSIFICAÇÃO E CONTEÚDO (segundo o artigo): as espécies mais abundantes são Heleobia australis (d'Orbigny, 1835), Cerithiopsis greeni (C.B. Adams, 1839), Crepidula plana, Nassarius vibex, Tellina (Eurytellina) lineata e Tagelus plebeius; as duas primeiras são tidas como estuarinas e as demais como marinhas litorâneas. Também são citadas Neritina virginea, Cerithium stratum, Bulla striata, Ostrea equestris, Codakia costata e Anomalocardia brasiliana. O artigo grafa «Cerithiopis greeni» e «Nassarius viabex»; a grafia foi corrigida aqui. SEDIMENTOLOGIA E TAFONOMIA: o depósito tem unidades tabulares com estratificação cruzada de grande porte, alternando camadas arenosas e conchíferas, com gradação inversa; os autores propõem transporte por barras de corrente e um bloqueio do transporte sul–norte por um terraço pleistocênico, o que teria depositado o cascalho de conchas. LOCALIZAÇÃO: o artigo de 2000 localiza o depósito no extremo norte do complexo lagunar Mirim–Imaruí–Santo Antônio, na região de Nova Brasília; Caruso Júnior (1992) o situa na localidade de Nova Brasília, município de Imbituba, na planície de inundação do rio D'Una. VERIFICAÇÃO (2026.10.09): o artigo de 2000 não chama as conchas de «fósseis»; elas vêm de depósitos holocênicos e são tratadas aqui como subfósseis, no mesmo critério dos demais moluscos holocênicos do banco. A lista de ~30 táxons do anexo de Caruso Júnior (1992), identificada por I.P.F. Esteves em 1986, não traz o depósito de origem no trecho legível e a bibliografia da obra só cita um trabalho de Esteves sobre o concheiro de Jaboticabeira; por isso ela não foi atribuída a Nova Brasília nem aproveitada aqui.</t>
-        </is>
-      </c>
-      <c r="L298" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1590/S0001-37652000000200011
 https://www.scielo.br/j/aabc/a/PV3LvmfpkshVK6wWx8WgWSc/?lang=en (Caruso Júnior, Suguio &amp; Nakamura, 2000 — texto integral)
 https://periodicos.ufsc.br/index.php/geosul/article/download/12805/11988/39566 (Caruso Júnior, 1992 — texto integral, Geosul)</t>
         </is>
       </c>
-      <c r="M298" s="5" t="inlineStr">
+      <c r="M297" s="7" t="inlineStr">
         <is>
           <t>CARUSO JÚNIOR, F.; SUGUIO, K.; NAKAMURA, T. 2000. The Quaternary geological history of the Santa Catarina Southeastern Region (Brazil). Anais da Academia Brasileira de Ciências, 72(2), 257–270. DOI: 10.1590/S0001-37652000000200011 | CARUSO JÚNIOR, F. 1992. Geologia dos depósitos de conchas calcárias no estado de Santa Catarina. Geosul, 7(14), 101–136.</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n">
+      <c r="N297" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="O298" s="4" t="inlineStr">
+      <c r="O297" s="6" t="inlineStr">
         <is>
           <t>Concheiro natural de Nova Brasília (Imbituba)</t>
         </is>
       </c>
-      <c r="P298" s="4" t="inlineStr">
+      <c r="P297" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q298" s="4" t="n">
+      <c r="Q297" s="6" t="n">
         <v>-28.193</v>
       </c>
-      <c r="R298" s="4" t="n">
+      <c r="R297" s="6" t="n">
         <v>-48.7019</v>
       </c>
-      <c r="S298" s="4" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="inlineStr">
+      <c r="S297" s="6" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B299" s="6" t="inlineStr">
+      <c r="B298" s="4" t="inlineStr">
         <is>
           <t>Depósitos holocênicos de turfa, lama detrítica e areia fina da planície costeira (unidade litoestratigráfica não nomeada no artigo)</t>
         </is>
       </c>
-      <c r="C299" s="7" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
         <is>
           <t>Pólen e esporos do perfil de Poço Grande (planície costeira: dunas, plantas aquáticas e floresta pluvial atlântica)</t>
         </is>
       </c>
-      <c r="D299" s="6" t="inlineStr">
+      <c r="D298" s="4" t="inlineStr">
         <is>
           <t>Microfóssil — palinomorfos (pólen e esporos)</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E298" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F299" s="7" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
         <is>
           <t>Planície costeira norte de SC, a 800 m a noroeste do fim da estrada para o Rancho Nutrimental, perto da vila de Poço Grande (15 km ao sul de Joinville e a cerca de 20 km do Atlântico, segundo o artigo); 26°25′ S, 48°52′ O; 10–16 m de altitude. O artigo não declara o município: pelas coordenadas, o ponto cai na malha deste site em Guaramirim, a ~1 km da divisa com Joinville (por isso «região»)</t>
         </is>
       </c>
-      <c r="G299" s="6" t="inlineStr">
+      <c r="G298" s="4" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H299" s="7" t="inlineStr">
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>Behling, H. (1995) — "Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil)", Vegetation History and Archaeobotany 4(3):127–152, DOI 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="I299" s="6" t="inlineStr">
+      <c r="I298" s="4" t="inlineStr">
         <is>
           <t>Institut für Palynologie und Quartärwissenschaften, Universität Göttingen (Alemanha)</t>
         </is>
       </c>
-      <c r="J299" s="6" t="inlineStr">
+      <c r="J298" s="4" t="inlineStr">
         <is>
           <t>Holoceno superior: base do perfil extrapolada em ~4.840 anos 14C AP, até o presente; datações de 4.680 ± 150 (507–514 cm), 4.265 ± 190 (327–332 cm), 4.230 ± 185 (214–219 cm) e 3.525 ± 175 (127–132 cm); idades não calibradas; provável hiato</t>
         </is>
       </c>
-      <c r="K299" s="7" t="inlineStr">
+      <c r="K298" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Classificação: microfósseis (pólen e esporos) de perfil sedimentar da planície costeira — registro paleoambiental do Holoceno superior. Behling (1995) estuda três turfeiras de altitude — Morro da Igreja, Serra do Rio Rastro e Serra da Boa Vista (registros nº 255, 256 e 270) — e um perfil da planície costeira, Poço Grande (registro nº 271), todos em SC. BASE (texto integral lido em 2026.10.09): perfil de 587 cm (turfa «carr» com madeira, lama detrítica e areia fina; começa 5 cm abaixo da superfície), amostrado em 12/10/1989 perto do Rancho Nutrimental (o autor não pôde terminar a coleta por uma mudança de proprietário do rancho); contagem mínima de 508 grãos por amostra (média de 1.383). Quatro datações por 14C (Hv 17559–17562): 3.525 ± 175 anos AP (127–132 cm), 4.230 ± 185 (214–219), 4.265 ± 190 (327–332) e 4.680 ± 150 (507–514); idades não calibradas. RESULTADO (zonas A–E, segundo o autor e o resumo): A (~4.840–4.590 anos AP) — alternância repetida de duas comunidades de dunas perto do local (Myrtaceae, de dunas estáveis; Palmae, Ilex, Weinmannia e Schinus, de dunas pouco móveis) com variações do nível da água; B (~4.590–4.265) — depósitos de água doce, com sucessão de plantas aquáticas (Cabomba, Potamogeton, Myriophyllum, Echinodorus) e pólen alto de Alchornea, Urticales e Rapanea; C (~4.265–4.230) — curta, com Rapanea chegando a 15%; D (~4.230–3.525) — Alchornea chega a 24% e indica floresta densa perto do local; E (0–133 cm, início datado em 3.525 anos AP) — alto de Cyperaceae e sinais de ação humana no topo (queda de Alchornea, alta de Rapanea, drenagem da área do rancho). O autor aponta um provável hiato (a idade extrapolada para o início de E seria ~4.030 anos AP) e que a parte superior de E pode ter só alguns séculos. Os valores de Araucaria angustifolia e Dicksonia sellowiana (até ~2% e 5%) indicam, segundo ele, expansão da floresta de araucária no planalto no Holoceno superior. O autor relaciona mudanças do nível d’água na planície a variações do nível do mar (Fairbridge, 1962; Bigarella, 1965), sem comprová-las neste perfil. LOCALIZAÇÃO: o município não consta no artigo; foi derivado pelas coordenadas (Guaramirim, a ~1 km da divisa com Joinville; coordenadas com precisão de minuto, ~2 km), e o pino é aproximado. NOTA DE FONTE: texto integral lido em 2026.10.09 (cópia fornecida pelo usuário); os diagramas polínicos (figs. 4–7) não foram lidos em detalhe — os percentuais citados vêm do texto. Número de tombo e depositário não informados. Registro cadastrado em 2026.10.09: antes, a localização do perfil não era conhecida pelas fontes consultadas (só o resumo). </t>
         </is>
       </c>
-      <c r="L299" s="7" t="inlineStr">
+      <c r="L298" s="5" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1007/BF00203932 (Behling, 1995 — página do artigo)
 https://doi.pangaea.de/10.1007/BF00203932 (cópia do resumo e das referências)
@@ -27176,38 +27088,38 @@
 https://en.wikipedia.org/wiki/Morro_da_Igreja (localização do morro)</t>
         </is>
       </c>
-      <c r="M299" s="7" t="inlineStr">
+      <c r="M298" s="5" t="inlineStr">
         <is>
           <t>BEHLING, H. 1995. Investigations into the late Pleistocene and Holocene history of vegetation and climate in Santa Catarina (S Brazil). Vegetation History and Archaeobotany, 4(3), 127–152. DOI: 10.1007/BF00203932</t>
         </is>
       </c>
-      <c r="N299" s="6" t="n">
+      <c r="N298" s="4" t="n">
         <v>271</v>
       </c>
-      <c r="O299" s="6" t="inlineStr">
+      <c r="O298" s="4" t="inlineStr">
         <is>
           <t>Poço Grande (Guaramirim / Joinville)</t>
         </is>
       </c>
-      <c r="P299" s="6" t="inlineStr">
+      <c r="P298" s="4" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q299" s="6" t="n">
+      <c r="Q298" s="4" t="n">
         <v>-26.4167</v>
       </c>
-      <c r="R299" s="6" t="n">
+      <c r="R298" s="4" t="n">
         <v>-48.8667</v>
       </c>
-      <c r="S299" s="6" t="inlineStr">
+      <c r="S298" s="4" t="inlineStr">
         <is>
           <t>10.1007/BF00203932</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S299"/>
+  <autoFilter ref="A3:S298"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -27222,7 +27134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B989"/>
+  <dimension ref="A1:B998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -37693,16 +37605,20 @@
         </is>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" s="9" t="n"/>
+      <c r="B981" s="9" t="n"/>
+    </row>
     <row r="982">
-      <c r="A982" s="10" t="inlineStr">
+      <c r="A982" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B982" s="9" t="inlineStr"/>
+      <c r="B982" s="9" t="n"/>
     </row>
     <row r="983">
-      <c r="A983" s="11" t="inlineStr">
+      <c r="A983" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -37714,7 +37630,7 @@
       </c>
     </row>
     <row r="984">
-      <c r="A984" s="11" t="inlineStr">
+      <c r="A984" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -37726,7 +37642,7 @@
       </c>
     </row>
     <row r="985">
-      <c r="A985" s="11" t="inlineStr">
+      <c r="A985" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -37738,7 +37654,7 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" s="11" t="inlineStr">
+      <c r="A986" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -37750,7 +37666,7 @@
       </c>
     </row>
     <row r="987">
-      <c r="A987" s="11" t="inlineStr">
+      <c r="A987" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -37762,7 +37678,7 @@
       </c>
     </row>
     <row r="988">
-      <c r="A988" s="11" t="inlineStr">
+      <c r="A988" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -37774,12 +37690,104 @@
       </c>
     </row>
     <row r="989">
-      <c r="A989" s="11" t="inlineStr">
+      <c r="A989" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B991" s="9" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B992" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B993" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B994" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B995" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B996" s="9" t="inlineStr">
+        <is>
+          <t>Gerada a partir do campo Descritor (scripts/citacoes-abnt.py), obra por obra, separadas por " | ". Obras sem formato bibliográfico (reportagem, nota) aparecem entre colchetes, transcritas — nunca completadas por suposição. Em 2026.09.13 as citações antigas foram substituídas porque 42 delas eram de outro trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B997" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B998" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Traço de pastagem, frequentemente ASSOCIADO a impressões de espículas de esponjas hexactinélidas — associação que liga diretamente a icnofauna à fauna corpórea da bacia. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): as escavações horizontais descritas como Gordia por Netto &amp; Zucatti-da-Rosa (1997) foram atribuídas a Helminthoidichnites isp. por Zucatti-da-Rosa (2006). O registro nº 211 trata do mesmo tipo de traço sob o nome posterior; este registro preserva o nome da descrição original. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Traço de pastagem, frequentemente ASSOCIADO a impressões de espículas de esponjas hexactinélidas — associação que liga diretamente a icnofauna à fauna corpórea da bacia. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): as escavações horizontais descritas como Gordia por Netto &amp; Zucatti-da-Rosa (1997) foram atribuídas a Helminthoidichnites isp. por Zucatti-da-Rosa (2006). O registro nº 202 trata do mesmo tipo de traço sob o nome posterior; este registro preserva o nome da descrição original. LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Traço de locomoção e pastagem de organismo provavelmente vermiforme e epifaunal. Indica ambiente marinho relativamente profundo, de águas calmas e substrato lamoso. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): o nome Helminthoidichnites isp. é de Zucatti-da-Rosa (2006); em Netto &amp; Zucatti-da-Rosa (1997) as mesmas escavações horizontais aparecem como Gordia (ver registro nº 209). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
+          <t>Traço de locomoção e pastagem de organismo provavelmente vermiforme e epifaunal. Indica ambiente marinho relativamente profundo, de águas calmas e substrato lamoso. Icnofauna dos siltitos prodeltaicos da base da Fm. Campo Alegre (Bacia do Itajaí). A associação é de BAIXA DIVERSIDADE e os traços têm tamanho e profundidade bem inferiores aos registrados na literatura paleoicnológica — os autores interpretam isso como situação de estresse ambiental. Estes icnofósseis sustentaram a atribuição de idade cambriana inferior a média para a bacia, em contraposição às datações absolutas por Pb/U, que apontam o Ediacarano (entre ~630 e ~541 Ma). A divergência entre idade bioestratigráfica e radiométrica permanece em aberto. HOMONÍMIA — ATENÇÃO: existem dois "Campo Alegre" na geologia catarinense, sem relação entre si. (1) A Fm. CAMPO ALEGRE, desta ficha, é unidade da BACIA DO ITAJAÍ, no vale do Itajaí, e é fossilífera. (2) A BACIA DE CAMPO ALEGRE fica no NORDESTE do estado, junto ao município homônimo, cobre ~500 km² e é vulcanossedimentar — riolitos, traquitos, tufos e sedimentos vulcanogênicos, com vulcanismo datado em ~602 Ma. Não há registro paleontológico conhecido para ela, o que é esperado dada a litologia predominantemente vulcânica. Um registro da Fm. Campo Alegre NÃO deve ser atribuído ao município de Campo Alegre. ATENÇÃO (2026.09.13): Becker-Kerber et al. (2024, Precambrian Research 403:107307, DOI 10.1016/j.precamres.2024.107307) descrevem, na Bacia do Itajaí, marcas horizontais repetitivas semelhantes a icnofósseis simples que interpretam como tectógrafos (pseudofósseis por cisalhamento entre camadas). Na leitura do texto integral (2026.10.09): trata-se de uma ocorrência nova, em Gaspar (26°54′54,59″S, 48°58′7,10″W), no topo da sequência deposicional 1, logo abaixo dos níveis de tufo datados em 563 ± 3 Ma (Becker-Kerber et al. 2020); o artigo NÃO reavalia os icnofósseis descritos antes na bacia (Netto &amp; Zucatti-da-Rosa 1997, Zucatti-da-Rosa 2006 e Netto 2012 não são citados). Ele compara os tectógrafos, em termos gerais, com traços horizontais simples e propõe critérios para distingui-los (traços verdadeiros raramente têm orientação preferencial nem morfologias repetidas no mesmo plano; tectógrafos associam-se a clastos, têm estrias longitudinais e a orientação do campo de deformação). Segundo o artigo, Gordia tem curvas sinuosas e irregulares, e Helminthoidichnites é simples, não ramificado e levemente sinuoso, mas sem orientação preferencial; esses critérios não foram aplicados, no artigo, aos exemplares deste registro. HISTÓRICO TAXONÔMICO (2026.10.09, segundo Netto, 2012): o nome Helminthoidichnites isp. é de Zucatti-da-Rosa (2006); em Netto &amp; Zucatti-da-Rosa (1997) as mesmas escavações horizontais aparecem como Gordia (ver registro nº 200). LOCALIZAÇÃO (2026.10.09): versões anteriores marcavam o município de Itajaí (foz da bacia) com a rubrica «BR-470»; nenhuma fonte consultada situa os afloramentos ali, e a rubrica «BR-470» não foi confirmada. A reportagem da Pesquisa FAPESP sobre a fauna ediacarana situa o terreno fossilífero sob os municípios de Blumenau, Indaial e Apiúna; o ponto no mapa é aproximado e a localidade exata não consta nos resumos consultados.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="N15" s="6" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Classificação: pista de artrópode; os autores sugerem crustáceos, possivelmente Isopoda ou outros Peracarida. HISTÓRICO TAXONÔMICO E ESTRATIGRÁFICO (2026.10.09, Silva &amp; Fernandes, 2021): o material foi descrito por Maury (1927, «Fósseis silurianos de Santa Catarina», Boletim do Serviço Geológico e Mineralógico do Brasil 23:1–15) como o anelídeo «Oliveirania santa catharinae» e atribuído ao Siluriano, por semelhança com fósseis de Nova York; Moraes Rego &amp; Guimarães (1926) haviam chamado a unidade de «Formação Anitápolis» e a tratado como ordoviciana, e Beurlen (1952) defendeu idade carbonífero-permiana. Silva &amp; Fernandes (2021) consideram os supostos anelídeos pseudofósseis de origem inorgânica e redescrevem as pistas associadas como Pterichnus mauryae isp. nov. — primeira ocorrência do icnogênero no Brasil e a mais antiga do mundo —, atribuem as camadas Anitápolis à Fm. Rio do Sul (Grupo Itararé) e idade carbonífera superior. Holótipo MCT.I.379; parátipos incluem MCT.I.380–384 e MCT.I.7042–7051. Gluckstadtella elongata ocorre associada (amostras MCT.I.380, MCT.I.7051 e MCT.I.7047; ver também o registro nº 74). Anitápolis era distrito de Palhoça até 1961 (mesma fonte). O ponto no mapa é aproximado (município). Balistieri et al. (2021) resumem o caso em revisão da paleoicnologia do Grupo Itararé catarinense. O resumo de Silva &amp; Fernandes (2021) consta no repositório da revista; o artigo não traz DOI na página consultada.</t>
+          <t>Classificação: pista de artrópode; os autores sugerem crustáceos, possivelmente Isopoda ou outros Peracarida. HISTÓRICO TAXONÔMICO E ESTRATIGRÁFICO (2026.10.09, Silva &amp; Fernandes, 2021): o material foi descrito por Maury (1927, «Fósseis silurianos de Santa Catarina», Boletim do Serviço Geológico e Mineralógico do Brasil 23:1–15) como o anelídeo «Oliveirania santa catharinae» e atribuído ao Siluriano, por semelhança com fósseis de Nova York; Moraes Rego &amp; Guimarães (1926) haviam chamado a unidade de «Formação Anitápolis» e a tratado como ordoviciana, e Beurlen (1952) defendeu idade carbonífero-permiana. Silva &amp; Fernandes (2021) consideram os supostos anelídeos pseudofósseis de origem inorgânica e redescrevem as pistas associadas como Pterichnus mauryae isp. nov. — primeira ocorrência do icnogênero no Brasil e a mais antiga do mundo —, atribuem as camadas Anitápolis à Fm. Rio do Sul (Grupo Itararé) e idade carbonífera superior. Holótipo MCT.I.379; parátipos incluem MCT.I.380–384 e MCT.I.7042–7051. Gluckstadtella elongata ocorre associada (amostras MCT.I.380, MCT.I.7051 e MCT.I.7047; ver também o registro nº 66). Anitápolis era distrito de Palhoça até 1961 (mesma fonte). O ponto no mapa é aproximado (município). Balistieri et al. (2021) resumem o caso em revisão da paleoicnologia do Grupo Itararé catarinense. O resumo de Silva &amp; Fernandes (2021) consta no repositório da revista; o artigo não traz DOI na página consultada.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="N17" s="6" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="N19" s="6" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="N21" s="6" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="N25" s="6" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Classificação: pista de artrópode (isópode/anostraca). Espécimes originalmente descritos como Isopodichnus por Marques-Toigo et al. (1989) constam hoje na literatura como pistas de artrópode atribuíveis a Cruziana cf. problematica (ver id 72). CORREÇÃO (2026.09.13): esta ficha atribuía a sinonímia a Balistieri et al. (2002); a atribuição foi retirada porque aquele trabalho trata dos ritmitos de Mafra e a revisão consultada (Balistieri, Netto &amp; Sedorko, 2021) não indica quem propôs a sinonímia</t>
+          <t>Classificação: pista de artrópode (isópode/anostraca). Espécimes originalmente descritos como Isopodichnus por Marques-Toigo et al. (1989) constam hoje na literatura como pistas de artrópode atribuíveis a Cruziana cf. problematica (ver id 64). CORREÇÃO (2026.09.13): esta ficha atribuía a sinonímia a Balistieri et al. (2002); a atribuição foi retirada porque aquele trabalho trata dos ritmitos de Mafra e a revisão consultada (Balistieri, Netto &amp; Sedorko, 2021) não indica quem propôs a sinonímia</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="N27" s="6" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio basal (paleoniscídeo). Pelo menos duzentos exemplares completos de actinopterígios basais, jovens e adultos, são conhecidos do afloramento — preservados sem compressão em concreções fosfáticas ou achatados no folhelho (Hamel, 2005). As espécies nomeadas estão em registros próprios. CORREÇÃO (2026.09.10): a ficha citava "Figueroa et al. (2025)" e a preservação de "coração", sem fonte, e apontava para o artigo de outra localidade; os morfotipos com encéfalo preservado estão no registro nº 098. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): CP.V 5202a é o exemplar da Fig. 3, legendado «A well-preserved Palaeoniscidae fish». O artigo resume a preservação dos peixes como fosfatizada (Fig. 5) e, citando Hamel (2005), infere soterramento rápido por correntes de turbidez episódicas. Na coluna do horizonte (Fig. 2, subníveis 1A–4B) há peixes ósseos em 11 dos 12 subníveis (todos menos 4B). PERFIL DO AFLORAMENTO: o Campáleo fica na BR-280, a 2 km do entroncamento com a BR-116, na área urbana de Mafra; a base expõe os primeiros 10 m do Folhelho Lontras, seguidos do horizonte de macrofósseis (LSMH), um folhelho preto de 1,10 m e, acima, 7 m de ritmito com conchas sem fósseis; Ricetti et al. (2016) dividiram o LSMH em quatro níveis, com subníveis. Na região de Mafra o Folhelho Lontras tem cerca de 50 m; no Campáleo ele começa com folhelho microvarvado com dropstones estriados, seguido de siltito com icnofósseis, e a máxima transgressão é atingida no LSMH. DESCOBERTA: o horizonte foi descoberto em 1908 por Jay Backus Woodworth e Euzébio Paulo de Oliveira, numa expedição em busca de camadas glaciais financiada pelo Shaler Memorial Fund (EUA), e recebeu pouca atenção por cerca de um século. AMBIENTE (interpretação dos autores, apoiada em Mouro et al., 2017): ambiente marinho restrito, provavelmente com 200–400 m de profundidade, com fundo recorrentemente anóxico/euxínico e euxinia intermitente na zona fótica; os autores «acreditam» num contexto de baía de fiorde, embora nenhum paleoalto tenha sido identificado perto do afloramento. STATUS: o artigo trata o depósito como um possível Lagerstätte do Paleozoico Superior; na conclusão, afirma que ele ainda não é considerado Lagerstätte, mas fornece dados valiosos sobre ecossistemas antigos. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Classificação: peixe actinopterígio basal (paleoniscídeo). Pelo menos duzentos exemplares completos de actinopterígios basais, jovens e adultos, são conhecidos do afloramento — preservados sem compressão em concreções fosfáticas ou achatados no folhelho (Hamel, 2005). As espécies nomeadas estão em registros próprios. CORREÇÃO (2026.09.10): a ficha citava "Figueroa et al. (2025)" e a preservação de "coração", sem fonte, e apontava para o artigo de outra localidade; os morfotipos com encéfalo preservado estão no registro nº 090. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): CP.V 5202a é o exemplar da Fig. 3, legendado «A well-preserved Palaeoniscidae fish». O artigo resume a preservação dos peixes como fosfatizada (Fig. 5) e, citando Hamel (2005), infere soterramento rápido por correntes de turbidez episódicas. Na coluna do horizonte (Fig. 2, subníveis 1A–4B) há peixes ósseos em 11 dos 12 subníveis (todos menos 4B). PERFIL DO AFLORAMENTO: o Campáleo fica na BR-280, a 2 km do entroncamento com a BR-116, na área urbana de Mafra; a base expõe os primeiros 10 m do Folhelho Lontras, seguidos do horizonte de macrofósseis (LSMH), um folhelho preto de 1,10 m e, acima, 7 m de ritmito com conchas sem fósseis; Ricetti et al. (2016) dividiram o LSMH em quatro níveis, com subníveis. Na região de Mafra o Folhelho Lontras tem cerca de 50 m; no Campáleo ele começa com folhelho microvarvado com dropstones estriados, seguido de siltito com icnofósseis, e a máxima transgressão é atingida no LSMH. DESCOBERTA: o horizonte foi descoberto em 1908 por Jay Backus Woodworth e Euzébio Paulo de Oliveira, numa expedição em busca de camadas glaciais financiada pelo Shaler Memorial Fund (EUA), e recebeu pouca atenção por cerca de um século. AMBIENTE (interpretação dos autores, apoiada em Mouro et al., 2017): ambiente marinho restrito, provavelmente com 200–400 m de profundidade, com fundo recorrentemente anóxico/euxínico e euxinia intermitente na zona fótica; os autores «acreditam» num contexto de baía de fiorde, embora nenhum paleoalto tenha sido identificado perto do afloramento. STATUS: o artigo trata o depósito como um possível Lagerstätte do Paleozoico Superior; na conclusão, afirma que ele ainda não é considerado Lagerstätte, mas fornece dados valiosos sobre ecossistemas antigos. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="N41" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="N43" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Fragmentos de plantas presentes na biota geral do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo cita lenhos carbonosos bem preservados e dispersos (gêneros Agathoxylon e Abietopitys; Gnaedinger et al., 2012; Urban et al., 2012, resumos), compressões carbonosas de caules e uma estrutura semelhante a âmbar em descrição (registro nº 231). Fig. 5: plantas paralelas ao plano de acamamento, com preservação querogenizada. Fig. 2: fragmentos de lenho («log fragments») assinalados no subnível 1D. Ver o registro nº 066 para o lenho. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Fragmentos de plantas presentes na biota geral do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo cita lenhos carbonosos bem preservados e dispersos (gêneros Agathoxylon e Abietopitys; Gnaedinger et al., 2012; Urban et al., 2012, resumos), compressões carbonosas de caules e uma estrutura semelhante a âmbar em descrição (registro nº 222). Fig. 5: plantas paralelas ao plano de acamamento, com preservação querogenizada. Fig. 2: fragmentos de lenho («log fragments») assinalados no subnível 1D. Ver o registro nº 059 para o lenho. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Coprólitos heteropolares, poucos, reconhecidos nos níveis inferiores do horizonte (Mouro et al., 2020): forma arredondada e cilíndrica, em média cerca de 24 mm de comprimento por 13 mm de largura (alguns com cerca de 6 mm de diâmetro); em certas amostras há acamamento interno concêntrico, em outras, fissuras radiais (Muller et al., 2017, resumo). A análise por MEV não mostrou inclusões fósseis preservadas. Fig. 5: tipo de fossilização «desconhecido». NOTA (corrigida em 2026.10.13): a ficha dizia «espiralados atribuídos a peixes»; o artigo não usa «espiralado» nem atribui os coprólitos a nenhum produtor (o rótulo «Coprolita espiralada» vem da ficha original). A Fig. 2 assinala coprólitos em sete subníveis (1A, 2A, 2B, 3C, 3D, 4A e 4B), embora o texto os trate como poucos e dos níveis inferiores. As enterospiras estão no registro nº 065. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Coprólitos heteropolares, poucos, reconhecidos nos níveis inferiores do horizonte (Mouro et al., 2020): forma arredondada e cilíndrica, em média cerca de 24 mm de comprimento por 13 mm de largura (alguns com cerca de 6 mm de diâmetro); em certas amostras há acamamento interno concêntrico, em outras, fissuras radiais (Muller et al., 2017, resumo). A análise por MEV não mostrou inclusões fósseis preservadas. Fig. 5: tipo de fossilização «desconhecido». NOTA (corrigida em 2026.10.13): a ficha dizia «espiralados atribuídos a peixes»; o artigo não usa «espiralado» nem atribui os coprólitos a nenhum produtor (o rótulo «Coprolita espiralada» vem da ficha original). A Fig. 2 assinala coprólitos em sete subníveis (1A, 2A, 2B, 3C, 3D, 4A e 4B), embora o texto os trate como poucos e dos níveis inferiores. As enterospiras estão no registro nº 058. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="N45" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo lista Orbiculoidea guaraunensis entre os braquiópodes do horizonte, citando Oliveira (1930) e Neves et al. (2017) (registro nº 021). HISTÓRICO (Mouro et al., 2018): as notas e cartas de Oliveira (1911, 1916, 1918) falam em «Discina» e «Lingula»; Ruedemann (1929) cita Lingula e Orbiculoidea; Oliveira (1930) descreve Lingula imbituvensis, Orbiculoidea guaraunensis e Chonetes rionegrensis (trechos lidos por ferramenta de leitura; conferir no original). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Um dos primeiros táxons descritos para o Folhelho Lontras; já citado nos trabalhos pioneiros de Ruedemann (1929) e Carvalho et al. (1942) sobre a fauna de Mafra. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo lista Orbiculoidea guaraunensis entre os braquiópodes do horizonte, citando Oliveira (1930) e Neves et al. (2017) (registro nº 019). HISTÓRICO (Mouro et al., 2018): as notas e cartas de Oliveira (1911, 1916, 1918) falam em «Discina» e «Lingula»; Ruedemann (1929) cita Lingula e Orbiculoidea; Oliveira (1930) descreve Lingula imbituvensis, Orbiculoidea guaraunensis e Chonetes rionegrensis (trechos lidos por ferramenta de leitura; conferir no original). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="N46" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Classificação: inseto. Mouro et al. (2020) registram mais de cem espécimes de insetos no afloramento, atribuídos às ordens Blattodea e Grylloblattodea; cerca de 54% pertencem a Anthracoblattina mendesi (registro nº 020). Preservação de dois tipos: compressões carbonosas ou piritizadas, e formas tridimensionais fosfatizadas — algumas com possível tecido muscular preservado (Fig. 4C–H); no espécime CP.I 2276b (articulação fêmur-tíbia), as estruturas semelhantes a músculo são descritas como piritizadas. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): a espectroscopia Raman numa asa detectou querogênio nas nervuras e na matriz, mas não na membrana; MEV/EDS mostrou pontos de enxofre e pirita framboidal numa asa (CP.I 5332a, piritizada), e as formas piritizadas comprimidas se associam à preservação de morfologias submilimétricas (espinhos da tíbia, tarsômeros, flagelômeros; Ricetti et al., 2016). Exemplares figurados ou analisados no artigo, SEM determinação taxonômica específica (o artigo não os atribui a A. mendesi nem a outro táxon): CP/E 3243a,b (insetos tridimensionais fosfatizados), CP.I 2276a,b, CP.I 5332a (piritizado) e CP.I 680 (asa incarbonizada). A lista de amostras do horizonte estudadas inclui ainda CP 399a,b; CP.B 7196; CP/E 3755a,b; CP/E 6521a,b; CP.M 122; CP.I 556a,b; CP.I 877a,b; CP.I 2182a,b; CP.I 7220a,b,c; CP.V 7195a1,a2,b e CP.V 5202a,b, sem indicar o grupo de cada uma. Fig. 2: insetos em nove subníveis (1C, 1D, 2A, 2B, 3A, 3B, 3C, 3D e 4B). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Classificação: inseto. Mouro et al. (2020) registram mais de cem espécimes de insetos no afloramento, atribuídos às ordens Blattodea e Grylloblattodea; cerca de 54% pertencem a Anthracoblattina mendesi (registro nº 018). Preservação de dois tipos: compressões carbonosas ou piritizadas, e formas tridimensionais fosfatizadas — algumas com possível tecido muscular preservado (Fig. 4C–H); no espécime CP.I 2276b (articulação fêmur-tíbia), as estruturas semelhantes a músculo são descritas como piritizadas. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): a espectroscopia Raman numa asa detectou querogênio nas nervuras e na matriz, mas não na membrana; MEV/EDS mostrou pontos de enxofre e pirita framboidal numa asa (CP.I 5332a, piritizada), e as formas piritizadas comprimidas se associam à preservação de morfologias submilimétricas (espinhos da tíbia, tarsômeros, flagelômeros; Ricetti et al., 2016). Exemplares figurados ou analisados no artigo, SEM determinação taxonômica específica (o artigo não os atribui a A. mendesi nem a outro táxon): CP/E 3243a,b (insetos tridimensionais fosfatizados), CP.I 2276a,b, CP.I 5332a (piritizado) e CP.I 680 (asa incarbonizada). A lista de amostras do horizonte estudadas inclui ainda CP 399a,b; CP.B 7196; CP/E 3755a,b; CP/E 6521a,b; CP.M 122; CP.I 556a,b; CP.I 877a,b; CP.I 2182a,b; CP.I 7220a,b,c; CP.V 7195a1,a2,b e CP.V 5202a,b, sem indicar o grupo de cada uma. Fig. 2: insetos em nove subníveis (1C, 1D, 2A, 2B, 3A, 3B, 3C, 3D e 4B). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="N47" s="6" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>CITAÇÃO EM REVISÃO — o material não foi examinado por este banco. Segundo a síntese da Wikipédia sobre o Lagerstätte Folhelho Lontras, que remete a Saldanha et al. (2023, Sedimentary Geology 458:106533), há em Rio dos Cedros um depósito de folhelho com menos de 1 m de espessura, a cerca de 85 km do Folhelho Lontras (afloramento Campáleo, Mafra); não está claro se ele pertence ao mesmo Lagerstätte ou é um nível distinto, porque há poucos estudos. O texto integral do artigo não pôde ser aberto (acesso bloqueado). CONTEÚDO FOSSILÍFERO: a lista 'larvas, coprólitos, braquiópodes, esponjas, peixes' que constava neste registro NÃO foi confirmada em nenhuma fonte consultada e foi retirada do título. HISTÓRICO DE CORREÇÃO: o registro citava Ricetti et al. (2016, Rev. Bras. Paleontol. 19(2)) e Oliveira (1930), trabalhos que não mencionam Rio dos Cedros; foram substituídos pela fonte acima. POSSÍVEL LIGAÇÃO: o registro 37 cita um resumo sobre uma 'nova localidade equivalente ao Folhelho Lontras' que pode se referir a este mesmo depósito — não foi possível confirmar (o resumo não pôde ser aberto).</t>
+          <t>CITAÇÃO EM REVISÃO — o material não foi examinado por este banco. Segundo a síntese da Wikipédia sobre o Lagerstätte Folhelho Lontras, que remete a Saldanha et al. (2023, Sedimentary Geology 458:106533), há em Rio dos Cedros um depósito de folhelho com menos de 1 m de espessura, a cerca de 85 km do Folhelho Lontras (afloramento Campáleo, Mafra); não está claro se ele pertence ao mesmo Lagerstätte ou é um nível distinto, porque há poucos estudos. O texto integral do artigo não pôde ser aberto (acesso bloqueado). CONTEÚDO FOSSILÍFERO: a lista 'larvas, coprólitos, braquiópodes, esponjas, peixes' que constava neste registro NÃO foi confirmada em nenhuma fonte consultada e foi retirada do título. HISTÓRICO DE CORREÇÃO: o registro citava Ricetti et al. (2016, Rev. Bras. Paleontol. 19(2)) e Oliveira (1930), trabalhos que não mencionam Rio dos Cedros; foram substituídos pela fonte acima. POSSÍVEL LIGAÇÃO: o registro 31 cita um resumo sobre uma 'nova localidade equivalente ao Folhelho Lontras' que pode se referir a este mesmo depósito — não foi possível confirmar (o resumo não pôde ser aberto).</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="N49" s="6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 021). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Braquiópode quonetídeo da biota do Campáleo; espécimes geralmente de tamanho diminuto. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 019). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="N51" s="6" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 021). HISTÓRICO NOMENCLATURAL (Mouro et al., 2018, texto lido por ferramenta de leitura): Oliveira (1930) descreveu a espécie como Lingula imbituvensis; a revisão dos braquiópodes do Folhelho Lontras a registra como Langella imbituvensis (Oliveira). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Braquiópode lingulídeo; associado a icnofósseis de bioerosão (Arachnostega isp.) perfurando suas conchas. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 019). HISTÓRICO NOMENCLATURAL (Mouro et al., 2018, texto lido por ferramenta de leitura): Oliveira (1930) descreveu a espécie como Lingula imbituvensis; a revisão dos braquiópodes do Folhelho Lontras a registra como Langella imbituvensis (Oliveira). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="N52" s="4" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Braquiópode beecheriídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 021). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Braquiópode beecheriídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 019). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="N53" s="6" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Braquiópode amboceolídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 021). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Braquiópode amboceolídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 019). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Braquiópode rugosoquonetídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 021). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Braquiópode rugosoquonetídeo da biota do Campáleo. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): listado entre os braquiópodes do horizonte (seção 3.1; ver registro nº 019). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="N55" s="6" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo NÃO menciona Discinidae; lista Orbiculoidea guaraunensis (registro nº 041), gênero que é ele próprio um discinídeo, de modo que a ideia de uma família «distinta de Orbiculoidea» não vem deste artigo. HISTÓRICO (Mouro et al., 2018): notas de Oliveira (1911–1918) citam «Discina» no Folhelho Lontras, e Ruedemann (1929) cita Orbiculoidea (trechos lidos por ferramenta de leitura; conferir no original). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Família de braquiópodes adicional documentada na fauna do Campáleo, distinta de Orbiculoidea. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo NÃO menciona Discinidae; lista Orbiculoidea guaraunensis (registro nº 034), gênero que é ele próprio um discinídeo, de modo que a ideia de uma família «distinta de Orbiculoidea» não vem deste artigo. HISTÓRICO (Mouro et al., 2018): notas de Oliveira (1911–1918) citam «Discina» no Folhelho Lontras, e Ruedemann (1929) cita Orbiculoidea (trechos lidos por ferramenta de leitura; conferir no original). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="N57" s="6" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo não usa o termo «Reticulosa»; descreve os poríferos como esponjas hexactinelídeas articuladas (Microhemidiscia greinerti, registro nº 053) e uma possível demosponja (registro nº 022). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Ordem extinta de esponjas registrada na biota do Campáleo; possível demosponja também citada. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo não usa o termo «Reticulosa»; descreve os poríferos como esponjas hexactinelídeas articuladas (Microhemidiscia greinerti, registro nº 046) e uma possível demosponja (registro nº 020). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="N58" s="4" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Classificação: tubarão Symmoriiformes (Chondrichthyes). Primeiro Symmoriiformes registrado no Brasil. Novo táxon de tubarão symmoriiforme descrito formalmente a partir de dente isolado do Campáleo NOTA: versões anteriores do catálogo traziam também um registro nº 017, "Symmoriiformes gen. et sp. nov.", que era o MESMO dente antes de receber nome — duplicata removida em 2026.09.6. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Classificação: tubarão Symmoriiformes (Chondrichthyes). Primeiro Symmoriiformes registrado no Brasil. Novo táxon de tubarão symmoriiforme descrito formalmente a partir de dente isolado do Campáleo NOTA: versões anteriores do catálogo traziam também uma ficha «Symmoriiformes gen. et sp. nov.» (nº 017 na numeração anterior a 15/10/2026), que era o MESMO dente antes de receber nome — duplicata removida em 2026.09.6. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="N59" s="6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="N61" s="6" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="N62" s="4" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="N63" s="6" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>ATRIBUIÇÃO NÃO VERIFICADA EM FONTE PRIMÁRIA. Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras. NOTA DE FONTE (corrigida em 2026.10.13): o PDF integral de Mouro et al. (2020) foi lido e NÃO trata de escamas de peixe de nadadeira lobada nem cita Coelacanthus ou celacantos — a nota de 2026.10.09 dizia o contrário, e estava errada. A atribuição a Coelacanthus sp. aparece na listagem da Wikipédia, que cita esse artigo, e o capítulo de Mouro et al. (2021) não foi consultado (ver registro nº 19). O gênero deve ser tomado como atribuição não verificada em fonte primária. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>ATRIBUIÇÃO NÃO VERIFICADA EM FONTE PRIMÁRIA. Classificação: peixe de nadadeira lobada (Crossopterygii). Conhecido a partir de escamas; celacanto paleozoico do Folhelho Lontras. NOTA DE FONTE (corrigida em 2026.10.13): o PDF integral de Mouro et al. (2020) foi lido e NÃO trata de escamas de peixe de nadadeira lobada nem cita Coelacanthus ou celacantos — a nota de 2026.10.09 dizia o contrário, e estava errada. A atribuição a Coelacanthus sp. aparece na listagem da Wikipédia, que cita esse artigo, e o capítulo de Mouro et al. (2021) não foi consultado (ver registro nº 17). O gênero deve ser tomado como atribuição não verificada em fonte primária. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="N64" s="4" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="N65" s="6" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="N67" s="6" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Perfurações em conchas de braquiópodes, evidência provável de predação. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo não menciona Oichnus nem perfurações de predação em braquiópodes; a ocorrência segue o verbete da Wikipédia, que a atribui a outro trabalho (Saldanha, 2022, Palaeogeography, Palaeoclimatology, Palaeoecology 609, não localizado nem consultado) e não a Mouro et al. (2020). Este artigo sustenta nesta ficha apenas o contexto estratigráfico e a lista de braquiópodes (registro nº 021). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Perfurações em conchas de braquiópodes, evidência provável de predação. CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo não menciona Oichnus nem perfurações de predação em braquiópodes; a ocorrência segue o verbete da Wikipédia, que a atribui a outro trabalho (Saldanha, 2022, Palaeogeography, Palaeoclimatology, Palaeoecology 609, não localizado nem consultado) e não a Mouro et al. (2020). Este artigo sustenta nesta ficha apenas o contexto estratigráfico e a lista de braquiópodes (registro nº 019). UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="N68" s="4" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="N69" s="6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Restos lenhosos dispersos pelo folhelho, com fragmentos comuns; também há estruturas semelhantes a âmbar (resina fossilizada) CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo cita lenhos carbonosos bem preservados e dispersos, dos gêneros Agathoxylon e Abietopitys (Gnaedinger et al., 2012; Urban et al., 2012, resumos de congresso) — Abietopitys é característico do Carbonífero e do Permiano da Argentina, Brasil e África, e Agathoxylon tem distribuição mais ampla (Carbonífero–Terciário) —, além de compressões carbonosas de caules e de uma estrutura semelhante a âmbar em descrição (registro nº 231). Fig. 2: fragmentos de lenho no subnível 1D. NÃO constam no artigo a classificação como «gimnosperma araucariácea» (da categoria desta ficha) nem a expressão «fragmentos comuns»; o texto fala em exemplares dispersos. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Restos lenhosos dispersos pelo folhelho, com fragmentos comuns; também há estruturas semelhantes a âmbar (resina fossilizada) CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): o artigo cita lenhos carbonosos bem preservados e dispersos, dos gêneros Agathoxylon e Abietopitys (Gnaedinger et al., 2012; Urban et al., 2012, resumos de congresso) — Abietopitys é característico do Carbonífero e do Permiano da Argentina, Brasil e África, e Agathoxylon tem distribuição mais ampla (Carbonífero–Terciário) —, além de compressões carbonosas de caules e de uma estrutura semelhante a âmbar em descrição (registro nº 222). Fig. 2: fragmentos de lenho no subnível 1D. NÃO constam no artigo a classificação como «gimnosperma araucariácea» (da categoria desta ficha) nem a expressão «fragmentos comuns»; o texto fala em exemplares dispersos. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="N70" s="4" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Primeira ocorrência de conodontes (aparelhos alimentares completos e articulados) descrita para toda a Bacia do Paraná; dezenas de elementos ramiformes inicialmente confundidos macroscopicamente com espículas de poríferos; gênero gondolelídeo marcador do Cisuraliano NOTA: o registro nº 023 ("Conodontes indet. — 5–6 espécies", apoiado em reportagem) repetia este material e foi removido em 2026.09.10. Mouro et al. (2020) relatam dezenas de aparelhos articulados e centenas de elementos isolados de Mesogondolella spp., todos fosfatizados (Scomazzon et al., 2013; Wilner et al., 2016a). CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): os conodontes ocorrem em cinco subníveis (Fig. 2: 2B, 3B, 3C, 3D e 4A), alternando a preservação de elementos P1 e ramiformes; os elementos seguem em estudo, e Scomazzon et al. (2013) os descrevem como de fosfato de cálcio. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Primeira ocorrência de conodontes (aparelhos alimentares completos e articulados) descrita para toda a Bacia do Paraná; dezenas de elementos ramiformes inicialmente confundidos macroscopicamente com espículas de poríferos; gênero gondolelídeo marcador do Cisuraliano NOTA: uma ficha anterior («Conodontes indet. — 5–6 espécies», apoiada em reportagem; nº 023 na numeração anterior a 15/10/2026) repetia este material e foi removida em 2026.09.10. Mouro et al. (2020) relatam dezenas de aparelhos articulados e centenas de elementos isolados de Mesogondolella spp., todos fosfatizados (Scomazzon et al., 2013; Wilner et al., 2016a). CONFERÊNCIA COM O PDF INTEGRAL DE MOURO ET AL. (2020; 2026.10.13): os conodontes ocorrem em cinco subníveis (Fig. 2: 2B, 3B, 3C, 3D e 4A), alternando a preservação de elementos P1 e ramiformes; os elementos seguem em estudo, e Scomazzon et al. (2013) os descrevem como de fosfato de cálcio. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="N71" s="6" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio (tecidos moles preservados). Oito espécimes preservados em concreções sideríticas foram tomografados por micro-CT, revelando preservação tridimensional de encéfalo, nervos cranianos, olhos e possíveis tecidos cardiovasculares — condição raríssima no registro fóssil, já que o tecido neural se decompõe muito rápido. Os dois morfotipos diferem tanto no esqueleto quanto no encéfalo: o mais próximo dos actinopterígios viventes apresenta telencéfalo evertido (característica das formas atuais), ausente no outro morfotipo e em Coccocephalus. Fornece um modelo revisado para a evolução do encéfalo dos peixes de nadadeiras raiadas, o maior grupo de vertebrados vivos. NOTA: o registro nº 016 ("Actinopterygii indet. — morfotipo 2") repetia estes mesmos morfotipos e foi removido em 2026.09.10. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
+          <t>Classificação: peixe actinopterígio (tecidos moles preservados). Oito espécimes preservados em concreções sideríticas foram tomografados por micro-CT, revelando preservação tridimensional de encéfalo, nervos cranianos, olhos e possíveis tecidos cardiovasculares — condição raríssima no registro fóssil, já que o tecido neural se decompõe muito rápido. Os dois morfotipos diferem tanto no esqueleto quanto no encéfalo: o mais próximo dos actinopterígios viventes apresenta telencéfalo evertido (característica das formas atuais), ausente no outro morfotipo e em Coccocephalus. Fornece um modelo revisado para a evolução do encéfalo dos peixes de nadadeiras raiadas, o maior grupo de vertebrados vivos. NOTA: uma ficha anterior («Actinopterygii indet. — morfotipo 2»; nº 016 na numeração anterior a 15/10/2026) repetia estes mesmos morfotipos e foi removida em 2026.09.10. UNIDADE E IDADE (Mouro et al., 2020; PDF integral conferido em 2026.10.13): o Folhelho Lontras é a unidade mais alta da Fm. Campo Mourão, Grupo Itararé (França &amp; Potter, 1988), marcador estratigráfico de escala de bacia ligado a um evento de inundação marinha máxima. NOMENCLATURA: títulos de trabalhos locais citados no artigo situam o folhelho na base da Fm. Rio do Sul (Ricetti et al., 2012) ou no Membro Rio do Sul da Fm. Taciba (Kallen et al., 2014); o próprio artigo adota Campo Mourão. IDADE EM DISCUSSÃO: conodontes (Mesogondolella spp.) e palinologia (Zona Vittatina costabilis) indicam Cisuraliano, com apoio preliminar de datação Rb-Sr (Koester et al., 2016); datações U-Pb em zircão da porção superior do Grupo Itararé apontam Carbonífero Superior, e os autores consideram idade pensilvaniana para o afloramento Campáleo. O artigo não dá idade numérica; o intervalo do campo «idade» é uma convenção deste banco em torno do limite Carbonífero–Permiano.</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="N72" s="4" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="N73" s="6" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="O73" s="6" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="N74" s="4" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="N75" s="6" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="N76" s="4" t="n">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="N77" s="6" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="N78" s="4" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="N79" s="6" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="N80" s="4" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="N81" s="6" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="N82" s="4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="N83" s="6" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="N84" s="4" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="N85" s="6" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="O85" s="6" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="N86" s="4" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="N87" s="6" t="n">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="O87" s="6" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="N88" s="4" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="N89" s="6" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="N90" s="4" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="N91" s="6" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O91" s="6" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="N92" s="4" t="n">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Presente também no Folhelho Lontras (registro nº 50), segundo o mesmo resumo. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 41 e 47–51 (Lontras).</t>
+          <t>Presente também no Folhelho Lontras (registro nº 43), segundo o mesmo resumo. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 34 e 40–44 (Lontras).</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="N93" s="6" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>Identificação marcada como incerta («?») pelos autores. Mouro et al. (2020) listam «Chonetes rionegrensis» no Folhelho Lontras (registro nº 47); a relação entre esse nome e a «Quinquenella rionegrensis?» de Neves et al. (2017) não foi verificada. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 41 e 47–51 (Lontras).</t>
+          <t>Identificação marcada como incerta («?») pelos autores. Mouro et al. (2020) listam «Chonetes rionegrensis» no Folhelho Lontras (registro nº 40); a relação entre esse nome e a «Quinquenella rionegrensis?» de Neves et al. (2017) não foi verificada. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 34 e 40–44 (Lontras).</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="N94" s="4" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>HISTÓRICO NOMENCLATURAL: descrita por Oliveira (1930) como Lingula imbituvensis; o resumo adota Langella imbituvensis (ver registro nº 48). Presente também no Folhelho Lontras. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 41 e 47–51 (Lontras).</t>
+          <t>HISTÓRICO NOMENCLATURAL: descrita por Oliveira (1930) como Lingula imbituvensis; o resumo adota Langella imbituvensis (ver registro nº 41). Presente também no Folhelho Lontras. Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 34 e 40–44 (Lontras).</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="N95" s="6" t="n">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>Táxon descrito por Oliveira (1930), também presente no Folhelho Lontras (registro nº 41). Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 41 e 47–51 (Lontras).</t>
+          <t>Táxon descrito por Oliveira (1930), também presente no Folhelho Lontras (registro nº 34). Assembleia de braquiópodes da porção média da Fm. Mafra na Fazenda Potreiro (Mafra), a «associação de Mafra» de Neves et al. (2017); o resumo informa que o material está na coleção científica do CENPALEO e que só duas espécies haviam sido formalmente descritas ou identificadas antes, sendo as faunas mais diversas do que se supunha. Segundo o resumo, as faunas de Mafra e de Lontras (Campáleo) dividem vários táxons, três espécies ocorrem também na parte superior da Fm. Taciba (Paraná) e ambas são anteriores ao registro da fauna de Eurydesma. O resumo não traz descrições, medidas nem números de tombo. RESSALVA DE COORDENADA: a fonte não publica coordenada; usa-se a do sítio Fazenda Potreiro já existente (que é a da sede municipal de Mafra). NOTA DE FONTE (2026.10.14): o resumo foi lido por ferramenta de leitura automática do registro do CONICET Digital e conferido contra o índice do boletim; as demais espécies do resumo constam nos registros 34 e 40–44 (Lontras).</t>
         </is>
       </c>
       <c r="L96" s="5" t="inlineStr">
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="N96" s="4" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="N97" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O97" s="6" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>GP/3E 606A–D e 605 (segundo a dissertação; mesmo bloco do registro nº 26; depositário não esclarecido no trecho consultado)</t>
+          <t>GP/3E 606A–D e 605 (segundo a dissertação; mesmo bloco do registro nº 23; depositário não esclarecido no trecho consultado)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="N98" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="N99" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O99" s="6" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="N100" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="N101" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O101" s="6" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="N102" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         </is>
       </c>
       <c r="N103" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O103" s="6" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe ósseo. Inclui escamas de celacanto, coprólitos espiralados, braquiópodes, vegetais e poríferos POSSÍVEL LIGAÇÃO: a 'nova localidade' pode ser a de Rio dos Cedros (registro 43), único depósito equivalente ao Folhelho Lontras citado em Saldanha et al. (2023); não confirmado, porque o resumo não pôde ser aberto.</t>
+          <t>Classificação: peixe ósseo. Inclui escamas de celacanto, coprólitos espiralados, braquiópodes, vegetais e poríferos POSSÍVEL LIGAÇÃO: a 'nova localidade' pode ser a de Rio dos Cedros (registro 36), único depósito equivalente ao Folhelho Lontras citado em Saldanha et al. (2023); não confirmado, porque o resumo não pôde ser aberto.</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="N104" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="N105" s="6" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O105" s="6" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="N106" s="4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="O107" s="6" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="N108" s="4" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="N109" s="6" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="O109" s="6" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="N110" s="4" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="O111" s="6" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="N112" s="4" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="N113" s="6" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O113" s="6" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="N114" s="4" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="O115" s="6" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="N116" s="4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="O117" s="6" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="N118" s="4" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="O119" s="6" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="N120" s="4" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="N121" s="6" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="O121" s="6" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="N122" s="4" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="N123" s="6" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="O123" s="6" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="N124" s="4" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O125" s="6" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="N126" s="4" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         </is>
       </c>
       <c r="N127" s="6" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="O127" s="6" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         </is>
       </c>
       <c r="N128" s="4" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="N129" s="6" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O129" s="6" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="N130" s="4" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="O131" s="6" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="N132" s="4" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O133" s="6" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="N134" s="4" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="N135" s="6" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="O135" s="6" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
       <c r="N136" s="4" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="N137" s="6" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="O137" s="6" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="N138" s="4" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="N139" s="6" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O139" s="6" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="N140" s="4" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         </is>
       </c>
       <c r="N141" s="6" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O141" s="6" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="N142" s="4" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         </is>
       </c>
       <c r="N143" s="6" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="O143" s="6" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="N144" s="4" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="N145" s="6" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="O145" s="6" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="N146" s="4" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="N147" s="6" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="O147" s="6" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         </is>
       </c>
       <c r="N148" s="4" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="N149" s="6" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="O149" s="6" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="N150" s="4" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         </is>
       </c>
       <c r="N151" s="6" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="O151" s="6" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         </is>
       </c>
       <c r="N152" s="4" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="N153" s="6" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="O153" s="6" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="N154" s="4" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         </is>
       </c>
       <c r="N155" s="6" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O155" s="6" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="N156" s="4" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         </is>
       </c>
       <c r="N157" s="6" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="O157" s="6" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="N158" s="4" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="N159" s="6" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="O159" s="6" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="N160" s="4" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="N161" s="6" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="O161" s="6" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="N162" s="4" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="N163" s="6" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="O163" s="6" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="N164" s="4" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="N165" s="6" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="O165" s="6" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         </is>
       </c>
       <c r="N166" s="4" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="N167" s="6" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="O167" s="6" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         </is>
       </c>
       <c r="N168" s="4" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         </is>
       </c>
       <c r="N169" s="6" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="O169" s="6" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="N170" s="4" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O171" s="6" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         </is>
       </c>
       <c r="N172" s="4" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="K173" s="7" t="inlineStr">
         <is>
-          <t>GÊNERO E ESPÉCIE NOVOS, erigidos sobre material catarinense. Caso raro em paleobotânica: a assembleia é monoespecífica e autóctone, com as partes da planta ainda CONECTADAS ENTRE SI e alguns eixos preservados em posição de vida, o que permitiu reconstruir a planta INTEIRA — sistema radicular com eixos não articulados e radículas finas, eixos articulados do tipo Paracalamites e verticilos foliares do tipo Phyllotheca. A estrutura reprodutiva tem esporangióforos bifurcados, não peltados, com esporângios clavados terminais dispostos ao longo dos internós, sem formar estróbilos verdadeiros. Os autores interpretam que Paragiridia e formas afins descendem diretamente das Archaeocalamitaceae carboníferas, representando uma linhagem separada de esfenófitas que evoluiu rumo ao esporangióforo peltado organizado em estróbilo. Relaciona-se a Giridia, gênero que na Bacia do Paraná ocorre apenas no Afloramento Bainha. NOTA (2026.10.09): o afloramento Bruno Peiker é o mesmo da «nova forma» informal de Boardman (2006), registro nº 192; a equivalência entre as duas não foi verificada.</t>
+          <t>GÊNERO E ESPÉCIE NOVOS, erigidos sobre material catarinense. Caso raro em paleobotânica: a assembleia é monoespecífica e autóctone, com as partes da planta ainda CONECTADAS ENTRE SI e alguns eixos preservados em posição de vida, o que permitiu reconstruir a planta INTEIRA — sistema radicular com eixos não articulados e radículas finas, eixos articulados do tipo Paracalamites e verticilos foliares do tipo Phyllotheca. A estrutura reprodutiva tem esporangióforos bifurcados, não peltados, com esporângios clavados terminais dispostos ao longo dos internós, sem formar estróbilos verdadeiros. Os autores interpretam que Paragiridia e formas afins descendem diretamente das Archaeocalamitaceae carboníferas, representando uma linhagem separada de esfenófitas que evoluiu rumo ao esporangióforo peltado organizado em estróbilo. Relaciona-se a Giridia, gênero que na Bacia do Paraná ocorre apenas no Afloramento Bainha. NOTA (2026.10.09): o afloramento Bruno Peiker é o mesmo da «nova forma» informal de Boardman (2006), registro nº 183; a equivalência entre as duas não foi verificada.</t>
         </is>
       </c>
       <c r="L173" s="7" t="inlineStr">
@@ -15800,7 +15800,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="O173" s="6" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="N174" s="4" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="O175" s="6" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>Espécimes com arranjo semelhante ao das Archaeocalamitaceae, por não apresentarem verticilos foliares nem brácteas entre as regiões férteis; diferem de Notocalamites askosus (do Afloramento Bainha) por não terem nós nem folhas modificadas junto à região fértil. Os autores os consideram um NOVO TÁXON da família Notocalamitaceae — à época do estudo, ainda sem denominação formal. Taió era conhecida por suas exposições de depósitos MARINHOS, com pectinídeos e equinodermas do Membro Paraguaçu. O achado de níveis com restos vegetais na BASE do mesmo membro, próximo aos afloramentos já conhecidos, ampliou o registro fossilífero local e ajuda a entender a evolução dos paleoambientes deposicionais nesta porção da bacia. O material paleobotânico de Taió provém de três localidades distintas: afloramentos Bruno Peiker, Clube Caça e Tiro e Igreja. CORREÇÃO DE FONTE (2026.10.09): a ficha citava também o artigo de 2007 (Boardman et al.), que trata de Phyllotheca australis e Paracalamites australis e não registra Notocalamitaceae (a família só consta na lista de referências, via Rigby, 1972); por isso o artigo saiu do descritor. A «nova forma» é informal na dissertação — a autora a propõe como táxon novo, sem nomeá-lo por se tratar de dissertação, e propõe emendar a diagnose da família e de Notocalamites; o material inclui também folhas tipo Koretrophyllites (gênero de validade duvidosa, segundo Meyen, 1971) e rizomas indeterminados, comparados a Myriophyllites e Pinnularia. A capa da dissertação traz 2006; o registro de catalogação, 2005. Relação com o registro nº 189: ambos vêm do afloramento Bruno Peiker, mas a equivalência entre esta «nova forma» (2006) e Paragiridia taioensis (2016) não foi verificada nas fontes consultadas.</t>
+          <t>Espécimes com arranjo semelhante ao das Archaeocalamitaceae, por não apresentarem verticilos foliares nem brácteas entre as regiões férteis; diferem de Notocalamites askosus (do Afloramento Bainha) por não terem nós nem folhas modificadas junto à região fértil. Os autores os consideram um NOVO TÁXON da família Notocalamitaceae — à época do estudo, ainda sem denominação formal. Taió era conhecida por suas exposições de depósitos MARINHOS, com pectinídeos e equinodermas do Membro Paraguaçu. O achado de níveis com restos vegetais na BASE do mesmo membro, próximo aos afloramentos já conhecidos, ampliou o registro fossilífero local e ajuda a entender a evolução dos paleoambientes deposicionais nesta porção da bacia. O material paleobotânico de Taió provém de três localidades distintas: afloramentos Bruno Peiker, Clube Caça e Tiro e Igreja. CORREÇÃO DE FONTE (2026.10.09): a ficha citava também o artigo de 2007 (Boardman et al.), que trata de Phyllotheca australis e Paracalamites australis e não registra Notocalamitaceae (a família só consta na lista de referências, via Rigby, 1972); por isso o artigo saiu do descritor. A «nova forma» é informal na dissertação — a autora a propõe como táxon novo, sem nomeá-lo por se tratar de dissertação, e propõe emendar a diagnose da família e de Notocalamites; o material inclui também folhas tipo Koretrophyllites (gênero de validade duvidosa, segundo Meyen, 1971) e rizomas indeterminados, comparados a Myriophyllites e Pinnularia. A capa da dissertação traz 2006; o registro de catalogação, 2005. Relação com o registro nº 180: ambos vêm do afloramento Bruno Peiker, mas a equivalência entre esta «nova forma» (2006) e Paragiridia taioensis (2016) não foi verificada nas fontes consultadas.</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
@@ -16066,7 +16066,7 @@
         </is>
       </c>
       <c r="N176" s="4" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="O177" s="6" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="N178" s="4" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="O179" s="6" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="N180" s="4" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="O181" s="6" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="N182" s="4" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="O183" s="6" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="N184" s="4" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="O185" s="6" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         </is>
       </c>
       <c r="N186" s="4" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="O187" s="6" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         </is>
       </c>
       <c r="N188" s="4" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="O189" s="6" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="K190" s="5" t="inlineStr">
         <is>
-          <t>Classificação: lenho fóssil de gimnosperma, táxon novo (gênero e espécie descritos no artigo). Segundo o resumo, o estudo é morfoanatômico de uma tafoflora da Fm. Rio Bonito em Pouso Redondo (SC) que forneceu novos gêneros de gimnospermas; este lenho aparece em 9 das 25 amostras (36%), a segunda forma mais representada. A autora o compara a Megaporoxylon Kräusel, 1956 (medula sólida heterocelular, diferenciação vascular primária centrífuga, grandes pontoações nos campos de cruzamento), mas o sistema secretor, o contorno da medula e a configuração das pontoações areoladas das paredes radiais a levaram a criar o gênero novo. NOTA DE FONTE (2026.10.09): só a página do artigo (resumo) foi lida; o PDF não pôde ser obtido, de modo que afloramento, número de tombo, depositário e etimologia não foram verificados. O ponto do mapa é a sede de Pouso Redondo (Wikipédia), não o afloramento. Registro irmão: nº 259 (contramolde medular do mesmo material/município).</t>
+          <t>Classificação: lenho fóssil de gimnosperma, táxon novo (gênero e espécie descritos no artigo). Segundo o resumo, o estudo é morfoanatômico de uma tafoflora da Fm. Rio Bonito em Pouso Redondo (SC) que forneceu novos gêneros de gimnospermas; este lenho aparece em 9 das 25 amostras (36%), a segunda forma mais representada. A autora o compara a Megaporoxylon Kräusel, 1956 (medula sólida heterocelular, diferenciação vascular primária centrífuga, grandes pontoações nos campos de cruzamento), mas o sistema secretor, o contorno da medula e a configuração das pontoações areoladas das paredes radiais a levaram a criar o gênero novo. NOTA DE FONTE (2026.10.09): só a página do artigo (resumo) foi lida; o PDF não pôde ser obtido, de modo que afloramento, número de tombo, depositário e etimologia não foram verificados. O ponto do mapa é a sede de Pouso Redondo (Wikipédia), não o afloramento. Registro irmão: nº 250 (contramolde medular do mesmo material/município).</t>
         </is>
       </c>
       <c r="L190" s="5" t="inlineStr">
@@ -17305,7 +17305,7 @@
         </is>
       </c>
       <c r="N190" s="4" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="K191" s="7" t="inlineStr">
         <is>
-          <t>Classificação: lenho fóssil de gimnosperma com contramolde medular («pith cast») em conexão orgânica. Segundo o resumo, o contramolde é cilíndrico e muito silicoso, sem impressões diagnósticas, e está ligado a um fragmento lenhoso semicilíndrico, sem xilema primário e com xilema secundário de sistemas axial e radial pouco definidos. A anatomia associa o fragmento ao gênero mais representativo da assembleia (o título nomeia Retemedulloxylon; o resumo não dá a espécie). A autora propõe que fatores ambientais expliquem a ocorrência desses contramoldes nos sedimentos gondwânicos. NOTA DE FONTE (2026.10.09): só o resumo foi lido; afloramento, tombo e depositário não verificados. Ponto do mapa = sede de Pouso Redondo. Registro irmão: nº 258.</t>
+          <t>Classificação: lenho fóssil de gimnosperma com contramolde medular («pith cast») em conexão orgânica. Segundo o resumo, o contramolde é cilíndrico e muito silicoso, sem impressões diagnósticas, e está ligado a um fragmento lenhoso semicilíndrico, sem xilema primário e com xilema secundário de sistemas axial e radial pouco definidos. A anatomia associa o fragmento ao gênero mais representativo da assembleia (o título nomeia Retemedulloxylon; o resumo não dá a espécie). A autora propõe que fatores ambientais expliquem a ocorrência desses contramoldes nos sedimentos gondwânicos. NOTA DE FONTE (2026.10.09): só o resumo foi lido; afloramento, tombo e depositário não verificados. Ponto do mapa = sede de Pouso Redondo. Registro irmão: nº 249.</t>
         </is>
       </c>
       <c r="L191" s="7" t="inlineStr">
@@ -17397,7 +17397,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="O191" s="6" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="N192" s="4" t="n">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="O193" s="6" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="K194" s="5" t="inlineStr">
         <is>
-          <t>Licófita citada por Bernardes-de-Oliveira et al. (2016) como elemento endêmico do pântano de Treviso. HISTÓRICO TAXONÔMICO: Read (1941), segundo esse artigo, listou a licófita do carvão de Treviso como Lepidodendron pedroanum (Carruthers) Zeiller, junto com Lepidostrobus sp. e glossopterídeas (Glossopteris cf. G. ampla e G. indica); o nome hoje usado é Brasilodendron pedroanum (Carruthers) Chaloner, Leistikow &amp; Hill. O artigo de 2016 diz ter incluído essa associação na camada Irapuá, mas aceitar a posição de Putzer (1952), de que ela pertence a Treviso. O mesmo nome consta em Mina Bonito I (registro nº 229), outro afloramento da bacia carbonífera. O afloramento fica na margem do rio Ferreira, município de Treviso, e o horizonte é siltoso-argiloso, associado à camada de carvão Treviso, a mais alta das cinco camadas do Mb. Siderópolis (Putzer, 1952, segundo Bernardes-de-Oliveira et al., 2016). Esses autores afirmam que as licófitas formam, nesse afloramento, uma associação quase exclusiva e tratam Brasilodendron pedroanum e Cyclodendron brasiliense como elementos endêmicos do pântano de Treviso, junto com glossopterídeas alóctones raras. O artigo não dá mina, perfil nem coordenada. RESSALVA DE COORDENADA: ponto = sede do município de Treviso (aproximado). NOTA DE FONTE (2026.10.14): o artigo de 2016 foi lido por ferramenta de leitura automática; as obras de 1979 e de Read (1941) não foram consultadas.</t>
+          <t>Licófita citada por Bernardes-de-Oliveira et al. (2016) como elemento endêmico do pântano de Treviso. HISTÓRICO TAXONÔMICO: Read (1941), segundo esse artigo, listou a licófita do carvão de Treviso como Lepidodendron pedroanum (Carruthers) Zeiller, junto com Lepidostrobus sp. e glossopterídeas (Glossopteris cf. G. ampla e G. indica); o nome hoje usado é Brasilodendron pedroanum (Carruthers) Chaloner, Leistikow &amp; Hill. O artigo de 2016 diz ter incluído essa associação na camada Irapuá, mas aceitar a posição de Putzer (1952), de que ela pertence a Treviso. O mesmo nome consta em Mina Bonito I (registro nº 220), outro afloramento da bacia carbonífera. O afloramento fica na margem do rio Ferreira, município de Treviso, e o horizonte é siltoso-argiloso, associado à camada de carvão Treviso, a mais alta das cinco camadas do Mb. Siderópolis (Putzer, 1952, segundo Bernardes-de-Oliveira et al., 2016). Esses autores afirmam que as licófitas formam, nesse afloramento, uma associação quase exclusiva e tratam Brasilodendron pedroanum e Cyclodendron brasiliense como elementos endêmicos do pântano de Treviso, junto com glossopterídeas alóctones raras. O artigo não dá mina, perfil nem coordenada. RESSALVA DE COORDENADA: ponto = sede do município de Treviso (aproximado). NOTA DE FONTE (2026.10.14): o artigo de 2016 foi lido por ferramenta de leitura automática; as obras de 1979 e de Read (1941) não foram consultadas.</t>
         </is>
       </c>
       <c r="L194" s="5" t="inlineStr">
@@ -17674,7 +17674,7 @@
         </is>
       </c>
       <c r="N194" s="4" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="O195" s="6" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="K196" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). Grafia da tabela de 2016: griesbachi (o registro nº 103 usa griesbachii). O mesmo táxon consta no banco no registro nº 103 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). Grafia da tabela de 2016: griesbachi (o registro nº 95 usa griesbachii). O mesmo táxon consta no banco no registro nº 95 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L196" s="5" t="inlineStr">
@@ -17858,7 +17858,7 @@
         </is>
       </c>
       <c r="N196" s="4" t="n">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). O mesmo táxon consta no banco no registro nº 33 (Irineópolis (região)). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). O mesmo táxon consta no banco no registro nº 30 (Irineópolis (região)). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="O197" s="6" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II. O mesmo táxon consta no banco no registro nº 105 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II. O mesmo táxon consta no banco no registro nº 97 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L198" s="5" t="inlineStr">
@@ -18042,7 +18042,7 @@
         </is>
       </c>
       <c r="N198" s="4" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II. O mesmo táxon consta no banco no registro nº 110 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II. O mesmo táxon consta no banco no registro nº 102 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
@@ -18134,7 +18134,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="O199" s="6" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 121 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 113 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L200" s="5" t="inlineStr">
@@ -18226,7 +18226,7 @@
         </is>
       </c>
       <c r="N200" s="4" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 32 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 29 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="N201" s="6" t="n">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="O201" s="6" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
       </c>
       <c r="K202" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 126 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 118 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L202" s="5" t="inlineStr">
@@ -18410,7 +18410,7 @@
         </is>
       </c>
       <c r="N202" s="4" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="N203" s="6" t="n">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="O203" s="6" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="K204" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): II. O mesmo táxon consta no banco no registro nº 124 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): II. O mesmo táxon consta no banco no registro nº 116 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L204" s="5" t="inlineStr">
@@ -18594,7 +18594,7 @@
         </is>
       </c>
       <c r="N204" s="4" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 125 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 117 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="N205" s="6" t="n">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="O205" s="6" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III. Raiz/rizoma de glossopteridófita. O mesmo táxon consta no banco no registro nº 193 (Siderópolis (região)). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III. Raiz/rizoma de glossopteridófita. O mesmo táxon consta no banco no registro nº 184 (Siderópolis (região)). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="N206" s="4" t="n">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="K207" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 114 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). O mesmo táxon consta no banco no registro nº 106 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L207" s="7" t="inlineStr">
@@ -18870,7 +18870,7 @@
         </is>
       </c>
       <c r="N207" s="6" t="n">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="O207" s="6" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="N208" s="4" t="n">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="K209" s="7" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). Em Criciúma o banco registra N. hislopii (registro nº 142), não esta espécie. Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»), II, III, BB (estrada Lauro Müller–Barro Branco). Em Criciúma o banco registra N. hislopii (registro nº 134), não esta espécie. Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L209" s="7" t="inlineStr">
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N209" s="6" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="O209" s="6" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         </is>
       </c>
       <c r="N210" s="4" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         </is>
       </c>
       <c r="N211" s="6" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="O211" s="6" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         </is>
       </c>
       <c r="N212" s="4" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="N213" s="6" t="n">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="O213" s="6" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). Grafia da tabela de 2016: mendesi (o registro nº 147 usa mendesii). O mesmo táxon consta no banco no registro nº 147 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
+          <t>Ocorrência da paleoflora do Mb. Siderópolis em Lauro Müller (porção norte da região carbonífera de Santa Catarina), conforme a Tabela 1 de Bernardes-de-Oliveira et al. (2016), que reproduz a lista de Rigby (1972a). Consta no(s) horizonte(s): I (camada Barro Branco, «I ou Joaquim Branco»). Grafia da tabela de 2016: mendesi (o registro nº 139 usa mendesii). O mesmo táxon consta no banco no registro nº 139 (Criciúma). Os horizontes I a III, já estudados por White (1908a), estariam «provavelmente» associados às camadas Barro Branco e Bonito (Putzer, 1952); o horizonte BB, na estrada Lauro Müller–Barro Branco, é tratado como possivelmente mais antigo que a camada Bonito (a tabela traz «?»). O texto não nomeia minas nem dá números de tombo; a coleção de Rigby está depositada na Universidade de São Paulo. RESSALVA DE COORDENADA: ponto = sede de Lauro Müller (aproximado). NOTA DE FONTE (2026.10.14): a tabela foi lida por ferramenta de leitura automática do PDF, em duas leituras independentes que concordaram; Rigby (1972a) não foi consultado.</t>
         </is>
       </c>
       <c r="L214" s="5" t="inlineStr">
@@ -19514,7 +19514,7 @@
         </is>
       </c>
       <c r="N214" s="4" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         </is>
       </c>
       <c r="N215" s="6" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="O215" s="6" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         </is>
       </c>
       <c r="N216" s="4" t="n">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         </is>
       </c>
       <c r="N217" s="6" t="n">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="O217" s="6" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         </is>
       </c>
       <c r="N218" s="4" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
-          <t>Localidade-tipo e, até 2024, ÚNICA localidade conhecida do gênero em toda a Bacia do Paraná (nova ocorrência, em identificação preliminar, em Major Vieira — registro nº 195), e única conífera formalmente conhecida do Guadalupiano da porção gondwânica brasileira. Ramos estéreis com quatro ordens de ramificação, cutícula excepcionalmente preservada — o que permitiu análise anatômica da epiderme. Cutículas grossas, estômatos afundados e ductos resiníferos são adaptações xeromórficas, coerentes com o clima seco interpretado para a Fm. Teresina. Fanton et al. (2006) sinonimizaram K. catarinensis Yoshida em K. canoinhensis. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
+          <t>Localidade-tipo e, até 2024, ÚNICA localidade conhecida do gênero em toda a Bacia do Paraná (nova ocorrência, em identificação preliminar, em Major Vieira — registro nº 186), e única conífera formalmente conhecida do Guadalupiano da porção gondwânica brasileira. Ramos estéreis com quatro ordens de ramificação, cutícula excepcionalmente preservada — o que permitiu análise anatômica da epiderme. Cutículas grossas, estômatos afundados e ductos resiníferos são adaptações xeromórficas, coerentes com o clima seco interpretado para a Fm. Teresina. Fanton et al. (2006) sinonimizaram K. catarinensis Yoshida em K. canoinhensis. Afloramento de Canoinhas — sítio SIGEP 126, no km 242 da BR-280, 6 km a sudoeste de Canoinhas. Expõe 40 m da porção superior da Fm. Teresina, reunindo numa única localidade um conjunto de litofácies que raramente aparece junto. Registra a aridização gradual do Gondwana ocidental a partir do fim do Eopermiano. RISCO: o depósito fica no acostamento da rodovia e já foi parcialmente recoberto por obras; os autores do capítulo SIGEP pedem medidas de proteção.</t>
         </is>
       </c>
       <c r="L219" s="7" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="N219" s="6" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O219" s="6" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
       <c r="N220" s="4" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="N221" s="6" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O221" s="6" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         </is>
       </c>
       <c r="N222" s="4" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="O222" s="4" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="N223" s="6" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O223" s="6" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="N224" s="4" t="n">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="O224" s="4" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         </is>
       </c>
       <c r="N225" s="6" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O225" s="6" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         </is>
       </c>
       <c r="N226" s="4" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O226" s="4" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         </is>
       </c>
       <c r="N227" s="6" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O227" s="6" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         </is>
       </c>
       <c r="N228" s="4" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="O228" s="4" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         </is>
       </c>
       <c r="N229" s="6" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O229" s="6" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         </is>
       </c>
       <c r="N230" s="4" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="O230" s="4" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="N231" s="6" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="O231" s="6" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Não informada na reportagem (ocorrência-tipo do gênero: Fm. Teresina, Canoinhas — registro 159)</t>
+          <t>Não informada na reportagem (ocorrência-tipo do gênero: Fm. Teresina, Canoinhas — registro 151)</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="K232" s="5" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre esta ocorrência. Segundo o Notisul (22/08/2024), o fóssil foi descoberto em 1º de maio de 2024 por dois participantes de uma caminhada religiosa no interior de Major Vieira e identificado como Krauselcladus canoinhensis ('planta aparentada das atuais araucárias') pelo centro de pesquisa da Universidade do Contestado A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, sem exame direto do material documentado na reportagem; a idade de 270 milhões de anos é a da reportagem. A reportagem não informa localidade precisa, nome de quem identificou, tombo nem depositário. Se confirmada, seria uma segunda localidade do gênero, descrito no Afloramento de Canoinhas (SIGEP 126; registro 159).</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica sobre esta ocorrência. Segundo o Notisul (22/08/2024), o fóssil foi descoberto em 1º de maio de 2024 por dois participantes de uma caminhada religiosa no interior de Major Vieira e identificado como Krauselcladus canoinhensis ('planta aparentada das atuais araucárias') pelo centro de pesquisa da Universidade do Contestado A PARTIR DE FOTOS E VÍDEOS enviados pelos descobridores, sem exame direto do material documentado na reportagem; a idade de 270 milhões de anos é a da reportagem. A reportagem não informa localidade precisa, nome de quem identificou, tombo nem depositário. Se confirmada, seria uma segunda localidade do gênero, descrito no Afloramento de Canoinhas (SIGEP 126; registro 151).</t>
         </is>
       </c>
       <c r="L232" s="5" t="inlineStr">
@@ -21112,7 +21112,7 @@
         </is>
       </c>
       <c r="N232" s="4" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         </is>
       </c>
       <c r="N233" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O233" s="6" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
       </c>
       <c r="K234" s="5" t="inlineStr">
         <is>
-          <t>CITAÇÃO EM REVISÃO — o material original não foi examinado por este banco. Classificação: crustáceos filópodes (conchostráceos) permianos, que Maack (resumo de pesquisas até 1947) atribui a F.R. Cowper Reed: entre Valões e Poço Preto ocorrem horizontes vermelhos, argilosos e finamente laminados do Rio do Rasto, onde Reed descreveu «Estheria» e «Leaia»; o autor ressalva que esses horizontes não pertencem às camadas Estrada Nova, e informa que a base dos arenitos argilosos vermelhos sobrejacentes (correlacionados à fácies Pirambóia de São Paulo) fica cerca de um metro acima das camadas com Estheria. VERIFICAÇÃO E CORREÇÃO (2026.10.09): a ficha atribuía o texto a «Beurlen» e punha o ponto em Lages; a autoria é de Reinhard Maack, e «Lajes» no texto aparece só como destino da estrada Lomba Alta–Lajes e como outra área descrita. O par «Valões e Poço Preto» coincide com a localidade do material original de Reed (1929): Ferreira-Oliveira &amp; Rohn (2008, texto integral) o descrevem como «folhelhos vermelhos do Rio Iguassú, na povoação de Vallões» (sic), que situam na BR-280 perto de Poço Preto (ver registros nº 185 e 186). Por isso o ponto foi movido para a região de Poço Preto. A relação dos «Estheria/Leaia» de Reed com a espécie Palaeolimnadiopsis subalata (Reed, 1929) não foi verificada nesta revisão. A data original do texto de Maack não consta na página consultada (a página diz apenas que o levantamento cobre pesquisas até 1947); a obra de Reed (1929) não foi consultada diretamente.</t>
+          <t>CITAÇÃO EM REVISÃO — o material original não foi examinado por este banco. Classificação: crustáceos filópodes (conchostráceos) permianos, que Maack (resumo de pesquisas até 1947) atribui a F.R. Cowper Reed: entre Valões e Poço Preto ocorrem horizontes vermelhos, argilosos e finamente laminados do Rio do Rasto, onde Reed descreveu «Estheria» e «Leaia»; o autor ressalva que esses horizontes não pertencem às camadas Estrada Nova, e informa que a base dos arenitos argilosos vermelhos sobrejacentes (correlacionados à fácies Pirambóia de São Paulo) fica cerca de um metro acima das camadas com Estheria. VERIFICAÇÃO E CORREÇÃO (2026.10.09): a ficha atribuía o texto a «Beurlen» e punha o ponto em Lages; a autoria é de Reinhard Maack, e «Lajes» no texto aparece só como destino da estrada Lomba Alta–Lajes e como outra área descrita. O par «Valões e Poço Preto» coincide com a localidade do material original de Reed (1929): Ferreira-Oliveira &amp; Rohn (2008, texto integral) o descrevem como «folhelhos vermelhos do Rio Iguassú, na povoação de Vallões» (sic), que situam na BR-280 perto de Poço Preto (ver registros nº 176 e 177). Por isso o ponto foi movido para a região de Poço Preto. A relação dos «Estheria/Leaia» de Reed com a espécie Palaeolimnadiopsis subalata (Reed, 1929) não foi verificada nesta revisão. A data original do texto de Maack não consta na página consultada (a página diz apenas que o levantamento cobre pesquisas até 1947); a obra de Reed (1929) não foi consultada diretamente.</t>
         </is>
       </c>
       <c r="L234" s="5" t="inlineStr">
@@ -21294,7 +21294,7 @@
         </is>
       </c>
       <c r="N234" s="4" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="O234" s="4" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         </is>
       </c>
       <c r="N235" s="6" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O235" s="6" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         </is>
       </c>
       <c r="N236" s="4" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="O237" s="6" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         </is>
       </c>
       <c r="N238" s="4" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="O239" s="6" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         </is>
       </c>
       <c r="N240" s="4" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="O241" s="6" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         </is>
       </c>
       <c r="N242" s="4" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="K243" s="7" t="inlineStr">
         <is>
-          <t>Espécie de carapaça subelíptica, com umbo pequeno e subanterior. Define a Subzona Palaeolimnadiopsis subalata, uma das biozonas de conchostráceos da Fm. Rio do Rasto. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO E HISTÓRICO TAXONÔMICO (2026.10.09, texto integral de Ferreira-Oliveira &amp; Rohn, 2008): o holótipo (DNPM 1420 A) vem de Poço Preto, SC, na BR-280; o material original foi descrito por Reed (1929) de «folhelhos vermelhos do Rio Iguassú, na povoação de Vallões» (sic), que os autores situam na BR-280 perto de Poço Preto. Até 2008 todos os conchostráceos de linhas de crescimento recurvadas da Fm. Rio do Rasto eram atribuídos a P. subalata; Ferreira-Oliveira &amp; Rohn (2008) mantêm o nome para as formas subelípticas de umbo pequeno e anterior e separam outras duas espécies: P. riorastensis (subcircular; tipos no Paraná) e Falsisca brasiliensis (registro nº 186). CONTEXTO CIENTÍFICO: Rohn (1987, Boletim IG-USP, Série Científica 18:27–66, DOI 10.11606/issn.2316-8986.v18i0p27-66) trata conchostráceos de 67 afloramentos da Fm. Rio do Rasto no Paraná e no norte de SC.</t>
+          <t>Espécie de carapaça subelíptica, com umbo pequeno e subanterior. Define a Subzona Palaeolimnadiopsis subalata, uma das biozonas de conchostráceos da Fm. Rio do Rasto. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO E HISTÓRICO TAXONÔMICO (2026.10.09, texto integral de Ferreira-Oliveira &amp; Rohn, 2008): o holótipo (DNPM 1420 A) vem de Poço Preto, SC, na BR-280; o material original foi descrito por Reed (1929) de «folhelhos vermelhos do Rio Iguassú, na povoação de Vallões» (sic), que os autores situam na BR-280 perto de Poço Preto. Até 2008 todos os conchostráceos de linhas de crescimento recurvadas da Fm. Rio do Rasto eram atribuídos a P. subalata; Ferreira-Oliveira &amp; Rohn (2008) mantêm o nome para as formas subelípticas de umbo pequeno e anterior e separam outras duas espécies: P. riorastensis (subcircular; tipos no Paraná) e Falsisca brasiliensis (registro nº 177). CONTEXTO CIENTÍFICO: Rohn (1987, Boletim IG-USP, Série Científica 18:27–66, DOI 10.11606/issn.2316-8986.v18i0p27-66) trata conchostráceos de 67 afloramentos da Fm. Rio do Rasto no Paraná e no norte de SC.</t>
         </is>
       </c>
       <c r="L243" s="7" t="inlineStr">
@@ -22083,7 +22083,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O243" s="6" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="N244" s="4" t="n">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="K245" s="7" t="inlineStr">
         <is>
-          <t>Define a zona "Monoleaia unicostata" na bioestratigrafia da formação. Os leaiídeos ocorrem quase até o topo da unidade e constituem forte evidência cronoestratigráfica de idade não mais jovem que o Permiano. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO (2026.10.09, texto integral de Rohn, 1987, lido por OCR): o único afloramento catarinense do estudo (AF/GP 163 no PDF; 183 em Rohn &amp; Rösler, 1986 — mesmo local, estrada Poço Preto–Porto União) tem a subespécie Monoleaia unicostata timbensis (registro nº 263); a ocorrência de «Monoleiolophus unicostatus» em SC não foi confirmada nessa leitura, e a equivalência entre os dois nomes não foi verificada. Ponto do mapa = referência regional.</t>
+          <t>Define a zona "Monoleaia unicostata" na bioestratigrafia da formação. Os leaiídeos ocorrem quase até o topo da unidade e constituem forte evidência cronoestratigráfica de idade não mais jovem que o Permiano. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO (2026.10.09, texto integral de Rohn, 1987, lido por OCR): o único afloramento catarinense do estudo (AF/GP 163 no PDF; 183 em Rohn &amp; Rösler, 1986 — mesmo local, estrada Poço Preto–Porto União) tem a subespécie Monoleaia unicostata timbensis (registro nº 254); a ocorrência de «Monoleiolophus unicostatus» em SC não foi confirmada nessa leitura, e a equivalência entre os dois nomes não foi verificada. Ponto do mapa = referência regional.</t>
         </is>
       </c>
       <c r="L245" s="7" t="inlineStr">
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="O245" s="6" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="K246" s="5" t="inlineStr">
         <is>
-          <t>Um dos táxons considerados válidos na revisão de Ferreira-Oliveira (2007) para a Fm. Rio do Rasto. A espécie foi originalmente registrada no Tatariano superior (Wuchiapingiano) da Bacia de Sydney, Austrália — correlação que reforça a idade permiana dos estratos portadores. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO (2026.10.09, texto integral de Rohn, 1987, lido por OCR): o nome Hemicycloleaia mitchelli não foi encontrado nessa leitura, e o único afloramento catarinense do estudo (estrada Poço Preto–Porto União) lista outra espécie (registro nº 263). A ocorrência desta espécie em SC NÃO está confirmada; o registro é mantido com a ressalva até se achar a fonte da atribuição (a ficha cita Ferreira-Oliveira, 2007, que não foi consultada). Ponto do mapa = referência regional.</t>
+          <t>Um dos táxons considerados válidos na revisão de Ferreira-Oliveira (2007) para a Fm. Rio do Rasto. A espécie foi originalmente registrada no Tatariano superior (Wuchiapingiano) da Bacia de Sydney, Austrália — correlação que reforça a idade permiana dos estratos portadores. A Fm. Rio do Rasto tem nos conchostráceos seus fósseis mais abundantes: 13 espécies reconhecidas e ocorrências em pelo menos 192 afloramentos. Indicam água de baixa salinidade e sustentam a interpretação de clima relativamente seco no Neopermiano da Bacia do Paraná. VERIFICAÇÃO (2026.10.09, texto integral de Rohn, 1987, lido por OCR): o nome Hemicycloleaia mitchelli não foi encontrado nessa leitura, e o único afloramento catarinense do estudo (estrada Poço Preto–Porto União) lista outra espécie (registro nº 254). A ocorrência desta espécie em SC NÃO está confirmada; o registro é mantido com a ressalva até se achar a fonte da atribuição (a ficha cita Ferreira-Oliveira, 2007, que não foi consultada). Ponto do mapa = referência regional.</t>
         </is>
       </c>
       <c r="L246" s="5" t="inlineStr">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="N246" s="4" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
       </c>
       <c r="K247" s="7" t="inlineStr">
         <is>
-          <t>Classificação: impressões vegetais; a fonte lista no afloramento «Glossopteris indeterminada; outros fósseis: Paracalamites sp. 2». VERIFICAÇÃO (2026.10.09, texto integral de Rohn &amp; Rösler, 1989, lido por OCR): dos 20 afloramentos novos do estudo, só o AF/GP 282 fica em SC; os outros 19 estão no Paraná, e as dez espécies descritas (G. riorastensis, G. grafi, G. cf. indica, G. cf. surangei etc.) vêm de afloramentos paranaenses. As antigas fichas nº 34–36 atribuíam essas espécies a SC («Mafra (região)») e foram retiradas por isso (ver CHANGELOG 2026.10.09). LOCALIZAÇÃO: o artigo dá só «BR 470, aproximadamente km 207,5, SC». Boos (2016, p. 28) situa um ponto «na BR 470, km 207, próximo à cidade de Otacílio Costa»; a identidade entre os dois pontos (km 207,5 e km 207) é aproximação do compilador. Município e coordenadas não constam no artigo.</t>
+          <t>Classificação: impressões vegetais; a fonte lista no afloramento «Glossopteris indeterminada; outros fósseis: Paracalamites sp. 2». VERIFICAÇÃO (2026.10.09, texto integral de Rohn &amp; Rösler, 1989, lido por OCR): dos 20 afloramentos novos do estudo, só o AF/GP 282 fica em SC; os outros 19 estão no Paraná, e as dez espécies descritas (G. riorastensis, G. grafi, G. cf. indica, G. cf. surangei etc.) vêm de afloramentos paranaenses. As antigas fichas de Glossopteris riorastensis, G. grafi e G. cf. indica/surangei (nº 34–36 na numeração anterior a 15/10/2026) atribuíam essas espécies a SC («Mafra (região)») e foram retiradas por isso (ver CHANGELOG 2026.10.09). LOCALIZAÇÃO: o artigo dá só «BR 470, aproximadamente km 207,5, SC». Boos (2016, p. 28) situa um ponto «na BR 470, km 207, próximo à cidade de Otacílio Costa»; a identidade entre os dois pontos (km 207,5 e km 207) é aproximação do compilador. Município e coordenadas não constam no artigo.</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr">
@@ -22442,7 +22442,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="O247" s="6" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="K248" s="5" t="inlineStr">
         <is>
-          <t>Classificação: crânio de temnospôndilo (anfíbio) da Fm. Rio do Rasto. A tese, ao descrever as saídas de campo em SC (seção 4.2.2, p. 28), diz que há duas localidades de destaque: uma na Serra do Espigão (de onde provém Parapytanga catarinensis, registro nº 176) e outra «na BR 470, km 207, próximo à cidade de Otacílio Costa, de onde se conhece um crânio de temnospôndilo ainda não descrito formalmente, mas depositado no Laboratório de Geociências da FURB». A tese não informa número de tombo nem quem coletou, e não liga o crânio à expedição da própria autora. A mesma tese registra que o material coletado nas campanhas em Monte Castelo, Santa Cecília, Otacílio Costa e Lages foi, basicamente, de invertebrados e restos de plantas. NOTA DE FONTE (2026.10.09): a identificação do táxon não vai além de Temnospondyli; o registro não é uma descrição formal. Pode se tratar do mesmo ponto do registro nº 261 (BR-470, km 207,5), o que não foi confirmado.</t>
+          <t>Classificação: crânio de temnospôndilo (anfíbio) da Fm. Rio do Rasto. A tese, ao descrever as saídas de campo em SC (seção 4.2.2, p. 28), diz que há duas localidades de destaque: uma na Serra do Espigão (de onde provém Parapytanga catarinensis, registro nº 168) e outra «na BR 470, km 207, próximo à cidade de Otacílio Costa, de onde se conhece um crânio de temnospôndilo ainda não descrito formalmente, mas depositado no Laboratório de Geociências da FURB». A tese não informa número de tombo nem quem coletou, e não liga o crânio à expedição da própria autora. A mesma tese registra que o material coletado nas campanhas em Monte Castelo, Santa Cecília, Otacílio Costa e Lages foi, basicamente, de invertebrados e restos de plantas. NOTA DE FONTE (2026.10.09): a identificação do táxon não vai além de Temnospondyli; o registro não é uma descrição formal. Pode se tratar do mesmo ponto do registro nº 252 (BR-470, km 207,5), o que não foi confirmado.</t>
         </is>
       </c>
       <c r="L248" s="5" t="inlineStr">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="N248" s="4" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="O249" s="6" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
-          <t>Classificação: peixe sarcopterígio da subclasse Actinistia (celacantos). O material são TRÊS ESCAMAS ISOLADAS E INCOMPLETAS, coletadas em 2002 por F. Sedor e R. C. Silva: MCN.P.1197 (molde parcialmente quebrado, ~26 mm de comprimento e ~11 mm de largura, campo exposto de ~4 mm, cerca de 20 cristas muito próximas), MCN.P.1198 (fragmento espesso, ~10 mm de largura, ornamentado só na margem posterior) e MCN.P.1199 (fragmento de 15 × 3,5 mm com fibras de colágeno mineralizadas em padrão de zigue-zague, como as de Latimeria e de uma escama triássica de actinístio). Os autores atribuem as escamas a Actinistia pelo padrão de ornamentação (numerosas linhas de crescimento finas e paralelas, diferentes das linhas de Westoll dos dipnoicos), mas NÃO chegam a gênero ou espécie, por falta de caracteres diagnósticos. Interpretam as ocorrências do Rio do Rasto como de afinidade dulciaquícola, pelo ambiente deposicional e pela biota associada (conchostráceos de água doce). Os autores registram que os celacantos do Lopingiano são escassos no mundo. LOCALIDADE: o artigo publica as coordenadas da Serra do Espigão, mas não nomeia município nem afloramento; o município (Monte Castelo) foi derivado pela coordenada publicada e pela malha municipal do site. A mesma serra é a localidade de Parapytanga catarinensis (registro nº 176, cuja coordenada no site é aproximada, em Santa Cecília); não se afirma que seja o mesmo afloramento. DIVERGÊNCIA DE FONTE SECUNDÁRIA: o material suplementar de Francischini et al. (sobre um tubo de estivação de dipnoico do Rio do Rasto; periódico e ano não confirmados nesta revisão) lista este achado como «Acnistia indet.» e no Membro Morro Pelado; o artigo original traz «Actinistia indet.» e não especifica o membro. Este registro segue o artigo original. NOTA DE FONTE (2026.10.14): o PDF do artigo (aberto no site da SBP) foi lido por ferramenta de leitura automática; conferir medidas e tombos no original.</t>
+          <t>Classificação: peixe sarcopterígio da subclasse Actinistia (celacantos). O material são TRÊS ESCAMAS ISOLADAS E INCOMPLETAS, coletadas em 2002 por F. Sedor e R. C. Silva: MCN.P.1197 (molde parcialmente quebrado, ~26 mm de comprimento e ~11 mm de largura, campo exposto de ~4 mm, cerca de 20 cristas muito próximas), MCN.P.1198 (fragmento espesso, ~10 mm de largura, ornamentado só na margem posterior) e MCN.P.1199 (fragmento de 15 × 3,5 mm com fibras de colágeno mineralizadas em padrão de zigue-zague, como as de Latimeria e de uma escama triássica de actinístio). Os autores atribuem as escamas a Actinistia pelo padrão de ornamentação (numerosas linhas de crescimento finas e paralelas, diferentes das linhas de Westoll dos dipnoicos), mas NÃO chegam a gênero ou espécie, por falta de caracteres diagnósticos. Interpretam as ocorrências do Rio do Rasto como de afinidade dulciaquícola, pelo ambiente deposicional e pela biota associada (conchostráceos de água doce). Os autores registram que os celacantos do Lopingiano são escassos no mundo. LOCALIDADE: o artigo publica as coordenadas da Serra do Espigão, mas não nomeia município nem afloramento; o município (Monte Castelo) foi derivado pela coordenada publicada e pela malha municipal do site. A mesma serra é a localidade de Parapytanga catarinensis (registro nº 168, cuja coordenada no site é aproximada, em Santa Cecília); não se afirma que seja o mesmo afloramento. DIVERGÊNCIA DE FONTE SECUNDÁRIA: o material suplementar de Francischini et al. (sobre um tubo de estivação de dipnoico do Rio do Rasto; periódico e ano não confirmados nesta revisão) lista este achado como «Acnistia indet.» e no Membro Morro Pelado; o artigo original traz «Actinistia indet.» e não especifica o membro. Este registro segue o artigo original. NOTA DE FONTE (2026.10.14): o PDF do artigo (aberto no site da SBP) foi lido por ferramenta de leitura automática; conferir medidas e tombos no original.</t>
         </is>
       </c>
       <c r="L250" s="5" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="N250" s="4" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="K251" s="7" t="inlineStr">
         <is>
-          <t>Classificação: peixe actinopterígio («ray-finned fish»), gênero e espécie criados por Richter (2002) a partir de material do Permiano Superior de Santa Catarina; o BioNames lista, como nomes publicados no trabalho, Rubidus e Rubidus pascoalensis. A espécie é citada entre os actinopterígios do Permiano Superior da Bacia do Paraná por Dias (2012, Zootaxa 3192:1–23), e a introdução de um estudo sobre Brazilichthys (bioRxiv, 2019) a lista como componente da Fm. Rio do Rasto (Guadalupiano–Lopingiano). A tabela do material suplementar de Francischini et al. (sobre um tubo de estivação de dipnoico do Rio do Rasto; periódico e ano não confirmados nesta revisão) dá a localidade como «São Pascoal brook» (SC), sem litologia nem membro. COORDENADA: -26,253146; -50,727041, informada pelo autor do site (B. A. Benk) em 14/10/2026 como o local de coleta do peixe de Martha Richter; a associação com o Rubidus pascoalensis foi feita nesta revisão e a coordenada NÃO foi conferida no artigo original. O ponto cai no município de Irineópolis (malha municipal do site), cerca de 8 km a leste do Poço Preto (registros 33, 97, 185, 186 e 263), também Rio do Rasto. RESSALVAS: o artigo de Richter (2002) não pôde ser aberto, então holótipo, número de tombo, instituição depositária, horizonte/membro e descrição anatômica não foram verificados. Volume: BioNames e Wikipédia dão o v. 3 (2002); o material suplementar de Francischini et al. cita v. 2(1) — a conferir.</t>
+          <t>Classificação: peixe actinopterígio («ray-finned fish»), gênero e espécie criados por Richter (2002) a partir de material do Permiano Superior de Santa Catarina; o BioNames lista, como nomes publicados no trabalho, Rubidus e Rubidus pascoalensis. A espécie é citada entre os actinopterígios do Permiano Superior da Bacia do Paraná por Dias (2012, Zootaxa 3192:1–23), e a introdução de um estudo sobre Brazilichthys (bioRxiv, 2019) a lista como componente da Fm. Rio do Rasto (Guadalupiano–Lopingiano). A tabela do material suplementar de Francischini et al. (sobre um tubo de estivação de dipnoico do Rio do Rasto; periódico e ano não confirmados nesta revisão) dá a localidade como «São Pascoal brook» (SC), sem litologia nem membro. COORDENADA: -26,253146; -50,727041, informada pelo autor do site (B. A. Benk) em 14/10/2026 como o local de coleta do peixe de Martha Richter; a associação com o Rubidus pascoalensis foi feita nesta revisão e a coordenada NÃO foi conferida no artigo original. O ponto cai no município de Irineópolis (malha municipal do site), cerca de 8 km a leste do Poço Preto (registros 30, 89, 176, 177 e 254), também Rio do Rasto. RESSALVAS: o artigo de Richter (2002) não pôde ser aberto, então holótipo, número de tombo, instituição depositária, horizonte/membro e descrição anatômica não foram verificados. Volume: BioNames e Wikipédia dão o v. 3 (2002); o material suplementar de Francischini et al. cita v. 2(1) — a conferir.</t>
         </is>
       </c>
       <c r="L251" s="7" t="inlineStr">
@@ -22802,7 +22802,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O251" s="6" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica que descreva estas pegadas. A reportagem (ND Mais, 2023), com o paleontólogo L.C. Weinschütz (coordenador do CENPALEO/UnC) como fonte, diz que em Santa Catarina 'ainda não encontramos ossos fossilizados de dinossauros, mas já encontramos algumas pegadas', de terópodes bípedes 'não muito grande (+/-1,7m)' e 'provavelmente do grupo Carnosauria', 'principalmente no litoral sul do estado', e situa as ocorrências do Estado no Jurássico. Não informa formação, município, depósito, número de tombo nem datação, e não diz explicitamente que Weinschütz tenha estudado essas pegadas. Os campos de formação e bacia NÃO constam na reportagem. HISTÓRICO DE CORREÇÃO: versões anteriores deste banco atribuíam o registro à Fm. Botucatu, a 'ca. 150–145 Ma' e ao CENPALEO como depositário — informações que a fonte não traz e foram retiradas. Para pegadas de tetrápodes na Fm. Botucatu em SC com respaldo científico, ver o registro 96 (mamaliaformes, Turvo).</t>
+          <t>CITAÇÃO DE MÍDIA — não foi localizada publicação científica que descreva estas pegadas. A reportagem (ND Mais, 2023), com o paleontólogo L.C. Weinschütz (coordenador do CENPALEO/UnC) como fonte, diz que em Santa Catarina 'ainda não encontramos ossos fossilizados de dinossauros, mas já encontramos algumas pegadas', de terópodes bípedes 'não muito grande (+/-1,7m)' e 'provavelmente do grupo Carnosauria', 'principalmente no litoral sul do estado', e situa as ocorrências do Estado no Jurássico. Não informa formação, município, depósito, número de tombo nem datação, e não diz explicitamente que Weinschütz tenha estudado essas pegadas. Os campos de formação e bacia NÃO constam na reportagem. HISTÓRICO DE CORREÇÃO: versões anteriores deste banco atribuíam o registro à Fm. Botucatu, a 'ca. 150–145 Ma' e ao CENPALEO como depositário — informações que a fonte não traz e foram retiradas. Para pegadas de tetrápodes na Fm. Botucatu em SC com respaldo científico, ver o registro 88 (mamaliaformes, Turvo).</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
@@ -22889,7 +22889,7 @@
         </is>
       </c>
       <c r="N252" s="4" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="O253" s="6" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): a existência de paleotocas no Geoparque tem base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque Caminhos dos Cânions do Sul (2.830 km², sete municípios: Timbé do Sul, Jacinto Machado, Praia Grande e Morro Grande, em SC, e três no RS) e descrevem três delas — duas nas Escarpas da Serra Geral, em Morro Grande (registros nº 268 e 269), e uma no Planalto dos Campos Gerais, em Cambará do Sul/RS (fora do escopo deste banco). Segundo o texto consultado, foram catalogadas 24 paleotocas no Geoparque, a maior parte das feições descritas até agora está em Morro Grande, e a Toca do Tatu (Timbé do Sul, registro nº 82) é tratada com base em Frank et al. (2012). O artigo não individualiza, no texto consultado, cavidades de Praia Grande. Um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. CONTAGENS EM PUBLICAÇÕES (2026.10.09), por trabalho: 17 paleotocas — Bechtel et al. (2023, SINAGEO: 1 no Planalto da Serra Geral, 6 nos Patamares e 10 nas Escarpas; 16 em arenito da Fm. Botucatu e uma em basalto intemperizado, a «paleotoca do Parque»; altitude média de 382 m nas escarpas e de 87,5 m nos patamares) e um resumo da UDESC sem data (Bechtel &amp; Valdati, «Distribuição de paleotocas no território do Geoparque…»: 9 nas Escarpas, 4 nos Patamares, 2 na Planície colúvio-aluvionar e 1 no Planalto); 23 — Bechtel et al. (2023, Anais do Seminário de Pesquisas, vol. 2, p. 27: 1 no Planalto dos Campos Gerais, 9 nas Escarpas e 13 nos Patamares; 22 em Botucatu e uma em basalto; relatos de moradores sugerem que pode haver cerca do dobro) e o resumo da UDESC sem data «Registro da Megafauna do Quaternário…» (pelo menos 20 outras ainda sem visita); 24 — Valdati et al. (2024). O TCC de Bechtel (2022) nomeia só três no Geoparque (Aparência, Parque e Veisom), além de duas em Irineópolis, e cita a Toca do Tatu a partir de Frank et al. (2012). As contagens e as distribuições por compartimento são de épocas e critérios diferentes e não foram conciliadas; nenhuma é desagregada por município. Em Praia Grande, um relatório de iniciação científica da UDESC (Souza &amp; Valdati, sem ano na cópia consultada) descreve o complexo «Furnas do Itamar / Reserva Caeté» (campo em 19–23/03/2024: três paleotocas já conhecidas e oito novas, duas delas crotovinas — 11 feições), sem coordenadas nem dimensões no texto lido (ver registro nº 83). CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural que não traz inventário de paleotocas, registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a Paleotoca Toca do Tatu (registro nº 82) e que o de Praia Grande não cita paleotocas (lista Pedra Branca, Cânion Itaimbezinho e Cânion Malacara); o de Jacinto Machado cita paleotocas ocupadas pelos Laklãnõ-Xokleng (registros nº 81 e 83). CITAÇÃO DE MÍDIA: os números e a localização em Praia Grande e Timbé do Sul, aqui, vêm de reportagens, não de publicação. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. A Revista Oeste (31/03/2026), ao tratar do túnel de Lauro Müller (registro nº 44), diz que o acervo do Geoparque soma cerca de 30 paleotocas registradas em Morro Grande, Jacinto Machado e Timbé do Sul; não informa quantas há em cada município nem nomeia nenhuma [citação de mídia]. Litologia não informada nas reportagens. Esses números (mais de 40 estruturas; mais de duas mil no Brasil) não coincidem com o catálogo do artigo (24 no Geoparque) e os critérios de contagem das reportagens não foram conciliados. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Valores de Bechtel et al. (2023), dos resumos e do TCC da UDESC lidos em resumo da ferramenta de leitura, não nos PDFs: conferir nos originais antes de citar. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. FONTE MISTA (2026.10.09): a existência de paleotocas no Geoparque tem base em publicação — Valdati et al. (2024, Revista Brasileira de Geografia Física 17(3):1905–1920, DOI 10.26848/rbgf.v17.3.p1905-1920) catalogam paleotocas no território do Geoparque Caminhos dos Cânions do Sul (2.830 km², sete municípios: Timbé do Sul, Jacinto Machado, Praia Grande e Morro Grande, em SC, e três no RS) e descrevem três delas — duas nas Escarpas da Serra Geral, em Morro Grande (registros nº 259 e 260), e uma no Planalto dos Campos Gerais, em Cambará do Sul/RS (fora do escopo deste banco). Segundo o texto consultado, foram catalogadas 24 paleotocas no Geoparque, a maior parte das feições descritas até agora está em Morro Grande, e a Toca do Tatu (Timbé do Sul, registro nº 74) é tratada com base em Frank et al. (2012). O artigo não individualiza, no texto consultado, cavidades de Praia Grande. Um resumo expandido da UDESC (Bechtel &amp; Valdati, sem data na cópia consultada) informa que, de 17 paleotocas novas catalogadas, 16 estão em arenitos da Fm. Botucatu e uma em basalto intemperizado. CONTAGENS EM PUBLICAÇÕES (2026.10.09), por trabalho: 17 paleotocas — Bechtel et al. (2023, SINAGEO: 1 no Planalto da Serra Geral, 6 nos Patamares e 10 nas Escarpas; 16 em arenito da Fm. Botucatu e uma em basalto intemperizado, a «paleotoca do Parque»; altitude média de 382 m nas escarpas e de 87,5 m nos patamares) e um resumo da UDESC sem data (Bechtel &amp; Valdati, «Distribuição de paleotocas no território do Geoparque…»: 9 nas Escarpas, 4 nos Patamares, 2 na Planície colúvio-aluvionar e 1 no Planalto); 23 — Bechtel et al. (2023, Anais do Seminário de Pesquisas, vol. 2, p. 27: 1 no Planalto dos Campos Gerais, 9 nas Escarpas e 13 nos Patamares; 22 em Botucatu e uma em basalto; relatos de moradores sugerem que pode haver cerca do dobro) e o resumo da UDESC sem data «Registro da Megafauna do Quaternário…» (pelo menos 20 outras ainda sem visita); 24 — Valdati et al. (2024). O TCC de Bechtel (2022) nomeia só três no Geoparque (Aparência, Parque e Veisom), além de duas em Irineópolis, e cita a Toca do Tatu a partir de Frank et al. (2012). As contagens e as distribuições por compartimento são de épocas e critérios diferentes e não foram conciliadas; nenhuma é desagregada por município. Em Praia Grande, um relatório de iniciação científica da UDESC (Souza &amp; Valdati, sem ano na cópia consultada) descreve o complexo «Furnas do Itamar / Reserva Caeté» (campo em 19–23/03/2024: três paleotocas já conhecidas e oito novas, duas delas crotovinas — 11 feições), sem coordenadas nem dimensões no texto lido (ver registro nº 75). CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551), artigo de patrimônio cultural que não traz inventário de paleotocas, registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a Paleotoca Toca do Tatu (registro nº 74) e que o de Praia Grande não cita paleotocas (lista Pedra Branca, Cânion Itaimbezinho e Cânion Malacara); o de Jacinto Machado cita paleotocas ocupadas pelos Laklãnõ-Xokleng (registros nº 73 e 75). CITAÇÃO DE MÍDIA: os números e a localização em Praia Grande e Timbé do Sul, aqui, vêm de reportagens, não de publicação. O ND Mais (10/08/2025) informa 'mais de 40 estruturas escavadas por essa megafauna' identificadas na região, alguns túneis do Sul do estado com até 340 m e diâmetros de 0,7 a 4 m, extinção 'há mais de 10 mil anos' e nenhum fóssil associado às tocas. Segundo o Jornal da Unesp (18/01/2022), que relata declaração de F. S. C. Buchmann, há mais de duas mil paleotocas registradas no Brasil, 99% delas entre o sul de Santa Catarina e o norte do Rio Grande do Sul [citação de mídia]. A Revista Oeste (31/03/2026), ao tratar do túnel de Lauro Müller (registro nº 37), diz que o acervo do Geoparque soma cerca de 30 paleotocas registradas em Morro Grande, Jacinto Machado e Timbé do Sul; não informa quantas há em cada município nem nomeia nenhuma [citação de mídia]. Litologia não informada nas reportagens. Esses números (mais de 40 estruturas; mais de duas mil no Brasil) não coincidem com o catálogo do artigo (24 no Geoparque) e os critérios de contagem das reportagens não foram conciliados. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores do artigo lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Valores de Bechtel et al. (2023), dos resumos e do TCC da UDESC lidos em resumo da ferramenta de leitura, não nos PDFs: conferir nos originais antes de citar. </t>
         </is>
       </c>
       <c r="L254" s="5" t="inlineStr">
@@ -23080,7 +23080,7 @@
         </is>
       </c>
       <c r="N254" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="O255" s="6" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos). CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. ARTE RUPESTRE (2026.10.09): Cezaro, Santos &amp; Campos (2016, Revista Memorare 3(1):47–72) tratam a Toca do Tatu (Timbé do Sul) como caverna de 48,5 m com dois túneis, registrada pelo Projeto Paleotocas e descrita como abrigo «escavado provavelmente por preguiças gigantes durante o Cenozoico»; nas zonas iluminadas dos dois túneis há gravuras (não pinturas) que cobrem mais de 35 m², com sulcos finos de cerca de 5 mm e grafismos de mais de sete geometrias distintas, classificados pelos autores na Tradição Geométrica Meridional; a semelhança com motivos de pintura corporal de grupos Jê meridionais é, no artigo, uma hipótese interpretativa com ressalvas, não um achado. CONTEXTO CULTURAL (2026.10.09): Santos et al. (2024, Desenvolvimento Socioeconômico em Debate 10(1):86–104, DOI 10.18616/rdsd.v10i1.8551) — artigo de patrimônio cultural, não de paleontologia — registram que o Plano Municipal de Cultura de Timbé do Sul (2015) cita a «Paleotoca Toca do Tatu» e suas inscrições rupestres como sítios arqueológicos da região, e que a Toca do Tatu é um dos cinco geossítios catarinenses (de 23 catalogados pelo Geoparque) mencionados nos planos municipais; o artigo não traz dados paleontológicos sobre a cavidade. DADOS DO TEXTO DE FRANK ET AL. (2012) (2026.10.09): coordenada 28°46′21,2″S, 49°53′45,9″W; a caverna fica numa encosta íngreme voltada para SW, numa das «canhoneiras» do escarpamento da Serra Geral, a cerca de 100 m da margem esquerda do rio que corre no fundo do cânion e a 20–30 m acima do nível dele; planta em «U», com dois túneis quase paralelos (separados por menos de 3 m de rocha) que convergem para um salão; extensão total de 48,5 m; túnel norte quase retilíneo, com cerca de 4 m de largura na entrada (reduzida a ~2,6 m perto do salão) e ~2,0 m de altura; túnel sul em arco, com seção decrescente; salão com 1,48–2,86 m de altura; saída traseira com menos de 1,5 m de diâmetro; volume escavado superior a 100 m³ (mais de 200 t de arenito, segundo os autores); arenito eólico da Fm. Botucatu (Jurássico Superior–Cretáceo Inferior), coberto pelo basalto da Fm. Serra Geral; a dissolução é descartada (rocha não solúvel, sem sinais de drenagem subterrânea). Marcas de garras: sulcos largos (tipo C) de até ~5 cm de largura, ~6 cm de profundidade e ~50 cm de comprimento, até ~2,5 m de altura, na base das paredes dos dois túneis, e superfície contínua de marcas no salão. Grafismos de sulcos finos (tipo D), atribuídos a populações pré-coloniais, possivelmente do grupo Gê (Tradição Geométrica, Subtradição Morro do Avencal, segundo Prous, 1992): grades, radiais (as maiores com 1,0 e 1,2 m de diâmetro), ondulações angulares e cerca de uma dúzia de desenhos complexos, concentrados nos primeiros 11 m do túnel norte e cobrindo mais de 35 m² de paredes e teto (o resumo do texto fala em «mais de cinco geometrias»; Cezaro et al., 2016, em «mais de sete» — contagens não conciliadas). Escavação atribuída a preguiças-gigantes («possivelmente Scelidotherium, Mylodon, Glossotherium ou Lestodon»), em etapas; sem datação radiométrica — o limite inferior de idade é a extinção da megafauna, há cerca de 10 mil anos. Alterações posteriores: caçadores de tesouros (testemunhos locais os situam no início da década de 1970) removeram sedimentos e ampliaram entradas; visitantes deixaram 119 conjuntos de nomes, datas (1956–1991, entre outras) e símbolos nos primeiros 10 m do túnel norte; os autores recomendam interromper qualquer ação que possa destruir mais a caverna. O termo «baixos-relevos» da ficha anterior não aparece no resumo do texto consultado, que fala em sulcos finos (grafismos gravados): conferir no original. OUTRAS FONTES SOBRE A CAVIDADE (2026.10.09): o TCC de Provedan (2019, UDESC, Geografia) trata a Toca do Tatu como a única paleotoca que nomeia no município e a situa na comunidade que o texto grafa «Rochinha» (grafia a conferir; este banco usa «rio Rocinha», de Frank et al., 2012), a cerca de 7,5 km da sede; descreve dois túneis paralelos que convergem numa câmara maior, com cerca de 48,5 m (valor que o TCC atribui a Lima &amp; Vargas, 2018, trabalho não localizado), em arenito da Fm. Botucatu — rocha não solúvel, o que, segundo os autores, descarta a dissolução como origem. A dissertação de Miranda (2025, UNESC, Ciências Ambientais) mapeia a trilha Portal do Palmiro, que dá acesso à paleotoca, e calcula a capacidade de carga turística em 69 pessoas por dia (só o resumo foi lido). A página de geossítios do Geoparque dá 7,3 km do centro da cidade, trilha de cerca de 3,5 km (ida e volta) e guia obrigatório. Valdati et al. (2024) citam a Toca do Tatu como estudada por Frank et al. (2012) e, na discussão, listam «Tatu» — sem afirmar expressamente que seja esta cavidade — entre as exceções ao estado praticamente intocado das demais paleotocas do Geoparque (ver registro nº 81). A matéria de Rodrigues (2025, Nature 637:1036–1037, DOI 10.1038/d41586-025-00216-x) — texto jornalístico da seção de notícias, não artigo de pesquisa — chama a cavidade de «Toca do Tatu (Armadillo's Den)», diz que a entrada comporta uma van, que os sulcos do teto são atribuídos a preguiças-gigantes extintas há mais de 10 mil anos e que é uma das paleotocas mais bem preservadas do Brasil, embora coberta de grafites (Frank et al., 2012, descrevem danos e inscrições modernas), e cita um guia local segundo o qual uma gravura em zigue-zague representa o rio Rocinha; J. B. Campos (UNESC) a chama de «maravilha arqueológica e paleontológica». O nome «Rocinha» aparece, assim, ligado à cavidade em Provedan (comunidade «Rochinha») e na matéria da Nature (rio Rocinha, segundo o guia); o texto de Frank et al. não nomeia o rio, e Pontelli (1998, dissertação citada por Rapanos et al., 2022) registra um rio Rocinha em Timbé do Sul. O TCC de Bechtel (2022, UDESC) cita «a paleotoca do Tatu, no município de Timbé do Sul» como a estudada por Frank et al. (2012) e, no trecho lido, não traz paleotoca catalogada pelo autor nesse município. BUSCA DE OUTRAS PALEOTOCAS EM TIMBÉ DO SUL (2026.10.09): em artigos, teses, trabalhos de eventos, na página de geossítios do Geoparque e em reportagens não foi localizada nenhuma outra paleotoca nomeada no município; as reportagens consultadas (NSC Total, 14/09/2024; ND Mais, 22/02/2026 e 11/08/2025; Portal Tela, 28/01/2025) e a matéria da Nature (30/01/2025) tratam só da Toca do Tatu, e o TCC de Bechtel (2022) a cita como a única de Timbé do Sul. Isso não prova que não existam outras: as contagens do Geoparque (ver registro nº 38) não são desagregadas por município. CONTEXTO CIENTÍFICO (sobre o tipo de estrutura, não sobre este local): Lopes, Frank, Buchmann &amp; Caron (2017, Ichnos 24(2):133–145) erigiram o icnogênero Megaichnus (M. major, atribuído a preguiças-gigantes, Mylodontidae; M. minor, a tatus-gigantes, Cingulata); Buchmann, Lopes &amp; Caron (2009, Revista Brasileira de Paleontologia 12(3):247–256, DOI 10.4072/rbp.2009.3.07) tratam de paleotocas e crotovinas do sudeste e sul do Brasil. Valores de Cezaro et al. (2016) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar. Valores de Provedan (2019) lidos em resumo da ferramenta de leitura, não no PDF: conferir no original antes de citar (inclusive a grafia do nome do autor e da comunidade). Valores de Frank et al. (2012), do TCC de Bechtel (2022) e da matéria da Nature lidos em resumo da ferramenta de leitura, não nos PDFs: conferir nos originais antes de citar. </t>
+          <t xml:space="preserve">Classificação: paleotoca — estrutura de habitação (Domichnia) escavada por mamíferos da megafauna. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos). CORREÇÃO (2026.09.8): coordenada substituída pela publicada por Frank et al. (2012) — a anterior ficava a cerca de 6 km —, e a ficha passou a se apoiar no artigo que descreve a caverna. A página de geossítios do Geoparque confirma: 'paleotoca de 48,5 m desenvolvida nos arenitos da Formação Botucatu', em Timbé do Sul. ARTE RUPESTRE (2026.10.09): Cezaro, Santos &amp; Campos (2016, Revista Memorare 3(1):47–72) tratam a Toca do Tatu (Timbé do Sul) como caverna de 48,5 m com dois túneis, registrada pelo Projeto Paleotocas e descrita como abrigo «escavado provavelmente por preguiças gigantes durante o Cenozoico»; nas zonas iluminadas dos dois túneis há gravuras (não pinturas) que cobrem mais de 35 m², com sulcos finos de cerca de 5 mm e grafismos de mais de sete geometrias distintas, classificados pelos autores na Tradição Geométrica Meridional; a semelhança com motivos de pintura corporal de grupos Jê meridionais é, no artigo, uma hipótese interpretativa com ressalvas, não um achado.